--- a/NCAAF_Edge_Model.xlsx
+++ b/NCAAF_Edge_Model.xlsx
@@ -637,7 +637,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-21T04:30:02+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
+          <t>Generated 2026-08-21T04:59:28+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
         </is>
       </c>
     </row>
@@ -46301,7 +46301,7 @@
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>UNT @ IU</t>
+          <t>ECU @ ALA</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
@@ -46311,7 +46311,7 @@
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>UNT +40.5</t>
+          <t>ECU +28.5</t>
         </is>
       </c>
       <c r="E50" s="13" t="n">
@@ -46343,7 +46343,7 @@
         </is>
       </c>
       <c r="L50" s="14" t="n">
-        <v>0.2251</v>
+        <v>0.2175</v>
       </c>
       <c r="M50" s="14" t="n"/>
       <c r="N50" s="12" t="n"/>
@@ -46361,7 +46361,7 @@
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>ECU @ ALA</t>
+          <t>UNT @ IU</t>
         </is>
       </c>
       <c r="C51" s="17" t="inlineStr">
@@ -46371,7 +46371,7 @@
       </c>
       <c r="D51" s="17" t="inlineStr">
         <is>
-          <t>ECU +28.5</t>
+          <t>UNT +40.5</t>
         </is>
       </c>
       <c r="E51" s="18" t="n">
@@ -46403,7 +46403,7 @@
         </is>
       </c>
       <c r="L51" s="19" t="n">
-        <v>0.2175</v>
+        <v>0.2251</v>
       </c>
       <c r="M51" s="19" t="n"/>
       <c r="N51" s="17" t="n"/>

--- a/NCAAF_Edge_Model.xlsx
+++ b/NCAAF_Edge_Model.xlsx
@@ -637,7 +637,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-21T04:59:28+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
+          <t>Generated 2026-08-21T14:58:27+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
         </is>
       </c>
     </row>

--- a/NCAAF_Edge_Model.xlsx
+++ b/NCAAF_Edge_Model.xlsx
@@ -637,7 +637,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-21T14:58:27+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
+          <t>Generated 2026-08-21T18:01:28+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="P10" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q10" s="17" t="n"/>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="P12" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q12" s="17" t="n"/>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="P110" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q110" s="17" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="P124" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q124" s="17" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="P148" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q148" s="17" t="inlineStr">
@@ -11201,7 +11201,7 @@
       </c>
       <c r="P149" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q149" s="12" t="inlineStr">
@@ -11532,7 +11532,7 @@
       </c>
       <c r="P154" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q154" s="17" t="n"/>
@@ -12611,7 +12611,7 @@
       </c>
       <c r="P171" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q171" s="12" t="n"/>
@@ -14718,7 +14718,7 @@
       </c>
       <c r="P204" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q204" s="17" t="n"/>
@@ -15671,7 +15671,7 @@
       </c>
       <c r="P219" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q219" s="12" t="n"/>
@@ -16305,7 +16305,7 @@
       </c>
       <c r="P229" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q229" s="12" t="n"/>
@@ -16683,7 +16683,7 @@
       </c>
       <c r="P235" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q235" s="12" t="n"/>
@@ -17191,7 +17191,7 @@
       </c>
       <c r="P243" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q243" s="12" t="n"/>
@@ -18396,7 +18396,7 @@
       </c>
       <c r="P262" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q262" s="17" t="n"/>
@@ -18593,7 +18593,7 @@
       </c>
       <c r="P265" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q265" s="12" t="n"/>
@@ -19806,7 +19806,7 @@
       </c>
       <c r="P284" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q284" s="17" t="n"/>
@@ -25611,7 +25611,7 @@
       </c>
       <c r="P375" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q375" s="12" t="n"/>
@@ -26824,7 +26824,7 @@
       </c>
       <c r="P394" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q394" s="17" t="n"/>
@@ -27021,7 +27021,7 @@
       </c>
       <c r="P397" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q397" s="12" t="n"/>
@@ -28226,7 +28226,7 @@
       </c>
       <c r="P416" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q416" s="17" t="n"/>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="P424" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q424" s="17" t="n"/>
@@ -29112,7 +29112,7 @@
       </c>
       <c r="P430" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q430" s="17" t="n"/>
@@ -29746,7 +29746,7 @@
       </c>
       <c r="P440" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q440" s="17" t="n"/>
@@ -30699,7 +30699,7 @@
       </c>
       <c r="P455" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q455" s="12" t="n"/>
@@ -32806,7 +32806,7 @@
       </c>
       <c r="P488" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q488" s="17" t="n"/>
@@ -33885,7 +33885,7 @@
       </c>
       <c r="P505" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q505" s="12" t="n"/>
@@ -34145,7 +34145,7 @@
       </c>
       <c r="P509" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q509" s="12" t="n"/>
@@ -34334,7 +34334,7 @@
       </c>
       <c r="P512" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q512" s="17" t="n"/>
@@ -36512,7 +36512,7 @@
       </c>
       <c r="P546" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q546" s="17" t="n"/>
@@ -37993,7 +37993,7 @@
       </c>
       <c r="P569" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q569" s="12" t="n"/>
@@ -41601,7 +41601,7 @@
       </c>
       <c r="P625" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q625" s="12" t="n"/>
@@ -41928,7 +41928,7 @@
       </c>
       <c r="P630" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q630" s="17" t="n"/>
@@ -53377,7 +53377,7 @@
       <c r="L5" s="13" t="n"/>
       <c r="M5" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>
@@ -53422,7 +53422,7 @@
       <c r="L6" s="18" t="n"/>
       <c r="M6" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>
@@ -53467,7 +53467,7 @@
       <c r="L7" s="13" t="n"/>
       <c r="M7" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>
@@ -53512,7 +53512,7 @@
       <c r="L8" s="18" t="n"/>
       <c r="M8" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>
@@ -53557,7 +53557,7 @@
       <c r="L9" s="13" t="n"/>
       <c r="M9" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>
@@ -53602,7 +53602,7 @@
       <c r="L10" s="18" t="n"/>
       <c r="M10" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>
@@ -53647,7 +53647,7 @@
       <c r="L11" s="13" t="n"/>
       <c r="M11" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>
@@ -53692,7 +53692,7 @@
       <c r="L12" s="18" t="n"/>
       <c r="M12" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>

--- a/NCAAF_Edge_Model.xlsx
+++ b/NCAAF_Edge_Model.xlsx
@@ -637,7 +637,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-21T18:01:28+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
+          <t>Generated 2026-08-21T21:54:35+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
         </is>
       </c>
     </row>
@@ -18543,12 +18543,12 @@
       </c>
       <c r="B265" s="12" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>FAU @ FLA</t>
         </is>
       </c>
       <c r="C265" s="12" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-09-05 23:45</t>
         </is>
       </c>
       <c r="D265" s="22" t="n">
@@ -18561,17 +18561,17 @@
       </c>
       <c r="F265" s="12" t="inlineStr">
         <is>
-          <t>Over 56.5</t>
+          <t>Under 58.5</t>
         </is>
       </c>
       <c r="G265" s="23" t="n">
-        <v>56.5</v>
+        <v>58.5</v>
       </c>
       <c r="H265" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I265" s="15" t="n">
-        <v>0.5298211850615678</v>
+        <v>0.5298211834152686</v>
       </c>
       <c r="J265" s="15" t="n">
         <v>0.5</v>
@@ -18580,10 +18580,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L265" s="14" t="n">
-        <v>0.006011661252043998</v>
+        <v>0.00601165960574479</v>
       </c>
       <c r="M265" s="14" t="n">
-        <v>0.01147680784481137</v>
+        <v>0.01147680470187651</v>
       </c>
       <c r="N265" s="15" t="n">
         <v>0</v>
@@ -18606,16 +18606,16 @@
       </c>
       <c r="B266" s="17" t="inlineStr">
         <is>
-          <t>FAU @ FLA</t>
+          <t>WASH @ ORE</t>
         </is>
       </c>
       <c r="C266" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:45</t>
+          <t>2026-11-28 05:00</t>
         </is>
       </c>
       <c r="D266" s="25" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E266" s="17" t="inlineStr">
         <is>
@@ -18624,17 +18624,17 @@
       </c>
       <c r="F266" s="17" t="inlineStr">
         <is>
-          <t>Under 58.5</t>
+          <t>Over 54.5</t>
         </is>
       </c>
       <c r="G266" s="26" t="n">
-        <v>58.5</v>
+        <v>54.5</v>
       </c>
       <c r="H266" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I266" s="20" t="n">
-        <v>0.5298211834152686</v>
+        <v>0.5278465371051131</v>
       </c>
       <c r="J266" s="20" t="n">
         <v>0.5</v>
@@ -18643,10 +18643,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L266" s="19" t="n">
-        <v>0.00601165960574479</v>
+        <v>0.004037013295589253</v>
       </c>
       <c r="M266" s="19" t="n">
-        <v>0.01147680470187651</v>
+        <v>0.007707025382488686</v>
       </c>
       <c r="N266" s="20" t="n">
         <v>0</v>
@@ -18669,16 +18669,16 @@
       </c>
       <c r="B267" s="12" t="inlineStr">
         <is>
-          <t>WASH @ ORE</t>
+          <t>ULM @ MSST</t>
         </is>
       </c>
       <c r="C267" s="12" t="inlineStr">
         <is>
-          <t>2026-11-28 05:00</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D267" s="22" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E267" s="12" t="inlineStr">
         <is>
@@ -18687,17 +18687,17 @@
       </c>
       <c r="F267" s="12" t="inlineStr">
         <is>
-          <t>Over 54.5</t>
+          <t>Over 55.5</t>
         </is>
       </c>
       <c r="G267" s="23" t="n">
-        <v>54.5</v>
+        <v>55.5</v>
       </c>
       <c r="H267" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I267" s="15" t="n">
-        <v>0.5278465371051131</v>
+        <v>0.5278465360715345</v>
       </c>
       <c r="J267" s="15" t="n">
         <v>0.5</v>
@@ -18706,10 +18706,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L267" s="14" t="n">
-        <v>0.004037013295589253</v>
+        <v>0.004037012262010697</v>
       </c>
       <c r="M267" s="14" t="n">
-        <v>0.007707025382488686</v>
+        <v>0.007707023409293245</v>
       </c>
       <c r="N267" s="15" t="n">
         <v>0</v>
@@ -18732,12 +18732,12 @@
       </c>
       <c r="B268" s="17" t="inlineStr">
         <is>
-          <t>ULM @ MSST</t>
+          <t>IDHO @ UTAH</t>
         </is>
       </c>
       <c r="C268" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D268" s="25" t="n">
@@ -18750,17 +18750,17 @@
       </c>
       <c r="F268" s="17" t="inlineStr">
         <is>
-          <t>Over 55.5</t>
+          <t>Over 56.5</t>
         </is>
       </c>
       <c r="G268" s="26" t="n">
-        <v>55.5</v>
+        <v>56.5</v>
       </c>
       <c r="H268" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I268" s="20" t="n">
-        <v>0.5278465360715345</v>
+        <v>0.5278465354893196</v>
       </c>
       <c r="J268" s="20" t="n">
         <v>0.5</v>
@@ -18769,10 +18769,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L268" s="19" t="n">
-        <v>0.004037012262010697</v>
+        <v>0.004037011679795754</v>
       </c>
       <c r="M268" s="19" t="n">
-        <v>0.007707023409293245</v>
+        <v>0.007707022297791966</v>
       </c>
       <c r="N268" s="20" t="n">
         <v>0</v>
@@ -18785,7 +18785,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q268" s="17" t="n"/>
+      <c r="Q268" s="17" t="inlineStr">
+        <is>
+          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="12" t="inlineStr">
@@ -18795,16 +18799,16 @@
       </c>
       <c r="B269" s="12" t="inlineStr">
         <is>
-          <t>IDHO @ UTAH</t>
+          <t>TEX @ LSU</t>
         </is>
       </c>
       <c r="C269" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 01:00</t>
+          <t>2026-11-14 05:00</t>
         </is>
       </c>
       <c r="D269" s="22" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E269" s="12" t="inlineStr">
         <is>
@@ -18813,17 +18817,17 @@
       </c>
       <c r="F269" s="12" t="inlineStr">
         <is>
-          <t>Over 56.5</t>
+          <t>Under 54.5</t>
         </is>
       </c>
       <c r="G269" s="23" t="n">
-        <v>56.5</v>
+        <v>54.5</v>
       </c>
       <c r="H269" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I269" s="15" t="n">
-        <v>0.5278465354893196</v>
+        <v>0.5278465256441186</v>
       </c>
       <c r="J269" s="15" t="n">
         <v>0.5</v>
@@ -18832,10 +18836,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L269" s="14" t="n">
-        <v>0.004037011679795754</v>
+        <v>0.004037001834594767</v>
       </c>
       <c r="M269" s="14" t="n">
-        <v>0.007707022297791966</v>
+        <v>0.007707003502408272</v>
       </c>
       <c r="N269" s="15" t="n">
         <v>0</v>
@@ -18848,11 +18852,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q269" s="12" t="inlineStr">
-        <is>
-          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q269" s="12" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="17" t="inlineStr">
@@ -18862,35 +18862,35 @@
       </c>
       <c r="B270" s="17" t="inlineStr">
         <is>
-          <t>TEX @ LSU</t>
+          <t>NAVY @ ARMY</t>
         </is>
       </c>
       <c r="C270" s="17" t="inlineStr">
         <is>
-          <t>2026-11-14 05:00</t>
+          <t>2026-12-12 20:00</t>
         </is>
       </c>
       <c r="D270" s="25" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E270" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F270" s="17" t="inlineStr">
         <is>
-          <t>Under 54.5</t>
+          <t>ARMY +2.5</t>
         </is>
       </c>
       <c r="G270" s="26" t="n">
-        <v>54.5</v>
+        <v>2.5</v>
       </c>
       <c r="H270" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I270" s="20" t="n">
-        <v>0.5278465256441186</v>
+        <v>0.527327071096132</v>
       </c>
       <c r="J270" s="20" t="n">
         <v>0.5</v>
@@ -18899,10 +18899,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L270" s="19" t="n">
-        <v>0.004037001834594767</v>
+        <v>0.003517547286608136</v>
       </c>
       <c r="M270" s="19" t="n">
-        <v>0.007707003502408272</v>
+        <v>0.006715317547161093</v>
       </c>
       <c r="N270" s="20" t="n">
         <v>0</v>
@@ -18925,16 +18925,16 @@
       </c>
       <c r="B271" s="12" t="inlineStr">
         <is>
-          <t>NAVY @ ARMY</t>
+          <t>UVA @ VT</t>
         </is>
       </c>
       <c r="C271" s="12" t="inlineStr">
         <is>
-          <t>2026-12-12 20:00</t>
+          <t>2026-11-28 05:00</t>
         </is>
       </c>
       <c r="D271" s="22" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E271" s="12" t="inlineStr">
         <is>
@@ -18943,17 +18943,17 @@
       </c>
       <c r="F271" s="12" t="inlineStr">
         <is>
-          <t>ARMY +2.5</t>
+          <t>UVA +1.5</t>
         </is>
       </c>
       <c r="G271" s="23" t="n">
-        <v>2.5</v>
+        <v>-1.5</v>
       </c>
       <c r="H271" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I271" s="15" t="n">
-        <v>0.527327071096132</v>
+        <v>0.5262747671380312</v>
       </c>
       <c r="J271" s="15" t="n">
         <v>0.5</v>
@@ -18962,10 +18962,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L271" s="14" t="n">
-        <v>0.003517547286608136</v>
+        <v>0.002465243328507394</v>
       </c>
       <c r="M271" s="14" t="n">
-        <v>0.006715317547161093</v>
+        <v>0.004706373627150595</v>
       </c>
       <c r="N271" s="15" t="n">
         <v>0</v>
@@ -18988,35 +18988,35 @@
       </c>
       <c r="B272" s="17" t="inlineStr">
         <is>
-          <t>UVA @ VT</t>
+          <t>VMI @ VT</t>
         </is>
       </c>
       <c r="C272" s="17" t="inlineStr">
         <is>
-          <t>2026-11-28 05:00</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D272" s="25" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E272" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F272" s="17" t="inlineStr">
         <is>
-          <t>UVA +1.5</t>
+          <t>Under 57.5</t>
         </is>
       </c>
       <c r="G272" s="26" t="n">
-        <v>-1.5</v>
+        <v>57.5</v>
       </c>
       <c r="H272" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I272" s="20" t="n">
-        <v>0.5262747671380312</v>
+        <v>0.5258691148547187</v>
       </c>
       <c r="J272" s="20" t="n">
         <v>0.5</v>
@@ -19025,10 +19025,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L272" s="19" t="n">
-        <v>0.002465243328507394</v>
+        <v>0.00205959104519482</v>
       </c>
       <c r="M272" s="19" t="n">
-        <v>0.004706373627150595</v>
+        <v>0.00393194654082657</v>
       </c>
       <c r="N272" s="20" t="n">
         <v>0</v>
@@ -19041,7 +19041,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q272" s="17" t="n"/>
+      <c r="Q272" s="17" t="inlineStr">
+        <is>
+          <t>VMI isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="12" t="inlineStr">
@@ -19051,16 +19055,16 @@
       </c>
       <c r="B273" s="12" t="inlineStr">
         <is>
-          <t>VMI @ VT</t>
+          <t>NCSU @ UNC</t>
         </is>
       </c>
       <c r="C273" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-11-28 05:00</t>
         </is>
       </c>
       <c r="D273" s="22" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E273" s="12" t="inlineStr">
         <is>
@@ -19069,17 +19073,17 @@
       </c>
       <c r="F273" s="12" t="inlineStr">
         <is>
-          <t>Under 57.5</t>
+          <t>Under 55.5</t>
         </is>
       </c>
       <c r="G273" s="23" t="n">
-        <v>57.5</v>
+        <v>55.5</v>
       </c>
       <c r="H273" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I273" s="15" t="n">
-        <v>0.5258691148547187</v>
+        <v>0.5258691114540864</v>
       </c>
       <c r="J273" s="15" t="n">
         <v>0.5</v>
@@ -19088,10 +19092,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L273" s="14" t="n">
-        <v>0.00205959104519482</v>
+        <v>0.002059587644562599</v>
       </c>
       <c r="M273" s="14" t="n">
-        <v>0.00393194654082657</v>
+        <v>0.003931940048710503</v>
       </c>
       <c r="N273" s="15" t="n">
         <v>0</v>
@@ -19104,11 +19108,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q273" s="12" t="inlineStr">
-        <is>
-          <t>VMI isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q273" s="12" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="17" t="inlineStr">
@@ -19118,7 +19118,7 @@
       </c>
       <c r="B274" s="17" t="inlineStr">
         <is>
-          <t>NCSU @ UNC</t>
+          <t>ASU @ ARIZ</t>
         </is>
       </c>
       <c r="C274" s="17" t="inlineStr">
@@ -19131,22 +19131,22 @@
       </c>
       <c r="E274" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F274" s="17" t="inlineStr">
         <is>
-          <t>Under 55.5</t>
+          <t>ASU +4.5</t>
         </is>
       </c>
       <c r="G274" s="26" t="n">
-        <v>55.5</v>
+        <v>-4.5</v>
       </c>
       <c r="H274" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I274" s="20" t="n">
-        <v>0.5258691114540864</v>
+        <v>0.5240821001886855</v>
       </c>
       <c r="J274" s="20" t="n">
         <v>0.5</v>
@@ -19155,10 +19155,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L274" s="19" t="n">
-        <v>0.002059587644562599</v>
+        <v>0.0002725763791616709</v>
       </c>
       <c r="M274" s="19" t="n">
-        <v>0.003931940048710503</v>
+        <v>0.0005203730874905332</v>
       </c>
       <c r="N274" s="20" t="n">
         <v>0</v>
@@ -19181,35 +19181,35 @@
       </c>
       <c r="B275" s="12" t="inlineStr">
         <is>
-          <t>ASU @ ARIZ</t>
+          <t>KENT @ SC</t>
         </is>
       </c>
       <c r="C275" s="12" t="inlineStr">
         <is>
-          <t>2026-11-28 05:00</t>
+          <t>2026-09-05 16:45</t>
         </is>
       </c>
       <c r="D275" s="22" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E275" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F275" s="12" t="inlineStr">
         <is>
-          <t>ASU +4.5</t>
+          <t>Over 53.5</t>
         </is>
       </c>
       <c r="G275" s="23" t="n">
-        <v>-4.5</v>
+        <v>53.5</v>
       </c>
       <c r="H275" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I275" s="15" t="n">
-        <v>0.5240821001886855</v>
+        <v>0.5238891282317109</v>
       </c>
       <c r="J275" s="15" t="n">
         <v>0.5</v>
@@ -19218,10 +19218,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L275" s="14" t="n">
-        <v>0.0002725763791616709</v>
+        <v>7.960442218701846e-05</v>
       </c>
       <c r="M275" s="14" t="n">
-        <v>0.0005203730874905332</v>
+        <v>0.0001519720787207524</v>
       </c>
       <c r="N275" s="15" t="n">
         <v>0</v>
@@ -19244,16 +19244,16 @@
       </c>
       <c r="B276" s="17" t="inlineStr">
         <is>
-          <t>KENT @ SC</t>
+          <t>ALA @ TENN</t>
         </is>
       </c>
       <c r="C276" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 16:45</t>
+          <t>2026-10-17 04:00</t>
         </is>
       </c>
       <c r="D276" s="25" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E276" s="17" t="inlineStr">
         <is>
@@ -19262,17 +19262,17 @@
       </c>
       <c r="F276" s="17" t="inlineStr">
         <is>
-          <t>Over 53.5</t>
+          <t>Over 56.5</t>
         </is>
       </c>
       <c r="G276" s="26" t="n">
-        <v>53.5</v>
+        <v>56.5</v>
       </c>
       <c r="H276" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I276" s="20" t="n">
-        <v>0.5238891282317109</v>
+        <v>0.523889124443805</v>
       </c>
       <c r="J276" s="20" t="n">
         <v>0.5</v>
@@ -19281,16 +19281,16 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L276" s="19" t="n">
-        <v>7.960442218701846e-05</v>
+        <v>7.960063428114061e-05</v>
       </c>
       <c r="M276" s="19" t="n">
-        <v>0.0001519720787207524</v>
+        <v>0.0001519648472640966</v>
       </c>
       <c r="N276" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O276" s="27" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="P276" s="17" t="inlineStr">
         <is>
@@ -19307,16 +19307,16 @@
       </c>
       <c r="B277" s="12" t="inlineStr">
         <is>
-          <t>ALA @ TENN</t>
+          <t>ORE @ USC</t>
         </is>
       </c>
       <c r="C277" s="12" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00</t>
+          <t>2026-09-26 04:00</t>
         </is>
       </c>
       <c r="D277" s="22" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E277" s="12" t="inlineStr">
         <is>
@@ -19325,17 +19325,17 @@
       </c>
       <c r="F277" s="12" t="inlineStr">
         <is>
-          <t>Over 56.5</t>
+          <t>Under 58.5</t>
         </is>
       </c>
       <c r="G277" s="23" t="n">
-        <v>56.5</v>
+        <v>58.5</v>
       </c>
       <c r="H277" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I277" s="15" t="n">
-        <v>0.523889124443805</v>
+        <v>0.5238891228171049</v>
       </c>
       <c r="J277" s="15" t="n">
         <v>0.5</v>
@@ -19344,16 +19344,16 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L277" s="14" t="n">
-        <v>7.960063428114061e-05</v>
+        <v>7.959900758103267e-05</v>
       </c>
       <c r="M277" s="14" t="n">
-        <v>0.0001519648472640966</v>
+        <v>0.0001519617417456987</v>
       </c>
       <c r="N277" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O277" s="24" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="P277" s="12" t="inlineStr">
         <is>
@@ -19370,16 +19370,16 @@
       </c>
       <c r="B278" s="17" t="inlineStr">
         <is>
-          <t>ORE @ USC</t>
+          <t>TNST @ UGA</t>
         </is>
       </c>
       <c r="C278" s="17" t="inlineStr">
         <is>
-          <t>2026-09-26 04:00</t>
+          <t>2026-09-05 19:00</t>
         </is>
       </c>
       <c r="D278" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E278" s="17" t="inlineStr">
         <is>
@@ -19388,17 +19388,17 @@
       </c>
       <c r="F278" s="17" t="inlineStr">
         <is>
-          <t>Under 58.5</t>
+          <t>Under 56.5</t>
         </is>
       </c>
       <c r="G278" s="26" t="n">
-        <v>58.5</v>
+        <v>56.5</v>
       </c>
       <c r="H278" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I278" s="20" t="n">
-        <v>0.5238891228171049</v>
+        <v>0.5238891209664566</v>
       </c>
       <c r="J278" s="20" t="n">
         <v>0.5</v>
@@ -19407,10 +19407,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L278" s="19" t="n">
-        <v>7.959900758103267e-05</v>
+        <v>7.959715693273139e-05</v>
       </c>
       <c r="M278" s="19" t="n">
-        <v>0.0001519617417456987</v>
+        <v>0.0001519582086898508</v>
       </c>
       <c r="N278" s="20" t="n">
         <v>0</v>
@@ -19423,7 +19423,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q278" s="17" t="n"/>
+      <c r="Q278" s="17" t="inlineStr">
+        <is>
+          <t>TNST isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="12" t="inlineStr">
@@ -19433,16 +19437,16 @@
       </c>
       <c r="B279" s="12" t="inlineStr">
         <is>
-          <t>TNST @ UGA</t>
+          <t>SC @ CLEM</t>
         </is>
       </c>
       <c r="C279" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 19:00</t>
+          <t>2026-11-28 05:00</t>
         </is>
       </c>
       <c r="D279" s="22" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E279" s="12" t="inlineStr">
         <is>
@@ -19451,17 +19455,17 @@
       </c>
       <c r="F279" s="12" t="inlineStr">
         <is>
-          <t>Under 56.5</t>
+          <t>Under 53.5</t>
         </is>
       </c>
       <c r="G279" s="23" t="n">
-        <v>56.5</v>
+        <v>53.5</v>
       </c>
       <c r="H279" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I279" s="15" t="n">
-        <v>0.5238891209664566</v>
+        <v>0.5238891092187401</v>
       </c>
       <c r="J279" s="15" t="n">
         <v>0.5</v>
@@ -19470,10 +19474,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L279" s="14" t="n">
-        <v>7.959715693273139e-05</v>
+        <v>7.958540921626511e-05</v>
       </c>
       <c r="M279" s="14" t="n">
-        <v>0.0001519582086898508</v>
+        <v>0.0001519357812311273</v>
       </c>
       <c r="N279" s="15" t="n">
         <v>0</v>
@@ -19486,11 +19490,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q279" s="12" t="inlineStr">
-        <is>
-          <t>TNST isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q279" s="12" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="17" t="inlineStr">
@@ -19500,16 +19500,16 @@
       </c>
       <c r="B280" s="17" t="inlineStr">
         <is>
-          <t>SC @ CLEM</t>
+          <t>OU @ UGA</t>
         </is>
       </c>
       <c r="C280" s="17" t="inlineStr">
         <is>
-          <t>2026-11-28 05:00</t>
+          <t>2026-09-26 04:00</t>
         </is>
       </c>
       <c r="D280" s="25" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E280" s="17" t="inlineStr">
         <is>
@@ -19518,17 +19518,17 @@
       </c>
       <c r="F280" s="17" t="inlineStr">
         <is>
-          <t>Under 53.5</t>
+          <t>Under 52.5</t>
         </is>
       </c>
       <c r="G280" s="26" t="n">
-        <v>53.5</v>
+        <v>52.5</v>
       </c>
       <c r="H280" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I280" s="20" t="n">
-        <v>0.5238891092187401</v>
+        <v>0.5238890988524141</v>
       </c>
       <c r="J280" s="20" t="n">
         <v>0.5</v>
@@ -19537,10 +19537,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L280" s="19" t="n">
-        <v>7.958540921626511e-05</v>
+        <v>7.957504289024531e-05</v>
       </c>
       <c r="M280" s="19" t="n">
-        <v>0.0001519357812311273</v>
+        <v>0.0001519159909723622</v>
       </c>
       <c r="N280" s="20" t="n">
         <v>0</v>
@@ -19563,16 +19563,16 @@
       </c>
       <c r="B281" s="12" t="inlineStr">
         <is>
-          <t>OU @ UGA</t>
+          <t>UTU @ BYU</t>
         </is>
       </c>
       <c r="C281" s="12" t="inlineStr">
         <is>
-          <t>2026-09-26 04:00</t>
+          <t>2026-09-06 00:00</t>
         </is>
       </c>
       <c r="D281" s="22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E281" s="12" t="inlineStr">
         <is>
@@ -19581,17 +19581,17 @@
       </c>
       <c r="F281" s="12" t="inlineStr">
         <is>
-          <t>Under 52.5</t>
+          <t>Over 54.5</t>
         </is>
       </c>
       <c r="G281" s="23" t="n">
-        <v>52.5</v>
+        <v>54.5</v>
       </c>
       <c r="H281" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I281" s="15" t="n">
-        <v>0.5238890988524141</v>
+        <v>0.5219067541972648</v>
       </c>
       <c r="J281" s="15" t="n">
         <v>0.5</v>
@@ -19600,23 +19600,27 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L281" s="14" t="n">
-        <v>7.957504289024531e-05</v>
+        <v>-0.001902769612258992</v>
       </c>
       <c r="M281" s="14" t="n">
-        <v>0.0001519159909723622</v>
+        <v>-0.00363256016885799</v>
       </c>
       <c r="N281" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O281" s="24" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="P281" s="12" t="inlineStr">
         <is>
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q281" s="12" t="n"/>
+      <c r="Q281" s="12" t="inlineStr">
+        <is>
+          <t>UTU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="17" t="inlineStr">
@@ -19626,16 +19630,16 @@
       </c>
       <c r="B282" s="17" t="inlineStr">
         <is>
-          <t>UTU @ BYU</t>
+          <t>TA&amp;M @ OU</t>
         </is>
       </c>
       <c r="C282" s="17" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00</t>
+          <t>2026-11-21 05:00</t>
         </is>
       </c>
       <c r="D282" s="25" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E282" s="17" t="inlineStr">
         <is>
@@ -19644,17 +19648,17 @@
       </c>
       <c r="F282" s="17" t="inlineStr">
         <is>
-          <t>Over 54.5</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="G282" s="26" t="n">
-        <v>54.5</v>
+        <v>51.5</v>
       </c>
       <c r="H282" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I282" s="20" t="n">
-        <v>0.5219067541972648</v>
+        <v>0.5199222111459331</v>
       </c>
       <c r="J282" s="20" t="n">
         <v>0.5</v>
@@ -19663,27 +19667,23 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L282" s="19" t="n">
-        <v>-0.001902769612258992</v>
+        <v>-0.00388731266359077</v>
       </c>
       <c r="M282" s="19" t="n">
-        <v>-0.00363256016885799</v>
+        <v>-0.00742123326685501</v>
       </c>
       <c r="N282" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O282" s="27" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="P282" s="17" t="inlineStr">
         <is>
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q282" s="17" t="inlineStr">
-        <is>
-          <t>UTU isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q282" s="17" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="12" t="inlineStr">
@@ -19693,16 +19693,16 @@
       </c>
       <c r="B283" s="12" t="inlineStr">
         <is>
-          <t>TA&amp;M @ OU</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C283" s="12" t="inlineStr">
         <is>
-          <t>2026-11-21 05:00</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D283" s="22" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E283" s="12" t="inlineStr">
         <is>
@@ -19711,17 +19711,17 @@
       </c>
       <c r="F283" s="12" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>Over 53.5</t>
         </is>
       </c>
       <c r="G283" s="23" t="n">
-        <v>51.5</v>
+        <v>53.5</v>
       </c>
       <c r="H283" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I283" s="15" t="n">
-        <v>0.5199222111459331</v>
+        <v>0.5199222007643431</v>
       </c>
       <c r="J283" s="15" t="n">
         <v>0.5</v>
@@ -19730,10 +19730,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L283" s="14" t="n">
-        <v>-0.00388731266359077</v>
+        <v>-0.003887323045180691</v>
       </c>
       <c r="M283" s="14" t="n">
-        <v>-0.00742123326685501</v>
+        <v>-0.007421253086253965</v>
       </c>
       <c r="N283" s="15" t="n">
         <v>0</v>
@@ -19756,12 +19756,12 @@
       </c>
       <c r="B284" s="17" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>UAB @ ILL</t>
         </is>
       </c>
       <c r="C284" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D284" s="25" t="n">
@@ -19774,17 +19774,17 @@
       </c>
       <c r="F284" s="17" t="inlineStr">
         <is>
-          <t>Over 53.5</t>
+          <t>Over 56.5</t>
         </is>
       </c>
       <c r="G284" s="26" t="n">
-        <v>53.5</v>
+        <v>56.5</v>
       </c>
       <c r="H284" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I284" s="20" t="n">
-        <v>0.5199222007643431</v>
+        <v>0.51992219658688</v>
       </c>
       <c r="J284" s="20" t="n">
         <v>0.5</v>
@@ -19793,10 +19793,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L284" s="19" t="n">
-        <v>-0.003887323045180691</v>
+        <v>-0.003887327222643844</v>
       </c>
       <c r="M284" s="19" t="n">
-        <v>-0.007421253086253965</v>
+        <v>-0.007421261061410889</v>
       </c>
       <c r="N284" s="20" t="n">
         <v>0</v>
@@ -19819,16 +19819,16 @@
       </c>
       <c r="B285" s="12" t="inlineStr">
         <is>
-          <t>UAB @ ILL</t>
+          <t>OSU @ USC</t>
         </is>
       </c>
       <c r="C285" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 01:00</t>
+          <t>2026-10-31 04:00</t>
         </is>
       </c>
       <c r="D285" s="22" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E285" s="12" t="inlineStr">
         <is>
@@ -19837,17 +19837,17 @@
       </c>
       <c r="F285" s="12" t="inlineStr">
         <is>
-          <t>Over 56.5</t>
+          <t>Under 54.5</t>
         </is>
       </c>
       <c r="G285" s="23" t="n">
-        <v>56.5</v>
+        <v>54.5</v>
       </c>
       <c r="H285" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I285" s="15" t="n">
-        <v>0.51992219658688</v>
+        <v>0.5199221881338678</v>
       </c>
       <c r="J285" s="15" t="n">
         <v>0.5</v>
@@ -19856,10 +19856,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L285" s="14" t="n">
-        <v>-0.003887327222643844</v>
+        <v>-0.003887335675656023</v>
       </c>
       <c r="M285" s="14" t="n">
-        <v>-0.007421261061410889</v>
+        <v>-0.007421277198979614</v>
       </c>
       <c r="N285" s="15" t="n">
         <v>0</v>
@@ -19882,16 +19882,16 @@
       </c>
       <c r="B286" s="17" t="inlineStr">
         <is>
-          <t>OSU @ USC</t>
+          <t>MISS @ OU</t>
         </is>
       </c>
       <c r="C286" s="17" t="inlineStr">
         <is>
-          <t>2026-10-31 04:00</t>
+          <t>2026-11-14 05:00</t>
         </is>
       </c>
       <c r="D286" s="25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E286" s="17" t="inlineStr">
         <is>
@@ -19900,17 +19900,17 @@
       </c>
       <c r="F286" s="17" t="inlineStr">
         <is>
-          <t>Under 54.5</t>
+          <t>Over 53.5</t>
         </is>
       </c>
       <c r="G286" s="26" t="n">
-        <v>54.5</v>
+        <v>53.5</v>
       </c>
       <c r="H286" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I286" s="20" t="n">
-        <v>0.5199221881338678</v>
+        <v>0.5179356580520053</v>
       </c>
       <c r="J286" s="20" t="n">
         <v>0.5</v>
@@ -19919,10 +19919,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L286" s="19" t="n">
-        <v>-0.003887335675656023</v>
+        <v>-0.005873865757518582</v>
       </c>
       <c r="M286" s="19" t="n">
-        <v>-0.007421277198979614</v>
+        <v>-0.01121374371889899</v>
       </c>
       <c r="N286" s="20" t="n">
         <v>0</v>
@@ -19945,16 +19945,16 @@
       </c>
       <c r="B287" s="12" t="inlineStr">
         <is>
-          <t>MISS @ OU</t>
+          <t>USC @ UCLA</t>
         </is>
       </c>
       <c r="C287" s="12" t="inlineStr">
         <is>
-          <t>2026-11-14 05:00</t>
+          <t>2026-11-28 05:00</t>
         </is>
       </c>
       <c r="D287" s="22" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E287" s="12" t="inlineStr">
         <is>
@@ -19963,17 +19963,17 @@
       </c>
       <c r="F287" s="12" t="inlineStr">
         <is>
-          <t>Over 53.5</t>
+          <t>Over 55.5</t>
         </is>
       </c>
       <c r="G287" s="23" t="n">
-        <v>53.5</v>
+        <v>55.5</v>
       </c>
       <c r="H287" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I287" s="15" t="n">
-        <v>0.5179356580520053</v>
+        <v>0.5179356544150409</v>
       </c>
       <c r="J287" s="15" t="n">
         <v>0.5</v>
@@ -19982,10 +19982,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L287" s="14" t="n">
-        <v>-0.005873865757518582</v>
+        <v>-0.005873869394482978</v>
       </c>
       <c r="M287" s="14" t="n">
-        <v>-0.01121374371889899</v>
+        <v>-0.01121375066219471</v>
       </c>
       <c r="N287" s="15" t="n">
         <v>0</v>
@@ -20008,35 +20008,35 @@
       </c>
       <c r="B288" s="17" t="inlineStr">
         <is>
-          <t>USC @ UCLA</t>
+          <t>USC @ PSU</t>
         </is>
       </c>
       <c r="C288" s="17" t="inlineStr">
         <is>
-          <t>2026-11-28 05:00</t>
+          <t>2026-10-10 04:00</t>
         </is>
       </c>
       <c r="D288" s="25" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E288" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F288" s="17" t="inlineStr">
         <is>
-          <t>Over 55.5</t>
+          <t>PSU -1.5</t>
         </is>
       </c>
       <c r="G288" s="26" t="n">
-        <v>55.5</v>
+        <v>-1.5</v>
       </c>
       <c r="H288" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I288" s="20" t="n">
-        <v>0.5179356544150409</v>
+        <v>0.517195813494671</v>
       </c>
       <c r="J288" s="20" t="n">
         <v>0.5</v>
@@ -20045,10 +20045,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L288" s="19" t="n">
-        <v>-0.005873869394482978</v>
+        <v>-0.006613710314852805</v>
       </c>
       <c r="M288" s="19" t="n">
-        <v>-0.01121375066219471</v>
+        <v>-0.01262617423744616</v>
       </c>
       <c r="N288" s="20" t="n">
         <v>0</v>
@@ -20071,16 +20071,16 @@
       </c>
       <c r="B289" s="12" t="inlineStr">
         <is>
-          <t>USC @ PSU</t>
+          <t>UNC @ DUKE</t>
         </is>
       </c>
       <c r="C289" s="12" t="inlineStr">
         <is>
-          <t>2026-10-10 04:00</t>
+          <t>2026-10-17 04:00</t>
         </is>
       </c>
       <c r="D289" s="22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E289" s="12" t="inlineStr">
         <is>
@@ -20089,17 +20089,17 @@
       </c>
       <c r="F289" s="12" t="inlineStr">
         <is>
-          <t>PSU -1.5</t>
+          <t>UNC +4.5</t>
         </is>
       </c>
       <c r="G289" s="23" t="n">
-        <v>-1.5</v>
+        <v>-4.5</v>
       </c>
       <c r="H289" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I289" s="15" t="n">
-        <v>0.517195813494671</v>
+        <v>0.516626035872215</v>
       </c>
       <c r="J289" s="15" t="n">
         <v>0.5</v>
@@ -20108,10 +20108,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L289" s="14" t="n">
-        <v>-0.006613710314852805</v>
+        <v>-0.00718348793730883</v>
       </c>
       <c r="M289" s="14" t="n">
-        <v>-0.01262617423744616</v>
+        <v>-0.01371393151668038</v>
       </c>
       <c r="N289" s="15" t="n">
         <v>0</v>
@@ -20134,35 +20134,35 @@
       </c>
       <c r="B290" s="17" t="inlineStr">
         <is>
-          <t>UNC @ DUKE</t>
+          <t>LSU @ TENN</t>
         </is>
       </c>
       <c r="C290" s="17" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00</t>
+          <t>2026-11-21 05:00</t>
         </is>
       </c>
       <c r="D290" s="25" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E290" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F290" s="17" t="inlineStr">
         <is>
-          <t>UNC +4.5</t>
+          <t>Under 57.5</t>
         </is>
       </c>
       <c r="G290" s="26" t="n">
-        <v>-4.5</v>
+        <v>57.5</v>
       </c>
       <c r="H290" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I290" s="20" t="n">
-        <v>0.516626035872215</v>
+        <v>0.5159473183674262</v>
       </c>
       <c r="J290" s="20" t="n">
         <v>0.5</v>
@@ -20171,10 +20171,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L290" s="19" t="n">
-        <v>-0.00718348793730883</v>
+        <v>-0.007862205442097592</v>
       </c>
       <c r="M290" s="19" t="n">
-        <v>-0.01371393151668038</v>
+        <v>-0.01500966493491351</v>
       </c>
       <c r="N290" s="20" t="n">
         <v>0</v>
@@ -20197,16 +20197,16 @@
       </c>
       <c r="B291" s="12" t="inlineStr">
         <is>
-          <t>LSU @ TENN</t>
+          <t>NAU @ ARIZ</t>
         </is>
       </c>
       <c r="C291" s="12" t="inlineStr">
         <is>
-          <t>2026-11-21 05:00</t>
+          <t>2026-09-06 01:30</t>
         </is>
       </c>
       <c r="D291" s="22" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E291" s="12" t="inlineStr">
         <is>
@@ -20215,17 +20215,17 @@
       </c>
       <c r="F291" s="12" t="inlineStr">
         <is>
-          <t>Under 57.5</t>
+          <t>Under 56.5</t>
         </is>
       </c>
       <c r="G291" s="23" t="n">
-        <v>57.5</v>
+        <v>56.5</v>
       </c>
       <c r="H291" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I291" s="15" t="n">
-        <v>0.5159473183674262</v>
+        <v>0.5159473173920124</v>
       </c>
       <c r="J291" s="15" t="n">
         <v>0.5</v>
@@ -20234,10 +20234,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L291" s="14" t="n">
-        <v>-0.007862205442097592</v>
+        <v>-0.007862206417511453</v>
       </c>
       <c r="M291" s="14" t="n">
-        <v>-0.01500966493491351</v>
+        <v>-0.01500966679706722</v>
       </c>
       <c r="N291" s="15" t="n">
         <v>0</v>
@@ -20250,7 +20250,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q291" s="12" t="n"/>
+      <c r="Q291" s="12" t="inlineStr">
+        <is>
+          <t>NAU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="17" t="inlineStr">
@@ -20260,16 +20264,16 @@
       </c>
       <c r="B292" s="17" t="inlineStr">
         <is>
-          <t>NAU @ ARIZ</t>
+          <t>TCU @ TTU</t>
         </is>
       </c>
       <c r="C292" s="17" t="inlineStr">
         <is>
-          <t>2026-09-06 01:30</t>
+          <t>2026-11-27 01:00</t>
         </is>
       </c>
       <c r="D292" s="25" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E292" s="17" t="inlineStr">
         <is>
@@ -20278,17 +20282,17 @@
       </c>
       <c r="F292" s="17" t="inlineStr">
         <is>
-          <t>Under 56.5</t>
+          <t>Under 55.5</t>
         </is>
       </c>
       <c r="G292" s="26" t="n">
-        <v>56.5</v>
+        <v>55.5</v>
       </c>
       <c r="H292" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I292" s="20" t="n">
-        <v>0.5159473173920124</v>
+        <v>0.5159473156809926</v>
       </c>
       <c r="J292" s="20" t="n">
         <v>0.5</v>
@@ -20297,10 +20301,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L292" s="19" t="n">
-        <v>-0.007862206417511453</v>
+        <v>-0.007862208128531223</v>
       </c>
       <c r="M292" s="19" t="n">
-        <v>-0.01500966679706722</v>
+        <v>-0.01500967006355952</v>
       </c>
       <c r="N292" s="20" t="n">
         <v>0</v>
@@ -20313,11 +20317,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q292" s="17" t="inlineStr">
-        <is>
-          <t>NAU isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q292" s="17" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="12" t="inlineStr">
@@ -20327,16 +20327,16 @@
       </c>
       <c r="B293" s="12" t="inlineStr">
         <is>
-          <t>TCU @ TTU</t>
+          <t>FSU @ MIA</t>
         </is>
       </c>
       <c r="C293" s="12" t="inlineStr">
         <is>
-          <t>2026-11-27 01:00</t>
+          <t>2026-10-17 04:00</t>
         </is>
       </c>
       <c r="D293" s="22" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E293" s="12" t="inlineStr">
         <is>
@@ -20345,17 +20345,17 @@
       </c>
       <c r="F293" s="12" t="inlineStr">
         <is>
-          <t>Under 55.5</t>
+          <t>Under 53.5</t>
         </is>
       </c>
       <c r="G293" s="23" t="n">
-        <v>55.5</v>
+        <v>53.5</v>
       </c>
       <c r="H293" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I293" s="15" t="n">
-        <v>0.5159473156809926</v>
+        <v>0.51594730760003</v>
       </c>
       <c r="J293" s="15" t="n">
         <v>0.5</v>
@@ -20364,10 +20364,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L293" s="14" t="n">
-        <v>-0.007862208128531223</v>
+        <v>-0.007862216209493789</v>
       </c>
       <c r="M293" s="14" t="n">
-        <v>-0.01500967006355952</v>
+        <v>-0.01500968549085169</v>
       </c>
       <c r="N293" s="15" t="n">
         <v>0</v>
@@ -20390,16 +20390,16 @@
       </c>
       <c r="B294" s="17" t="inlineStr">
         <is>
-          <t>FSU @ MIA</t>
+          <t>FLA @ AUB</t>
         </is>
       </c>
       <c r="C294" s="17" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00</t>
+          <t>2026-09-19 23:00</t>
         </is>
       </c>
       <c r="D294" s="25" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E294" s="17" t="inlineStr">
         <is>
@@ -20418,7 +20418,7 @@
         <v>-110</v>
       </c>
       <c r="I294" s="20" t="n">
-        <v>0.51594730760003</v>
+        <v>0.5139573823881913</v>
       </c>
       <c r="J294" s="20" t="n">
         <v>0.5</v>
@@ -20427,10 +20427,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L294" s="19" t="n">
-        <v>-0.007862216209493789</v>
+        <v>-0.009852141421332505</v>
       </c>
       <c r="M294" s="19" t="n">
-        <v>-0.01500968549085169</v>
+        <v>-0.01880863362254376</v>
       </c>
       <c r="N294" s="20" t="n">
         <v>0</v>
@@ -20453,35 +20453,35 @@
       </c>
       <c r="B295" s="12" t="inlineStr">
         <is>
-          <t>FLA @ AUB</t>
+          <t>OSU @ TEX</t>
         </is>
       </c>
       <c r="C295" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-12 23:30</t>
         </is>
       </c>
       <c r="D295" s="22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E295" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F295" s="12" t="inlineStr">
         <is>
-          <t>Under 53.5</t>
+          <t>OSU +1.5</t>
         </is>
       </c>
       <c r="G295" s="23" t="n">
-        <v>53.5</v>
+        <v>-1.5</v>
       </c>
       <c r="H295" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I295" s="15" t="n">
-        <v>0.5139573823881913</v>
+        <v>0.5135482219987958</v>
       </c>
       <c r="J295" s="15" t="n">
         <v>0.5</v>
@@ -20490,10 +20490,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L295" s="14" t="n">
-        <v>-0.009852141421332505</v>
+        <v>-0.01026130181072804</v>
       </c>
       <c r="M295" s="14" t="n">
-        <v>-0.01880863362254376</v>
+        <v>-0.0195897580022989</v>
       </c>
       <c r="N295" s="15" t="n">
         <v>0</v>
@@ -20516,12 +20516,12 @@
       </c>
       <c r="B296" s="17" t="inlineStr">
         <is>
-          <t>OSU @ TEX</t>
+          <t>OU @ MICH</t>
         </is>
       </c>
       <c r="C296" s="17" t="inlineStr">
         <is>
-          <t>2026-09-12 23:30</t>
+          <t>2026-09-12 16:00</t>
         </is>
       </c>
       <c r="D296" s="25" t="n">
@@ -20534,7 +20534,7 @@
       </c>
       <c r="F296" s="17" t="inlineStr">
         <is>
-          <t>OSU +1.5</t>
+          <t>MICH -1.5</t>
         </is>
       </c>
       <c r="G296" s="26" t="n">
@@ -20544,7 +20544,7 @@
         <v>-110</v>
       </c>
       <c r="I296" s="20" t="n">
-        <v>0.5135482219987958</v>
+        <v>0.5120296819535175</v>
       </c>
       <c r="J296" s="20" t="n">
         <v>0.5</v>
@@ -20553,10 +20553,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L296" s="19" t="n">
-        <v>-0.01026130181072804</v>
+        <v>-0.01177984185600633</v>
       </c>
       <c r="M296" s="19" t="n">
-        <v>-0.0195897580022989</v>
+        <v>-0.02248878899783019</v>
       </c>
       <c r="N296" s="20" t="n">
         <v>0</v>
@@ -20579,35 +20579,35 @@
       </c>
       <c r="B297" s="12" t="inlineStr">
         <is>
-          <t>OU @ MICH</t>
+          <t>WIS @ ND</t>
         </is>
       </c>
       <c r="C297" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12 16:00</t>
+          <t>2026-09-06 23:30</t>
         </is>
       </c>
       <c r="D297" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E297" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F297" s="12" t="inlineStr">
         <is>
-          <t>MICH -1.5</t>
+          <t>Over 47.5</t>
         </is>
       </c>
       <c r="G297" s="23" t="n">
-        <v>-1.5</v>
+        <v>47.5</v>
       </c>
       <c r="H297" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I297" s="15" t="n">
-        <v>0.5120296819535175</v>
+        <v>0.5119662256857437</v>
       </c>
       <c r="J297" s="15" t="n">
         <v>0.5</v>
@@ -20616,10 +20616,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L297" s="14" t="n">
-        <v>-0.01177984185600633</v>
+        <v>-0.01184329812378015</v>
       </c>
       <c r="M297" s="14" t="n">
-        <v>-0.02248878899783019</v>
+        <v>-0.02260993278176204</v>
       </c>
       <c r="N297" s="15" t="n">
         <v>0</v>
@@ -20642,16 +20642,16 @@
       </c>
       <c r="B298" s="17" t="inlineStr">
         <is>
-          <t>WIS @ ND</t>
+          <t>ORE @ OSU</t>
         </is>
       </c>
       <c r="C298" s="17" t="inlineStr">
         <is>
-          <t>2026-09-06 23:30</t>
+          <t>2026-11-07 05:00</t>
         </is>
       </c>
       <c r="D298" s="25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E298" s="17" t="inlineStr">
         <is>
@@ -20660,17 +20660,17 @@
       </c>
       <c r="F298" s="17" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
+          <t>Over 52.5</t>
         </is>
       </c>
       <c r="G298" s="26" t="n">
-        <v>47.5</v>
+        <v>52.5</v>
       </c>
       <c r="H298" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I298" s="20" t="n">
-        <v>0.5119662256857437</v>
+        <v>0.5119660842604348</v>
       </c>
       <c r="J298" s="20" t="n">
         <v>0.5</v>
@@ -20679,10 +20679,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L298" s="19" t="n">
-        <v>-0.01184329812378015</v>
+        <v>-0.01184343954908906</v>
       </c>
       <c r="M298" s="19" t="n">
-        <v>-0.02260993278176204</v>
+        <v>-0.02261020277553355</v>
       </c>
       <c r="N298" s="20" t="n">
         <v>0</v>
@@ -20705,16 +20705,16 @@
       </c>
       <c r="B299" s="12" t="inlineStr">
         <is>
-          <t>ORE @ OSU</t>
+          <t>TA&amp;M @ ALA</t>
         </is>
       </c>
       <c r="C299" s="12" t="inlineStr">
         <is>
-          <t>2026-11-07 05:00</t>
+          <t>2026-10-24 04:00</t>
         </is>
       </c>
       <c r="D299" s="22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E299" s="12" t="inlineStr">
         <is>
@@ -20723,17 +20723,17 @@
       </c>
       <c r="F299" s="12" t="inlineStr">
         <is>
-          <t>Over 52.5</t>
+          <t>Under 54.5</t>
         </is>
       </c>
       <c r="G299" s="23" t="n">
-        <v>52.5</v>
+        <v>54.5</v>
       </c>
       <c r="H299" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I299" s="15" t="n">
-        <v>0.5119660842604348</v>
+        <v>0.511966067232297</v>
       </c>
       <c r="J299" s="15" t="n">
         <v>0.5</v>
@@ -20742,10 +20742,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L299" s="14" t="n">
-        <v>-0.01184343954908906</v>
+        <v>-0.01184345657722685</v>
       </c>
       <c r="M299" s="14" t="n">
-        <v>-0.02261020277553355</v>
+        <v>-0.02261023528379663</v>
       </c>
       <c r="N299" s="15" t="n">
         <v>0</v>
@@ -20768,16 +20768,16 @@
       </c>
       <c r="B300" s="17" t="inlineStr">
         <is>
-          <t>TA&amp;M @ ALA</t>
+          <t>AUB @ ALA</t>
         </is>
       </c>
       <c r="C300" s="17" t="inlineStr">
         <is>
-          <t>2026-10-24 04:00</t>
+          <t>2026-11-28 05:00</t>
         </is>
       </c>
       <c r="D300" s="25" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E300" s="17" t="inlineStr">
         <is>
@@ -20786,17 +20786,17 @@
       </c>
       <c r="F300" s="17" t="inlineStr">
         <is>
-          <t>Under 54.5</t>
+          <t>Under 53.5</t>
         </is>
       </c>
       <c r="G300" s="26" t="n">
-        <v>54.5</v>
+        <v>53.5</v>
       </c>
       <c r="H300" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I300" s="20" t="n">
-        <v>0.511966067232297</v>
+        <v>0.51196606256607</v>
       </c>
       <c r="J300" s="20" t="n">
         <v>0.5</v>
@@ -20805,10 +20805,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L300" s="19" t="n">
-        <v>-0.01184345657722685</v>
+        <v>-0.01184346124345381</v>
       </c>
       <c r="M300" s="19" t="n">
-        <v>-0.02261023528379663</v>
+        <v>-0.0226102441920481</v>
       </c>
       <c r="N300" s="20" t="n">
         <v>0</v>
@@ -20831,16 +20831,16 @@
       </c>
       <c r="B301" s="12" t="inlineStr">
         <is>
-          <t>AUB @ ALA</t>
+          <t>UGA @ MISS</t>
         </is>
       </c>
       <c r="C301" s="12" t="inlineStr">
         <is>
-          <t>2026-11-28 05:00</t>
+          <t>2026-11-07 05:00</t>
         </is>
       </c>
       <c r="D301" s="22" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E301" s="12" t="inlineStr">
         <is>
@@ -20849,17 +20849,17 @@
       </c>
       <c r="F301" s="12" t="inlineStr">
         <is>
-          <t>Under 53.5</t>
+          <t>Over 55.5</t>
         </is>
       </c>
       <c r="G301" s="23" t="n">
-        <v>53.5</v>
+        <v>55.5</v>
       </c>
       <c r="H301" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I301" s="15" t="n">
-        <v>0.51196606256607</v>
+        <v>0.5099735590672994</v>
       </c>
       <c r="J301" s="15" t="n">
         <v>0.5</v>
@@ -20868,10 +20868,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L301" s="14" t="n">
-        <v>-0.01184346124345381</v>
+        <v>-0.01383596474222448</v>
       </c>
       <c r="M301" s="14" t="n">
-        <v>-0.0226102441920481</v>
+        <v>-0.026414114507883</v>
       </c>
       <c r="N301" s="15" t="n">
         <v>0</v>
@@ -20894,16 +20894,16 @@
       </c>
       <c r="B302" s="17" t="inlineStr">
         <is>
-          <t>UGA @ MISS</t>
+          <t>DUKE @ MIA</t>
         </is>
       </c>
       <c r="C302" s="17" t="inlineStr">
         <is>
-          <t>2026-11-07 05:00</t>
+          <t>2026-11-14 05:00</t>
         </is>
       </c>
       <c r="D302" s="25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E302" s="17" t="inlineStr">
         <is>
@@ -20957,16 +20957,16 @@
       </c>
       <c r="B303" s="12" t="inlineStr">
         <is>
-          <t>DUKE @ MIA</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C303" s="12" t="inlineStr">
         <is>
-          <t>2026-11-14 05:00</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D303" s="22" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E303" s="12" t="inlineStr">
         <is>
@@ -20975,17 +20975,17 @@
       </c>
       <c r="F303" s="12" t="inlineStr">
         <is>
-          <t>Over 55.5</t>
+          <t>Over 57.5</t>
         </is>
       </c>
       <c r="G303" s="23" t="n">
-        <v>55.5</v>
+        <v>57.5</v>
       </c>
       <c r="H303" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I303" s="15" t="n">
-        <v>0.5099735590672994</v>
+        <v>0.5099735576396345</v>
       </c>
       <c r="J303" s="15" t="n">
         <v>0.5</v>
@@ -20994,10 +20994,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L303" s="14" t="n">
-        <v>-0.01383596474222448</v>
+        <v>-0.01383596616988936</v>
       </c>
       <c r="M303" s="14" t="n">
-        <v>-0.026414114507883</v>
+        <v>-0.02641411723342507</v>
       </c>
       <c r="N303" s="15" t="n">
         <v>0</v>
@@ -24360,16 +24360,16 @@
       </c>
       <c r="B356" s="17" t="inlineStr">
         <is>
-          <t>UGA @ MISS</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C356" s="17" t="inlineStr">
         <is>
-          <t>2026-11-07 05:00</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D356" s="25" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E356" s="17" t="inlineStr">
         <is>
@@ -24378,17 +24378,17 @@
       </c>
       <c r="F356" s="17" t="inlineStr">
         <is>
-          <t>Under 55.5</t>
+          <t>Under 57.5</t>
         </is>
       </c>
       <c r="G356" s="26" t="n">
-        <v>55.5</v>
+        <v>57.5</v>
       </c>
       <c r="H356" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I356" s="20" t="n">
-        <v>0.4900264409327006</v>
+        <v>0.4900264423603655</v>
       </c>
       <c r="J356" s="20" t="n">
         <v>0.5</v>
@@ -24397,10 +24397,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L356" s="19" t="n">
-        <v>-0.03378308287682319</v>
+        <v>-0.03378308144915831</v>
       </c>
       <c r="M356" s="19" t="n">
-        <v>-0.06449497640120783</v>
+        <v>-0.06449497367566576</v>
       </c>
       <c r="N356" s="20" t="n">
         <v>0</v>
@@ -24423,16 +24423,16 @@
       </c>
       <c r="B357" s="12" t="inlineStr">
         <is>
-          <t>DUKE @ MIA</t>
+          <t>UGA @ MISS</t>
         </is>
       </c>
       <c r="C357" s="12" t="inlineStr">
         <is>
-          <t>2026-11-14 05:00</t>
+          <t>2026-11-07 05:00</t>
         </is>
       </c>
       <c r="D357" s="22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E357" s="12" t="inlineStr">
         <is>
@@ -24486,16 +24486,16 @@
       </c>
       <c r="B358" s="17" t="inlineStr">
         <is>
-          <t>AUB @ ALA</t>
+          <t>DUKE @ MIA</t>
         </is>
       </c>
       <c r="C358" s="17" t="inlineStr">
         <is>
-          <t>2026-11-28 05:00</t>
+          <t>2026-11-14 05:00</t>
         </is>
       </c>
       <c r="D358" s="25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E358" s="17" t="inlineStr">
         <is>
@@ -24504,17 +24504,17 @@
       </c>
       <c r="F358" s="17" t="inlineStr">
         <is>
-          <t>Over 53.5</t>
+          <t>Under 55.5</t>
         </is>
       </c>
       <c r="G358" s="26" t="n">
-        <v>53.5</v>
+        <v>55.5</v>
       </c>
       <c r="H358" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I358" s="20" t="n">
-        <v>0.48803393743393</v>
+        <v>0.4900264409327006</v>
       </c>
       <c r="J358" s="20" t="n">
         <v>0.5</v>
@@ -24523,10 +24523,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L358" s="19" t="n">
-        <v>-0.03577558637559386</v>
+        <v>-0.03378308287682319</v>
       </c>
       <c r="M358" s="19" t="n">
-        <v>-0.06829884671704273</v>
+        <v>-0.06449497640120783</v>
       </c>
       <c r="N358" s="20" t="n">
         <v>0</v>
@@ -24549,16 +24549,16 @@
       </c>
       <c r="B359" s="12" t="inlineStr">
         <is>
-          <t>TA&amp;M @ ALA</t>
+          <t>AUB @ ALA</t>
         </is>
       </c>
       <c r="C359" s="12" t="inlineStr">
         <is>
-          <t>2026-10-24 04:00</t>
+          <t>2026-11-28 05:00</t>
         </is>
       </c>
       <c r="D359" s="22" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E359" s="12" t="inlineStr">
         <is>
@@ -24567,17 +24567,17 @@
       </c>
       <c r="F359" s="12" t="inlineStr">
         <is>
-          <t>Over 54.5</t>
+          <t>Over 53.5</t>
         </is>
       </c>
       <c r="G359" s="23" t="n">
-        <v>54.5</v>
+        <v>53.5</v>
       </c>
       <c r="H359" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I359" s="15" t="n">
-        <v>0.488033932767703</v>
+        <v>0.48803393743393</v>
       </c>
       <c r="J359" s="15" t="n">
         <v>0.5</v>
@@ -24586,10 +24586,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L359" s="14" t="n">
-        <v>-0.03577559104182082</v>
+        <v>-0.03577558637559386</v>
       </c>
       <c r="M359" s="14" t="n">
-        <v>-0.0682988556252942</v>
+        <v>-0.06829884671704273</v>
       </c>
       <c r="N359" s="15" t="n">
         <v>0</v>
@@ -24612,16 +24612,16 @@
       </c>
       <c r="B360" s="17" t="inlineStr">
         <is>
-          <t>ORE @ OSU</t>
+          <t>TA&amp;M @ ALA</t>
         </is>
       </c>
       <c r="C360" s="17" t="inlineStr">
         <is>
-          <t>2026-11-07 05:00</t>
+          <t>2026-10-24 04:00</t>
         </is>
       </c>
       <c r="D360" s="25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E360" s="17" t="inlineStr">
         <is>
@@ -24630,17 +24630,17 @@
       </c>
       <c r="F360" s="17" t="inlineStr">
         <is>
-          <t>Under 52.5</t>
+          <t>Over 54.5</t>
         </is>
       </c>
       <c r="G360" s="26" t="n">
-        <v>52.5</v>
+        <v>54.5</v>
       </c>
       <c r="H360" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I360" s="20" t="n">
-        <v>0.4880339157395652</v>
+        <v>0.488033932767703</v>
       </c>
       <c r="J360" s="20" t="n">
         <v>0.5</v>
@@ -24649,10 +24649,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L360" s="19" t="n">
-        <v>-0.03577560806995861</v>
+        <v>-0.03577559104182082</v>
       </c>
       <c r="M360" s="19" t="n">
-        <v>-0.06829888813355728</v>
+        <v>-0.0682988556252942</v>
       </c>
       <c r="N360" s="20" t="n">
         <v>0</v>
@@ -24675,16 +24675,16 @@
       </c>
       <c r="B361" s="12" t="inlineStr">
         <is>
-          <t>WIS @ ND</t>
+          <t>ORE @ OSU</t>
         </is>
       </c>
       <c r="C361" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 23:30</t>
+          <t>2026-11-07 05:00</t>
         </is>
       </c>
       <c r="D361" s="22" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E361" s="12" t="inlineStr">
         <is>
@@ -24693,17 +24693,17 @@
       </c>
       <c r="F361" s="12" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
+          <t>Under 52.5</t>
         </is>
       </c>
       <c r="G361" s="23" t="n">
-        <v>47.5</v>
+        <v>52.5</v>
       </c>
       <c r="H361" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I361" s="15" t="n">
-        <v>0.4880337743142563</v>
+        <v>0.4880339157395652</v>
       </c>
       <c r="J361" s="15" t="n">
         <v>0.5</v>
@@ -24712,10 +24712,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L361" s="14" t="n">
-        <v>-0.03577574949526752</v>
+        <v>-0.03577560806995861</v>
       </c>
       <c r="M361" s="14" t="n">
-        <v>-0.06829915812732879</v>
+        <v>-0.06829888813355728</v>
       </c>
       <c r="N361" s="15" t="n">
         <v>0</v>
@@ -24738,35 +24738,35 @@
       </c>
       <c r="B362" s="17" t="inlineStr">
         <is>
-          <t>OU @ MICH</t>
+          <t>WIS @ ND</t>
         </is>
       </c>
       <c r="C362" s="17" t="inlineStr">
         <is>
-          <t>2026-09-12 16:00</t>
+          <t>2026-09-06 23:30</t>
         </is>
       </c>
       <c r="D362" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E362" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F362" s="17" t="inlineStr">
         <is>
-          <t>OU +1.5</t>
+          <t>Under 47.5</t>
         </is>
       </c>
       <c r="G362" s="26" t="n">
-        <v>-1.5</v>
+        <v>47.5</v>
       </c>
       <c r="H362" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I362" s="20" t="n">
-        <v>0.4879703180464825</v>
+        <v>0.4880337743142563</v>
       </c>
       <c r="J362" s="20" t="n">
         <v>0.5</v>
@@ -24775,10 +24775,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L362" s="19" t="n">
-        <v>-0.03583920576304134</v>
+        <v>-0.03577574949526752</v>
       </c>
       <c r="M362" s="19" t="n">
-        <v>-0.06842030191126064</v>
+        <v>-0.06829915812732879</v>
       </c>
       <c r="N362" s="20" t="n">
         <v>0</v>
@@ -24801,12 +24801,12 @@
       </c>
       <c r="B363" s="12" t="inlineStr">
         <is>
-          <t>OSU @ TEX</t>
+          <t>OU @ MICH</t>
         </is>
       </c>
       <c r="C363" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12 23:30</t>
+          <t>2026-09-12 16:00</t>
         </is>
       </c>
       <c r="D363" s="22" t="n">
@@ -24819,7 +24819,7 @@
       </c>
       <c r="F363" s="12" t="inlineStr">
         <is>
-          <t>TEX -1.5</t>
+          <t>OU +1.5</t>
         </is>
       </c>
       <c r="G363" s="23" t="n">
@@ -24829,7 +24829,7 @@
         <v>-110</v>
       </c>
       <c r="I363" s="15" t="n">
-        <v>0.4864517780012042</v>
+        <v>0.4879703180464825</v>
       </c>
       <c r="J363" s="15" t="n">
         <v>0.5</v>
@@ -24838,10 +24838,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L363" s="14" t="n">
-        <v>-0.03735774580831963</v>
+        <v>-0.03583920576304134</v>
       </c>
       <c r="M363" s="14" t="n">
-        <v>-0.07131933290679193</v>
+        <v>-0.06842030191126064</v>
       </c>
       <c r="N363" s="15" t="n">
         <v>0</v>
@@ -24864,35 +24864,35 @@
       </c>
       <c r="B364" s="17" t="inlineStr">
         <is>
-          <t>FLA @ AUB</t>
+          <t>OSU @ TEX</t>
         </is>
       </c>
       <c r="C364" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-12 23:30</t>
         </is>
       </c>
       <c r="D364" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E364" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F364" s="17" t="inlineStr">
         <is>
-          <t>Over 53.5</t>
+          <t>TEX -1.5</t>
         </is>
       </c>
       <c r="G364" s="26" t="n">
-        <v>53.5</v>
+        <v>-1.5</v>
       </c>
       <c r="H364" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I364" s="20" t="n">
-        <v>0.4860426176118087</v>
+        <v>0.4864517780012042</v>
       </c>
       <c r="J364" s="20" t="n">
         <v>0.5</v>
@@ -24901,10 +24901,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L364" s="19" t="n">
-        <v>-0.03776690619771517</v>
+        <v>-0.03735774580831963</v>
       </c>
       <c r="M364" s="19" t="n">
-        <v>-0.07210045728654707</v>
+        <v>-0.07131933290679193</v>
       </c>
       <c r="N364" s="20" t="n">
         <v>0</v>
@@ -24927,16 +24927,16 @@
       </c>
       <c r="B365" s="12" t="inlineStr">
         <is>
-          <t>FSU @ MIA</t>
+          <t>FLA @ AUB</t>
         </is>
       </c>
       <c r="C365" s="12" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00</t>
+          <t>2026-09-19 23:00</t>
         </is>
       </c>
       <c r="D365" s="22" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E365" s="12" t="inlineStr">
         <is>
@@ -24955,7 +24955,7 @@
         <v>-110</v>
       </c>
       <c r="I365" s="15" t="n">
-        <v>0.48405269239997</v>
+        <v>0.4860426176118087</v>
       </c>
       <c r="J365" s="15" t="n">
         <v>0.5</v>
@@ -24964,10 +24964,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L365" s="14" t="n">
-        <v>-0.03975683140955388</v>
+        <v>-0.03776690619771517</v>
       </c>
       <c r="M365" s="14" t="n">
-        <v>-0.07589940541823914</v>
+        <v>-0.07210045728654707</v>
       </c>
       <c r="N365" s="15" t="n">
         <v>0</v>
@@ -24990,16 +24990,16 @@
       </c>
       <c r="B366" s="17" t="inlineStr">
         <is>
-          <t>TCU @ TTU</t>
+          <t>FSU @ MIA</t>
         </is>
       </c>
       <c r="C366" s="17" t="inlineStr">
         <is>
-          <t>2026-11-27 01:00</t>
+          <t>2026-10-17 04:00</t>
         </is>
       </c>
       <c r="D366" s="25" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E366" s="17" t="inlineStr">
         <is>
@@ -25008,17 +25008,17 @@
       </c>
       <c r="F366" s="17" t="inlineStr">
         <is>
-          <t>Over 55.5</t>
+          <t>Over 53.5</t>
         </is>
       </c>
       <c r="G366" s="26" t="n">
-        <v>55.5</v>
+        <v>53.5</v>
       </c>
       <c r="H366" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I366" s="20" t="n">
-        <v>0.4840526843190074</v>
+        <v>0.48405269239997</v>
       </c>
       <c r="J366" s="20" t="n">
         <v>0.5</v>
@@ -25027,10 +25027,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L366" s="19" t="n">
-        <v>-0.03975683949051639</v>
+        <v>-0.03975683140955388</v>
       </c>
       <c r="M366" s="19" t="n">
-        <v>-0.07589942084553125</v>
+        <v>-0.07589940541823914</v>
       </c>
       <c r="N366" s="20" t="n">
         <v>0</v>
@@ -25053,16 +25053,16 @@
       </c>
       <c r="B367" s="12" t="inlineStr">
         <is>
-          <t>NAU @ ARIZ</t>
+          <t>TCU @ TTU</t>
         </is>
       </c>
       <c r="C367" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 01:30</t>
+          <t>2026-11-27 01:00</t>
         </is>
       </c>
       <c r="D367" s="22" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E367" s="12" t="inlineStr">
         <is>
@@ -25071,17 +25071,17 @@
       </c>
       <c r="F367" s="12" t="inlineStr">
         <is>
-          <t>Over 56.5</t>
+          <t>Over 55.5</t>
         </is>
       </c>
       <c r="G367" s="23" t="n">
-        <v>56.5</v>
+        <v>55.5</v>
       </c>
       <c r="H367" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I367" s="15" t="n">
-        <v>0.4840526826079876</v>
+        <v>0.4840526843190074</v>
       </c>
       <c r="J367" s="15" t="n">
         <v>0.5</v>
@@ -25090,10 +25090,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L367" s="14" t="n">
-        <v>-0.03975684120153622</v>
+        <v>-0.03975683949051639</v>
       </c>
       <c r="M367" s="14" t="n">
-        <v>-0.07589942411202361</v>
+        <v>-0.07589942084553125</v>
       </c>
       <c r="N367" s="15" t="n">
         <v>0</v>
@@ -25106,11 +25106,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q367" s="12" t="inlineStr">
-        <is>
-          <t>NAU isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q367" s="12" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="17" t="inlineStr">
@@ -25120,16 +25116,16 @@
       </c>
       <c r="B368" s="17" t="inlineStr">
         <is>
-          <t>LSU @ TENN</t>
+          <t>NAU @ ARIZ</t>
         </is>
       </c>
       <c r="C368" s="17" t="inlineStr">
         <is>
-          <t>2026-11-21 05:00</t>
+          <t>2026-09-06 01:30</t>
         </is>
       </c>
       <c r="D368" s="25" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E368" s="17" t="inlineStr">
         <is>
@@ -25138,17 +25134,17 @@
       </c>
       <c r="F368" s="17" t="inlineStr">
         <is>
-          <t>Over 57.5</t>
+          <t>Over 56.5</t>
         </is>
       </c>
       <c r="G368" s="26" t="n">
-        <v>57.5</v>
+        <v>56.5</v>
       </c>
       <c r="H368" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I368" s="20" t="n">
-        <v>0.4840526816325738</v>
+        <v>0.4840526826079876</v>
       </c>
       <c r="J368" s="20" t="n">
         <v>0.5</v>
@@ -25157,10 +25153,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L368" s="19" t="n">
-        <v>-0.03975684217695008</v>
+        <v>-0.03975684120153622</v>
       </c>
       <c r="M368" s="19" t="n">
-        <v>-0.07589942597417731</v>
+        <v>-0.07589942411202361</v>
       </c>
       <c r="N368" s="20" t="n">
         <v>0</v>
@@ -25173,7 +25169,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q368" s="17" t="n"/>
+      <c r="Q368" s="17" t="inlineStr">
+        <is>
+          <t>NAU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="12" t="inlineStr">
@@ -25183,35 +25183,35 @@
       </c>
       <c r="B369" s="12" t="inlineStr">
         <is>
-          <t>UNC @ DUKE</t>
+          <t>LSU @ TENN</t>
         </is>
       </c>
       <c r="C369" s="12" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00</t>
+          <t>2026-11-21 05:00</t>
         </is>
       </c>
       <c r="D369" s="22" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E369" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F369" s="12" t="inlineStr">
         <is>
-          <t>DUKE -4.5</t>
+          <t>Over 57.5</t>
         </is>
       </c>
       <c r="G369" s="23" t="n">
-        <v>-4.5</v>
+        <v>57.5</v>
       </c>
       <c r="H369" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I369" s="15" t="n">
-        <v>0.483373964127785</v>
+        <v>0.4840526816325738</v>
       </c>
       <c r="J369" s="15" t="n">
         <v>0.5</v>
@@ -25220,10 +25220,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L369" s="14" t="n">
-        <v>-0.04043555968173884</v>
+        <v>-0.03975684217695008</v>
       </c>
       <c r="M369" s="14" t="n">
-        <v>-0.07719515939241045</v>
+        <v>-0.07589942597417731</v>
       </c>
       <c r="N369" s="15" t="n">
         <v>0</v>
@@ -25246,16 +25246,16 @@
       </c>
       <c r="B370" s="17" t="inlineStr">
         <is>
-          <t>USC @ PSU</t>
+          <t>UNC @ DUKE</t>
         </is>
       </c>
       <c r="C370" s="17" t="inlineStr">
         <is>
-          <t>2026-10-10 04:00</t>
+          <t>2026-10-17 04:00</t>
         </is>
       </c>
       <c r="D370" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E370" s="17" t="inlineStr">
         <is>
@@ -25264,17 +25264,17 @@
       </c>
       <c r="F370" s="17" t="inlineStr">
         <is>
-          <t>USC +1.5</t>
+          <t>DUKE -4.5</t>
         </is>
       </c>
       <c r="G370" s="26" t="n">
-        <v>-1.5</v>
+        <v>-4.5</v>
       </c>
       <c r="H370" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I370" s="20" t="n">
-        <v>0.482804186505329</v>
+        <v>0.483373964127785</v>
       </c>
       <c r="J370" s="20" t="n">
         <v>0.5</v>
@@ -25283,10 +25283,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L370" s="19" t="n">
-        <v>-0.04100533730419487</v>
+        <v>-0.04043555968173884</v>
       </c>
       <c r="M370" s="19" t="n">
-        <v>-0.07828291667164466</v>
+        <v>-0.07719515939241045</v>
       </c>
       <c r="N370" s="20" t="n">
         <v>0</v>
@@ -25309,35 +25309,35 @@
       </c>
       <c r="B371" s="12" t="inlineStr">
         <is>
-          <t>USC @ UCLA</t>
+          <t>USC @ PSU</t>
         </is>
       </c>
       <c r="C371" s="12" t="inlineStr">
         <is>
-          <t>2026-11-28 05:00</t>
+          <t>2026-10-10 04:00</t>
         </is>
       </c>
       <c r="D371" s="22" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E371" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F371" s="12" t="inlineStr">
         <is>
-          <t>Under 55.5</t>
+          <t>USC +1.5</t>
         </is>
       </c>
       <c r="G371" s="23" t="n">
-        <v>55.5</v>
+        <v>-1.5</v>
       </c>
       <c r="H371" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I371" s="15" t="n">
-        <v>0.4820643455849591</v>
+        <v>0.482804186505329</v>
       </c>
       <c r="J371" s="15" t="n">
         <v>0.5</v>
@@ -25346,10 +25346,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L371" s="14" t="n">
-        <v>-0.04174517822456469</v>
+        <v>-0.04100533730419487</v>
       </c>
       <c r="M371" s="14" t="n">
-        <v>-0.07969534024689612</v>
+        <v>-0.07828291667164466</v>
       </c>
       <c r="N371" s="15" t="n">
         <v>0</v>
@@ -25372,16 +25372,16 @@
       </c>
       <c r="B372" s="17" t="inlineStr">
         <is>
-          <t>MISS @ OU</t>
+          <t>USC @ UCLA</t>
         </is>
       </c>
       <c r="C372" s="17" t="inlineStr">
         <is>
-          <t>2026-11-14 05:00</t>
+          <t>2026-11-28 05:00</t>
         </is>
       </c>
       <c r="D372" s="25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E372" s="17" t="inlineStr">
         <is>
@@ -25390,17 +25390,17 @@
       </c>
       <c r="F372" s="17" t="inlineStr">
         <is>
-          <t>Under 53.5</t>
+          <t>Under 55.5</t>
         </is>
       </c>
       <c r="G372" s="26" t="n">
-        <v>53.5</v>
+        <v>55.5</v>
       </c>
       <c r="H372" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I372" s="20" t="n">
-        <v>0.4820643419479947</v>
+        <v>0.4820643455849591</v>
       </c>
       <c r="J372" s="20" t="n">
         <v>0.5</v>
@@ -25409,10 +25409,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L372" s="19" t="n">
-        <v>-0.04174518186152909</v>
+        <v>-0.04174517822456469</v>
       </c>
       <c r="M372" s="19" t="n">
-        <v>-0.07969534719019183</v>
+        <v>-0.07969534024689612</v>
       </c>
       <c r="N372" s="20" t="n">
         <v>0</v>
@@ -25435,16 +25435,16 @@
       </c>
       <c r="B373" s="12" t="inlineStr">
         <is>
-          <t>OSU @ USC</t>
+          <t>MISS @ OU</t>
         </is>
       </c>
       <c r="C373" s="12" t="inlineStr">
         <is>
-          <t>2026-10-31 04:00</t>
+          <t>2026-11-14 05:00</t>
         </is>
       </c>
       <c r="D373" s="22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E373" s="12" t="inlineStr">
         <is>
@@ -25453,17 +25453,17 @@
       </c>
       <c r="F373" s="12" t="inlineStr">
         <is>
-          <t>Over 54.5</t>
+          <t>Under 53.5</t>
         </is>
       </c>
       <c r="G373" s="23" t="n">
-        <v>54.5</v>
+        <v>53.5</v>
       </c>
       <c r="H373" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I373" s="15" t="n">
-        <v>0.4800778118661322</v>
+        <v>0.4820643419479947</v>
       </c>
       <c r="J373" s="15" t="n">
         <v>0.5</v>
@@ -25472,10 +25472,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L373" s="14" t="n">
-        <v>-0.04373171194339165</v>
+        <v>-0.04174518186152909</v>
       </c>
       <c r="M373" s="14" t="n">
-        <v>-0.08348781371011121</v>
+        <v>-0.07969534719019183</v>
       </c>
       <c r="N373" s="15" t="n">
         <v>0</v>
@@ -25498,16 +25498,16 @@
       </c>
       <c r="B374" s="17" t="inlineStr">
         <is>
-          <t>UAB @ ILL</t>
+          <t>OSU @ USC</t>
         </is>
       </c>
       <c r="C374" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 01:00</t>
+          <t>2026-10-31 04:00</t>
         </is>
       </c>
       <c r="D374" s="25" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E374" s="17" t="inlineStr">
         <is>
@@ -25516,17 +25516,17 @@
       </c>
       <c r="F374" s="17" t="inlineStr">
         <is>
-          <t>Under 56.5</t>
+          <t>Over 54.5</t>
         </is>
       </c>
       <c r="G374" s="26" t="n">
-        <v>56.5</v>
+        <v>54.5</v>
       </c>
       <c r="H374" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I374" s="20" t="n">
-        <v>0.48007780341312</v>
+        <v>0.4800778118661322</v>
       </c>
       <c r="J374" s="20" t="n">
         <v>0.5</v>
@@ -25535,10 +25535,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L374" s="19" t="n">
-        <v>-0.04373172039640383</v>
+        <v>-0.04373171194339165</v>
       </c>
       <c r="M374" s="19" t="n">
-        <v>-0.08348782984767994</v>
+        <v>-0.08348781371011121</v>
       </c>
       <c r="N374" s="20" t="n">
         <v>0</v>
@@ -25561,12 +25561,12 @@
       </c>
       <c r="B375" s="12" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>UAB @ ILL</t>
         </is>
       </c>
       <c r="C375" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D375" s="22" t="n">
@@ -25579,17 +25579,17 @@
       </c>
       <c r="F375" s="12" t="inlineStr">
         <is>
-          <t>Under 53.5</t>
+          <t>Under 56.5</t>
         </is>
       </c>
       <c r="G375" s="23" t="n">
-        <v>53.5</v>
+        <v>56.5</v>
       </c>
       <c r="H375" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I375" s="15" t="n">
-        <v>0.4800777992356569</v>
+        <v>0.48007780341312</v>
       </c>
       <c r="J375" s="15" t="n">
         <v>0.5</v>
@@ -25598,10 +25598,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L375" s="14" t="n">
-        <v>-0.04373172457386698</v>
+        <v>-0.04373172039640383</v>
       </c>
       <c r="M375" s="14" t="n">
-        <v>-0.08348783782283686</v>
+        <v>-0.08348782984767994</v>
       </c>
       <c r="N375" s="15" t="n">
         <v>0</v>
@@ -25624,16 +25624,16 @@
       </c>
       <c r="B376" s="17" t="inlineStr">
         <is>
-          <t>TA&amp;M @ OU</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C376" s="17" t="inlineStr">
         <is>
-          <t>2026-11-21 05:00</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D376" s="25" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E376" s="17" t="inlineStr">
         <is>
@@ -25642,17 +25642,17 @@
       </c>
       <c r="F376" s="17" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>Under 53.5</t>
         </is>
       </c>
       <c r="G376" s="26" t="n">
-        <v>51.5</v>
+        <v>53.5</v>
       </c>
       <c r="H376" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I376" s="20" t="n">
-        <v>0.4800777888540669</v>
+        <v>0.4800777992356569</v>
       </c>
       <c r="J376" s="20" t="n">
         <v>0.5</v>
@@ -25661,10 +25661,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L376" s="19" t="n">
-        <v>-0.0437317349554569</v>
+        <v>-0.04373172457386698</v>
       </c>
       <c r="M376" s="19" t="n">
-        <v>-0.08348785764223582</v>
+        <v>-0.08348783782283686</v>
       </c>
       <c r="N376" s="20" t="n">
         <v>0</v>
@@ -25687,16 +25687,16 @@
       </c>
       <c r="B377" s="12" t="inlineStr">
         <is>
-          <t>UTU @ BYU</t>
+          <t>TA&amp;M @ OU</t>
         </is>
       </c>
       <c r="C377" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00</t>
+          <t>2026-11-21 05:00</t>
         </is>
       </c>
       <c r="D377" s="22" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E377" s="12" t="inlineStr">
         <is>
@@ -25705,17 +25705,17 @@
       </c>
       <c r="F377" s="12" t="inlineStr">
         <is>
-          <t>Under 54.5</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="G377" s="23" t="n">
-        <v>54.5</v>
+        <v>51.5</v>
       </c>
       <c r="H377" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I377" s="15" t="n">
-        <v>0.4780932458027352</v>
+        <v>0.4800777888540669</v>
       </c>
       <c r="J377" s="15" t="n">
         <v>0.5</v>
@@ -25724,27 +25724,23 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L377" s="14" t="n">
-        <v>-0.04571627800678868</v>
+        <v>-0.0437317349554569</v>
       </c>
       <c r="M377" s="14" t="n">
-        <v>-0.08727653074023284</v>
+        <v>-0.08348785764223582</v>
       </c>
       <c r="N377" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O377" s="24" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="P377" s="12" t="inlineStr">
         <is>
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q377" s="12" t="inlineStr">
-        <is>
-          <t>UTU isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q377" s="12" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="17" t="inlineStr">
@@ -25754,16 +25750,16 @@
       </c>
       <c r="B378" s="17" t="inlineStr">
         <is>
-          <t>OU @ UGA</t>
+          <t>UTU @ BYU</t>
         </is>
       </c>
       <c r="C378" s="17" t="inlineStr">
         <is>
-          <t>2026-09-26 04:00</t>
+          <t>2026-09-06 00:00</t>
         </is>
       </c>
       <c r="D378" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E378" s="17" t="inlineStr">
         <is>
@@ -25772,17 +25768,17 @@
       </c>
       <c r="F378" s="17" t="inlineStr">
         <is>
-          <t>Over 52.5</t>
+          <t>Under 54.5</t>
         </is>
       </c>
       <c r="G378" s="26" t="n">
-        <v>52.5</v>
+        <v>54.5</v>
       </c>
       <c r="H378" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I378" s="20" t="n">
-        <v>0.476110901147586</v>
+        <v>0.4780932458027352</v>
       </c>
       <c r="J378" s="20" t="n">
         <v>0.5</v>
@@ -25791,23 +25787,27 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L378" s="19" t="n">
-        <v>-0.04769862266193786</v>
+        <v>-0.04571627800678868</v>
       </c>
       <c r="M378" s="19" t="n">
-        <v>-0.09106100690006314</v>
+        <v>-0.08727653074023284</v>
       </c>
       <c r="N378" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O378" s="27" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="P378" s="17" t="inlineStr">
         <is>
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q378" s="17" t="n"/>
+      <c r="Q378" s="17" t="inlineStr">
+        <is>
+          <t>UTU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="12" t="inlineStr">
@@ -25817,16 +25817,16 @@
       </c>
       <c r="B379" s="12" t="inlineStr">
         <is>
-          <t>SC @ CLEM</t>
+          <t>OU @ UGA</t>
         </is>
       </c>
       <c r="C379" s="12" t="inlineStr">
         <is>
-          <t>2026-11-28 05:00</t>
+          <t>2026-09-26 04:00</t>
         </is>
       </c>
       <c r="D379" s="22" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E379" s="12" t="inlineStr">
         <is>
@@ -25835,17 +25835,17 @@
       </c>
       <c r="F379" s="12" t="inlineStr">
         <is>
-          <t>Over 53.5</t>
+          <t>Over 52.5</t>
         </is>
       </c>
       <c r="G379" s="23" t="n">
-        <v>53.5</v>
+        <v>52.5</v>
       </c>
       <c r="H379" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I379" s="15" t="n">
-        <v>0.4761108907812599</v>
+        <v>0.476110901147586</v>
       </c>
       <c r="J379" s="15" t="n">
         <v>0.5</v>
@@ -25854,10 +25854,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L379" s="14" t="n">
-        <v>-0.04769863302826394</v>
+        <v>-0.04769862266193786</v>
       </c>
       <c r="M379" s="14" t="n">
-        <v>-0.09106102669032196</v>
+        <v>-0.09106100690006314</v>
       </c>
       <c r="N379" s="15" t="n">
         <v>0</v>
@@ -25880,16 +25880,16 @@
       </c>
       <c r="B380" s="17" t="inlineStr">
         <is>
-          <t>TNST @ UGA</t>
+          <t>SC @ CLEM</t>
         </is>
       </c>
       <c r="C380" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 19:00</t>
+          <t>2026-11-28 05:00</t>
         </is>
       </c>
       <c r="D380" s="25" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E380" s="17" t="inlineStr">
         <is>
@@ -25898,17 +25898,17 @@
       </c>
       <c r="F380" s="17" t="inlineStr">
         <is>
-          <t>Over 56.5</t>
+          <t>Over 53.5</t>
         </is>
       </c>
       <c r="G380" s="26" t="n">
-        <v>56.5</v>
+        <v>53.5</v>
       </c>
       <c r="H380" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I380" s="20" t="n">
-        <v>0.4761108790335434</v>
+        <v>0.4761108907812599</v>
       </c>
       <c r="J380" s="20" t="n">
         <v>0.5</v>
@@ -25917,10 +25917,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L380" s="19" t="n">
-        <v>-0.0476986447759804</v>
+        <v>-0.04769863302826394</v>
       </c>
       <c r="M380" s="19" t="n">
-        <v>-0.09106104911778068</v>
+        <v>-0.09106102669032196</v>
       </c>
       <c r="N380" s="20" t="n">
         <v>0</v>
@@ -25933,11 +25933,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q380" s="17" t="inlineStr">
-        <is>
-          <t>TNST isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q380" s="17" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="12" t="inlineStr">
@@ -25947,16 +25943,16 @@
       </c>
       <c r="B381" s="12" t="inlineStr">
         <is>
-          <t>ORE @ USC</t>
+          <t>TNST @ UGA</t>
         </is>
       </c>
       <c r="C381" s="12" t="inlineStr">
         <is>
-          <t>2026-09-26 04:00</t>
+          <t>2026-09-05 19:00</t>
         </is>
       </c>
       <c r="D381" s="22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E381" s="12" t="inlineStr">
         <is>
@@ -25965,17 +25961,17 @@
       </c>
       <c r="F381" s="12" t="inlineStr">
         <is>
-          <t>Over 58.5</t>
+          <t>Over 56.5</t>
         </is>
       </c>
       <c r="G381" s="23" t="n">
-        <v>58.5</v>
+        <v>56.5</v>
       </c>
       <c r="H381" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I381" s="15" t="n">
-        <v>0.4761108771828951</v>
+        <v>0.4761108790335434</v>
       </c>
       <c r="J381" s="15" t="n">
         <v>0.5</v>
@@ -25984,10 +25980,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L381" s="14" t="n">
-        <v>-0.0476986466266287</v>
+        <v>-0.0476986447759804</v>
       </c>
       <c r="M381" s="14" t="n">
-        <v>-0.09106105265083653</v>
+        <v>-0.09106104911778068</v>
       </c>
       <c r="N381" s="15" t="n">
         <v>0</v>
@@ -26000,7 +25996,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q381" s="12" t="n"/>
+      <c r="Q381" s="12" t="inlineStr">
+        <is>
+          <t>TNST isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="17" t="inlineStr">
@@ -26010,16 +26010,16 @@
       </c>
       <c r="B382" s="17" t="inlineStr">
         <is>
-          <t>ALA @ TENN</t>
+          <t>ORE @ USC</t>
         </is>
       </c>
       <c r="C382" s="17" t="inlineStr">
         <is>
-          <t>2026-10-17 04:00</t>
+          <t>2026-09-26 04:00</t>
         </is>
       </c>
       <c r="D382" s="25" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E382" s="17" t="inlineStr">
         <is>
@@ -26028,17 +26028,17 @@
       </c>
       <c r="F382" s="17" t="inlineStr">
         <is>
-          <t>Under 56.5</t>
+          <t>Over 58.5</t>
         </is>
       </c>
       <c r="G382" s="26" t="n">
-        <v>56.5</v>
+        <v>58.5</v>
       </c>
       <c r="H382" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I382" s="20" t="n">
-        <v>0.476110875556195</v>
+        <v>0.4761108771828951</v>
       </c>
       <c r="J382" s="20" t="n">
         <v>0.5</v>
@@ -26047,16 +26047,16 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L382" s="19" t="n">
-        <v>-0.04769864825332881</v>
+        <v>-0.0476986466266287</v>
       </c>
       <c r="M382" s="19" t="n">
-        <v>-0.09106105575635492</v>
+        <v>-0.09106105265083653</v>
       </c>
       <c r="N382" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O382" s="27" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="P382" s="17" t="inlineStr">
         <is>
@@ -26073,16 +26073,16 @@
       </c>
       <c r="B383" s="12" t="inlineStr">
         <is>
-          <t>KENT @ SC</t>
+          <t>ALA @ TENN</t>
         </is>
       </c>
       <c r="C383" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 16:45</t>
+          <t>2026-10-17 04:00</t>
         </is>
       </c>
       <c r="D383" s="22" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E383" s="12" t="inlineStr">
         <is>
@@ -26091,17 +26091,17 @@
       </c>
       <c r="F383" s="12" t="inlineStr">
         <is>
-          <t>Under 53.5</t>
+          <t>Under 56.5</t>
         </is>
       </c>
       <c r="G383" s="23" t="n">
-        <v>53.5</v>
+        <v>56.5</v>
       </c>
       <c r="H383" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I383" s="15" t="n">
-        <v>0.4761108717682891</v>
+        <v>0.476110875556195</v>
       </c>
       <c r="J383" s="15" t="n">
         <v>0.5</v>
@@ -26110,16 +26110,16 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L383" s="14" t="n">
-        <v>-0.04769865204123469</v>
+        <v>-0.04769864825332881</v>
       </c>
       <c r="M383" s="14" t="n">
-        <v>-0.09106106298781158</v>
+        <v>-0.09106105575635492</v>
       </c>
       <c r="N383" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O383" s="24" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="P383" s="12" t="inlineStr">
         <is>
@@ -26136,35 +26136,35 @@
       </c>
       <c r="B384" s="17" t="inlineStr">
         <is>
-          <t>ASU @ ARIZ</t>
+          <t>KENT @ SC</t>
         </is>
       </c>
       <c r="C384" s="17" t="inlineStr">
         <is>
-          <t>2026-11-28 05:00</t>
+          <t>2026-09-05 16:45</t>
         </is>
       </c>
       <c r="D384" s="25" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E384" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F384" s="17" t="inlineStr">
         <is>
-          <t>ARIZ -4.5</t>
+          <t>Under 53.5</t>
         </is>
       </c>
       <c r="G384" s="26" t="n">
-        <v>-4.5</v>
+        <v>53.5</v>
       </c>
       <c r="H384" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I384" s="20" t="n">
-        <v>0.4759178998113145</v>
+        <v>0.4761108717682891</v>
       </c>
       <c r="J384" s="20" t="n">
         <v>0.5</v>
@@ -26173,10 +26173,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L384" s="19" t="n">
-        <v>-0.04789162399820934</v>
+        <v>-0.04769865204123469</v>
       </c>
       <c r="M384" s="19" t="n">
-        <v>-0.09142946399658136</v>
+        <v>-0.09106106298781158</v>
       </c>
       <c r="N384" s="20" t="n">
         <v>0</v>
@@ -26199,7 +26199,7 @@
       </c>
       <c r="B385" s="12" t="inlineStr">
         <is>
-          <t>NCSU @ UNC</t>
+          <t>ASU @ ARIZ</t>
         </is>
       </c>
       <c r="C385" s="12" t="inlineStr">
@@ -26212,22 +26212,22 @@
       </c>
       <c r="E385" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F385" s="12" t="inlineStr">
         <is>
-          <t>Over 55.5</t>
+          <t>ARIZ -4.5</t>
         </is>
       </c>
       <c r="G385" s="23" t="n">
-        <v>55.5</v>
+        <v>-4.5</v>
       </c>
       <c r="H385" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I385" s="15" t="n">
-        <v>0.4741308885459136</v>
+        <v>0.4759178998113145</v>
       </c>
       <c r="J385" s="15" t="n">
         <v>0.5</v>
@@ -26236,10 +26236,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L385" s="14" t="n">
-        <v>-0.04967863526361027</v>
+        <v>-0.04789162399820934</v>
       </c>
       <c r="M385" s="14" t="n">
-        <v>-0.09484103095780133</v>
+        <v>-0.09142946399658136</v>
       </c>
       <c r="N385" s="15" t="n">
         <v>0</v>
@@ -26262,16 +26262,16 @@
       </c>
       <c r="B386" s="17" t="inlineStr">
         <is>
-          <t>VMI @ VT</t>
+          <t>NCSU @ UNC</t>
         </is>
       </c>
       <c r="C386" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-11-28 05:00</t>
         </is>
       </c>
       <c r="D386" s="25" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E386" s="17" t="inlineStr">
         <is>
@@ -26280,17 +26280,17 @@
       </c>
       <c r="F386" s="17" t="inlineStr">
         <is>
-          <t>Over 57.5</t>
+          <t>Over 55.5</t>
         </is>
       </c>
       <c r="G386" s="26" t="n">
-        <v>57.5</v>
+        <v>55.5</v>
       </c>
       <c r="H386" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I386" s="20" t="n">
-        <v>0.4741308851452813</v>
+        <v>0.4741308885459136</v>
       </c>
       <c r="J386" s="20" t="n">
         <v>0.5</v>
@@ -26299,10 +26299,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L386" s="19" t="n">
-        <v>-0.04967863866424249</v>
+        <v>-0.04967863526361027</v>
       </c>
       <c r="M386" s="19" t="n">
-        <v>-0.0948410374499174</v>
+        <v>-0.09484103095780133</v>
       </c>
       <c r="N386" s="20" t="n">
         <v>0</v>
@@ -26315,11 +26315,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q386" s="17" t="inlineStr">
-        <is>
-          <t>VMI isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q386" s="17" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="12" t="inlineStr">
@@ -26329,35 +26325,35 @@
       </c>
       <c r="B387" s="12" t="inlineStr">
         <is>
-          <t>UVA @ VT</t>
+          <t>VMI @ VT</t>
         </is>
       </c>
       <c r="C387" s="12" t="inlineStr">
         <is>
-          <t>2026-11-28 05:00</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D387" s="22" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E387" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F387" s="12" t="inlineStr">
         <is>
-          <t>VT -1.5</t>
+          <t>Over 57.5</t>
         </is>
       </c>
       <c r="G387" s="23" t="n">
-        <v>-1.5</v>
+        <v>57.5</v>
       </c>
       <c r="H387" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I387" s="15" t="n">
-        <v>0.4737252328619687</v>
+        <v>0.4741308851452813</v>
       </c>
       <c r="J387" s="15" t="n">
         <v>0.5</v>
@@ -26366,10 +26362,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L387" s="14" t="n">
-        <v>-0.05008429094755512</v>
+        <v>-0.04967863866424249</v>
       </c>
       <c r="M387" s="14" t="n">
-        <v>-0.09561546453624142</v>
+        <v>-0.0948410374499174</v>
       </c>
       <c r="N387" s="15" t="n">
         <v>0</v>
@@ -26382,7 +26378,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q387" s="12" t="n"/>
+      <c r="Q387" s="12" t="inlineStr">
+        <is>
+          <t>VMI isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="17" t="inlineStr">
@@ -26392,16 +26392,16 @@
       </c>
       <c r="B388" s="17" t="inlineStr">
         <is>
-          <t>NAVY @ ARMY</t>
+          <t>UVA @ VT</t>
         </is>
       </c>
       <c r="C388" s="17" t="inlineStr">
         <is>
-          <t>2026-12-12 20:00</t>
+          <t>2026-11-28 05:00</t>
         </is>
       </c>
       <c r="D388" s="25" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E388" s="17" t="inlineStr">
         <is>
@@ -26410,17 +26410,17 @@
       </c>
       <c r="F388" s="17" t="inlineStr">
         <is>
-          <t>NAVY -2.5</t>
+          <t>VT -1.5</t>
         </is>
       </c>
       <c r="G388" s="26" t="n">
-        <v>2.5</v>
+        <v>-1.5</v>
       </c>
       <c r="H388" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I388" s="20" t="n">
-        <v>0.472672928903868</v>
+        <v>0.4737252328619687</v>
       </c>
       <c r="J388" s="20" t="n">
         <v>0.5</v>
@@ -26429,10 +26429,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L388" s="19" t="n">
-        <v>-0.05113659490565581</v>
+        <v>-0.05008429094755512</v>
       </c>
       <c r="M388" s="19" t="n">
-        <v>-0.09762440845625192</v>
+        <v>-0.09561546453624142</v>
       </c>
       <c r="N388" s="20" t="n">
         <v>0</v>
@@ -26455,35 +26455,35 @@
       </c>
       <c r="B389" s="12" t="inlineStr">
         <is>
-          <t>TEX @ LSU</t>
+          <t>NAVY @ ARMY</t>
         </is>
       </c>
       <c r="C389" s="12" t="inlineStr">
         <is>
-          <t>2026-11-14 05:00</t>
+          <t>2026-12-12 20:00</t>
         </is>
       </c>
       <c r="D389" s="22" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E389" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F389" s="12" t="inlineStr">
         <is>
-          <t>Over 54.5</t>
+          <t>NAVY -2.5</t>
         </is>
       </c>
       <c r="G389" s="23" t="n">
-        <v>54.5</v>
+        <v>2.5</v>
       </c>
       <c r="H389" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I389" s="15" t="n">
-        <v>0.4721534743558814</v>
+        <v>0.472672928903868</v>
       </c>
       <c r="J389" s="15" t="n">
         <v>0.5</v>
@@ -26492,10 +26492,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L389" s="14" t="n">
-        <v>-0.05165604945364244</v>
+        <v>-0.05113659490565581</v>
       </c>
       <c r="M389" s="14" t="n">
-        <v>-0.0986160944114991</v>
+        <v>-0.09762440845625192</v>
       </c>
       <c r="N389" s="15" t="n">
         <v>0</v>
@@ -26518,16 +26518,16 @@
       </c>
       <c r="B390" s="17" t="inlineStr">
         <is>
-          <t>IDHO @ UTAH</t>
+          <t>TEX @ LSU</t>
         </is>
       </c>
       <c r="C390" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 01:00</t>
+          <t>2026-11-14 05:00</t>
         </is>
       </c>
       <c r="D390" s="25" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E390" s="17" t="inlineStr">
         <is>
@@ -26536,17 +26536,17 @@
       </c>
       <c r="F390" s="17" t="inlineStr">
         <is>
-          <t>Under 56.5</t>
+          <t>Over 54.5</t>
         </is>
       </c>
       <c r="G390" s="26" t="n">
-        <v>56.5</v>
+        <v>54.5</v>
       </c>
       <c r="H390" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I390" s="20" t="n">
-        <v>0.4721534645106804</v>
+        <v>0.4721534743558814</v>
       </c>
       <c r="J390" s="20" t="n">
         <v>0.5</v>
@@ -26555,10 +26555,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L390" s="19" t="n">
-        <v>-0.05165605929884343</v>
+        <v>-0.05165604945364244</v>
       </c>
       <c r="M390" s="19" t="n">
-        <v>-0.09861611320688279</v>
+        <v>-0.0986160944114991</v>
       </c>
       <c r="N390" s="20" t="n">
         <v>0</v>
@@ -26571,11 +26571,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q390" s="17" t="inlineStr">
-        <is>
-          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q390" s="17" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="12" t="inlineStr">
@@ -26585,12 +26581,12 @@
       </c>
       <c r="B391" s="12" t="inlineStr">
         <is>
-          <t>ULM @ MSST</t>
+          <t>IDHO @ UTAH</t>
         </is>
       </c>
       <c r="C391" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D391" s="22" t="n">
@@ -26603,17 +26599,17 @@
       </c>
       <c r="F391" s="12" t="inlineStr">
         <is>
-          <t>Under 55.5</t>
+          <t>Under 56.5</t>
         </is>
       </c>
       <c r="G391" s="23" t="n">
-        <v>55.5</v>
+        <v>56.5</v>
       </c>
       <c r="H391" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I391" s="15" t="n">
-        <v>0.4721534639284655</v>
+        <v>0.4721534645106804</v>
       </c>
       <c r="J391" s="15" t="n">
         <v>0.5</v>
@@ -26622,10 +26618,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L391" s="14" t="n">
-        <v>-0.05165605988105837</v>
+        <v>-0.05165605929884343</v>
       </c>
       <c r="M391" s="14" t="n">
-        <v>-0.09861611431838407</v>
+        <v>-0.09861611320688279</v>
       </c>
       <c r="N391" s="15" t="n">
         <v>0</v>
@@ -26638,7 +26634,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q391" s="12" t="n"/>
+      <c r="Q391" s="12" t="inlineStr">
+        <is>
+          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="17" t="inlineStr">
@@ -26648,16 +26648,16 @@
       </c>
       <c r="B392" s="17" t="inlineStr">
         <is>
-          <t>WASH @ ORE</t>
+          <t>ULM @ MSST</t>
         </is>
       </c>
       <c r="C392" s="17" t="inlineStr">
         <is>
-          <t>2026-11-28 05:00</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D392" s="25" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E392" s="17" t="inlineStr">
         <is>
@@ -26666,17 +26666,17 @@
       </c>
       <c r="F392" s="17" t="inlineStr">
         <is>
-          <t>Under 54.5</t>
+          <t>Under 55.5</t>
         </is>
       </c>
       <c r="G392" s="26" t="n">
-        <v>54.5</v>
+        <v>55.5</v>
       </c>
       <c r="H392" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I392" s="20" t="n">
-        <v>0.4721534628948869</v>
+        <v>0.4721534639284655</v>
       </c>
       <c r="J392" s="20" t="n">
         <v>0.5</v>
@@ -26685,10 +26685,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L392" s="19" t="n">
-        <v>-0.05165606091463693</v>
+        <v>-0.05165605988105837</v>
       </c>
       <c r="M392" s="19" t="n">
-        <v>-0.09861611629157951</v>
+        <v>-0.09861611431838407</v>
       </c>
       <c r="N392" s="20" t="n">
         <v>0</v>
@@ -26711,16 +26711,16 @@
       </c>
       <c r="B393" s="12" t="inlineStr">
         <is>
-          <t>FAU @ FLA</t>
+          <t>WASH @ ORE</t>
         </is>
       </c>
       <c r="C393" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:45</t>
+          <t>2026-11-28 05:00</t>
         </is>
       </c>
       <c r="D393" s="22" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E393" s="12" t="inlineStr">
         <is>
@@ -26729,17 +26729,17 @@
       </c>
       <c r="F393" s="12" t="inlineStr">
         <is>
-          <t>Over 58.5</t>
+          <t>Under 54.5</t>
         </is>
       </c>
       <c r="G393" s="23" t="n">
-        <v>58.5</v>
+        <v>54.5</v>
       </c>
       <c r="H393" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I393" s="15" t="n">
-        <v>0.4701788165847314</v>
+        <v>0.4721534628948869</v>
       </c>
       <c r="J393" s="15" t="n">
         <v>0.5</v>
@@ -26748,10 +26748,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L393" s="14" t="n">
-        <v>-0.05363070722479246</v>
+        <v>-0.05165606091463693</v>
       </c>
       <c r="M393" s="14" t="n">
-        <v>-0.1023858956109673</v>
+        <v>-0.09861611629157951</v>
       </c>
       <c r="N393" s="15" t="n">
         <v>0</v>
@@ -26774,12 +26774,12 @@
       </c>
       <c r="B394" s="17" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>FAU @ FLA</t>
         </is>
       </c>
       <c r="C394" s="17" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-09-05 23:45</t>
         </is>
       </c>
       <c r="D394" s="25" t="n">
@@ -26792,17 +26792,17 @@
       </c>
       <c r="F394" s="17" t="inlineStr">
         <is>
-          <t>Under 56.5</t>
+          <t>Over 58.5</t>
         </is>
       </c>
       <c r="G394" s="26" t="n">
-        <v>56.5</v>
+        <v>58.5</v>
       </c>
       <c r="H394" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I394" s="20" t="n">
-        <v>0.4701788149384322</v>
+        <v>0.4701788165847314</v>
       </c>
       <c r="J394" s="20" t="n">
         <v>0.5</v>
@@ -26811,10 +26811,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L394" s="19" t="n">
-        <v>-0.05363070887109167</v>
+        <v>-0.05363070722479246</v>
       </c>
       <c r="M394" s="19" t="n">
-        <v>-0.1023858987539022</v>
+        <v>-0.1023858956109673</v>
       </c>
       <c r="N394" s="20" t="n">
         <v>0</v>
@@ -53686,7 +53686,7 @@
         <v>-5.5</v>
       </c>
       <c r="J12" s="30" t="n">
-        <v>56.5</v>
+        <v>57.5</v>
       </c>
       <c r="K12" s="18" t="n"/>
       <c r="L12" s="18" t="n"/>

--- a/NCAAF_Edge_Model.xlsx
+++ b/NCAAF_Edge_Model.xlsx
@@ -637,7 +637,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-21T21:54:35+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
+          <t>Generated 2026-08-22T04:18:43+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
         </is>
       </c>
     </row>

--- a/NCAAF_Edge_Model.xlsx
+++ b/NCAAF_Edge_Model.xlsx
@@ -637,7 +637,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-22T04:18:43+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
+          <t>Generated 2026-08-22T13:55:24+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
         </is>
       </c>
     </row>

--- a/NCAAF_Edge_Model.xlsx
+++ b/NCAAF_Edge_Model.xlsx
@@ -637,7 +637,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-22T13:55:24+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
+          <t>Generated 2026-08-22T17:44:49+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="P10" s="17" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q10" s="17" t="n"/>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="P12" s="17" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q12" s="17" t="n"/>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="P110" s="17" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q110" s="17" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="P124" s="17" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q124" s="17" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="P148" s="17" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q148" s="17" t="inlineStr">
@@ -11201,7 +11201,7 @@
       </c>
       <c r="P149" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q149" s="12" t="inlineStr">
@@ -11532,7 +11532,7 @@
       </c>
       <c r="P154" s="17" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q154" s="17" t="n"/>
@@ -12611,7 +12611,7 @@
       </c>
       <c r="P171" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q171" s="12" t="n"/>
@@ -14718,7 +14718,7 @@
       </c>
       <c r="P204" s="17" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q204" s="17" t="n"/>
@@ -15671,7 +15671,7 @@
       </c>
       <c r="P219" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q219" s="12" t="n"/>
@@ -16305,7 +16305,7 @@
       </c>
       <c r="P229" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q229" s="12" t="n"/>
@@ -16683,7 +16683,7 @@
       </c>
       <c r="P235" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q235" s="12" t="n"/>
@@ -17191,7 +17191,7 @@
       </c>
       <c r="P243" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q243" s="12" t="n"/>
@@ -18396,7 +18396,7 @@
       </c>
       <c r="P262" s="17" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q262" s="17" t="n"/>
@@ -19743,7 +19743,7 @@
       </c>
       <c r="P283" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q283" s="12" t="n"/>
@@ -21007,7 +21007,7 @@
       </c>
       <c r="P303" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q303" s="12" t="n"/>
@@ -24410,7 +24410,7 @@
       </c>
       <c r="P356" s="17" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q356" s="17" t="n"/>
@@ -25674,7 +25674,7 @@
       </c>
       <c r="P376" s="17" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q376" s="17" t="n"/>
@@ -27021,7 +27021,7 @@
       </c>
       <c r="P397" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q397" s="12" t="n"/>
@@ -28226,7 +28226,7 @@
       </c>
       <c r="P416" s="17" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q416" s="17" t="n"/>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="P424" s="17" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q424" s="17" t="n"/>
@@ -29112,7 +29112,7 @@
       </c>
       <c r="P430" s="17" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q430" s="17" t="n"/>
@@ -29746,7 +29746,7 @@
       </c>
       <c r="P440" s="17" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q440" s="17" t="n"/>
@@ -30699,7 +30699,7 @@
       </c>
       <c r="P455" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q455" s="12" t="n"/>
@@ -32806,7 +32806,7 @@
       </c>
       <c r="P488" s="17" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q488" s="17" t="n"/>
@@ -33885,7 +33885,7 @@
       </c>
       <c r="P505" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q505" s="12" t="n"/>
@@ -34145,7 +34145,7 @@
       </c>
       <c r="P509" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q509" s="12" t="n"/>
@@ -34334,7 +34334,7 @@
       </c>
       <c r="P512" s="17" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q512" s="17" t="n"/>
@@ -36512,7 +36512,7 @@
       </c>
       <c r="P546" s="17" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q546" s="17" t="n"/>
@@ -37993,7 +37993,7 @@
       </c>
       <c r="P569" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q569" s="12" t="n"/>
@@ -41601,7 +41601,7 @@
       </c>
       <c r="P625" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q625" s="12" t="n"/>
@@ -41928,7 +41928,7 @@
       </c>
       <c r="P630" s="17" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q630" s="17" t="n"/>
@@ -53377,7 +53377,7 @@
       <c r="L5" s="13" t="n"/>
       <c r="M5" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
     </row>
@@ -53422,7 +53422,7 @@
       <c r="L6" s="18" t="n"/>
       <c r="M6" s="17" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
     </row>
@@ -53467,7 +53467,7 @@
       <c r="L7" s="13" t="n"/>
       <c r="M7" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
     </row>
@@ -53512,7 +53512,7 @@
       <c r="L8" s="18" t="n"/>
       <c r="M8" s="17" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
     </row>
@@ -53557,7 +53557,7 @@
       <c r="L9" s="13" t="n"/>
       <c r="M9" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
     </row>
@@ -53602,7 +53602,7 @@
       <c r="L10" s="18" t="n"/>
       <c r="M10" s="17" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
     </row>
@@ -53647,7 +53647,7 @@
       <c r="L11" s="13" t="n"/>
       <c r="M11" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
     </row>
@@ -53692,7 +53692,7 @@
       <c r="L12" s="18" t="n"/>
       <c r="M12" s="17" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
     </row>

--- a/NCAAF_Edge_Model.xlsx
+++ b/NCAAF_Edge_Model.xlsx
@@ -637,7 +637,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-22T17:44:49+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
+          <t>Generated 2026-08-22T21:45:54+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="P10" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q10" s="17" t="n"/>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="P12" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q12" s="17" t="n"/>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="P110" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q110" s="17" t="inlineStr">
@@ -9141,12 +9141,12 @@
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>FIU @ USF</t>
+          <t>SAC @ EMU</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-08-29 22:30</t>
         </is>
       </c>
       <c r="D119" s="22" t="n">
@@ -9159,17 +9159,17 @@
       </c>
       <c r="F119" s="12" t="inlineStr">
         <is>
-          <t>FIU +13.5</t>
+          <t>SAC +9.5</t>
         </is>
       </c>
       <c r="G119" s="23" t="n">
-        <v>-13.5</v>
+        <v>-9.5</v>
       </c>
       <c r="H119" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I119" s="15" t="n">
-        <v>0.6366620259462109</v>
+        <v>0.6373042089106218</v>
       </c>
       <c r="J119" s="15" t="n">
         <v>0.5</v>
@@ -9178,10 +9178,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L119" s="14" t="n">
-        <v>0.1128525021366871</v>
+        <v>0.1134946851010979</v>
       </c>
       <c r="M119" s="14" t="n">
-        <v>0.2154456858973118</v>
+        <v>0.2166716715566417</v>
       </c>
       <c r="N119" s="15" t="n">
         <v>0</v>
@@ -9208,12 +9208,12 @@
       </c>
       <c r="B120" s="17" t="inlineStr">
         <is>
-          <t>URI @ TEM</t>
+          <t>FIU @ USF</t>
         </is>
       </c>
       <c r="C120" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 18:00</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D120" s="25" t="n">
@@ -9226,17 +9226,17 @@
       </c>
       <c r="F120" s="17" t="inlineStr">
         <is>
-          <t>URI +10</t>
+          <t>FIU +13.5</t>
         </is>
       </c>
       <c r="G120" s="26" t="n">
-        <v>-10</v>
+        <v>-13.5</v>
       </c>
       <c r="H120" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I120" s="20" t="n">
-        <v>0.6338812332726149</v>
+        <v>0.6366620259462109</v>
       </c>
       <c r="J120" s="20" t="n">
         <v>0.5</v>
@@ -9245,13 +9245,13 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L120" s="19" t="n">
-        <v>0.1100717094630911</v>
+        <v>0.1128525021366871</v>
       </c>
       <c r="M120" s="19" t="n">
-        <v>0.2031606380380864</v>
+        <v>0.2154456858973118</v>
       </c>
       <c r="N120" s="20" t="n">
-        <v>0.0332</v>
+        <v>0</v>
       </c>
       <c r="O120" s="27" t="n">
         <v>0.45</v>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="Q120" s="17" t="inlineStr">
         <is>
-          <t>URI isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>outside the top 10 plays for this week</t>
         </is>
       </c>
     </row>
@@ -9275,16 +9275,16 @@
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>ISU @ IOWA</t>
+          <t>URI @ TEM</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12 23:30</t>
+          <t>2026-09-05 18:00</t>
         </is>
       </c>
       <c r="D121" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E121" s="12" t="inlineStr">
         <is>
@@ -9293,17 +9293,17 @@
       </c>
       <c r="F121" s="12" t="inlineStr">
         <is>
-          <t>ISU +11.5</t>
+          <t>URI +10</t>
         </is>
       </c>
       <c r="G121" s="23" t="n">
-        <v>-11.5</v>
+        <v>-10</v>
       </c>
       <c r="H121" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I121" s="15" t="n">
-        <v>0.6332052980165461</v>
+        <v>0.6338812332726149</v>
       </c>
       <c r="J121" s="15" t="n">
         <v>0.5</v>
@@ -9312,13 +9312,13 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L121" s="14" t="n">
-        <v>0.1093957742070223</v>
+        <v>0.1100717094630911</v>
       </c>
       <c r="M121" s="14" t="n">
-        <v>0.2088464780315881</v>
+        <v>0.2031606380380864</v>
       </c>
       <c r="N121" s="15" t="n">
-        <v>0</v>
+        <v>0.0332</v>
       </c>
       <c r="O121" s="24" t="n">
         <v>0.45</v>
@@ -9330,7 +9330,7 @@
       </c>
       <c r="Q121" s="12" t="inlineStr">
         <is>
-          <t>correlated with a stronger play on the same game</t>
+          <t>URI isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -9342,35 +9342,35 @@
       </c>
       <c r="B122" s="17" t="inlineStr">
         <is>
-          <t>TAR @ BGSU</t>
+          <t>ISU @ IOWA</t>
         </is>
       </c>
       <c r="C122" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-09-12 23:30</t>
         </is>
       </c>
       <c r="D122" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E122" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F122" s="17" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
+          <t>ISU +11.5</t>
         </is>
       </c>
       <c r="G122" s="26" t="n">
-        <v>47.5</v>
+        <v>-11.5</v>
       </c>
       <c r="H122" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I122" s="20" t="n">
-        <v>0.6321649686522863</v>
+        <v>0.6332052980165461</v>
       </c>
       <c r="J122" s="20" t="n">
         <v>0.5</v>
@@ -9379,10 +9379,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L122" s="19" t="n">
-        <v>0.1083554448427625</v>
+        <v>0.1093957742070223</v>
       </c>
       <c r="M122" s="19" t="n">
-        <v>0.2068603946998194</v>
+        <v>0.2088464780315881</v>
       </c>
       <c r="N122" s="20" t="n">
         <v>0</v>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="Q122" s="17" t="inlineStr">
         <is>
-          <t>TAR isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>correlated with a stronger play on the same game</t>
         </is>
       </c>
     </row>
@@ -9409,7 +9409,7 @@
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>OHIO @ NEB</t>
+          <t>TAR @ BGSU</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
@@ -9437,7 +9437,7 @@
         <v>-110</v>
       </c>
       <c r="I123" s="15" t="n">
-        <v>0.6306198692024518</v>
+        <v>0.6321649686522863</v>
       </c>
       <c r="J123" s="15" t="n">
         <v>0.5</v>
@@ -9446,10 +9446,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L123" s="14" t="n">
-        <v>0.106810345392928</v>
+        <v>0.1083554448427625</v>
       </c>
       <c r="M123" s="14" t="n">
-        <v>0.203910659386499</v>
+        <v>0.2068603946998194</v>
       </c>
       <c r="N123" s="15" t="n">
         <v>0</v>
@@ -9464,7 +9464,7 @@
       </c>
       <c r="Q123" s="12" t="inlineStr">
         <is>
-          <t>correlated with a stronger play on the same game</t>
+          <t>TAR isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -9476,12 +9476,12 @@
       </c>
       <c r="B124" s="17" t="inlineStr">
         <is>
-          <t>SAC @ EMU</t>
+          <t>OHIO @ NEB</t>
         </is>
       </c>
       <c r="C124" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 22:30</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D124" s="25" t="n">
@@ -9489,22 +9489,22 @@
       </c>
       <c r="E124" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F124" s="17" t="inlineStr">
         <is>
-          <t>SAC +8.5</t>
+          <t>Over 47.5</t>
         </is>
       </c>
       <c r="G124" s="26" t="n">
-        <v>-8.5</v>
+        <v>47.5</v>
       </c>
       <c r="H124" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I124" s="20" t="n">
-        <v>0.6278769996316718</v>
+        <v>0.6306198692024518</v>
       </c>
       <c r="J124" s="20" t="n">
         <v>0.5</v>
@@ -9513,10 +9513,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L124" s="19" t="n">
-        <v>0.1040674758221479</v>
+        <v>0.106810345392928</v>
       </c>
       <c r="M124" s="19" t="n">
-        <v>0.1986742720241007</v>
+        <v>0.203910659386499</v>
       </c>
       <c r="N124" s="20" t="n">
         <v>0</v>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="P124" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q124" s="17" t="inlineStr">
         <is>
-          <t>outside the top 10 plays for this week</t>
+          <t>correlated with a stronger play on the same game</t>
         </is>
       </c>
     </row>
@@ -11134,7 +11134,7 @@
       </c>
       <c r="P148" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q148" s="17" t="inlineStr">
@@ -11201,7 +11201,7 @@
       </c>
       <c r="P149" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q149" s="12" t="inlineStr">
@@ -11532,7 +11532,7 @@
       </c>
       <c r="P154" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q154" s="17" t="n"/>
@@ -12611,7 +12611,7 @@
       </c>
       <c r="P171" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q171" s="12" t="n"/>
@@ -14718,7 +14718,7 @@
       </c>
       <c r="P204" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q204" s="17" t="n"/>
@@ -15671,7 +15671,7 @@
       </c>
       <c r="P219" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q219" s="12" t="n"/>
@@ -16305,7 +16305,7 @@
       </c>
       <c r="P229" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q229" s="12" t="n"/>
@@ -16683,7 +16683,7 @@
       </c>
       <c r="P235" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q235" s="12" t="n"/>
@@ -17191,7 +17191,7 @@
       </c>
       <c r="P243" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q243" s="12" t="n"/>
@@ -18396,7 +18396,7 @@
       </c>
       <c r="P262" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q262" s="17" t="n"/>
@@ -19743,7 +19743,7 @@
       </c>
       <c r="P283" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q283" s="12" t="n"/>
@@ -21007,7 +21007,7 @@
       </c>
       <c r="P303" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q303" s="12" t="n"/>
@@ -24410,7 +24410,7 @@
       </c>
       <c r="P356" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q356" s="17" t="n"/>
@@ -25674,7 +25674,7 @@
       </c>
       <c r="P376" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q376" s="17" t="n"/>
@@ -27021,7 +27021,7 @@
       </c>
       <c r="P397" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q397" s="12" t="n"/>
@@ -28226,7 +28226,7 @@
       </c>
       <c r="P416" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q416" s="17" t="n"/>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="P424" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q424" s="17" t="n"/>
@@ -29112,7 +29112,7 @@
       </c>
       <c r="P430" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q430" s="17" t="n"/>
@@ -29746,7 +29746,7 @@
       </c>
       <c r="P440" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q440" s="17" t="n"/>
@@ -30699,7 +30699,7 @@
       </c>
       <c r="P455" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q455" s="12" t="n"/>
@@ -32806,7 +32806,7 @@
       </c>
       <c r="P488" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q488" s="17" t="n"/>
@@ -33885,7 +33885,7 @@
       </c>
       <c r="P505" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q505" s="12" t="n"/>
@@ -34145,7 +34145,7 @@
       </c>
       <c r="P509" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q509" s="12" t="n"/>
@@ -34334,7 +34334,7 @@
       </c>
       <c r="P512" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q512" s="17" t="n"/>
@@ -36462,12 +36462,12 @@
       </c>
       <c r="B546" s="17" t="inlineStr">
         <is>
-          <t>SAC @ EMU</t>
+          <t>OHIO @ NEB</t>
         </is>
       </c>
       <c r="C546" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 22:30</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D546" s="25" t="n">
@@ -36475,22 +36475,22 @@
       </c>
       <c r="E546" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F546" s="17" t="inlineStr">
         <is>
-          <t>EMU -8.5</t>
+          <t>Under 47.5</t>
         </is>
       </c>
       <c r="G546" s="26" t="n">
-        <v>-8.5</v>
+        <v>47.5</v>
       </c>
       <c r="H546" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I546" s="20" t="n">
-        <v>0.3721230003683282</v>
+        <v>0.3693801307975482</v>
       </c>
       <c r="J546" s="20" t="n">
         <v>0.5</v>
@@ -36499,10 +36499,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L546" s="19" t="n">
-        <v>-0.1516865234411957</v>
+        <v>-0.1544293930119757</v>
       </c>
       <c r="M546" s="19" t="n">
-        <v>-0.2895833629331916</v>
+        <v>-0.2948197502955898</v>
       </c>
       <c r="N546" s="20" t="n">
         <v>0</v>
@@ -36512,7 +36512,7 @@
       </c>
       <c r="P546" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q546" s="17" t="n"/>
@@ -36525,35 +36525,35 @@
       </c>
       <c r="B547" s="12" t="inlineStr">
         <is>
-          <t>OHIO @ NEB</t>
+          <t>MIZ @ KU</t>
         </is>
       </c>
       <c r="C547" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-09-12 00:00</t>
         </is>
       </c>
       <c r="D547" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E547" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F547" s="12" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
+          <t>MIZ -7</t>
         </is>
       </c>
       <c r="G547" s="23" t="n">
-        <v>47.5</v>
+        <v>7</v>
       </c>
       <c r="H547" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I547" s="15" t="n">
-        <v>0.3693801307975482</v>
+        <v>0.3681981876751432</v>
       </c>
       <c r="J547" s="15" t="n">
         <v>0.5</v>
@@ -36562,13 +36562,13 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L547" s="14" t="n">
-        <v>-0.1544293930119757</v>
+        <v>-0.1556113361343806</v>
       </c>
       <c r="M547" s="14" t="n">
-        <v>-0.2948197502955898</v>
+        <v>-0.2848080826211447</v>
       </c>
       <c r="N547" s="15" t="n">
-        <v>0</v>
+        <v>0.0413</v>
       </c>
       <c r="O547" s="24" t="n">
         <v>0.45</v>
@@ -36588,35 +36588,35 @@
       </c>
       <c r="B548" s="17" t="inlineStr">
         <is>
-          <t>MIZ @ KU</t>
+          <t>TAR @ BGSU</t>
         </is>
       </c>
       <c r="C548" s="17" t="inlineStr">
         <is>
-          <t>2026-09-12 00:00</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D548" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E548" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F548" s="17" t="inlineStr">
         <is>
-          <t>MIZ -7</t>
+          <t>Under 47.5</t>
         </is>
       </c>
       <c r="G548" s="26" t="n">
-        <v>7</v>
+        <v>47.5</v>
       </c>
       <c r="H548" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I548" s="20" t="n">
-        <v>0.3681981876751432</v>
+        <v>0.3678350313477137</v>
       </c>
       <c r="J548" s="20" t="n">
         <v>0.5</v>
@@ -36625,13 +36625,13 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L548" s="19" t="n">
-        <v>-0.1556113361343806</v>
+        <v>-0.1559744924618102</v>
       </c>
       <c r="M548" s="19" t="n">
-        <v>-0.2848080826211447</v>
+        <v>-0.2977694856089103</v>
       </c>
       <c r="N548" s="20" t="n">
-        <v>0.0413</v>
+        <v>0</v>
       </c>
       <c r="O548" s="27" t="n">
         <v>0.45</v>
@@ -36641,7 +36641,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q548" s="17" t="n"/>
+      <c r="Q548" s="17" t="inlineStr">
+        <is>
+          <t>TAR isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" s="12" t="inlineStr">
@@ -36651,35 +36655,35 @@
       </c>
       <c r="B549" s="12" t="inlineStr">
         <is>
-          <t>TAR @ BGSU</t>
+          <t>ISU @ IOWA</t>
         </is>
       </c>
       <c r="C549" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-09-12 23:30</t>
         </is>
       </c>
       <c r="D549" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E549" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F549" s="12" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
+          <t>IOWA -11.5</t>
         </is>
       </c>
       <c r="G549" s="23" t="n">
-        <v>47.5</v>
+        <v>-11.5</v>
       </c>
       <c r="H549" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I549" s="15" t="n">
-        <v>0.3678350313477137</v>
+        <v>0.3667947019834538</v>
       </c>
       <c r="J549" s="15" t="n">
         <v>0.5</v>
@@ -36688,10 +36692,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L549" s="14" t="n">
-        <v>-0.1559744924618102</v>
+        <v>-0.15701482182607</v>
       </c>
       <c r="M549" s="14" t="n">
-        <v>-0.2977694856089103</v>
+        <v>-0.299755568940679</v>
       </c>
       <c r="N549" s="15" t="n">
         <v>0</v>
@@ -36704,11 +36708,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q549" s="12" t="inlineStr">
-        <is>
-          <t>TAR isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q549" s="12" t="n"/>
     </row>
     <row r="550">
       <c r="A550" s="17" t="inlineStr">
@@ -36718,16 +36718,16 @@
       </c>
       <c r="B550" s="17" t="inlineStr">
         <is>
-          <t>ISU @ IOWA</t>
+          <t>MICH @ OSU</t>
         </is>
       </c>
       <c r="C550" s="17" t="inlineStr">
         <is>
-          <t>2026-09-12 23:30</t>
+          <t>2026-11-28 17:00</t>
         </is>
       </c>
       <c r="D550" s="25" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E550" s="17" t="inlineStr">
         <is>
@@ -36736,17 +36736,17 @@
       </c>
       <c r="F550" s="17" t="inlineStr">
         <is>
-          <t>IOWA -11.5</t>
+          <t>OSU -13.5</t>
         </is>
       </c>
       <c r="G550" s="26" t="n">
-        <v>-11.5</v>
+        <v>-13.5</v>
       </c>
       <c r="H550" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I550" s="20" t="n">
-        <v>0.3667947019834538</v>
+        <v>0.3661416831903596</v>
       </c>
       <c r="J550" s="20" t="n">
         <v>0.5</v>
@@ -36755,10 +36755,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L550" s="19" t="n">
-        <v>-0.15701482182607</v>
+        <v>-0.1576678406191643</v>
       </c>
       <c r="M550" s="19" t="n">
-        <v>-0.299755568940679</v>
+        <v>-0.3010022411820408</v>
       </c>
       <c r="N550" s="20" t="n">
         <v>0</v>
@@ -36781,16 +36781,16 @@
       </c>
       <c r="B551" s="12" t="inlineStr">
         <is>
-          <t>MICH @ OSU</t>
+          <t>URI @ TEM</t>
         </is>
       </c>
       <c r="C551" s="12" t="inlineStr">
         <is>
-          <t>2026-11-28 17:00</t>
+          <t>2026-09-05 18:00</t>
         </is>
       </c>
       <c r="D551" s="22" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E551" s="12" t="inlineStr">
         <is>
@@ -36799,17 +36799,17 @@
       </c>
       <c r="F551" s="12" t="inlineStr">
         <is>
-          <t>OSU -13.5</t>
+          <t>TEM -10</t>
         </is>
       </c>
       <c r="G551" s="23" t="n">
-        <v>-13.5</v>
+        <v>-10</v>
       </c>
       <c r="H551" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I551" s="15" t="n">
-        <v>0.3661416831903596</v>
+        <v>0.366118766727385</v>
       </c>
       <c r="J551" s="15" t="n">
         <v>0.5</v>
@@ -36818,13 +36818,13 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L551" s="14" t="n">
-        <v>-0.1576678406191643</v>
+        <v>-0.1576907570821388</v>
       </c>
       <c r="M551" s="14" t="n">
-        <v>-0.3010022411820408</v>
+        <v>-0.2910516696595741</v>
       </c>
       <c r="N551" s="15" t="n">
-        <v>0</v>
+        <v>0.0332</v>
       </c>
       <c r="O551" s="24" t="n">
         <v>0.45</v>
@@ -36834,7 +36834,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q551" s="12" t="n"/>
+      <c r="Q551" s="12" t="inlineStr">
+        <is>
+          <t>URI isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" s="17" t="inlineStr">
@@ -36844,16 +36848,16 @@
       </c>
       <c r="B552" s="17" t="inlineStr">
         <is>
-          <t>URI @ TEM</t>
+          <t>HOU @ TTU</t>
         </is>
       </c>
       <c r="C552" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 18:00</t>
+          <t>2026-09-19 00:00</t>
         </is>
       </c>
       <c r="D552" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E552" s="17" t="inlineStr">
         <is>
@@ -36862,17 +36866,17 @@
       </c>
       <c r="F552" s="17" t="inlineStr">
         <is>
-          <t>TEM -10</t>
+          <t>TTU -13.5</t>
         </is>
       </c>
       <c r="G552" s="26" t="n">
-        <v>-10</v>
+        <v>-13.5</v>
       </c>
       <c r="H552" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I552" s="20" t="n">
-        <v>0.366118766727385</v>
+        <v>0.3658031010190383</v>
       </c>
       <c r="J552" s="20" t="n">
         <v>0.5</v>
@@ -36881,13 +36885,13 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L552" s="19" t="n">
-        <v>-0.1576907570821388</v>
+        <v>-0.1580064227904855</v>
       </c>
       <c r="M552" s="19" t="n">
-        <v>-0.2910516696595741</v>
+        <v>-0.3016486253272904</v>
       </c>
       <c r="N552" s="20" t="n">
-        <v>0.0332</v>
+        <v>0</v>
       </c>
       <c r="O552" s="27" t="n">
         <v>0.45</v>
@@ -36897,11 +36901,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q552" s="17" t="inlineStr">
-        <is>
-          <t>URI isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q552" s="17" t="n"/>
     </row>
     <row r="553">
       <c r="A553" s="12" t="inlineStr">
@@ -36911,16 +36911,16 @@
       </c>
       <c r="B553" s="12" t="inlineStr">
         <is>
-          <t>HOU @ TTU</t>
+          <t>FIU @ USF</t>
         </is>
       </c>
       <c r="C553" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 00:00</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D553" s="22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E553" s="12" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
       </c>
       <c r="F553" s="12" t="inlineStr">
         <is>
-          <t>TTU -13.5</t>
+          <t>USF -13.5</t>
         </is>
       </c>
       <c r="G553" s="23" t="n">
@@ -36939,7 +36939,7 @@
         <v>-110</v>
       </c>
       <c r="I553" s="15" t="n">
-        <v>0.3658031010190383</v>
+        <v>0.3633379740537891</v>
       </c>
       <c r="J553" s="15" t="n">
         <v>0.5</v>
@@ -36948,10 +36948,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L553" s="14" t="n">
-        <v>-0.1580064227904855</v>
+        <v>-0.1604715497557347</v>
       </c>
       <c r="M553" s="14" t="n">
-        <v>-0.3016486253272904</v>
+        <v>-0.3063547768064026</v>
       </c>
       <c r="N553" s="15" t="n">
         <v>0</v>
@@ -36974,12 +36974,12 @@
       </c>
       <c r="B554" s="17" t="inlineStr">
         <is>
-          <t>FIU @ USF</t>
+          <t>SAC @ EMU</t>
         </is>
       </c>
       <c r="C554" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-08-29 22:30</t>
         </is>
       </c>
       <c r="D554" s="25" t="n">
@@ -36992,17 +36992,17 @@
       </c>
       <c r="F554" s="17" t="inlineStr">
         <is>
-          <t>USF -13.5</t>
+          <t>EMU -9.5</t>
         </is>
       </c>
       <c r="G554" s="26" t="n">
-        <v>-13.5</v>
+        <v>-9.5</v>
       </c>
       <c r="H554" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I554" s="20" t="n">
-        <v>0.3633379740537891</v>
+        <v>0.3626957910893782</v>
       </c>
       <c r="J554" s="20" t="n">
         <v>0.5</v>
@@ -37011,10 +37011,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L554" s="19" t="n">
-        <v>-0.1604715497557347</v>
+        <v>-0.1611137327201456</v>
       </c>
       <c r="M554" s="19" t="n">
-        <v>-0.3063547768064026</v>
+        <v>-0.3075807624657325</v>
       </c>
       <c r="N554" s="20" t="n">
         <v>0</v>
@@ -37993,7 +37993,7 @@
       </c>
       <c r="P569" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q569" s="12" t="n"/>
@@ -41601,7 +41601,7 @@
       </c>
       <c r="P625" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q625" s="12" t="n"/>
@@ -41928,7 +41928,7 @@
       </c>
       <c r="P630" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q630" s="17" t="n"/>
@@ -53377,7 +53377,7 @@
       <c r="L5" s="13" t="n"/>
       <c r="M5" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>
@@ -53422,7 +53422,7 @@
       <c r="L6" s="18" t="n"/>
       <c r="M6" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>
@@ -53467,7 +53467,7 @@
       <c r="L7" s="13" t="n"/>
       <c r="M7" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>
@@ -53512,7 +53512,7 @@
       <c r="L8" s="18" t="n"/>
       <c r="M8" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>
@@ -53548,7 +53548,7 @@
       </c>
       <c r="H9" s="12" t="inlineStr"/>
       <c r="I9" s="23" t="n">
-        <v>-8.5</v>
+        <v>-9.5</v>
       </c>
       <c r="J9" s="29" t="n">
         <v>52.5</v>
@@ -53557,7 +53557,7 @@
       <c r="L9" s="13" t="n"/>
       <c r="M9" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>
@@ -53602,7 +53602,7 @@
       <c r="L10" s="18" t="n"/>
       <c r="M10" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>
@@ -53647,7 +53647,7 @@
       <c r="L11" s="13" t="n"/>
       <c r="M11" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>
@@ -53692,7 +53692,7 @@
       <c r="L12" s="18" t="n"/>
       <c r="M12" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>

--- a/NCAAF_Edge_Model.xlsx
+++ b/NCAAF_Edge_Model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Board" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bet Ledger" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Power Ratings" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Games &amp; Results" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model Health" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model History" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Board" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Bet Ledger" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Power Ratings" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Games &amp; Results" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Settings" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Model Health" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Model History" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -269,8 +269,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BoardTable" displayName="BoardTable" ref="A4:Q84" headerRowCount="1">
-  <autoFilter ref="A4:Q84"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BoardTable" displayName="BoardTable" ref="A4:Q50" headerRowCount="1">
+  <autoFilter ref="A4:Q50"/>
   <tableColumns count="17">
     <tableColumn id="1" name="Tier"/>
     <tableColumn id="2" name="Game"/>
@@ -638,7 +638,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-23T18:59:30+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
+          <t>Generated 2026-08-23T19:08:04+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q84"/>
+  <dimension ref="A1:Q50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>BCU @ UCF</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D5" s="13" t="n">
@@ -1140,44 +1140,44 @@
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>BCU +42.5</t>
+          <t>SJSU +38.5</t>
         </is>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-42.5</v>
+        <v>-38.5</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-112</v>
+        <v>-118</v>
       </c>
       <c r="I5" s="16" t="n">
-        <v>0.7517481901856816</v>
+        <v>0.7563609789069304</v>
       </c>
       <c r="J5" s="16" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5173641257162701</v>
       </c>
       <c r="K5" s="16" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5412844036697247</v>
       </c>
       <c r="L5" s="17" t="n">
-        <v>0.2234463033932288</v>
+        <v>0.2150765752372057</v>
       </c>
       <c r="M5" s="17" t="n">
-        <v>0.4229519314228973</v>
+        <v>0.3973448593365325</v>
       </c>
       <c r="N5" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O5" s="18" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P5" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q5" s="12" t="inlineStr">
         <is>
-          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>MRMK @ DEL</t>
+          <t>NMSU @ FSU</t>
         </is>
       </c>
       <c r="C6" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D6" s="20" t="n">
@@ -1207,44 +1207,44 @@
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>MRMK +28.5</t>
+          <t>NMSU +31.5</t>
         </is>
       </c>
       <c r="G6" s="21" t="n">
-        <v>-28.5</v>
+        <v>-31.5</v>
       </c>
       <c r="H6" s="22" t="n">
-        <v>-108</v>
+        <v>-115</v>
       </c>
       <c r="I6" s="23" t="n">
-        <v>0.7386849373798826</v>
+        <v>0.7484052544756881</v>
       </c>
       <c r="J6" s="23" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K6" s="23" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L6" s="24" t="n">
-        <v>0.2194541681491133</v>
+        <v>0.2135215335454556</v>
       </c>
       <c r="M6" s="24" t="n">
-        <v>0.4226524719908851</v>
+        <v>0.3991924322806341</v>
       </c>
       <c r="N6" s="23" t="n">
         <v>0</v>
       </c>
       <c r="O6" s="25" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P6" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q6" s="19" t="inlineStr">
         <is>
-          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>MASS @ RUTG</t>
+          <t>NMSU @ FSU</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 22:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D7" s="13" t="n">
@@ -1269,49 +1269,47 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>MASS +30.5</t>
-        </is>
-      </c>
-      <c r="G7" s="14" t="n">
-        <v>-30.5</v>
-      </c>
+          <t>NMSU ML</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="n"/>
       <c r="H7" s="15" t="n">
-        <v>-108</v>
+        <v>2000</v>
       </c>
       <c r="I7" s="16" t="n">
-        <v>0.7362293114467701</v>
+        <v>0.2189772153156186</v>
       </c>
       <c r="J7" s="16" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.0461215932914046</v>
       </c>
       <c r="K7" s="16" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.04761904761904762</v>
       </c>
       <c r="L7" s="17" t="n">
-        <v>0.2169985422160008</v>
+        <v>0.171358167696571</v>
       </c>
       <c r="M7" s="17" t="n">
-        <v>0.4179231183419276</v>
+        <v>3.598521521627991</v>
       </c>
       <c r="N7" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O7" s="18" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P7" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q7" s="12" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>price outside allowed range</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1321,12 @@
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>JVST @ NDSU</t>
         </is>
       </c>
       <c r="C8" s="19" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-08-29 21:30</t>
         </is>
       </c>
       <c r="D8" s="20" t="n">
@@ -1336,44 +1334,44 @@
       </c>
       <c r="E8" s="19" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F8" s="19" t="inlineStr">
         <is>
-          <t>SJSU +38.5</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="G8" s="21" t="n">
-        <v>-38.5</v>
+        <v>46.5</v>
       </c>
       <c r="H8" s="22" t="n">
-        <v>-118</v>
+        <v>-110</v>
       </c>
       <c r="I8" s="23" t="n">
-        <v>0.7563609789069304</v>
+        <v>0.6553348680813179</v>
       </c>
       <c r="J8" s="23" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.5</v>
       </c>
       <c r="K8" s="23" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L8" s="24" t="n">
-        <v>0.2150765752372057</v>
+        <v>0.1315253442717941</v>
       </c>
       <c r="M8" s="24" t="n">
-        <v>0.3973448593365325</v>
+        <v>0.2510938390643342</v>
       </c>
       <c r="N8" s="23" t="n">
         <v>0</v>
       </c>
       <c r="O8" s="25" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P8" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q8" s="19" t="inlineStr">
@@ -1390,12 +1388,12 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>NMSU @ FSU</t>
+          <t>SAC @ EMU</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-08-29 22:30</t>
         </is>
       </c>
       <c r="D9" s="13" t="n">
@@ -1408,39 +1406,39 @@
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>NMSU +31.5</t>
+          <t>SAC +9.5</t>
         </is>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-31.5</v>
+        <v>-9.5</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="I9" s="16" t="n">
-        <v>0.7484052544756881</v>
+        <v>0.6373042089106218</v>
       </c>
       <c r="J9" s="16" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5</v>
       </c>
       <c r="K9" s="16" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L9" s="17" t="n">
-        <v>0.2135215335454556</v>
+        <v>0.1134946851010979</v>
       </c>
       <c r="M9" s="17" t="n">
-        <v>0.3991924322806341</v>
+        <v>0.2166716715566417</v>
       </c>
       <c r="N9" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O9" s="18" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P9" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q9" s="12" t="inlineStr">
@@ -1457,12 +1455,12 @@
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>ALB @ BUFF</t>
+          <t>SAC @ EMU</t>
         </is>
       </c>
       <c r="C10" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-29 22:30</t>
         </is>
       </c>
       <c r="D10" s="20" t="n">
@@ -1470,49 +1468,47 @@
       </c>
       <c r="E10" s="19" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F10" s="19" t="inlineStr">
         <is>
-          <t>ALB +24.5</t>
-        </is>
-      </c>
-      <c r="G10" s="21" t="n">
-        <v>-24.5</v>
-      </c>
+          <t>SAC ML</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="n"/>
       <c r="H10" s="22" t="n">
-        <v>-112</v>
+        <v>280</v>
       </c>
       <c r="I10" s="23" t="n">
-        <v>0.7342550223888921</v>
+        <v>0.3686221870504205</v>
       </c>
       <c r="J10" s="23" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.2522172949002217</v>
       </c>
       <c r="K10" s="23" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="L10" s="24" t="n">
-        <v>0.2059531355964392</v>
+        <v>0.1054642923135784</v>
       </c>
       <c r="M10" s="24" t="n">
-        <v>0.3898398638075457</v>
+        <v>0.4007643107915979</v>
       </c>
       <c r="N10" s="23" t="n">
         <v>0</v>
       </c>
       <c r="O10" s="25" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P10" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q10" s="19" t="inlineStr">
         <is>
-          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1520,12 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>MRMK @ DEL</t>
+          <t>HAW @ STAN</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D11" s="13" t="n">
@@ -1537,47 +1533,49 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>MRMK ML</t>
-        </is>
-      </c>
-      <c r="G11" s="14" t="n"/>
+          <t>Over 49.5</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>49.5</v>
+      </c>
       <c r="H11" s="15" t="n">
-        <v>3000</v>
+        <v>-105</v>
       </c>
       <c r="I11" s="16" t="n">
-        <v>0.2342202661742625</v>
+        <v>0.5955932130438462</v>
       </c>
       <c r="J11" s="16" t="n">
-        <v>0.03155263980006248</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K11" s="16" t="n">
-        <v>0.03225806451612903</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L11" s="17" t="n">
-        <v>0.2019622016581335</v>
+        <v>0.08339809109262664</v>
       </c>
       <c r="M11" s="17" t="n">
-        <v>6.260828251402137</v>
+        <v>0.1628248445141758</v>
       </c>
       <c r="N11" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O11" s="18" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P11" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q11" s="12" t="inlineStr">
         <is>
-          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1587,12 @@
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>AKR @ WAKE</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C12" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D12" s="20" t="n">
@@ -1607,17 +1605,17 @@
       </c>
       <c r="F12" s="19" t="inlineStr">
         <is>
-          <t>AKR +23.5</t>
+          <t>UNC +7.5</t>
         </is>
       </c>
       <c r="G12" s="21" t="n">
-        <v>-23.5</v>
+        <v>-7.5</v>
       </c>
       <c r="H12" s="22" t="n">
         <v>-108</v>
       </c>
       <c r="I12" s="23" t="n">
-        <v>0.7202139758215249</v>
+        <v>0.5993079841952912</v>
       </c>
       <c r="J12" s="23" t="n">
         <v>0.4956702459300312</v>
@@ -1626,20 +1624,20 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L12" s="24" t="n">
-        <v>0.2009832065907556</v>
+        <v>0.08007721496452191</v>
       </c>
       <c r="M12" s="24" t="n">
-        <v>0.3870787682488629</v>
+        <v>0.1542227843761165</v>
       </c>
       <c r="N12" s="23" t="n">
         <v>0</v>
       </c>
       <c r="O12" s="25" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P12" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q12" s="19" t="inlineStr">
@@ -1656,12 +1654,12 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>ALB @ BUFF</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D13" s="13" t="n">
@@ -1674,44 +1672,40 @@
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>ALB ML</t>
+          <t>UNC ML</t>
         </is>
       </c>
       <c r="G13" s="14" t="n"/>
       <c r="H13" s="15" t="n">
-        <v>2200</v>
+        <v>250</v>
       </c>
       <c r="I13" s="16" t="n">
-        <v>0.2400960739565308</v>
+        <v>0.3621290026789783</v>
       </c>
       <c r="J13" s="16" t="n">
-        <v>0.04216553878188443</v>
+        <v>0.274247491638796</v>
       </c>
       <c r="K13" s="16" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="L13" s="17" t="n">
-        <v>0.1966178130869655</v>
+        <v>0.0764147169646926</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>4.522209701000207</v>
+        <v>0.267451509376424</v>
       </c>
       <c r="N13" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O13" s="18" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P13" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q13" s="12" t="inlineStr">
-        <is>
-          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+          <t>Draft Kings</t>
+        </is>
+      </c>
+      <c r="Q13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="19" t="inlineStr">
@@ -1721,12 +1715,12 @@
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>WES @ KENN</t>
+          <t>SAC @ EMU</t>
         </is>
       </c>
       <c r="C14" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-29 22:30</t>
         </is>
       </c>
       <c r="D14" s="20" t="n">
@@ -1734,49 +1728,49 @@
       </c>
       <c r="E14" s="19" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F14" s="19" t="inlineStr">
         <is>
-          <t>WES +22.5</t>
+          <t>Over 52.5</t>
         </is>
       </c>
       <c r="G14" s="21" t="n">
-        <v>-22.5</v>
+        <v>52.5</v>
       </c>
       <c r="H14" s="22" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="I14" s="23" t="n">
-        <v>0.7273466517420963</v>
+        <v>0.595359506876733</v>
       </c>
       <c r="J14" s="23" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K14" s="23" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L14" s="24" t="n">
-        <v>0.1924629308118638</v>
+        <v>0.07612873764596373</v>
       </c>
       <c r="M14" s="24" t="n">
-        <v>0.3598220010830496</v>
+        <v>0.1466183095403747</v>
       </c>
       <c r="N14" s="23" t="n">
         <v>0</v>
       </c>
       <c r="O14" s="25" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P14" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q14" s="19" t="inlineStr">
         <is>
-          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -1788,12 +1782,12 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>WES @ KENN</t>
+          <t>HAW @ STAN</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D15" s="13" t="n">
@@ -1806,44 +1800,40 @@
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>WES ML</t>
+          <t>HAW ML</t>
         </is>
       </c>
       <c r="G15" s="14" t="n"/>
       <c r="H15" s="15" t="n">
-        <v>1500</v>
+        <v>180</v>
       </c>
       <c r="I15" s="16" t="n">
-        <v>0.2370117476831352</v>
+        <v>0.414495505906456</v>
       </c>
       <c r="J15" s="16" t="n">
-        <v>0.06035889070146819</v>
+        <v>0.3425247738043947</v>
       </c>
       <c r="K15" s="16" t="n">
-        <v>0.0625</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="L15" s="17" t="n">
-        <v>0.1745117476831352</v>
+        <v>0.05735264876359886</v>
       </c>
       <c r="M15" s="17" t="n">
-        <v>2.792187962930162</v>
+        <v>0.1605874165380767</v>
       </c>
       <c r="N15" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O15" s="18" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P15" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q15" s="12" t="inlineStr">
-        <is>
-          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+          <t>Draft Kings</t>
+        </is>
+      </c>
+      <c r="Q15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="19" t="inlineStr">
@@ -1853,7 +1843,7 @@
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>NMSU @ FSU</t>
+          <t>HAW @ STAN</t>
         </is>
       </c>
       <c r="C16" s="19" t="inlineStr">
@@ -1866,49 +1856,47 @@
       </c>
       <c r="E16" s="19" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>NMSU ML</t>
-        </is>
-      </c>
-      <c r="G16" s="21" t="n"/>
+          <t>HAW +5.5</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="n">
+        <v>-5.5</v>
+      </c>
       <c r="H16" s="22" t="n">
-        <v>2000</v>
+        <v>-112</v>
       </c>
       <c r="I16" s="23" t="n">
-        <v>0.2189772153156186</v>
+        <v>0.5838108250777737</v>
       </c>
       <c r="J16" s="23" t="n">
-        <v>0.0461215932914046</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K16" s="23" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L16" s="24" t="n">
-        <v>0.171358167696571</v>
+        <v>0.05550893828532089</v>
       </c>
       <c r="M16" s="24" t="n">
-        <v>3.598521521627991</v>
+        <v>0.1050704903257859</v>
       </c>
       <c r="N16" s="23" t="n">
         <v>0</v>
       </c>
       <c r="O16" s="25" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P16" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q16" s="19" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+          <t>Draft Kings</t>
+        </is>
+      </c>
+      <c r="Q16" s="19" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -1918,12 +1906,12 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>AKR @ WAKE</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D17" s="13" t="n">
@@ -1936,44 +1924,40 @@
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>AKR ML</t>
+          <t>MEM ML</t>
         </is>
       </c>
       <c r="G17" s="14" t="n"/>
       <c r="H17" s="15" t="n">
-        <v>1300</v>
+        <v>185</v>
       </c>
       <c r="I17" s="16" t="n">
-        <v>0.2310535567636653</v>
+        <v>0.3799494426906008</v>
       </c>
       <c r="J17" s="16" t="n">
-        <v>0.06888361045130641</v>
+        <v>0.3363518758085381</v>
       </c>
       <c r="K17" s="16" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.3508771929824561</v>
       </c>
       <c r="L17" s="17" t="n">
-        <v>0.1596249853350939</v>
+        <v>0.0290722497081447</v>
       </c>
       <c r="M17" s="17" t="n">
-        <v>2.234749794691315</v>
+        <v>0.08285591166821238</v>
       </c>
       <c r="N17" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O17" s="18" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P17" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q17" s="12" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+          <t>Draft Kings</t>
+        </is>
+      </c>
+      <c r="Q17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="19" t="inlineStr">
@@ -1983,12 +1967,12 @@
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>MASS @ RUTG</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C18" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03 22:00</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D18" s="20" t="n">
@@ -1996,49 +1980,47 @@
       </c>
       <c r="E18" s="19" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F18" s="19" t="inlineStr">
         <is>
-          <t>MASS ML</t>
-        </is>
-      </c>
-      <c r="G18" s="21" t="n"/>
+          <t>MEM +5.5</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="n">
+        <v>-5.5</v>
+      </c>
       <c r="H18" s="22" t="n">
-        <v>2000</v>
+        <v>-112</v>
       </c>
       <c r="I18" s="23" t="n">
-        <v>0.1963076315941712</v>
+        <v>0.5540130817463144</v>
       </c>
       <c r="J18" s="23" t="n">
-        <v>0.0461215932914046</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K18" s="23" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L18" s="24" t="n">
-        <v>0.1486885839751236</v>
+        <v>0.02571119495386154</v>
       </c>
       <c r="M18" s="24" t="n">
-        <v>3.122460263477595</v>
+        <v>0.04866761901980932</v>
       </c>
       <c r="N18" s="23" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="25" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P18" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q18" s="19" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+          <t>Draft Kings</t>
+        </is>
+      </c>
+      <c r="Q18" s="19" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
@@ -2048,12 +2030,12 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>JVST @ NDSU</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D19" s="13" t="n">
@@ -2061,51 +2043,47 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
+          <t>NCSU +5.5</t>
         </is>
       </c>
       <c r="G19" s="14" t="n">
-        <v>46.5</v>
+        <v>-5.5</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I19" s="16" t="n">
-        <v>0.6553348680813179</v>
+        <v>0.5412896688794703</v>
       </c>
       <c r="J19" s="16" t="n">
-        <v>0.5</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K19" s="16" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L19" s="17" t="n">
-        <v>0.1315253442717941</v>
+        <v>0.022058899648701</v>
       </c>
       <c r="M19" s="17" t="n">
-        <v>0.2510938390643342</v>
+        <v>0.04248380673083174</v>
       </c>
       <c r="N19" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O19" s="18" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P19" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q19" s="12" t="inlineStr">
-        <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
-        </is>
-      </c>
+          <t>Draft Kings</t>
+        </is>
+      </c>
+      <c r="Q19" s="12" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="19" t="inlineStr">
@@ -2115,12 +2093,12 @@
       </c>
       <c r="B20" s="19" t="inlineStr">
         <is>
-          <t>SAC @ EMU</t>
+          <t>JVST @ NDSU</t>
         </is>
       </c>
       <c r="C20" s="19" t="inlineStr">
         <is>
-          <t>2026-08-29 22:30</t>
+          <t>2026-08-29 21:30</t>
         </is>
       </c>
       <c r="D20" s="20" t="n">
@@ -2133,17 +2111,17 @@
       </c>
       <c r="F20" s="19" t="inlineStr">
         <is>
-          <t>SAC +9.5</t>
+          <t>JVST +7</t>
         </is>
       </c>
       <c r="G20" s="21" t="n">
-        <v>-9.5</v>
+        <v>-7</v>
       </c>
       <c r="H20" s="22" t="n">
         <v>-110</v>
       </c>
       <c r="I20" s="23" t="n">
-        <v>0.6373042089106218</v>
+        <v>0.5445684137563569</v>
       </c>
       <c r="J20" s="23" t="n">
         <v>0.5</v>
@@ -2152,27 +2130,23 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L20" s="24" t="n">
-        <v>0.1134946851010979</v>
+        <v>0.02075888994683306</v>
       </c>
       <c r="M20" s="24" t="n">
-        <v>0.2166716715566417</v>
+        <v>0.03762929802911508</v>
       </c>
       <c r="N20" s="23" t="n">
-        <v>0</v>
+        <v>0.0505</v>
       </c>
       <c r="O20" s="25" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P20" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q20" s="19" t="inlineStr">
-        <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
-        </is>
-      </c>
+          <t>Draft Kings</t>
+        </is>
+      </c>
+      <c r="Q20" s="19" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
@@ -2182,12 +2156,12 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>SAC @ EMU</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 22:30</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D21" s="13" t="n">
@@ -2195,49 +2169,47 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>SAC ML</t>
-        </is>
-      </c>
-      <c r="G21" s="14" t="n"/>
+          <t>Under 59.5</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="n">
+        <v>59.5</v>
+      </c>
       <c r="H21" s="15" t="n">
-        <v>280</v>
+        <v>-110</v>
       </c>
       <c r="I21" s="16" t="n">
-        <v>0.3686221870504205</v>
+        <v>0.543550073621027</v>
       </c>
       <c r="J21" s="16" t="n">
-        <v>0.2522172949002217</v>
+        <v>0.5</v>
       </c>
       <c r="K21" s="16" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L21" s="17" t="n">
-        <v>0.1054642923135784</v>
+        <v>0.01974054981150319</v>
       </c>
       <c r="M21" s="17" t="n">
-        <v>0.4007643107915979</v>
+        <v>0.0376865041855971</v>
       </c>
       <c r="N21" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O21" s="18" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P21" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q21" s="12" t="inlineStr">
-        <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
-        </is>
-      </c>
+          <t>Draft Kings</t>
+        </is>
+      </c>
+      <c r="Q21" s="12" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
@@ -2247,12 +2219,12 @@
       </c>
       <c r="B22" s="19" t="inlineStr">
         <is>
-          <t>ALB @ BUFF</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C22" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D22" s="20" t="n">
@@ -2260,51 +2232,45 @@
       </c>
       <c r="E22" s="19" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F22" s="19" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
-        </is>
-      </c>
-      <c r="G22" s="21" t="n">
-        <v>48.5</v>
-      </c>
+          <t>NCSU ML</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="n"/>
       <c r="H22" s="22" t="n">
-        <v>-108</v>
+        <v>180</v>
       </c>
       <c r="I22" s="23" t="n">
-        <v>0.6237538960930264</v>
+        <v>0.3745807138274095</v>
       </c>
       <c r="J22" s="23" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.3425247738043947</v>
       </c>
       <c r="K22" s="23" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="L22" s="24" t="n">
-        <v>0.1045231268622572</v>
+        <v>0.01743785668455239</v>
       </c>
       <c r="M22" s="24" t="n">
-        <v>0.2013037998828658</v>
+        <v>0.04882599871674664</v>
       </c>
       <c r="N22" s="23" t="n">
         <v>0</v>
       </c>
       <c r="O22" s="25" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P22" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q22" s="19" t="inlineStr">
-        <is>
-          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+          <t>Draft Kings</t>
+        </is>
+      </c>
+      <c r="Q22" s="19" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
@@ -2314,12 +2280,12 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>HAW @ STAN</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D23" s="13" t="n">
@@ -2332,46 +2298,42 @@
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
+          <t>Over 47.5</t>
         </is>
       </c>
       <c r="G23" s="14" t="n">
-        <v>49.5</v>
+        <v>47.5</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="I23" s="16" t="n">
-        <v>0.5955932130438462</v>
+        <v>0.5376883257015108</v>
       </c>
       <c r="J23" s="16" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5</v>
       </c>
       <c r="K23" s="16" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L23" s="17" t="n">
-        <v>0.08339809109262664</v>
+        <v>0.01387880189198698</v>
       </c>
       <c r="M23" s="17" t="n">
-        <v>0.1628248445141758</v>
+        <v>0.02649589452106615</v>
       </c>
       <c r="N23" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O23" s="18" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P23" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q23" s="12" t="inlineStr">
-        <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
-        </is>
-      </c>
+          <t>Draft Kings</t>
+        </is>
+      </c>
+      <c r="Q23" s="12" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="19" t="inlineStr">
@@ -2381,12 +2343,12 @@
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>JVST @ NDSU</t>
         </is>
       </c>
       <c r="C24" s="19" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-08-29 21:30</t>
         </is>
       </c>
       <c r="D24" s="20" t="n">
@@ -2394,51 +2356,45 @@
       </c>
       <c r="E24" s="19" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F24" s="19" t="inlineStr">
         <is>
-          <t>UNC +7.5</t>
-        </is>
-      </c>
-      <c r="G24" s="21" t="n">
-        <v>-7.5</v>
-      </c>
+          <t>JVST ML</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="n"/>
       <c r="H24" s="22" t="n">
-        <v>-108</v>
+        <v>220</v>
       </c>
       <c r="I24" s="23" t="n">
-        <v>0.5993079841952912</v>
+        <v>0.3261190128306598</v>
       </c>
       <c r="J24" s="23" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.299837925445705</v>
       </c>
       <c r="K24" s="23" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.3125</v>
       </c>
       <c r="L24" s="24" t="n">
-        <v>0.08007721496452191</v>
+        <v>0.0136190128306598</v>
       </c>
       <c r="M24" s="24" t="n">
-        <v>0.1542227843761165</v>
+        <v>0.04358084105811144</v>
       </c>
       <c r="N24" s="23" t="n">
         <v>0</v>
       </c>
       <c r="O24" s="25" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P24" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q24" s="19" t="inlineStr">
-        <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
-        </is>
-      </c>
+          <t>Draft Kings</t>
+        </is>
+      </c>
+      <c r="Q24" s="19" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
@@ -2448,12 +2404,12 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>WES @ KENN</t>
+          <t>NMSU @ FSU</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D25" s="13" t="n">
@@ -2466,46 +2422,42 @@
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>Over 53.5</t>
         </is>
       </c>
       <c r="G25" s="14" t="n">
-        <v>51.5</v>
+        <v>53.5</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I25" s="16" t="n">
-        <v>0.5971070144741464</v>
+        <v>0.5298211883282545</v>
       </c>
       <c r="J25" s="16" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5</v>
       </c>
       <c r="K25" s="16" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L25" s="17" t="n">
-        <v>0.07787624524337711</v>
+        <v>0.006011664518730697</v>
       </c>
       <c r="M25" s="17" t="n">
-        <v>0.1499838797279857</v>
+        <v>0.01147681408121326</v>
       </c>
       <c r="N25" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O25" s="18" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P25" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q25" s="12" t="inlineStr">
-        <is>
-          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+          <t>Draft Kings</t>
+        </is>
+      </c>
+      <c r="Q25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="19" t="inlineStr">
@@ -2515,12 +2467,12 @@
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C26" s="19" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D26" s="20" t="n">
@@ -2528,42 +2480,44 @@
       </c>
       <c r="E26" s="19" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F26" s="19" t="inlineStr">
         <is>
-          <t>UNC ML</t>
-        </is>
-      </c>
-      <c r="G26" s="21" t="n"/>
+          <t>Over 53.5</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="n">
+        <v>53.5</v>
+      </c>
       <c r="H26" s="22" t="n">
-        <v>250</v>
+        <v>-108</v>
       </c>
       <c r="I26" s="23" t="n">
-        <v>0.3621290026789783</v>
+        <v>0.5177573237293587</v>
       </c>
       <c r="J26" s="23" t="n">
-        <v>0.274247491638796</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K26" s="23" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L26" s="24" t="n">
-        <v>0.0764147169646926</v>
+        <v>-0.001473445501410597</v>
       </c>
       <c r="M26" s="24" t="n">
-        <v>0.267451509376424</v>
+        <v>-0.00283774689160543</v>
       </c>
       <c r="N26" s="23" t="n">
         <v>0</v>
       </c>
       <c r="O26" s="25" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P26" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q26" s="19" t="n"/>
@@ -2576,12 +2530,12 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>SAC @ EMU</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 22:30</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D27" s="13" t="n">
@@ -2594,17 +2548,17 @@
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>Over 52.5</t>
+          <t>Over 57.5</t>
         </is>
       </c>
       <c r="G27" s="14" t="n">
-        <v>52.5</v>
+        <v>57.5</v>
       </c>
       <c r="H27" s="15" t="n">
         <v>-108</v>
       </c>
       <c r="I27" s="16" t="n">
-        <v>0.595359506876733</v>
+        <v>0.50780868060465</v>
       </c>
       <c r="J27" s="16" t="n">
         <v>0.4956702459300312</v>
@@ -2613,27 +2567,23 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L27" s="17" t="n">
-        <v>0.07612873764596373</v>
+        <v>-0.01142208862611926</v>
       </c>
       <c r="M27" s="17" t="n">
-        <v>0.1466183095403747</v>
+        <v>-0.02199809661326657</v>
       </c>
       <c r="N27" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O27" s="18" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P27" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q27" s="12" t="inlineStr">
-        <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
-        </is>
-      </c>
+          <t>Draft Kings</t>
+        </is>
+      </c>
+      <c r="Q27" s="12" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="19" t="inlineStr">
@@ -2643,12 +2593,12 @@
       </c>
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>AKR @ WAKE</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D28" s="20" t="n">
@@ -2661,17 +2611,17 @@
       </c>
       <c r="F28" s="19" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
+          <t>Under 57.5</t>
         </is>
       </c>
       <c r="G28" s="21" t="n">
-        <v>49.5</v>
+        <v>57.5</v>
       </c>
       <c r="H28" s="22" t="n">
         <v>-112</v>
       </c>
       <c r="I28" s="23" t="n">
-        <v>0.603175208172005</v>
+        <v>0.49219131939535</v>
       </c>
       <c r="J28" s="23" t="n">
         <v>0.5043297540699688</v>
@@ -2680,27 +2630,23 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L28" s="24" t="n">
-        <v>0.07487332137955216</v>
+        <v>-0.03611056739710283</v>
       </c>
       <c r="M28" s="24" t="n">
-        <v>0.1417245011827237</v>
+        <v>-0.06835214543023038</v>
       </c>
       <c r="N28" s="23" t="n">
         <v>0</v>
       </c>
       <c r="O28" s="25" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P28" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q28" s="19" t="inlineStr">
-        <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
-        </is>
-      </c>
+          <t>Draft Kings</t>
+        </is>
+      </c>
+      <c r="Q28" s="19" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
@@ -2710,12 +2656,12 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>BCU @ UCF</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D29" s="13" t="n">
@@ -2728,46 +2674,42 @@
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>Under 59.5</t>
+          <t>Under 53.5</t>
         </is>
       </c>
       <c r="G29" s="14" t="n">
-        <v>59.5</v>
+        <v>53.5</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I29" s="16" t="n">
-        <v>0.5828840668418837</v>
+        <v>0.4822426762706413</v>
       </c>
       <c r="J29" s="16" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K29" s="16" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L29" s="17" t="n">
-        <v>0.06365329761111438</v>
+        <v>-0.0460592105218115</v>
       </c>
       <c r="M29" s="17" t="n">
-        <v>0.1225915361399241</v>
+        <v>-0.08718350563057181</v>
       </c>
       <c r="N29" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O29" s="18" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P29" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q29" s="12" t="inlineStr">
-        <is>
-          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+          <t>Draft Kings</t>
+        </is>
+      </c>
+      <c r="Q29" s="12" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="19" t="inlineStr">
@@ -2777,7 +2719,7 @@
       </c>
       <c r="B30" s="19" t="inlineStr">
         <is>
-          <t>HAW @ STAN</t>
+          <t>NMSU @ FSU</t>
         </is>
       </c>
       <c r="C30" s="19" t="inlineStr">
@@ -2790,42 +2732,44 @@
       </c>
       <c r="E30" s="19" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F30" s="19" t="inlineStr">
         <is>
-          <t>HAW ML</t>
-        </is>
-      </c>
-      <c r="G30" s="21" t="n"/>
+          <t>Under 53.5</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="n">
+        <v>53.5</v>
+      </c>
       <c r="H30" s="22" t="n">
-        <v>180</v>
+        <v>-110</v>
       </c>
       <c r="I30" s="23" t="n">
-        <v>0.414495505906456</v>
+        <v>0.4701788116717455</v>
       </c>
       <c r="J30" s="23" t="n">
-        <v>0.3425247738043947</v>
+        <v>0.5</v>
       </c>
       <c r="K30" s="23" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L30" s="24" t="n">
-        <v>0.05735264876359886</v>
+        <v>-0.05363071213777837</v>
       </c>
       <c r="M30" s="24" t="n">
-        <v>0.1605874165380767</v>
+        <v>-0.1023859049903041</v>
       </c>
       <c r="N30" s="23" t="n">
         <v>0</v>
       </c>
       <c r="O30" s="25" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P30" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q30" s="19" t="n"/>
@@ -2838,12 +2782,12 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>HAW @ STAN</t>
+          <t>JVST @ NDSU</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-08-29 21:30</t>
         </is>
       </c>
       <c r="D31" s="13" t="n">
@@ -2851,44 +2795,42 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>HAW +5.5</t>
-        </is>
-      </c>
-      <c r="G31" s="14" t="n">
-        <v>-5.5</v>
-      </c>
+          <t>NDSU ML</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="n"/>
       <c r="H31" s="15" t="n">
-        <v>-112</v>
+        <v>-270</v>
       </c>
       <c r="I31" s="16" t="n">
-        <v>0.5838108250777737</v>
+        <v>0.6738809871693402</v>
       </c>
       <c r="J31" s="16" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.7001620745542949</v>
       </c>
       <c r="K31" s="16" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.7297297297297297</v>
       </c>
       <c r="L31" s="17" t="n">
-        <v>0.05550893828532089</v>
+        <v>-0.05584874256038952</v>
       </c>
       <c r="M31" s="17" t="n">
-        <v>0.1050704903257859</v>
+        <v>-0.07653346202720057</v>
       </c>
       <c r="N31" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O31" s="18" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P31" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q31" s="12" t="n"/>
@@ -2901,12 +2843,12 @@
       </c>
       <c r="B32" s="19" t="inlineStr">
         <is>
-          <t>MASS @ RUTG</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C32" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03 22:00</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D32" s="20" t="n">
@@ -2914,44 +2856,42 @@
       </c>
       <c r="E32" s="19" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F32" s="19" t="inlineStr">
         <is>
-          <t>Over 53.5</t>
-        </is>
-      </c>
-      <c r="G32" s="21" t="n">
-        <v>53.5</v>
-      </c>
+          <t>UVA ML</t>
+        </is>
+      </c>
+      <c r="G32" s="21" t="n"/>
       <c r="H32" s="22" t="n">
-        <v>-110</v>
+        <v>-218</v>
       </c>
       <c r="I32" s="23" t="n">
-        <v>0.5740430549239717</v>
+        <v>0.6254192861725905</v>
       </c>
       <c r="J32" s="23" t="n">
-        <v>0.5</v>
+        <v>0.6574752261956054</v>
       </c>
       <c r="K32" s="23" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.6855345911949685</v>
       </c>
       <c r="L32" s="24" t="n">
-        <v>0.05023353111444784</v>
+        <v>-0.06011530502237805</v>
       </c>
       <c r="M32" s="24" t="n">
-        <v>0.09590037758212777</v>
+        <v>-0.08769113301429471</v>
       </c>
       <c r="N32" s="23" t="n">
         <v>0</v>
       </c>
       <c r="O32" s="25" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P32" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q32" s="19" t="n"/>
@@ -2964,12 +2904,12 @@
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D33" s="13" t="n">
@@ -2977,42 +2917,44 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>MEM ML</t>
-        </is>
-      </c>
-      <c r="G33" s="14" t="n"/>
+          <t>Under 47.5</t>
+        </is>
+      </c>
+      <c r="G33" s="14" t="n">
+        <v>47.5</v>
+      </c>
       <c r="H33" s="15" t="n">
-        <v>185</v>
+        <v>-110</v>
       </c>
       <c r="I33" s="16" t="n">
-        <v>0.3799494426906008</v>
+        <v>0.4623116742984892</v>
       </c>
       <c r="J33" s="16" t="n">
-        <v>0.3363518758085381</v>
+        <v>0.5</v>
       </c>
       <c r="K33" s="16" t="n">
-        <v>0.3508771929824561</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L33" s="17" t="n">
-        <v>0.0290722497081447</v>
+        <v>-0.06149784951103465</v>
       </c>
       <c r="M33" s="17" t="n">
-        <v>0.08285591166821238</v>
+        <v>-0.117404985430157</v>
       </c>
       <c r="N33" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O33" s="18" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P33" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q33" s="12" t="n"/>
@@ -3025,12 +2967,12 @@
       </c>
       <c r="B34" s="19" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C34" s="19" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
@@ -3038,44 +2980,44 @@
       </c>
       <c r="E34" s="19" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F34" s="19" t="inlineStr">
         <is>
-          <t>MEM +5.5</t>
+          <t>Over 59.5</t>
         </is>
       </c>
       <c r="G34" s="21" t="n">
-        <v>-5.5</v>
+        <v>59.5</v>
       </c>
       <c r="H34" s="22" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I34" s="23" t="n">
-        <v>0.5540130817463144</v>
+        <v>0.456449926378973</v>
       </c>
       <c r="J34" s="23" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K34" s="23" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L34" s="24" t="n">
-        <v>0.02571119495386154</v>
+        <v>-0.06735959743055087</v>
       </c>
       <c r="M34" s="24" t="n">
-        <v>0.04866761901980932</v>
+        <v>-0.1285955950946879</v>
       </c>
       <c r="N34" s="23" t="n">
         <v>0</v>
       </c>
       <c r="O34" s="25" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P34" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q34" s="19" t="n"/>
@@ -3088,12 +3030,12 @@
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>JVST @ NDSU</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-08-29 21:30</t>
         </is>
       </c>
       <c r="D35" s="13" t="n">
@@ -3106,39 +3048,39 @@
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>NCSU +5.5</t>
+          <t>NDSU -7</t>
         </is>
       </c>
       <c r="G35" s="14" t="n">
-        <v>-5.5</v>
+        <v>-7</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I35" s="16" t="n">
-        <v>0.5412896688794703</v>
+        <v>0.4554315862436431</v>
       </c>
       <c r="J35" s="16" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5</v>
       </c>
       <c r="K35" s="16" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L35" s="17" t="n">
-        <v>0.022058899648701</v>
+        <v>-0.06837793756588073</v>
       </c>
       <c r="M35" s="17" t="n">
-        <v>0.04248380673083174</v>
+        <v>-0.1239475616409477</v>
       </c>
       <c r="N35" s="16" t="n">
-        <v>0</v>
+        <v>0.0505</v>
       </c>
       <c r="O35" s="18" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P35" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q35" s="12" t="n"/>
@@ -3151,12 +3093,12 @@
       </c>
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>JVST @ NDSU</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C36" s="19" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
@@ -3169,39 +3111,39 @@
       </c>
       <c r="F36" s="19" t="inlineStr">
         <is>
-          <t>JVST +7</t>
+          <t>UVA -5.5</t>
         </is>
       </c>
       <c r="G36" s="21" t="n">
-        <v>-7</v>
+        <v>-5.5</v>
       </c>
       <c r="H36" s="22" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="I36" s="23" t="n">
-        <v>0.5445684137563569</v>
+        <v>0.4587103311205297</v>
       </c>
       <c r="J36" s="23" t="n">
-        <v>0.5</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K36" s="23" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L36" s="24" t="n">
-        <v>0.02075888994683306</v>
+        <v>-0.0695915556719231</v>
       </c>
       <c r="M36" s="24" t="n">
-        <v>0.03762929802911508</v>
+        <v>-0.1317268732361402</v>
       </c>
       <c r="N36" s="23" t="n">
-        <v>0.0505</v>
+        <v>0</v>
       </c>
       <c r="O36" s="25" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P36" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q36" s="19" t="n"/>
@@ -3214,12 +3156,12 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D37" s="13" t="n">
@@ -3227,44 +3169,42 @@
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>Under 59.5</t>
-        </is>
-      </c>
-      <c r="G37" s="14" t="n">
-        <v>59.5</v>
-      </c>
+          <t>UNLV ML</t>
+        </is>
+      </c>
+      <c r="G37" s="14" t="n"/>
       <c r="H37" s="15" t="n">
-        <v>-110</v>
+        <v>-225</v>
       </c>
       <c r="I37" s="16" t="n">
-        <v>0.543550073621027</v>
+        <v>0.6200505573093992</v>
       </c>
       <c r="J37" s="16" t="n">
-        <v>0.5</v>
+        <v>0.6636481241914618</v>
       </c>
       <c r="K37" s="16" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="L37" s="17" t="n">
-        <v>0.01974054981150319</v>
+        <v>-0.07225713499829312</v>
       </c>
       <c r="M37" s="17" t="n">
-        <v>0.0376865041855971</v>
+        <v>-0.1043714172197567</v>
       </c>
       <c r="N37" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O37" s="18" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P37" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q37" s="12" t="n"/>
@@ -3277,12 +3217,12 @@
       </c>
       <c r="B38" s="19" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C38" s="19" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D38" s="20" t="n">
@@ -3290,42 +3230,44 @@
       </c>
       <c r="E38" s="19" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F38" s="19" t="inlineStr">
         <is>
-          <t>NCSU ML</t>
-        </is>
-      </c>
-      <c r="G38" s="21" t="n"/>
+          <t>UNLV -5.5</t>
+        </is>
+      </c>
+      <c r="G38" s="21" t="n">
+        <v>-5.5</v>
+      </c>
       <c r="H38" s="22" t="n">
-        <v>180</v>
+        <v>-108</v>
       </c>
       <c r="I38" s="23" t="n">
-        <v>0.3745807138274095</v>
+        <v>0.4459869182536856</v>
       </c>
       <c r="J38" s="23" t="n">
-        <v>0.3425247738043947</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K38" s="23" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L38" s="24" t="n">
-        <v>0.01743785668455239</v>
+        <v>-0.07324385097708364</v>
       </c>
       <c r="M38" s="24" t="n">
-        <v>0.04882599871674664</v>
+        <v>-0.1410622315114202</v>
       </c>
       <c r="N38" s="23" t="n">
         <v>0</v>
       </c>
       <c r="O38" s="25" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P38" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q38" s="19" t="n"/>
@@ -3338,12 +3280,12 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>MRMK @ DEL</t>
+          <t>HAW @ STAN</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D39" s="13" t="n">
@@ -3351,51 +3293,45 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>Over 55.5</t>
-        </is>
-      </c>
-      <c r="G39" s="14" t="n">
-        <v>55.5</v>
-      </c>
+          <t>STAN ML</t>
+        </is>
+      </c>
+      <c r="G39" s="14" t="n"/>
       <c r="H39" s="15" t="n">
-        <v>-112</v>
+        <v>-218</v>
       </c>
       <c r="I39" s="16" t="n">
-        <v>0.5437650474945759</v>
+        <v>0.585504494093544</v>
       </c>
       <c r="J39" s="16" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.6574752261956054</v>
       </c>
       <c r="K39" s="16" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.6855345911949685</v>
       </c>
       <c r="L39" s="17" t="n">
-        <v>0.01546316070212306</v>
+        <v>-0.1000300971014245</v>
       </c>
       <c r="M39" s="17" t="n">
-        <v>0.02926955418616145</v>
+        <v>-0.1459154627442799</v>
       </c>
       <c r="N39" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O39" s="18" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P39" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q39" s="12" t="inlineStr">
-        <is>
-          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+          <t>Draft Kings</t>
+        </is>
+      </c>
+      <c r="Q39" s="12" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="19" t="inlineStr">
@@ -3405,12 +3341,12 @@
       </c>
       <c r="B40" s="19" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>HAW @ STAN</t>
         </is>
       </c>
       <c r="C40" s="19" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D40" s="20" t="n">
@@ -3418,44 +3354,44 @@
       </c>
       <c r="E40" s="19" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F40" s="19" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
+          <t>STAN -5.5</t>
         </is>
       </c>
       <c r="G40" s="21" t="n">
-        <v>47.5</v>
+        <v>-5.5</v>
       </c>
       <c r="H40" s="22" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I40" s="23" t="n">
-        <v>0.5376883257015108</v>
+        <v>0.4161891749222263</v>
       </c>
       <c r="J40" s="23" t="n">
-        <v>0.5</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K40" s="23" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L40" s="24" t="n">
-        <v>0.01387880189198698</v>
+        <v>-0.103041594308543</v>
       </c>
       <c r="M40" s="24" t="n">
-        <v>0.02649589452106615</v>
+        <v>-0.1984504779275642</v>
       </c>
       <c r="N40" s="23" t="n">
         <v>0</v>
       </c>
       <c r="O40" s="25" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P40" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q40" s="19" t="n"/>
@@ -3468,12 +3404,12 @@
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>JVST @ NDSU</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D41" s="13" t="n">
@@ -3486,37 +3422,37 @@
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>JVST ML</t>
+          <t>TCU ML</t>
         </is>
       </c>
       <c r="G41" s="14" t="n"/>
       <c r="H41" s="15" t="n">
-        <v>220</v>
+        <v>-310</v>
       </c>
       <c r="I41" s="16" t="n">
-        <v>0.3261190128306598</v>
+        <v>0.6378709973210217</v>
       </c>
       <c r="J41" s="16" t="n">
-        <v>0.299837925445705</v>
+        <v>0.725752508361204</v>
       </c>
       <c r="K41" s="16" t="n">
-        <v>0.3125</v>
+        <v>0.7560975609756098</v>
       </c>
       <c r="L41" s="17" t="n">
-        <v>0.0136190128306598</v>
+        <v>-0.1182265636545881</v>
       </c>
       <c r="M41" s="17" t="n">
-        <v>0.04358084105811144</v>
+        <v>-0.1563641648334875</v>
       </c>
       <c r="N41" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O41" s="18" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P41" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q41" s="12" t="n"/>
@@ -3529,12 +3465,12 @@
       </c>
       <c r="B42" s="19" t="inlineStr">
         <is>
-          <t>NMSU @ FSU</t>
+          <t>SAC @ EMU</t>
         </is>
       </c>
       <c r="C42" s="19" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-08-29 22:30</t>
         </is>
       </c>
       <c r="D42" s="20" t="n">
@@ -3547,42 +3483,46 @@
       </c>
       <c r="F42" s="19" t="inlineStr">
         <is>
-          <t>Over 53.5</t>
+          <t>Under 52.5</t>
         </is>
       </c>
       <c r="G42" s="21" t="n">
-        <v>53.5</v>
+        <v>52.5</v>
       </c>
       <c r="H42" s="22" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="I42" s="23" t="n">
-        <v>0.5298211883282545</v>
+        <v>0.404640493123267</v>
       </c>
       <c r="J42" s="23" t="n">
-        <v>0.5</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K42" s="23" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L42" s="24" t="n">
-        <v>0.006011664518730697</v>
+        <v>-0.1236613936691858</v>
       </c>
       <c r="M42" s="24" t="n">
-        <v>0.01147681408121326</v>
+        <v>-0.2340733523023875</v>
       </c>
       <c r="N42" s="23" t="n">
         <v>0</v>
       </c>
       <c r="O42" s="25" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P42" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q42" s="19" t="n"/>
+          <t>Draft Kings</t>
+        </is>
+      </c>
+      <c r="Q42" s="19" t="inlineStr">
+        <is>
+          <t>raw model/market disagreement exceeds the safety limit</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
@@ -3592,12 +3532,12 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D43" s="13" t="n">
@@ -3605,47 +3545,51 @@
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>Over 53.5</t>
+          <t>TCU -7.5</t>
         </is>
       </c>
       <c r="G43" s="14" t="n">
-        <v>53.5</v>
+        <v>-7.5</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I43" s="16" t="n">
-        <v>0.5177573237293587</v>
+        <v>0.4006920158047088</v>
       </c>
       <c r="J43" s="16" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K43" s="16" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L43" s="17" t="n">
-        <v>-0.001473445501410597</v>
+        <v>-0.127609870987744</v>
       </c>
       <c r="M43" s="17" t="n">
-        <v>-0.00283774689160543</v>
+        <v>-0.2415472557982298</v>
       </c>
       <c r="N43" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P43" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q43" s="12" t="n"/>
+          <t>Draft Kings</t>
+        </is>
+      </c>
+      <c r="Q43" s="12" t="inlineStr">
+        <is>
+          <t>raw model/market disagreement exceeds the safety limit</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="19" t="inlineStr">
@@ -3655,12 +3599,12 @@
       </c>
       <c r="B44" s="19" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>HAW @ STAN</t>
         </is>
       </c>
       <c r="C44" s="19" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D44" s="20" t="n">
@@ -3673,42 +3617,46 @@
       </c>
       <c r="F44" s="19" t="inlineStr">
         <is>
-          <t>Over 57.5</t>
+          <t>Under 49.5</t>
         </is>
       </c>
       <c r="G44" s="21" t="n">
-        <v>57.5</v>
+        <v>49.5</v>
       </c>
       <c r="H44" s="22" t="n">
-        <v>-108</v>
+        <v>-115</v>
       </c>
       <c r="I44" s="23" t="n">
-        <v>0.50780868060465</v>
+        <v>0.4044067869561538</v>
       </c>
       <c r="J44" s="23" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K44" s="23" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L44" s="24" t="n">
-        <v>-0.01142208862611926</v>
+        <v>-0.1304769339740787</v>
       </c>
       <c r="M44" s="24" t="n">
-        <v>-0.02199809661326657</v>
+        <v>-0.2439351374297994</v>
       </c>
       <c r="N44" s="23" t="n">
         <v>0</v>
       </c>
       <c r="O44" s="25" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P44" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q44" s="19" t="n"/>
+          <t>Draft Kings</t>
+        </is>
+      </c>
+      <c r="Q44" s="19" t="inlineStr">
+        <is>
+          <t>raw model/market disagreement exceeds the safety limit</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
@@ -3718,12 +3666,12 @@
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>SAC @ EMU</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-08-29 22:30</t>
         </is>
       </c>
       <c r="D45" s="13" t="n">
@@ -3731,47 +3679,49 @@
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
-          <t>Under 57.5</t>
-        </is>
-      </c>
-      <c r="G45" s="14" t="n">
-        <v>57.5</v>
-      </c>
+          <t>EMU ML</t>
+        </is>
+      </c>
+      <c r="G45" s="14" t="n"/>
       <c r="H45" s="15" t="n">
-        <v>-112</v>
+        <v>-355</v>
       </c>
       <c r="I45" s="16" t="n">
-        <v>0.49219131939535</v>
+        <v>0.6313778129495795</v>
       </c>
       <c r="J45" s="16" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.7477827050997783</v>
       </c>
       <c r="K45" s="16" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.7802197802197802</v>
       </c>
       <c r="L45" s="17" t="n">
-        <v>-0.03611056739710283</v>
+        <v>-0.1488419672702007</v>
       </c>
       <c r="M45" s="17" t="n">
-        <v>-0.06835214543023038</v>
+        <v>-0.1907692819942009</v>
       </c>
       <c r="N45" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O45" s="18" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P45" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q45" s="12" t="n"/>
+          <t>Draft Kings</t>
+        </is>
+      </c>
+      <c r="Q45" s="12" t="inlineStr">
+        <is>
+          <t>raw model/market disagreement exceeds the safety limit</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="19" t="inlineStr">
@@ -3781,12 +3731,12 @@
       </c>
       <c r="B46" s="19" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>SAC @ EMU</t>
         </is>
       </c>
       <c r="C46" s="19" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-08-29 22:30</t>
         </is>
       </c>
       <c r="D46" s="20" t="n">
@@ -3794,47 +3744,51 @@
       </c>
       <c r="E46" s="19" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F46" s="19" t="inlineStr">
         <is>
-          <t>Under 53.5</t>
+          <t>EMU -9.5</t>
         </is>
       </c>
       <c r="G46" s="21" t="n">
-        <v>53.5</v>
+        <v>-9.5</v>
       </c>
       <c r="H46" s="22" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I46" s="23" t="n">
-        <v>0.4822426762706413</v>
+        <v>0.3626957910893782</v>
       </c>
       <c r="J46" s="23" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K46" s="23" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L46" s="24" t="n">
-        <v>-0.0460592105218115</v>
+        <v>-0.1611137327201456</v>
       </c>
       <c r="M46" s="24" t="n">
-        <v>-0.08718350563057181</v>
+        <v>-0.3075807624657325</v>
       </c>
       <c r="N46" s="23" t="n">
         <v>0</v>
       </c>
       <c r="O46" s="25" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P46" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q46" s="19" t="n"/>
+          <t>Draft Kings</t>
+        </is>
+      </c>
+      <c r="Q46" s="19" t="inlineStr">
+        <is>
+          <t>raw model/market disagreement exceeds the safety limit</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
@@ -3844,12 +3798,12 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>NMSU @ FSU</t>
+          <t>JVST @ NDSU</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-08-29 21:30</t>
         </is>
       </c>
       <c r="D47" s="13" t="n">
@@ -3862,17 +3816,17 @@
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>Under 53.5</t>
+          <t>Under 46.5</t>
         </is>
       </c>
       <c r="G47" s="14" t="n">
-        <v>53.5</v>
+        <v>46.5</v>
       </c>
       <c r="H47" s="15" t="n">
         <v>-110</v>
       </c>
       <c r="I47" s="16" t="n">
-        <v>0.4701788116717455</v>
+        <v>0.3446651319186821</v>
       </c>
       <c r="J47" s="16" t="n">
         <v>0.5</v>
@@ -3881,23 +3835,27 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L47" s="17" t="n">
-        <v>-0.05363071213777837</v>
+        <v>-0.1791443918908417</v>
       </c>
       <c r="M47" s="17" t="n">
-        <v>-0.1023859049903041</v>
+        <v>-0.3420029299734251</v>
       </c>
       <c r="N47" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P47" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q47" s="12" t="n"/>
+          <t>Draft Kings</t>
+        </is>
+      </c>
+      <c r="Q47" s="12" t="inlineStr">
+        <is>
+          <t>raw model/market disagreement exceeds the safety limit</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="19" t="inlineStr">
@@ -3907,12 +3865,12 @@
       </c>
       <c r="B48" s="19" t="inlineStr">
         <is>
-          <t>JVST @ NDSU</t>
+          <t>NMSU @ FSU</t>
         </is>
       </c>
       <c r="C48" s="19" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D48" s="20" t="n">
@@ -3925,40 +3883,44 @@
       </c>
       <c r="F48" s="19" t="inlineStr">
         <is>
-          <t>NDSU ML</t>
+          <t>FSU ML</t>
         </is>
       </c>
       <c r="G48" s="21" t="n"/>
       <c r="H48" s="22" t="n">
-        <v>-270</v>
+        <v>-6500</v>
       </c>
       <c r="I48" s="23" t="n">
-        <v>0.6738809871693402</v>
+        <v>0.7810227846843814</v>
       </c>
       <c r="J48" s="23" t="n">
-        <v>0.7001620745542949</v>
+        <v>0.9538784067085954</v>
       </c>
       <c r="K48" s="23" t="n">
-        <v>0.7297297297297297</v>
+        <v>0.9848484848484849</v>
       </c>
       <c r="L48" s="24" t="n">
-        <v>-0.05584874256038952</v>
+        <v>-0.2038257001641035</v>
       </c>
       <c r="M48" s="24" t="n">
-        <v>-0.07653346202720057</v>
+        <v>-0.2069614801666282</v>
       </c>
       <c r="N48" s="23" t="n">
         <v>0</v>
       </c>
       <c r="O48" s="25" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P48" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q48" s="19" t="n"/>
+          <t>Draft Kings</t>
+        </is>
+      </c>
+      <c r="Q48" s="19" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
@@ -3968,12 +3930,12 @@
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>NMSU @ FSU</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D49" s="13" t="n">
@@ -3981,45 +3943,51 @@
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
-          <t>UVA ML</t>
-        </is>
-      </c>
-      <c r="G49" s="14" t="n"/>
+          <t>FSU -31.5</t>
+        </is>
+      </c>
+      <c r="G49" s="14" t="n">
+        <v>-31.5</v>
+      </c>
       <c r="H49" s="15" t="n">
-        <v>-218</v>
+        <v>-105</v>
       </c>
       <c r="I49" s="16" t="n">
-        <v>0.6254192861725905</v>
+        <v>0.2515947455243119</v>
       </c>
       <c r="J49" s="16" t="n">
-        <v>0.6574752261956054</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K49" s="16" t="n">
-        <v>0.6855345911949685</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L49" s="17" t="n">
-        <v>-0.06011530502237805</v>
+        <v>-0.2606003764269076</v>
       </c>
       <c r="M49" s="17" t="n">
-        <v>-0.08769113301429471</v>
+        <v>-0.5087912111192006</v>
       </c>
       <c r="N49" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O49" s="18" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P49" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q49" s="12" t="n"/>
+          <t>Draft Kings</t>
+        </is>
+      </c>
+      <c r="Q49" s="12" t="inlineStr">
+        <is>
+          <t>raw model/market disagreement exceeds the safety limit</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="19" t="inlineStr">
@@ -4029,12 +3997,12 @@
       </c>
       <c r="B50" s="19" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C50" s="19" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D50" s="20" t="n">
@@ -4042,2267 +4010,49 @@
       </c>
       <c r="E50" s="19" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F50" s="19" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
+          <t>USC -38.5</t>
         </is>
       </c>
       <c r="G50" s="21" t="n">
-        <v>47.5</v>
+        <v>-38.5</v>
       </c>
       <c r="H50" s="22" t="n">
-        <v>-110</v>
+        <v>-102</v>
       </c>
       <c r="I50" s="23" t="n">
-        <v>0.4623116742984892</v>
+        <v>0.2436390210930696</v>
       </c>
       <c r="J50" s="23" t="n">
-        <v>0.5</v>
+        <v>0.4826358742837298</v>
       </c>
       <c r="K50" s="23" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.504950495049505</v>
       </c>
       <c r="L50" s="24" t="n">
-        <v>-0.06149784951103465</v>
+        <v>-0.2613114739564354</v>
       </c>
       <c r="M50" s="24" t="n">
-        <v>-0.117404985430157</v>
+        <v>-0.517499193521568</v>
       </c>
       <c r="N50" s="23" t="n">
         <v>0</v>
       </c>
       <c r="O50" s="25" t="n">
-        <v>0.3375</v>
+        <v>0.375</v>
       </c>
       <c r="P50" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q50" s="19" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B51" s="12" t="inlineStr">
-        <is>
-          <t>MRMK @ DEL</t>
-        </is>
-      </c>
-      <c r="C51" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-03 23:00</t>
-        </is>
-      </c>
-      <c r="D51" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" s="12" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="F51" s="12" t="inlineStr">
-        <is>
-          <t>Under 55.5</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="n">
-        <v>55.5</v>
-      </c>
-      <c r="H51" s="15" t="n">
-        <v>-108</v>
-      </c>
-      <c r="I51" s="16" t="n">
-        <v>0.4562349525054241</v>
-      </c>
-      <c r="J51" s="16" t="n">
-        <v>0.4956702459300312</v>
-      </c>
-      <c r="K51" s="16" t="n">
-        <v>0.5192307692307693</v>
-      </c>
-      <c r="L51" s="17" t="n">
-        <v>-0.06299581672534516</v>
-      </c>
-      <c r="M51" s="17" t="n">
-        <v>-0.1213252766562202</v>
-      </c>
-      <c r="N51" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" s="18" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="P51" s="12" t="inlineStr">
-        <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q51" s="12" t="inlineStr">
-        <is>
-          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B52" s="19" t="inlineStr">
-        <is>
-          <t>SJSU @ USC</t>
-        </is>
-      </c>
-      <c r="C52" s="19" t="inlineStr">
-        <is>
-          <t>2026-08-29 19:00</t>
-        </is>
-      </c>
-      <c r="D52" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" s="19" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="F52" s="19" t="inlineStr">
-        <is>
-          <t>Over 59.5</t>
-        </is>
-      </c>
-      <c r="G52" s="21" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="H52" s="22" t="n">
-        <v>-110</v>
-      </c>
-      <c r="I52" s="23" t="n">
-        <v>0.456449926378973</v>
-      </c>
-      <c r="J52" s="23" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K52" s="23" t="n">
-        <v>0.5238095238095238</v>
-      </c>
-      <c r="L52" s="24" t="n">
-        <v>-0.06735959743055087</v>
-      </c>
-      <c r="M52" s="24" t="n">
-        <v>-0.1285955950946879</v>
-      </c>
-      <c r="N52" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" s="25" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="P52" s="19" t="inlineStr">
-        <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q52" s="19" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B53" s="12" t="inlineStr">
-        <is>
-          <t>JVST @ NDSU</t>
-        </is>
-      </c>
-      <c r="C53" s="12" t="inlineStr">
-        <is>
-          <t>2026-08-29 21:30</t>
-        </is>
-      </c>
-      <c r="D53" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" s="12" t="inlineStr">
-        <is>
-          <t>ATS</t>
-        </is>
-      </c>
-      <c r="F53" s="12" t="inlineStr">
-        <is>
-          <t>NDSU -7</t>
-        </is>
-      </c>
-      <c r="G53" s="14" t="n">
-        <v>-7</v>
-      </c>
-      <c r="H53" s="15" t="n">
-        <v>-110</v>
-      </c>
-      <c r="I53" s="16" t="n">
-        <v>0.4554315862436431</v>
-      </c>
-      <c r="J53" s="16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K53" s="16" t="n">
-        <v>0.5238095238095238</v>
-      </c>
-      <c r="L53" s="17" t="n">
-        <v>-0.06837793756588073</v>
-      </c>
-      <c r="M53" s="17" t="n">
-        <v>-0.1239475616409477</v>
-      </c>
-      <c r="N53" s="16" t="n">
-        <v>0.0505</v>
-      </c>
-      <c r="O53" s="18" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="P53" s="12" t="inlineStr">
-        <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q53" s="12" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B54" s="19" t="inlineStr">
-        <is>
-          <t>NCSU @ UVA</t>
-        </is>
-      </c>
-      <c r="C54" s="19" t="inlineStr">
-        <is>
-          <t>2026-08-29 19:30</t>
-        </is>
-      </c>
-      <c r="D54" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" s="19" t="inlineStr">
-        <is>
-          <t>ATS</t>
-        </is>
-      </c>
-      <c r="F54" s="19" t="inlineStr">
-        <is>
-          <t>UVA -5.5</t>
-        </is>
-      </c>
-      <c r="G54" s="21" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="H54" s="22" t="n">
-        <v>-112</v>
-      </c>
-      <c r="I54" s="23" t="n">
-        <v>0.4587103311205297</v>
-      </c>
-      <c r="J54" s="23" t="n">
-        <v>0.5043297540699688</v>
-      </c>
-      <c r="K54" s="23" t="n">
-        <v>0.5283018867924528</v>
-      </c>
-      <c r="L54" s="24" t="n">
-        <v>-0.0695915556719231</v>
-      </c>
-      <c r="M54" s="24" t="n">
-        <v>-0.1317268732361402</v>
-      </c>
-      <c r="N54" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="25" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="P54" s="19" t="inlineStr">
-        <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q54" s="19" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B55" s="12" t="inlineStr">
-        <is>
-          <t>MEM @ UNLV</t>
-        </is>
-      </c>
-      <c r="C55" s="12" t="inlineStr">
-        <is>
-          <t>2026-08-30 02:00</t>
-        </is>
-      </c>
-      <c r="D55" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" s="12" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="F55" s="12" t="inlineStr">
-        <is>
-          <t>UNLV ML</t>
-        </is>
-      </c>
-      <c r="G55" s="14" t="n"/>
-      <c r="H55" s="15" t="n">
-        <v>-225</v>
-      </c>
-      <c r="I55" s="16" t="n">
-        <v>0.6200505573093992</v>
-      </c>
-      <c r="J55" s="16" t="n">
-        <v>0.6636481241914618</v>
-      </c>
-      <c r="K55" s="16" t="n">
-        <v>0.6923076923076923</v>
-      </c>
-      <c r="L55" s="17" t="n">
-        <v>-0.07225713499829312</v>
-      </c>
-      <c r="M55" s="17" t="n">
-        <v>-0.1043714172197567</v>
-      </c>
-      <c r="N55" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="18" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="P55" s="12" t="inlineStr">
-        <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q55" s="12" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B56" s="19" t="inlineStr">
-        <is>
-          <t>MEM @ UNLV</t>
-        </is>
-      </c>
-      <c r="C56" s="19" t="inlineStr">
-        <is>
-          <t>2026-08-30 02:00</t>
-        </is>
-      </c>
-      <c r="D56" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" s="19" t="inlineStr">
-        <is>
-          <t>ATS</t>
-        </is>
-      </c>
-      <c r="F56" s="19" t="inlineStr">
-        <is>
-          <t>UNLV -5.5</t>
-        </is>
-      </c>
-      <c r="G56" s="21" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="H56" s="22" t="n">
-        <v>-108</v>
-      </c>
-      <c r="I56" s="23" t="n">
-        <v>0.4459869182536856</v>
-      </c>
-      <c r="J56" s="23" t="n">
-        <v>0.4956702459300312</v>
-      </c>
-      <c r="K56" s="23" t="n">
-        <v>0.5192307692307693</v>
-      </c>
-      <c r="L56" s="24" t="n">
-        <v>-0.07324385097708364</v>
-      </c>
-      <c r="M56" s="24" t="n">
-        <v>-0.1410622315114202</v>
-      </c>
-      <c r="N56" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="25" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="P56" s="19" t="inlineStr">
-        <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q56" s="19" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B57" s="12" t="inlineStr">
-        <is>
-          <t>MASS @ RUTG</t>
-        </is>
-      </c>
-      <c r="C57" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-03 22:00</t>
-        </is>
-      </c>
-      <c r="D57" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" s="12" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="F57" s="12" t="inlineStr">
-        <is>
-          <t>Under 53.5</t>
-        </is>
-      </c>
-      <c r="G57" s="14" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="H57" s="15" t="n">
-        <v>-110</v>
-      </c>
-      <c r="I57" s="16" t="n">
-        <v>0.4259569450760283</v>
-      </c>
-      <c r="J57" s="16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K57" s="16" t="n">
-        <v>0.5238095238095238</v>
-      </c>
-      <c r="L57" s="17" t="n">
-        <v>-0.09785257873349551</v>
-      </c>
-      <c r="M57" s="17" t="n">
-        <v>-0.1868094684912186</v>
-      </c>
-      <c r="N57" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="18" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="P57" s="12" t="inlineStr">
-        <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q57" s="12" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B58" s="19" t="inlineStr">
-        <is>
-          <t>HAW @ STAN</t>
-        </is>
-      </c>
-      <c r="C58" s="19" t="inlineStr">
-        <is>
-          <t>2026-08-29 23:00</t>
-        </is>
-      </c>
-      <c r="D58" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" s="19" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="F58" s="19" t="inlineStr">
-        <is>
-          <t>STAN ML</t>
-        </is>
-      </c>
-      <c r="G58" s="21" t="n"/>
-      <c r="H58" s="22" t="n">
-        <v>-218</v>
-      </c>
-      <c r="I58" s="23" t="n">
-        <v>0.585504494093544</v>
-      </c>
-      <c r="J58" s="23" t="n">
-        <v>0.6574752261956054</v>
-      </c>
-      <c r="K58" s="23" t="n">
-        <v>0.6855345911949685</v>
-      </c>
-      <c r="L58" s="24" t="n">
-        <v>-0.1000300971014245</v>
-      </c>
-      <c r="M58" s="24" t="n">
-        <v>-0.1459154627442799</v>
-      </c>
-      <c r="N58" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="25" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="P58" s="19" t="inlineStr">
-        <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q58" s="19" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B59" s="12" t="inlineStr">
-        <is>
-          <t>HAW @ STAN</t>
-        </is>
-      </c>
-      <c r="C59" s="12" t="inlineStr">
-        <is>
-          <t>2026-08-29 23:00</t>
-        </is>
-      </c>
-      <c r="D59" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E59" s="12" t="inlineStr">
-        <is>
-          <t>ATS</t>
-        </is>
-      </c>
-      <c r="F59" s="12" t="inlineStr">
-        <is>
-          <t>STAN -5.5</t>
-        </is>
-      </c>
-      <c r="G59" s="14" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="H59" s="15" t="n">
-        <v>-108</v>
-      </c>
-      <c r="I59" s="16" t="n">
-        <v>0.4161891749222263</v>
-      </c>
-      <c r="J59" s="16" t="n">
-        <v>0.4956702459300312</v>
-      </c>
-      <c r="K59" s="16" t="n">
-        <v>0.5192307692307693</v>
-      </c>
-      <c r="L59" s="17" t="n">
-        <v>-0.103041594308543</v>
-      </c>
-      <c r="M59" s="17" t="n">
-        <v>-0.1984504779275642</v>
-      </c>
-      <c r="N59" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" s="18" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="P59" s="12" t="inlineStr">
-        <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q59" s="12" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B60" s="19" t="inlineStr">
-        <is>
-          <t>BCU @ UCF</t>
-        </is>
-      </c>
-      <c r="C60" s="19" t="inlineStr">
-        <is>
-          <t>2026-09-03 23:00</t>
-        </is>
-      </c>
-      <c r="D60" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" s="19" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="F60" s="19" t="inlineStr">
-        <is>
-          <t>Over 59.5</t>
-        </is>
-      </c>
-      <c r="G60" s="21" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="H60" s="22" t="n">
-        <v>-112</v>
-      </c>
-      <c r="I60" s="23" t="n">
-        <v>0.4171159331581163</v>
-      </c>
-      <c r="J60" s="23" t="n">
-        <v>0.5043297540699688</v>
-      </c>
-      <c r="K60" s="23" t="n">
-        <v>0.5283018867924528</v>
-      </c>
-      <c r="L60" s="24" t="n">
-        <v>-0.1111859536343365</v>
-      </c>
-      <c r="M60" s="24" t="n">
-        <v>-0.2104591265221369</v>
-      </c>
-      <c r="N60" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" s="25" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="P60" s="19" t="inlineStr">
-        <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q60" s="19" t="inlineStr">
-        <is>
-          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B61" s="12" t="inlineStr">
-        <is>
-          <t>UNC @ TCU</t>
-        </is>
-      </c>
-      <c r="C61" s="12" t="inlineStr">
-        <is>
-          <t>2026-08-29 16:00</t>
-        </is>
-      </c>
-      <c r="D61" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" s="12" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="F61" s="12" t="inlineStr">
-        <is>
-          <t>TCU ML</t>
-        </is>
-      </c>
-      <c r="G61" s="14" t="n"/>
-      <c r="H61" s="15" t="n">
-        <v>-310</v>
-      </c>
-      <c r="I61" s="16" t="n">
-        <v>0.6378709973210217</v>
-      </c>
-      <c r="J61" s="16" t="n">
-        <v>0.725752508361204</v>
-      </c>
-      <c r="K61" s="16" t="n">
-        <v>0.7560975609756098</v>
-      </c>
-      <c r="L61" s="17" t="n">
-        <v>-0.1182265636545881</v>
-      </c>
-      <c r="M61" s="17" t="n">
-        <v>-0.1563641648334875</v>
-      </c>
-      <c r="N61" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" s="18" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="P61" s="12" t="inlineStr">
-        <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q61" s="12" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B62" s="19" t="inlineStr">
-        <is>
-          <t>AKR @ WAKE</t>
-        </is>
-      </c>
-      <c r="C62" s="19" t="inlineStr">
-        <is>
-          <t>2026-09-03 23:00</t>
-        </is>
-      </c>
-      <c r="D62" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" s="19" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="F62" s="19" t="inlineStr">
-        <is>
-          <t>Under 49.5</t>
-        </is>
-      </c>
-      <c r="G62" s="21" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="H62" s="22" t="n">
-        <v>-108</v>
-      </c>
-      <c r="I62" s="23" t="n">
-        <v>0.396824791827995</v>
-      </c>
-      <c r="J62" s="23" t="n">
-        <v>0.4956702459300312</v>
-      </c>
-      <c r="K62" s="23" t="n">
-        <v>0.5192307692307693</v>
-      </c>
-      <c r="L62" s="24" t="n">
-        <v>-0.1224059774027743</v>
-      </c>
-      <c r="M62" s="24" t="n">
-        <v>-0.2357448453683059</v>
-      </c>
-      <c r="N62" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" s="25" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="P62" s="19" t="inlineStr">
-        <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q62" s="19" t="inlineStr">
+          <t>Draft Kings</t>
+        </is>
+      </c>
+      <c r="Q50" s="19" t="inlineStr">
         <is>
           <t>raw model/market disagreement exceeds the safety limit</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B63" s="12" t="inlineStr">
-        <is>
-          <t>SAC @ EMU</t>
-        </is>
-      </c>
-      <c r="C63" s="12" t="inlineStr">
-        <is>
-          <t>2026-08-29 22:30</t>
-        </is>
-      </c>
-      <c r="D63" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E63" s="12" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="F63" s="12" t="inlineStr">
-        <is>
-          <t>Under 52.5</t>
-        </is>
-      </c>
-      <c r="G63" s="14" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="H63" s="15" t="n">
-        <v>-112</v>
-      </c>
-      <c r="I63" s="16" t="n">
-        <v>0.404640493123267</v>
-      </c>
-      <c r="J63" s="16" t="n">
-        <v>0.5043297540699688</v>
-      </c>
-      <c r="K63" s="16" t="n">
-        <v>0.5283018867924528</v>
-      </c>
-      <c r="L63" s="17" t="n">
-        <v>-0.1236613936691858</v>
-      </c>
-      <c r="M63" s="17" t="n">
-        <v>-0.2340733523023875</v>
-      </c>
-      <c r="N63" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" s="18" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="P63" s="12" t="inlineStr">
-        <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q63" s="12" t="inlineStr">
-        <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B64" s="19" t="inlineStr">
-        <is>
-          <t>WES @ KENN</t>
-        </is>
-      </c>
-      <c r="C64" s="19" t="inlineStr">
-        <is>
-          <t>2026-09-03 23:00</t>
-        </is>
-      </c>
-      <c r="D64" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" s="19" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="F64" s="19" t="inlineStr">
-        <is>
-          <t>Under 51.5</t>
-        </is>
-      </c>
-      <c r="G64" s="21" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="H64" s="22" t="n">
-        <v>-112</v>
-      </c>
-      <c r="I64" s="23" t="n">
-        <v>0.4028929855258536</v>
-      </c>
-      <c r="J64" s="23" t="n">
-        <v>0.5043297540699688</v>
-      </c>
-      <c r="K64" s="23" t="n">
-        <v>0.5283018867924528</v>
-      </c>
-      <c r="L64" s="24" t="n">
-        <v>-0.1254089012665992</v>
-      </c>
-      <c r="M64" s="24" t="n">
-        <v>-0.2373811345403485</v>
-      </c>
-      <c r="N64" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" s="25" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="P64" s="19" t="inlineStr">
-        <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q64" s="19" t="inlineStr">
-        <is>
-          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B65" s="12" t="inlineStr">
-        <is>
-          <t>UNC @ TCU</t>
-        </is>
-      </c>
-      <c r="C65" s="12" t="inlineStr">
-        <is>
-          <t>2026-08-29 16:00</t>
-        </is>
-      </c>
-      <c r="D65" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" s="12" t="inlineStr">
-        <is>
-          <t>ATS</t>
-        </is>
-      </c>
-      <c r="F65" s="12" t="inlineStr">
-        <is>
-          <t>TCU -7.5</t>
-        </is>
-      </c>
-      <c r="G65" s="14" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="H65" s="15" t="n">
-        <v>-112</v>
-      </c>
-      <c r="I65" s="16" t="n">
-        <v>0.4006920158047088</v>
-      </c>
-      <c r="J65" s="16" t="n">
-        <v>0.5043297540699688</v>
-      </c>
-      <c r="K65" s="16" t="n">
-        <v>0.5283018867924528</v>
-      </c>
-      <c r="L65" s="17" t="n">
-        <v>-0.127609870987744</v>
-      </c>
-      <c r="M65" s="17" t="n">
-        <v>-0.2415472557982298</v>
-      </c>
-      <c r="N65" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" s="18" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="P65" s="12" t="inlineStr">
-        <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q65" s="12" t="inlineStr">
-        <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B66" s="19" t="inlineStr">
-        <is>
-          <t>HAW @ STAN</t>
-        </is>
-      </c>
-      <c r="C66" s="19" t="inlineStr">
-        <is>
-          <t>2026-08-29 23:00</t>
-        </is>
-      </c>
-      <c r="D66" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E66" s="19" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="F66" s="19" t="inlineStr">
-        <is>
-          <t>Under 49.5</t>
-        </is>
-      </c>
-      <c r="G66" s="21" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="H66" s="22" t="n">
-        <v>-115</v>
-      </c>
-      <c r="I66" s="23" t="n">
-        <v>0.4044067869561538</v>
-      </c>
-      <c r="J66" s="23" t="n">
-        <v>0.5108342361863488</v>
-      </c>
-      <c r="K66" s="23" t="n">
-        <v>0.5348837209302325</v>
-      </c>
-      <c r="L66" s="24" t="n">
-        <v>-0.1304769339740787</v>
-      </c>
-      <c r="M66" s="24" t="n">
-        <v>-0.2439351374297994</v>
-      </c>
-      <c r="N66" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" s="25" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="P66" s="19" t="inlineStr">
-        <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q66" s="19" t="inlineStr">
-        <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B67" s="12" t="inlineStr">
-        <is>
-          <t>SAC @ EMU</t>
-        </is>
-      </c>
-      <c r="C67" s="12" t="inlineStr">
-        <is>
-          <t>2026-08-29 22:30</t>
-        </is>
-      </c>
-      <c r="D67" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E67" s="12" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="F67" s="12" t="inlineStr">
-        <is>
-          <t>EMU ML</t>
-        </is>
-      </c>
-      <c r="G67" s="14" t="n"/>
-      <c r="H67" s="15" t="n">
-        <v>-355</v>
-      </c>
-      <c r="I67" s="16" t="n">
-        <v>0.6313778129495795</v>
-      </c>
-      <c r="J67" s="16" t="n">
-        <v>0.7477827050997783</v>
-      </c>
-      <c r="K67" s="16" t="n">
-        <v>0.7802197802197802</v>
-      </c>
-      <c r="L67" s="17" t="n">
-        <v>-0.1488419672702007</v>
-      </c>
-      <c r="M67" s="17" t="n">
-        <v>-0.1907692819942009</v>
-      </c>
-      <c r="N67" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O67" s="18" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="P67" s="12" t="inlineStr">
-        <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q67" s="12" t="inlineStr">
-        <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B68" s="19" t="inlineStr">
-        <is>
-          <t>ALB @ BUFF</t>
-        </is>
-      </c>
-      <c r="C68" s="19" t="inlineStr">
-        <is>
-          <t>2026-09-03 23:00</t>
-        </is>
-      </c>
-      <c r="D68" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E68" s="19" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="F68" s="19" t="inlineStr">
-        <is>
-          <t>Under 48.5</t>
-        </is>
-      </c>
-      <c r="G68" s="21" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="H68" s="22" t="n">
-        <v>-112</v>
-      </c>
-      <c r="I68" s="23" t="n">
-        <v>0.3762461039069736</v>
-      </c>
-      <c r="J68" s="23" t="n">
-        <v>0.5043297540699688</v>
-      </c>
-      <c r="K68" s="23" t="n">
-        <v>0.5283018867924528</v>
-      </c>
-      <c r="L68" s="24" t="n">
-        <v>-0.1520557828854793</v>
-      </c>
-      <c r="M68" s="24" t="n">
-        <v>-0.2878198747475144</v>
-      </c>
-      <c r="N68" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" s="25" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="P68" s="19" t="inlineStr">
-        <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q68" s="19" t="inlineStr">
-        <is>
-          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B69" s="12" t="inlineStr">
-        <is>
-          <t>SAC @ EMU</t>
-        </is>
-      </c>
-      <c r="C69" s="12" t="inlineStr">
-        <is>
-          <t>2026-08-29 22:30</t>
-        </is>
-      </c>
-      <c r="D69" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" s="12" t="inlineStr">
-        <is>
-          <t>ATS</t>
-        </is>
-      </c>
-      <c r="F69" s="12" t="inlineStr">
-        <is>
-          <t>EMU -9.5</t>
-        </is>
-      </c>
-      <c r="G69" s="14" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="H69" s="15" t="n">
-        <v>-110</v>
-      </c>
-      <c r="I69" s="16" t="n">
-        <v>0.3626957910893782</v>
-      </c>
-      <c r="J69" s="16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K69" s="16" t="n">
-        <v>0.5238095238095238</v>
-      </c>
-      <c r="L69" s="17" t="n">
-        <v>-0.1611137327201456</v>
-      </c>
-      <c r="M69" s="17" t="n">
-        <v>-0.3075807624657325</v>
-      </c>
-      <c r="N69" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" s="18" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="P69" s="12" t="inlineStr">
-        <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q69" s="12" t="inlineStr">
-        <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B70" s="19" t="inlineStr">
-        <is>
-          <t>JVST @ NDSU</t>
-        </is>
-      </c>
-      <c r="C70" s="19" t="inlineStr">
-        <is>
-          <t>2026-08-29 21:30</t>
-        </is>
-      </c>
-      <c r="D70" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E70" s="19" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="F70" s="19" t="inlineStr">
-        <is>
-          <t>Under 46.5</t>
-        </is>
-      </c>
-      <c r="G70" s="21" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="H70" s="22" t="n">
-        <v>-110</v>
-      </c>
-      <c r="I70" s="23" t="n">
-        <v>0.3446651319186821</v>
-      </c>
-      <c r="J70" s="23" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K70" s="23" t="n">
-        <v>0.5238095238095238</v>
-      </c>
-      <c r="L70" s="24" t="n">
-        <v>-0.1791443918908417</v>
-      </c>
-      <c r="M70" s="24" t="n">
-        <v>-0.3420029299734251</v>
-      </c>
-      <c r="N70" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" s="25" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="P70" s="19" t="inlineStr">
-        <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q70" s="19" t="inlineStr">
-        <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B71" s="12" t="inlineStr">
-        <is>
-          <t>MASS @ RUTG</t>
-        </is>
-      </c>
-      <c r="C71" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-03 22:00</t>
-        </is>
-      </c>
-      <c r="D71" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E71" s="12" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="F71" s="12" t="inlineStr">
-        <is>
-          <t>RUTG ML</t>
-        </is>
-      </c>
-      <c r="G71" s="14" t="n"/>
-      <c r="H71" s="15" t="n">
-        <v>-6500</v>
-      </c>
-      <c r="I71" s="16" t="n">
-        <v>0.8036923684058288</v>
-      </c>
-      <c r="J71" s="16" t="n">
-        <v>0.9538784067085954</v>
-      </c>
-      <c r="K71" s="16" t="n">
-        <v>0.9848484848484849</v>
-      </c>
-      <c r="L71" s="17" t="n">
-        <v>-0.1811561164426561</v>
-      </c>
-      <c r="M71" s="17" t="n">
-        <v>-0.183943133618697</v>
-      </c>
-      <c r="N71" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" s="18" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="P71" s="12" t="inlineStr">
-        <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q71" s="12" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B72" s="19" t="inlineStr">
-        <is>
-          <t>AKR @ WAKE</t>
-        </is>
-      </c>
-      <c r="C72" s="19" t="inlineStr">
-        <is>
-          <t>2026-09-03 23:00</t>
-        </is>
-      </c>
-      <c r="D72" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E72" s="19" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="F72" s="19" t="inlineStr">
-        <is>
-          <t>WAKE ML</t>
-        </is>
-      </c>
-      <c r="G72" s="21" t="n"/>
-      <c r="H72" s="22" t="n">
-        <v>-2800</v>
-      </c>
-      <c r="I72" s="23" t="n">
-        <v>0.7689464432363347</v>
-      </c>
-      <c r="J72" s="23" t="n">
-        <v>0.9311163895486935</v>
-      </c>
-      <c r="K72" s="23" t="n">
-        <v>0.9655172413793104</v>
-      </c>
-      <c r="L72" s="24" t="n">
-        <v>-0.1965707981429757</v>
-      </c>
-      <c r="M72" s="24" t="n">
-        <v>-0.203591183790939</v>
-      </c>
-      <c r="N72" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" s="25" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="P72" s="19" t="inlineStr">
-        <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q72" s="19" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B73" s="12" t="inlineStr">
-        <is>
-          <t>NMSU @ FSU</t>
-        </is>
-      </c>
-      <c r="C73" s="12" t="inlineStr">
-        <is>
-          <t>2026-08-29 23:00</t>
-        </is>
-      </c>
-      <c r="D73" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" s="12" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="F73" s="12" t="inlineStr">
-        <is>
-          <t>FSU ML</t>
-        </is>
-      </c>
-      <c r="G73" s="14" t="n"/>
-      <c r="H73" s="15" t="n">
-        <v>-6500</v>
-      </c>
-      <c r="I73" s="16" t="n">
-        <v>0.7810227846843814</v>
-      </c>
-      <c r="J73" s="16" t="n">
-        <v>0.9538784067085954</v>
-      </c>
-      <c r="K73" s="16" t="n">
-        <v>0.9848484848484849</v>
-      </c>
-      <c r="L73" s="17" t="n">
-        <v>-0.2038257001641035</v>
-      </c>
-      <c r="M73" s="17" t="n">
-        <v>-0.2069614801666282</v>
-      </c>
-      <c r="N73" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" s="18" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="P73" s="12" t="inlineStr">
-        <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q73" s="12" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B74" s="19" t="inlineStr">
-        <is>
-          <t>WES @ KENN</t>
-        </is>
-      </c>
-      <c r="C74" s="19" t="inlineStr">
-        <is>
-          <t>2026-09-03 23:00</t>
-        </is>
-      </c>
-      <c r="D74" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E74" s="19" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="F74" s="19" t="inlineStr">
-        <is>
-          <t>KENN ML</t>
-        </is>
-      </c>
-      <c r="G74" s="21" t="n"/>
-      <c r="H74" s="22" t="n">
-        <v>-3600</v>
-      </c>
-      <c r="I74" s="23" t="n">
-        <v>0.7629882523168648</v>
-      </c>
-      <c r="J74" s="23" t="n">
-        <v>0.9396411092985318</v>
-      </c>
-      <c r="K74" s="23" t="n">
-        <v>0.972972972972973</v>
-      </c>
-      <c r="L74" s="24" t="n">
-        <v>-0.2099847206561082</v>
-      </c>
-      <c r="M74" s="24" t="n">
-        <v>-0.2158176295632223</v>
-      </c>
-      <c r="N74" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" s="25" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="P74" s="19" t="inlineStr">
-        <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q74" s="19" t="inlineStr">
-        <is>
-          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B75" s="12" t="inlineStr">
-        <is>
-          <t>MRMK @ DEL</t>
-        </is>
-      </c>
-      <c r="C75" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-03 23:00</t>
-        </is>
-      </c>
-      <c r="D75" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E75" s="12" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="F75" s="12" t="inlineStr">
-        <is>
-          <t>DEL ML</t>
-        </is>
-      </c>
-      <c r="G75" s="14" t="n"/>
-      <c r="H75" s="15" t="n">
-        <v>-10000</v>
-      </c>
-      <c r="I75" s="16" t="n">
-        <v>0.7657797338257375</v>
-      </c>
-      <c r="J75" s="16" t="n">
-        <v>0.9684473601999376</v>
-      </c>
-      <c r="K75" s="16" t="n">
-        <v>0.9900990099009901</v>
-      </c>
-      <c r="L75" s="17" t="n">
-        <v>-0.2243192760752526</v>
-      </c>
-      <c r="M75" s="17" t="n">
-        <v>-0.2265624688360051</v>
-      </c>
-      <c r="N75" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" s="18" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="P75" s="12" t="inlineStr">
-        <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q75" s="12" t="inlineStr">
-        <is>
-          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B76" s="19" t="inlineStr">
-        <is>
-          <t>ALB @ BUFF</t>
-        </is>
-      </c>
-      <c r="C76" s="19" t="inlineStr">
-        <is>
-          <t>2026-09-03 23:00</t>
-        </is>
-      </c>
-      <c r="D76" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E76" s="19" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="F76" s="19" t="inlineStr">
-        <is>
-          <t>BUFF ML</t>
-        </is>
-      </c>
-      <c r="G76" s="21" t="n"/>
-      <c r="H76" s="22" t="n">
-        <v>-8000</v>
-      </c>
-      <c r="I76" s="23" t="n">
-        <v>0.7599039260434692</v>
-      </c>
-      <c r="J76" s="23" t="n">
-        <v>0.9578344612181156</v>
-      </c>
-      <c r="K76" s="23" t="n">
-        <v>0.9876543209876543</v>
-      </c>
-      <c r="L76" s="24" t="n">
-        <v>-0.227750394944185</v>
-      </c>
-      <c r="M76" s="24" t="n">
-        <v>-0.2305972748809874</v>
-      </c>
-      <c r="N76" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" s="25" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="P76" s="19" t="inlineStr">
-        <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q76" s="19" t="inlineStr">
-        <is>
-          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B77" s="12" t="inlineStr">
-        <is>
-          <t>WES @ KENN</t>
-        </is>
-      </c>
-      <c r="C77" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-03 23:00</t>
-        </is>
-      </c>
-      <c r="D77" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E77" s="12" t="inlineStr">
-        <is>
-          <t>ATS</t>
-        </is>
-      </c>
-      <c r="F77" s="12" t="inlineStr">
-        <is>
-          <t>KENN -22.5</t>
-        </is>
-      </c>
-      <c r="G77" s="14" t="n">
-        <v>-22.5</v>
-      </c>
-      <c r="H77" s="15" t="n">
-        <v>-105</v>
-      </c>
-      <c r="I77" s="16" t="n">
-        <v>0.2726533482579036</v>
-      </c>
-      <c r="J77" s="16" t="n">
-        <v>0.4891657638136511</v>
-      </c>
-      <c r="K77" s="16" t="n">
-        <v>0.5121951219512195</v>
-      </c>
-      <c r="L77" s="17" t="n">
-        <v>-0.2395417736933159</v>
-      </c>
-      <c r="M77" s="17" t="n">
-        <v>-0.4676767962583787</v>
-      </c>
-      <c r="N77" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" s="18" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="P77" s="12" t="inlineStr">
-        <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q77" s="12" t="inlineStr">
-        <is>
-          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B78" s="19" t="inlineStr">
-        <is>
-          <t>AKR @ WAKE</t>
-        </is>
-      </c>
-      <c r="C78" s="19" t="inlineStr">
-        <is>
-          <t>2026-09-03 23:00</t>
-        </is>
-      </c>
-      <c r="D78" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E78" s="19" t="inlineStr">
-        <is>
-          <t>ATS</t>
-        </is>
-      </c>
-      <c r="F78" s="19" t="inlineStr">
-        <is>
-          <t>WAKE -23.5</t>
-        </is>
-      </c>
-      <c r="G78" s="21" t="n">
-        <v>-23.5</v>
-      </c>
-      <c r="H78" s="22" t="n">
-        <v>-112</v>
-      </c>
-      <c r="I78" s="23" t="n">
-        <v>0.279786024178475</v>
-      </c>
-      <c r="J78" s="23" t="n">
-        <v>0.5043297540699688</v>
-      </c>
-      <c r="K78" s="23" t="n">
-        <v>0.5283018867924528</v>
-      </c>
-      <c r="L78" s="24" t="n">
-        <v>-0.2485158626139778</v>
-      </c>
-      <c r="M78" s="24" t="n">
-        <v>-0.4704050256621722</v>
-      </c>
-      <c r="N78" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" s="25" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="P78" s="19" t="inlineStr">
-        <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q78" s="19" t="inlineStr">
-        <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B79" s="12" t="inlineStr">
-        <is>
-          <t>ALB @ BUFF</t>
-        </is>
-      </c>
-      <c r="C79" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-03 23:00</t>
-        </is>
-      </c>
-      <c r="D79" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E79" s="12" t="inlineStr">
-        <is>
-          <t>ATS</t>
-        </is>
-      </c>
-      <c r="F79" s="12" t="inlineStr">
-        <is>
-          <t>BUFF -24.5</t>
-        </is>
-      </c>
-      <c r="G79" s="14" t="n">
-        <v>-24.5</v>
-      </c>
-      <c r="H79" s="15" t="n">
-        <v>-108</v>
-      </c>
-      <c r="I79" s="16" t="n">
-        <v>0.2657449776111079</v>
-      </c>
-      <c r="J79" s="16" t="n">
-        <v>0.4956702459300312</v>
-      </c>
-      <c r="K79" s="16" t="n">
-        <v>0.5192307692307693</v>
-      </c>
-      <c r="L79" s="17" t="n">
-        <v>-0.2534857916196613</v>
-      </c>
-      <c r="M79" s="17" t="n">
-        <v>-0.4881948579341625</v>
-      </c>
-      <c r="N79" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" s="18" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="P79" s="12" t="inlineStr">
-        <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q79" s="12" t="inlineStr">
-        <is>
-          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B80" s="19" t="inlineStr">
-        <is>
-          <t>NMSU @ FSU</t>
-        </is>
-      </c>
-      <c r="C80" s="19" t="inlineStr">
-        <is>
-          <t>2026-08-29 23:00</t>
-        </is>
-      </c>
-      <c r="D80" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E80" s="19" t="inlineStr">
-        <is>
-          <t>ATS</t>
-        </is>
-      </c>
-      <c r="F80" s="19" t="inlineStr">
-        <is>
-          <t>FSU -31.5</t>
-        </is>
-      </c>
-      <c r="G80" s="21" t="n">
-        <v>-31.5</v>
-      </c>
-      <c r="H80" s="22" t="n">
-        <v>-105</v>
-      </c>
-      <c r="I80" s="23" t="n">
-        <v>0.2515947455243119</v>
-      </c>
-      <c r="J80" s="23" t="n">
-        <v>0.4891657638136511</v>
-      </c>
-      <c r="K80" s="23" t="n">
-        <v>0.5121951219512195</v>
-      </c>
-      <c r="L80" s="24" t="n">
-        <v>-0.2606003764269076</v>
-      </c>
-      <c r="M80" s="24" t="n">
-        <v>-0.5087912111192006</v>
-      </c>
-      <c r="N80" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" s="25" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="P80" s="19" t="inlineStr">
-        <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q80" s="19" t="inlineStr">
-        <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B81" s="12" t="inlineStr">
-        <is>
-          <t>SJSU @ USC</t>
-        </is>
-      </c>
-      <c r="C81" s="12" t="inlineStr">
-        <is>
-          <t>2026-08-29 19:00</t>
-        </is>
-      </c>
-      <c r="D81" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E81" s="12" t="inlineStr">
-        <is>
-          <t>ATS</t>
-        </is>
-      </c>
-      <c r="F81" s="12" t="inlineStr">
-        <is>
-          <t>USC -38.5</t>
-        </is>
-      </c>
-      <c r="G81" s="14" t="n">
-        <v>-38.5</v>
-      </c>
-      <c r="H81" s="15" t="n">
-        <v>-102</v>
-      </c>
-      <c r="I81" s="16" t="n">
-        <v>0.2436390210930696</v>
-      </c>
-      <c r="J81" s="16" t="n">
-        <v>0.4826358742837298</v>
-      </c>
-      <c r="K81" s="16" t="n">
-        <v>0.504950495049505</v>
-      </c>
-      <c r="L81" s="17" t="n">
-        <v>-0.2613114739564354</v>
-      </c>
-      <c r="M81" s="17" t="n">
-        <v>-0.517499193521568</v>
-      </c>
-      <c r="N81" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" s="18" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="P81" s="12" t="inlineStr">
-        <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q81" s="12" t="inlineStr">
-        <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B82" s="19" t="inlineStr">
-        <is>
-          <t>MASS @ RUTG</t>
-        </is>
-      </c>
-      <c r="C82" s="19" t="inlineStr">
-        <is>
-          <t>2026-09-03 22:00</t>
-        </is>
-      </c>
-      <c r="D82" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E82" s="19" t="inlineStr">
-        <is>
-          <t>ATS</t>
-        </is>
-      </c>
-      <c r="F82" s="19" t="inlineStr">
-        <is>
-          <t>RUTG -30.5</t>
-        </is>
-      </c>
-      <c r="G82" s="21" t="n">
-        <v>-30.5</v>
-      </c>
-      <c r="H82" s="22" t="n">
-        <v>-112</v>
-      </c>
-      <c r="I82" s="23" t="n">
-        <v>0.2637706885532299</v>
-      </c>
-      <c r="J82" s="23" t="n">
-        <v>0.5043297540699688</v>
-      </c>
-      <c r="K82" s="23" t="n">
-        <v>0.5283018867924528</v>
-      </c>
-      <c r="L82" s="24" t="n">
-        <v>-0.2645311982392229</v>
-      </c>
-      <c r="M82" s="24" t="n">
-        <v>-0.5007197680956719</v>
-      </c>
-      <c r="N82" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" s="25" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="P82" s="19" t="inlineStr">
-        <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q82" s="19" t="inlineStr">
-        <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B83" s="12" t="inlineStr">
-        <is>
-          <t>MRMK @ DEL</t>
-        </is>
-      </c>
-      <c r="C83" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-03 23:00</t>
-        </is>
-      </c>
-      <c r="D83" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E83" s="12" t="inlineStr">
-        <is>
-          <t>ATS</t>
-        </is>
-      </c>
-      <c r="F83" s="12" t="inlineStr">
-        <is>
-          <t>DEL -28.5</t>
-        </is>
-      </c>
-      <c r="G83" s="14" t="n">
-        <v>-28.5</v>
-      </c>
-      <c r="H83" s="15" t="n">
-        <v>-112</v>
-      </c>
-      <c r="I83" s="16" t="n">
-        <v>0.2613150626201174</v>
-      </c>
-      <c r="J83" s="16" t="n">
-        <v>0.5043297540699688</v>
-      </c>
-      <c r="K83" s="16" t="n">
-        <v>0.5283018867924528</v>
-      </c>
-      <c r="L83" s="17" t="n">
-        <v>-0.2669868241723354</v>
-      </c>
-      <c r="M83" s="17" t="n">
-        <v>-0.5053679171833493</v>
-      </c>
-      <c r="N83" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" s="18" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="P83" s="12" t="inlineStr">
-        <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q83" s="12" t="inlineStr">
-        <is>
-          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B84" s="19" t="inlineStr">
-        <is>
-          <t>BCU @ UCF</t>
-        </is>
-      </c>
-      <c r="C84" s="19" t="inlineStr">
-        <is>
-          <t>2026-09-03 23:00</t>
-        </is>
-      </c>
-      <c r="D84" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E84" s="19" t="inlineStr">
-        <is>
-          <t>ATS</t>
-        </is>
-      </c>
-      <c r="F84" s="19" t="inlineStr">
-        <is>
-          <t>UCF -42.5</t>
-        </is>
-      </c>
-      <c r="G84" s="21" t="n">
-        <v>-42.5</v>
-      </c>
-      <c r="H84" s="22" t="n">
-        <v>-108</v>
-      </c>
-      <c r="I84" s="23" t="n">
-        <v>0.2482518098143184</v>
-      </c>
-      <c r="J84" s="23" t="n">
-        <v>0.4956702459300312</v>
-      </c>
-      <c r="K84" s="23" t="n">
-        <v>0.5192307692307693</v>
-      </c>
-      <c r="L84" s="24" t="n">
-        <v>-0.2709789594164509</v>
-      </c>
-      <c r="M84" s="24" t="n">
-        <v>-0.521885403320572</v>
-      </c>
-      <c r="N84" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" s="25" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="P84" s="19" t="inlineStr">
-        <is>
-          <t>DraftKings</t>
-        </is>
-      </c>
-      <c r="Q84" s="19" t="inlineStr">
-        <is>
-          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -13047,7 +10797,7 @@
       </c>
       <c r="M5" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
     </row>
@@ -13092,7 +10842,7 @@
       <c r="L6" s="22" t="n"/>
       <c r="M6" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
     </row>
@@ -13141,7 +10891,7 @@
       </c>
       <c r="M7" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
     </row>
@@ -13190,7 +10940,7 @@
       </c>
       <c r="M8" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
     </row>
@@ -13239,7 +10989,7 @@
       </c>
       <c r="M9" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
     </row>
@@ -13288,7 +11038,7 @@
       </c>
       <c r="M10" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
     </row>
@@ -13337,7 +11087,7 @@
       </c>
       <c r="M11" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
     </row>
@@ -13386,7 +11136,7 @@
       </c>
       <c r="M12" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
     </row>

--- a/NCAAF_Edge_Model.xlsx
+++ b/NCAAF_Edge_Model.xlsx
@@ -638,7 +638,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-23T19:08:04+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
+          <t>Generated 2026-08-23T21:44:22+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
         </is>
       </c>
     </row>
@@ -1168,11 +1168,11 @@
         <v>0</v>
       </c>
       <c r="O5" s="18" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P5" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q5" s="12" t="inlineStr">
@@ -1235,11 +1235,11 @@
         <v>0</v>
       </c>
       <c r="O6" s="25" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P6" s="19" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q6" s="19" t="inlineStr">
@@ -1300,11 +1300,11 @@
         <v>0</v>
       </c>
       <c r="O7" s="18" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P7" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q7" s="12" t="inlineStr">
@@ -1367,11 +1367,11 @@
         <v>0</v>
       </c>
       <c r="O8" s="25" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P8" s="19" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q8" s="19" t="inlineStr">
@@ -1434,11 +1434,11 @@
         <v>0</v>
       </c>
       <c r="O9" s="18" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P9" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q9" s="12" t="inlineStr">
@@ -1499,11 +1499,11 @@
         <v>0</v>
       </c>
       <c r="O10" s="25" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P10" s="19" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q10" s="19" t="inlineStr">
@@ -1566,11 +1566,11 @@
         <v>0</v>
       </c>
       <c r="O11" s="18" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P11" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q11" s="12" t="inlineStr">
@@ -1633,11 +1633,11 @@
         <v>0</v>
       </c>
       <c r="O12" s="25" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P12" s="19" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q12" s="19" t="inlineStr">
@@ -1698,11 +1698,11 @@
         <v>0</v>
       </c>
       <c r="O13" s="18" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P13" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q13" s="12" t="n"/>
@@ -1761,11 +1761,11 @@
         <v>0</v>
       </c>
       <c r="O14" s="25" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P14" s="19" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q14" s="19" t="inlineStr">
@@ -1826,11 +1826,11 @@
         <v>0</v>
       </c>
       <c r="O15" s="18" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P15" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q15" s="12" t="n"/>
@@ -1889,11 +1889,11 @@
         <v>0</v>
       </c>
       <c r="O16" s="25" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P16" s="19" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q16" s="19" t="n"/>
@@ -1950,11 +1950,11 @@
         <v>0</v>
       </c>
       <c r="O17" s="18" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P17" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q17" s="12" t="n"/>
@@ -2013,11 +2013,11 @@
         <v>0</v>
       </c>
       <c r="O18" s="25" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P18" s="19" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q18" s="19" t="n"/>
@@ -2076,11 +2076,11 @@
         <v>0</v>
       </c>
       <c r="O19" s="18" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P19" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q19" s="12" t="n"/>
@@ -2139,11 +2139,11 @@
         <v>0.0505</v>
       </c>
       <c r="O20" s="25" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P20" s="19" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q20" s="19" t="n"/>
@@ -2202,11 +2202,11 @@
         <v>0</v>
       </c>
       <c r="O21" s="18" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P21" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q21" s="12" t="n"/>
@@ -2263,11 +2263,11 @@
         <v>0</v>
       </c>
       <c r="O22" s="25" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P22" s="19" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q22" s="19" t="n"/>
@@ -2326,11 +2326,11 @@
         <v>0</v>
       </c>
       <c r="O23" s="18" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P23" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q23" s="12" t="n"/>
@@ -2387,11 +2387,11 @@
         <v>0</v>
       </c>
       <c r="O24" s="25" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P24" s="19" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q24" s="19" t="n"/>
@@ -2450,11 +2450,11 @@
         <v>0</v>
       </c>
       <c r="O25" s="18" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P25" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q25" s="12" t="n"/>
@@ -2513,11 +2513,11 @@
         <v>0</v>
       </c>
       <c r="O26" s="25" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P26" s="19" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q26" s="19" t="n"/>
@@ -2576,11 +2576,11 @@
         <v>0</v>
       </c>
       <c r="O27" s="18" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P27" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q27" s="12" t="n"/>
@@ -2639,11 +2639,11 @@
         <v>0</v>
       </c>
       <c r="O28" s="25" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P28" s="19" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q28" s="19" t="n"/>
@@ -2702,11 +2702,11 @@
         <v>0</v>
       </c>
       <c r="O29" s="18" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P29" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q29" s="12" t="n"/>
@@ -2765,11 +2765,11 @@
         <v>0</v>
       </c>
       <c r="O30" s="25" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P30" s="19" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q30" s="19" t="n"/>
@@ -2826,11 +2826,11 @@
         <v>0</v>
       </c>
       <c r="O31" s="18" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P31" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q31" s="12" t="n"/>
@@ -2887,11 +2887,11 @@
         <v>0</v>
       </c>
       <c r="O32" s="25" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P32" s="19" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q32" s="19" t="n"/>
@@ -2950,11 +2950,11 @@
         <v>0</v>
       </c>
       <c r="O33" s="18" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P33" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q33" s="12" t="n"/>
@@ -3013,11 +3013,11 @@
         <v>0</v>
       </c>
       <c r="O34" s="25" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P34" s="19" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q34" s="19" t="n"/>
@@ -3076,11 +3076,11 @@
         <v>0.0505</v>
       </c>
       <c r="O35" s="18" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P35" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q35" s="12" t="n"/>
@@ -3139,11 +3139,11 @@
         <v>0</v>
       </c>
       <c r="O36" s="25" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P36" s="19" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q36" s="19" t="n"/>
@@ -3200,11 +3200,11 @@
         <v>0</v>
       </c>
       <c r="O37" s="18" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P37" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q37" s="12" t="n"/>
@@ -3263,11 +3263,11 @@
         <v>0</v>
       </c>
       <c r="O38" s="25" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P38" s="19" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q38" s="19" t="n"/>
@@ -3324,11 +3324,11 @@
         <v>0</v>
       </c>
       <c r="O39" s="18" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P39" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q39" s="12" t="n"/>
@@ -3387,11 +3387,11 @@
         <v>0</v>
       </c>
       <c r="O40" s="25" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P40" s="19" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q40" s="19" t="n"/>
@@ -3448,11 +3448,11 @@
         <v>0</v>
       </c>
       <c r="O41" s="18" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P41" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q41" s="12" t="n"/>
@@ -3511,11 +3511,11 @@
         <v>0</v>
       </c>
       <c r="O42" s="25" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P42" s="19" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q42" s="19" t="inlineStr">
@@ -3578,11 +3578,11 @@
         <v>0</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P43" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q43" s="12" t="inlineStr">
@@ -3645,11 +3645,11 @@
         <v>0</v>
       </c>
       <c r="O44" s="25" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P44" s="19" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q44" s="19" t="inlineStr">
@@ -3710,11 +3710,11 @@
         <v>0</v>
       </c>
       <c r="O45" s="18" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P45" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q45" s="12" t="inlineStr">
@@ -3777,11 +3777,11 @@
         <v>0</v>
       </c>
       <c r="O46" s="25" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P46" s="19" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q46" s="19" t="inlineStr">
@@ -3844,11 +3844,11 @@
         <v>0</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P47" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q47" s="12" t="inlineStr">
@@ -3909,11 +3909,11 @@
         <v>0</v>
       </c>
       <c r="O48" s="25" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P48" s="19" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q48" s="19" t="inlineStr">
@@ -3976,11 +3976,11 @@
         <v>0</v>
       </c>
       <c r="O49" s="18" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P49" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q49" s="12" t="inlineStr">
@@ -4043,11 +4043,11 @@
         <v>0</v>
       </c>
       <c r="O50" s="25" t="n">
-        <v>0.375</v>
+        <v>0.4125</v>
       </c>
       <c r="P50" s="19" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q50" s="19" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="M5" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       <c r="L6" s="22" t="n"/>
       <c r="M6" s="19" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="M7" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="M8" s="19" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="M9" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="M10" s="19" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="M11" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="M12" s="19" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>

--- a/NCAAF_Edge_Model.xlsx
+++ b/NCAAF_Edge_Model.xlsx
@@ -638,7 +638,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-23T21:44:22+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
+          <t>Generated 2026-08-23T22:20:07+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
         </is>
       </c>
     </row>
@@ -1168,11 +1168,11 @@
         <v>0</v>
       </c>
       <c r="O5" s="18" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P5" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q5" s="12" t="inlineStr">
@@ -1235,11 +1235,11 @@
         <v>0</v>
       </c>
       <c r="O6" s="25" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P6" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q6" s="19" t="inlineStr">
@@ -1300,11 +1300,11 @@
         <v>0</v>
       </c>
       <c r="O7" s="18" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P7" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q7" s="12" t="inlineStr">
@@ -1367,11 +1367,11 @@
         <v>0</v>
       </c>
       <c r="O8" s="25" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P8" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q8" s="19" t="inlineStr">
@@ -1434,11 +1434,11 @@
         <v>0</v>
       </c>
       <c r="O9" s="18" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P9" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q9" s="12" t="inlineStr">
@@ -1499,11 +1499,11 @@
         <v>0</v>
       </c>
       <c r="O10" s="25" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P10" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q10" s="19" t="inlineStr">
@@ -1566,11 +1566,11 @@
         <v>0</v>
       </c>
       <c r="O11" s="18" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P11" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q11" s="12" t="inlineStr">
@@ -1633,11 +1633,11 @@
         <v>0</v>
       </c>
       <c r="O12" s="25" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P12" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q12" s="19" t="inlineStr">
@@ -1698,11 +1698,11 @@
         <v>0</v>
       </c>
       <c r="O13" s="18" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P13" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q13" s="12" t="n"/>
@@ -1761,11 +1761,11 @@
         <v>0</v>
       </c>
       <c r="O14" s="25" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P14" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q14" s="19" t="inlineStr">
@@ -1826,11 +1826,11 @@
         <v>0</v>
       </c>
       <c r="O15" s="18" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P15" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q15" s="12" t="n"/>
@@ -1889,11 +1889,11 @@
         <v>0</v>
       </c>
       <c r="O16" s="25" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P16" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q16" s="19" t="n"/>
@@ -1950,11 +1950,11 @@
         <v>0</v>
       </c>
       <c r="O17" s="18" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P17" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q17" s="12" t="n"/>
@@ -2013,11 +2013,11 @@
         <v>0</v>
       </c>
       <c r="O18" s="25" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P18" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q18" s="19" t="n"/>
@@ -2076,11 +2076,11 @@
         <v>0</v>
       </c>
       <c r="O19" s="18" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P19" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q19" s="12" t="n"/>
@@ -2139,11 +2139,11 @@
         <v>0.0505</v>
       </c>
       <c r="O20" s="25" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P20" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q20" s="19" t="n"/>
@@ -2202,11 +2202,11 @@
         <v>0</v>
       </c>
       <c r="O21" s="18" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P21" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q21" s="12" t="n"/>
@@ -2263,11 +2263,11 @@
         <v>0</v>
       </c>
       <c r="O22" s="25" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P22" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q22" s="19" t="n"/>
@@ -2326,11 +2326,11 @@
         <v>0</v>
       </c>
       <c r="O23" s="18" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P23" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q23" s="12" t="n"/>
@@ -2387,11 +2387,11 @@
         <v>0</v>
       </c>
       <c r="O24" s="25" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P24" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q24" s="19" t="n"/>
@@ -2450,11 +2450,11 @@
         <v>0</v>
       </c>
       <c r="O25" s="18" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P25" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q25" s="12" t="n"/>
@@ -2513,11 +2513,11 @@
         <v>0</v>
       </c>
       <c r="O26" s="25" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P26" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q26" s="19" t="n"/>
@@ -2576,11 +2576,11 @@
         <v>0</v>
       </c>
       <c r="O27" s="18" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P27" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q27" s="12" t="n"/>
@@ -2639,11 +2639,11 @@
         <v>0</v>
       </c>
       <c r="O28" s="25" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P28" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q28" s="19" t="n"/>
@@ -2702,11 +2702,11 @@
         <v>0</v>
       </c>
       <c r="O29" s="18" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P29" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q29" s="12" t="n"/>
@@ -2765,11 +2765,11 @@
         <v>0</v>
       </c>
       <c r="O30" s="25" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P30" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q30" s="19" t="n"/>
@@ -2826,11 +2826,11 @@
         <v>0</v>
       </c>
       <c r="O31" s="18" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P31" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q31" s="12" t="n"/>
@@ -2887,11 +2887,11 @@
         <v>0</v>
       </c>
       <c r="O32" s="25" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P32" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q32" s="19" t="n"/>
@@ -2950,11 +2950,11 @@
         <v>0</v>
       </c>
       <c r="O33" s="18" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P33" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q33" s="12" t="n"/>
@@ -3013,11 +3013,11 @@
         <v>0</v>
       </c>
       <c r="O34" s="25" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P34" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q34" s="19" t="n"/>
@@ -3076,11 +3076,11 @@
         <v>0.0505</v>
       </c>
       <c r="O35" s="18" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P35" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q35" s="12" t="n"/>
@@ -3139,11 +3139,11 @@
         <v>0</v>
       </c>
       <c r="O36" s="25" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P36" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q36" s="19" t="n"/>
@@ -3200,11 +3200,11 @@
         <v>0</v>
       </c>
       <c r="O37" s="18" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P37" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q37" s="12" t="n"/>
@@ -3263,11 +3263,11 @@
         <v>0</v>
       </c>
       <c r="O38" s="25" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P38" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q38" s="19" t="n"/>
@@ -3324,11 +3324,11 @@
         <v>0</v>
       </c>
       <c r="O39" s="18" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P39" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q39" s="12" t="n"/>
@@ -3387,11 +3387,11 @@
         <v>0</v>
       </c>
       <c r="O40" s="25" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P40" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q40" s="19" t="n"/>
@@ -3448,11 +3448,11 @@
         <v>0</v>
       </c>
       <c r="O41" s="18" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P41" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q41" s="12" t="n"/>
@@ -3511,11 +3511,11 @@
         <v>0</v>
       </c>
       <c r="O42" s="25" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P42" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q42" s="19" t="inlineStr">
@@ -3578,11 +3578,11 @@
         <v>0</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P43" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q43" s="12" t="inlineStr">
@@ -3645,11 +3645,11 @@
         <v>0</v>
       </c>
       <c r="O44" s="25" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P44" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q44" s="19" t="inlineStr">
@@ -3710,11 +3710,11 @@
         <v>0</v>
       </c>
       <c r="O45" s="18" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P45" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q45" s="12" t="inlineStr">
@@ -3777,11 +3777,11 @@
         <v>0</v>
       </c>
       <c r="O46" s="25" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P46" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q46" s="19" t="inlineStr">
@@ -3844,11 +3844,11 @@
         <v>0</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P47" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q47" s="12" t="inlineStr">
@@ -3909,11 +3909,11 @@
         <v>0</v>
       </c>
       <c r="O48" s="25" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P48" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q48" s="19" t="inlineStr">
@@ -3976,11 +3976,11 @@
         <v>0</v>
       </c>
       <c r="O49" s="18" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P49" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q49" s="12" t="inlineStr">
@@ -4043,11 +4043,11 @@
         <v>0</v>
       </c>
       <c r="O50" s="25" t="n">
-        <v>0.4125</v>
+        <v>0.45</v>
       </c>
       <c r="P50" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
       <c r="Q50" s="19" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="M5" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       <c r="L6" s="22" t="n"/>
       <c r="M6" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="M7" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="M8" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="M9" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="M10" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="M11" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="M12" s="19" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
     </row>

--- a/NCAAF_Edge_Model.xlsx
+++ b/NCAAF_Edge_Model.xlsx
@@ -271,8 +271,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BoardTable" displayName="BoardTable" ref="A4:Q50" headerRowCount="1">
-  <autoFilter ref="A4:Q50"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BoardTable" displayName="BoardTable" ref="A4:Q84" headerRowCount="1">
+  <autoFilter ref="A4:Q84"/>
   <tableColumns count="17">
     <tableColumn id="1" name="Tier"/>
     <tableColumn id="2" name="Game"/>
@@ -640,7 +640,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-23T22:54:08+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
+          <t>Generated 2026-08-24T05:24:18+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q50"/>
+  <dimension ref="A1:Q84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="P5" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q5" s="12" t="n"/>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="P6" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q6" s="17" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P7" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q7" s="12" t="n"/>
@@ -1421,12 +1421,12 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>BCU @ UCF</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D8" s="25" t="n">
@@ -1439,29 +1439,29 @@
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t>SJSU +38.5</t>
+          <t>BCU +42.5</t>
         </is>
       </c>
       <c r="G8" s="26" t="n">
-        <v>-38.5</v>
+        <v>-42.5</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>-118</v>
+        <v>-112</v>
       </c>
       <c r="I8" s="20" t="n">
-        <v>0.7563609789069304</v>
+        <v>0.7517481901856816</v>
       </c>
       <c r="J8" s="20" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K8" s="20" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L8" s="19" t="n">
-        <v>0.2150765752372057</v>
+        <v>0.2234463033932288</v>
       </c>
       <c r="M8" s="19" t="n">
-        <v>0.3973448593365325</v>
+        <v>0.4229519314228973</v>
       </c>
       <c r="N8" s="20" t="n">
         <v>0</v>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="P8" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q8" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>NMSU @ FSU</t>
+          <t>MRMK @ DEL</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D9" s="22" t="n">
@@ -1506,29 +1506,29 @@
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>NMSU +31.5</t>
+          <t>MRMK +28.5</t>
         </is>
       </c>
       <c r="G9" s="23" t="n">
-        <v>-31.5</v>
+        <v>-28.5</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>0.7484052544756881</v>
+        <v>0.7386849373798826</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K9" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L9" s="14" t="n">
-        <v>0.2135215335454556</v>
+        <v>0.2194541681491133</v>
       </c>
       <c r="M9" s="14" t="n">
-        <v>0.3991924322806341</v>
+        <v>0.4226524719908851</v>
       </c>
       <c r="N9" s="15" t="n">
         <v>0</v>
@@ -1538,12 +1538,12 @@
       </c>
       <c r="P9" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q9" s="12" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -1555,12 +1555,12 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>NMSU @ FSU</t>
+          <t>MASS @ RUTG</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-03 22:00</t>
         </is>
       </c>
       <c r="D10" s="25" t="n">
@@ -1568,32 +1568,34 @@
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t>NMSU ML</t>
-        </is>
-      </c>
-      <c r="G10" s="26" t="n"/>
+          <t>MASS +30.5</t>
+        </is>
+      </c>
+      <c r="G10" s="26" t="n">
+        <v>-30.5</v>
+      </c>
       <c r="H10" s="18" t="n">
-        <v>2000</v>
+        <v>-108</v>
       </c>
       <c r="I10" s="20" t="n">
-        <v>0.2189772153156186</v>
+        <v>0.7362293114467701</v>
       </c>
       <c r="J10" s="20" t="n">
-        <v>0.0461215932914046</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K10" s="20" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L10" s="19" t="n">
-        <v>0.171358167696571</v>
+        <v>0.2169985422160008</v>
       </c>
       <c r="M10" s="19" t="n">
-        <v>3.598521521627991</v>
+        <v>0.4179231183419276</v>
       </c>
       <c r="N10" s="20" t="n">
         <v>0</v>
@@ -1603,12 +1605,12 @@
       </c>
       <c r="P10" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q10" s="17" t="inlineStr">
         <is>
-          <t>price outside allowed range</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -1620,12 +1622,12 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>JVST @ NDSU</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D11" s="22" t="n">
@@ -1633,34 +1635,34 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
+          <t>SJSU +38.5</t>
         </is>
       </c>
       <c r="G11" s="23" t="n">
-        <v>46.5</v>
+        <v>-38.5</v>
       </c>
       <c r="H11" s="13" t="n">
-        <v>-110</v>
+        <v>-118</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>0.6553348680813179</v>
+        <v>0.7563609789069304</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5173641257162701</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5412844036697247</v>
       </c>
       <c r="L11" s="14" t="n">
-        <v>0.1315253442717941</v>
+        <v>0.2150765752372057</v>
       </c>
       <c r="M11" s="14" t="n">
-        <v>0.2510938390643342</v>
+        <v>0.3973448593365325</v>
       </c>
       <c r="N11" s="15" t="n">
         <v>0</v>
@@ -1670,7 +1672,7 @@
       </c>
       <c r="P11" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q11" s="12" t="inlineStr">
@@ -1687,12 +1689,12 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>SAC @ EMU</t>
+          <t>NMSU @ FSU</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 22:30</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D12" s="25" t="n">
@@ -1705,29 +1707,29 @@
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>SAC +9.5</t>
+          <t>NMSU +31.5</t>
         </is>
       </c>
       <c r="G12" s="26" t="n">
-        <v>-9.5</v>
+        <v>-31.5</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="I12" s="20" t="n">
-        <v>0.6373042089106218</v>
+        <v>0.7484052544756881</v>
       </c>
       <c r="J12" s="20" t="n">
-        <v>0.5</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K12" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L12" s="19" t="n">
-        <v>0.1134946851010979</v>
+        <v>0.2135215335454556</v>
       </c>
       <c r="M12" s="19" t="n">
-        <v>0.2166716715566417</v>
+        <v>0.3991924322806341</v>
       </c>
       <c r="N12" s="20" t="n">
         <v>0</v>
@@ -1737,7 +1739,7 @@
       </c>
       <c r="P12" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q12" s="17" t="inlineStr">
@@ -1754,12 +1756,12 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>ALB @ BUFF</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D13" s="22" t="n">
@@ -1767,32 +1769,34 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>UNC ML</t>
-        </is>
-      </c>
-      <c r="G13" s="23" t="n"/>
+          <t>ALB +24.5</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="n">
+        <v>-24.5</v>
+      </c>
       <c r="H13" s="13" t="n">
-        <v>250</v>
+        <v>-112</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>0.3621290026789783</v>
+        <v>0.7342550223888921</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>0.274247491638796</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L13" s="14" t="n">
-        <v>0.0764147169646926</v>
+        <v>0.2059531355964392</v>
       </c>
       <c r="M13" s="14" t="n">
-        <v>0.267451509376424</v>
+        <v>0.3898398638075457</v>
       </c>
       <c r="N13" s="15" t="n">
         <v>0</v>
@@ -1802,10 +1806,14 @@
       </c>
       <c r="P13" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
-        </is>
-      </c>
-      <c r="Q13" s="12" t="n"/>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q13" s="12" t="inlineStr">
+        <is>
+          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
@@ -1815,12 +1823,12 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>SAC @ EMU</t>
+          <t>MRMK @ DEL</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 22:30</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D14" s="25" t="n">
@@ -1828,34 +1836,32 @@
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t>Over 52.5</t>
-        </is>
-      </c>
-      <c r="G14" s="26" t="n">
-        <v>52.5</v>
-      </c>
+          <t>MRMK ML</t>
+        </is>
+      </c>
+      <c r="G14" s="26" t="n"/>
       <c r="H14" s="18" t="n">
-        <v>-108</v>
+        <v>3000</v>
       </c>
       <c r="I14" s="20" t="n">
-        <v>0.595359506876733</v>
+        <v>0.2342202661742625</v>
       </c>
       <c r="J14" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.03155263980006248</v>
       </c>
       <c r="K14" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="L14" s="19" t="n">
-        <v>0.07612873764596373</v>
+        <v>0.2019622016581335</v>
       </c>
       <c r="M14" s="19" t="n">
-        <v>0.1466183095403747</v>
+        <v>6.260828251402137</v>
       </c>
       <c r="N14" s="20" t="n">
         <v>0</v>
@@ -1865,10 +1871,14 @@
       </c>
       <c r="P14" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
-        </is>
-      </c>
-      <c r="Q14" s="17" t="n"/>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q14" s="17" t="inlineStr">
+        <is>
+          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
@@ -1878,12 +1888,12 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>HAW @ STAN</t>
+          <t>AKR @ WAKE</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D15" s="22" t="n">
@@ -1891,32 +1901,34 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>HAW ML</t>
-        </is>
-      </c>
-      <c r="G15" s="23" t="n"/>
+          <t>AKR +23.5</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="n">
+        <v>-23.5</v>
+      </c>
       <c r="H15" s="13" t="n">
-        <v>180</v>
+        <v>-108</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>0.414495505906456</v>
+        <v>0.7202139758215249</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>0.3425247738043947</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L15" s="14" t="n">
-        <v>0.05735264876359886</v>
+        <v>0.2009832065907556</v>
       </c>
       <c r="M15" s="14" t="n">
-        <v>0.1605874165380767</v>
+        <v>0.3870787682488629</v>
       </c>
       <c r="N15" s="15" t="n">
         <v>0</v>
@@ -1926,10 +1938,14 @@
       </c>
       <c r="P15" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
-        </is>
-      </c>
-      <c r="Q15" s="12" t="n"/>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q15" s="12" t="inlineStr">
+        <is>
+          <t>raw model/market disagreement exceeds the safety limit</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -1939,12 +1955,12 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>HAW @ STAN</t>
+          <t>ALB @ BUFF</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D16" s="25" t="n">
@@ -1952,34 +1968,32 @@
       </c>
       <c r="E16" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
-          <t>HAW +5.5</t>
-        </is>
-      </c>
-      <c r="G16" s="26" t="n">
-        <v>-5.5</v>
-      </c>
+          <t>ALB ML</t>
+        </is>
+      </c>
+      <c r="G16" s="26" t="n"/>
       <c r="H16" s="18" t="n">
-        <v>-112</v>
+        <v>2200</v>
       </c>
       <c r="I16" s="20" t="n">
-        <v>0.5838108250777737</v>
+        <v>0.2400960739565308</v>
       </c>
       <c r="J16" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.04216553878188443</v>
       </c>
       <c r="K16" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="L16" s="19" t="n">
-        <v>0.05550893828532089</v>
+        <v>0.1966178130869655</v>
       </c>
       <c r="M16" s="19" t="n">
-        <v>0.1050704903257859</v>
+        <v>4.522209701000207</v>
       </c>
       <c r="N16" s="20" t="n">
         <v>0</v>
@@ -1989,10 +2003,14 @@
       </c>
       <c r="P16" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
-        </is>
-      </c>
-      <c r="Q16" s="17" t="n"/>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q16" s="17" t="inlineStr">
+        <is>
+          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -2002,12 +2020,12 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>WES @ KENN</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D17" s="22" t="n">
@@ -2015,45 +2033,51 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>MEM ML</t>
-        </is>
-      </c>
-      <c r="G17" s="23" t="n"/>
+          <t>WES +22.5</t>
+        </is>
+      </c>
+      <c r="G17" s="23" t="n">
+        <v>-22.5</v>
+      </c>
       <c r="H17" s="13" t="n">
-        <v>185</v>
+        <v>-115</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>0.3799494426906008</v>
+        <v>0.7273466517420963</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>0.3363518758085381</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K17" s="15" t="n">
-        <v>0.3508771929824561</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L17" s="14" t="n">
-        <v>0.0290722497081447</v>
+        <v>0.1924629308118638</v>
       </c>
       <c r="M17" s="14" t="n">
-        <v>0.08285591166821238</v>
+        <v>0.3598220010830496</v>
       </c>
       <c r="N17" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O17" s="24" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="P17" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
-        </is>
-      </c>
-      <c r="Q17" s="12" t="n"/>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q17" s="12" t="inlineStr">
+        <is>
+          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="17" t="inlineStr">
@@ -2063,12 +2087,12 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>WES @ KENN</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D18" s="25" t="n">
@@ -2076,47 +2100,49 @@
       </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>MEM +5.5</t>
-        </is>
-      </c>
-      <c r="G18" s="26" t="n">
-        <v>-5.5</v>
-      </c>
+          <t>WES ML</t>
+        </is>
+      </c>
+      <c r="G18" s="26" t="n"/>
       <c r="H18" s="18" t="n">
-        <v>-112</v>
+        <v>1500</v>
       </c>
       <c r="I18" s="20" t="n">
-        <v>0.5540130817463144</v>
+        <v>0.2370117476831352</v>
       </c>
       <c r="J18" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.06035889070146819</v>
       </c>
       <c r="K18" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.0625</v>
       </c>
       <c r="L18" s="19" t="n">
-        <v>0.02571119495386154</v>
+        <v>0.1745117476831352</v>
       </c>
       <c r="M18" s="19" t="n">
-        <v>0.04866761901980932</v>
+        <v>2.792187962930162</v>
       </c>
       <c r="N18" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="27" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="P18" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
-        </is>
-      </c>
-      <c r="Q18" s="17" t="n"/>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q18" s="17" t="inlineStr">
+        <is>
+          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
@@ -2126,12 +2152,12 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>NMSU @ FSU</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D19" s="22" t="n">
@@ -2139,34 +2165,32 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>NCSU +5.5</t>
-        </is>
-      </c>
-      <c r="G19" s="23" t="n">
-        <v>-5.5</v>
-      </c>
+          <t>NMSU ML</t>
+        </is>
+      </c>
+      <c r="G19" s="23" t="n"/>
       <c r="H19" s="13" t="n">
-        <v>-108</v>
+        <v>2000</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>0.5412896688794703</v>
+        <v>0.2189772153156186</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.0461215932914046</v>
       </c>
       <c r="K19" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.04761904761904762</v>
       </c>
       <c r="L19" s="14" t="n">
-        <v>0.022058899648701</v>
+        <v>0.171358167696571</v>
       </c>
       <c r="M19" s="14" t="n">
-        <v>0.04248380673083174</v>
+        <v>3.598521521627991</v>
       </c>
       <c r="N19" s="15" t="n">
         <v>0</v>
@@ -2176,10 +2200,14 @@
       </c>
       <c r="P19" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
-        </is>
-      </c>
-      <c r="Q19" s="12" t="n"/>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q19" s="12" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
@@ -2189,12 +2217,12 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>JVST @ NDSU</t>
+          <t>AKR @ WAKE</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D20" s="25" t="n">
@@ -2202,47 +2230,49 @@
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F20" s="17" t="inlineStr">
         <is>
-          <t>JVST +7</t>
-        </is>
-      </c>
-      <c r="G20" s="26" t="n">
-        <v>-7</v>
-      </c>
+          <t>AKR ML</t>
+        </is>
+      </c>
+      <c r="G20" s="26" t="n"/>
       <c r="H20" s="18" t="n">
-        <v>-110</v>
+        <v>1300</v>
       </c>
       <c r="I20" s="20" t="n">
-        <v>0.5445684137563569</v>
+        <v>0.2310535567636653</v>
       </c>
       <c r="J20" s="20" t="n">
-        <v>0.5</v>
+        <v>0.06888361045130641</v>
       </c>
       <c r="K20" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="L20" s="19" t="n">
-        <v>0.02075888994683306</v>
+        <v>0.1596249853350939</v>
       </c>
       <c r="M20" s="19" t="n">
-        <v>0.03762929802911508</v>
+        <v>2.234749794691315</v>
       </c>
       <c r="N20" s="20" t="n">
-        <v>0.0505</v>
+        <v>0</v>
       </c>
       <c r="O20" s="27" t="n">
         <v>0.45</v>
       </c>
       <c r="P20" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
-        </is>
-      </c>
-      <c r="Q20" s="17" t="n"/>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q20" s="17" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
@@ -2252,12 +2282,12 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>MASS @ RUTG</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-09-03 22:00</t>
         </is>
       </c>
       <c r="D21" s="22" t="n">
@@ -2265,34 +2295,32 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>Under 59.5</t>
-        </is>
-      </c>
-      <c r="G21" s="23" t="n">
-        <v>59.5</v>
-      </c>
+          <t>MASS ML</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="n"/>
       <c r="H21" s="13" t="n">
-        <v>-110</v>
+        <v>2000</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>0.543550073621027</v>
+        <v>0.1963076315941712</v>
       </c>
       <c r="J21" s="15" t="n">
-        <v>0.5</v>
+        <v>0.0461215932914046</v>
       </c>
       <c r="K21" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.04761904761904762</v>
       </c>
       <c r="L21" s="14" t="n">
-        <v>0.01974054981150319</v>
+        <v>0.1486885839751236</v>
       </c>
       <c r="M21" s="14" t="n">
-        <v>0.0376865041855971</v>
+        <v>3.122460263477595</v>
       </c>
       <c r="N21" s="15" t="n">
         <v>0</v>
@@ -2302,10 +2330,14 @@
       </c>
       <c r="P21" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
-        </is>
-      </c>
-      <c r="Q21" s="12" t="n"/>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q21" s="12" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="17" t="inlineStr">
@@ -2315,12 +2347,12 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>JVST @ NDSU</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-08-29 21:30</t>
         </is>
       </c>
       <c r="D22" s="25" t="n">
@@ -2328,32 +2360,34 @@
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F22" s="17" t="inlineStr">
         <is>
-          <t>NCSU ML</t>
-        </is>
-      </c>
-      <c r="G22" s="26" t="n"/>
+          <t>Over 46.5</t>
+        </is>
+      </c>
+      <c r="G22" s="26" t="n">
+        <v>46.5</v>
+      </c>
       <c r="H22" s="18" t="n">
-        <v>180</v>
+        <v>-110</v>
       </c>
       <c r="I22" s="20" t="n">
-        <v>0.3745807138274095</v>
+        <v>0.6553348680813179</v>
       </c>
       <c r="J22" s="20" t="n">
-        <v>0.3425247738043947</v>
+        <v>0.5</v>
       </c>
       <c r="K22" s="20" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L22" s="19" t="n">
-        <v>0.01743785668455239</v>
+        <v>0.1315253442717941</v>
       </c>
       <c r="M22" s="19" t="n">
-        <v>0.04882599871674664</v>
+        <v>0.2510938390643342</v>
       </c>
       <c r="N22" s="20" t="n">
         <v>0</v>
@@ -2363,10 +2397,14 @@
       </c>
       <c r="P22" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
-        </is>
-      </c>
-      <c r="Q22" s="17" t="n"/>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q22" s="17" t="inlineStr">
+        <is>
+          <t>raw model/market disagreement exceeds the safety limit</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
@@ -2376,12 +2414,12 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>SAC @ EMU</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-08-29 22:30</t>
         </is>
       </c>
       <c r="D23" s="22" t="n">
@@ -2389,22 +2427,22 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
+          <t>SAC +9.5</t>
         </is>
       </c>
       <c r="G23" s="23" t="n">
-        <v>47.5</v>
+        <v>-9.5</v>
       </c>
       <c r="H23" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>0.5376883257015108</v>
+        <v>0.6373042089106218</v>
       </c>
       <c r="J23" s="15" t="n">
         <v>0.5</v>
@@ -2413,10 +2451,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L23" s="14" t="n">
-        <v>0.01387880189198698</v>
+        <v>0.1134946851010979</v>
       </c>
       <c r="M23" s="14" t="n">
-        <v>0.02649589452106615</v>
+        <v>0.2166716715566417</v>
       </c>
       <c r="N23" s="15" t="n">
         <v>0</v>
@@ -2426,10 +2464,14 @@
       </c>
       <c r="P23" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
-        </is>
-      </c>
-      <c r="Q23" s="12" t="n"/>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q23" s="12" t="inlineStr">
+        <is>
+          <t>raw model/market disagreement exceeds the safety limit</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="17" t="inlineStr">
@@ -2439,12 +2481,12 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>JVST @ NDSU</t>
+          <t>ALB @ BUFF</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D24" s="25" t="n">
@@ -2452,32 +2494,34 @@
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>JVST ML</t>
-        </is>
-      </c>
-      <c r="G24" s="26" t="n"/>
+          <t>Over 48.5</t>
+        </is>
+      </c>
+      <c r="G24" s="26" t="n">
+        <v>48.5</v>
+      </c>
       <c r="H24" s="18" t="n">
-        <v>220</v>
+        <v>-108</v>
       </c>
       <c r="I24" s="20" t="n">
-        <v>0.3261190128306598</v>
+        <v>0.6237538960930264</v>
       </c>
       <c r="J24" s="20" t="n">
-        <v>0.299837925445705</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K24" s="20" t="n">
-        <v>0.3125</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L24" s="19" t="n">
-        <v>0.0136190128306598</v>
+        <v>0.1045231268622572</v>
       </c>
       <c r="M24" s="19" t="n">
-        <v>0.04358084105811144</v>
+        <v>0.2013037998828658</v>
       </c>
       <c r="N24" s="20" t="n">
         <v>0</v>
@@ -2487,10 +2531,14 @@
       </c>
       <c r="P24" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
-        </is>
-      </c>
-      <c r="Q24" s="17" t="n"/>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q24" s="17" t="inlineStr">
+        <is>
+          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
@@ -2500,12 +2548,12 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>NMSU @ FSU</t>
+          <t>WES @ KENN</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D25" s="22" t="n">
@@ -2518,42 +2566,46 @@
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>Over 53.5</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="G25" s="23" t="n">
-        <v>53.5</v>
+        <v>51.5</v>
       </c>
       <c r="H25" s="13" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>0.5298211883282545</v>
+        <v>0.5971070144741464</v>
       </c>
       <c r="J25" s="15" t="n">
-        <v>0.5</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K25" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L25" s="14" t="n">
-        <v>0.006011664518730697</v>
+        <v>0.07787624524337711</v>
       </c>
       <c r="M25" s="14" t="n">
-        <v>0.01147681408121326</v>
+        <v>0.1499838797279857</v>
       </c>
       <c r="N25" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O25" s="24" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="P25" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
-        </is>
-      </c>
-      <c r="Q25" s="12" t="n"/>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q25" s="12" t="inlineStr">
+        <is>
+          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="17" t="inlineStr">
@@ -2563,12 +2615,12 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D26" s="25" t="n">
@@ -2576,34 +2628,32 @@
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>Over 53.5</t>
-        </is>
-      </c>
-      <c r="G26" s="26" t="n">
-        <v>53.5</v>
-      </c>
+          <t>UNC ML</t>
+        </is>
+      </c>
+      <c r="G26" s="26" t="n"/>
       <c r="H26" s="18" t="n">
-        <v>-108</v>
+        <v>250</v>
       </c>
       <c r="I26" s="20" t="n">
-        <v>0.5177573237293587</v>
+        <v>0.3621290026789783</v>
       </c>
       <c r="J26" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.274247491638796</v>
       </c>
       <c r="K26" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="L26" s="19" t="n">
-        <v>-0.001473445501410597</v>
+        <v>0.0764147169646926</v>
       </c>
       <c r="M26" s="19" t="n">
-        <v>-0.00283774689160543</v>
+        <v>0.267451509376424</v>
       </c>
       <c r="N26" s="20" t="n">
         <v>0</v>
@@ -2613,7 +2663,7 @@
       </c>
       <c r="P26" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q26" s="17" t="n"/>
@@ -2626,12 +2676,12 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>SAC @ EMU</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-08-29 22:30</t>
         </is>
       </c>
       <c r="D27" s="22" t="n">
@@ -2644,17 +2694,17 @@
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>Over 57.5</t>
+          <t>Over 52.5</t>
         </is>
       </c>
       <c r="G27" s="23" t="n">
-        <v>57.5</v>
+        <v>52.5</v>
       </c>
       <c r="H27" s="13" t="n">
         <v>-108</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>0.50780868060465</v>
+        <v>0.595359506876733</v>
       </c>
       <c r="J27" s="15" t="n">
         <v>0.4956702459300312</v>
@@ -2663,10 +2713,10 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L27" s="14" t="n">
-        <v>-0.01142208862611926</v>
+        <v>0.07612873764596373</v>
       </c>
       <c r="M27" s="14" t="n">
-        <v>-0.02199809661326657</v>
+        <v>0.1466183095403747</v>
       </c>
       <c r="N27" s="15" t="n">
         <v>0</v>
@@ -2676,7 +2726,7 @@
       </c>
       <c r="P27" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q27" s="12" t="n"/>
@@ -2689,12 +2739,12 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>AKR @ WAKE</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D28" s="25" t="n">
@@ -2707,17 +2757,17 @@
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>Under 57.5</t>
+          <t>Over 49.5</t>
         </is>
       </c>
       <c r="G28" s="26" t="n">
-        <v>57.5</v>
+        <v>49.5</v>
       </c>
       <c r="H28" s="18" t="n">
         <v>-112</v>
       </c>
       <c r="I28" s="20" t="n">
-        <v>0.49219131939535</v>
+        <v>0.603175208172005</v>
       </c>
       <c r="J28" s="20" t="n">
         <v>0.5043297540699688</v>
@@ -2726,10 +2776,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L28" s="19" t="n">
-        <v>-0.03611056739710283</v>
+        <v>0.07487332137955216</v>
       </c>
       <c r="M28" s="19" t="n">
-        <v>-0.06835214543023038</v>
+        <v>0.1417245011827237</v>
       </c>
       <c r="N28" s="20" t="n">
         <v>0</v>
@@ -2739,7 +2789,7 @@
       </c>
       <c r="P28" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q28" s="17" t="n"/>
@@ -2752,12 +2802,12 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>BCU @ UCF</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D29" s="22" t="n">
@@ -2770,29 +2820,29 @@
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>Under 53.5</t>
+          <t>Under 59.5</t>
         </is>
       </c>
       <c r="G29" s="23" t="n">
-        <v>53.5</v>
+        <v>59.5</v>
       </c>
       <c r="H29" s="13" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>0.4822426762706413</v>
+        <v>0.5828840668418837</v>
       </c>
       <c r="J29" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K29" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L29" s="14" t="n">
-        <v>-0.0460592105218115</v>
+        <v>0.06365329761111438</v>
       </c>
       <c r="M29" s="14" t="n">
-        <v>-0.08718350563057181</v>
+        <v>0.1225915361399241</v>
       </c>
       <c r="N29" s="15" t="n">
         <v>0</v>
@@ -2802,10 +2852,14 @@
       </c>
       <c r="P29" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
-        </is>
-      </c>
-      <c r="Q29" s="12" t="n"/>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q29" s="12" t="inlineStr">
+        <is>
+          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="17" t="inlineStr">
@@ -2815,7 +2869,7 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>NMSU @ FSU</t>
+          <t>HAW @ STAN</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
@@ -2828,34 +2882,32 @@
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F30" s="17" t="inlineStr">
         <is>
-          <t>Under 53.5</t>
-        </is>
-      </c>
-      <c r="G30" s="26" t="n">
-        <v>53.5</v>
-      </c>
+          <t>HAW ML</t>
+        </is>
+      </c>
+      <c r="G30" s="26" t="n"/>
       <c r="H30" s="18" t="n">
-        <v>-110</v>
+        <v>180</v>
       </c>
       <c r="I30" s="20" t="n">
-        <v>0.4701788116717455</v>
+        <v>0.414495505906456</v>
       </c>
       <c r="J30" s="20" t="n">
-        <v>0.5</v>
+        <v>0.3425247738043947</v>
       </c>
       <c r="K30" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>-0.05363071213777837</v>
+        <v>0.05735264876359886</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>-0.1023859049903041</v>
+        <v>0.1605874165380767</v>
       </c>
       <c r="N30" s="20" t="n">
         <v>0</v>
@@ -2865,7 +2917,7 @@
       </c>
       <c r="P30" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q30" s="17" t="n"/>
@@ -2878,12 +2930,12 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>JVST @ NDSU</t>
+          <t>HAW @ STAN</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D31" s="22" t="n">
@@ -2891,32 +2943,34 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>NDSU ML</t>
-        </is>
-      </c>
-      <c r="G31" s="23" t="n"/>
+          <t>HAW +5.5</t>
+        </is>
+      </c>
+      <c r="G31" s="23" t="n">
+        <v>-5.5</v>
+      </c>
       <c r="H31" s="13" t="n">
-        <v>-270</v>
+        <v>-112</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>0.6738809871693402</v>
+        <v>0.5838108250777737</v>
       </c>
       <c r="J31" s="15" t="n">
-        <v>0.7001620745542949</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K31" s="15" t="n">
-        <v>0.7297297297297297</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L31" s="14" t="n">
-        <v>-0.05584874256038952</v>
+        <v>0.05550893828532089</v>
       </c>
       <c r="M31" s="14" t="n">
-        <v>-0.07653346202720057</v>
+        <v>0.1050704903257859</v>
       </c>
       <c r="N31" s="15" t="n">
         <v>0</v>
@@ -2926,7 +2980,7 @@
       </c>
       <c r="P31" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q31" s="12" t="n"/>
@@ -2939,12 +2993,12 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>MASS @ RUTG</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-09-03 22:00</t>
         </is>
       </c>
       <c r="D32" s="25" t="n">
@@ -2952,32 +3006,34 @@
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F32" s="17" t="inlineStr">
         <is>
-          <t>UVA ML</t>
-        </is>
-      </c>
-      <c r="G32" s="26" t="n"/>
+          <t>Over 53.5</t>
+        </is>
+      </c>
+      <c r="G32" s="26" t="n">
+        <v>53.5</v>
+      </c>
       <c r="H32" s="18" t="n">
-        <v>-218</v>
+        <v>-110</v>
       </c>
       <c r="I32" s="20" t="n">
-        <v>0.6254192861725905</v>
+        <v>0.5740430549239717</v>
       </c>
       <c r="J32" s="20" t="n">
-        <v>0.6574752261956054</v>
+        <v>0.5</v>
       </c>
       <c r="K32" s="20" t="n">
-        <v>0.6855345911949685</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L32" s="19" t="n">
-        <v>-0.06011530502237805</v>
+        <v>0.05023353111444784</v>
       </c>
       <c r="M32" s="19" t="n">
-        <v>-0.08769113301429471</v>
+        <v>0.09590037758212777</v>
       </c>
       <c r="N32" s="20" t="n">
         <v>0</v>
@@ -2987,7 +3043,7 @@
       </c>
       <c r="P32" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q32" s="17" t="n"/>
@@ -3000,12 +3056,12 @@
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D33" s="22" t="n">
@@ -3013,34 +3069,32 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
-        </is>
-      </c>
-      <c r="G33" s="23" t="n">
-        <v>47.5</v>
-      </c>
+          <t>MEM ML</t>
+        </is>
+      </c>
+      <c r="G33" s="23" t="n"/>
       <c r="H33" s="13" t="n">
-        <v>-110</v>
+        <v>185</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>0.4623116742984892</v>
+        <v>0.3799494426906008</v>
       </c>
       <c r="J33" s="15" t="n">
-        <v>0.5</v>
+        <v>0.3363518758085381</v>
       </c>
       <c r="K33" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.3508771929824561</v>
       </c>
       <c r="L33" s="14" t="n">
-        <v>-0.06149784951103465</v>
+        <v>0.0290722497081447</v>
       </c>
       <c r="M33" s="14" t="n">
-        <v>-0.117404985430157</v>
+        <v>0.08285591166821238</v>
       </c>
       <c r="N33" s="15" t="n">
         <v>0</v>
@@ -3050,7 +3104,7 @@
       </c>
       <c r="P33" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q33" s="12" t="n"/>
@@ -3063,12 +3117,12 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D34" s="25" t="n">
@@ -3076,34 +3130,34 @@
       </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F34" s="17" t="inlineStr">
         <is>
-          <t>Over 59.5</t>
+          <t>MEM +5.5</t>
         </is>
       </c>
       <c r="G34" s="26" t="n">
-        <v>59.5</v>
+        <v>-5.5</v>
       </c>
       <c r="H34" s="18" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="I34" s="20" t="n">
-        <v>0.456449926378973</v>
+        <v>0.5540130817463144</v>
       </c>
       <c r="J34" s="20" t="n">
-        <v>0.5</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K34" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L34" s="19" t="n">
-        <v>-0.06735959743055087</v>
+        <v>0.02571119495386154</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>-0.1285955950946879</v>
+        <v>0.04866761901980932</v>
       </c>
       <c r="N34" s="20" t="n">
         <v>0</v>
@@ -3113,7 +3167,7 @@
       </c>
       <c r="P34" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q34" s="17" t="n"/>
@@ -3126,12 +3180,12 @@
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>JVST @ NDSU</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D35" s="22" t="n">
@@ -3144,39 +3198,39 @@
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>NDSU -7</t>
+          <t>NCSU +5.5</t>
         </is>
       </c>
       <c r="G35" s="23" t="n">
-        <v>-7</v>
+        <v>-5.5</v>
       </c>
       <c r="H35" s="13" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>0.4554315862436431</v>
+        <v>0.5412896688794703</v>
       </c>
       <c r="J35" s="15" t="n">
-        <v>0.5</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K35" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L35" s="14" t="n">
-        <v>-0.06837793756588073</v>
+        <v>0.022058899648701</v>
       </c>
       <c r="M35" s="14" t="n">
-        <v>-0.1239475616409477</v>
+        <v>0.04248380673083174</v>
       </c>
       <c r="N35" s="15" t="n">
-        <v>0.0505</v>
+        <v>0</v>
       </c>
       <c r="O35" s="24" t="n">
         <v>0.45</v>
       </c>
       <c r="P35" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q35" s="12" t="n"/>
@@ -3189,12 +3243,12 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>JVST @ NDSU</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-08-29 21:30</t>
         </is>
       </c>
       <c r="D36" s="25" t="n">
@@ -3207,39 +3261,39 @@
       </c>
       <c r="F36" s="17" t="inlineStr">
         <is>
-          <t>UVA -5.5</t>
+          <t>JVST +7</t>
         </is>
       </c>
       <c r="G36" s="26" t="n">
-        <v>-5.5</v>
+        <v>-7</v>
       </c>
       <c r="H36" s="18" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I36" s="20" t="n">
-        <v>0.4587103311205297</v>
+        <v>0.5445684137563569</v>
       </c>
       <c r="J36" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K36" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L36" s="19" t="n">
-        <v>-0.0695915556719231</v>
+        <v>0.02075888994683306</v>
       </c>
       <c r="M36" s="19" t="n">
-        <v>-0.1317268732361402</v>
+        <v>0.03762929802911508</v>
       </c>
       <c r="N36" s="20" t="n">
-        <v>0</v>
+        <v>0.0505</v>
       </c>
       <c r="O36" s="27" t="n">
         <v>0.45</v>
       </c>
       <c r="P36" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q36" s="17" t="n"/>
@@ -3252,12 +3306,12 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D37" s="22" t="n">
@@ -3265,32 +3319,34 @@
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>UNLV ML</t>
-        </is>
-      </c>
-      <c r="G37" s="23" t="n"/>
+          <t>Under 59.5</t>
+        </is>
+      </c>
+      <c r="G37" s="23" t="n">
+        <v>59.5</v>
+      </c>
       <c r="H37" s="13" t="n">
-        <v>-225</v>
+        <v>-110</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>0.6200505573093992</v>
+        <v>0.543550073621027</v>
       </c>
       <c r="J37" s="15" t="n">
-        <v>0.6636481241914618</v>
+        <v>0.5</v>
       </c>
       <c r="K37" s="15" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L37" s="14" t="n">
-        <v>-0.07225713499829312</v>
+        <v>0.01974054981150319</v>
       </c>
       <c r="M37" s="14" t="n">
-        <v>-0.1043714172197567</v>
+        <v>0.0376865041855971</v>
       </c>
       <c r="N37" s="15" t="n">
         <v>0</v>
@@ -3300,7 +3356,7 @@
       </c>
       <c r="P37" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q37" s="12" t="n"/>
@@ -3313,12 +3369,12 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D38" s="25" t="n">
@@ -3326,34 +3382,32 @@
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F38" s="17" t="inlineStr">
         <is>
-          <t>UNLV -5.5</t>
-        </is>
-      </c>
-      <c r="G38" s="26" t="n">
-        <v>-5.5</v>
-      </c>
+          <t>NCSU ML</t>
+        </is>
+      </c>
+      <c r="G38" s="26" t="n"/>
       <c r="H38" s="18" t="n">
-        <v>-108</v>
+        <v>180</v>
       </c>
       <c r="I38" s="20" t="n">
-        <v>0.4459869182536856</v>
+        <v>0.3745807138274095</v>
       </c>
       <c r="J38" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.3425247738043947</v>
       </c>
       <c r="K38" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>-0.07324385097708364</v>
+        <v>0.01743785668455239</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>-0.1410622315114202</v>
+        <v>0.04882599871674664</v>
       </c>
       <c r="N38" s="20" t="n">
         <v>0</v>
@@ -3363,7 +3417,7 @@
       </c>
       <c r="P38" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q38" s="17" t="n"/>
@@ -3376,12 +3430,12 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>HAW @ STAN</t>
+          <t>MRMK @ DEL</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D39" s="22" t="n">
@@ -3389,32 +3443,34 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>STAN ML</t>
-        </is>
-      </c>
-      <c r="G39" s="23" t="n"/>
+          <t>Over 55.5</t>
+        </is>
+      </c>
+      <c r="G39" s="23" t="n">
+        <v>55.5</v>
+      </c>
       <c r="H39" s="13" t="n">
-        <v>-218</v>
+        <v>-112</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>0.585504494093544</v>
+        <v>0.5437650474945759</v>
       </c>
       <c r="J39" s="15" t="n">
-        <v>0.6574752261956054</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K39" s="15" t="n">
-        <v>0.6855345911949685</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L39" s="14" t="n">
-        <v>-0.1000300971014245</v>
+        <v>0.01546316070212306</v>
       </c>
       <c r="M39" s="14" t="n">
-        <v>-0.1459154627442799</v>
+        <v>0.02926955418616145</v>
       </c>
       <c r="N39" s="15" t="n">
         <v>0</v>
@@ -3424,10 +3480,14 @@
       </c>
       <c r="P39" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
-        </is>
-      </c>
-      <c r="Q39" s="12" t="n"/>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q39" s="12" t="inlineStr">
+        <is>
+          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="17" t="inlineStr">
@@ -3437,12 +3497,12 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>HAW @ STAN</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D40" s="25" t="n">
@@ -3450,34 +3510,34 @@
       </c>
       <c r="E40" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F40" s="17" t="inlineStr">
         <is>
-          <t>STAN -5.5</t>
+          <t>Over 47.5</t>
         </is>
       </c>
       <c r="G40" s="26" t="n">
-        <v>-5.5</v>
+        <v>47.5</v>
       </c>
       <c r="H40" s="18" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I40" s="20" t="n">
-        <v>0.4161891749222263</v>
+        <v>0.5376883257015108</v>
       </c>
       <c r="J40" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5</v>
       </c>
       <c r="K40" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L40" s="19" t="n">
-        <v>-0.103041594308543</v>
+        <v>0.01387880189198698</v>
       </c>
       <c r="M40" s="19" t="n">
-        <v>-0.1984504779275642</v>
+        <v>0.02649589452106615</v>
       </c>
       <c r="N40" s="20" t="n">
         <v>0</v>
@@ -3487,7 +3547,7 @@
       </c>
       <c r="P40" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q40" s="17" t="n"/>
@@ -3500,12 +3560,12 @@
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>JVST @ NDSU</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-08-29 21:30</t>
         </is>
       </c>
       <c r="D41" s="22" t="n">
@@ -3518,27 +3578,27 @@
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>TCU ML</t>
+          <t>JVST ML</t>
         </is>
       </c>
       <c r="G41" s="23" t="n"/>
       <c r="H41" s="13" t="n">
-        <v>-310</v>
+        <v>220</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>0.6378709973210217</v>
+        <v>0.3261190128306598</v>
       </c>
       <c r="J41" s="15" t="n">
-        <v>0.725752508361204</v>
+        <v>0.299837925445705</v>
       </c>
       <c r="K41" s="15" t="n">
-        <v>0.7560975609756098</v>
+        <v>0.3125</v>
       </c>
       <c r="L41" s="14" t="n">
-        <v>-0.1182265636545881</v>
+        <v>0.0136190128306598</v>
       </c>
       <c r="M41" s="14" t="n">
-        <v>-0.1563641648334875</v>
+        <v>0.04358084105811144</v>
       </c>
       <c r="N41" s="15" t="n">
         <v>0</v>
@@ -3548,7 +3608,7 @@
       </c>
       <c r="P41" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q41" s="12" t="n"/>
@@ -3561,12 +3621,12 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>SAC @ EMU</t>
+          <t>NMSU @ FSU</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 22:30</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D42" s="25" t="n">
@@ -3579,29 +3639,29 @@
       </c>
       <c r="F42" s="17" t="inlineStr">
         <is>
-          <t>Under 52.5</t>
+          <t>Over 53.5</t>
         </is>
       </c>
       <c r="G42" s="26" t="n">
-        <v>52.5</v>
+        <v>53.5</v>
       </c>
       <c r="H42" s="18" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I42" s="20" t="n">
-        <v>0.404640493123267</v>
+        <v>0.5298211883282545</v>
       </c>
       <c r="J42" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K42" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L42" s="19" t="n">
-        <v>-0.1236613936691858</v>
+        <v>0.006011664518730697</v>
       </c>
       <c r="M42" s="19" t="n">
-        <v>-0.2340733523023875</v>
+        <v>0.01147681408121326</v>
       </c>
       <c r="N42" s="20" t="n">
         <v>0</v>
@@ -3611,7 +3671,7 @@
       </c>
       <c r="P42" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q42" s="17" t="n"/>
@@ -3624,12 +3684,12 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D43" s="22" t="n">
@@ -3637,34 +3697,34 @@
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>TCU -7.5</t>
+          <t>Over 53.5</t>
         </is>
       </c>
       <c r="G43" s="23" t="n">
-        <v>-7.5</v>
+        <v>53.5</v>
       </c>
       <c r="H43" s="13" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>0.4006920158047088</v>
+        <v>0.5177573237293587</v>
       </c>
       <c r="J43" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K43" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L43" s="14" t="n">
-        <v>-0.127609870987744</v>
+        <v>-0.001473445501410597</v>
       </c>
       <c r="M43" s="14" t="n">
-        <v>-0.2415472557982298</v>
+        <v>-0.00283774689160543</v>
       </c>
       <c r="N43" s="15" t="n">
         <v>0</v>
@@ -3674,7 +3734,7 @@
       </c>
       <c r="P43" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q43" s="12" t="n"/>
@@ -3687,12 +3747,12 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>HAW @ STAN</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D44" s="25" t="n">
@@ -3705,29 +3765,29 @@
       </c>
       <c r="F44" s="17" t="inlineStr">
         <is>
-          <t>Under 49.5</t>
+          <t>Over 57.5</t>
         </is>
       </c>
       <c r="G44" s="26" t="n">
-        <v>49.5</v>
+        <v>57.5</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="I44" s="20" t="n">
-        <v>0.4044067869561538</v>
+        <v>0.50780868060465</v>
       </c>
       <c r="J44" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K44" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L44" s="19" t="n">
-        <v>-0.1304769339740787</v>
+        <v>-0.01142208862611926</v>
       </c>
       <c r="M44" s="19" t="n">
-        <v>-0.2439351374297994</v>
+        <v>-0.02199809661326657</v>
       </c>
       <c r="N44" s="20" t="n">
         <v>0</v>
@@ -3737,7 +3797,7 @@
       </c>
       <c r="P44" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q44" s="17" t="n"/>
@@ -3750,12 +3810,12 @@
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>SAC @ EMU</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 22:30</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D45" s="22" t="n">
@@ -3763,32 +3823,34 @@
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
-          <t>EMU ML</t>
-        </is>
-      </c>
-      <c r="G45" s="23" t="n"/>
+          <t>Under 57.5</t>
+        </is>
+      </c>
+      <c r="G45" s="23" t="n">
+        <v>57.5</v>
+      </c>
       <c r="H45" s="13" t="n">
-        <v>-355</v>
+        <v>-112</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>0.6313778129495795</v>
+        <v>0.49219131939535</v>
       </c>
       <c r="J45" s="15" t="n">
-        <v>0.7477827050997783</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K45" s="15" t="n">
-        <v>0.7802197802197802</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L45" s="14" t="n">
-        <v>-0.1488419672702007</v>
+        <v>-0.03611056739710283</v>
       </c>
       <c r="M45" s="14" t="n">
-        <v>-0.1907692819942009</v>
+        <v>-0.06835214543023038</v>
       </c>
       <c r="N45" s="15" t="n">
         <v>0</v>
@@ -3798,7 +3860,7 @@
       </c>
       <c r="P45" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="Q45" s="12" t="n"/>
@@ -3811,12 +3873,12 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>SAC @ EMU</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 22:30</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D46" s="25" t="n">
@@ -3824,34 +3886,34 @@
       </c>
       <c r="E46" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F46" s="17" t="inlineStr">
         <is>
-          <t>EMU -9.5</t>
+          <t>Under 53.5</t>
         </is>
       </c>
       <c r="G46" s="26" t="n">
-        <v>-9.5</v>
+        <v>53.5</v>
       </c>
       <c r="H46" s="18" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="I46" s="20" t="n">
-        <v>0.3626957910893782</v>
+        <v>0.4822426762706413</v>
       </c>
       <c r="J46" s="20" t="n">
-        <v>0.5</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K46" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L46" s="19" t="n">
-        <v>-0.1611137327201456</v>
+        <v>-0.0460592105218115</v>
       </c>
       <c r="M46" s="19" t="n">
-        <v>-0.3075807624657325</v>
+        <v>-0.08718350563057181</v>
       </c>
       <c r="N46" s="20" t="n">
         <v>0</v>
@@ -3861,14 +3923,10 @@
       </c>
       <c r="P46" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
-        </is>
-      </c>
-      <c r="Q46" s="17" t="inlineStr">
-        <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
-        </is>
-      </c>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q46" s="17" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
@@ -3878,12 +3936,12 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>JVST @ NDSU</t>
+          <t>NMSU @ FSU</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D47" s="22" t="n">
@@ -3896,17 +3954,17 @@
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>Under 46.5</t>
+          <t>Under 53.5</t>
         </is>
       </c>
       <c r="G47" s="23" t="n">
-        <v>46.5</v>
+        <v>53.5</v>
       </c>
       <c r="H47" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>0.3446651319186821</v>
+        <v>0.4701788116717455</v>
       </c>
       <c r="J47" s="15" t="n">
         <v>0.5</v>
@@ -3915,10 +3973,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L47" s="14" t="n">
-        <v>-0.1791443918908417</v>
+        <v>-0.05363071213777837</v>
       </c>
       <c r="M47" s="14" t="n">
-        <v>-0.3420029299734251</v>
+        <v>-0.1023859049903041</v>
       </c>
       <c r="N47" s="15" t="n">
         <v>0</v>
@@ -3928,14 +3986,10 @@
       </c>
       <c r="P47" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
-        </is>
-      </c>
-      <c r="Q47" s="12" t="inlineStr">
-        <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
-        </is>
-      </c>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q47" s="12" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="17" t="inlineStr">
@@ -3945,12 +3999,12 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>NMSU @ FSU</t>
+          <t>JVST @ NDSU</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-08-29 21:30</t>
         </is>
       </c>
       <c r="D48" s="25" t="n">
@@ -3963,27 +4017,27 @@
       </c>
       <c r="F48" s="17" t="inlineStr">
         <is>
-          <t>FSU ML</t>
+          <t>NDSU ML</t>
         </is>
       </c>
       <c r="G48" s="26" t="n"/>
       <c r="H48" s="18" t="n">
-        <v>-6500</v>
+        <v>-270</v>
       </c>
       <c r="I48" s="20" t="n">
-        <v>0.7810227846843814</v>
+        <v>0.6738809871693402</v>
       </c>
       <c r="J48" s="20" t="n">
-        <v>0.9538784067085954</v>
+        <v>0.7001620745542949</v>
       </c>
       <c r="K48" s="20" t="n">
-        <v>0.9848484848484849</v>
+        <v>0.7297297297297297</v>
       </c>
       <c r="L48" s="19" t="n">
-        <v>-0.2038257001641035</v>
+        <v>-0.05584874256038952</v>
       </c>
       <c r="M48" s="19" t="n">
-        <v>-0.2069614801666282</v>
+        <v>-0.07653346202720057</v>
       </c>
       <c r="N48" s="20" t="n">
         <v>0</v>
@@ -3993,14 +4047,10 @@
       </c>
       <c r="P48" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
-        </is>
-      </c>
-      <c r="Q48" s="17" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q48" s="17" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
@@ -4010,12 +4060,12 @@
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>NMSU @ FSU</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D49" s="22" t="n">
@@ -4023,34 +4073,32 @@
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
-          <t>FSU -31.5</t>
-        </is>
-      </c>
-      <c r="G49" s="23" t="n">
-        <v>-31.5</v>
-      </c>
+          <t>UVA ML</t>
+        </is>
+      </c>
+      <c r="G49" s="23" t="n"/>
       <c r="H49" s="13" t="n">
-        <v>-105</v>
+        <v>-218</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>0.2515947455243119</v>
+        <v>0.6254192861725905</v>
       </c>
       <c r="J49" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.6574752261956054</v>
       </c>
       <c r="K49" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.6855345911949685</v>
       </c>
       <c r="L49" s="14" t="n">
-        <v>-0.2606003764269076</v>
+        <v>-0.06011530502237805</v>
       </c>
       <c r="M49" s="14" t="n">
-        <v>-0.5087912111192006</v>
+        <v>-0.08769113301429471</v>
       </c>
       <c r="N49" s="15" t="n">
         <v>0</v>
@@ -4060,14 +4108,10 @@
       </c>
       <c r="P49" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
-        </is>
-      </c>
-      <c r="Q49" s="12" t="inlineStr">
-        <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
-        </is>
-      </c>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q49" s="12" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="17" t="inlineStr">
@@ -4077,12 +4121,12 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D50" s="25" t="n">
@@ -4090,34 +4134,34 @@
       </c>
       <c r="E50" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F50" s="17" t="inlineStr">
         <is>
-          <t>USC -38.5</t>
+          <t>Under 47.5</t>
         </is>
       </c>
       <c r="G50" s="26" t="n">
-        <v>-38.5</v>
+        <v>47.5</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>-102</v>
+        <v>-110</v>
       </c>
       <c r="I50" s="20" t="n">
-        <v>0.2436390210930696</v>
+        <v>0.4623116742984892</v>
       </c>
       <c r="J50" s="20" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.5</v>
       </c>
       <c r="K50" s="20" t="n">
-        <v>0.504950495049505</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L50" s="19" t="n">
-        <v>-0.2613114739564354</v>
+        <v>-0.06149784951103465</v>
       </c>
       <c r="M50" s="19" t="n">
-        <v>-0.517499193521568</v>
+        <v>-0.117404985430157</v>
       </c>
       <c r="N50" s="20" t="n">
         <v>0</v>
@@ -4127,12 +4171,2210 @@
       </c>
       <c r="P50" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
-        </is>
-      </c>
-      <c r="Q50" s="17" t="inlineStr">
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q50" s="17" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>MRMK @ DEL</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-03 23:00</t>
+        </is>
+      </c>
+      <c r="D51" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="inlineStr">
+        <is>
+          <t>Under 55.5</t>
+        </is>
+      </c>
+      <c r="G51" s="23" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="H51" s="13" t="n">
+        <v>-108</v>
+      </c>
+      <c r="I51" s="15" t="n">
+        <v>0.4562349525054241</v>
+      </c>
+      <c r="J51" s="15" t="n">
+        <v>0.4956702459300312</v>
+      </c>
+      <c r="K51" s="15" t="n">
+        <v>0.5192307692307693</v>
+      </c>
+      <c r="L51" s="14" t="n">
+        <v>-0.06299581672534516</v>
+      </c>
+      <c r="M51" s="14" t="n">
+        <v>-0.1213252766562202</v>
+      </c>
+      <c r="N51" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P51" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q51" s="12" t="inlineStr">
+        <is>
+          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="inlineStr">
+        <is>
+          <t>SJSU @ USC</t>
+        </is>
+      </c>
+      <c r="C52" s="17" t="inlineStr">
+        <is>
+          <t>2026-08-29 19:00</t>
+        </is>
+      </c>
+      <c r="D52" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="17" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="F52" s="17" t="inlineStr">
+        <is>
+          <t>Over 59.5</t>
+        </is>
+      </c>
+      <c r="G52" s="26" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="H52" s="18" t="n">
+        <v>-110</v>
+      </c>
+      <c r="I52" s="20" t="n">
+        <v>0.456449926378973</v>
+      </c>
+      <c r="J52" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K52" s="20" t="n">
+        <v>0.5238095238095238</v>
+      </c>
+      <c r="L52" s="19" t="n">
+        <v>-0.06735959743055087</v>
+      </c>
+      <c r="M52" s="19" t="n">
+        <v>-0.1285955950946879</v>
+      </c>
+      <c r="N52" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P52" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q52" s="17" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>JVST @ NDSU</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-29 21:30</t>
+        </is>
+      </c>
+      <c r="D53" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="12" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="inlineStr">
+        <is>
+          <t>NDSU -7</t>
+        </is>
+      </c>
+      <c r="G53" s="23" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H53" s="13" t="n">
+        <v>-110</v>
+      </c>
+      <c r="I53" s="15" t="n">
+        <v>0.4554315862436431</v>
+      </c>
+      <c r="J53" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K53" s="15" t="n">
+        <v>0.5238095238095238</v>
+      </c>
+      <c r="L53" s="14" t="n">
+        <v>-0.06837793756588073</v>
+      </c>
+      <c r="M53" s="14" t="n">
+        <v>-0.1239475616409477</v>
+      </c>
+      <c r="N53" s="15" t="n">
+        <v>0.0505</v>
+      </c>
+      <c r="O53" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P53" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q53" s="12" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="inlineStr">
+        <is>
+          <t>NCSU @ UVA</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="inlineStr">
+        <is>
+          <t>2026-08-29 19:30</t>
+        </is>
+      </c>
+      <c r="D54" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" s="17" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="F54" s="17" t="inlineStr">
+        <is>
+          <t>UVA -5.5</t>
+        </is>
+      </c>
+      <c r="G54" s="26" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H54" s="18" t="n">
+        <v>-112</v>
+      </c>
+      <c r="I54" s="20" t="n">
+        <v>0.4587103311205297</v>
+      </c>
+      <c r="J54" s="20" t="n">
+        <v>0.5043297540699688</v>
+      </c>
+      <c r="K54" s="20" t="n">
+        <v>0.5283018867924528</v>
+      </c>
+      <c r="L54" s="19" t="n">
+        <v>-0.0695915556719231</v>
+      </c>
+      <c r="M54" s="19" t="n">
+        <v>-0.1317268732361402</v>
+      </c>
+      <c r="N54" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P54" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q54" s="17" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>MEM @ UNLV</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-30 02:00</t>
+        </is>
+      </c>
+      <c r="D55" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="inlineStr">
+        <is>
+          <t>UNLV ML</t>
+        </is>
+      </c>
+      <c r="G55" s="23" t="n"/>
+      <c r="H55" s="13" t="n">
+        <v>-225</v>
+      </c>
+      <c r="I55" s="15" t="n">
+        <v>0.6200505573093992</v>
+      </c>
+      <c r="J55" s="15" t="n">
+        <v>0.6636481241914618</v>
+      </c>
+      <c r="K55" s="15" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="L55" s="14" t="n">
+        <v>-0.07225713499829312</v>
+      </c>
+      <c r="M55" s="14" t="n">
+        <v>-0.1043714172197567</v>
+      </c>
+      <c r="N55" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P55" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q55" s="12" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="inlineStr">
+        <is>
+          <t>MEM @ UNLV</t>
+        </is>
+      </c>
+      <c r="C56" s="17" t="inlineStr">
+        <is>
+          <t>2026-08-30 02:00</t>
+        </is>
+      </c>
+      <c r="D56" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" s="17" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="F56" s="17" t="inlineStr">
+        <is>
+          <t>UNLV -5.5</t>
+        </is>
+      </c>
+      <c r="G56" s="26" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H56" s="18" t="n">
+        <v>-108</v>
+      </c>
+      <c r="I56" s="20" t="n">
+        <v>0.4459869182536856</v>
+      </c>
+      <c r="J56" s="20" t="n">
+        <v>0.4956702459300312</v>
+      </c>
+      <c r="K56" s="20" t="n">
+        <v>0.5192307692307693</v>
+      </c>
+      <c r="L56" s="19" t="n">
+        <v>-0.07324385097708364</v>
+      </c>
+      <c r="M56" s="19" t="n">
+        <v>-0.1410622315114202</v>
+      </c>
+      <c r="N56" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P56" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q56" s="17" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>MASS @ RUTG</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-03 22:00</t>
+        </is>
+      </c>
+      <c r="D57" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="F57" s="12" t="inlineStr">
+        <is>
+          <t>Under 53.5</t>
+        </is>
+      </c>
+      <c r="G57" s="23" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="H57" s="13" t="n">
+        <v>-110</v>
+      </c>
+      <c r="I57" s="15" t="n">
+        <v>0.4259569450760283</v>
+      </c>
+      <c r="J57" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K57" s="15" t="n">
+        <v>0.5238095238095238</v>
+      </c>
+      <c r="L57" s="14" t="n">
+        <v>-0.09785257873349551</v>
+      </c>
+      <c r="M57" s="14" t="n">
+        <v>-0.1868094684912186</v>
+      </c>
+      <c r="N57" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P57" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q57" s="12" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="inlineStr">
+        <is>
+          <t>HAW @ STAN</t>
+        </is>
+      </c>
+      <c r="C58" s="17" t="inlineStr">
+        <is>
+          <t>2026-08-29 23:00</t>
+        </is>
+      </c>
+      <c r="D58" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" s="17" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="F58" s="17" t="inlineStr">
+        <is>
+          <t>STAN ML</t>
+        </is>
+      </c>
+      <c r="G58" s="26" t="n"/>
+      <c r="H58" s="18" t="n">
+        <v>-218</v>
+      </c>
+      <c r="I58" s="20" t="n">
+        <v>0.585504494093544</v>
+      </c>
+      <c r="J58" s="20" t="n">
+        <v>0.6574752261956054</v>
+      </c>
+      <c r="K58" s="20" t="n">
+        <v>0.6855345911949685</v>
+      </c>
+      <c r="L58" s="19" t="n">
+        <v>-0.1000300971014245</v>
+      </c>
+      <c r="M58" s="19" t="n">
+        <v>-0.1459154627442799</v>
+      </c>
+      <c r="N58" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P58" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q58" s="17" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>HAW @ STAN</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-29 23:00</t>
+        </is>
+      </c>
+      <c r="D59" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" s="12" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="F59" s="12" t="inlineStr">
+        <is>
+          <t>STAN -5.5</t>
+        </is>
+      </c>
+      <c r="G59" s="23" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H59" s="13" t="n">
+        <v>-108</v>
+      </c>
+      <c r="I59" s="15" t="n">
+        <v>0.4161891749222263</v>
+      </c>
+      <c r="J59" s="15" t="n">
+        <v>0.4956702459300312</v>
+      </c>
+      <c r="K59" s="15" t="n">
+        <v>0.5192307692307693</v>
+      </c>
+      <c r="L59" s="14" t="n">
+        <v>-0.103041594308543</v>
+      </c>
+      <c r="M59" s="14" t="n">
+        <v>-0.1984504779275642</v>
+      </c>
+      <c r="N59" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P59" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q59" s="12" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B60" s="17" t="inlineStr">
+        <is>
+          <t>BCU @ UCF</t>
+        </is>
+      </c>
+      <c r="C60" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-03 23:00</t>
+        </is>
+      </c>
+      <c r="D60" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="17" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="F60" s="17" t="inlineStr">
+        <is>
+          <t>Over 59.5</t>
+        </is>
+      </c>
+      <c r="G60" s="26" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="H60" s="18" t="n">
+        <v>-112</v>
+      </c>
+      <c r="I60" s="20" t="n">
+        <v>0.4171159331581163</v>
+      </c>
+      <c r="J60" s="20" t="n">
+        <v>0.5043297540699688</v>
+      </c>
+      <c r="K60" s="20" t="n">
+        <v>0.5283018867924528</v>
+      </c>
+      <c r="L60" s="19" t="n">
+        <v>-0.1111859536343365</v>
+      </c>
+      <c r="M60" s="19" t="n">
+        <v>-0.2104591265221369</v>
+      </c>
+      <c r="N60" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P60" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q60" s="17" t="inlineStr">
+        <is>
+          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B61" s="12" t="inlineStr">
+        <is>
+          <t>UNC @ TCU</t>
+        </is>
+      </c>
+      <c r="C61" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-29 16:00</t>
+        </is>
+      </c>
+      <c r="D61" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="12" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="F61" s="12" t="inlineStr">
+        <is>
+          <t>TCU ML</t>
+        </is>
+      </c>
+      <c r="G61" s="23" t="n"/>
+      <c r="H61" s="13" t="n">
+        <v>-310</v>
+      </c>
+      <c r="I61" s="15" t="n">
+        <v>0.6378709973210217</v>
+      </c>
+      <c r="J61" s="15" t="n">
+        <v>0.725752508361204</v>
+      </c>
+      <c r="K61" s="15" t="n">
+        <v>0.7560975609756098</v>
+      </c>
+      <c r="L61" s="14" t="n">
+        <v>-0.1182265636545881</v>
+      </c>
+      <c r="M61" s="14" t="n">
+        <v>-0.1563641648334875</v>
+      </c>
+      <c r="N61" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P61" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q61" s="12" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B62" s="17" t="inlineStr">
+        <is>
+          <t>AKR @ WAKE</t>
+        </is>
+      </c>
+      <c r="C62" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-03 23:00</t>
+        </is>
+      </c>
+      <c r="D62" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="17" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="F62" s="17" t="inlineStr">
+        <is>
+          <t>Under 49.5</t>
+        </is>
+      </c>
+      <c r="G62" s="26" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="H62" s="18" t="n">
+        <v>-108</v>
+      </c>
+      <c r="I62" s="20" t="n">
+        <v>0.396824791827995</v>
+      </c>
+      <c r="J62" s="20" t="n">
+        <v>0.4956702459300312</v>
+      </c>
+      <c r="K62" s="20" t="n">
+        <v>0.5192307692307693</v>
+      </c>
+      <c r="L62" s="19" t="n">
+        <v>-0.1224059774027743</v>
+      </c>
+      <c r="M62" s="19" t="n">
+        <v>-0.2357448453683059</v>
+      </c>
+      <c r="N62" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P62" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q62" s="17" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B63" s="12" t="inlineStr">
+        <is>
+          <t>SAC @ EMU</t>
+        </is>
+      </c>
+      <c r="C63" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:30</t>
+        </is>
+      </c>
+      <c r="D63" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="F63" s="12" t="inlineStr">
+        <is>
+          <t>Under 52.5</t>
+        </is>
+      </c>
+      <c r="G63" s="23" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="H63" s="13" t="n">
+        <v>-112</v>
+      </c>
+      <c r="I63" s="15" t="n">
+        <v>0.404640493123267</v>
+      </c>
+      <c r="J63" s="15" t="n">
+        <v>0.5043297540699688</v>
+      </c>
+      <c r="K63" s="15" t="n">
+        <v>0.5283018867924528</v>
+      </c>
+      <c r="L63" s="14" t="n">
+        <v>-0.1236613936691858</v>
+      </c>
+      <c r="M63" s="14" t="n">
+        <v>-0.2340733523023875</v>
+      </c>
+      <c r="N63" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P63" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q63" s="12" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B64" s="17" t="inlineStr">
+        <is>
+          <t>WES @ KENN</t>
+        </is>
+      </c>
+      <c r="C64" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-03 23:00</t>
+        </is>
+      </c>
+      <c r="D64" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="17" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="F64" s="17" t="inlineStr">
+        <is>
+          <t>Under 51.5</t>
+        </is>
+      </c>
+      <c r="G64" s="26" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="H64" s="18" t="n">
+        <v>-112</v>
+      </c>
+      <c r="I64" s="20" t="n">
+        <v>0.4028929855258536</v>
+      </c>
+      <c r="J64" s="20" t="n">
+        <v>0.5043297540699688</v>
+      </c>
+      <c r="K64" s="20" t="n">
+        <v>0.5283018867924528</v>
+      </c>
+      <c r="L64" s="19" t="n">
+        <v>-0.1254089012665992</v>
+      </c>
+      <c r="M64" s="19" t="n">
+        <v>-0.2373811345403485</v>
+      </c>
+      <c r="N64" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P64" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q64" s="17" t="inlineStr">
+        <is>
+          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>UNC @ TCU</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-29 16:00</t>
+        </is>
+      </c>
+      <c r="D65" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="12" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="F65" s="12" t="inlineStr">
+        <is>
+          <t>TCU -7.5</t>
+        </is>
+      </c>
+      <c r="G65" s="23" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H65" s="13" t="n">
+        <v>-112</v>
+      </c>
+      <c r="I65" s="15" t="n">
+        <v>0.4006920158047088</v>
+      </c>
+      <c r="J65" s="15" t="n">
+        <v>0.5043297540699688</v>
+      </c>
+      <c r="K65" s="15" t="n">
+        <v>0.5283018867924528</v>
+      </c>
+      <c r="L65" s="14" t="n">
+        <v>-0.127609870987744</v>
+      </c>
+      <c r="M65" s="14" t="n">
+        <v>-0.2415472557982298</v>
+      </c>
+      <c r="N65" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P65" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q65" s="12" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B66" s="17" t="inlineStr">
+        <is>
+          <t>HAW @ STAN</t>
+        </is>
+      </c>
+      <c r="C66" s="17" t="inlineStr">
+        <is>
+          <t>2026-08-29 23:00</t>
+        </is>
+      </c>
+      <c r="D66" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="17" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="F66" s="17" t="inlineStr">
+        <is>
+          <t>Under 49.5</t>
+        </is>
+      </c>
+      <c r="G66" s="26" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="H66" s="18" t="n">
+        <v>-115</v>
+      </c>
+      <c r="I66" s="20" t="n">
+        <v>0.4044067869561538</v>
+      </c>
+      <c r="J66" s="20" t="n">
+        <v>0.5108342361863488</v>
+      </c>
+      <c r="K66" s="20" t="n">
+        <v>0.5348837209302325</v>
+      </c>
+      <c r="L66" s="19" t="n">
+        <v>-0.1304769339740787</v>
+      </c>
+      <c r="M66" s="19" t="n">
+        <v>-0.2439351374297994</v>
+      </c>
+      <c r="N66" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P66" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q66" s="17" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B67" s="12" t="inlineStr">
+        <is>
+          <t>SAC @ EMU</t>
+        </is>
+      </c>
+      <c r="C67" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:30</t>
+        </is>
+      </c>
+      <c r="D67" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" s="12" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="F67" s="12" t="inlineStr">
+        <is>
+          <t>EMU ML</t>
+        </is>
+      </c>
+      <c r="G67" s="23" t="n"/>
+      <c r="H67" s="13" t="n">
+        <v>-355</v>
+      </c>
+      <c r="I67" s="15" t="n">
+        <v>0.6313778129495795</v>
+      </c>
+      <c r="J67" s="15" t="n">
+        <v>0.7477827050997783</v>
+      </c>
+      <c r="K67" s="15" t="n">
+        <v>0.7802197802197802</v>
+      </c>
+      <c r="L67" s="14" t="n">
+        <v>-0.1488419672702007</v>
+      </c>
+      <c r="M67" s="14" t="n">
+        <v>-0.1907692819942009</v>
+      </c>
+      <c r="N67" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P67" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q67" s="12" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B68" s="17" t="inlineStr">
+        <is>
+          <t>ALB @ BUFF</t>
+        </is>
+      </c>
+      <c r="C68" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-03 23:00</t>
+        </is>
+      </c>
+      <c r="D68" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="17" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="F68" s="17" t="inlineStr">
+        <is>
+          <t>Under 48.5</t>
+        </is>
+      </c>
+      <c r="G68" s="26" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="H68" s="18" t="n">
+        <v>-112</v>
+      </c>
+      <c r="I68" s="20" t="n">
+        <v>0.3762461039069736</v>
+      </c>
+      <c r="J68" s="20" t="n">
+        <v>0.5043297540699688</v>
+      </c>
+      <c r="K68" s="20" t="n">
+        <v>0.5283018867924528</v>
+      </c>
+      <c r="L68" s="19" t="n">
+        <v>-0.1520557828854793</v>
+      </c>
+      <c r="M68" s="19" t="n">
+        <v>-0.2878198747475144</v>
+      </c>
+      <c r="N68" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P68" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q68" s="17" t="inlineStr">
+        <is>
+          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="inlineStr">
+        <is>
+          <t>SAC @ EMU</t>
+        </is>
+      </c>
+      <c r="C69" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:30</t>
+        </is>
+      </c>
+      <c r="D69" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" s="12" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="F69" s="12" t="inlineStr">
+        <is>
+          <t>EMU -9.5</t>
+        </is>
+      </c>
+      <c r="G69" s="23" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H69" s="13" t="n">
+        <v>-110</v>
+      </c>
+      <c r="I69" s="15" t="n">
+        <v>0.3626957910893782</v>
+      </c>
+      <c r="J69" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K69" s="15" t="n">
+        <v>0.5238095238095238</v>
+      </c>
+      <c r="L69" s="14" t="n">
+        <v>-0.1611137327201456</v>
+      </c>
+      <c r="M69" s="14" t="n">
+        <v>-0.3075807624657325</v>
+      </c>
+      <c r="N69" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P69" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q69" s="12" t="inlineStr">
         <is>
           <t>raw model/market disagreement exceeds the safety limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B70" s="17" t="inlineStr">
+        <is>
+          <t>JVST @ NDSU</t>
+        </is>
+      </c>
+      <c r="C70" s="17" t="inlineStr">
+        <is>
+          <t>2026-08-29 21:30</t>
+        </is>
+      </c>
+      <c r="D70" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="17" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="F70" s="17" t="inlineStr">
+        <is>
+          <t>Under 46.5</t>
+        </is>
+      </c>
+      <c r="G70" s="26" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="H70" s="18" t="n">
+        <v>-110</v>
+      </c>
+      <c r="I70" s="20" t="n">
+        <v>0.3446651319186821</v>
+      </c>
+      <c r="J70" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K70" s="20" t="n">
+        <v>0.5238095238095238</v>
+      </c>
+      <c r="L70" s="19" t="n">
+        <v>-0.1791443918908417</v>
+      </c>
+      <c r="M70" s="19" t="n">
+        <v>-0.3420029299734251</v>
+      </c>
+      <c r="N70" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P70" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q70" s="17" t="inlineStr">
+        <is>
+          <t>raw model/market disagreement exceeds the safety limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B71" s="12" t="inlineStr">
+        <is>
+          <t>MASS @ RUTG</t>
+        </is>
+      </c>
+      <c r="C71" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-03 22:00</t>
+        </is>
+      </c>
+      <c r="D71" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" s="12" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="F71" s="12" t="inlineStr">
+        <is>
+          <t>RUTG ML</t>
+        </is>
+      </c>
+      <c r="G71" s="23" t="n"/>
+      <c r="H71" s="13" t="n">
+        <v>-6500</v>
+      </c>
+      <c r="I71" s="15" t="n">
+        <v>0.8036923684058288</v>
+      </c>
+      <c r="J71" s="15" t="n">
+        <v>0.9538784067085954</v>
+      </c>
+      <c r="K71" s="15" t="n">
+        <v>0.9848484848484849</v>
+      </c>
+      <c r="L71" s="14" t="n">
+        <v>-0.1811561164426561</v>
+      </c>
+      <c r="M71" s="14" t="n">
+        <v>-0.183943133618697</v>
+      </c>
+      <c r="N71" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P71" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q71" s="12" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B72" s="17" t="inlineStr">
+        <is>
+          <t>AKR @ WAKE</t>
+        </is>
+      </c>
+      <c r="C72" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-03 23:00</t>
+        </is>
+      </c>
+      <c r="D72" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" s="17" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="F72" s="17" t="inlineStr">
+        <is>
+          <t>WAKE ML</t>
+        </is>
+      </c>
+      <c r="G72" s="26" t="n"/>
+      <c r="H72" s="18" t="n">
+        <v>-2800</v>
+      </c>
+      <c r="I72" s="20" t="n">
+        <v>0.7689464432363347</v>
+      </c>
+      <c r="J72" s="20" t="n">
+        <v>0.9311163895486935</v>
+      </c>
+      <c r="K72" s="20" t="n">
+        <v>0.9655172413793104</v>
+      </c>
+      <c r="L72" s="19" t="n">
+        <v>-0.1965707981429757</v>
+      </c>
+      <c r="M72" s="19" t="n">
+        <v>-0.203591183790939</v>
+      </c>
+      <c r="N72" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P72" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q72" s="17" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B73" s="12" t="inlineStr">
+        <is>
+          <t>NMSU @ FSU</t>
+        </is>
+      </c>
+      <c r="C73" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-29 23:00</t>
+        </is>
+      </c>
+      <c r="D73" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" s="12" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="F73" s="12" t="inlineStr">
+        <is>
+          <t>FSU ML</t>
+        </is>
+      </c>
+      <c r="G73" s="23" t="n"/>
+      <c r="H73" s="13" t="n">
+        <v>-6500</v>
+      </c>
+      <c r="I73" s="15" t="n">
+        <v>0.7810227846843814</v>
+      </c>
+      <c r="J73" s="15" t="n">
+        <v>0.9538784067085954</v>
+      </c>
+      <c r="K73" s="15" t="n">
+        <v>0.9848484848484849</v>
+      </c>
+      <c r="L73" s="14" t="n">
+        <v>-0.2038257001641035</v>
+      </c>
+      <c r="M73" s="14" t="n">
+        <v>-0.2069614801666282</v>
+      </c>
+      <c r="N73" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P73" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q73" s="12" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B74" s="17" t="inlineStr">
+        <is>
+          <t>WES @ KENN</t>
+        </is>
+      </c>
+      <c r="C74" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-03 23:00</t>
+        </is>
+      </c>
+      <c r="D74" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" s="17" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="F74" s="17" t="inlineStr">
+        <is>
+          <t>KENN ML</t>
+        </is>
+      </c>
+      <c r="G74" s="26" t="n"/>
+      <c r="H74" s="18" t="n">
+        <v>-3600</v>
+      </c>
+      <c r="I74" s="20" t="n">
+        <v>0.7629882523168648</v>
+      </c>
+      <c r="J74" s="20" t="n">
+        <v>0.9396411092985318</v>
+      </c>
+      <c r="K74" s="20" t="n">
+        <v>0.972972972972973</v>
+      </c>
+      <c r="L74" s="19" t="n">
+        <v>-0.2099847206561082</v>
+      </c>
+      <c r="M74" s="19" t="n">
+        <v>-0.2158176295632223</v>
+      </c>
+      <c r="N74" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P74" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q74" s="17" t="inlineStr">
+        <is>
+          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B75" s="12" t="inlineStr">
+        <is>
+          <t>MRMK @ DEL</t>
+        </is>
+      </c>
+      <c r="C75" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-03 23:00</t>
+        </is>
+      </c>
+      <c r="D75" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" s="12" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="F75" s="12" t="inlineStr">
+        <is>
+          <t>DEL ML</t>
+        </is>
+      </c>
+      <c r="G75" s="23" t="n"/>
+      <c r="H75" s="13" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="I75" s="15" t="n">
+        <v>0.7657797338257375</v>
+      </c>
+      <c r="J75" s="15" t="n">
+        <v>0.9684473601999376</v>
+      </c>
+      <c r="K75" s="15" t="n">
+        <v>0.9900990099009901</v>
+      </c>
+      <c r="L75" s="14" t="n">
+        <v>-0.2243192760752526</v>
+      </c>
+      <c r="M75" s="14" t="n">
+        <v>-0.2265624688360051</v>
+      </c>
+      <c r="N75" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P75" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q75" s="12" t="inlineStr">
+        <is>
+          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B76" s="17" t="inlineStr">
+        <is>
+          <t>ALB @ BUFF</t>
+        </is>
+      </c>
+      <c r="C76" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-03 23:00</t>
+        </is>
+      </c>
+      <c r="D76" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" s="17" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="F76" s="17" t="inlineStr">
+        <is>
+          <t>BUFF ML</t>
+        </is>
+      </c>
+      <c r="G76" s="26" t="n"/>
+      <c r="H76" s="18" t="n">
+        <v>-8000</v>
+      </c>
+      <c r="I76" s="20" t="n">
+        <v>0.7599039260434692</v>
+      </c>
+      <c r="J76" s="20" t="n">
+        <v>0.9578344612181156</v>
+      </c>
+      <c r="K76" s="20" t="n">
+        <v>0.9876543209876543</v>
+      </c>
+      <c r="L76" s="19" t="n">
+        <v>-0.227750394944185</v>
+      </c>
+      <c r="M76" s="19" t="n">
+        <v>-0.2305972748809874</v>
+      </c>
+      <c r="N76" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P76" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q76" s="17" t="inlineStr">
+        <is>
+          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B77" s="12" t="inlineStr">
+        <is>
+          <t>WES @ KENN</t>
+        </is>
+      </c>
+      <c r="C77" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-03 23:00</t>
+        </is>
+      </c>
+      <c r="D77" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" s="12" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="F77" s="12" t="inlineStr">
+        <is>
+          <t>KENN -22.5</t>
+        </is>
+      </c>
+      <c r="G77" s="23" t="n">
+        <v>-22.5</v>
+      </c>
+      <c r="H77" s="13" t="n">
+        <v>-105</v>
+      </c>
+      <c r="I77" s="15" t="n">
+        <v>0.2726533482579036</v>
+      </c>
+      <c r="J77" s="15" t="n">
+        <v>0.4891657638136511</v>
+      </c>
+      <c r="K77" s="15" t="n">
+        <v>0.5121951219512195</v>
+      </c>
+      <c r="L77" s="14" t="n">
+        <v>-0.2395417736933159</v>
+      </c>
+      <c r="M77" s="14" t="n">
+        <v>-0.4676767962583787</v>
+      </c>
+      <c r="N77" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" s="24" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P77" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q77" s="12" t="inlineStr">
+        <is>
+          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B78" s="17" t="inlineStr">
+        <is>
+          <t>AKR @ WAKE</t>
+        </is>
+      </c>
+      <c r="C78" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-03 23:00</t>
+        </is>
+      </c>
+      <c r="D78" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" s="17" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="F78" s="17" t="inlineStr">
+        <is>
+          <t>WAKE -23.5</t>
+        </is>
+      </c>
+      <c r="G78" s="26" t="n">
+        <v>-23.5</v>
+      </c>
+      <c r="H78" s="18" t="n">
+        <v>-112</v>
+      </c>
+      <c r="I78" s="20" t="n">
+        <v>0.279786024178475</v>
+      </c>
+      <c r="J78" s="20" t="n">
+        <v>0.5043297540699688</v>
+      </c>
+      <c r="K78" s="20" t="n">
+        <v>0.5283018867924528</v>
+      </c>
+      <c r="L78" s="19" t="n">
+        <v>-0.2485158626139778</v>
+      </c>
+      <c r="M78" s="19" t="n">
+        <v>-0.4704050256621722</v>
+      </c>
+      <c r="N78" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P78" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q78" s="17" t="inlineStr">
+        <is>
+          <t>raw model/market disagreement exceeds the safety limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="inlineStr">
+        <is>
+          <t>ALB @ BUFF</t>
+        </is>
+      </c>
+      <c r="C79" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-03 23:00</t>
+        </is>
+      </c>
+      <c r="D79" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" s="12" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="F79" s="12" t="inlineStr">
+        <is>
+          <t>BUFF -24.5</t>
+        </is>
+      </c>
+      <c r="G79" s="23" t="n">
+        <v>-24.5</v>
+      </c>
+      <c r="H79" s="13" t="n">
+        <v>-108</v>
+      </c>
+      <c r="I79" s="15" t="n">
+        <v>0.2657449776111079</v>
+      </c>
+      <c r="J79" s="15" t="n">
+        <v>0.4956702459300312</v>
+      </c>
+      <c r="K79" s="15" t="n">
+        <v>0.5192307692307693</v>
+      </c>
+      <c r="L79" s="14" t="n">
+        <v>-0.2534857916196613</v>
+      </c>
+      <c r="M79" s="14" t="n">
+        <v>-0.4881948579341625</v>
+      </c>
+      <c r="N79" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P79" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q79" s="12" t="inlineStr">
+        <is>
+          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B80" s="17" t="inlineStr">
+        <is>
+          <t>NMSU @ FSU</t>
+        </is>
+      </c>
+      <c r="C80" s="17" t="inlineStr">
+        <is>
+          <t>2026-08-29 23:00</t>
+        </is>
+      </c>
+      <c r="D80" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" s="17" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="F80" s="17" t="inlineStr">
+        <is>
+          <t>FSU -31.5</t>
+        </is>
+      </c>
+      <c r="G80" s="26" t="n">
+        <v>-31.5</v>
+      </c>
+      <c r="H80" s="18" t="n">
+        <v>-105</v>
+      </c>
+      <c r="I80" s="20" t="n">
+        <v>0.2515947455243119</v>
+      </c>
+      <c r="J80" s="20" t="n">
+        <v>0.4891657638136511</v>
+      </c>
+      <c r="K80" s="20" t="n">
+        <v>0.5121951219512195</v>
+      </c>
+      <c r="L80" s="19" t="n">
+        <v>-0.2606003764269076</v>
+      </c>
+      <c r="M80" s="19" t="n">
+        <v>-0.5087912111192006</v>
+      </c>
+      <c r="N80" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P80" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q80" s="17" t="inlineStr">
+        <is>
+          <t>raw model/market disagreement exceeds the safety limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B81" s="12" t="inlineStr">
+        <is>
+          <t>SJSU @ USC</t>
+        </is>
+      </c>
+      <c r="C81" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-29 19:00</t>
+        </is>
+      </c>
+      <c r="D81" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="12" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="F81" s="12" t="inlineStr">
+        <is>
+          <t>USC -38.5</t>
+        </is>
+      </c>
+      <c r="G81" s="23" t="n">
+        <v>-38.5</v>
+      </c>
+      <c r="H81" s="13" t="n">
+        <v>-102</v>
+      </c>
+      <c r="I81" s="15" t="n">
+        <v>0.2436390210930696</v>
+      </c>
+      <c r="J81" s="15" t="n">
+        <v>0.4826358742837298</v>
+      </c>
+      <c r="K81" s="15" t="n">
+        <v>0.504950495049505</v>
+      </c>
+      <c r="L81" s="14" t="n">
+        <v>-0.2613114739564354</v>
+      </c>
+      <c r="M81" s="14" t="n">
+        <v>-0.517499193521568</v>
+      </c>
+      <c r="N81" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P81" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q81" s="12" t="inlineStr">
+        <is>
+          <t>raw model/market disagreement exceeds the safety limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B82" s="17" t="inlineStr">
+        <is>
+          <t>MASS @ RUTG</t>
+        </is>
+      </c>
+      <c r="C82" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-03 22:00</t>
+        </is>
+      </c>
+      <c r="D82" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="17" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="F82" s="17" t="inlineStr">
+        <is>
+          <t>RUTG -30.5</t>
+        </is>
+      </c>
+      <c r="G82" s="26" t="n">
+        <v>-30.5</v>
+      </c>
+      <c r="H82" s="18" t="n">
+        <v>-112</v>
+      </c>
+      <c r="I82" s="20" t="n">
+        <v>0.2637706885532299</v>
+      </c>
+      <c r="J82" s="20" t="n">
+        <v>0.5043297540699688</v>
+      </c>
+      <c r="K82" s="20" t="n">
+        <v>0.5283018867924528</v>
+      </c>
+      <c r="L82" s="19" t="n">
+        <v>-0.2645311982392229</v>
+      </c>
+      <c r="M82" s="19" t="n">
+        <v>-0.5007197680956719</v>
+      </c>
+      <c r="N82" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P82" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q82" s="17" t="inlineStr">
+        <is>
+          <t>raw model/market disagreement exceeds the safety limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B83" s="12" t="inlineStr">
+        <is>
+          <t>MRMK @ DEL</t>
+        </is>
+      </c>
+      <c r="C83" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-03 23:00</t>
+        </is>
+      </c>
+      <c r="D83" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" s="12" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="F83" s="12" t="inlineStr">
+        <is>
+          <t>DEL -28.5</t>
+        </is>
+      </c>
+      <c r="G83" s="23" t="n">
+        <v>-28.5</v>
+      </c>
+      <c r="H83" s="13" t="n">
+        <v>-112</v>
+      </c>
+      <c r="I83" s="15" t="n">
+        <v>0.2613150626201174</v>
+      </c>
+      <c r="J83" s="15" t="n">
+        <v>0.5043297540699688</v>
+      </c>
+      <c r="K83" s="15" t="n">
+        <v>0.5283018867924528</v>
+      </c>
+      <c r="L83" s="14" t="n">
+        <v>-0.2669868241723354</v>
+      </c>
+      <c r="M83" s="14" t="n">
+        <v>-0.5053679171833493</v>
+      </c>
+      <c r="N83" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P83" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q83" s="12" t="inlineStr">
+        <is>
+          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B84" s="17" t="inlineStr">
+        <is>
+          <t>BCU @ UCF</t>
+        </is>
+      </c>
+      <c r="C84" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-03 23:00</t>
+        </is>
+      </c>
+      <c r="D84" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" s="17" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="F84" s="17" t="inlineStr">
+        <is>
+          <t>UCF -42.5</t>
+        </is>
+      </c>
+      <c r="G84" s="26" t="n">
+        <v>-42.5</v>
+      </c>
+      <c r="H84" s="18" t="n">
+        <v>-108</v>
+      </c>
+      <c r="I84" s="20" t="n">
+        <v>0.2482518098143184</v>
+      </c>
+      <c r="J84" s="20" t="n">
+        <v>0.4956702459300312</v>
+      </c>
+      <c r="K84" s="20" t="n">
+        <v>0.5192307692307693</v>
+      </c>
+      <c r="L84" s="19" t="n">
+        <v>-0.2709789594164509</v>
+      </c>
+      <c r="M84" s="19" t="n">
+        <v>-0.521885403320572</v>
+      </c>
+      <c r="N84" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P84" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q84" s="17" t="inlineStr">
+        <is>
+          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -11056,7 +13298,7 @@
       </c>
       <c r="M5" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>
@@ -11101,7 +13343,7 @@
       <c r="L6" s="18" t="n"/>
       <c r="M6" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>
@@ -11150,7 +13392,7 @@
       </c>
       <c r="M7" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>
@@ -11199,7 +13441,7 @@
       </c>
       <c r="M8" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>
@@ -11248,7 +13490,7 @@
       </c>
       <c r="M9" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>
@@ -11297,7 +13539,7 @@
       </c>
       <c r="M10" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>
@@ -11346,7 +13588,7 @@
       </c>
       <c r="M11" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>
@@ -11395,7 +13637,7 @@
       </c>
       <c r="M12" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>

--- a/NCAAF_Edge_Model.xlsx
+++ b/NCAAF_Edge_Model.xlsx
@@ -640,7 +640,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-24T05:24:18+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
+          <t>Generated 2026-08-24T15:20:51+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
         </is>
       </c>
     </row>
@@ -2372,22 +2372,22 @@
         <v>46.5</v>
       </c>
       <c r="H22" s="18" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="I22" s="20" t="n">
-        <v>0.6553348680813179</v>
+        <v>0.6574997451163023</v>
       </c>
       <c r="J22" s="20" t="n">
-        <v>0.5</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K22" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L22" s="19" t="n">
-        <v>0.1315253442717941</v>
+        <v>0.1291978583238494</v>
       </c>
       <c r="M22" s="19" t="n">
-        <v>0.2510938390643342</v>
+        <v>0.2445530889701435</v>
       </c>
       <c r="N22" s="20" t="n">
         <v>0</v>
@@ -2506,22 +2506,22 @@
         <v>48.5</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="I24" s="20" t="n">
-        <v>0.6237538960930264</v>
+        <v>0.6205016550348365</v>
       </c>
       <c r="J24" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K24" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L24" s="19" t="n">
-        <v>0.1045231268622572</v>
+        <v>0.1083065330836169</v>
       </c>
       <c r="M24" s="19" t="n">
-        <v>0.2013037998828658</v>
+        <v>0.2114556122108712</v>
       </c>
       <c r="N24" s="20" t="n">
         <v>0</v>
@@ -3497,12 +3497,12 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>JVST @ NDSU</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-08-29 21:30</t>
         </is>
       </c>
       <c r="D40" s="25" t="n">
@@ -3510,34 +3510,32 @@
       </c>
       <c r="E40" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F40" s="17" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
-        </is>
-      </c>
-      <c r="G40" s="26" t="n">
-        <v>47.5</v>
-      </c>
+          <t>JVST ML</t>
+        </is>
+      </c>
+      <c r="G40" s="26" t="n"/>
       <c r="H40" s="18" t="n">
-        <v>-110</v>
+        <v>220</v>
       </c>
       <c r="I40" s="20" t="n">
-        <v>0.5376883257015108</v>
+        <v>0.3261190128306598</v>
       </c>
       <c r="J40" s="20" t="n">
-        <v>0.5</v>
+        <v>0.299837925445705</v>
       </c>
       <c r="K40" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.3125</v>
       </c>
       <c r="L40" s="19" t="n">
-        <v>0.01387880189198698</v>
+        <v>0.0136190128306598</v>
       </c>
       <c r="M40" s="19" t="n">
-        <v>0.02649589452106615</v>
+        <v>0.04358084105811144</v>
       </c>
       <c r="N40" s="20" t="n">
         <v>0</v>
@@ -3560,12 +3558,12 @@
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>JVST @ NDSU</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D41" s="22" t="n">
@@ -3573,32 +3571,34 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>JVST ML</t>
-        </is>
-      </c>
-      <c r="G41" s="23" t="n"/>
+          <t>Over 47.5</t>
+        </is>
+      </c>
+      <c r="G41" s="23" t="n">
+        <v>47.5</v>
+      </c>
       <c r="H41" s="13" t="n">
-        <v>220</v>
+        <v>-112</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>0.3261190128306598</v>
+        <v>0.5398532027364953</v>
       </c>
       <c r="J41" s="15" t="n">
-        <v>0.299837925445705</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K41" s="15" t="n">
-        <v>0.3125</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L41" s="14" t="n">
-        <v>0.0136190128306598</v>
+        <v>0.01155131594404246</v>
       </c>
       <c r="M41" s="14" t="n">
-        <v>0.04358084105811144</v>
+        <v>0.02186499089408034</v>
       </c>
       <c r="N41" s="15" t="n">
         <v>0</v>
@@ -4060,12 +4060,12 @@
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D49" s="22" t="n">
@@ -4073,32 +4073,34 @@
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
-          <t>UVA ML</t>
-        </is>
-      </c>
-      <c r="G49" s="23" t="n"/>
+          <t>Under 47.5</t>
+        </is>
+      </c>
+      <c r="G49" s="23" t="n">
+        <v>47.5</v>
+      </c>
       <c r="H49" s="13" t="n">
-        <v>-218</v>
+        <v>-108</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>0.6254192861725905</v>
+        <v>0.4601467972635047</v>
       </c>
       <c r="J49" s="15" t="n">
-        <v>0.6574752261956054</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K49" s="15" t="n">
-        <v>0.6855345911949685</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L49" s="14" t="n">
-        <v>-0.06011530502237805</v>
+        <v>-0.05908397196726456</v>
       </c>
       <c r="M49" s="14" t="n">
-        <v>-0.08769113301429471</v>
+        <v>-0.1137913534184353</v>
       </c>
       <c r="N49" s="15" t="n">
         <v>0</v>
@@ -4121,12 +4123,12 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D50" s="25" t="n">
@@ -4134,34 +4136,32 @@
       </c>
       <c r="E50" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F50" s="17" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
-        </is>
-      </c>
-      <c r="G50" s="26" t="n">
-        <v>47.5</v>
-      </c>
+          <t>UVA ML</t>
+        </is>
+      </c>
+      <c r="G50" s="26" t="n"/>
       <c r="H50" s="18" t="n">
-        <v>-110</v>
+        <v>-218</v>
       </c>
       <c r="I50" s="20" t="n">
-        <v>0.4623116742984892</v>
+        <v>0.6254192861725905</v>
       </c>
       <c r="J50" s="20" t="n">
-        <v>0.5</v>
+        <v>0.6574752261956054</v>
       </c>
       <c r="K50" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.6855345911949685</v>
       </c>
       <c r="L50" s="19" t="n">
-        <v>-0.06149784951103465</v>
+        <v>-0.06011530502237805</v>
       </c>
       <c r="M50" s="19" t="n">
-        <v>-0.117404985430157</v>
+        <v>-0.08769113301429471</v>
       </c>
       <c r="N50" s="20" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
         <v>48.5</v>
       </c>
       <c r="H68" s="18" t="n">
-        <v>-112</v>
+        <v>-115</v>
       </c>
       <c r="I68" s="20" t="n">
-        <v>0.3762461039069736</v>
+        <v>0.3794983449651635</v>
       </c>
       <c r="J68" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K68" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L68" s="19" t="n">
-        <v>-0.1520557828854793</v>
+        <v>-0.155385375965069</v>
       </c>
       <c r="M68" s="19" t="n">
-        <v>-0.2878198747475144</v>
+        <v>-0.2905030941955639</v>
       </c>
       <c r="N68" s="20" t="n">
         <v>0</v>
@@ -5418,22 +5418,22 @@
         <v>46.5</v>
       </c>
       <c r="H70" s="18" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I70" s="20" t="n">
-        <v>0.3446651319186821</v>
+        <v>0.3425002548836977</v>
       </c>
       <c r="J70" s="20" t="n">
-        <v>0.5</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K70" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L70" s="19" t="n">
-        <v>-0.1791443918908417</v>
+        <v>-0.1767305143470715</v>
       </c>
       <c r="M70" s="19" t="n">
-        <v>-0.3420029299734251</v>
+        <v>-0.3403698794832488</v>
       </c>
       <c r="N70" s="20" t="n">
         <v>0</v>

--- a/NCAAF_Edge_Model.xlsx
+++ b/NCAAF_Edge_Model.xlsx
@@ -640,7 +640,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-24T15:20:51+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
+          <t>Generated 2026-08-24T18:03:18+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
         </is>
       </c>
     </row>
@@ -1036,17 +1036,17 @@
       </c>
       <c r="D22" s="17" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E22" s="18" t="n">
-        <v>-105</v>
+        <v>-115</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>0.08339809109262664</v>
+        <v>0.08840272575750341</v>
       </c>
       <c r="G22" s="20" t="n">
-        <v>0.5955932130438462</v>
+        <v>0.6232864466877359</v>
       </c>
       <c r="H22" s="21" t="n"/>
       <c r="I22" s="17" t="inlineStr">
@@ -1313,29 +1313,29 @@
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="G6" s="26" t="n">
-        <v>49.5</v>
+        <v>48.5</v>
       </c>
       <c r="H6" s="18" t="n">
-        <v>-105</v>
+        <v>-115</v>
       </c>
       <c r="I6" s="20" t="n">
-        <v>0.5955932130438462</v>
+        <v>0.6232864466877359</v>
       </c>
       <c r="J6" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K6" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L6" s="19" t="n">
-        <v>0.08339809109262664</v>
+        <v>0.08840272575750341</v>
       </c>
       <c r="M6" s="19" t="n">
-        <v>0.1628248445141758</v>
+        <v>0.1652746611988105</v>
       </c>
       <c r="N6" s="20" t="n">
         <v>0</v>
@@ -1622,12 +1622,12 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>NMSU @ FSU</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D11" s="22" t="n">
@@ -1640,29 +1640,29 @@
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>SJSU +38.5</t>
+          <t>NMSU +31.5</t>
         </is>
       </c>
       <c r="G11" s="23" t="n">
-        <v>-38.5</v>
+        <v>-31.5</v>
       </c>
       <c r="H11" s="13" t="n">
-        <v>-118</v>
+        <v>-115</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>0.7563609789069304</v>
+        <v>0.7484052544756881</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L11" s="14" t="n">
-        <v>0.2150765752372057</v>
+        <v>0.2135215335454556</v>
       </c>
       <c r="M11" s="14" t="n">
-        <v>0.3973448593365325</v>
+        <v>0.3991924322806341</v>
       </c>
       <c r="N11" s="15" t="n">
         <v>0</v>
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>NMSU @ FSU</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D12" s="25" t="n">
@@ -1707,29 +1707,29 @@
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>NMSU +31.5</t>
+          <t>SJSU +38.5</t>
         </is>
       </c>
       <c r="G12" s="26" t="n">
-        <v>-31.5</v>
+        <v>-38.5</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>-115</v>
+        <v>-120</v>
       </c>
       <c r="I12" s="20" t="n">
-        <v>0.7484052544756881</v>
+        <v>0.7585484812661867</v>
       </c>
       <c r="J12" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="K12" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="L12" s="19" t="n">
-        <v>0.2135215335454556</v>
+        <v>0.2130939358116413</v>
       </c>
       <c r="M12" s="19" t="n">
-        <v>0.3991924322806341</v>
+        <v>0.3906722156546757</v>
       </c>
       <c r="N12" s="20" t="n">
         <v>0</v>
@@ -2615,12 +2615,12 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>SAC @ EMU</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-08-29 22:30</t>
         </is>
       </c>
       <c r="D26" s="25" t="n">
@@ -2628,32 +2628,34 @@
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>UNC ML</t>
-        </is>
-      </c>
-      <c r="G26" s="26" t="n"/>
+          <t>Over 52.5</t>
+        </is>
+      </c>
+      <c r="G26" s="26" t="n">
+        <v>52.5</v>
+      </c>
       <c r="H26" s="18" t="n">
-        <v>250</v>
+        <v>-108</v>
       </c>
       <c r="I26" s="20" t="n">
-        <v>0.3621290026789783</v>
+        <v>0.595359506876733</v>
       </c>
       <c r="J26" s="20" t="n">
-        <v>0.274247491638796</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K26" s="20" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L26" s="19" t="n">
-        <v>0.0764147169646926</v>
+        <v>0.07612873764596373</v>
       </c>
       <c r="M26" s="19" t="n">
-        <v>0.267451509376424</v>
+        <v>0.1466183095403747</v>
       </c>
       <c r="N26" s="20" t="n">
         <v>0</v>
@@ -2676,12 +2678,12 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>SAC @ EMU</t>
+          <t>AKR @ WAKE</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 22:30</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D27" s="22" t="n">
@@ -2694,29 +2696,29 @@
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>Over 52.5</t>
+          <t>Over 49.5</t>
         </is>
       </c>
       <c r="G27" s="23" t="n">
-        <v>52.5</v>
+        <v>49.5</v>
       </c>
       <c r="H27" s="13" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>0.595359506876733</v>
+        <v>0.603175208172005</v>
       </c>
       <c r="J27" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K27" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L27" s="14" t="n">
-        <v>0.07612873764596373</v>
+        <v>0.07487332137955216</v>
       </c>
       <c r="M27" s="14" t="n">
-        <v>0.1466183095403747</v>
+        <v>0.1417245011827237</v>
       </c>
       <c r="N27" s="15" t="n">
         <v>0</v>
@@ -2739,12 +2741,12 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>AKR @ WAKE</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D28" s="25" t="n">
@@ -2752,34 +2754,32 @@
       </c>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
-        </is>
-      </c>
-      <c r="G28" s="26" t="n">
-        <v>49.5</v>
-      </c>
+          <t>UNC ML</t>
+        </is>
+      </c>
+      <c r="G28" s="26" t="n"/>
       <c r="H28" s="18" t="n">
-        <v>-112</v>
+        <v>240</v>
       </c>
       <c r="I28" s="20" t="n">
-        <v>0.603175208172005</v>
+        <v>0.3660199960886052</v>
       </c>
       <c r="J28" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.2820294784580499</v>
       </c>
       <c r="K28" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="L28" s="19" t="n">
-        <v>0.07487332137955216</v>
+        <v>0.07190234902978171</v>
       </c>
       <c r="M28" s="19" t="n">
-        <v>0.1417245011827237</v>
+        <v>0.2444679867012578</v>
       </c>
       <c r="N28" s="20" t="n">
         <v>0</v>
@@ -3180,12 +3180,12 @@
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D35" s="22" t="n">
@@ -3193,22 +3193,22 @@
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>NCSU +5.5</t>
+          <t>Under 59.5</t>
         </is>
       </c>
       <c r="G35" s="23" t="n">
-        <v>-5.5</v>
+        <v>59.5</v>
       </c>
       <c r="H35" s="13" t="n">
         <v>-108</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>0.5412896688794703</v>
+        <v>0.5413851965860426</v>
       </c>
       <c r="J35" s="15" t="n">
         <v>0.4956702459300312</v>
@@ -3217,10 +3217,10 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L35" s="14" t="n">
-        <v>0.022058899648701</v>
+        <v>0.02215442735527329</v>
       </c>
       <c r="M35" s="14" t="n">
-        <v>0.04248380673083174</v>
+        <v>0.04266778601756349</v>
       </c>
       <c r="N35" s="15" t="n">
         <v>0</v>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>JVST @ NDSU</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D36" s="25" t="n">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="F36" s="17" t="inlineStr">
         <is>
-          <t>JVST +7</t>
+          <t>NCSU +5.5</t>
         </is>
       </c>
       <c r="G36" s="26" t="n">
-        <v>-7</v>
+        <v>-5.5</v>
       </c>
       <c r="H36" s="18" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I36" s="20" t="n">
-        <v>0.5445684137563569</v>
+        <v>0.5412896688794703</v>
       </c>
       <c r="J36" s="20" t="n">
-        <v>0.5</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K36" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L36" s="19" t="n">
-        <v>0.02075888994683306</v>
+        <v>0.022058899648701</v>
       </c>
       <c r="M36" s="19" t="n">
-        <v>0.03762929802911508</v>
+        <v>0.04248380673083174</v>
       </c>
       <c r="N36" s="20" t="n">
-        <v>0.0505</v>
+        <v>0</v>
       </c>
       <c r="O36" s="27" t="n">
         <v>0.45</v>
@@ -3306,12 +3306,12 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D37" s="22" t="n">
@@ -3319,34 +3319,32 @@
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>Under 59.5</t>
-        </is>
-      </c>
-      <c r="G37" s="23" t="n">
-        <v>59.5</v>
-      </c>
+          <t>NCSU ML</t>
+        </is>
+      </c>
+      <c r="G37" s="23" t="n"/>
       <c r="H37" s="13" t="n">
-        <v>-110</v>
+        <v>180</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>0.543550073621027</v>
+        <v>0.3745807138274095</v>
       </c>
       <c r="J37" s="15" t="n">
-        <v>0.5</v>
+        <v>0.3425247738043947</v>
       </c>
       <c r="K37" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="L37" s="14" t="n">
-        <v>0.01974054981150319</v>
+        <v>0.01743785668455239</v>
       </c>
       <c r="M37" s="14" t="n">
-        <v>0.0376865041855971</v>
+        <v>0.04882599871674664</v>
       </c>
       <c r="N37" s="15" t="n">
         <v>0</v>
@@ -3369,12 +3367,12 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>MRMK @ DEL</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D38" s="25" t="n">
@@ -3382,32 +3380,34 @@
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F38" s="17" t="inlineStr">
         <is>
-          <t>NCSU ML</t>
-        </is>
-      </c>
-      <c r="G38" s="26" t="n"/>
+          <t>Over 55.5</t>
+        </is>
+      </c>
+      <c r="G38" s="26" t="n">
+        <v>55.5</v>
+      </c>
       <c r="H38" s="18" t="n">
-        <v>180</v>
+        <v>-112</v>
       </c>
       <c r="I38" s="20" t="n">
-        <v>0.3745807138274095</v>
+        <v>0.5437650474945759</v>
       </c>
       <c r="J38" s="20" t="n">
-        <v>0.3425247738043947</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K38" s="20" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>0.01743785668455239</v>
+        <v>0.01546316070212306</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>0.04882599871674664</v>
+        <v>0.02926955418616145</v>
       </c>
       <c r="N38" s="20" t="n">
         <v>0</v>
@@ -3420,7 +3420,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q38" s="17" t="n"/>
+      <c r="Q38" s="17" t="inlineStr">
+        <is>
+          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
@@ -3430,12 +3434,12 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>MRMK @ DEL</t>
+          <t>JVST @ NDSU</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-29 21:30</t>
         </is>
       </c>
       <c r="D39" s="22" t="n">
@@ -3443,37 +3447,37 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>Over 55.5</t>
+          <t>JVST +7</t>
         </is>
       </c>
       <c r="G39" s="23" t="n">
-        <v>55.5</v>
+        <v>-7</v>
       </c>
       <c r="H39" s="13" t="n">
-        <v>-112</v>
+        <v>-115</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>0.5437650474945759</v>
+        <v>0.5499855318495314</v>
       </c>
       <c r="J39" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K39" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L39" s="14" t="n">
-        <v>0.01546316070212306</v>
+        <v>0.01510181091929885</v>
       </c>
       <c r="M39" s="14" t="n">
-        <v>0.02926955418616145</v>
+        <v>0.02680803788623665</v>
       </c>
       <c r="N39" s="15" t="n">
-        <v>0</v>
+        <v>0.0505</v>
       </c>
       <c r="O39" s="24" t="n">
         <v>0.45</v>
@@ -3483,11 +3487,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q39" s="12" t="inlineStr">
-        <is>
-          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q39" s="12" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="17" t="inlineStr">
@@ -3497,12 +3497,12 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>JVST @ NDSU</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D40" s="25" t="n">
@@ -3510,32 +3510,34 @@
       </c>
       <c r="E40" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F40" s="17" t="inlineStr">
         <is>
-          <t>JVST ML</t>
-        </is>
-      </c>
-      <c r="G40" s="26" t="n"/>
+          <t>Over 47.5</t>
+        </is>
+      </c>
+      <c r="G40" s="26" t="n">
+        <v>47.5</v>
+      </c>
       <c r="H40" s="18" t="n">
-        <v>220</v>
+        <v>-112</v>
       </c>
       <c r="I40" s="20" t="n">
-        <v>0.3261190128306598</v>
+        <v>0.5398532027364953</v>
       </c>
       <c r="J40" s="20" t="n">
-        <v>0.299837925445705</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K40" s="20" t="n">
-        <v>0.3125</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L40" s="19" t="n">
-        <v>0.0136190128306598</v>
+        <v>0.01155131594404246</v>
       </c>
       <c r="M40" s="19" t="n">
-        <v>0.04358084105811144</v>
+        <v>0.02186499089408034</v>
       </c>
       <c r="N40" s="20" t="n">
         <v>0</v>
@@ -3558,12 +3560,12 @@
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>JVST @ NDSU</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-08-29 21:30</t>
         </is>
       </c>
       <c r="D41" s="22" t="n">
@@ -3571,34 +3573,32 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
-        </is>
-      </c>
-      <c r="G41" s="23" t="n">
-        <v>47.5</v>
-      </c>
+          <t>JVST ML</t>
+        </is>
+      </c>
+      <c r="G41" s="23" t="n"/>
       <c r="H41" s="13" t="n">
-        <v>-112</v>
+        <v>210</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>0.5398532027364953</v>
+        <v>0.3308036085807733</v>
       </c>
       <c r="J41" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.3092071169459319</v>
       </c>
       <c r="K41" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.3225806451612903</v>
       </c>
       <c r="L41" s="14" t="n">
-        <v>0.01155131594404246</v>
+        <v>0.008222963419482976</v>
       </c>
       <c r="M41" s="14" t="n">
-        <v>0.02186499089408034</v>
+        <v>0.02549118660039718</v>
       </c>
       <c r="N41" s="15" t="n">
         <v>0</v>
@@ -3936,12 +3936,12 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>NMSU @ FSU</t>
+          <t>JVST @ NDSU</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-08-29 21:30</t>
         </is>
       </c>
       <c r="D47" s="22" t="n">
@@ -3949,34 +3949,32 @@
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>Under 53.5</t>
-        </is>
-      </c>
-      <c r="G47" s="23" t="n">
-        <v>53.5</v>
-      </c>
+          <t>NDSU ML</t>
+        </is>
+      </c>
+      <c r="G47" s="23" t="n"/>
       <c r="H47" s="13" t="n">
-        <v>-110</v>
+        <v>-258</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>0.4701788116717455</v>
+        <v>0.6691963914192267</v>
       </c>
       <c r="J47" s="15" t="n">
-        <v>0.5</v>
+        <v>0.6907928830540681</v>
       </c>
       <c r="K47" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.7206703910614525</v>
       </c>
       <c r="L47" s="14" t="n">
-        <v>-0.05363071213777837</v>
+        <v>-0.05147399964222577</v>
       </c>
       <c r="M47" s="14" t="n">
-        <v>-0.1023859049903041</v>
+        <v>-0.07142516229425128</v>
       </c>
       <c r="N47" s="15" t="n">
         <v>0</v>
@@ -3999,12 +3997,12 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>JVST @ NDSU</t>
+          <t>NMSU @ FSU</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D48" s="25" t="n">
@@ -4012,32 +4010,34 @@
       </c>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F48" s="17" t="inlineStr">
         <is>
-          <t>NDSU ML</t>
-        </is>
-      </c>
-      <c r="G48" s="26" t="n"/>
+          <t>Under 53.5</t>
+        </is>
+      </c>
+      <c r="G48" s="26" t="n">
+        <v>53.5</v>
+      </c>
       <c r="H48" s="18" t="n">
-        <v>-270</v>
+        <v>-110</v>
       </c>
       <c r="I48" s="20" t="n">
-        <v>0.6738809871693402</v>
+        <v>0.4701788116717455</v>
       </c>
       <c r="J48" s="20" t="n">
-        <v>0.7001620745542949</v>
+        <v>0.5</v>
       </c>
       <c r="K48" s="20" t="n">
-        <v>0.7297297297297297</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L48" s="19" t="n">
-        <v>-0.05584874256038952</v>
+        <v>-0.05363071213777837</v>
       </c>
       <c r="M48" s="19" t="n">
-        <v>-0.07653346202720057</v>
+        <v>-0.1023859049903041</v>
       </c>
       <c r="N48" s="20" t="n">
         <v>0</v>
@@ -4184,12 +4184,12 @@
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>MRMK @ DEL</t>
+          <t>JVST @ NDSU</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-29 21:30</t>
         </is>
       </c>
       <c r="D51" s="22" t="n">
@@ -4197,37 +4197,37 @@
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
         <is>
-          <t>Under 55.5</t>
+          <t>NDSU -7</t>
         </is>
       </c>
       <c r="G51" s="23" t="n">
-        <v>55.5</v>
+        <v>-7</v>
       </c>
       <c r="H51" s="13" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>0.4562349525054241</v>
+        <v>0.4500144681504686</v>
       </c>
       <c r="J51" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K51" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L51" s="14" t="n">
-        <v>-0.06299581672534516</v>
+        <v>-0.06218065380075088</v>
       </c>
       <c r="M51" s="14" t="n">
-        <v>-0.1213252766562202</v>
+        <v>-0.1152697169483107</v>
       </c>
       <c r="N51" s="15" t="n">
-        <v>0</v>
+        <v>0.0505</v>
       </c>
       <c r="O51" s="24" t="n">
         <v>0.45</v>
@@ -4237,11 +4237,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q51" s="12" t="inlineStr">
-        <is>
-          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q51" s="12" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="17" t="inlineStr">
@@ -4251,12 +4247,12 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>MRMK @ DEL</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D52" s="25" t="n">
@@ -4269,29 +4265,29 @@
       </c>
       <c r="F52" s="17" t="inlineStr">
         <is>
-          <t>Over 59.5</t>
+          <t>Under 55.5</t>
         </is>
       </c>
       <c r="G52" s="26" t="n">
-        <v>59.5</v>
+        <v>55.5</v>
       </c>
       <c r="H52" s="18" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I52" s="20" t="n">
-        <v>0.456449926378973</v>
+        <v>0.4562349525054241</v>
       </c>
       <c r="J52" s="20" t="n">
-        <v>0.5</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K52" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L52" s="19" t="n">
-        <v>-0.06735959743055087</v>
+        <v>-0.06299581672534516</v>
       </c>
       <c r="M52" s="19" t="n">
-        <v>-0.1285955950946879</v>
+        <v>-0.1213252766562202</v>
       </c>
       <c r="N52" s="20" t="n">
         <v>0</v>
@@ -4304,7 +4300,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q52" s="17" t="n"/>
+      <c r="Q52" s="17" t="inlineStr">
+        <is>
+          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
@@ -4314,12 +4314,12 @@
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>JVST @ NDSU</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D53" s="22" t="n">
@@ -4332,32 +4332,32 @@
       </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
-          <t>NDSU -7</t>
+          <t>UVA -5.5</t>
         </is>
       </c>
       <c r="G53" s="23" t="n">
-        <v>-7</v>
+        <v>-5.5</v>
       </c>
       <c r="H53" s="13" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>0.4554315862436431</v>
+        <v>0.4587103311205297</v>
       </c>
       <c r="J53" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K53" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L53" s="14" t="n">
-        <v>-0.06837793756588073</v>
+        <v>-0.0695915556719231</v>
       </c>
       <c r="M53" s="14" t="n">
-        <v>-0.1239475616409477</v>
+        <v>-0.1317268732361402</v>
       </c>
       <c r="N53" s="15" t="n">
-        <v>0.0505</v>
+        <v>0</v>
       </c>
       <c r="O53" s="24" t="n">
         <v>0.45</v>
@@ -4377,12 +4377,12 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D54" s="25" t="n">
@@ -4390,22 +4390,22 @@
       </c>
       <c r="E54" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F54" s="17" t="inlineStr">
         <is>
-          <t>UVA -5.5</t>
+          <t>Over 59.5</t>
         </is>
       </c>
       <c r="G54" s="26" t="n">
-        <v>-5.5</v>
+        <v>59.5</v>
       </c>
       <c r="H54" s="18" t="n">
         <v>-112</v>
       </c>
       <c r="I54" s="20" t="n">
-        <v>0.4587103311205297</v>
+        <v>0.4586148034139574</v>
       </c>
       <c r="J54" s="20" t="n">
         <v>0.5043297540699688</v>
@@ -4414,10 +4414,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L54" s="19" t="n">
-        <v>-0.0695915556719231</v>
+        <v>-0.06968708337849544</v>
       </c>
       <c r="M54" s="19" t="n">
-        <v>-0.1317268732361402</v>
+        <v>-0.1319076935378664</v>
       </c>
       <c r="N54" s="20" t="n">
         <v>0</v>
@@ -4841,22 +4841,22 @@
       </c>
       <c r="G61" s="23" t="n"/>
       <c r="H61" s="13" t="n">
-        <v>-310</v>
+        <v>-298</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>0.6378709973210217</v>
+        <v>0.6339800039113948</v>
       </c>
       <c r="J61" s="15" t="n">
-        <v>0.725752508361204</v>
+        <v>0.7179705215419501</v>
       </c>
       <c r="K61" s="15" t="n">
-        <v>0.7560975609756098</v>
+        <v>0.7487437185929648</v>
       </c>
       <c r="L61" s="14" t="n">
-        <v>-0.1182265636545881</v>
+        <v>-0.1147637146815701</v>
       </c>
       <c r="M61" s="14" t="n">
-        <v>-0.1563641648334875</v>
+        <v>-0.1532750283331037</v>
       </c>
       <c r="N61" s="15" t="n">
         <v>0</v>
@@ -5153,29 +5153,29 @@
       </c>
       <c r="F66" s="17" t="inlineStr">
         <is>
-          <t>Under 49.5</t>
+          <t>Under 48.5</t>
         </is>
       </c>
       <c r="G66" s="26" t="n">
-        <v>49.5</v>
+        <v>48.5</v>
       </c>
       <c r="H66" s="18" t="n">
-        <v>-115</v>
+        <v>-105</v>
       </c>
       <c r="I66" s="20" t="n">
-        <v>0.4044067869561538</v>
+        <v>0.3767135533122641</v>
       </c>
       <c r="J66" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K66" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L66" s="19" t="n">
-        <v>-0.1304769339740787</v>
+        <v>-0.1354815686389554</v>
       </c>
       <c r="M66" s="19" t="n">
-        <v>-0.2439351374297994</v>
+        <v>-0.2645116340093892</v>
       </c>
       <c r="N66" s="20" t="n">
         <v>0</v>
@@ -6051,12 +6051,12 @@
       </c>
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>NMSU @ FSU</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C80" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D80" s="25" t="n">
@@ -6069,29 +6069,29 @@
       </c>
       <c r="F80" s="17" t="inlineStr">
         <is>
-          <t>FSU -31.5</t>
+          <t>USC -38.5</t>
         </is>
       </c>
       <c r="G80" s="26" t="n">
-        <v>-31.5</v>
+        <v>-38.5</v>
       </c>
       <c r="H80" s="18" t="n">
-        <v>-105</v>
+        <v>100</v>
       </c>
       <c r="I80" s="20" t="n">
-        <v>0.2515947455243119</v>
+        <v>0.2414515187338134</v>
       </c>
       <c r="J80" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="K80" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5</v>
       </c>
       <c r="L80" s="19" t="n">
-        <v>-0.2606003764269076</v>
+        <v>-0.2585484812661866</v>
       </c>
       <c r="M80" s="19" t="n">
-        <v>-0.5087912111192006</v>
+        <v>-0.5170969625323734</v>
       </c>
       <c r="N80" s="20" t="n">
         <v>0</v>
@@ -6118,12 +6118,12 @@
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>NMSU @ FSU</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D81" s="22" t="n">
@@ -6136,29 +6136,29 @@
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
-          <t>USC -38.5</t>
+          <t>FSU -31.5</t>
         </is>
       </c>
       <c r="G81" s="23" t="n">
-        <v>-38.5</v>
+        <v>-31.5</v>
       </c>
       <c r="H81" s="13" t="n">
-        <v>-102</v>
+        <v>-105</v>
       </c>
       <c r="I81" s="15" t="n">
-        <v>0.2436390210930696</v>
+        <v>0.2515947455243119</v>
       </c>
       <c r="J81" s="15" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K81" s="15" t="n">
-        <v>0.504950495049505</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L81" s="14" t="n">
-        <v>-0.2613114739564354</v>
+        <v>-0.2606003764269076</v>
       </c>
       <c r="M81" s="14" t="n">
-        <v>-0.517499193521568</v>
+        <v>-0.5087912111192006</v>
       </c>
       <c r="N81" s="15" t="n">
         <v>0</v>
@@ -13291,10 +13291,10 @@
         <v>47.5</v>
       </c>
       <c r="K5" s="13" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="L5" s="13" t="n">
-        <v>-310</v>
+        <v>-298</v>
       </c>
       <c r="M5" s="12" t="inlineStr">
         <is>
@@ -13434,10 +13434,10 @@
         <v>46.5</v>
       </c>
       <c r="K8" s="18" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="L8" s="18" t="n">
-        <v>-270</v>
+        <v>-258</v>
       </c>
       <c r="M8" s="17" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>-5.5</v>
       </c>
       <c r="J10" s="30" t="n">
-        <v>49.5</v>
+        <v>48.5</v>
       </c>
       <c r="K10" s="18" t="n">
         <v>180</v>

--- a/NCAAF_Edge_Model.xlsx
+++ b/NCAAF_Edge_Model.xlsx
@@ -640,7 +640,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-24T18:03:18+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
+          <t>Generated 2026-08-24T21:57:37+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
         </is>
       </c>
     </row>
@@ -3079,22 +3079,22 @@
       </c>
       <c r="G33" s="23" t="n"/>
       <c r="H33" s="13" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>0.3799494426906008</v>
+        <v>0.383035891688529</v>
       </c>
       <c r="J33" s="15" t="n">
-        <v>0.3363518758085381</v>
+        <v>0.3425247738043947</v>
       </c>
       <c r="K33" s="15" t="n">
-        <v>0.3508771929824561</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="L33" s="14" t="n">
-        <v>0.0290722497081447</v>
+        <v>0.02589303454567188</v>
       </c>
       <c r="M33" s="14" t="n">
-        <v>0.08285591166821238</v>
+        <v>0.07250049672788117</v>
       </c>
       <c r="N33" s="15" t="n">
         <v>0</v>
@@ -4314,12 +4314,12 @@
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D53" s="22" t="n">
@@ -4327,34 +4327,32 @@
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
-          <t>UVA -5.5</t>
-        </is>
-      </c>
-      <c r="G53" s="23" t="n">
-        <v>-5.5</v>
-      </c>
+          <t>UNLV ML</t>
+        </is>
+      </c>
+      <c r="G53" s="23" t="n"/>
       <c r="H53" s="13" t="n">
-        <v>-112</v>
+        <v>-218</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>0.4587103311205297</v>
+        <v>0.616964108311471</v>
       </c>
       <c r="J53" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.6574752261956054</v>
       </c>
       <c r="K53" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.6855345911949685</v>
       </c>
       <c r="L53" s="14" t="n">
-        <v>-0.0695915556719231</v>
+        <v>-0.06857048288349754</v>
       </c>
       <c r="M53" s="14" t="n">
-        <v>-0.1317268732361402</v>
+        <v>-0.1000248328300561</v>
       </c>
       <c r="N53" s="15" t="n">
         <v>0</v>
@@ -4377,12 +4375,12 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D54" s="25" t="n">
@@ -4390,22 +4388,22 @@
       </c>
       <c r="E54" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F54" s="17" t="inlineStr">
         <is>
-          <t>Over 59.5</t>
+          <t>UVA -5.5</t>
         </is>
       </c>
       <c r="G54" s="26" t="n">
-        <v>59.5</v>
+        <v>-5.5</v>
       </c>
       <c r="H54" s="18" t="n">
         <v>-112</v>
       </c>
       <c r="I54" s="20" t="n">
-        <v>0.4586148034139574</v>
+        <v>0.4587103311205297</v>
       </c>
       <c r="J54" s="20" t="n">
         <v>0.5043297540699688</v>
@@ -4414,10 +4412,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L54" s="19" t="n">
-        <v>-0.06968708337849544</v>
+        <v>-0.0695915556719231</v>
       </c>
       <c r="M54" s="19" t="n">
-        <v>-0.1319076935378664</v>
+        <v>-0.1317268732361402</v>
       </c>
       <c r="N54" s="20" t="n">
         <v>0</v>
@@ -4440,12 +4438,12 @@
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D55" s="22" t="n">
@@ -4453,32 +4451,34 @@
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
         <is>
-          <t>UNLV ML</t>
-        </is>
-      </c>
-      <c r="G55" s="23" t="n"/>
+          <t>Over 59.5</t>
+        </is>
+      </c>
+      <c r="G55" s="23" t="n">
+        <v>59.5</v>
+      </c>
       <c r="H55" s="13" t="n">
-        <v>-225</v>
+        <v>-112</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>0.6200505573093992</v>
+        <v>0.4586148034139574</v>
       </c>
       <c r="J55" s="15" t="n">
-        <v>0.6636481241914618</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K55" s="15" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L55" s="14" t="n">
-        <v>-0.07225713499829312</v>
+        <v>-0.06968708337849544</v>
       </c>
       <c r="M55" s="14" t="n">
-        <v>-0.1043714172197567</v>
+        <v>-0.1319076935378664</v>
       </c>
       <c r="N55" s="15" t="n">
         <v>0</v>
@@ -13630,10 +13630,10 @@
         <v>57.5</v>
       </c>
       <c r="K12" s="18" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="L12" s="18" t="n">
-        <v>-225</v>
+        <v>-218</v>
       </c>
       <c r="M12" s="17" t="inlineStr">
         <is>

--- a/NCAAF_Edge_Model.xlsx
+++ b/NCAAF_Edge_Model.xlsx
@@ -271,8 +271,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BoardTable" displayName="BoardTable" ref="A4:Q84" headerRowCount="1">
-  <autoFilter ref="A4:Q84"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BoardTable" displayName="BoardTable" ref="A4:Q124" headerRowCount="1">
+  <autoFilter ref="A4:Q124"/>
   <tableColumns count="17">
     <tableColumn id="1" name="Tier"/>
     <tableColumn id="2" name="Game"/>
@@ -640,7 +640,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-24T21:57:37+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
+          <t>Generated 2026-08-25T05:00:08+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>Settings!B5+SUMIF('Bet Ledger'!$G$6:$G$8,"&lt;&gt;Pending",'Bet Ledger'!$H$6:$H$8)</f>
+        <f>Settings!B5+SUMIF('Bet Ledger'!$G$6:$G$9,"&lt;&gt;Pending",'Bet Ledger'!$H$6:$H$9)</f>
         <v/>
       </c>
     </row>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>SUMIF('Bet Ledger'!$G$6:$G$8,"&lt;&gt;Pending",'Bet Ledger'!$F$6:$F$8)</f>
+        <f>SUMIF('Bet Ledger'!$G$6:$G$9,"&lt;&gt;Pending",'Bet Ledger'!$F$6:$F$9)</f>
         <v/>
       </c>
     </row>
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>SUMIF('Bet Ledger'!$G$6:$G$8,"&lt;&gt;Pending",'Bet Ledger'!$H$6:$H$8)</f>
+        <f>SUMIF('Bet Ledger'!$G$6:$G$9,"&lt;&gt;Pending",'Bet Ledger'!$H$6:$H$9)</f>
         <v/>
       </c>
     </row>
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="B9" s="7">
-        <f>COUNTIFS('Bet Ledger'!$G$6:$G$8,"&lt;&gt;Pending",'Bet Ledger'!$G$6:$G$8,"&lt;&gt;")</f>
+        <f>COUNTIFS('Bet Ledger'!$G$6:$G$9,"&lt;&gt;Pending",'Bet Ledger'!$G$6:$G$9,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>COUNTIF('Bet Ledger'!$G$6:$G$8,"Win")</f>
+        <f>COUNTIF('Bet Ledger'!$G$6:$G$9,"Win")</f>
         <v/>
       </c>
     </row>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>COUNTIF('Bet Ledger'!$G$6:$G$8,"Loss")</f>
+        <f>COUNTIF('Bet Ledger'!$G$6:$G$9,"Loss")</f>
         <v/>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B12" s="7">
-        <f>COUNTIF('Bet Ledger'!$G$6:$G$8,"Push")</f>
+        <f>COUNTIF('Bet Ledger'!$G$6:$G$9,"Push")</f>
         <v/>
       </c>
     </row>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="B14" s="7">
-        <f>COUNTIF('Bet Ledger'!$G$6:$G$8,"Pending")</f>
+        <f>COUNTIF('Bet Ledger'!$G$6:$G$9,"Pending")</f>
         <v/>
       </c>
     </row>
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1040,13 +1040,13 @@
         </is>
       </c>
       <c r="E22" s="18" t="n">
-        <v>-115</v>
+        <v>-112</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>0.08840272575750341</v>
+        <v>0.0917323188370931</v>
       </c>
       <c r="G22" s="20" t="n">
-        <v>0.6232864466877359</v>
+        <v>0.6200342056295459</v>
       </c>
       <c r="H22" s="21" t="n"/>
       <c r="I22" s="17" t="inlineStr">
@@ -1077,18 +1077,55 @@
         </is>
       </c>
       <c r="E23" s="13" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0.08007721496452191</v>
+        <v>0.08386062118588167</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0.5993079841952912</v>
+        <v>0.5960557431371012</v>
       </c>
       <c r="H23" s="16" t="n"/>
       <c r="I23" s="12" t="inlineStr">
         <is>
           <t>2026-08-29 16:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>LEAN</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>COLO @ GT</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>Over 50.5</t>
+        </is>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>-115</v>
+      </c>
+      <c r="F24" s="19" t="n">
+        <v>0.07840427762989666</v>
+      </c>
+      <c r="G24" s="20" t="n">
+        <v>0.6132879985601292</v>
+      </c>
+      <c r="H24" s="21" t="n"/>
+      <c r="I24" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q84"/>
+  <dimension ref="A1:Q124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1320,22 +1357,22 @@
         <v>48.5</v>
       </c>
       <c r="H6" s="18" t="n">
-        <v>-115</v>
+        <v>-112</v>
       </c>
       <c r="I6" s="20" t="n">
-        <v>0.6232864466877359</v>
+        <v>0.6200342056295459</v>
       </c>
       <c r="J6" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K6" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L6" s="19" t="n">
-        <v>0.08840272575750341</v>
+        <v>0.0917323188370931</v>
       </c>
       <c r="M6" s="19" t="n">
-        <v>0.1652746611988105</v>
+        <v>0.1736361749416404</v>
       </c>
       <c r="N6" s="20" t="n">
         <v>0</v>
@@ -1383,22 +1420,22 @@
         <v>-7.5</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>0.5993079841952912</v>
+        <v>0.5960557431371012</v>
       </c>
       <c r="J7" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K7" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L7" s="14" t="n">
-        <v>0.08007721496452191</v>
+        <v>0.08386062118588167</v>
       </c>
       <c r="M7" s="14" t="n">
-        <v>0.1542227843761165</v>
+        <v>0.1637278794581499</v>
       </c>
       <c r="N7" s="15" t="n">
         <v>0</v>
@@ -1416,17 +1453,17 @@
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>BCU @ UCF</t>
+          <t>COLO @ GT</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D8" s="25" t="n">
@@ -1434,34 +1471,34 @@
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t>BCU +42.5</t>
+          <t>Over 50.5</t>
         </is>
       </c>
       <c r="G8" s="26" t="n">
-        <v>-42.5</v>
+        <v>50.5</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>-112</v>
+        <v>-115</v>
       </c>
       <c r="I8" s="20" t="n">
-        <v>0.7517481901856816</v>
+        <v>0.6132879985601292</v>
       </c>
       <c r="J8" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K8" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L8" s="19" t="n">
-        <v>0.2234463033932288</v>
+        <v>0.07840427762989666</v>
       </c>
       <c r="M8" s="19" t="n">
-        <v>0.4229519314228973</v>
+        <v>0.1465819103515458</v>
       </c>
       <c r="N8" s="20" t="n">
         <v>0</v>
@@ -1474,11 +1511,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q8" s="17" t="inlineStr">
-        <is>
-          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q8" s="17" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
@@ -1488,12 +1521,12 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>MRMK @ DEL</t>
+          <t>EIU @ MINN</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D9" s="22" t="n">
@@ -1506,17 +1539,17 @@
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>MRMK +28.5</t>
+          <t>EIU +43.5</t>
         </is>
       </c>
       <c r="G9" s="23" t="n">
-        <v>-28.5</v>
+        <v>-43.5</v>
       </c>
       <c r="H9" s="13" t="n">
         <v>-108</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>0.7386849373798826</v>
+        <v>0.7474934197068306</v>
       </c>
       <c r="J9" s="15" t="n">
         <v>0.4956702459300312</v>
@@ -1525,10 +1558,10 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L9" s="14" t="n">
-        <v>0.2194541681491133</v>
+        <v>0.2282626504760613</v>
       </c>
       <c r="M9" s="14" t="n">
-        <v>0.4226524719908851</v>
+        <v>0.4396169564724145</v>
       </c>
       <c r="N9" s="15" t="n">
         <v>0</v>
@@ -1543,7 +1576,7 @@
       </c>
       <c r="Q9" s="12" t="inlineStr">
         <is>
-          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -1555,12 +1588,12 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>MASS @ RUTG</t>
+          <t>INST @ PUR</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 22:00</t>
+          <t>2026-09-04 23:00</t>
         </is>
       </c>
       <c r="D10" s="25" t="n">
@@ -1573,17 +1606,17 @@
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t>MASS +30.5</t>
+          <t>INST +35.5</t>
         </is>
       </c>
       <c r="G10" s="26" t="n">
-        <v>-30.5</v>
+        <v>-35.5</v>
       </c>
       <c r="H10" s="18" t="n">
         <v>-108</v>
       </c>
       <c r="I10" s="20" t="n">
-        <v>0.7362293114467701</v>
+        <v>0.7460391470401289</v>
       </c>
       <c r="J10" s="20" t="n">
         <v>0.4956702459300312</v>
@@ -1592,10 +1625,10 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L10" s="19" t="n">
-        <v>0.2169985422160008</v>
+        <v>0.2268083778093596</v>
       </c>
       <c r="M10" s="19" t="n">
-        <v>0.4179231183419276</v>
+        <v>0.4368161350402483</v>
       </c>
       <c r="N10" s="20" t="n">
         <v>0</v>
@@ -1610,7 +1643,7 @@
       </c>
       <c r="Q10" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>INST isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -1622,12 +1655,12 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>NMSU @ FSU</t>
+          <t>UAPB @ MIZ</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D11" s="22" t="n">
@@ -1640,29 +1673,29 @@
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>NMSU +31.5</t>
+          <t>UAPB +54.5</t>
         </is>
       </c>
       <c r="G11" s="23" t="n">
-        <v>-31.5</v>
+        <v>-54.5</v>
       </c>
       <c r="H11" s="13" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>0.7484052544756881</v>
+        <v>0.749981952327064</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L11" s="14" t="n">
-        <v>0.2135215335454556</v>
+        <v>0.2261724285175402</v>
       </c>
       <c r="M11" s="14" t="n">
-        <v>0.3991924322806341</v>
+        <v>0.4317837271698495</v>
       </c>
       <c r="N11" s="15" t="n">
         <v>0</v>
@@ -1677,7 +1710,7 @@
       </c>
       <c r="Q11" s="12" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>UAPB isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -1689,12 +1722,12 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>BCU @ UCF</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D12" s="25" t="n">
@@ -1707,29 +1740,29 @@
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>SJSU +38.5</t>
+          <t>BCU +42.5</t>
         </is>
       </c>
       <c r="G12" s="26" t="n">
-        <v>-38.5</v>
+        <v>-42.5</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>-120</v>
+        <v>-112</v>
       </c>
       <c r="I12" s="20" t="n">
-        <v>0.7585484812661867</v>
+        <v>0.7517481901856816</v>
       </c>
       <c r="J12" s="20" t="n">
-        <v>0.5217391304347826</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K12" s="20" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L12" s="19" t="n">
-        <v>0.2130939358116413</v>
+        <v>0.2234463033932288</v>
       </c>
       <c r="M12" s="19" t="n">
-        <v>0.3906722156546757</v>
+        <v>0.4229519314228973</v>
       </c>
       <c r="N12" s="20" t="n">
         <v>0</v>
@@ -1744,7 +1777,7 @@
       </c>
       <c r="Q12" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -1756,12 +1789,12 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>ALB @ BUFF</t>
+          <t>IDHO @ UTAH</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D13" s="22" t="n">
@@ -1774,29 +1807,29 @@
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>ALB +24.5</t>
+          <t>IDHO +33.5</t>
         </is>
       </c>
       <c r="G13" s="23" t="n">
-        <v>-24.5</v>
+        <v>-33.5</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>0.7342550223888921</v>
+        <v>0.7414791527526444</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L13" s="14" t="n">
-        <v>0.2059531355964392</v>
+        <v>0.2222483835218751</v>
       </c>
       <c r="M13" s="14" t="n">
-        <v>0.3898398638075457</v>
+        <v>0.4280339238199079</v>
       </c>
       <c r="N13" s="15" t="n">
         <v>0</v>
@@ -1811,7 +1844,7 @@
       </c>
       <c r="Q13" s="12" t="inlineStr">
         <is>
-          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -1823,12 +1856,12 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>MRMK @ DEL</t>
+          <t>NCAT @ GAST</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-04 23:00</t>
         </is>
       </c>
       <c r="D14" s="25" t="n">
@@ -1836,32 +1869,34 @@
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t>MRMK ML</t>
-        </is>
-      </c>
-      <c r="G14" s="26" t="n"/>
+          <t>NCAT +28.5</t>
+        </is>
+      </c>
+      <c r="G14" s="26" t="n">
+        <v>-28.5</v>
+      </c>
       <c r="H14" s="18" t="n">
-        <v>3000</v>
+        <v>-108</v>
       </c>
       <c r="I14" s="20" t="n">
-        <v>0.2342202661742625</v>
+        <v>0.7409568774443602</v>
       </c>
       <c r="J14" s="20" t="n">
-        <v>0.03155263980006248</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K14" s="20" t="n">
-        <v>0.03225806451612903</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L14" s="19" t="n">
-        <v>0.2019622016581335</v>
+        <v>0.221726108213591</v>
       </c>
       <c r="M14" s="19" t="n">
-        <v>6.260828251402137</v>
+        <v>0.4270280602632124</v>
       </c>
       <c r="N14" s="20" t="n">
         <v>0</v>
@@ -1876,7 +1911,7 @@
       </c>
       <c r="Q14" s="17" t="inlineStr">
         <is>
-          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1923,7 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>AKR @ WAKE</t>
+          <t>MRMK @ DEL</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -1906,17 +1941,17 @@
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>AKR +23.5</t>
+          <t>MRMK +28.5</t>
         </is>
       </c>
       <c r="G15" s="23" t="n">
-        <v>-23.5</v>
+        <v>-28.5</v>
       </c>
       <c r="H15" s="13" t="n">
         <v>-108</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>0.7202139758215249</v>
+        <v>0.7386849373798826</v>
       </c>
       <c r="J15" s="15" t="n">
         <v>0.4956702459300312</v>
@@ -1925,10 +1960,10 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L15" s="14" t="n">
-        <v>0.2009832065907556</v>
+        <v>0.2194541681491133</v>
       </c>
       <c r="M15" s="14" t="n">
-        <v>0.3870787682488629</v>
+        <v>0.4226524719908851</v>
       </c>
       <c r="N15" s="15" t="n">
         <v>0</v>
@@ -1943,7 +1978,7 @@
       </c>
       <c r="Q15" s="12" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -1955,12 +1990,12 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>ALB @ BUFF</t>
+          <t>MASS @ RUTG</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-03 22:00</t>
         </is>
       </c>
       <c r="D16" s="25" t="n">
@@ -1968,32 +2003,34 @@
       </c>
       <c r="E16" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
-          <t>ALB ML</t>
-        </is>
-      </c>
-      <c r="G16" s="26" t="n"/>
+          <t>MASS +30.5</t>
+        </is>
+      </c>
+      <c r="G16" s="26" t="n">
+        <v>-30.5</v>
+      </c>
       <c r="H16" s="18" t="n">
-        <v>2200</v>
+        <v>-108</v>
       </c>
       <c r="I16" s="20" t="n">
-        <v>0.2400960739565308</v>
+        <v>0.7362293114467701</v>
       </c>
       <c r="J16" s="20" t="n">
-        <v>0.04216553878188443</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K16" s="20" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L16" s="19" t="n">
-        <v>0.1966178130869655</v>
+        <v>0.2169985422160008</v>
       </c>
       <c r="M16" s="19" t="n">
-        <v>4.522209701000207</v>
+        <v>0.4179231183419276</v>
       </c>
       <c r="N16" s="20" t="n">
         <v>0</v>
@@ -2008,7 +2045,7 @@
       </c>
       <c r="Q16" s="17" t="inlineStr">
         <is>
-          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -2020,12 +2057,12 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>WES @ KENN</t>
+          <t>NMSU @ FSU</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D17" s="22" t="n">
@@ -2038,17 +2075,17 @@
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>WES +22.5</t>
+          <t>NMSU +31.5</t>
         </is>
       </c>
       <c r="G17" s="23" t="n">
-        <v>-22.5</v>
+        <v>-31.5</v>
       </c>
       <c r="H17" s="13" t="n">
         <v>-115</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>0.7273466517420963</v>
+        <v>0.7484052544756881</v>
       </c>
       <c r="J17" s="15" t="n">
         <v>0.5108342361863488</v>
@@ -2057,16 +2094,16 @@
         <v>0.5348837209302325</v>
       </c>
       <c r="L17" s="14" t="n">
-        <v>0.1924629308118638</v>
+        <v>0.2135215335454556</v>
       </c>
       <c r="M17" s="14" t="n">
-        <v>0.3598220010830496</v>
+        <v>0.3991924322806341</v>
       </c>
       <c r="N17" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O17" s="24" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="P17" s="12" t="inlineStr">
         <is>
@@ -2075,7 +2112,7 @@
       </c>
       <c r="Q17" s="12" t="inlineStr">
         <is>
-          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -2087,12 +2124,12 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>WES @ KENN</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D18" s="25" t="n">
@@ -2100,38 +2137,40 @@
       </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>WES ML</t>
-        </is>
-      </c>
-      <c r="G18" s="26" t="n"/>
+          <t>SJSU +38.5</t>
+        </is>
+      </c>
+      <c r="G18" s="26" t="n">
+        <v>-38.5</v>
+      </c>
       <c r="H18" s="18" t="n">
-        <v>1500</v>
+        <v>-120</v>
       </c>
       <c r="I18" s="20" t="n">
-        <v>0.2370117476831352</v>
+        <v>0.7585484812661867</v>
       </c>
       <c r="J18" s="20" t="n">
-        <v>0.06035889070146819</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="K18" s="20" t="n">
-        <v>0.0625</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="L18" s="19" t="n">
-        <v>0.1745117476831352</v>
+        <v>0.2130939358116413</v>
       </c>
       <c r="M18" s="19" t="n">
-        <v>2.792187962930162</v>
+        <v>0.3906722156546757</v>
       </c>
       <c r="N18" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="27" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="P18" s="17" t="inlineStr">
         <is>
@@ -2140,7 +2179,7 @@
       </c>
       <c r="Q18" s="17" t="inlineStr">
         <is>
-          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -2152,12 +2191,12 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>NMSU @ FSU</t>
+          <t>NCAT @ GAST</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-04 23:00</t>
         </is>
       </c>
       <c r="D19" s="22" t="n">
@@ -2170,27 +2209,27 @@
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>NMSU ML</t>
+          <t>NCAT ML</t>
         </is>
       </c>
       <c r="G19" s="23" t="n"/>
       <c r="H19" s="13" t="n">
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>0.2189772153156186</v>
+        <v>0.2655422309319856</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>0.0461215932914046</v>
+        <v>0.05094905094905094</v>
       </c>
       <c r="K19" s="15" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L19" s="14" t="n">
-        <v>0.171358167696571</v>
+        <v>0.2129106519846172</v>
       </c>
       <c r="M19" s="14" t="n">
-        <v>3.598521521627991</v>
+        <v>4.045302387707726</v>
       </c>
       <c r="N19" s="15" t="n">
         <v>0</v>
@@ -2205,7 +2244,7 @@
       </c>
       <c r="Q19" s="12" t="inlineStr">
         <is>
-          <t>price outside allowed range</t>
+          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2256,7 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>AKR @ WAKE</t>
+          <t>ALB @ BUFF</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
@@ -2230,32 +2269,34 @@
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F20" s="17" t="inlineStr">
         <is>
-          <t>AKR ML</t>
-        </is>
-      </c>
-      <c r="G20" s="26" t="n"/>
+          <t>ALB +24.5</t>
+        </is>
+      </c>
+      <c r="G20" s="26" t="n">
+        <v>-24.5</v>
+      </c>
       <c r="H20" s="18" t="n">
-        <v>1300</v>
+        <v>-112</v>
       </c>
       <c r="I20" s="20" t="n">
-        <v>0.2310535567636653</v>
+        <v>0.7342550223888921</v>
       </c>
       <c r="J20" s="20" t="n">
-        <v>0.06888361045130641</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K20" s="20" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L20" s="19" t="n">
-        <v>0.1596249853350939</v>
+        <v>0.2059531355964392</v>
       </c>
       <c r="M20" s="19" t="n">
-        <v>2.234749794691315</v>
+        <v>0.3898398638075457</v>
       </c>
       <c r="N20" s="20" t="n">
         <v>0</v>
@@ -2270,7 +2311,7 @@
       </c>
       <c r="Q20" s="17" t="inlineStr">
         <is>
-          <t>price outside allowed range</t>
+          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -2282,12 +2323,12 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>MASS @ RUTG</t>
+          <t>UAB @ ILL</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 22:00</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D21" s="22" t="n">
@@ -2295,32 +2336,34 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>MASS ML</t>
-        </is>
-      </c>
-      <c r="G21" s="23" t="n"/>
+          <t>UAB +28.5</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="n">
+        <v>-28.5</v>
+      </c>
       <c r="H21" s="13" t="n">
-        <v>2000</v>
+        <v>-118</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>0.1963076315941712</v>
+        <v>0.7438096015477024</v>
       </c>
       <c r="J21" s="15" t="n">
-        <v>0.0461215932914046</v>
+        <v>0.5173641257162701</v>
       </c>
       <c r="K21" s="15" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.5412844036697247</v>
       </c>
       <c r="L21" s="14" t="n">
-        <v>0.1486885839751236</v>
+        <v>0.2025251978779776</v>
       </c>
       <c r="M21" s="14" t="n">
-        <v>3.122460263477595</v>
+        <v>0.3741567215033823</v>
       </c>
       <c r="N21" s="15" t="n">
         <v>0</v>
@@ -2335,7 +2378,7 @@
       </c>
       <c r="Q21" s="12" t="inlineStr">
         <is>
-          <t>price outside allowed range</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -2347,12 +2390,12 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>JVST @ NDSU</t>
+          <t>MRMK @ DEL</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D22" s="25" t="n">
@@ -2360,34 +2403,32 @@
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F22" s="17" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
-        </is>
-      </c>
-      <c r="G22" s="26" t="n">
-        <v>46.5</v>
-      </c>
+          <t>MRMK ML</t>
+        </is>
+      </c>
+      <c r="G22" s="26" t="n"/>
       <c r="H22" s="18" t="n">
-        <v>-112</v>
+        <v>3000</v>
       </c>
       <c r="I22" s="20" t="n">
-        <v>0.6574997451163023</v>
+        <v>0.2342202661742625</v>
       </c>
       <c r="J22" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.03155263980006248</v>
       </c>
       <c r="K22" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="L22" s="19" t="n">
-        <v>0.1291978583238494</v>
+        <v>0.2019622016581335</v>
       </c>
       <c r="M22" s="19" t="n">
-        <v>0.2445530889701435</v>
+        <v>6.260828251402137</v>
       </c>
       <c r="N22" s="20" t="n">
         <v>0</v>
@@ -2402,7 +2443,7 @@
       </c>
       <c r="Q22" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -2414,12 +2455,12 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>SAC @ EMU</t>
+          <t>AKR @ WAKE</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 22:30</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D23" s="22" t="n">
@@ -2432,29 +2473,29 @@
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>SAC +9.5</t>
+          <t>AKR +23.5</t>
         </is>
       </c>
       <c r="G23" s="23" t="n">
-        <v>-9.5</v>
+        <v>-23.5</v>
       </c>
       <c r="H23" s="13" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>0.6373042089106218</v>
+        <v>0.7202139758215249</v>
       </c>
       <c r="J23" s="15" t="n">
-        <v>0.5</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K23" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L23" s="14" t="n">
-        <v>0.1134946851010979</v>
+        <v>0.2009832065907556</v>
       </c>
       <c r="M23" s="14" t="n">
-        <v>0.2166716715566417</v>
+        <v>0.3870787682488629</v>
       </c>
       <c r="N23" s="15" t="n">
         <v>0</v>
@@ -2494,34 +2535,32 @@
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
-        </is>
-      </c>
-      <c r="G24" s="26" t="n">
-        <v>48.5</v>
-      </c>
+          <t>ALB ML</t>
+        </is>
+      </c>
+      <c r="G24" s="26" t="n"/>
       <c r="H24" s="18" t="n">
-        <v>-105</v>
+        <v>2200</v>
       </c>
       <c r="I24" s="20" t="n">
-        <v>0.6205016550348365</v>
+        <v>0.2400960739565308</v>
       </c>
       <c r="J24" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.04216553878188443</v>
       </c>
       <c r="K24" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="L24" s="19" t="n">
-        <v>0.1083065330836169</v>
+        <v>0.1966178130869655</v>
       </c>
       <c r="M24" s="19" t="n">
-        <v>0.2114556122108712</v>
+        <v>4.522209701000207</v>
       </c>
       <c r="N24" s="20" t="n">
         <v>0</v>
@@ -2561,34 +2600,34 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>WES +22.5</t>
         </is>
       </c>
       <c r="G25" s="23" t="n">
-        <v>51.5</v>
+        <v>-22.5</v>
       </c>
       <c r="H25" s="13" t="n">
-        <v>-108</v>
+        <v>-115</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>0.5971070144741464</v>
+        <v>0.7273466517420963</v>
       </c>
       <c r="J25" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K25" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L25" s="14" t="n">
-        <v>0.07787624524337711</v>
+        <v>0.1924629308118638</v>
       </c>
       <c r="M25" s="14" t="n">
-        <v>0.1499838797279857</v>
+        <v>0.3598220010830496</v>
       </c>
       <c r="N25" s="15" t="n">
         <v>0</v>
@@ -2615,12 +2654,12 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>SAC @ EMU</t>
+          <t>WES @ KENN</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 22:30</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D26" s="25" t="n">
@@ -2628,47 +2667,49 @@
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>Over 52.5</t>
-        </is>
-      </c>
-      <c r="G26" s="26" t="n">
-        <v>52.5</v>
-      </c>
+          <t>WES ML</t>
+        </is>
+      </c>
+      <c r="G26" s="26" t="n"/>
       <c r="H26" s="18" t="n">
-        <v>-108</v>
+        <v>1500</v>
       </c>
       <c r="I26" s="20" t="n">
-        <v>0.595359506876733</v>
+        <v>0.2370117476831352</v>
       </c>
       <c r="J26" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.06035889070146819</v>
       </c>
       <c r="K26" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.0625</v>
       </c>
       <c r="L26" s="19" t="n">
-        <v>0.07612873764596373</v>
+        <v>0.1745117476831352</v>
       </c>
       <c r="M26" s="19" t="n">
-        <v>0.1466183095403747</v>
+        <v>2.792187962930162</v>
       </c>
       <c r="N26" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O26" s="27" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="P26" s="17" t="inlineStr">
         <is>
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q26" s="17" t="n"/>
+      <c r="Q26" s="17" t="inlineStr">
+        <is>
+          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
@@ -2678,12 +2719,12 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>AKR @ WAKE</t>
+          <t>NMSU @ FSU</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D27" s="22" t="n">
@@ -2691,34 +2732,32 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
-        </is>
-      </c>
-      <c r="G27" s="23" t="n">
-        <v>49.5</v>
-      </c>
+          <t>NMSU ML</t>
+        </is>
+      </c>
+      <c r="G27" s="23" t="n"/>
       <c r="H27" s="13" t="n">
-        <v>-112</v>
+        <v>2000</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>0.603175208172005</v>
+        <v>0.2189772153156186</v>
       </c>
       <c r="J27" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.0461215932914046</v>
       </c>
       <c r="K27" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.04761904761904762</v>
       </c>
       <c r="L27" s="14" t="n">
-        <v>0.07487332137955216</v>
+        <v>0.171358167696571</v>
       </c>
       <c r="M27" s="14" t="n">
-        <v>0.1417245011827237</v>
+        <v>3.598521521627991</v>
       </c>
       <c r="N27" s="15" t="n">
         <v>0</v>
@@ -2731,7 +2770,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q27" s="12" t="n"/>
+      <c r="Q27" s="12" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="17" t="inlineStr">
@@ -2741,12 +2784,12 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>UAB @ ILL</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D28" s="25" t="n">
@@ -2759,27 +2802,27 @@
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>UNC ML</t>
+          <t>UAB ML</t>
         </is>
       </c>
       <c r="G28" s="26" t="n"/>
       <c r="H28" s="18" t="n">
-        <v>240</v>
+        <v>3000</v>
       </c>
       <c r="I28" s="20" t="n">
-        <v>0.3660199960886052</v>
+        <v>0.1964375380312305</v>
       </c>
       <c r="J28" s="20" t="n">
-        <v>0.2820294784580499</v>
+        <v>0.03155263980006248</v>
       </c>
       <c r="K28" s="20" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="L28" s="19" t="n">
-        <v>0.07190234902978171</v>
+        <v>0.1641794735151015</v>
       </c>
       <c r="M28" s="19" t="n">
-        <v>0.2444679867012578</v>
+        <v>5.089563678968147</v>
       </c>
       <c r="N28" s="20" t="n">
         <v>0</v>
@@ -2792,7 +2835,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q28" s="17" t="n"/>
+      <c r="Q28" s="17" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
@@ -2802,7 +2849,7 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>BCU @ UCF</t>
+          <t>AKR @ WAKE</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
@@ -2815,34 +2862,32 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>Under 59.5</t>
-        </is>
-      </c>
-      <c r="G29" s="23" t="n">
-        <v>59.5</v>
-      </c>
+          <t>AKR ML</t>
+        </is>
+      </c>
+      <c r="G29" s="23" t="n"/>
       <c r="H29" s="13" t="n">
-        <v>-108</v>
+        <v>1300</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>0.5828840668418837</v>
+        <v>0.2310535567636653</v>
       </c>
       <c r="J29" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.06888361045130641</v>
       </c>
       <c r="K29" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="L29" s="14" t="n">
-        <v>0.06365329761111438</v>
+        <v>0.1596249853350939</v>
       </c>
       <c r="M29" s="14" t="n">
-        <v>0.1225915361399241</v>
+        <v>2.234749794691315</v>
       </c>
       <c r="N29" s="15" t="n">
         <v>0</v>
@@ -2857,7 +2902,7 @@
       </c>
       <c r="Q29" s="12" t="inlineStr">
         <is>
-          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>price outside allowed range</t>
         </is>
       </c>
     </row>
@@ -2869,12 +2914,12 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>HAW @ STAN</t>
+          <t>IDHO @ UTAH</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D30" s="25" t="n">
@@ -2887,27 +2932,27 @@
       </c>
       <c r="F30" s="17" t="inlineStr">
         <is>
-          <t>HAW ML</t>
+          <t>IDHO ML</t>
         </is>
       </c>
       <c r="G30" s="26" t="n"/>
       <c r="H30" s="18" t="n">
-        <v>180</v>
+        <v>3000</v>
       </c>
       <c r="I30" s="20" t="n">
-        <v>0.414495505906456</v>
+        <v>0.1915726544041398</v>
       </c>
       <c r="J30" s="20" t="n">
-        <v>0.3425247738043947</v>
+        <v>0.03155263980006248</v>
       </c>
       <c r="K30" s="20" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>0.05735264876359886</v>
+        <v>0.1593145898880108</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>0.1605874165380767</v>
+        <v>4.938752286528335</v>
       </c>
       <c r="N30" s="20" t="n">
         <v>0</v>
@@ -2920,7 +2965,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q30" s="17" t="n"/>
+      <c r="Q30" s="17" t="inlineStr">
+        <is>
+          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
@@ -2930,12 +2979,12 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>HAW @ STAN</t>
+          <t>MASS @ RUTG</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-03 22:00</t>
         </is>
       </c>
       <c r="D31" s="22" t="n">
@@ -2943,34 +2992,32 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>HAW +5.5</t>
-        </is>
-      </c>
-      <c r="G31" s="23" t="n">
-        <v>-5.5</v>
-      </c>
+          <t>MASS ML</t>
+        </is>
+      </c>
+      <c r="G31" s="23" t="n"/>
       <c r="H31" s="13" t="n">
-        <v>-112</v>
+        <v>2000</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>0.5838108250777737</v>
+        <v>0.1963076315941712</v>
       </c>
       <c r="J31" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.0461215932914046</v>
       </c>
       <c r="K31" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.04761904761904762</v>
       </c>
       <c r="L31" s="14" t="n">
-        <v>0.05550893828532089</v>
+        <v>0.1486885839751236</v>
       </c>
       <c r="M31" s="14" t="n">
-        <v>0.1050704903257859</v>
+        <v>3.122460263477595</v>
       </c>
       <c r="N31" s="15" t="n">
         <v>0</v>
@@ -2983,7 +3030,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q31" s="12" t="n"/>
+      <c r="Q31" s="12" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
@@ -2993,12 +3044,12 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>MASS @ RUTG</t>
+          <t>JVST @ NDSU</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 22:00</t>
+          <t>2026-08-29 21:30</t>
         </is>
       </c>
       <c r="D32" s="25" t="n">
@@ -3011,29 +3062,29 @@
       </c>
       <c r="F32" s="17" t="inlineStr">
         <is>
-          <t>Over 53.5</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="G32" s="26" t="n">
-        <v>53.5</v>
+        <v>46.5</v>
       </c>
       <c r="H32" s="18" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="I32" s="20" t="n">
-        <v>0.5740430549239717</v>
+        <v>0.6574997451163023</v>
       </c>
       <c r="J32" s="20" t="n">
-        <v>0.5</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K32" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L32" s="19" t="n">
-        <v>0.05023353111444784</v>
+        <v>0.1291978583238494</v>
       </c>
       <c r="M32" s="19" t="n">
-        <v>0.09590037758212777</v>
+        <v>0.2445530889701435</v>
       </c>
       <c r="N32" s="20" t="n">
         <v>0</v>
@@ -3046,7 +3097,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q32" s="17" t="n"/>
+      <c r="Q32" s="17" t="inlineStr">
+        <is>
+          <t>raw model/market disagreement exceeds the safety limit</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
@@ -3056,12 +3111,12 @@
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>SAC @ EMU</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-08-29 22:30</t>
         </is>
       </c>
       <c r="D33" s="22" t="n">
@@ -3069,32 +3124,34 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>MEM ML</t>
-        </is>
-      </c>
-      <c r="G33" s="23" t="n"/>
+          <t>SAC +9.5</t>
+        </is>
+      </c>
+      <c r="G33" s="23" t="n">
+        <v>-9.5</v>
+      </c>
       <c r="H33" s="13" t="n">
-        <v>180</v>
+        <v>-105</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>0.383035891688529</v>
+        <v>0.6318870908174474</v>
       </c>
       <c r="J33" s="15" t="n">
-        <v>0.3425247738043947</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K33" s="15" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L33" s="14" t="n">
-        <v>0.02589303454567188</v>
+        <v>0.1196919688662279</v>
       </c>
       <c r="M33" s="14" t="n">
-        <v>0.07250049672788117</v>
+        <v>0.2336843201673974</v>
       </c>
       <c r="N33" s="15" t="n">
         <v>0</v>
@@ -3107,7 +3164,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q33" s="12" t="n"/>
+      <c r="Q33" s="12" t="inlineStr">
+        <is>
+          <t>raw model/market disagreement exceeds the safety limit</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="17" t="inlineStr">
@@ -3117,12 +3178,12 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>ALB @ BUFF</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D34" s="25" t="n">
@@ -3130,34 +3191,34 @@
       </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F34" s="17" t="inlineStr">
         <is>
-          <t>MEM +5.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="G34" s="26" t="n">
-        <v>-5.5</v>
+        <v>48.5</v>
       </c>
       <c r="H34" s="18" t="n">
-        <v>-112</v>
+        <v>-105</v>
       </c>
       <c r="I34" s="20" t="n">
-        <v>0.5540130817463144</v>
+        <v>0.6205016550348365</v>
       </c>
       <c r="J34" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K34" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L34" s="19" t="n">
-        <v>0.02571119495386154</v>
+        <v>0.1083065330836169</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>0.04866761901980932</v>
+        <v>0.2114556122108712</v>
       </c>
       <c r="N34" s="20" t="n">
         <v>0</v>
@@ -3170,7 +3231,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q34" s="17" t="n"/>
+      <c r="Q34" s="17" t="inlineStr">
+        <is>
+          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
@@ -3180,12 +3245,12 @@
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>NCAT @ GAST</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-09-04 23:00</t>
         </is>
       </c>
       <c r="D35" s="22" t="n">
@@ -3198,29 +3263,29 @@
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>Under 59.5</t>
+          <t>Under 63.5</t>
         </is>
       </c>
       <c r="G35" s="23" t="n">
-        <v>59.5</v>
+        <v>63.5</v>
       </c>
       <c r="H35" s="13" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>0.5413851965860426</v>
+        <v>0.6117269964441806</v>
       </c>
       <c r="J35" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K35" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L35" s="14" t="n">
-        <v>0.02215442735527329</v>
+        <v>0.08342510965172778</v>
       </c>
       <c r="M35" s="14" t="n">
-        <v>0.04266778601756349</v>
+        <v>0.1579118146979133</v>
       </c>
       <c r="N35" s="15" t="n">
         <v>0</v>
@@ -3233,7 +3298,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q35" s="12" t="n"/>
+      <c r="Q35" s="12" t="inlineStr">
+        <is>
+          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="17" t="inlineStr">
@@ -3243,12 +3312,12 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>UAPB @ MIZ</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D36" s="25" t="n">
@@ -3256,22 +3325,22 @@
       </c>
       <c r="E36" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F36" s="17" t="inlineStr">
         <is>
-          <t>NCSU +5.5</t>
+          <t>Under 60.5</t>
         </is>
       </c>
       <c r="G36" s="26" t="n">
-        <v>-5.5</v>
+        <v>60.5</v>
       </c>
       <c r="H36" s="18" t="n">
         <v>-108</v>
       </c>
       <c r="I36" s="20" t="n">
-        <v>0.5412896688794703</v>
+        <v>0.6022946041225494</v>
       </c>
       <c r="J36" s="20" t="n">
         <v>0.4956702459300312</v>
@@ -3280,10 +3349,10 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L36" s="19" t="n">
-        <v>0.022058899648701</v>
+        <v>0.08306383489178015</v>
       </c>
       <c r="M36" s="19" t="n">
-        <v>0.04248380673083174</v>
+        <v>0.15997479312491</v>
       </c>
       <c r="N36" s="20" t="n">
         <v>0</v>
@@ -3296,7 +3365,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q36" s="17" t="n"/>
+      <c r="Q36" s="17" t="inlineStr">
+        <is>
+          <t>UAPB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
@@ -3306,12 +3379,12 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>SAC @ EMU</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-08-29 22:30</t>
         </is>
       </c>
       <c r="D37" s="22" t="n">
@@ -3319,32 +3392,34 @@
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>NCSU ML</t>
-        </is>
-      </c>
-      <c r="G37" s="23" t="n"/>
+          <t>Over 52.5</t>
+        </is>
+      </c>
+      <c r="G37" s="23" t="n">
+        <v>52.5</v>
+      </c>
       <c r="H37" s="13" t="n">
-        <v>180</v>
+        <v>-105</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>0.3745807138274095</v>
+        <v>0.592107265818543</v>
       </c>
       <c r="J37" s="15" t="n">
-        <v>0.3425247738043947</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K37" s="15" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L37" s="14" t="n">
-        <v>0.01743785668455239</v>
+        <v>0.07991214386732348</v>
       </c>
       <c r="M37" s="14" t="n">
-        <v>0.04882599871674664</v>
+        <v>0.1560189475504887</v>
       </c>
       <c r="N37" s="15" t="n">
         <v>0</v>
@@ -3357,7 +3432,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q37" s="12" t="n"/>
+      <c r="Q37" s="12" t="inlineStr">
+        <is>
+          <t>correlated with a stronger play on the same game</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="17" t="inlineStr">
@@ -3367,7 +3446,7 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>MRMK @ DEL</t>
+          <t>WES @ KENN</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
@@ -3385,35 +3464,35 @@
       </c>
       <c r="F38" s="17" t="inlineStr">
         <is>
-          <t>Over 55.5</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="G38" s="26" t="n">
-        <v>55.5</v>
+        <v>51.5</v>
       </c>
       <c r="H38" s="18" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="I38" s="20" t="n">
-        <v>0.5437650474945759</v>
+        <v>0.5971070144741464</v>
       </c>
       <c r="J38" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K38" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>0.01546316070212306</v>
+        <v>0.07787624524337711</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>0.02926955418616145</v>
+        <v>0.1499838797279857</v>
       </c>
       <c r="N38" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O38" s="27" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="P38" s="17" t="inlineStr">
         <is>
@@ -3422,7 +3501,7 @@
       </c>
       <c r="Q38" s="17" t="inlineStr">
         <is>
-          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -3434,12 +3513,12 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>JVST @ NDSU</t>
+          <t>AKR @ WAKE</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D39" s="22" t="n">
@@ -3447,37 +3526,37 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>JVST +7</t>
+          <t>Over 49.5</t>
         </is>
       </c>
       <c r="G39" s="23" t="n">
-        <v>-7</v>
+        <v>49.5</v>
       </c>
       <c r="H39" s="13" t="n">
-        <v>-115</v>
+        <v>-112</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>0.5499855318495314</v>
+        <v>0.603175208172005</v>
       </c>
       <c r="J39" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K39" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L39" s="14" t="n">
-        <v>0.01510181091929885</v>
+        <v>0.07487332137955216</v>
       </c>
       <c r="M39" s="14" t="n">
-        <v>0.02680803788623665</v>
+        <v>0.1417245011827237</v>
       </c>
       <c r="N39" s="15" t="n">
-        <v>0.0505</v>
+        <v>0</v>
       </c>
       <c r="O39" s="24" t="n">
         <v>0.45</v>
@@ -3510,34 +3589,32 @@
       </c>
       <c r="E40" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F40" s="17" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
-        </is>
-      </c>
-      <c r="G40" s="26" t="n">
-        <v>47.5</v>
-      </c>
+          <t>UNC ML</t>
+        </is>
+      </c>
+      <c r="G40" s="26" t="n"/>
       <c r="H40" s="18" t="n">
-        <v>-112</v>
+        <v>240</v>
       </c>
       <c r="I40" s="20" t="n">
-        <v>0.5398532027364953</v>
+        <v>0.3660199960886052</v>
       </c>
       <c r="J40" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.2820294784580499</v>
       </c>
       <c r="K40" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="L40" s="19" t="n">
-        <v>0.01155131594404246</v>
+        <v>0.07190234902978171</v>
       </c>
       <c r="M40" s="19" t="n">
-        <v>0.02186499089408034</v>
+        <v>0.2444679867012578</v>
       </c>
       <c r="N40" s="20" t="n">
         <v>0</v>
@@ -3560,12 +3637,12 @@
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>JVST @ NDSU</t>
+          <t>BCU @ UCF</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D41" s="22" t="n">
@@ -3573,32 +3650,34 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>JVST ML</t>
-        </is>
-      </c>
-      <c r="G41" s="23" t="n"/>
+          <t>Under 59.5</t>
+        </is>
+      </c>
+      <c r="G41" s="23" t="n">
+        <v>59.5</v>
+      </c>
       <c r="H41" s="13" t="n">
-        <v>210</v>
+        <v>-108</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>0.3308036085807733</v>
+        <v>0.5828840668418837</v>
       </c>
       <c r="J41" s="15" t="n">
-        <v>0.3092071169459319</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K41" s="15" t="n">
-        <v>0.3225806451612903</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L41" s="14" t="n">
-        <v>0.008222963419482976</v>
+        <v>0.06365329761111438</v>
       </c>
       <c r="M41" s="14" t="n">
-        <v>0.02549118660039718</v>
+        <v>0.1225915361399241</v>
       </c>
       <c r="N41" s="15" t="n">
         <v>0</v>
@@ -3611,7 +3690,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q41" s="12" t="n"/>
+      <c r="Q41" s="12" t="inlineStr">
+        <is>
+          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="17" t="inlineStr">
@@ -3621,12 +3704,12 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>NMSU @ FSU</t>
+          <t>MASS @ RUTG</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-03 22:00</t>
         </is>
       </c>
       <c r="D42" s="25" t="n">
@@ -3649,7 +3732,7 @@
         <v>-110</v>
       </c>
       <c r="I42" s="20" t="n">
-        <v>0.5298211883282545</v>
+        <v>0.5740430549239717</v>
       </c>
       <c r="J42" s="20" t="n">
         <v>0.5</v>
@@ -3658,10 +3741,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L42" s="19" t="n">
-        <v>0.006011664518730697</v>
+        <v>0.05023353111444784</v>
       </c>
       <c r="M42" s="19" t="n">
-        <v>0.01147681408121326</v>
+        <v>0.09590037758212777</v>
       </c>
       <c r="N42" s="20" t="n">
         <v>0</v>
@@ -3684,12 +3767,12 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>HAW @ STAN</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D43" s="22" t="n">
@@ -3697,37 +3780,37 @@
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>Over 53.5</t>
+          <t>HAW +4</t>
         </is>
       </c>
       <c r="G43" s="23" t="n">
-        <v>53.5</v>
+        <v>-4</v>
       </c>
       <c r="H43" s="13" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>0.5177573237293587</v>
+        <v>0.5666660811488681</v>
       </c>
       <c r="J43" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K43" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L43" s="14" t="n">
-        <v>-0.001473445501410597</v>
+        <v>0.03836419435641525</v>
       </c>
       <c r="M43" s="14" t="n">
-        <v>-0.00283774689160543</v>
+        <v>0.07044135577437555</v>
       </c>
       <c r="N43" s="15" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="O43" s="24" t="n">
         <v>0.45</v>
@@ -3747,12 +3830,12 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>HAW @ STAN</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D44" s="25" t="n">
@@ -3760,34 +3843,32 @@
       </c>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F44" s="17" t="inlineStr">
         <is>
-          <t>Over 57.5</t>
-        </is>
-      </c>
-      <c r="G44" s="26" t="n">
-        <v>57.5</v>
-      </c>
+          <t>HAW ML</t>
+        </is>
+      </c>
+      <c r="G44" s="26" t="n"/>
       <c r="H44" s="18" t="n">
-        <v>-108</v>
+        <v>154</v>
       </c>
       <c r="I44" s="20" t="n">
-        <v>0.50780868060465</v>
+        <v>0.4319998430736718</v>
       </c>
       <c r="J44" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.3775334481388264</v>
       </c>
       <c r="K44" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.3937007874015748</v>
       </c>
       <c r="L44" s="19" t="n">
-        <v>-0.01142208862611926</v>
+        <v>0.03829905567209696</v>
       </c>
       <c r="M44" s="19" t="n">
-        <v>-0.02199809661326657</v>
+        <v>0.09727960140712633</v>
       </c>
       <c r="N44" s="20" t="n">
         <v>0</v>
@@ -3810,12 +3891,12 @@
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>SJSU @ EMU</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-09-04 22:30</t>
         </is>
       </c>
       <c r="D45" s="22" t="n">
@@ -3828,17 +3909,17 @@
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
-          <t>Under 57.5</t>
+          <t>Over 53.5</t>
         </is>
       </c>
       <c r="G45" s="23" t="n">
-        <v>57.5</v>
+        <v>53.5</v>
       </c>
       <c r="H45" s="13" t="n">
         <v>-112</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>0.49219131939535</v>
+        <v>0.559233949493164</v>
       </c>
       <c r="J45" s="15" t="n">
         <v>0.5043297540699688</v>
@@ -3847,10 +3928,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L45" s="14" t="n">
-        <v>-0.03611056739710283</v>
+        <v>0.03093206270071114</v>
       </c>
       <c r="M45" s="14" t="n">
-        <v>-0.06835214543023038</v>
+        <v>0.05854997582634602</v>
       </c>
       <c r="N45" s="15" t="n">
         <v>0</v>
@@ -3873,12 +3954,12 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D46" s="25" t="n">
@@ -3886,34 +3967,34 @@
       </c>
       <c r="E46" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F46" s="17" t="inlineStr">
         <is>
-          <t>Under 53.5</t>
+          <t>MEM +5.5</t>
         </is>
       </c>
       <c r="G46" s="26" t="n">
-        <v>53.5</v>
+        <v>-5.5</v>
       </c>
       <c r="H46" s="18" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I46" s="20" t="n">
-        <v>0.4822426762706413</v>
+        <v>0.55184820471133</v>
       </c>
       <c r="J46" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K46" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L46" s="19" t="n">
-        <v>-0.0460592105218115</v>
+        <v>0.02803868090180617</v>
       </c>
       <c r="M46" s="19" t="n">
-        <v>-0.08718350563057181</v>
+        <v>0.05352839081253913</v>
       </c>
       <c r="N46" s="20" t="n">
         <v>0</v>
@@ -3936,12 +4017,12 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>JVST @ NDSU</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D47" s="22" t="n">
@@ -3954,27 +4035,27 @@
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>NDSU ML</t>
+          <t>MEM ML</t>
         </is>
       </c>
       <c r="G47" s="23" t="n"/>
       <c r="H47" s="13" t="n">
-        <v>-258</v>
+        <v>180</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>0.6691963914192267</v>
+        <v>0.383035891688529</v>
       </c>
       <c r="J47" s="15" t="n">
-        <v>0.6907928830540681</v>
+        <v>0.3425247738043947</v>
       </c>
       <c r="K47" s="15" t="n">
-        <v>0.7206703910614525</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="L47" s="14" t="n">
-        <v>-0.05147399964222577</v>
+        <v>0.02589303454567188</v>
       </c>
       <c r="M47" s="14" t="n">
-        <v>-0.07142516229425128</v>
+        <v>0.07250049672788117</v>
       </c>
       <c r="N47" s="15" t="n">
         <v>0</v>
@@ -3997,12 +4078,12 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>NMSU @ FSU</t>
+          <t>COLO @ GT</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D48" s="25" t="n">
@@ -4010,34 +4091,34 @@
       </c>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F48" s="17" t="inlineStr">
         <is>
-          <t>Under 53.5</t>
+          <t>COLO +6.5</t>
         </is>
       </c>
       <c r="G48" s="26" t="n">
-        <v>53.5</v>
+        <v>-6.5</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="I48" s="20" t="n">
-        <v>0.4701788116717455</v>
+        <v>0.5359459352051367</v>
       </c>
       <c r="J48" s="20" t="n">
-        <v>0.5</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K48" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L48" s="19" t="n">
-        <v>-0.05363071213777837</v>
+        <v>0.02375081325391715</v>
       </c>
       <c r="M48" s="19" t="n">
-        <v>-0.1023859049903041</v>
+        <v>0.0463706354005049</v>
       </c>
       <c r="N48" s="20" t="n">
         <v>0</v>
@@ -4060,12 +4141,12 @@
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D49" s="22" t="n">
@@ -4078,17 +4159,17 @@
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
+          <t>Under 59.5</t>
         </is>
       </c>
       <c r="G49" s="23" t="n">
-        <v>47.5</v>
+        <v>59.5</v>
       </c>
       <c r="H49" s="13" t="n">
         <v>-108</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>0.4601467972635047</v>
+        <v>0.5413851965860426</v>
       </c>
       <c r="J49" s="15" t="n">
         <v>0.4956702459300312</v>
@@ -4097,10 +4178,10 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L49" s="14" t="n">
-        <v>-0.05908397196726456</v>
+        <v>0.02215442735527329</v>
       </c>
       <c r="M49" s="14" t="n">
-        <v>-0.1137913534184353</v>
+        <v>0.04266778601756349</v>
       </c>
       <c r="N49" s="15" t="n">
         <v>0</v>
@@ -4136,32 +4217,34 @@
       </c>
       <c r="E50" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F50" s="17" t="inlineStr">
         <is>
-          <t>UVA ML</t>
-        </is>
-      </c>
-      <c r="G50" s="26" t="n"/>
+          <t>NCSU +5.5</t>
+        </is>
+      </c>
+      <c r="G50" s="26" t="n">
+        <v>-5.5</v>
+      </c>
       <c r="H50" s="18" t="n">
-        <v>-218</v>
+        <v>-108</v>
       </c>
       <c r="I50" s="20" t="n">
-        <v>0.6254192861725905</v>
+        <v>0.5412896688794703</v>
       </c>
       <c r="J50" s="20" t="n">
-        <v>0.6574752261956054</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K50" s="20" t="n">
-        <v>0.6855345911949685</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L50" s="19" t="n">
-        <v>-0.06011530502237805</v>
+        <v>0.022058899648701</v>
       </c>
       <c r="M50" s="19" t="n">
-        <v>-0.08769113301429471</v>
+        <v>0.04248380673083174</v>
       </c>
       <c r="N50" s="20" t="n">
         <v>0</v>
@@ -4184,12 +4267,12 @@
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>JVST @ NDSU</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D51" s="22" t="n">
@@ -4197,37 +4280,35 @@
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
         <is>
-          <t>NDSU -7</t>
-        </is>
-      </c>
-      <c r="G51" s="23" t="n">
-        <v>-7</v>
-      </c>
+          <t>NCSU ML</t>
+        </is>
+      </c>
+      <c r="G51" s="23" t="n"/>
       <c r="H51" s="13" t="n">
-        <v>-105</v>
+        <v>180</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>0.4500144681504686</v>
+        <v>0.3745807138274095</v>
       </c>
       <c r="J51" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.3425247738043947</v>
       </c>
       <c r="K51" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="L51" s="14" t="n">
-        <v>-0.06218065380075088</v>
+        <v>0.01743785668455239</v>
       </c>
       <c r="M51" s="14" t="n">
-        <v>-0.1152697169483107</v>
+        <v>0.04882599871674664</v>
       </c>
       <c r="N51" s="15" t="n">
-        <v>0.0505</v>
+        <v>0</v>
       </c>
       <c r="O51" s="24" t="n">
         <v>0.45</v>
@@ -4247,12 +4328,12 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>MRMK @ DEL</t>
+          <t>SJSU @ EMU</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-04 22:30</t>
         </is>
       </c>
       <c r="D52" s="25" t="n">
@@ -4260,34 +4341,32 @@
       </c>
       <c r="E52" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F52" s="17" t="inlineStr">
         <is>
-          <t>Under 55.5</t>
-        </is>
-      </c>
-      <c r="G52" s="26" t="n">
-        <v>55.5</v>
-      </c>
+          <t>SJSU ML</t>
+        </is>
+      </c>
+      <c r="G52" s="26" t="n"/>
       <c r="H52" s="18" t="n">
-        <v>-108</v>
+        <v>180</v>
       </c>
       <c r="I52" s="20" t="n">
-        <v>0.4562349525054241</v>
+        <v>0.3741599606283899</v>
       </c>
       <c r="J52" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.3425247738043947</v>
       </c>
       <c r="K52" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="L52" s="19" t="n">
-        <v>-0.06299581672534516</v>
+        <v>0.0170171034855327</v>
       </c>
       <c r="M52" s="19" t="n">
-        <v>-0.1213252766562202</v>
+        <v>0.04764788975949152</v>
       </c>
       <c r="N52" s="20" t="n">
         <v>0</v>
@@ -4300,11 +4379,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q52" s="17" t="inlineStr">
-        <is>
-          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q52" s="17" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
@@ -4314,12 +4389,12 @@
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>SJSU @ EMU</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-09-04 22:30</t>
         </is>
       </c>
       <c r="D53" s="22" t="n">
@@ -4327,32 +4402,34 @@
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
-          <t>UNLV ML</t>
-        </is>
-      </c>
-      <c r="G53" s="23" t="n"/>
+          <t>SJSU +5.5</t>
+        </is>
+      </c>
+      <c r="G53" s="23" t="n">
+        <v>-5.5</v>
+      </c>
       <c r="H53" s="13" t="n">
-        <v>-218</v>
+        <v>-112</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>0.616964108311471</v>
+        <v>0.5451972766345791</v>
       </c>
       <c r="J53" s="15" t="n">
-        <v>0.6574752261956054</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K53" s="15" t="n">
-        <v>0.6855345911949685</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L53" s="14" t="n">
-        <v>-0.06857048288349754</v>
+        <v>0.01689538984212624</v>
       </c>
       <c r="M53" s="14" t="n">
-        <v>-0.1000248328300561</v>
+        <v>0.03198055934402461</v>
       </c>
       <c r="N53" s="15" t="n">
         <v>0</v>
@@ -4375,12 +4452,12 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>COLO @ GT</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D54" s="25" t="n">
@@ -4388,34 +4465,32 @@
       </c>
       <c r="E54" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F54" s="17" t="inlineStr">
         <is>
-          <t>UVA -5.5</t>
-        </is>
-      </c>
-      <c r="G54" s="26" t="n">
-        <v>-5.5</v>
-      </c>
+          <t>COLO ML</t>
+        </is>
+      </c>
+      <c r="G54" s="26" t="n"/>
       <c r="H54" s="18" t="n">
-        <v>-112</v>
+        <v>205</v>
       </c>
       <c r="I54" s="20" t="n">
-        <v>0.4587103311205297</v>
+        <v>0.3446539939839948</v>
       </c>
       <c r="J54" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.3146067415730336</v>
       </c>
       <c r="K54" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.3278688524590164</v>
       </c>
       <c r="L54" s="19" t="n">
-        <v>-0.0695915556719231</v>
+        <v>0.0167851415249784</v>
       </c>
       <c r="M54" s="19" t="n">
-        <v>-0.1317268732361402</v>
+        <v>0.05119468165118402</v>
       </c>
       <c r="N54" s="20" t="n">
         <v>0</v>
@@ -4438,12 +4513,12 @@
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D55" s="22" t="n">
@@ -4456,29 +4531,29 @@
       </c>
       <c r="F55" s="12" t="inlineStr">
         <is>
-          <t>Over 59.5</t>
+          <t>Over 47.5</t>
         </is>
       </c>
       <c r="G55" s="23" t="n">
-        <v>59.5</v>
+        <v>47.5</v>
       </c>
       <c r="H55" s="13" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>0.4586148034139574</v>
+        <v>0.5355234486665263</v>
       </c>
       <c r="J55" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K55" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L55" s="14" t="n">
-        <v>-0.06968708337849544</v>
+        <v>0.01629267943575707</v>
       </c>
       <c r="M55" s="14" t="n">
-        <v>-0.1319076935378664</v>
+        <v>0.0313784937281249</v>
       </c>
       <c r="N55" s="15" t="n">
         <v>0</v>
@@ -4501,12 +4576,12 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>MRMK @ DEL</t>
         </is>
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
@@ -4514,34 +4589,34 @@
       </c>
       <c r="E56" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F56" s="17" t="inlineStr">
         <is>
-          <t>UNLV -5.5</t>
+          <t>Over 55.5</t>
         </is>
       </c>
       <c r="G56" s="26" t="n">
-        <v>-5.5</v>
+        <v>55.5</v>
       </c>
       <c r="H56" s="18" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I56" s="20" t="n">
-        <v>0.4459869182536856</v>
+        <v>0.5437650474945759</v>
       </c>
       <c r="J56" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K56" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L56" s="19" t="n">
-        <v>-0.07324385097708364</v>
+        <v>0.01546316070212306</v>
       </c>
       <c r="M56" s="19" t="n">
-        <v>-0.1410622315114202</v>
+        <v>0.02926955418616145</v>
       </c>
       <c r="N56" s="20" t="n">
         <v>0</v>
@@ -4554,7 +4629,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q56" s="17" t="n"/>
+      <c r="Q56" s="17" t="inlineStr">
+        <is>
+          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
@@ -4564,12 +4643,12 @@
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>MASS @ RUTG</t>
+          <t>JVST @ NDSU</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 22:00</t>
+          <t>2026-08-29 21:30</t>
         </is>
       </c>
       <c r="D57" s="22" t="n">
@@ -4577,37 +4656,37 @@
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
         <is>
-          <t>Under 53.5</t>
+          <t>JVST +7</t>
         </is>
       </c>
       <c r="G57" s="23" t="n">
-        <v>53.5</v>
+        <v>-7</v>
       </c>
       <c r="H57" s="13" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>0.4259569450760283</v>
+        <v>0.5499855318495314</v>
       </c>
       <c r="J57" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K57" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L57" s="14" t="n">
-        <v>-0.09785257873349551</v>
+        <v>0.01510181091929885</v>
       </c>
       <c r="M57" s="14" t="n">
-        <v>-0.1868094684912186</v>
+        <v>0.02680803788623665</v>
       </c>
       <c r="N57" s="15" t="n">
-        <v>0</v>
+        <v>0.0505</v>
       </c>
       <c r="O57" s="24" t="n">
         <v>0.45</v>
@@ -4627,12 +4706,12 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>HAW @ STAN</t>
+          <t>JVST @ NDSU</t>
         </is>
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-08-29 21:30</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
@@ -4645,27 +4724,27 @@
       </c>
       <c r="F58" s="17" t="inlineStr">
         <is>
-          <t>STAN ML</t>
+          <t>JVST ML</t>
         </is>
       </c>
       <c r="G58" s="26" t="n"/>
       <c r="H58" s="18" t="n">
-        <v>-218</v>
+        <v>210</v>
       </c>
       <c r="I58" s="20" t="n">
-        <v>0.585504494093544</v>
+        <v>0.3308036085807733</v>
       </c>
       <c r="J58" s="20" t="n">
-        <v>0.6574752261956054</v>
+        <v>0.3092071169459319</v>
       </c>
       <c r="K58" s="20" t="n">
-        <v>0.6855345911949685</v>
+        <v>0.3225806451612903</v>
       </c>
       <c r="L58" s="19" t="n">
-        <v>-0.1000300971014245</v>
+        <v>0.008222963419482976</v>
       </c>
       <c r="M58" s="19" t="n">
-        <v>-0.1459154627442799</v>
+        <v>0.02549118660039718</v>
       </c>
       <c r="N58" s="20" t="n">
         <v>0</v>
@@ -4688,7 +4767,7 @@
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>HAW @ STAN</t>
+          <t>NMSU @ FSU</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
@@ -4701,34 +4780,34 @@
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
-          <t>STAN -5.5</t>
+          <t>Over 53.5</t>
         </is>
       </c>
       <c r="G59" s="23" t="n">
-        <v>-5.5</v>
+        <v>53.5</v>
       </c>
       <c r="H59" s="13" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>0.4161891749222263</v>
+        <v>0.5298211883282545</v>
       </c>
       <c r="J59" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5</v>
       </c>
       <c r="K59" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L59" s="14" t="n">
-        <v>-0.103041594308543</v>
+        <v>0.006011664518730697</v>
       </c>
       <c r="M59" s="14" t="n">
-        <v>-0.1984504779275642</v>
+        <v>0.01147681408121326</v>
       </c>
       <c r="N59" s="15" t="n">
         <v>0</v>
@@ -4751,12 +4830,12 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>BCU @ UCF</t>
+          <t>IDHO @ UTAH</t>
         </is>
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
@@ -4769,29 +4848,29 @@
       </c>
       <c r="F60" s="17" t="inlineStr">
         <is>
-          <t>Over 59.5</t>
+          <t>Over 56.5</t>
         </is>
       </c>
       <c r="G60" s="26" t="n">
-        <v>59.5</v>
+        <v>56.5</v>
       </c>
       <c r="H60" s="18" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I60" s="20" t="n">
-        <v>0.4171159331581163</v>
+        <v>0.5278465354893196</v>
       </c>
       <c r="J60" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K60" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L60" s="19" t="n">
-        <v>-0.1111859536343365</v>
+        <v>0.004037011679795754</v>
       </c>
       <c r="M60" s="19" t="n">
-        <v>-0.2104591265221369</v>
+        <v>0.007707022297791966</v>
       </c>
       <c r="N60" s="20" t="n">
         <v>0</v>
@@ -4806,7 +4885,7 @@
       </c>
       <c r="Q60" s="17" t="inlineStr">
         <is>
-          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -4818,12 +4897,12 @@
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D61" s="22" t="n">
@@ -4831,32 +4910,34 @@
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
-          <t>TCU ML</t>
-        </is>
-      </c>
-      <c r="G61" s="23" t="n"/>
+          <t>Over 56.5</t>
+        </is>
+      </c>
+      <c r="G61" s="23" t="n">
+        <v>56.5</v>
+      </c>
       <c r="H61" s="13" t="n">
-        <v>-298</v>
+        <v>-112</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>0.6339800039113948</v>
+        <v>0.5319860620965522</v>
       </c>
       <c r="J61" s="15" t="n">
-        <v>0.7179705215419501</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K61" s="15" t="n">
-        <v>0.7487437185929648</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L61" s="14" t="n">
-        <v>-0.1147637146815701</v>
+        <v>0.003684175304099369</v>
       </c>
       <c r="M61" s="14" t="n">
-        <v>-0.1532750283331037</v>
+        <v>0.006973617539902333</v>
       </c>
       <c r="N61" s="15" t="n">
         <v>0</v>
@@ -4879,12 +4960,12 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>AKR @ WAKE</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
@@ -4897,17 +4978,17 @@
       </c>
       <c r="F62" s="17" t="inlineStr">
         <is>
-          <t>Under 49.5</t>
+          <t>Over 53.5</t>
         </is>
       </c>
       <c r="G62" s="26" t="n">
-        <v>49.5</v>
+        <v>53.5</v>
       </c>
       <c r="H62" s="18" t="n">
         <v>-108</v>
       </c>
       <c r="I62" s="20" t="n">
-        <v>0.396824791827995</v>
+        <v>0.5177573237293587</v>
       </c>
       <c r="J62" s="20" t="n">
         <v>0.4956702459300312</v>
@@ -4916,10 +4997,10 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L62" s="19" t="n">
-        <v>-0.1224059774027743</v>
+        <v>-0.001473445501410597</v>
       </c>
       <c r="M62" s="19" t="n">
-        <v>-0.2357448453683059</v>
+        <v>-0.00283774689160543</v>
       </c>
       <c r="N62" s="20" t="n">
         <v>0</v>
@@ -4942,12 +5023,12 @@
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>SAC @ EMU</t>
+          <t>UAB @ ILL</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 22:30</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D63" s="22" t="n">
@@ -4960,29 +5041,29 @@
       </c>
       <c r="F63" s="12" t="inlineStr">
         <is>
-          <t>Under 52.5</t>
+          <t>Over 56.5</t>
         </is>
       </c>
       <c r="G63" s="23" t="n">
-        <v>52.5</v>
+        <v>56.5</v>
       </c>
       <c r="H63" s="13" t="n">
-        <v>-112</v>
+        <v>-115</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>0.404640493123267</v>
+        <v>0.5253393146800545</v>
       </c>
       <c r="J63" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K63" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L63" s="14" t="n">
-        <v>-0.1236613936691858</v>
+        <v>-0.00954440625017805</v>
       </c>
       <c r="M63" s="14" t="n">
-        <v>-0.2340733523023875</v>
+        <v>-0.01784388994598524</v>
       </c>
       <c r="N63" s="15" t="n">
         <v>0</v>
@@ -5005,12 +5086,12 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>WES @ KENN</t>
+          <t>INST @ PUR</t>
         </is>
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-04 23:00</t>
         </is>
       </c>
       <c r="D64" s="25" t="n">
@@ -5023,35 +5104,35 @@
       </c>
       <c r="F64" s="17" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>Under 56.5</t>
         </is>
       </c>
       <c r="G64" s="26" t="n">
-        <v>51.5</v>
+        <v>56.5</v>
       </c>
       <c r="H64" s="18" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I64" s="20" t="n">
-        <v>0.4028929855258536</v>
+        <v>0.5079800413890019</v>
       </c>
       <c r="J64" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K64" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L64" s="19" t="n">
-        <v>-0.1254089012665992</v>
+        <v>-0.01582948242052196</v>
       </c>
       <c r="M64" s="19" t="n">
-        <v>-0.2373811345403485</v>
+        <v>-0.03021992098463272</v>
       </c>
       <c r="N64" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O64" s="27" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="P64" s="17" t="inlineStr">
         <is>
@@ -5060,7 +5141,7 @@
       </c>
       <c r="Q64" s="17" t="inlineStr">
         <is>
-          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>INST isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5153,12 @@
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>INST @ PUR</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-09-04 23:00</t>
         </is>
       </c>
       <c r="D65" s="22" t="n">
@@ -5085,34 +5166,34 @@
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F65" s="12" t="inlineStr">
         <is>
-          <t>TCU -7.5</t>
+          <t>Over 56.5</t>
         </is>
       </c>
       <c r="G65" s="23" t="n">
-        <v>-7.5</v>
+        <v>56.5</v>
       </c>
       <c r="H65" s="13" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>0.4006920158047088</v>
+        <v>0.4920199586109981</v>
       </c>
       <c r="J65" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K65" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L65" s="14" t="n">
-        <v>-0.127609870987744</v>
+        <v>-0.03178956519852572</v>
       </c>
       <c r="M65" s="14" t="n">
-        <v>-0.2415472557982298</v>
+        <v>-0.06068916992445811</v>
       </c>
       <c r="N65" s="15" t="n">
         <v>0</v>
@@ -5125,7 +5206,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q65" s="12" t="n"/>
+      <c r="Q65" s="12" t="inlineStr">
+        <is>
+          <t>INST isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="17" t="inlineStr">
@@ -5135,12 +5220,12 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>HAW @ STAN</t>
+          <t>UAB @ ILL</t>
         </is>
       </c>
       <c r="C66" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D66" s="25" t="n">
@@ -5153,17 +5238,17 @@
       </c>
       <c r="F66" s="17" t="inlineStr">
         <is>
-          <t>Under 48.5</t>
+          <t>Under 56.5</t>
         </is>
       </c>
       <c r="G66" s="26" t="n">
-        <v>48.5</v>
+        <v>56.5</v>
       </c>
       <c r="H66" s="18" t="n">
         <v>-105</v>
       </c>
       <c r="I66" s="20" t="n">
-        <v>0.3767135533122641</v>
+        <v>0.4746606853199455</v>
       </c>
       <c r="J66" s="20" t="n">
         <v>0.4891657638136511</v>
@@ -5172,10 +5257,10 @@
         <v>0.5121951219512195</v>
       </c>
       <c r="L66" s="19" t="n">
-        <v>-0.1354815686389554</v>
+        <v>-0.03753443663127398</v>
       </c>
       <c r="M66" s="19" t="n">
-        <v>-0.2645116340093892</v>
+        <v>-0.07328151913724923</v>
       </c>
       <c r="N66" s="20" t="n">
         <v>0</v>
@@ -5198,12 +5283,12 @@
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>SAC @ EMU</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 22:30</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D67" s="22" t="n">
@@ -5211,32 +5296,34 @@
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
         <is>
-          <t>EMU ML</t>
-        </is>
-      </c>
-      <c r="G67" s="23" t="n"/>
+          <t>Under 53.5</t>
+        </is>
+      </c>
+      <c r="G67" s="23" t="n">
+        <v>53.5</v>
+      </c>
       <c r="H67" s="13" t="n">
-        <v>-355</v>
+        <v>-112</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>0.6313778129495795</v>
+        <v>0.4822426762706413</v>
       </c>
       <c r="J67" s="15" t="n">
-        <v>0.7477827050997783</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K67" s="15" t="n">
-        <v>0.7802197802197802</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L67" s="14" t="n">
-        <v>-0.1488419672702007</v>
+        <v>-0.0460592105218115</v>
       </c>
       <c r="M67" s="14" t="n">
-        <v>-0.1907692819942009</v>
+        <v>-0.08718350563057181</v>
       </c>
       <c r="N67" s="15" t="n">
         <v>0</v>
@@ -5259,12 +5346,12 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>ALB @ BUFF</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C68" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D68" s="25" t="n">
@@ -5277,29 +5364,29 @@
       </c>
       <c r="F68" s="17" t="inlineStr">
         <is>
-          <t>Under 48.5</t>
+          <t>Under 56.5</t>
         </is>
       </c>
       <c r="G68" s="26" t="n">
-        <v>48.5</v>
+        <v>56.5</v>
       </c>
       <c r="H68" s="18" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="I68" s="20" t="n">
-        <v>0.3794983449651635</v>
+        <v>0.4680139379034478</v>
       </c>
       <c r="J68" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K68" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L68" s="19" t="n">
-        <v>-0.155385375965069</v>
+        <v>-0.05121683132732147</v>
       </c>
       <c r="M68" s="19" t="n">
-        <v>-0.2905030941955639</v>
+        <v>-0.09863982329706344</v>
       </c>
       <c r="N68" s="20" t="n">
         <v>0</v>
@@ -5312,11 +5399,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q68" s="17" t="inlineStr">
-        <is>
-          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q68" s="17" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
@@ -5326,12 +5409,12 @@
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>SAC @ EMU</t>
+          <t>JVST @ NDSU</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 22:30</t>
+          <t>2026-08-29 21:30</t>
         </is>
       </c>
       <c r="D69" s="22" t="n">
@@ -5339,34 +5422,32 @@
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
         <is>
-          <t>EMU -9.5</t>
-        </is>
-      </c>
-      <c r="G69" s="23" t="n">
-        <v>-9.5</v>
-      </c>
+          <t>NDSU ML</t>
+        </is>
+      </c>
+      <c r="G69" s="23" t="n"/>
       <c r="H69" s="13" t="n">
-        <v>-110</v>
+        <v>-258</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>0.3626957910893782</v>
+        <v>0.6691963914192267</v>
       </c>
       <c r="J69" s="15" t="n">
-        <v>0.5</v>
+        <v>0.6907928830540681</v>
       </c>
       <c r="K69" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.7206703910614525</v>
       </c>
       <c r="L69" s="14" t="n">
-        <v>-0.1611137327201456</v>
+        <v>-0.05147399964222577</v>
       </c>
       <c r="M69" s="14" t="n">
-        <v>-0.3075807624657325</v>
+        <v>-0.07142516229425128</v>
       </c>
       <c r="N69" s="15" t="n">
         <v>0</v>
@@ -5379,11 +5460,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q69" s="12" t="inlineStr">
-        <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
-        </is>
-      </c>
+      <c r="Q69" s="12" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="17" t="inlineStr">
@@ -5393,12 +5470,12 @@
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>JVST @ NDSU</t>
+          <t>IDHO @ UTAH</t>
         </is>
       </c>
       <c r="C70" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D70" s="25" t="n">
@@ -5411,29 +5488,29 @@
       </c>
       <c r="F70" s="17" t="inlineStr">
         <is>
-          <t>Under 46.5</t>
+          <t>Under 56.5</t>
         </is>
       </c>
       <c r="G70" s="26" t="n">
-        <v>46.5</v>
+        <v>56.5</v>
       </c>
       <c r="H70" s="18" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I70" s="20" t="n">
-        <v>0.3425002548836977</v>
+        <v>0.4721534645106804</v>
       </c>
       <c r="J70" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5</v>
       </c>
       <c r="K70" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L70" s="19" t="n">
-        <v>-0.1767305143470715</v>
+        <v>-0.05165605929884343</v>
       </c>
       <c r="M70" s="19" t="n">
-        <v>-0.3403698794832488</v>
+        <v>-0.09861611320688279</v>
       </c>
       <c r="N70" s="20" t="n">
         <v>0</v>
@@ -5448,7 +5525,7 @@
       </c>
       <c r="Q70" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -5460,12 +5537,12 @@
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>MASS @ RUTG</t>
+          <t>NMSU @ FSU</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 22:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D71" s="22" t="n">
@@ -5473,32 +5550,34 @@
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
         <is>
-          <t>RUTG ML</t>
-        </is>
-      </c>
-      <c r="G71" s="23" t="n"/>
+          <t>Under 53.5</t>
+        </is>
+      </c>
+      <c r="G71" s="23" t="n">
+        <v>53.5</v>
+      </c>
       <c r="H71" s="13" t="n">
-        <v>-6500</v>
+        <v>-110</v>
       </c>
       <c r="I71" s="15" t="n">
-        <v>0.8036923684058288</v>
+        <v>0.4701788116717455</v>
       </c>
       <c r="J71" s="15" t="n">
-        <v>0.9538784067085954</v>
+        <v>0.5</v>
       </c>
       <c r="K71" s="15" t="n">
-        <v>0.9848484848484849</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L71" s="14" t="n">
-        <v>-0.1811561164426561</v>
+        <v>-0.05363071213777837</v>
       </c>
       <c r="M71" s="14" t="n">
-        <v>-0.183943133618697</v>
+        <v>-0.1023859049903041</v>
       </c>
       <c r="N71" s="15" t="n">
         <v>0</v>
@@ -5511,11 +5590,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q71" s="12" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+      <c r="Q71" s="12" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="17" t="inlineStr">
@@ -5525,12 +5600,12 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>AKR @ WAKE</t>
+          <t>COLO @ GT</t>
         </is>
       </c>
       <c r="C72" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D72" s="25" t="n">
@@ -5543,27 +5618,27 @@
       </c>
       <c r="F72" s="17" t="inlineStr">
         <is>
-          <t>WAKE ML</t>
+          <t>GT ML</t>
         </is>
       </c>
       <c r="G72" s="26" t="n"/>
       <c r="H72" s="18" t="n">
-        <v>-2800</v>
+        <v>-250</v>
       </c>
       <c r="I72" s="20" t="n">
-        <v>0.7689464432363347</v>
+        <v>0.6553460060160052</v>
       </c>
       <c r="J72" s="20" t="n">
-        <v>0.9311163895486935</v>
+        <v>0.6853932584269663</v>
       </c>
       <c r="K72" s="20" t="n">
-        <v>0.9655172413793104</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="L72" s="19" t="n">
-        <v>-0.1965707981429757</v>
+        <v>-0.05893970826970907</v>
       </c>
       <c r="M72" s="19" t="n">
-        <v>-0.203591183790939</v>
+        <v>-0.08251559157759275</v>
       </c>
       <c r="N72" s="20" t="n">
         <v>0</v>
@@ -5576,11 +5651,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q72" s="17" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+      <c r="Q72" s="17" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
@@ -5590,12 +5661,12 @@
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>NMSU @ FSU</t>
+          <t>SJSU @ EMU</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-04 22:30</t>
         </is>
       </c>
       <c r="D73" s="22" t="n">
@@ -5608,27 +5679,27 @@
       </c>
       <c r="F73" s="12" t="inlineStr">
         <is>
-          <t>FSU ML</t>
+          <t>EMU ML</t>
         </is>
       </c>
       <c r="G73" s="23" t="n"/>
       <c r="H73" s="13" t="n">
-        <v>-6500</v>
+        <v>-218</v>
       </c>
       <c r="I73" s="15" t="n">
-        <v>0.7810227846843814</v>
+        <v>0.6258400393716101</v>
       </c>
       <c r="J73" s="15" t="n">
-        <v>0.9538784067085954</v>
+        <v>0.6574752261956054</v>
       </c>
       <c r="K73" s="15" t="n">
-        <v>0.9848484848484849</v>
+        <v>0.6855345911949685</v>
       </c>
       <c r="L73" s="14" t="n">
-        <v>-0.2038257001641035</v>
+        <v>-0.05969455182335837</v>
       </c>
       <c r="M73" s="14" t="n">
-        <v>-0.2069614801666282</v>
+        <v>-0.08707737376067881</v>
       </c>
       <c r="N73" s="15" t="n">
         <v>0</v>
@@ -5641,11 +5712,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q73" s="12" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+      <c r="Q73" s="12" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="17" t="inlineStr">
@@ -5655,12 +5722,12 @@
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>WES @ KENN</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C74" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D74" s="25" t="n">
@@ -5673,44 +5740,40 @@
       </c>
       <c r="F74" s="17" t="inlineStr">
         <is>
-          <t>KENN ML</t>
+          <t>UVA ML</t>
         </is>
       </c>
       <c r="G74" s="26" t="n"/>
       <c r="H74" s="18" t="n">
-        <v>-3600</v>
+        <v>-218</v>
       </c>
       <c r="I74" s="20" t="n">
-        <v>0.7629882523168648</v>
+        <v>0.6254192861725905</v>
       </c>
       <c r="J74" s="20" t="n">
-        <v>0.9396411092985318</v>
+        <v>0.6574752261956054</v>
       </c>
       <c r="K74" s="20" t="n">
-        <v>0.972972972972973</v>
+        <v>0.6855345911949685</v>
       </c>
       <c r="L74" s="19" t="n">
-        <v>-0.2099847206561082</v>
+        <v>-0.06011530502237805</v>
       </c>
       <c r="M74" s="19" t="n">
-        <v>-0.2158176295632223</v>
+        <v>-0.08769113301429471</v>
       </c>
       <c r="N74" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O74" s="27" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="P74" s="17" t="inlineStr">
         <is>
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q74" s="17" t="inlineStr">
-        <is>
-          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q74" s="17" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
@@ -5720,12 +5783,12 @@
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>MRMK @ DEL</t>
+          <t>JVST @ NDSU</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-29 21:30</t>
         </is>
       </c>
       <c r="D75" s="22" t="n">
@@ -5733,35 +5796,37 @@
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
-          <t>DEL ML</t>
-        </is>
-      </c>
-      <c r="G75" s="23" t="n"/>
+          <t>NDSU -7</t>
+        </is>
+      </c>
+      <c r="G75" s="23" t="n">
+        <v>-7</v>
+      </c>
       <c r="H75" s="13" t="n">
-        <v>-10000</v>
+        <v>-105</v>
       </c>
       <c r="I75" s="15" t="n">
-        <v>0.7657797338257375</v>
+        <v>0.4500144681504686</v>
       </c>
       <c r="J75" s="15" t="n">
-        <v>0.9684473601999376</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K75" s="15" t="n">
-        <v>0.9900990099009901</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L75" s="14" t="n">
-        <v>-0.2243192760752526</v>
+        <v>-0.06218065380075088</v>
       </c>
       <c r="M75" s="14" t="n">
-        <v>-0.2265624688360051</v>
+        <v>-0.1152697169483107</v>
       </c>
       <c r="N75" s="15" t="n">
-        <v>0</v>
+        <v>0.0505</v>
       </c>
       <c r="O75" s="24" t="n">
         <v>0.45</v>
@@ -5771,11 +5836,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q75" s="12" t="inlineStr">
-        <is>
-          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q75" s="12" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="17" t="inlineStr">
@@ -5785,7 +5846,7 @@
       </c>
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>ALB @ BUFF</t>
+          <t>MRMK @ DEL</t>
         </is>
       </c>
       <c r="C76" s="17" t="inlineStr">
@@ -5798,32 +5859,34 @@
       </c>
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F76" s="17" t="inlineStr">
         <is>
-          <t>BUFF ML</t>
-        </is>
-      </c>
-      <c r="G76" s="26" t="n"/>
+          <t>Under 55.5</t>
+        </is>
+      </c>
+      <c r="G76" s="26" t="n">
+        <v>55.5</v>
+      </c>
       <c r="H76" s="18" t="n">
-        <v>-8000</v>
+        <v>-108</v>
       </c>
       <c r="I76" s="20" t="n">
-        <v>0.7599039260434692</v>
+        <v>0.4562349525054241</v>
       </c>
       <c r="J76" s="20" t="n">
-        <v>0.9578344612181156</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K76" s="20" t="n">
-        <v>0.9876543209876543</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L76" s="19" t="n">
-        <v>-0.227750394944185</v>
+        <v>-0.06299581672534516</v>
       </c>
       <c r="M76" s="19" t="n">
-        <v>-0.2305972748809874</v>
+        <v>-0.1213252766562202</v>
       </c>
       <c r="N76" s="20" t="n">
         <v>0</v>
@@ -5838,7 +5901,7 @@
       </c>
       <c r="Q76" s="17" t="inlineStr">
         <is>
-          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5913,12 @@
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>WES @ KENN</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D77" s="22" t="n">
@@ -5863,51 +5926,47 @@
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
-          <t>KENN -22.5</t>
+          <t>Under 47.5</t>
         </is>
       </c>
       <c r="G77" s="23" t="n">
-        <v>-22.5</v>
+        <v>47.5</v>
       </c>
       <c r="H77" s="13" t="n">
-        <v>-105</v>
+        <v>-112</v>
       </c>
       <c r="I77" s="15" t="n">
-        <v>0.2726533482579036</v>
+        <v>0.4644765513334737</v>
       </c>
       <c r="J77" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K77" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L77" s="14" t="n">
-        <v>-0.2395417736933159</v>
+        <v>-0.06382533545897917</v>
       </c>
       <c r="M77" s="14" t="n">
-        <v>-0.4676767962583787</v>
+        <v>-0.1208122421187821</v>
       </c>
       <c r="N77" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O77" s="24" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="P77" s="12" t="inlineStr">
         <is>
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q77" s="12" t="inlineStr">
-        <is>
-          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q77" s="12" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="17" t="inlineStr">
@@ -5917,12 +5976,12 @@
       </c>
       <c r="B78" s="17" t="inlineStr">
         <is>
-          <t>AKR @ WAKE</t>
+          <t>SJSU @ EMU</t>
         </is>
       </c>
       <c r="C78" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-04 22:30</t>
         </is>
       </c>
       <c r="D78" s="25" t="n">
@@ -5935,29 +5994,29 @@
       </c>
       <c r="F78" s="17" t="inlineStr">
         <is>
-          <t>WAKE -23.5</t>
+          <t>EMU -5.5</t>
         </is>
       </c>
       <c r="G78" s="26" t="n">
-        <v>-23.5</v>
+        <v>-5.5</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="I78" s="20" t="n">
-        <v>0.279786024178475</v>
+        <v>0.4548027233654209</v>
       </c>
       <c r="J78" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K78" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L78" s="19" t="n">
-        <v>-0.2485158626139778</v>
+        <v>-0.06442804586534834</v>
       </c>
       <c r="M78" s="19" t="n">
-        <v>-0.4704050256621722</v>
+        <v>-0.1240836438888189</v>
       </c>
       <c r="N78" s="20" t="n">
         <v>0</v>
@@ -5970,11 +6029,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q78" s="17" t="inlineStr">
-        <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
-        </is>
-      </c>
+      <c r="Q78" s="17" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="12" t="inlineStr">
@@ -5984,12 +6039,12 @@
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>ALB @ BUFF</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D79" s="22" t="n">
@@ -5997,34 +6052,32 @@
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
-          <t>BUFF -24.5</t>
-        </is>
-      </c>
-      <c r="G79" s="23" t="n">
-        <v>-24.5</v>
-      </c>
+          <t>UNLV ML</t>
+        </is>
+      </c>
+      <c r="G79" s="23" t="n"/>
       <c r="H79" s="13" t="n">
-        <v>-108</v>
+        <v>-218</v>
       </c>
       <c r="I79" s="15" t="n">
-        <v>0.2657449776111079</v>
+        <v>0.616964108311471</v>
       </c>
       <c r="J79" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.6574752261956054</v>
       </c>
       <c r="K79" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.6855345911949685</v>
       </c>
       <c r="L79" s="14" t="n">
-        <v>-0.2534857916196613</v>
+        <v>-0.06857048288349754</v>
       </c>
       <c r="M79" s="14" t="n">
-        <v>-0.4881948579341625</v>
+        <v>-0.1000248328300561</v>
       </c>
       <c r="N79" s="15" t="n">
         <v>0</v>
@@ -6037,11 +6090,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q79" s="12" t="inlineStr">
-        <is>
-          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q79" s="12" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="17" t="inlineStr">
@@ -6051,12 +6100,12 @@
       </c>
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C80" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D80" s="25" t="n">
@@ -6069,29 +6118,29 @@
       </c>
       <c r="F80" s="17" t="inlineStr">
         <is>
-          <t>USC -38.5</t>
+          <t>UVA -5.5</t>
         </is>
       </c>
       <c r="G80" s="26" t="n">
-        <v>-38.5</v>
+        <v>-5.5</v>
       </c>
       <c r="H80" s="18" t="n">
-        <v>100</v>
+        <v>-112</v>
       </c>
       <c r="I80" s="20" t="n">
-        <v>0.2414515187338134</v>
+        <v>0.4587103311205297</v>
       </c>
       <c r="J80" s="20" t="n">
-        <v>0.4782608695652174</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K80" s="20" t="n">
-        <v>0.5</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L80" s="19" t="n">
-        <v>-0.2585484812661866</v>
+        <v>-0.0695915556719231</v>
       </c>
       <c r="M80" s="19" t="n">
-        <v>-0.5170969625323734</v>
+        <v>-0.1317268732361402</v>
       </c>
       <c r="N80" s="20" t="n">
         <v>0</v>
@@ -6104,11 +6153,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q80" s="17" t="inlineStr">
-        <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
-        </is>
-      </c>
+      <c r="Q80" s="17" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="12" t="inlineStr">
@@ -6118,12 +6163,12 @@
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>NMSU @ FSU</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D81" s="22" t="n">
@@ -6131,34 +6176,34 @@
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
-          <t>FSU -31.5</t>
+          <t>Over 59.5</t>
         </is>
       </c>
       <c r="G81" s="23" t="n">
-        <v>-31.5</v>
+        <v>59.5</v>
       </c>
       <c r="H81" s="13" t="n">
-        <v>-105</v>
+        <v>-112</v>
       </c>
       <c r="I81" s="15" t="n">
-        <v>0.2515947455243119</v>
+        <v>0.4586148034139574</v>
       </c>
       <c r="J81" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K81" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L81" s="14" t="n">
-        <v>-0.2606003764269076</v>
+        <v>-0.06968708337849544</v>
       </c>
       <c r="M81" s="14" t="n">
-        <v>-0.5087912111192006</v>
+        <v>-0.1319076935378664</v>
       </c>
       <c r="N81" s="15" t="n">
         <v>0</v>
@@ -6171,11 +6216,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q81" s="12" t="inlineStr">
-        <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
-        </is>
-      </c>
+      <c r="Q81" s="12" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="17" t="inlineStr">
@@ -6185,12 +6226,12 @@
       </c>
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>MASS @ RUTG</t>
+          <t>COLO @ GT</t>
         </is>
       </c>
       <c r="C82" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 22:00</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D82" s="25" t="n">
@@ -6203,29 +6244,29 @@
       </c>
       <c r="F82" s="17" t="inlineStr">
         <is>
-          <t>RUTG -30.5</t>
+          <t>GT -6.5</t>
         </is>
       </c>
       <c r="G82" s="26" t="n">
-        <v>-30.5</v>
+        <v>-6.5</v>
       </c>
       <c r="H82" s="18" t="n">
-        <v>-112</v>
+        <v>-115</v>
       </c>
       <c r="I82" s="20" t="n">
-        <v>0.2637706885532299</v>
+        <v>0.4640540647948633</v>
       </c>
       <c r="J82" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K82" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L82" s="19" t="n">
-        <v>-0.2645311982392229</v>
+        <v>-0.07082965613536918</v>
       </c>
       <c r="M82" s="19" t="n">
-        <v>-0.5007197680956719</v>
+        <v>-0.132420661470473</v>
       </c>
       <c r="N82" s="20" t="n">
         <v>0</v>
@@ -6238,11 +6279,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q82" s="17" t="inlineStr">
-        <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
-        </is>
-      </c>
+      <c r="Q82" s="17" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="12" t="inlineStr">
@@ -6252,12 +6289,12 @@
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>MRMK @ DEL</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D83" s="22" t="n">
@@ -6270,29 +6307,29 @@
       </c>
       <c r="F83" s="12" t="inlineStr">
         <is>
-          <t>DEL -28.5</t>
+          <t>UNLV -5.5</t>
         </is>
       </c>
       <c r="G83" s="23" t="n">
-        <v>-28.5</v>
+        <v>-5.5</v>
       </c>
       <c r="H83" s="13" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I83" s="15" t="n">
-        <v>0.2613150626201174</v>
+        <v>0.4481517952886701</v>
       </c>
       <c r="J83" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K83" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L83" s="14" t="n">
-        <v>-0.2669868241723354</v>
+        <v>-0.07565772852085378</v>
       </c>
       <c r="M83" s="14" t="n">
-        <v>-0.5053679171833493</v>
+        <v>-0.1444374817216299</v>
       </c>
       <c r="N83" s="15" t="n">
         <v>0</v>
@@ -6305,11 +6342,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q83" s="12" t="inlineStr">
-        <is>
-          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q83" s="12" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="17" t="inlineStr">
@@ -6319,12 +6352,12 @@
       </c>
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>BCU @ UCF</t>
+          <t>SJSU @ EMU</t>
         </is>
       </c>
       <c r="C84" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-04 22:30</t>
         </is>
       </c>
       <c r="D84" s="25" t="n">
@@ -6332,22 +6365,22 @@
       </c>
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F84" s="17" t="inlineStr">
         <is>
-          <t>UCF -42.5</t>
+          <t>Under 53.5</t>
         </is>
       </c>
       <c r="G84" s="26" t="n">
-        <v>-42.5</v>
+        <v>53.5</v>
       </c>
       <c r="H84" s="18" t="n">
         <v>-108</v>
       </c>
       <c r="I84" s="20" t="n">
-        <v>0.2482518098143184</v>
+        <v>0.440766050506836</v>
       </c>
       <c r="J84" s="20" t="n">
         <v>0.4956702459300312</v>
@@ -6356,10 +6389,10 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L84" s="19" t="n">
-        <v>-0.2709789594164509</v>
+        <v>-0.07846471872393324</v>
       </c>
       <c r="M84" s="19" t="n">
-        <v>-0.521885403320572</v>
+        <v>-0.1511172360609083</v>
       </c>
       <c r="N84" s="20" t="n">
         <v>0</v>
@@ -6372,9 +6405,2621 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q84" s="17" t="inlineStr">
+      <c r="Q84" s="17" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B85" s="12" t="inlineStr">
+        <is>
+          <t>HAW @ STAN</t>
+        </is>
+      </c>
+      <c r="C85" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-29 23:00</t>
+        </is>
+      </c>
+      <c r="D85" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="12" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="F85" s="12" t="inlineStr">
+        <is>
+          <t>STAN ML</t>
+        </is>
+      </c>
+      <c r="G85" s="23" t="n"/>
+      <c r="H85" s="13" t="n">
+        <v>-185</v>
+      </c>
+      <c r="I85" s="15" t="n">
+        <v>0.5680001569263282</v>
+      </c>
+      <c r="J85" s="15" t="n">
+        <v>0.6224665518611737</v>
+      </c>
+      <c r="K85" s="15" t="n">
+        <v>0.6491228070175439</v>
+      </c>
+      <c r="L85" s="14" t="n">
+        <v>-0.08112265009121566</v>
+      </c>
+      <c r="M85" s="14" t="n">
+        <v>-0.1249727312216025</v>
+      </c>
+      <c r="N85" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P85" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q85" s="12" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B86" s="17" t="inlineStr">
+        <is>
+          <t>HAW @ STAN</t>
+        </is>
+      </c>
+      <c r="C86" s="17" t="inlineStr">
+        <is>
+          <t>2026-08-29 23:00</t>
+        </is>
+      </c>
+      <c r="D86" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" s="17" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="F86" s="17" t="inlineStr">
+        <is>
+          <t>STAN -4</t>
+        </is>
+      </c>
+      <c r="G86" s="26" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H86" s="18" t="n">
+        <v>-108</v>
+      </c>
+      <c r="I86" s="20" t="n">
+        <v>0.4333339188511319</v>
+      </c>
+      <c r="J86" s="20" t="n">
+        <v>0.4956702459300312</v>
+      </c>
+      <c r="K86" s="20" t="n">
+        <v>0.5192307692307693</v>
+      </c>
+      <c r="L86" s="19" t="n">
+        <v>-0.08589685037963735</v>
+      </c>
+      <c r="M86" s="19" t="n">
+        <v>-0.1604724948268336</v>
+      </c>
+      <c r="N86" s="20" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="O86" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P86" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q86" s="17" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B87" s="12" t="inlineStr">
+        <is>
+          <t>MASS @ RUTG</t>
+        </is>
+      </c>
+      <c r="C87" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-03 22:00</t>
+        </is>
+      </c>
+      <c r="D87" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="F87" s="12" t="inlineStr">
+        <is>
+          <t>Under 53.5</t>
+        </is>
+      </c>
+      <c r="G87" s="23" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="H87" s="13" t="n">
+        <v>-110</v>
+      </c>
+      <c r="I87" s="15" t="n">
+        <v>0.4259569450760283</v>
+      </c>
+      <c r="J87" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K87" s="15" t="n">
+        <v>0.5238095238095238</v>
+      </c>
+      <c r="L87" s="14" t="n">
+        <v>-0.09785257873349551</v>
+      </c>
+      <c r="M87" s="14" t="n">
+        <v>-0.1868094684912186</v>
+      </c>
+      <c r="N87" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P87" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q87" s="12" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B88" s="17" t="inlineStr">
+        <is>
+          <t>BCU @ UCF</t>
+        </is>
+      </c>
+      <c r="C88" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-03 23:00</t>
+        </is>
+      </c>
+      <c r="D88" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" s="17" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="F88" s="17" t="inlineStr">
+        <is>
+          <t>Over 59.5</t>
+        </is>
+      </c>
+      <c r="G88" s="26" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="H88" s="18" t="n">
+        <v>-112</v>
+      </c>
+      <c r="I88" s="20" t="n">
+        <v>0.4171159331581163</v>
+      </c>
+      <c r="J88" s="20" t="n">
+        <v>0.5043297540699688</v>
+      </c>
+      <c r="K88" s="20" t="n">
+        <v>0.5283018867924528</v>
+      </c>
+      <c r="L88" s="19" t="n">
+        <v>-0.1111859536343365</v>
+      </c>
+      <c r="M88" s="19" t="n">
+        <v>-0.2104591265221369</v>
+      </c>
+      <c r="N88" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P88" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q88" s="17" t="inlineStr">
         <is>
           <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B89" s="12" t="inlineStr">
+        <is>
+          <t>UNC @ TCU</t>
+        </is>
+      </c>
+      <c r="C89" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-29 16:00</t>
+        </is>
+      </c>
+      <c r="D89" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" s="12" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="F89" s="12" t="inlineStr">
+        <is>
+          <t>TCU ML</t>
+        </is>
+      </c>
+      <c r="G89" s="23" t="n"/>
+      <c r="H89" s="13" t="n">
+        <v>-298</v>
+      </c>
+      <c r="I89" s="15" t="n">
+        <v>0.6339800039113948</v>
+      </c>
+      <c r="J89" s="15" t="n">
+        <v>0.7179705215419501</v>
+      </c>
+      <c r="K89" s="15" t="n">
+        <v>0.7487437185929648</v>
+      </c>
+      <c r="L89" s="14" t="n">
+        <v>-0.1147637146815701</v>
+      </c>
+      <c r="M89" s="14" t="n">
+        <v>-0.1532750283331037</v>
+      </c>
+      <c r="N89" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P89" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q89" s="12" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B90" s="17" t="inlineStr">
+        <is>
+          <t>AKR @ WAKE</t>
+        </is>
+      </c>
+      <c r="C90" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-03 23:00</t>
+        </is>
+      </c>
+      <c r="D90" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" s="17" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="F90" s="17" t="inlineStr">
+        <is>
+          <t>Under 49.5</t>
+        </is>
+      </c>
+      <c r="G90" s="26" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="H90" s="18" t="n">
+        <v>-108</v>
+      </c>
+      <c r="I90" s="20" t="n">
+        <v>0.396824791827995</v>
+      </c>
+      <c r="J90" s="20" t="n">
+        <v>0.4956702459300312</v>
+      </c>
+      <c r="K90" s="20" t="n">
+        <v>0.5192307692307693</v>
+      </c>
+      <c r="L90" s="19" t="n">
+        <v>-0.1224059774027743</v>
+      </c>
+      <c r="M90" s="19" t="n">
+        <v>-0.2357448453683059</v>
+      </c>
+      <c r="N90" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P90" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q90" s="17" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B91" s="12" t="inlineStr">
+        <is>
+          <t>WES @ KENN</t>
+        </is>
+      </c>
+      <c r="C91" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-03 23:00</t>
+        </is>
+      </c>
+      <c r="D91" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="F91" s="12" t="inlineStr">
+        <is>
+          <t>Under 51.5</t>
+        </is>
+      </c>
+      <c r="G91" s="23" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="H91" s="13" t="n">
+        <v>-112</v>
+      </c>
+      <c r="I91" s="15" t="n">
+        <v>0.4028929855258536</v>
+      </c>
+      <c r="J91" s="15" t="n">
+        <v>0.5043297540699688</v>
+      </c>
+      <c r="K91" s="15" t="n">
+        <v>0.5283018867924528</v>
+      </c>
+      <c r="L91" s="14" t="n">
+        <v>-0.1254089012665992</v>
+      </c>
+      <c r="M91" s="14" t="n">
+        <v>-0.2373811345403485</v>
+      </c>
+      <c r="N91" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" s="24" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P91" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q91" s="12" t="inlineStr">
+        <is>
+          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B92" s="17" t="inlineStr">
+        <is>
+          <t>COLO @ GT</t>
+        </is>
+      </c>
+      <c r="C92" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-04 00:00</t>
+        </is>
+      </c>
+      <c r="D92" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" s="17" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="F92" s="17" t="inlineStr">
+        <is>
+          <t>Under 50.5</t>
+        </is>
+      </c>
+      <c r="G92" s="26" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="H92" s="18" t="n">
+        <v>-105</v>
+      </c>
+      <c r="I92" s="20" t="n">
+        <v>0.3867120014398708</v>
+      </c>
+      <c r="J92" s="20" t="n">
+        <v>0.4891657638136511</v>
+      </c>
+      <c r="K92" s="20" t="n">
+        <v>0.5121951219512195</v>
+      </c>
+      <c r="L92" s="19" t="n">
+        <v>-0.1254831205113487</v>
+      </c>
+      <c r="M92" s="19" t="n">
+        <v>-0.2449908543316808</v>
+      </c>
+      <c r="N92" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P92" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q92" s="17" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B93" s="12" t="inlineStr">
+        <is>
+          <t>SAC @ EMU</t>
+        </is>
+      </c>
+      <c r="C93" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:30</t>
+        </is>
+      </c>
+      <c r="D93" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="F93" s="12" t="inlineStr">
+        <is>
+          <t>Under 52.5</t>
+        </is>
+      </c>
+      <c r="G93" s="23" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="H93" s="13" t="n">
+        <v>-115</v>
+      </c>
+      <c r="I93" s="15" t="n">
+        <v>0.407892734181457</v>
+      </c>
+      <c r="J93" s="15" t="n">
+        <v>0.5108342361863488</v>
+      </c>
+      <c r="K93" s="15" t="n">
+        <v>0.5348837209302325</v>
+      </c>
+      <c r="L93" s="14" t="n">
+        <v>-0.1269909867487755</v>
+      </c>
+      <c r="M93" s="14" t="n">
+        <v>-0.2374179317477109</v>
+      </c>
+      <c r="N93" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P93" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q93" s="12" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B94" s="17" t="inlineStr">
+        <is>
+          <t>UAPB @ MIZ</t>
+        </is>
+      </c>
+      <c r="C94" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-04 00:00</t>
+        </is>
+      </c>
+      <c r="D94" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" s="17" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="F94" s="17" t="inlineStr">
+        <is>
+          <t>Over 60.5</t>
+        </is>
+      </c>
+      <c r="G94" s="26" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="H94" s="18" t="n">
+        <v>-112</v>
+      </c>
+      <c r="I94" s="20" t="n">
+        <v>0.3977053958774506</v>
+      </c>
+      <c r="J94" s="20" t="n">
+        <v>0.5043297540699688</v>
+      </c>
+      <c r="K94" s="20" t="n">
+        <v>0.5283018867924528</v>
+      </c>
+      <c r="L94" s="19" t="n">
+        <v>-0.1305964909150022</v>
+      </c>
+      <c r="M94" s="19" t="n">
+        <v>-0.2472005006605399</v>
+      </c>
+      <c r="N94" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P94" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q94" s="17" t="inlineStr">
+        <is>
+          <t>UAPB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B95" s="12" t="inlineStr">
+        <is>
+          <t>UNC @ TCU</t>
+        </is>
+      </c>
+      <c r="C95" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-29 16:00</t>
+        </is>
+      </c>
+      <c r="D95" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" s="12" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="F95" s="12" t="inlineStr">
+        <is>
+          <t>TCU -7.5</t>
+        </is>
+      </c>
+      <c r="G95" s="23" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H95" s="13" t="n">
+        <v>-115</v>
+      </c>
+      <c r="I95" s="15" t="n">
+        <v>0.4039442568628988</v>
+      </c>
+      <c r="J95" s="15" t="n">
+        <v>0.5108342361863488</v>
+      </c>
+      <c r="K95" s="15" t="n">
+        <v>0.5348837209302325</v>
+      </c>
+      <c r="L95" s="14" t="n">
+        <v>-0.1309394640673337</v>
+      </c>
+      <c r="M95" s="14" t="n">
+        <v>-0.2447998676041457</v>
+      </c>
+      <c r="N95" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P95" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q95" s="12" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B96" s="17" t="inlineStr">
+        <is>
+          <t>NCAT @ GAST</t>
+        </is>
+      </c>
+      <c r="C96" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-04 23:00</t>
+        </is>
+      </c>
+      <c r="D96" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" s="17" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="F96" s="17" t="inlineStr">
+        <is>
+          <t>Over 63.5</t>
+        </is>
+      </c>
+      <c r="G96" s="26" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="H96" s="18" t="n">
+        <v>-108</v>
+      </c>
+      <c r="I96" s="20" t="n">
+        <v>0.3882730035558194</v>
+      </c>
+      <c r="J96" s="20" t="n">
+        <v>0.4956702459300312</v>
+      </c>
+      <c r="K96" s="20" t="n">
+        <v>0.5192307692307693</v>
+      </c>
+      <c r="L96" s="19" t="n">
+        <v>-0.1309577656749499</v>
+      </c>
+      <c r="M96" s="19" t="n">
+        <v>-0.2522149561147182</v>
+      </c>
+      <c r="N96" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P96" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q96" s="17" t="inlineStr">
+        <is>
+          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B97" s="12" t="inlineStr">
+        <is>
+          <t>HAW @ STAN</t>
+        </is>
+      </c>
+      <c r="C97" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-29 23:00</t>
+        </is>
+      </c>
+      <c r="D97" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="F97" s="12" t="inlineStr">
+        <is>
+          <t>Under 48.5</t>
+        </is>
+      </c>
+      <c r="G97" s="23" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="H97" s="13" t="n">
+        <v>-108</v>
+      </c>
+      <c r="I97" s="15" t="n">
+        <v>0.3799657943704541</v>
+      </c>
+      <c r="J97" s="15" t="n">
+        <v>0.4956702459300312</v>
+      </c>
+      <c r="K97" s="15" t="n">
+        <v>0.5192307692307693</v>
+      </c>
+      <c r="L97" s="14" t="n">
+        <v>-0.1392649748603152</v>
+      </c>
+      <c r="M97" s="14" t="n">
+        <v>-0.2682140256569032</v>
+      </c>
+      <c r="N97" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P97" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q97" s="12" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B98" s="17" t="inlineStr">
+        <is>
+          <t>SAC @ EMU</t>
+        </is>
+      </c>
+      <c r="C98" s="17" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:30</t>
+        </is>
+      </c>
+      <c r="D98" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" s="17" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="F98" s="17" t="inlineStr">
+        <is>
+          <t>EMU ML</t>
+        </is>
+      </c>
+      <c r="G98" s="26" t="n"/>
+      <c r="H98" s="18" t="n">
+        <v>-355</v>
+      </c>
+      <c r="I98" s="20" t="n">
+        <v>0.6313778129495795</v>
+      </c>
+      <c r="J98" s="20" t="n">
+        <v>0.7477827050997783</v>
+      </c>
+      <c r="K98" s="20" t="n">
+        <v>0.7802197802197802</v>
+      </c>
+      <c r="L98" s="19" t="n">
+        <v>-0.1488419672702007</v>
+      </c>
+      <c r="M98" s="19" t="n">
+        <v>-0.1907692819942009</v>
+      </c>
+      <c r="N98" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P98" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q98" s="17" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B99" s="12" t="inlineStr">
+        <is>
+          <t>ALB @ BUFF</t>
+        </is>
+      </c>
+      <c r="C99" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-03 23:00</t>
+        </is>
+      </c>
+      <c r="D99" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="F99" s="12" t="inlineStr">
+        <is>
+          <t>Under 48.5</t>
+        </is>
+      </c>
+      <c r="G99" s="23" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="H99" s="13" t="n">
+        <v>-115</v>
+      </c>
+      <c r="I99" s="15" t="n">
+        <v>0.3794983449651635</v>
+      </c>
+      <c r="J99" s="15" t="n">
+        <v>0.5108342361863488</v>
+      </c>
+      <c r="K99" s="15" t="n">
+        <v>0.5348837209302325</v>
+      </c>
+      <c r="L99" s="14" t="n">
+        <v>-0.155385375965069</v>
+      </c>
+      <c r="M99" s="14" t="n">
+        <v>-0.2905030941955639</v>
+      </c>
+      <c r="N99" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P99" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q99" s="12" t="inlineStr">
+        <is>
+          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B100" s="17" t="inlineStr">
+        <is>
+          <t>SAC @ EMU</t>
+        </is>
+      </c>
+      <c r="C100" s="17" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:30</t>
+        </is>
+      </c>
+      <c r="D100" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" s="17" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="F100" s="17" t="inlineStr">
+        <is>
+          <t>EMU -9.5</t>
+        </is>
+      </c>
+      <c r="G100" s="26" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H100" s="18" t="n">
+        <v>-115</v>
+      </c>
+      <c r="I100" s="20" t="n">
+        <v>0.3681129091825526</v>
+      </c>
+      <c r="J100" s="20" t="n">
+        <v>0.5108342361863488</v>
+      </c>
+      <c r="K100" s="20" t="n">
+        <v>0.5348837209302325</v>
+      </c>
+      <c r="L100" s="19" t="n">
+        <v>-0.1667708117476799</v>
+      </c>
+      <c r="M100" s="19" t="n">
+        <v>-0.3117889089195756</v>
+      </c>
+      <c r="N100" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P100" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q100" s="17" t="inlineStr">
+        <is>
+          <t>raw model/market disagreement exceeds the safety limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B101" s="12" t="inlineStr">
+        <is>
+          <t>JVST @ NDSU</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-29 21:30</t>
+        </is>
+      </c>
+      <c r="D101" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="F101" s="12" t="inlineStr">
+        <is>
+          <t>Under 46.5</t>
+        </is>
+      </c>
+      <c r="G101" s="23" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="H101" s="13" t="n">
+        <v>-108</v>
+      </c>
+      <c r="I101" s="15" t="n">
+        <v>0.3425002548836977</v>
+      </c>
+      <c r="J101" s="15" t="n">
+        <v>0.4956702459300312</v>
+      </c>
+      <c r="K101" s="15" t="n">
+        <v>0.5192307692307693</v>
+      </c>
+      <c r="L101" s="14" t="n">
+        <v>-0.1767305143470715</v>
+      </c>
+      <c r="M101" s="14" t="n">
+        <v>-0.3403698794832488</v>
+      </c>
+      <c r="N101" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P101" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q101" s="12" t="inlineStr">
+        <is>
+          <t>raw model/market disagreement exceeds the safety limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B102" s="17" t="inlineStr">
+        <is>
+          <t>MASS @ RUTG</t>
+        </is>
+      </c>
+      <c r="C102" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-03 22:00</t>
+        </is>
+      </c>
+      <c r="D102" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" s="17" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="F102" s="17" t="inlineStr">
+        <is>
+          <t>RUTG ML</t>
+        </is>
+      </c>
+      <c r="G102" s="26" t="n"/>
+      <c r="H102" s="18" t="n">
+        <v>-6500</v>
+      </c>
+      <c r="I102" s="20" t="n">
+        <v>0.8036923684058288</v>
+      </c>
+      <c r="J102" s="20" t="n">
+        <v>0.9538784067085954</v>
+      </c>
+      <c r="K102" s="20" t="n">
+        <v>0.9848484848484849</v>
+      </c>
+      <c r="L102" s="19" t="n">
+        <v>-0.1811561164426561</v>
+      </c>
+      <c r="M102" s="19" t="n">
+        <v>-0.183943133618697</v>
+      </c>
+      <c r="N102" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P102" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q102" s="17" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B103" s="12" t="inlineStr">
+        <is>
+          <t>IDHO @ UTAH</t>
+        </is>
+      </c>
+      <c r="C103" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-04 01:00</t>
+        </is>
+      </c>
+      <c r="D103" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" s="12" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="F103" s="12" t="inlineStr">
+        <is>
+          <t>UTAH ML</t>
+        </is>
+      </c>
+      <c r="G103" s="23" t="n"/>
+      <c r="H103" s="13" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="I103" s="15" t="n">
+        <v>0.8084273455958602</v>
+      </c>
+      <c r="J103" s="15" t="n">
+        <v>0.9684473601999376</v>
+      </c>
+      <c r="K103" s="15" t="n">
+        <v>0.9900990099009901</v>
+      </c>
+      <c r="L103" s="14" t="n">
+        <v>-0.1816716643051299</v>
+      </c>
+      <c r="M103" s="14" t="n">
+        <v>-0.1834883809481812</v>
+      </c>
+      <c r="N103" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P103" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q103" s="12" t="inlineStr">
+        <is>
+          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B104" s="17" t="inlineStr">
+        <is>
+          <t>UAB @ ILL</t>
+        </is>
+      </c>
+      <c r="C104" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-04 01:00</t>
+        </is>
+      </c>
+      <c r="D104" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" s="17" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="F104" s="17" t="inlineStr">
+        <is>
+          <t>ILL ML</t>
+        </is>
+      </c>
+      <c r="G104" s="26" t="n"/>
+      <c r="H104" s="18" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="I104" s="20" t="n">
+        <v>0.8035624619687695</v>
+      </c>
+      <c r="J104" s="20" t="n">
+        <v>0.9684473601999376</v>
+      </c>
+      <c r="K104" s="20" t="n">
+        <v>0.9900990099009901</v>
+      </c>
+      <c r="L104" s="19" t="n">
+        <v>-0.1865365479322206</v>
+      </c>
+      <c r="M104" s="19" t="n">
+        <v>-0.1884019134115428</v>
+      </c>
+      <c r="N104" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P104" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q104" s="17" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B105" s="12" t="inlineStr">
+        <is>
+          <t>AKR @ WAKE</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-03 23:00</t>
+        </is>
+      </c>
+      <c r="D105" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" s="12" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="F105" s="12" t="inlineStr">
+        <is>
+          <t>WAKE ML</t>
+        </is>
+      </c>
+      <c r="G105" s="23" t="n"/>
+      <c r="H105" s="13" t="n">
+        <v>-2800</v>
+      </c>
+      <c r="I105" s="15" t="n">
+        <v>0.7689464432363347</v>
+      </c>
+      <c r="J105" s="15" t="n">
+        <v>0.9311163895486935</v>
+      </c>
+      <c r="K105" s="15" t="n">
+        <v>0.9655172413793104</v>
+      </c>
+      <c r="L105" s="14" t="n">
+        <v>-0.1965707981429757</v>
+      </c>
+      <c r="M105" s="14" t="n">
+        <v>-0.203591183790939</v>
+      </c>
+      <c r="N105" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P105" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q105" s="12" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B106" s="17" t="inlineStr">
+        <is>
+          <t>NMSU @ FSU</t>
+        </is>
+      </c>
+      <c r="C106" s="17" t="inlineStr">
+        <is>
+          <t>2026-08-29 23:00</t>
+        </is>
+      </c>
+      <c r="D106" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" s="17" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="F106" s="17" t="inlineStr">
+        <is>
+          <t>FSU ML</t>
+        </is>
+      </c>
+      <c r="G106" s="26" t="n"/>
+      <c r="H106" s="18" t="n">
+        <v>-6500</v>
+      </c>
+      <c r="I106" s="20" t="n">
+        <v>0.7810227846843814</v>
+      </c>
+      <c r="J106" s="20" t="n">
+        <v>0.9538784067085954</v>
+      </c>
+      <c r="K106" s="20" t="n">
+        <v>0.9848484848484849</v>
+      </c>
+      <c r="L106" s="19" t="n">
+        <v>-0.2038257001641035</v>
+      </c>
+      <c r="M106" s="19" t="n">
+        <v>-0.2069614801666282</v>
+      </c>
+      <c r="N106" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P106" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q106" s="17" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B107" s="12" t="inlineStr">
+        <is>
+          <t>WES @ KENN</t>
+        </is>
+      </c>
+      <c r="C107" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-03 23:00</t>
+        </is>
+      </c>
+      <c r="D107" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" s="12" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="F107" s="12" t="inlineStr">
+        <is>
+          <t>KENN ML</t>
+        </is>
+      </c>
+      <c r="G107" s="23" t="n"/>
+      <c r="H107" s="13" t="n">
+        <v>-3600</v>
+      </c>
+      <c r="I107" s="15" t="n">
+        <v>0.7629882523168648</v>
+      </c>
+      <c r="J107" s="15" t="n">
+        <v>0.9396411092985318</v>
+      </c>
+      <c r="K107" s="15" t="n">
+        <v>0.972972972972973</v>
+      </c>
+      <c r="L107" s="14" t="n">
+        <v>-0.2099847206561082</v>
+      </c>
+      <c r="M107" s="14" t="n">
+        <v>-0.2158176295632223</v>
+      </c>
+      <c r="N107" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" s="24" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P107" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q107" s="12" t="inlineStr">
+        <is>
+          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B108" s="17" t="inlineStr">
+        <is>
+          <t>MRMK @ DEL</t>
+        </is>
+      </c>
+      <c r="C108" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-03 23:00</t>
+        </is>
+      </c>
+      <c r="D108" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" s="17" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="F108" s="17" t="inlineStr">
+        <is>
+          <t>DEL ML</t>
+        </is>
+      </c>
+      <c r="G108" s="26" t="n"/>
+      <c r="H108" s="18" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="I108" s="20" t="n">
+        <v>0.7657797338257375</v>
+      </c>
+      <c r="J108" s="20" t="n">
+        <v>0.9684473601999376</v>
+      </c>
+      <c r="K108" s="20" t="n">
+        <v>0.9900990099009901</v>
+      </c>
+      <c r="L108" s="19" t="n">
+        <v>-0.2243192760752526</v>
+      </c>
+      <c r="M108" s="19" t="n">
+        <v>-0.2265624688360051</v>
+      </c>
+      <c r="N108" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P108" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q108" s="17" t="inlineStr">
+        <is>
+          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B109" s="12" t="inlineStr">
+        <is>
+          <t>ALB @ BUFF</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-03 23:00</t>
+        </is>
+      </c>
+      <c r="D109" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" s="12" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="F109" s="12" t="inlineStr">
+        <is>
+          <t>BUFF ML</t>
+        </is>
+      </c>
+      <c r="G109" s="23" t="n"/>
+      <c r="H109" s="13" t="n">
+        <v>-8000</v>
+      </c>
+      <c r="I109" s="15" t="n">
+        <v>0.7599039260434692</v>
+      </c>
+      <c r="J109" s="15" t="n">
+        <v>0.9578344612181156</v>
+      </c>
+      <c r="K109" s="15" t="n">
+        <v>0.9876543209876543</v>
+      </c>
+      <c r="L109" s="14" t="n">
+        <v>-0.227750394944185</v>
+      </c>
+      <c r="M109" s="14" t="n">
+        <v>-0.2305972748809874</v>
+      </c>
+      <c r="N109" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P109" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q109" s="12" t="inlineStr">
+        <is>
+          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B110" s="17" t="inlineStr">
+        <is>
+          <t>WES @ KENN</t>
+        </is>
+      </c>
+      <c r="C110" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-03 23:00</t>
+        </is>
+      </c>
+      <c r="D110" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" s="17" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="F110" s="17" t="inlineStr">
+        <is>
+          <t>KENN -22.5</t>
+        </is>
+      </c>
+      <c r="G110" s="26" t="n">
+        <v>-22.5</v>
+      </c>
+      <c r="H110" s="18" t="n">
+        <v>-105</v>
+      </c>
+      <c r="I110" s="20" t="n">
+        <v>0.2726533482579036</v>
+      </c>
+      <c r="J110" s="20" t="n">
+        <v>0.4891657638136511</v>
+      </c>
+      <c r="K110" s="20" t="n">
+        <v>0.5121951219512195</v>
+      </c>
+      <c r="L110" s="19" t="n">
+        <v>-0.2395417736933159</v>
+      </c>
+      <c r="M110" s="19" t="n">
+        <v>-0.4676767962583787</v>
+      </c>
+      <c r="N110" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" s="27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P110" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q110" s="17" t="inlineStr">
+        <is>
+          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B111" s="12" t="inlineStr">
+        <is>
+          <t>NCAT @ GAST</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-04 23:00</t>
+        </is>
+      </c>
+      <c r="D111" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" s="12" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="F111" s="12" t="inlineStr">
+        <is>
+          <t>GAST ML</t>
+        </is>
+      </c>
+      <c r="G111" s="23" t="n"/>
+      <c r="H111" s="13" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="I111" s="15" t="n">
+        <v>0.7344577690680144</v>
+      </c>
+      <c r="J111" s="15" t="n">
+        <v>0.949050949050949</v>
+      </c>
+      <c r="K111" s="15" t="n">
+        <v>0.9803921568627451</v>
+      </c>
+      <c r="L111" s="14" t="n">
+        <v>-0.2459343877947306</v>
+      </c>
+      <c r="M111" s="14" t="n">
+        <v>-0.2508530755506253</v>
+      </c>
+      <c r="N111" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P111" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q111" s="12" t="inlineStr">
+        <is>
+          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B112" s="17" t="inlineStr">
+        <is>
+          <t>AKR @ WAKE</t>
+        </is>
+      </c>
+      <c r="C112" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-03 23:00</t>
+        </is>
+      </c>
+      <c r="D112" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" s="17" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="F112" s="17" t="inlineStr">
+        <is>
+          <t>WAKE -23.5</t>
+        </is>
+      </c>
+      <c r="G112" s="26" t="n">
+        <v>-23.5</v>
+      </c>
+      <c r="H112" s="18" t="n">
+        <v>-112</v>
+      </c>
+      <c r="I112" s="20" t="n">
+        <v>0.279786024178475</v>
+      </c>
+      <c r="J112" s="20" t="n">
+        <v>0.5043297540699688</v>
+      </c>
+      <c r="K112" s="20" t="n">
+        <v>0.5283018867924528</v>
+      </c>
+      <c r="L112" s="19" t="n">
+        <v>-0.2485158626139778</v>
+      </c>
+      <c r="M112" s="19" t="n">
+        <v>-0.4704050256621722</v>
+      </c>
+      <c r="N112" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P112" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q112" s="17" t="inlineStr">
+        <is>
+          <t>raw model/market disagreement exceeds the safety limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B113" s="12" t="inlineStr">
+        <is>
+          <t>UAB @ ILL</t>
+        </is>
+      </c>
+      <c r="C113" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-04 01:00</t>
+        </is>
+      </c>
+      <c r="D113" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" s="12" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="F113" s="12" t="inlineStr">
+        <is>
+          <t>ILL -28.5</t>
+        </is>
+      </c>
+      <c r="G113" s="23" t="n">
+        <v>-28.5</v>
+      </c>
+      <c r="H113" s="13" t="n">
+        <v>-102</v>
+      </c>
+      <c r="I113" s="15" t="n">
+        <v>0.2561903984522976</v>
+      </c>
+      <c r="J113" s="15" t="n">
+        <v>0.4826358742837298</v>
+      </c>
+      <c r="K113" s="15" t="n">
+        <v>0.504950495049505</v>
+      </c>
+      <c r="L113" s="14" t="n">
+        <v>-0.2487600965972073</v>
+      </c>
+      <c r="M113" s="14" t="n">
+        <v>-0.4926425442415282</v>
+      </c>
+      <c r="N113" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P113" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q113" s="12" t="inlineStr">
+        <is>
+          <t>raw model/market disagreement exceeds the safety limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B114" s="17" t="inlineStr">
+        <is>
+          <t>ALB @ BUFF</t>
+        </is>
+      </c>
+      <c r="C114" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-03 23:00</t>
+        </is>
+      </c>
+      <c r="D114" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" s="17" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="F114" s="17" t="inlineStr">
+        <is>
+          <t>BUFF -24.5</t>
+        </is>
+      </c>
+      <c r="G114" s="26" t="n">
+        <v>-24.5</v>
+      </c>
+      <c r="H114" s="18" t="n">
+        <v>-108</v>
+      </c>
+      <c r="I114" s="20" t="n">
+        <v>0.2657449776111079</v>
+      </c>
+      <c r="J114" s="20" t="n">
+        <v>0.4956702459300312</v>
+      </c>
+      <c r="K114" s="20" t="n">
+        <v>0.5192307692307693</v>
+      </c>
+      <c r="L114" s="19" t="n">
+        <v>-0.2534857916196613</v>
+      </c>
+      <c r="M114" s="19" t="n">
+        <v>-0.4881948579341625</v>
+      </c>
+      <c r="N114" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P114" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q114" s="17" t="inlineStr">
+        <is>
+          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B115" s="12" t="inlineStr">
+        <is>
+          <t>SJSU @ USC</t>
+        </is>
+      </c>
+      <c r="C115" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-29 19:00</t>
+        </is>
+      </c>
+      <c r="D115" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" s="12" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="F115" s="12" t="inlineStr">
+        <is>
+          <t>USC -38.5</t>
+        </is>
+      </c>
+      <c r="G115" s="23" t="n">
+        <v>-38.5</v>
+      </c>
+      <c r="H115" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="I115" s="15" t="n">
+        <v>0.2414515187338134</v>
+      </c>
+      <c r="J115" s="15" t="n">
+        <v>0.4782608695652174</v>
+      </c>
+      <c r="K115" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L115" s="14" t="n">
+        <v>-0.2585484812661866</v>
+      </c>
+      <c r="M115" s="14" t="n">
+        <v>-0.5170969625323734</v>
+      </c>
+      <c r="N115" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P115" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q115" s="12" t="inlineStr">
+        <is>
+          <t>raw model/market disagreement exceeds the safety limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B116" s="17" t="inlineStr">
+        <is>
+          <t>NMSU @ FSU</t>
+        </is>
+      </c>
+      <c r="C116" s="17" t="inlineStr">
+        <is>
+          <t>2026-08-29 23:00</t>
+        </is>
+      </c>
+      <c r="D116" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" s="17" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="F116" s="17" t="inlineStr">
+        <is>
+          <t>FSU -31.5</t>
+        </is>
+      </c>
+      <c r="G116" s="26" t="n">
+        <v>-31.5</v>
+      </c>
+      <c r="H116" s="18" t="n">
+        <v>-105</v>
+      </c>
+      <c r="I116" s="20" t="n">
+        <v>0.2515947455243119</v>
+      </c>
+      <c r="J116" s="20" t="n">
+        <v>0.4891657638136511</v>
+      </c>
+      <c r="K116" s="20" t="n">
+        <v>0.5121951219512195</v>
+      </c>
+      <c r="L116" s="19" t="n">
+        <v>-0.2606003764269076</v>
+      </c>
+      <c r="M116" s="19" t="n">
+        <v>-0.5087912111192006</v>
+      </c>
+      <c r="N116" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P116" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q116" s="17" t="inlineStr">
+        <is>
+          <t>raw model/market disagreement exceeds the safety limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B117" s="12" t="inlineStr">
+        <is>
+          <t>MASS @ RUTG</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-03 22:00</t>
+        </is>
+      </c>
+      <c r="D117" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E117" s="12" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="F117" s="12" t="inlineStr">
+        <is>
+          <t>RUTG -30.5</t>
+        </is>
+      </c>
+      <c r="G117" s="23" t="n">
+        <v>-30.5</v>
+      </c>
+      <c r="H117" s="13" t="n">
+        <v>-112</v>
+      </c>
+      <c r="I117" s="15" t="n">
+        <v>0.2637706885532299</v>
+      </c>
+      <c r="J117" s="15" t="n">
+        <v>0.5043297540699688</v>
+      </c>
+      <c r="K117" s="15" t="n">
+        <v>0.5283018867924528</v>
+      </c>
+      <c r="L117" s="14" t="n">
+        <v>-0.2645311982392229</v>
+      </c>
+      <c r="M117" s="14" t="n">
+        <v>-0.5007197680956719</v>
+      </c>
+      <c r="N117" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P117" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q117" s="12" t="inlineStr">
+        <is>
+          <t>raw model/market disagreement exceeds the safety limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B118" s="17" t="inlineStr">
+        <is>
+          <t>MRMK @ DEL</t>
+        </is>
+      </c>
+      <c r="C118" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-03 23:00</t>
+        </is>
+      </c>
+      <c r="D118" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" s="17" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="F118" s="17" t="inlineStr">
+        <is>
+          <t>DEL -28.5</t>
+        </is>
+      </c>
+      <c r="G118" s="26" t="n">
+        <v>-28.5</v>
+      </c>
+      <c r="H118" s="18" t="n">
+        <v>-112</v>
+      </c>
+      <c r="I118" s="20" t="n">
+        <v>0.2613150626201174</v>
+      </c>
+      <c r="J118" s="20" t="n">
+        <v>0.5043297540699688</v>
+      </c>
+      <c r="K118" s="20" t="n">
+        <v>0.5283018867924528</v>
+      </c>
+      <c r="L118" s="19" t="n">
+        <v>-0.2669868241723354</v>
+      </c>
+      <c r="M118" s="19" t="n">
+        <v>-0.5053679171833493</v>
+      </c>
+      <c r="N118" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P118" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q118" s="17" t="inlineStr">
+        <is>
+          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B119" s="12" t="inlineStr">
+        <is>
+          <t>NCAT @ GAST</t>
+        </is>
+      </c>
+      <c r="C119" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-04 23:00</t>
+        </is>
+      </c>
+      <c r="D119" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" s="12" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="F119" s="12" t="inlineStr">
+        <is>
+          <t>GAST -28.5</t>
+        </is>
+      </c>
+      <c r="G119" s="23" t="n">
+        <v>-28.5</v>
+      </c>
+      <c r="H119" s="13" t="n">
+        <v>-112</v>
+      </c>
+      <c r="I119" s="15" t="n">
+        <v>0.2590431225556397</v>
+      </c>
+      <c r="J119" s="15" t="n">
+        <v>0.5043297540699688</v>
+      </c>
+      <c r="K119" s="15" t="n">
+        <v>0.5283018867924528</v>
+      </c>
+      <c r="L119" s="14" t="n">
+        <v>-0.2692587642368131</v>
+      </c>
+      <c r="M119" s="14" t="n">
+        <v>-0.509668375162539</v>
+      </c>
+      <c r="N119" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P119" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q119" s="12" t="inlineStr">
+        <is>
+          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B120" s="17" t="inlineStr">
+        <is>
+          <t>IDHO @ UTAH</t>
+        </is>
+      </c>
+      <c r="C120" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-04 01:00</t>
+        </is>
+      </c>
+      <c r="D120" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" s="17" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="F120" s="17" t="inlineStr">
+        <is>
+          <t>UTAH -33.5</t>
+        </is>
+      </c>
+      <c r="G120" s="26" t="n">
+        <v>-33.5</v>
+      </c>
+      <c r="H120" s="18" t="n">
+        <v>-112</v>
+      </c>
+      <c r="I120" s="20" t="n">
+        <v>0.2585208472473556</v>
+      </c>
+      <c r="J120" s="20" t="n">
+        <v>0.5043297540699688</v>
+      </c>
+      <c r="K120" s="20" t="n">
+        <v>0.5283018867924528</v>
+      </c>
+      <c r="L120" s="19" t="n">
+        <v>-0.2697810395450972</v>
+      </c>
+      <c r="M120" s="19" t="n">
+        <v>-0.5106569677103627</v>
+      </c>
+      <c r="N120" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P120" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q120" s="17" t="inlineStr">
+        <is>
+          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B121" s="12" t="inlineStr">
+        <is>
+          <t>BCU @ UCF</t>
+        </is>
+      </c>
+      <c r="C121" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-03 23:00</t>
+        </is>
+      </c>
+      <c r="D121" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" s="12" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="F121" s="12" t="inlineStr">
+        <is>
+          <t>UCF -42.5</t>
+        </is>
+      </c>
+      <c r="G121" s="23" t="n">
+        <v>-42.5</v>
+      </c>
+      <c r="H121" s="13" t="n">
+        <v>-108</v>
+      </c>
+      <c r="I121" s="15" t="n">
+        <v>0.2482518098143184</v>
+      </c>
+      <c r="J121" s="15" t="n">
+        <v>0.4956702459300312</v>
+      </c>
+      <c r="K121" s="15" t="n">
+        <v>0.5192307692307693</v>
+      </c>
+      <c r="L121" s="14" t="n">
+        <v>-0.2709789594164509</v>
+      </c>
+      <c r="M121" s="14" t="n">
+        <v>-0.521885403320572</v>
+      </c>
+      <c r="N121" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P121" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q121" s="12" t="inlineStr">
+        <is>
+          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B122" s="17" t="inlineStr">
+        <is>
+          <t>UAPB @ MIZ</t>
+        </is>
+      </c>
+      <c r="C122" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-04 00:00</t>
+        </is>
+      </c>
+      <c r="D122" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" s="17" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="F122" s="17" t="inlineStr">
+        <is>
+          <t>MIZ -54.5</t>
+        </is>
+      </c>
+      <c r="G122" s="26" t="n">
+        <v>-54.5</v>
+      </c>
+      <c r="H122" s="18" t="n">
+        <v>-110</v>
+      </c>
+      <c r="I122" s="20" t="n">
+        <v>0.250018047672936</v>
+      </c>
+      <c r="J122" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K122" s="20" t="n">
+        <v>0.5238095238095238</v>
+      </c>
+      <c r="L122" s="19" t="n">
+        <v>-0.2737914761365878</v>
+      </c>
+      <c r="M122" s="19" t="n">
+        <v>-0.5226928180789403</v>
+      </c>
+      <c r="N122" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P122" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q122" s="17" t="inlineStr">
+        <is>
+          <t>UAPB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B123" s="12" t="inlineStr">
+        <is>
+          <t>INST @ PUR</t>
+        </is>
+      </c>
+      <c r="C123" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-04 23:00</t>
+        </is>
+      </c>
+      <c r="D123" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" s="12" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="F123" s="12" t="inlineStr">
+        <is>
+          <t>PUR -35.5</t>
+        </is>
+      </c>
+      <c r="G123" s="23" t="n">
+        <v>-35.5</v>
+      </c>
+      <c r="H123" s="13" t="n">
+        <v>-112</v>
+      </c>
+      <c r="I123" s="15" t="n">
+        <v>0.2539608529598711</v>
+      </c>
+      <c r="J123" s="15" t="n">
+        <v>0.5043297540699688</v>
+      </c>
+      <c r="K123" s="15" t="n">
+        <v>0.5283018867924528</v>
+      </c>
+      <c r="L123" s="14" t="n">
+        <v>-0.2743410338325817</v>
+      </c>
+      <c r="M123" s="14" t="n">
+        <v>-0.5192883854688154</v>
+      </c>
+      <c r="N123" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P123" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q123" s="12" t="inlineStr">
+        <is>
+          <t>INST isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B124" s="17" t="inlineStr">
+        <is>
+          <t>EIU @ MINN</t>
+        </is>
+      </c>
+      <c r="C124" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-04 00:00</t>
+        </is>
+      </c>
+      <c r="D124" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" s="17" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="F124" s="17" t="inlineStr">
+        <is>
+          <t>MINN -43.5</t>
+        </is>
+      </c>
+      <c r="G124" s="26" t="n">
+        <v>-43.5</v>
+      </c>
+      <c r="H124" s="18" t="n">
+        <v>-112</v>
+      </c>
+      <c r="I124" s="20" t="n">
+        <v>0.2525065802931694</v>
+      </c>
+      <c r="J124" s="20" t="n">
+        <v>0.5043297540699688</v>
+      </c>
+      <c r="K124" s="20" t="n">
+        <v>0.5283018867924528</v>
+      </c>
+      <c r="L124" s="19" t="n">
+        <v>-0.2757953064992834</v>
+      </c>
+      <c r="M124" s="19" t="n">
+        <v>-0.5220411158736437</v>
+      </c>
+      <c r="N124" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P124" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q124" s="17" t="inlineStr">
+        <is>
+          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -6392,7 +9037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -6513,12 +9158,12 @@
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>HAW @ STAN</t>
+          <t>COLO @ GT</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -6528,14 +9173,14 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
+          <t>Over 50.5</t>
         </is>
       </c>
       <c r="E6" s="13" t="n">
-        <v>-105</v>
+        <v>-115</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>21.5</v>
+        <v>21</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -6560,13 +9205,13 @@
         </is>
       </c>
       <c r="L6" s="14" t="n">
-        <v>0.0834</v>
+        <v>0.0784</v>
       </c>
       <c r="M6" s="14" t="n"/>
       <c r="N6" s="12" t="n"/>
       <c r="O6" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>
@@ -6578,24 +9223,24 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>SAC @ EMU</t>
+          <t>HAW @ STAN</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t>SAC ML</t>
+          <t>Over 49.5</t>
         </is>
       </c>
       <c r="E7" s="18" t="n">
-        <v>280</v>
+        <v>-105</v>
       </c>
       <c r="F7" s="21" t="n">
-        <v>18</v>
+        <v>21.5</v>
       </c>
       <c r="G7" s="17" t="inlineStr">
         <is>
@@ -6620,7 +9265,7 @@
         </is>
       </c>
       <c r="L7" s="19" t="n">
-        <v>0.1055</v>
+        <v>0.0834</v>
       </c>
       <c r="M7" s="19" t="n"/>
       <c r="N7" s="17" t="n"/>
@@ -6638,24 +9283,24 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>SAC @ EMU</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>UNC +7.5</t>
+          <t>SAC ML</t>
         </is>
       </c>
       <c r="E8" s="13" t="n">
-        <v>-108</v>
+        <v>280</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -6680,11 +9325,71 @@
         </is>
       </c>
       <c r="L8" s="14" t="n">
-        <v>0.0801</v>
+        <v>0.1055</v>
       </c>
       <c r="M8" s="14" t="n"/>
       <c r="N8" s="12" t="n"/>
       <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t>Draft Kings</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>UNC @ TCU</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>UNC +7.5</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>-108</v>
+      </c>
+      <c r="F9" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="G9" s="17" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H9" s="21">
+        <f>IF(OR($G9="",$G9="Pending"),"",ROUND(IF($G9="Win",IF($E9&gt;0,$F9*$E9/100,$F9*100/-$E9),IF($G9="Loss",-$F9,0)),2))</f>
+        <v/>
+      </c>
+      <c r="I9" s="21">
+        <f>Settings!$B$5+SUM($H$6:$H9)</f>
+        <v/>
+      </c>
+      <c r="J9" s="19">
+        <f>IFERROR(SUM($H$6:$H9)/SUMIF($G$6:$G9,"&lt;&gt;Pending",$F$6:$F9),"")</f>
+        <v/>
+      </c>
+      <c r="K9" s="17" t="inlineStr">
+        <is>
+          <t>LEAN</t>
+        </is>
+      </c>
+      <c r="L9" s="19" t="n">
+        <v>0.0801</v>
+      </c>
+      <c r="M9" s="19" t="n"/>
+      <c r="N9" s="17" t="n"/>
+      <c r="O9" s="17" t="inlineStr">
         <is>
           <t>Draft Kings</t>
         </is>
@@ -13526,16 +16231,16 @@
       </c>
       <c r="H10" s="17" t="inlineStr"/>
       <c r="I10" s="26" t="n">
-        <v>-5.5</v>
+        <v>-4</v>
       </c>
       <c r="J10" s="30" t="n">
         <v>48.5</v>
       </c>
       <c r="K10" s="18" t="n">
-        <v>180</v>
+        <v>154</v>
       </c>
       <c r="L10" s="18" t="n">
-        <v>-218</v>
+        <v>-185</v>
       </c>
       <c r="M10" s="17" t="inlineStr">
         <is>
@@ -13627,7 +16332,7 @@
         <v>-5.5</v>
       </c>
       <c r="J12" s="30" t="n">
-        <v>57.5</v>
+        <v>56.5</v>
       </c>
       <c r="K12" s="18" t="n">
         <v>180</v>
@@ -14197,11 +16902,23 @@
         </is>
       </c>
       <c r="H24" s="17" t="inlineStr"/>
-      <c r="I24" s="26" t="n"/>
-      <c r="J24" s="30" t="n"/>
-      <c r="K24" s="18" t="n"/>
-      <c r="L24" s="18" t="n"/>
-      <c r="M24" s="17" t="n"/>
+      <c r="I24" s="26" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="J24" s="30" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="K24" s="18" t="n">
+        <v>180</v>
+      </c>
+      <c r="L24" s="18" t="n">
+        <v>-218</v>
+      </c>
+      <c r="M24" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
@@ -14234,11 +16951,19 @@
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr"/>
-      <c r="I25" s="23" t="n"/>
-      <c r="J25" s="29" t="n"/>
+      <c r="I25" s="23" t="n">
+        <v>-35.5</v>
+      </c>
+      <c r="J25" s="29" t="n">
+        <v>56.5</v>
+      </c>
       <c r="K25" s="13" t="n"/>
       <c r="L25" s="13" t="n"/>
-      <c r="M25" s="12" t="n"/>
+      <c r="M25" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="17" t="inlineStr">
@@ -14271,11 +16996,23 @@
         </is>
       </c>
       <c r="H26" s="17" t="inlineStr"/>
-      <c r="I26" s="26" t="n"/>
-      <c r="J26" s="30" t="n"/>
-      <c r="K26" s="18" t="n"/>
-      <c r="L26" s="18" t="n"/>
-      <c r="M26" s="17" t="n"/>
+      <c r="I26" s="26" t="n">
+        <v>-28.5</v>
+      </c>
+      <c r="J26" s="30" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="K26" s="18" t="n">
+        <v>1800</v>
+      </c>
+      <c r="L26" s="18" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="M26" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
@@ -14308,11 +17045,19 @@
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr"/>
-      <c r="I27" s="23" t="n"/>
-      <c r="J27" s="29" t="n"/>
+      <c r="I27" s="23" t="n">
+        <v>-41.5</v>
+      </c>
+      <c r="J27" s="29" t="n">
+        <v>50.5</v>
+      </c>
       <c r="K27" s="13" t="n"/>
       <c r="L27" s="13" t="n"/>
-      <c r="M27" s="12" t="n"/>
+      <c r="M27" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="17" t="inlineStr">
@@ -14345,11 +17090,19 @@
         </is>
       </c>
       <c r="H28" s="17" t="inlineStr"/>
-      <c r="I28" s="26" t="n"/>
-      <c r="J28" s="30" t="n"/>
+      <c r="I28" s="26" t="n">
+        <v>-38.5</v>
+      </c>
+      <c r="J28" s="30" t="n">
+        <v>53.5</v>
+      </c>
       <c r="K28" s="18" t="n"/>
       <c r="L28" s="18" t="n"/>
-      <c r="M28" s="17" t="n"/>
+      <c r="M28" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
@@ -14382,11 +17135,23 @@
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr"/>
-      <c r="I29" s="23" t="n"/>
-      <c r="J29" s="29" t="n"/>
-      <c r="K29" s="13" t="n"/>
-      <c r="L29" s="13" t="n"/>
-      <c r="M29" s="12" t="n"/>
+      <c r="I29" s="23" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J29" s="29" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="K29" s="13" t="n">
+        <v>320</v>
+      </c>
+      <c r="L29" s="13" t="n">
+        <v>-410</v>
+      </c>
+      <c r="M29" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="17" t="inlineStr">
@@ -14419,11 +17184,23 @@
         </is>
       </c>
       <c r="H30" s="17" t="inlineStr"/>
-      <c r="I30" s="26" t="n"/>
-      <c r="J30" s="30" t="n"/>
-      <c r="K30" s="18" t="n"/>
-      <c r="L30" s="18" t="n"/>
-      <c r="M30" s="17" t="n"/>
+      <c r="I30" s="26" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="J30" s="30" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="K30" s="18" t="n">
+        <v>-3200</v>
+      </c>
+      <c r="L30" s="18" t="n">
+        <v>1400</v>
+      </c>
+      <c r="M30" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
@@ -14456,11 +17233,23 @@
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr"/>
-      <c r="I31" s="23" t="n"/>
-      <c r="J31" s="29" t="n"/>
-      <c r="K31" s="13" t="n"/>
-      <c r="L31" s="13" t="n"/>
-      <c r="M31" s="12" t="n"/>
+      <c r="I31" s="23" t="n">
+        <v>-22.5</v>
+      </c>
+      <c r="J31" s="29" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="K31" s="13" t="n">
+        <v>1400</v>
+      </c>
+      <c r="L31" s="13" t="n">
+        <v>-3200</v>
+      </c>
+      <c r="M31" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
@@ -49208,7 +51997,7 @@
         </is>
       </c>
       <c r="B4" s="39" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -49228,7 +52017,7 @@
         </is>
       </c>
       <c r="B6" s="39" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">

--- a/NCAAF_Edge_Model.xlsx
+++ b/NCAAF_Edge_Model.xlsx
@@ -271,8 +271,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BoardTable" displayName="BoardTable" ref="A4:Q124" headerRowCount="1">
-  <autoFilter ref="A4:Q124"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BoardTable" displayName="BoardTable" ref="A4:Q126" headerRowCount="1">
+  <autoFilter ref="A4:Q126"/>
   <tableColumns count="17">
     <tableColumn id="1" name="Tier"/>
     <tableColumn id="2" name="Game"/>
@@ -640,7 +640,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-25T05:00:08+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
+          <t>Generated 2026-08-25T15:27:48+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
         </is>
       </c>
     </row>
@@ -1003,13 +1003,13 @@
         </is>
       </c>
       <c r="E21" s="13" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>0.1054642923135784</v>
+        <v>0.1125135396003096</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>0.3686221870504205</v>
+        <v>0.3625135396003096</v>
       </c>
       <c r="H21" s="16" t="n"/>
       <c r="I21" s="12" t="inlineStr">
@@ -1036,17 +1036,17 @@
       </c>
       <c r="D22" s="17" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>Over 49.5</t>
         </is>
       </c>
       <c r="E22" s="18" t="n">
-        <v>-112</v>
+        <v>-105</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>0.0917323188370931</v>
+        <v>0.08339809109262664</v>
       </c>
       <c r="G22" s="20" t="n">
-        <v>0.6200342056295459</v>
+        <v>0.5955932130438462</v>
       </c>
       <c r="H22" s="21" t="n"/>
       <c r="I22" s="17" t="inlineStr">
@@ -1077,13 +1077,13 @@
         </is>
       </c>
       <c r="E23" s="13" t="n">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0.08386062118588167</v>
+        <v>0.08007721496452191</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0.5960557431371012</v>
+        <v>0.5993079841952912</v>
       </c>
       <c r="H23" s="16" t="n"/>
       <c r="I23" s="12" t="inlineStr">
@@ -1140,7 +1140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q124"/>
+  <dimension ref="A1:Q126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1294,22 +1294,22 @@
       </c>
       <c r="G5" s="23" t="n"/>
       <c r="H5" s="13" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="I5" s="15" t="n">
-        <v>0.3686221870504205</v>
+        <v>0.3625135396003096</v>
       </c>
       <c r="J5" s="15" t="n">
-        <v>0.2522172949002217</v>
+        <v>0.24</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.25</v>
       </c>
       <c r="L5" s="14" t="n">
-        <v>0.1054642923135784</v>
+        <v>0.1125135396003096</v>
       </c>
       <c r="M5" s="14" t="n">
-        <v>0.4007643107915979</v>
+        <v>0.4500541584012385</v>
       </c>
       <c r="N5" s="15" t="n">
         <v>0</v>
@@ -1350,29 +1350,29 @@
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>Over 49.5</t>
         </is>
       </c>
       <c r="G6" s="26" t="n">
-        <v>48.5</v>
+        <v>49.5</v>
       </c>
       <c r="H6" s="18" t="n">
-        <v>-112</v>
+        <v>-105</v>
       </c>
       <c r="I6" s="20" t="n">
-        <v>0.6200342056295459</v>
+        <v>0.5955932130438462</v>
       </c>
       <c r="J6" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K6" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L6" s="19" t="n">
-        <v>0.0917323188370931</v>
+        <v>0.08339809109262664</v>
       </c>
       <c r="M6" s="19" t="n">
-        <v>0.1736361749416404</v>
+        <v>0.1628248445141758</v>
       </c>
       <c r="N6" s="20" t="n">
         <v>0</v>
@@ -1420,22 +1420,22 @@
         <v>-7.5</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>0.5960557431371012</v>
+        <v>0.5993079841952912</v>
       </c>
       <c r="J7" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K7" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L7" s="14" t="n">
-        <v>0.08386062118588167</v>
+        <v>0.08007721496452191</v>
       </c>
       <c r="M7" s="14" t="n">
-        <v>0.1637278794581499</v>
+        <v>0.1542227843761165</v>
       </c>
       <c r="N7" s="15" t="n">
         <v>0</v>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>EIU @ MINN</t>
+          <t>INST @ PUR</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-09-04 23:00</t>
         </is>
       </c>
       <c r="D9" s="22" t="n">
@@ -1539,17 +1539,17 @@
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>EIU +43.5</t>
+          <t>INST +35.5</t>
         </is>
       </c>
       <c r="G9" s="23" t="n">
-        <v>-43.5</v>
+        <v>-35.5</v>
       </c>
       <c r="H9" s="13" t="n">
         <v>-108</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>0.7474934197068306</v>
+        <v>0.7460391470401289</v>
       </c>
       <c r="J9" s="15" t="n">
         <v>0.4956702459300312</v>
@@ -1558,10 +1558,10 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L9" s="14" t="n">
-        <v>0.2282626504760613</v>
+        <v>0.2268083778093596</v>
       </c>
       <c r="M9" s="14" t="n">
-        <v>0.4396169564724145</v>
+        <v>0.4368161350402483</v>
       </c>
       <c r="N9" s="15" t="n">
         <v>0</v>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="Q9" s="12" t="inlineStr">
         <is>
-          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>INST isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -1588,12 +1588,12 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>INST @ PUR</t>
+          <t>EIU @ MINN</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 23:00</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D10" s="25" t="n">
@@ -1606,29 +1606,29 @@
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t>INST +35.5</t>
+          <t>EIU +43.5</t>
         </is>
       </c>
       <c r="G10" s="26" t="n">
-        <v>-35.5</v>
+        <v>-43.5</v>
       </c>
       <c r="H10" s="18" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I10" s="20" t="n">
-        <v>0.7460391470401289</v>
+        <v>0.7496582967418151</v>
       </c>
       <c r="J10" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5</v>
       </c>
       <c r="K10" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L10" s="19" t="n">
-        <v>0.2268083778093596</v>
+        <v>0.2258487729322912</v>
       </c>
       <c r="M10" s="19" t="n">
-        <v>0.4368161350402483</v>
+        <v>0.4311658392343742</v>
       </c>
       <c r="N10" s="20" t="n">
         <v>0</v>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="Q10" s="17" t="inlineStr">
         <is>
-          <t>INST isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -1655,12 +1655,12 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>UAPB @ MIZ</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D11" s="22" t="n">
@@ -1673,17 +1673,17 @@
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>UAPB +54.5</t>
+          <t>SJSU +38.5</t>
         </is>
       </c>
       <c r="G11" s="23" t="n">
-        <v>-54.5</v>
+        <v>-38.5</v>
       </c>
       <c r="H11" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>0.749981952327064</v>
+        <v>0.7476789160487953</v>
       </c>
       <c r="J11" s="15" t="n">
         <v>0.5</v>
@@ -1692,10 +1692,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L11" s="14" t="n">
-        <v>0.2261724285175402</v>
+        <v>0.2238693922392715</v>
       </c>
       <c r="M11" s="14" t="n">
-        <v>0.4317837271698495</v>
+        <v>0.4273870215477003</v>
       </c>
       <c r="N11" s="15" t="n">
         <v>0</v>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="Q11" s="12" t="inlineStr">
         <is>
-          <t>UAPB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -1722,12 +1722,12 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>BCU @ UCF</t>
+          <t>UAPB @ MIZ</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D12" s="25" t="n">
@@ -1740,17 +1740,17 @@
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>BCU +42.5</t>
+          <t>UAPB +54.5</t>
         </is>
       </c>
       <c r="G12" s="26" t="n">
-        <v>-42.5</v>
+        <v>-54.5</v>
       </c>
       <c r="H12" s="18" t="n">
         <v>-112</v>
       </c>
       <c r="I12" s="20" t="n">
-        <v>0.7517481901856816</v>
+        <v>0.7521468293620484</v>
       </c>
       <c r="J12" s="20" t="n">
         <v>0.5043297540699688</v>
@@ -1759,10 +1759,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L12" s="19" t="n">
-        <v>0.2234463033932288</v>
+        <v>0.2238449425695955</v>
       </c>
       <c r="M12" s="19" t="n">
-        <v>0.4229519314228973</v>
+        <v>0.4237064984353057</v>
       </c>
       <c r="N12" s="20" t="n">
         <v>0</v>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="Q12" s="17" t="inlineStr">
         <is>
-          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>UAPB isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>IDHO @ UTAH</t>
+          <t>BCU @ UCF</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 01:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D13" s="22" t="n">
@@ -1807,29 +1807,29 @@
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>IDHO +33.5</t>
+          <t>BCU +42.5</t>
         </is>
       </c>
       <c r="G13" s="23" t="n">
-        <v>-33.5</v>
+        <v>-42.5</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>-108</v>
+        <v>-115</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>0.7414791527526444</v>
+        <v>0.7550004312438716</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L13" s="14" t="n">
-        <v>0.2222483835218751</v>
+        <v>0.2201167103136391</v>
       </c>
       <c r="M13" s="14" t="n">
-        <v>0.4280339238199079</v>
+        <v>0.4115225453689773</v>
       </c>
       <c r="N13" s="15" t="n">
         <v>0</v>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Q13" s="12" t="inlineStr">
         <is>
-          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -1856,12 +1856,12 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>NCAT @ GAST</t>
+          <t>IDHO @ UTAH</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 23:00</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D14" s="25" t="n">
@@ -1874,29 +1874,29 @@
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t>NCAT +28.5</t>
+          <t>IDHO +33.5</t>
         </is>
       </c>
       <c r="G14" s="26" t="n">
-        <v>-28.5</v>
+        <v>-33.5</v>
       </c>
       <c r="H14" s="18" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I14" s="20" t="n">
-        <v>0.7409568774443602</v>
+        <v>0.7436440297876288</v>
       </c>
       <c r="J14" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5</v>
       </c>
       <c r="K14" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L14" s="19" t="n">
-        <v>0.221726108213591</v>
+        <v>0.2198345059781049</v>
       </c>
       <c r="M14" s="19" t="n">
-        <v>0.4270280602632124</v>
+        <v>0.4196840568672914</v>
       </c>
       <c r="N14" s="20" t="n">
         <v>0</v>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="Q14" s="17" t="inlineStr">
         <is>
-          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -1990,12 +1990,12 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>MASS @ RUTG</t>
+          <t>NCAT @ GAST</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 22:00</t>
+          <t>2026-09-04 23:00</t>
         </is>
       </c>
       <c r="D16" s="25" t="n">
@@ -2008,29 +2008,29 @@
       </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
-          <t>MASS +30.5</t>
+          <t>NCAT +28.5</t>
         </is>
       </c>
       <c r="G16" s="26" t="n">
-        <v>-30.5</v>
+        <v>-28.5</v>
       </c>
       <c r="H16" s="18" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I16" s="20" t="n">
-        <v>0.7362293114467701</v>
+        <v>0.7431217544793447</v>
       </c>
       <c r="J16" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5</v>
       </c>
       <c r="K16" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L16" s="19" t="n">
-        <v>0.2169985422160008</v>
+        <v>0.2193122306698209</v>
       </c>
       <c r="M16" s="19" t="n">
-        <v>0.4179231183419276</v>
+        <v>0.4186869858242036</v>
       </c>
       <c r="N16" s="20" t="n">
         <v>0</v>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="Q16" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -2057,12 +2057,12 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>NMSU @ FSU</t>
+          <t>MASS @ RUTG</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-03 22:00</t>
         </is>
       </c>
       <c r="D17" s="22" t="n">
@@ -2075,29 +2075,29 @@
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>NMSU +31.5</t>
+          <t>MASS +30.5</t>
         </is>
       </c>
       <c r="G17" s="23" t="n">
-        <v>-31.5</v>
+        <v>-30.5</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>0.7484052544756881</v>
+        <v>0.7362293114467701</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K17" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L17" s="14" t="n">
-        <v>0.2135215335454556</v>
+        <v>0.2169985422160008</v>
       </c>
       <c r="M17" s="14" t="n">
-        <v>0.3991924322806341</v>
+        <v>0.4179231183419276</v>
       </c>
       <c r="N17" s="15" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>NMSU @ FSU</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D18" s="25" t="n">
@@ -2142,29 +2142,29 @@
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>SJSU +38.5</t>
+          <t>NMSU +31.5</t>
         </is>
       </c>
       <c r="G18" s="26" t="n">
-        <v>-38.5</v>
+        <v>-31.5</v>
       </c>
       <c r="H18" s="18" t="n">
-        <v>-120</v>
+        <v>-115</v>
       </c>
       <c r="I18" s="20" t="n">
-        <v>0.7585484812661867</v>
+        <v>0.7484052544756881</v>
       </c>
       <c r="J18" s="20" t="n">
-        <v>0.5217391304347826</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K18" s="20" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L18" s="19" t="n">
-        <v>0.2130939358116413</v>
+        <v>0.2135215335454556</v>
       </c>
       <c r="M18" s="19" t="n">
-        <v>0.3906722156546757</v>
+        <v>0.3991924322806341</v>
       </c>
       <c r="N18" s="20" t="n">
         <v>0</v>
@@ -2281,22 +2281,22 @@
         <v>-24.5</v>
       </c>
       <c r="H20" s="18" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I20" s="20" t="n">
-        <v>0.7342550223888921</v>
+        <v>0.7320901453539077</v>
       </c>
       <c r="J20" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K20" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L20" s="19" t="n">
-        <v>0.2059531355964392</v>
+        <v>0.2082806215443839</v>
       </c>
       <c r="M20" s="19" t="n">
-        <v>0.3898398638075457</v>
+        <v>0.3976266411301875</v>
       </c>
       <c r="N20" s="20" t="n">
         <v>0</v>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>UAB @ ILL</t>
+          <t>MRMK @ DEL</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 01:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D21" s="22" t="n">
@@ -2336,34 +2336,32 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>UAB +28.5</t>
-        </is>
-      </c>
-      <c r="G21" s="23" t="n">
-        <v>-28.5</v>
-      </c>
+          <t>MRMK ML</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="n"/>
       <c r="H21" s="13" t="n">
-        <v>-118</v>
+        <v>3500</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>0.7438096015477024</v>
+        <v>0.2320231923220626</v>
       </c>
       <c r="J21" s="15" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.02715849209566274</v>
       </c>
       <c r="K21" s="15" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="L21" s="14" t="n">
-        <v>0.2025251978779776</v>
+        <v>0.2042454145442848</v>
       </c>
       <c r="M21" s="14" t="n">
-        <v>0.3741567215033823</v>
+        <v>7.352834923594253</v>
       </c>
       <c r="N21" s="15" t="n">
         <v>0</v>
@@ -2378,7 +2376,7 @@
       </c>
       <c r="Q21" s="12" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -2390,12 +2388,12 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>MRMK @ DEL</t>
+          <t>UAB @ ILL</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D22" s="25" t="n">
@@ -2403,32 +2401,34 @@
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F22" s="17" t="inlineStr">
         <is>
-          <t>MRMK ML</t>
-        </is>
-      </c>
-      <c r="G22" s="26" t="n"/>
+          <t>UAB +28.5</t>
+        </is>
+      </c>
+      <c r="G22" s="26" t="n">
+        <v>-28.5</v>
+      </c>
       <c r="H22" s="18" t="n">
-        <v>3000</v>
+        <v>-118</v>
       </c>
       <c r="I22" s="20" t="n">
-        <v>0.2342202661742625</v>
+        <v>0.7438096015477024</v>
       </c>
       <c r="J22" s="20" t="n">
-        <v>0.03155263980006248</v>
+        <v>0.5173641257162701</v>
       </c>
       <c r="K22" s="20" t="n">
-        <v>0.03225806451612903</v>
+        <v>0.5412844036697247</v>
       </c>
       <c r="L22" s="19" t="n">
-        <v>0.2019622016581335</v>
+        <v>0.2025251978779776</v>
       </c>
       <c r="M22" s="19" t="n">
-        <v>6.260828251402137</v>
+        <v>0.3741567215033823</v>
       </c>
       <c r="N22" s="20" t="n">
         <v>0</v>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="Q22" s="17" t="inlineStr">
         <is>
-          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -2742,22 +2742,22 @@
       </c>
       <c r="G27" s="23" t="n"/>
       <c r="H27" s="13" t="n">
-        <v>2000</v>
+        <v>2200</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>0.2189772153156186</v>
+        <v>0.2169991880608585</v>
       </c>
       <c r="J27" s="15" t="n">
-        <v>0.0461215932914046</v>
+        <v>0.04216553878188443</v>
       </c>
       <c r="K27" s="15" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="L27" s="14" t="n">
-        <v>0.171358167696571</v>
+        <v>0.1735209271912933</v>
       </c>
       <c r="M27" s="14" t="n">
-        <v>3.598521521627991</v>
+        <v>3.990981325399745</v>
       </c>
       <c r="N27" s="15" t="n">
         <v>0</v>
@@ -2784,12 +2784,12 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>UAB @ ILL</t>
+          <t>AKR @ WAKE</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 01:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D28" s="25" t="n">
@@ -2802,27 +2802,27 @@
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>UAB ML</t>
+          <t>AKR ML</t>
         </is>
       </c>
       <c r="G28" s="26" t="n"/>
       <c r="H28" s="18" t="n">
-        <v>3000</v>
+        <v>1400</v>
       </c>
       <c r="I28" s="20" t="n">
-        <v>0.1964375380312305</v>
+        <v>0.2287754942280706</v>
       </c>
       <c r="J28" s="20" t="n">
-        <v>0.03155263980006248</v>
+        <v>0.06432748538011696</v>
       </c>
       <c r="K28" s="20" t="n">
-        <v>0.03225806451612903</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="L28" s="19" t="n">
-        <v>0.1641794735151015</v>
+        <v>0.162108827561404</v>
       </c>
       <c r="M28" s="19" t="n">
-        <v>5.089563678968147</v>
+        <v>2.43163241342106</v>
       </c>
       <c r="N28" s="20" t="n">
         <v>0</v>
@@ -2849,12 +2849,12 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>AKR @ WAKE</t>
+          <t>IDHO @ UTAH</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D29" s="22" t="n">
@@ -2867,27 +2867,27 @@
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>AKR ML</t>
+          <t>IDHO ML</t>
         </is>
       </c>
       <c r="G29" s="23" t="n"/>
       <c r="H29" s="13" t="n">
-        <v>1300</v>
+        <v>3000</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>0.2310535567636653</v>
+        <v>0.1915726544041398</v>
       </c>
       <c r="J29" s="15" t="n">
-        <v>0.06888361045130641</v>
+        <v>0.03155263980006248</v>
       </c>
       <c r="K29" s="15" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="L29" s="14" t="n">
-        <v>0.1596249853350939</v>
+        <v>0.1593145898880108</v>
       </c>
       <c r="M29" s="14" t="n">
-        <v>2.234749794691315</v>
+        <v>4.938752286528335</v>
       </c>
       <c r="N29" s="15" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="Q29" s="12" t="inlineStr">
         <is>
-          <t>price outside allowed range</t>
+          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>IDHO @ UTAH</t>
+          <t>UAB @ ILL</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
@@ -2932,27 +2932,27 @@
       </c>
       <c r="F30" s="17" t="inlineStr">
         <is>
-          <t>IDHO ML</t>
+          <t>UAB ML</t>
         </is>
       </c>
       <c r="G30" s="26" t="n"/>
       <c r="H30" s="18" t="n">
-        <v>3000</v>
+        <v>2200</v>
       </c>
       <c r="I30" s="20" t="n">
-        <v>0.1915726544041398</v>
+        <v>0.2017439875221416</v>
       </c>
       <c r="J30" s="20" t="n">
-        <v>0.03155263980006248</v>
+        <v>0.04216553878188443</v>
       </c>
       <c r="K30" s="20" t="n">
-        <v>0.03225806451612903</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>0.1593145898880108</v>
+        <v>0.1582657266525764</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>4.938752286528335</v>
+        <v>3.640111713009257</v>
       </c>
       <c r="N30" s="20" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="Q30" s="17" t="inlineStr">
         <is>
-          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>price outside allowed range</t>
         </is>
       </c>
     </row>
@@ -3129,32 +3129,32 @@
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>SAC +9.5</t>
+          <t>SAC +10</t>
         </is>
       </c>
       <c r="G33" s="23" t="n">
-        <v>-9.5</v>
+        <v>-10</v>
       </c>
       <c r="H33" s="13" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>0.6318870908174474</v>
+        <v>0.6496086093420973</v>
       </c>
       <c r="J33" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5</v>
       </c>
       <c r="K33" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L33" s="14" t="n">
-        <v>0.1196919688662279</v>
+        <v>0.1257990855325735</v>
       </c>
       <c r="M33" s="14" t="n">
-        <v>0.2336843201673974</v>
+        <v>0.2327670346937839</v>
       </c>
       <c r="N33" s="15" t="n">
-        <v>0</v>
+        <v>0.0308</v>
       </c>
       <c r="O33" s="24" t="n">
         <v>0.45</v>
@@ -3203,22 +3203,22 @@
         <v>48.5</v>
       </c>
       <c r="H34" s="18" t="n">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="I34" s="20" t="n">
-        <v>0.6205016550348365</v>
+        <v>0.6237538960930264</v>
       </c>
       <c r="J34" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K34" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L34" s="19" t="n">
-        <v>0.1083065330836169</v>
+        <v>0.1045231268622572</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>0.2114556122108712</v>
+        <v>0.2013037998828658</v>
       </c>
       <c r="N34" s="20" t="n">
         <v>0</v>
@@ -3513,12 +3513,12 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>AKR @ WAKE</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D39" s="22" t="n">
@@ -3526,34 +3526,32 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
-        </is>
-      </c>
-      <c r="G39" s="23" t="n">
-        <v>49.5</v>
-      </c>
+          <t>UNC ML</t>
+        </is>
+      </c>
+      <c r="G39" s="23" t="n"/>
       <c r="H39" s="13" t="n">
-        <v>-112</v>
+        <v>250</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>0.603175208172005</v>
+        <v>0.3621290026789783</v>
       </c>
       <c r="J39" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.274247491638796</v>
       </c>
       <c r="K39" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="L39" s="14" t="n">
-        <v>0.07487332137955216</v>
+        <v>0.0764147169646926</v>
       </c>
       <c r="M39" s="14" t="n">
-        <v>0.1417245011827237</v>
+        <v>0.267451509376424</v>
       </c>
       <c r="N39" s="15" t="n">
         <v>0</v>
@@ -3576,12 +3574,12 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>AKR @ WAKE</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D40" s="25" t="n">
@@ -3589,32 +3587,34 @@
       </c>
       <c r="E40" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F40" s="17" t="inlineStr">
         <is>
-          <t>UNC ML</t>
-        </is>
-      </c>
-      <c r="G40" s="26" t="n"/>
+          <t>Over 49.5</t>
+        </is>
+      </c>
+      <c r="G40" s="26" t="n">
+        <v>49.5</v>
+      </c>
       <c r="H40" s="18" t="n">
-        <v>240</v>
+        <v>-112</v>
       </c>
       <c r="I40" s="20" t="n">
-        <v>0.3660199960886052</v>
+        <v>0.603175208172005</v>
       </c>
       <c r="J40" s="20" t="n">
-        <v>0.2820294784580499</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K40" s="20" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L40" s="19" t="n">
-        <v>0.07190234902978171</v>
+        <v>0.07487332137955216</v>
       </c>
       <c r="M40" s="19" t="n">
-        <v>0.2444679867012578</v>
+        <v>0.1417245011827237</v>
       </c>
       <c r="N40" s="20" t="n">
         <v>0</v>
@@ -3767,12 +3767,12 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>HAW @ STAN</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D43" s="22" t="n">
@@ -3780,37 +3780,37 @@
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>HAW +4</t>
+          <t>Under 60.5</t>
         </is>
       </c>
       <c r="G43" s="23" t="n">
-        <v>-4</v>
+        <v>60.5</v>
       </c>
       <c r="H43" s="13" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>0.5666660811488681</v>
+        <v>0.5606183297218017</v>
       </c>
       <c r="J43" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K43" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L43" s="14" t="n">
-        <v>0.03836419435641525</v>
+        <v>0.04138756049103243</v>
       </c>
       <c r="M43" s="14" t="n">
-        <v>0.07044135577437555</v>
+        <v>0.07970937576050707</v>
       </c>
       <c r="N43" s="15" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="O43" s="24" t="n">
         <v>0.45</v>
@@ -3843,35 +3843,37 @@
       </c>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F44" s="17" t="inlineStr">
         <is>
-          <t>HAW ML</t>
-        </is>
-      </c>
-      <c r="G44" s="26" t="n"/>
+          <t>HAW +4</t>
+        </is>
+      </c>
+      <c r="G44" s="26" t="n">
+        <v>-4</v>
+      </c>
       <c r="H44" s="18" t="n">
-        <v>154</v>
+        <v>-112</v>
       </c>
       <c r="I44" s="20" t="n">
-        <v>0.4319998430736718</v>
+        <v>0.5666660811488681</v>
       </c>
       <c r="J44" s="20" t="n">
-        <v>0.3775334481388264</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K44" s="20" t="n">
-        <v>0.3937007874015748</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L44" s="19" t="n">
-        <v>0.03829905567209696</v>
+        <v>0.03836419435641525</v>
       </c>
       <c r="M44" s="19" t="n">
-        <v>0.09727960140712633</v>
+        <v>0.07044135577437555</v>
       </c>
       <c r="N44" s="20" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="O44" s="27" t="n">
         <v>0.45</v>
@@ -3891,12 +3893,12 @@
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>SJSU @ EMU</t>
+          <t>HAW @ STAN</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 22:30</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D45" s="22" t="n">
@@ -3904,34 +3906,32 @@
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
-          <t>Over 53.5</t>
-        </is>
-      </c>
-      <c r="G45" s="23" t="n">
-        <v>53.5</v>
-      </c>
+          <t>HAW ML</t>
+        </is>
+      </c>
+      <c r="G45" s="23" t="n"/>
       <c r="H45" s="13" t="n">
-        <v>-112</v>
+        <v>154</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>0.559233949493164</v>
+        <v>0.4319998430736718</v>
       </c>
       <c r="J45" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.3775334481388264</v>
       </c>
       <c r="K45" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.3937007874015748</v>
       </c>
       <c r="L45" s="14" t="n">
-        <v>0.03093206270071114</v>
+        <v>0.03829905567209696</v>
       </c>
       <c r="M45" s="14" t="n">
-        <v>0.05854997582634602</v>
+        <v>0.09727960140712633</v>
       </c>
       <c r="N45" s="15" t="n">
         <v>0</v>
@@ -3954,12 +3954,12 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>EIU @ MINN</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D46" s="25" t="n">
@@ -3967,34 +3967,34 @@
       </c>
       <c r="E46" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F46" s="17" t="inlineStr">
         <is>
-          <t>MEM +5.5</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="G46" s="26" t="n">
-        <v>-5.5</v>
+        <v>51.5</v>
       </c>
       <c r="H46" s="18" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="I46" s="20" t="n">
-        <v>0.55184820471133</v>
+        <v>0.5649480897138526</v>
       </c>
       <c r="J46" s="20" t="n">
-        <v>0.5</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K46" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L46" s="19" t="n">
-        <v>0.02803868090180617</v>
+        <v>0.03664620292139975</v>
       </c>
       <c r="M46" s="19" t="n">
-        <v>0.05352839081253913</v>
+        <v>0.0693660269583638</v>
       </c>
       <c r="N46" s="20" t="n">
         <v>0</v>
@@ -4007,7 +4007,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q46" s="17" t="n"/>
+      <c r="Q46" s="17" t="inlineStr">
+        <is>
+          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
@@ -4017,12 +4021,12 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>SJSU @ EMU</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-09-04 22:30</t>
         </is>
       </c>
       <c r="D47" s="22" t="n">
@@ -4030,32 +4034,34 @@
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>MEM ML</t>
-        </is>
-      </c>
-      <c r="G47" s="23" t="n"/>
+          <t>Over 53.5</t>
+        </is>
+      </c>
+      <c r="G47" s="23" t="n">
+        <v>53.5</v>
+      </c>
       <c r="H47" s="13" t="n">
-        <v>180</v>
+        <v>-112</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>0.383035891688529</v>
+        <v>0.559233949493164</v>
       </c>
       <c r="J47" s="15" t="n">
-        <v>0.3425247738043947</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K47" s="15" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L47" s="14" t="n">
-        <v>0.02589303454567188</v>
+        <v>0.03093206270071114</v>
       </c>
       <c r="M47" s="14" t="n">
-        <v>0.07250049672788117</v>
+        <v>0.05854997582634602</v>
       </c>
       <c r="N47" s="15" t="n">
         <v>0</v>
@@ -4078,12 +4084,12 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>COLO @ GT</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D48" s="25" t="n">
@@ -4091,34 +4097,32 @@
       </c>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F48" s="17" t="inlineStr">
         <is>
-          <t>COLO +6.5</t>
-        </is>
-      </c>
-      <c r="G48" s="26" t="n">
-        <v>-6.5</v>
-      </c>
+          <t>MEM ML</t>
+        </is>
+      </c>
+      <c r="G48" s="26" t="n"/>
       <c r="H48" s="18" t="n">
-        <v>-105</v>
+        <v>180</v>
       </c>
       <c r="I48" s="20" t="n">
-        <v>0.5359459352051367</v>
+        <v>0.383035891688529</v>
       </c>
       <c r="J48" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.3425247738043947</v>
       </c>
       <c r="K48" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="L48" s="19" t="n">
-        <v>0.02375081325391715</v>
+        <v>0.02589303454567188</v>
       </c>
       <c r="M48" s="19" t="n">
-        <v>0.0463706354005049</v>
+        <v>0.07250049672788117</v>
       </c>
       <c r="N48" s="20" t="n">
         <v>0</v>
@@ -4141,12 +4145,12 @@
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D49" s="22" t="n">
@@ -4154,34 +4158,34 @@
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
-          <t>Under 59.5</t>
+          <t>NCSU +5.5</t>
         </is>
       </c>
       <c r="G49" s="23" t="n">
-        <v>59.5</v>
+        <v>-5.5</v>
       </c>
       <c r="H49" s="13" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>0.5413851965860426</v>
+        <v>0.5380374278212803</v>
       </c>
       <c r="J49" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K49" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L49" s="14" t="n">
-        <v>0.02215442735527329</v>
+        <v>0.02584230587006076</v>
       </c>
       <c r="M49" s="14" t="n">
-        <v>0.04266778601756349</v>
+        <v>0.05045402574630908</v>
       </c>
       <c r="N49" s="15" t="n">
         <v>0</v>
@@ -4204,12 +4208,12 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D50" s="25" t="n">
@@ -4222,29 +4226,29 @@
       </c>
       <c r="F50" s="17" t="inlineStr">
         <is>
-          <t>NCSU +5.5</t>
+          <t>MEM +5.5</t>
         </is>
       </c>
       <c r="G50" s="26" t="n">
         <v>-5.5</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I50" s="20" t="n">
-        <v>0.5412896688794703</v>
+        <v>0.5540130817463144</v>
       </c>
       <c r="J50" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K50" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L50" s="19" t="n">
-        <v>0.022058899648701</v>
+        <v>0.02571119495386154</v>
       </c>
       <c r="M50" s="19" t="n">
-        <v>0.04248380673083174</v>
+        <v>0.04866761901980932</v>
       </c>
       <c r="N50" s="20" t="n">
         <v>0</v>
@@ -4267,12 +4271,12 @@
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>COLO @ GT</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D51" s="22" t="n">
@@ -4280,32 +4284,34 @@
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
         <is>
-          <t>NCSU ML</t>
-        </is>
-      </c>
-      <c r="G51" s="23" t="n"/>
+          <t>COLO +6.5</t>
+        </is>
+      </c>
+      <c r="G51" s="23" t="n">
+        <v>-6.5</v>
+      </c>
       <c r="H51" s="13" t="n">
-        <v>180</v>
+        <v>-105</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>0.3745807138274095</v>
+        <v>0.5359459352051367</v>
       </c>
       <c r="J51" s="15" t="n">
-        <v>0.3425247738043947</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K51" s="15" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L51" s="14" t="n">
-        <v>0.01743785668455239</v>
+        <v>0.02375081325391715</v>
       </c>
       <c r="M51" s="14" t="n">
-        <v>0.04882599871674664</v>
+        <v>0.0463706354005049</v>
       </c>
       <c r="N51" s="15" t="n">
         <v>0</v>
@@ -4328,12 +4334,12 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>SJSU @ EMU</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 22:30</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D52" s="25" t="n">
@@ -4346,27 +4352,27 @@
       </c>
       <c r="F52" s="17" t="inlineStr">
         <is>
-          <t>SJSU ML</t>
+          <t>NCSU ML</t>
         </is>
       </c>
       <c r="G52" s="26" t="n"/>
       <c r="H52" s="18" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="I52" s="20" t="n">
-        <v>0.3741599606283899</v>
+        <v>0.3714942648294812</v>
       </c>
       <c r="J52" s="20" t="n">
-        <v>0.3425247738043947</v>
+        <v>0.3363518758085381</v>
       </c>
       <c r="K52" s="20" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.3508771929824561</v>
       </c>
       <c r="L52" s="19" t="n">
-        <v>0.0170171034855327</v>
+        <v>0.0206170718470251</v>
       </c>
       <c r="M52" s="19" t="n">
-        <v>0.04764788975949152</v>
+        <v>0.05875865476402153</v>
       </c>
       <c r="N52" s="20" t="n">
         <v>0</v>
@@ -4389,12 +4395,12 @@
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>SJSU @ EMU</t>
+          <t>MRMK @ DEL</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 22:30</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D53" s="22" t="n">
@@ -4402,34 +4408,34 @@
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
-          <t>SJSU +5.5</t>
+          <t>Over 55.5</t>
         </is>
       </c>
       <c r="G53" s="23" t="n">
-        <v>-5.5</v>
+        <v>55.5</v>
       </c>
       <c r="H53" s="13" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>0.5451972766345791</v>
+        <v>0.5416001704595914</v>
       </c>
       <c r="J53" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K53" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L53" s="14" t="n">
-        <v>0.01689538984212624</v>
+        <v>0.01779064665006758</v>
       </c>
       <c r="M53" s="14" t="n">
-        <v>0.03198055934402461</v>
+        <v>0.03396396178649275</v>
       </c>
       <c r="N53" s="15" t="n">
         <v>0</v>
@@ -4442,7 +4448,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q53" s="12" t="n"/>
+      <c r="Q53" s="12" t="inlineStr">
+        <is>
+          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="17" t="inlineStr">
@@ -4452,12 +4462,12 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>COLO @ GT</t>
+          <t>SJSU @ EMU</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-09-04 22:30</t>
         </is>
       </c>
       <c r="D54" s="25" t="n">
@@ -4470,27 +4480,27 @@
       </c>
       <c r="F54" s="17" t="inlineStr">
         <is>
-          <t>COLO ML</t>
+          <t>SJSU ML</t>
         </is>
       </c>
       <c r="G54" s="26" t="n"/>
       <c r="H54" s="18" t="n">
-        <v>205</v>
+        <v>180</v>
       </c>
       <c r="I54" s="20" t="n">
-        <v>0.3446539939839948</v>
+        <v>0.3741599606283899</v>
       </c>
       <c r="J54" s="20" t="n">
-        <v>0.3146067415730336</v>
+        <v>0.3425247738043947</v>
       </c>
       <c r="K54" s="20" t="n">
-        <v>0.3278688524590164</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="L54" s="19" t="n">
-        <v>0.0167851415249784</v>
+        <v>0.0170171034855327</v>
       </c>
       <c r="M54" s="19" t="n">
-        <v>0.05119468165118402</v>
+        <v>0.04764788975949152</v>
       </c>
       <c r="N54" s="20" t="n">
         <v>0</v>
@@ -4513,12 +4523,12 @@
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>SJSU @ EMU</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-09-04 22:30</t>
         </is>
       </c>
       <c r="D55" s="22" t="n">
@@ -4526,34 +4536,34 @@
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
+          <t>SJSU +5.5</t>
         </is>
       </c>
       <c r="G55" s="23" t="n">
-        <v>47.5</v>
+        <v>-5.5</v>
       </c>
       <c r="H55" s="13" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>0.5355234486665263</v>
+        <v>0.5451972766345791</v>
       </c>
       <c r="J55" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K55" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L55" s="14" t="n">
-        <v>0.01629267943575707</v>
+        <v>0.01689538984212624</v>
       </c>
       <c r="M55" s="14" t="n">
-        <v>0.0313784937281249</v>
+        <v>0.03198055934402461</v>
       </c>
       <c r="N55" s="15" t="n">
         <v>0</v>
@@ -4576,12 +4586,12 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>MRMK @ DEL</t>
+          <t>COLO @ GT</t>
         </is>
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
@@ -4589,34 +4599,32 @@
       </c>
       <c r="E56" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F56" s="17" t="inlineStr">
         <is>
-          <t>Over 55.5</t>
-        </is>
-      </c>
-      <c r="G56" s="26" t="n">
-        <v>55.5</v>
-      </c>
+          <t>COLO ML</t>
+        </is>
+      </c>
+      <c r="G56" s="26" t="n"/>
       <c r="H56" s="18" t="n">
-        <v>-112</v>
+        <v>205</v>
       </c>
       <c r="I56" s="20" t="n">
-        <v>0.5437650474945759</v>
+        <v>0.3446539939839948</v>
       </c>
       <c r="J56" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.3146067415730336</v>
       </c>
       <c r="K56" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.3278688524590164</v>
       </c>
       <c r="L56" s="19" t="n">
-        <v>0.01546316070212306</v>
+        <v>0.0167851415249784</v>
       </c>
       <c r="M56" s="19" t="n">
-        <v>0.02926955418616145</v>
+        <v>0.05119468165118402</v>
       </c>
       <c r="N56" s="20" t="n">
         <v>0</v>
@@ -4629,11 +4637,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q56" s="17" t="inlineStr">
-        <is>
-          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q56" s="17" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
@@ -4706,12 +4710,12 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>JVST @ NDSU</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
@@ -4719,32 +4723,34 @@
       </c>
       <c r="E58" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F58" s="17" t="inlineStr">
         <is>
-          <t>JVST ML</t>
-        </is>
-      </c>
-      <c r="G58" s="26" t="n"/>
+          <t>Over 47.5</t>
+        </is>
+      </c>
+      <c r="G58" s="26" t="n">
+        <v>47.5</v>
+      </c>
       <c r="H58" s="18" t="n">
-        <v>210</v>
+        <v>-110</v>
       </c>
       <c r="I58" s="20" t="n">
-        <v>0.3308036085807733</v>
+        <v>0.5376883257015108</v>
       </c>
       <c r="J58" s="20" t="n">
-        <v>0.3092071169459319</v>
+        <v>0.5</v>
       </c>
       <c r="K58" s="20" t="n">
-        <v>0.3225806451612903</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L58" s="19" t="n">
-        <v>0.008222963419482976</v>
+        <v>0.01387880189198698</v>
       </c>
       <c r="M58" s="19" t="n">
-        <v>0.02549118660039718</v>
+        <v>0.02649589452106615</v>
       </c>
       <c r="N58" s="20" t="n">
         <v>0</v>
@@ -4792,22 +4798,22 @@
         <v>53.5</v>
       </c>
       <c r="H59" s="13" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>0.5298211883282545</v>
+        <v>0.5276563112932702</v>
       </c>
       <c r="J59" s="15" t="n">
-        <v>0.5</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K59" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L59" s="14" t="n">
-        <v>0.006011664518730697</v>
+        <v>0.008425542062500901</v>
       </c>
       <c r="M59" s="14" t="n">
-        <v>0.01147681408121326</v>
+        <v>0.01622696989815003</v>
       </c>
       <c r="N59" s="15" t="n">
         <v>0</v>
@@ -4830,12 +4836,12 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>IDHO @ UTAH</t>
+          <t>JVST @ NDSU</t>
         </is>
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 01:00</t>
+          <t>2026-08-29 21:30</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
@@ -4843,34 +4849,32 @@
       </c>
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F60" s="17" t="inlineStr">
         <is>
-          <t>Over 56.5</t>
-        </is>
-      </c>
-      <c r="G60" s="26" t="n">
-        <v>56.5</v>
-      </c>
+          <t>JVST ML</t>
+        </is>
+      </c>
+      <c r="G60" s="26" t="n"/>
       <c r="H60" s="18" t="n">
-        <v>-110</v>
+        <v>210</v>
       </c>
       <c r="I60" s="20" t="n">
-        <v>0.5278465354893196</v>
+        <v>0.3308036085807733</v>
       </c>
       <c r="J60" s="20" t="n">
-        <v>0.5</v>
+        <v>0.3092071169459319</v>
       </c>
       <c r="K60" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.3225806451612903</v>
       </c>
       <c r="L60" s="19" t="n">
-        <v>0.004037011679795754</v>
+        <v>0.008222963419482976</v>
       </c>
       <c r="M60" s="19" t="n">
-        <v>0.007707022297791966</v>
+        <v>0.02549118660039718</v>
       </c>
       <c r="N60" s="20" t="n">
         <v>0</v>
@@ -4883,11 +4887,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q60" s="17" t="inlineStr">
-        <is>
-          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q60" s="17" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>IDHO @ UTAH</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D61" s="22" t="n">
@@ -4922,22 +4922,22 @@
         <v>56.5</v>
       </c>
       <c r="H61" s="13" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>0.5319860620965522</v>
+        <v>0.5278465354893196</v>
       </c>
       <c r="J61" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K61" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L61" s="14" t="n">
-        <v>0.003684175304099369</v>
+        <v>0.004037011679795754</v>
       </c>
       <c r="M61" s="14" t="n">
-        <v>0.006973617539902333</v>
+        <v>0.007707022297791966</v>
       </c>
       <c r="N61" s="15" t="n">
         <v>0</v>
@@ -4950,7 +4950,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q61" s="12" t="n"/>
+      <c r="Q61" s="12" t="inlineStr">
+        <is>
+          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="17" t="inlineStr">
@@ -4960,12 +4964,12 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
@@ -4978,29 +4982,29 @@
       </c>
       <c r="F62" s="17" t="inlineStr">
         <is>
-          <t>Over 53.5</t>
+          <t>Over 56.5</t>
         </is>
       </c>
       <c r="G62" s="26" t="n">
-        <v>53.5</v>
+        <v>56.5</v>
       </c>
       <c r="H62" s="18" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I62" s="20" t="n">
-        <v>0.5177573237293587</v>
+        <v>0.5319860620965522</v>
       </c>
       <c r="J62" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K62" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L62" s="19" t="n">
-        <v>-0.001473445501410597</v>
+        <v>0.003684175304099369</v>
       </c>
       <c r="M62" s="19" t="n">
-        <v>-0.00283774689160543</v>
+        <v>0.006973617539902333</v>
       </c>
       <c r="N62" s="20" t="n">
         <v>0</v>
@@ -5048,22 +5052,22 @@
         <v>56.5</v>
       </c>
       <c r="H63" s="13" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>0.5253393146800545</v>
+        <v>0.5177573195518956</v>
       </c>
       <c r="J63" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K63" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L63" s="14" t="n">
-        <v>-0.00954440625017805</v>
+        <v>-0.00147344967887364</v>
       </c>
       <c r="M63" s="14" t="n">
-        <v>-0.01784388994598524</v>
+        <v>-0.00283775493708982</v>
       </c>
       <c r="N63" s="15" t="n">
         <v>0</v>
@@ -5086,12 +5090,12 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>INST @ PUR</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 23:00</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D64" s="25" t="n">
@@ -5104,17 +5108,17 @@
       </c>
       <c r="F64" s="17" t="inlineStr">
         <is>
-          <t>Under 56.5</t>
+          <t>Over 53.5</t>
         </is>
       </c>
       <c r="G64" s="26" t="n">
-        <v>56.5</v>
+        <v>53.5</v>
       </c>
       <c r="H64" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I64" s="20" t="n">
-        <v>0.5079800413890019</v>
+        <v>0.5199222007643431</v>
       </c>
       <c r="J64" s="20" t="n">
         <v>0.5</v>
@@ -5123,10 +5127,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L64" s="19" t="n">
-        <v>-0.01582948242052196</v>
+        <v>-0.003887323045180691</v>
       </c>
       <c r="M64" s="19" t="n">
-        <v>-0.03021992098463272</v>
+        <v>-0.007421253086253965</v>
       </c>
       <c r="N64" s="20" t="n">
         <v>0</v>
@@ -5139,11 +5143,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q64" s="17" t="inlineStr">
-        <is>
-          <t>INST isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q64" s="17" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="F65" s="12" t="inlineStr">
         <is>
-          <t>Over 56.5</t>
+          <t>Under 56.5</t>
         </is>
       </c>
       <c r="G65" s="23" t="n">
@@ -5181,7 +5181,7 @@
         <v>-110</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>0.4920199586109981</v>
+        <v>0.5079800413890019</v>
       </c>
       <c r="J65" s="15" t="n">
         <v>0.5</v>
@@ -5190,10 +5190,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L65" s="14" t="n">
-        <v>-0.03178956519852572</v>
+        <v>-0.01582948242052196</v>
       </c>
       <c r="M65" s="14" t="n">
-        <v>-0.06068916992445811</v>
+        <v>-0.03021992098463272</v>
       </c>
       <c r="N65" s="15" t="n">
         <v>0</v>
@@ -5220,12 +5220,12 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>UAB @ ILL</t>
+          <t>INST @ PUR</t>
         </is>
       </c>
       <c r="C66" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 01:00</t>
+          <t>2026-09-04 23:00</t>
         </is>
       </c>
       <c r="D66" s="25" t="n">
@@ -5238,29 +5238,29 @@
       </c>
       <c r="F66" s="17" t="inlineStr">
         <is>
-          <t>Under 56.5</t>
+          <t>Over 56.5</t>
         </is>
       </c>
       <c r="G66" s="26" t="n">
         <v>56.5</v>
       </c>
       <c r="H66" s="18" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="I66" s="20" t="n">
-        <v>0.4746606853199455</v>
+        <v>0.4920199586109981</v>
       </c>
       <c r="J66" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5</v>
       </c>
       <c r="K66" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L66" s="19" t="n">
-        <v>-0.03753443663127398</v>
+        <v>-0.03178956519852572</v>
       </c>
       <c r="M66" s="19" t="n">
-        <v>-0.07328151913724923</v>
+        <v>-0.06068916992445811</v>
       </c>
       <c r="N66" s="20" t="n">
         <v>0</v>
@@ -5273,7 +5273,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q66" s="17" t="n"/>
+      <c r="Q66" s="17" t="inlineStr">
+        <is>
+          <t>INST isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
@@ -5308,22 +5312,22 @@
         <v>53.5</v>
       </c>
       <c r="H67" s="13" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>0.4822426762706413</v>
+        <v>0.4800777992356569</v>
       </c>
       <c r="J67" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K67" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L67" s="14" t="n">
-        <v>-0.0460592105218115</v>
+        <v>-0.04373172457386698</v>
       </c>
       <c r="M67" s="14" t="n">
-        <v>-0.08718350563057181</v>
+        <v>-0.08348783782283686</v>
       </c>
       <c r="N67" s="15" t="n">
         <v>0</v>
@@ -5346,12 +5350,12 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>UAB @ ILL</t>
         </is>
       </c>
       <c r="C68" s="17" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D68" s="25" t="n">
@@ -5371,22 +5375,22 @@
         <v>56.5</v>
       </c>
       <c r="H68" s="18" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I68" s="20" t="n">
-        <v>0.4680139379034478</v>
+        <v>0.4822426804481044</v>
       </c>
       <c r="J68" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K68" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L68" s="19" t="n">
-        <v>-0.05121683132732147</v>
+        <v>-0.04605920634434846</v>
       </c>
       <c r="M68" s="19" t="n">
-        <v>-0.09863982329706344</v>
+        <v>-0.08718349772323103</v>
       </c>
       <c r="N68" s="20" t="n">
         <v>0</v>
@@ -5409,12 +5413,12 @@
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>JVST @ NDSU</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D69" s="22" t="n">
@@ -5422,32 +5426,34 @@
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
         <is>
-          <t>NDSU ML</t>
-        </is>
-      </c>
-      <c r="G69" s="23" t="n"/>
+          <t>Under 56.5</t>
+        </is>
+      </c>
+      <c r="G69" s="23" t="n">
+        <v>56.5</v>
+      </c>
       <c r="H69" s="13" t="n">
-        <v>-258</v>
+        <v>-108</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>0.6691963914192267</v>
+        <v>0.4680139379034478</v>
       </c>
       <c r="J69" s="15" t="n">
-        <v>0.6907928830540681</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K69" s="15" t="n">
-        <v>0.7206703910614525</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L69" s="14" t="n">
-        <v>-0.05147399964222577</v>
+        <v>-0.05121683132732147</v>
       </c>
       <c r="M69" s="14" t="n">
-        <v>-0.07142516229425128</v>
+        <v>-0.09863982329706344</v>
       </c>
       <c r="N69" s="15" t="n">
         <v>0</v>
@@ -5470,12 +5476,12 @@
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>IDHO @ UTAH</t>
+          <t>JVST @ NDSU</t>
         </is>
       </c>
       <c r="C70" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 01:00</t>
+          <t>2026-08-29 21:30</t>
         </is>
       </c>
       <c r="D70" s="25" t="n">
@@ -5483,34 +5489,32 @@
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F70" s="17" t="inlineStr">
         <is>
-          <t>Under 56.5</t>
-        </is>
-      </c>
-      <c r="G70" s="26" t="n">
-        <v>56.5</v>
-      </c>
+          <t>NDSU ML</t>
+        </is>
+      </c>
+      <c r="G70" s="26" t="n"/>
       <c r="H70" s="18" t="n">
-        <v>-110</v>
+        <v>-258</v>
       </c>
       <c r="I70" s="20" t="n">
-        <v>0.4721534645106804</v>
+        <v>0.6691963914192267</v>
       </c>
       <c r="J70" s="20" t="n">
-        <v>0.5</v>
+        <v>0.6907928830540681</v>
       </c>
       <c r="K70" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.7206703910614525</v>
       </c>
       <c r="L70" s="19" t="n">
-        <v>-0.05165605929884343</v>
+        <v>-0.05147399964222577</v>
       </c>
       <c r="M70" s="19" t="n">
-        <v>-0.09861611320688279</v>
+        <v>-0.07142516229425128</v>
       </c>
       <c r="N70" s="20" t="n">
         <v>0</v>
@@ -5523,11 +5527,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q70" s="17" t="inlineStr">
-        <is>
-          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q70" s="17" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
@@ -5537,12 +5537,12 @@
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>NMSU @ FSU</t>
+          <t>IDHO @ UTAH</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D71" s="22" t="n">
@@ -5555,17 +5555,17 @@
       </c>
       <c r="F71" s="12" t="inlineStr">
         <is>
-          <t>Under 53.5</t>
+          <t>Under 56.5</t>
         </is>
       </c>
       <c r="G71" s="23" t="n">
-        <v>53.5</v>
+        <v>56.5</v>
       </c>
       <c r="H71" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I71" s="15" t="n">
-        <v>0.4701788116717455</v>
+        <v>0.4721534645106804</v>
       </c>
       <c r="J71" s="15" t="n">
         <v>0.5</v>
@@ -5574,10 +5574,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L71" s="14" t="n">
-        <v>-0.05363071213777837</v>
+        <v>-0.05165605929884343</v>
       </c>
       <c r="M71" s="14" t="n">
-        <v>-0.1023859049903041</v>
+        <v>-0.09861611320688279</v>
       </c>
       <c r="N71" s="15" t="n">
         <v>0</v>
@@ -5590,7 +5590,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q71" s="12" t="n"/>
+      <c r="Q71" s="12" t="inlineStr">
+        <is>
+          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="17" t="inlineStr">
@@ -5600,12 +5604,12 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>COLO @ GT</t>
+          <t>NMSU @ FSU</t>
         </is>
       </c>
       <c r="C72" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D72" s="25" t="n">
@@ -5613,32 +5617,34 @@
       </c>
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F72" s="17" t="inlineStr">
         <is>
-          <t>GT ML</t>
-        </is>
-      </c>
-      <c r="G72" s="26" t="n"/>
+          <t>Under 53.5</t>
+        </is>
+      </c>
+      <c r="G72" s="26" t="n">
+        <v>53.5</v>
+      </c>
       <c r="H72" s="18" t="n">
-        <v>-250</v>
+        <v>-112</v>
       </c>
       <c r="I72" s="20" t="n">
-        <v>0.6553460060160052</v>
+        <v>0.4723436887067298</v>
       </c>
       <c r="J72" s="20" t="n">
-        <v>0.6853932584269663</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K72" s="20" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L72" s="19" t="n">
-        <v>-0.05893970826970907</v>
+        <v>-0.055958198085723</v>
       </c>
       <c r="M72" s="19" t="n">
-        <v>-0.08251559157759275</v>
+        <v>-0.1059208749479757</v>
       </c>
       <c r="N72" s="20" t="n">
         <v>0</v>
@@ -5661,12 +5667,12 @@
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>SJSU @ EMU</t>
+          <t>COLO @ GT</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 22:30</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D73" s="22" t="n">
@@ -5679,27 +5685,27 @@
       </c>
       <c r="F73" s="12" t="inlineStr">
         <is>
-          <t>EMU ML</t>
+          <t>GT ML</t>
         </is>
       </c>
       <c r="G73" s="23" t="n"/>
       <c r="H73" s="13" t="n">
-        <v>-218</v>
+        <v>-250</v>
       </c>
       <c r="I73" s="15" t="n">
-        <v>0.6258400393716101</v>
+        <v>0.6553460060160052</v>
       </c>
       <c r="J73" s="15" t="n">
-        <v>0.6574752261956054</v>
+        <v>0.6853932584269663</v>
       </c>
       <c r="K73" s="15" t="n">
-        <v>0.6855345911949685</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="L73" s="14" t="n">
-        <v>-0.05969455182335837</v>
+        <v>-0.05893970826970907</v>
       </c>
       <c r="M73" s="14" t="n">
-        <v>-0.08707737376067881</v>
+        <v>-0.08251559157759275</v>
       </c>
       <c r="N73" s="15" t="n">
         <v>0</v>
@@ -5722,12 +5728,12 @@
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>SJSU @ EMU</t>
         </is>
       </c>
       <c r="C74" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-09-04 22:30</t>
         </is>
       </c>
       <c r="D74" s="25" t="n">
@@ -5740,7 +5746,7 @@
       </c>
       <c r="F74" s="17" t="inlineStr">
         <is>
-          <t>UVA ML</t>
+          <t>EMU ML</t>
         </is>
       </c>
       <c r="G74" s="26" t="n"/>
@@ -5748,7 +5754,7 @@
         <v>-218</v>
       </c>
       <c r="I74" s="20" t="n">
-        <v>0.6254192861725905</v>
+        <v>0.6258400393716101</v>
       </c>
       <c r="J74" s="20" t="n">
         <v>0.6574752261956054</v>
@@ -5757,10 +5763,10 @@
         <v>0.6855345911949685</v>
       </c>
       <c r="L74" s="19" t="n">
-        <v>-0.06011530502237805</v>
+        <v>-0.05969455182335837</v>
       </c>
       <c r="M74" s="19" t="n">
-        <v>-0.08769113301429471</v>
+        <v>-0.08707737376067881</v>
       </c>
       <c r="N74" s="20" t="n">
         <v>0</v>
@@ -5783,12 +5789,12 @@
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>JVST @ NDSU</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D75" s="22" t="n">
@@ -5796,37 +5802,37 @@
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
-          <t>NDSU -7</t>
+          <t>Under 47.5</t>
         </is>
       </c>
       <c r="G75" s="23" t="n">
-        <v>-7</v>
+        <v>47.5</v>
       </c>
       <c r="H75" s="13" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="I75" s="15" t="n">
-        <v>0.4500144681504686</v>
+        <v>0.4623116742984892</v>
       </c>
       <c r="J75" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5</v>
       </c>
       <c r="K75" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L75" s="14" t="n">
-        <v>-0.06218065380075088</v>
+        <v>-0.06149784951103465</v>
       </c>
       <c r="M75" s="14" t="n">
-        <v>-0.1152697169483107</v>
+        <v>-0.117404985430157</v>
       </c>
       <c r="N75" s="15" t="n">
-        <v>0.0505</v>
+        <v>0</v>
       </c>
       <c r="O75" s="24" t="n">
         <v>0.45</v>
@@ -5846,12 +5852,12 @@
       </c>
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>MRMK @ DEL</t>
+          <t>JVST @ NDSU</t>
         </is>
       </c>
       <c r="C76" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-29 21:30</t>
         </is>
       </c>
       <c r="D76" s="25" t="n">
@@ -5859,37 +5865,37 @@
       </c>
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F76" s="17" t="inlineStr">
         <is>
-          <t>Under 55.5</t>
+          <t>NDSU -7</t>
         </is>
       </c>
       <c r="G76" s="26" t="n">
-        <v>55.5</v>
+        <v>-7</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="I76" s="20" t="n">
-        <v>0.4562349525054241</v>
+        <v>0.4500144681504686</v>
       </c>
       <c r="J76" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K76" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L76" s="19" t="n">
-        <v>-0.06299581672534516</v>
+        <v>-0.06218065380075088</v>
       </c>
       <c r="M76" s="19" t="n">
-        <v>-0.1213252766562202</v>
+        <v>-0.1152697169483107</v>
       </c>
       <c r="N76" s="20" t="n">
-        <v>0</v>
+        <v>0.0505</v>
       </c>
       <c r="O76" s="27" t="n">
         <v>0.45</v>
@@ -5899,11 +5905,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q76" s="17" t="inlineStr">
-        <is>
-          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q76" s="17" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
@@ -5913,12 +5915,12 @@
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D77" s="22" t="n">
@@ -5926,34 +5928,32 @@
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
-        </is>
-      </c>
-      <c r="G77" s="23" t="n">
-        <v>47.5</v>
-      </c>
+          <t>UVA ML</t>
+        </is>
+      </c>
+      <c r="G77" s="23" t="n"/>
       <c r="H77" s="13" t="n">
-        <v>-112</v>
+        <v>-225</v>
       </c>
       <c r="I77" s="15" t="n">
-        <v>0.4644765513334737</v>
+        <v>0.6285057351705188</v>
       </c>
       <c r="J77" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.6636481241914618</v>
       </c>
       <c r="K77" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="L77" s="14" t="n">
-        <v>-0.06382533545897917</v>
+        <v>-0.06380195713717352</v>
       </c>
       <c r="M77" s="14" t="n">
-        <v>-0.1208122421187821</v>
+        <v>-0.0921583825314729</v>
       </c>
       <c r="N77" s="15" t="n">
         <v>0</v>
@@ -6039,12 +6039,12 @@
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>MRMK @ DEL</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D79" s="22" t="n">
@@ -6052,32 +6052,34 @@
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
-          <t>UNLV ML</t>
-        </is>
-      </c>
-      <c r="G79" s="23" t="n"/>
+          <t>Under 55.5</t>
+        </is>
+      </c>
+      <c r="G79" s="23" t="n">
+        <v>55.5</v>
+      </c>
       <c r="H79" s="13" t="n">
-        <v>-218</v>
+        <v>-110</v>
       </c>
       <c r="I79" s="15" t="n">
-        <v>0.616964108311471</v>
+        <v>0.4583998295404086</v>
       </c>
       <c r="J79" s="15" t="n">
-        <v>0.6574752261956054</v>
+        <v>0.5</v>
       </c>
       <c r="K79" s="15" t="n">
-        <v>0.6855345911949685</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L79" s="14" t="n">
-        <v>-0.06857048288349754</v>
+        <v>-0.06540969426911525</v>
       </c>
       <c r="M79" s="14" t="n">
-        <v>-0.1000248328300561</v>
+        <v>-0.1248730526955836</v>
       </c>
       <c r="N79" s="15" t="n">
         <v>0</v>
@@ -6090,7 +6092,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q79" s="12" t="n"/>
+      <c r="Q79" s="12" t="inlineStr">
+        <is>
+          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="17" t="inlineStr">
@@ -6100,12 +6106,12 @@
       </c>
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C80" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D80" s="25" t="n">
@@ -6113,34 +6119,32 @@
       </c>
       <c r="E80" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F80" s="17" t="inlineStr">
         <is>
-          <t>UVA -5.5</t>
-        </is>
-      </c>
-      <c r="G80" s="26" t="n">
-        <v>-5.5</v>
-      </c>
+          <t>UNLV ML</t>
+        </is>
+      </c>
+      <c r="G80" s="26" t="n"/>
       <c r="H80" s="18" t="n">
-        <v>-112</v>
+        <v>-218</v>
       </c>
       <c r="I80" s="20" t="n">
-        <v>0.4587103311205297</v>
+        <v>0.616964108311471</v>
       </c>
       <c r="J80" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.6574752261956054</v>
       </c>
       <c r="K80" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.6855345911949685</v>
       </c>
       <c r="L80" s="19" t="n">
-        <v>-0.0695915556719231</v>
+        <v>-0.06857048288349754</v>
       </c>
       <c r="M80" s="19" t="n">
-        <v>-0.1317268732361402</v>
+        <v>-0.1000248328300561</v>
       </c>
       <c r="N80" s="20" t="n">
         <v>0</v>
@@ -6163,12 +6167,12 @@
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>COLO @ GT</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D81" s="22" t="n">
@@ -6176,34 +6180,34 @@
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
-          <t>Over 59.5</t>
+          <t>GT -6.5</t>
         </is>
       </c>
       <c r="G81" s="23" t="n">
-        <v>59.5</v>
+        <v>-6.5</v>
       </c>
       <c r="H81" s="13" t="n">
-        <v>-112</v>
+        <v>-115</v>
       </c>
       <c r="I81" s="15" t="n">
-        <v>0.4586148034139574</v>
+        <v>0.4640540647948633</v>
       </c>
       <c r="J81" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K81" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L81" s="14" t="n">
-        <v>-0.06968708337849544</v>
+        <v>-0.07082965613536918</v>
       </c>
       <c r="M81" s="14" t="n">
-        <v>-0.1319076935378664</v>
+        <v>-0.132420661470473</v>
       </c>
       <c r="N81" s="15" t="n">
         <v>0</v>
@@ -6226,12 +6230,12 @@
       </c>
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>COLO @ GT</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C82" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D82" s="25" t="n">
@@ -6244,17 +6248,17 @@
       </c>
       <c r="F82" s="17" t="inlineStr">
         <is>
-          <t>GT -6.5</t>
+          <t>UVA -5.5</t>
         </is>
       </c>
       <c r="G82" s="26" t="n">
-        <v>-6.5</v>
+        <v>-5.5</v>
       </c>
       <c r="H82" s="18" t="n">
         <v>-115</v>
       </c>
       <c r="I82" s="20" t="n">
-        <v>0.4640540647948633</v>
+        <v>0.4619625721787197</v>
       </c>
       <c r="J82" s="20" t="n">
         <v>0.5108342361863488</v>
@@ -6263,10 +6267,10 @@
         <v>0.5348837209302325</v>
       </c>
       <c r="L82" s="19" t="n">
-        <v>-0.07082965613536918</v>
+        <v>-0.07292114875151279</v>
       </c>
       <c r="M82" s="19" t="n">
-        <v>-0.132420661470473</v>
+        <v>-0.1363308433180458</v>
       </c>
       <c r="N82" s="20" t="n">
         <v>0</v>
@@ -6314,22 +6318,22 @@
         <v>-5.5</v>
       </c>
       <c r="H83" s="13" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I83" s="15" t="n">
-        <v>0.4481517952886701</v>
+        <v>0.4459869182536856</v>
       </c>
       <c r="J83" s="15" t="n">
-        <v>0.5</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K83" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L83" s="14" t="n">
-        <v>-0.07565772852085378</v>
+        <v>-0.07324385097708364</v>
       </c>
       <c r="M83" s="14" t="n">
-        <v>-0.1444374817216299</v>
+        <v>-0.1410622315114202</v>
       </c>
       <c r="N83" s="15" t="n">
         <v>0</v>
@@ -6476,12 +6480,12 @@
       </c>
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>HAW @ STAN</t>
+          <t>EIU @ MINN</t>
         </is>
       </c>
       <c r="C86" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D86" s="25" t="n">
@@ -6489,22 +6493,22 @@
       </c>
       <c r="E86" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F86" s="17" t="inlineStr">
         <is>
-          <t>STAN -4</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="G86" s="26" t="n">
-        <v>-4</v>
+        <v>51.5</v>
       </c>
       <c r="H86" s="18" t="n">
         <v>-108</v>
       </c>
       <c r="I86" s="20" t="n">
-        <v>0.4333339188511319</v>
+        <v>0.4350519102861474</v>
       </c>
       <c r="J86" s="20" t="n">
         <v>0.4956702459300312</v>
@@ -6513,13 +6517,13 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L86" s="19" t="n">
-        <v>-0.08589685037963735</v>
+        <v>-0.08417885894462185</v>
       </c>
       <c r="M86" s="19" t="n">
-        <v>-0.1604724948268336</v>
+        <v>-0.1621222468563086</v>
       </c>
       <c r="N86" s="20" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="O86" s="27" t="n">
         <v>0.45</v>
@@ -6529,7 +6533,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q86" s="17" t="n"/>
+      <c r="Q86" s="17" t="inlineStr">
+        <is>
+          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="12" t="inlineStr">
@@ -6539,12 +6547,12 @@
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>MASS @ RUTG</t>
+          <t>HAW @ STAN</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 22:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D87" s="22" t="n">
@@ -6552,37 +6560,37 @@
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F87" s="12" t="inlineStr">
         <is>
-          <t>Under 53.5</t>
+          <t>STAN -4</t>
         </is>
       </c>
       <c r="G87" s="23" t="n">
-        <v>53.5</v>
+        <v>-4</v>
       </c>
       <c r="H87" s="13" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I87" s="15" t="n">
-        <v>0.4259569450760283</v>
+        <v>0.4333339188511319</v>
       </c>
       <c r="J87" s="15" t="n">
-        <v>0.5</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K87" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L87" s="14" t="n">
-        <v>-0.09785257873349551</v>
+        <v>-0.08589685037963735</v>
       </c>
       <c r="M87" s="14" t="n">
-        <v>-0.1868094684912186</v>
+        <v>-0.1604724948268336</v>
       </c>
       <c r="N87" s="15" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="O87" s="24" t="n">
         <v>0.45</v>
@@ -6602,12 +6610,12 @@
       </c>
       <c r="B88" s="17" t="inlineStr">
         <is>
-          <t>BCU @ UCF</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C88" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D88" s="25" t="n">
@@ -6620,17 +6628,17 @@
       </c>
       <c r="F88" s="17" t="inlineStr">
         <is>
-          <t>Over 59.5</t>
+          <t>Over 60.5</t>
         </is>
       </c>
       <c r="G88" s="26" t="n">
-        <v>59.5</v>
+        <v>60.5</v>
       </c>
       <c r="H88" s="18" t="n">
         <v>-112</v>
       </c>
       <c r="I88" s="20" t="n">
-        <v>0.4171159331581163</v>
+        <v>0.4393816702781982</v>
       </c>
       <c r="J88" s="20" t="n">
         <v>0.5043297540699688</v>
@@ -6639,10 +6647,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L88" s="19" t="n">
-        <v>-0.1111859536343365</v>
+        <v>-0.08892021651425458</v>
       </c>
       <c r="M88" s="19" t="n">
-        <v>-0.2104591265221369</v>
+        <v>-0.1683132669734104</v>
       </c>
       <c r="N88" s="20" t="n">
         <v>0</v>
@@ -6655,11 +6663,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q88" s="17" t="inlineStr">
-        <is>
-          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q88" s="17" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="12" t="inlineStr">
@@ -6669,12 +6673,12 @@
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>MASS @ RUTG</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-09-03 22:00</t>
         </is>
       </c>
       <c r="D89" s="22" t="n">
@@ -6682,32 +6686,34 @@
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F89" s="12" t="inlineStr">
         <is>
-          <t>TCU ML</t>
-        </is>
-      </c>
-      <c r="G89" s="23" t="n"/>
+          <t>Under 53.5</t>
+        </is>
+      </c>
+      <c r="G89" s="23" t="n">
+        <v>53.5</v>
+      </c>
       <c r="H89" s="13" t="n">
-        <v>-298</v>
+        <v>-110</v>
       </c>
       <c r="I89" s="15" t="n">
-        <v>0.6339800039113948</v>
+        <v>0.4259569450760283</v>
       </c>
       <c r="J89" s="15" t="n">
-        <v>0.7179705215419501</v>
+        <v>0.5</v>
       </c>
       <c r="K89" s="15" t="n">
-        <v>0.7487437185929648</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L89" s="14" t="n">
-        <v>-0.1147637146815701</v>
+        <v>-0.09785257873349551</v>
       </c>
       <c r="M89" s="14" t="n">
-        <v>-0.1532750283331037</v>
+        <v>-0.1868094684912186</v>
       </c>
       <c r="N89" s="15" t="n">
         <v>0</v>
@@ -6730,7 +6736,7 @@
       </c>
       <c r="B90" s="17" t="inlineStr">
         <is>
-          <t>AKR @ WAKE</t>
+          <t>BCU @ UCF</t>
         </is>
       </c>
       <c r="C90" s="17" t="inlineStr">
@@ -6748,29 +6754,29 @@
       </c>
       <c r="F90" s="17" t="inlineStr">
         <is>
-          <t>Under 49.5</t>
+          <t>Over 59.5</t>
         </is>
       </c>
       <c r="G90" s="26" t="n">
-        <v>49.5</v>
+        <v>59.5</v>
       </c>
       <c r="H90" s="18" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I90" s="20" t="n">
-        <v>0.396824791827995</v>
+        <v>0.4171159331581163</v>
       </c>
       <c r="J90" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K90" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L90" s="19" t="n">
-        <v>-0.1224059774027743</v>
+        <v>-0.1111859536343365</v>
       </c>
       <c r="M90" s="19" t="n">
-        <v>-0.2357448453683059</v>
+        <v>-0.2104591265221369</v>
       </c>
       <c r="N90" s="20" t="n">
         <v>0</v>
@@ -6783,7 +6789,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q90" s="17" t="n"/>
+      <c r="Q90" s="17" t="inlineStr">
+        <is>
+          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="12" t="inlineStr">
@@ -6793,12 +6803,12 @@
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>WES @ KENN</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D91" s="22" t="n">
@@ -6806,51 +6816,45 @@
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F91" s="12" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
-        </is>
-      </c>
-      <c r="G91" s="23" t="n">
-        <v>51.5</v>
-      </c>
+          <t>TCU ML</t>
+        </is>
+      </c>
+      <c r="G91" s="23" t="n"/>
       <c r="H91" s="13" t="n">
-        <v>-112</v>
+        <v>-310</v>
       </c>
       <c r="I91" s="15" t="n">
-        <v>0.4028929855258536</v>
+        <v>0.6378709973210217</v>
       </c>
       <c r="J91" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.725752508361204</v>
       </c>
       <c r="K91" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.7560975609756098</v>
       </c>
       <c r="L91" s="14" t="n">
-        <v>-0.1254089012665992</v>
+        <v>-0.1182265636545881</v>
       </c>
       <c r="M91" s="14" t="n">
-        <v>-0.2373811345403485</v>
+        <v>-0.1563641648334875</v>
       </c>
       <c r="N91" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O91" s="24" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="P91" s="12" t="inlineStr">
         <is>
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q91" s="12" t="inlineStr">
-        <is>
-          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q91" s="12" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="17" t="inlineStr">
@@ -6860,12 +6864,12 @@
       </c>
       <c r="B92" s="17" t="inlineStr">
         <is>
-          <t>COLO @ GT</t>
+          <t>AKR @ WAKE</t>
         </is>
       </c>
       <c r="C92" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D92" s="25" t="n">
@@ -6878,29 +6882,29 @@
       </c>
       <c r="F92" s="17" t="inlineStr">
         <is>
-          <t>Under 50.5</t>
+          <t>Under 49.5</t>
         </is>
       </c>
       <c r="G92" s="26" t="n">
-        <v>50.5</v>
+        <v>49.5</v>
       </c>
       <c r="H92" s="18" t="n">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="I92" s="20" t="n">
-        <v>0.3867120014398708</v>
+        <v>0.396824791827995</v>
       </c>
       <c r="J92" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K92" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L92" s="19" t="n">
-        <v>-0.1254831205113487</v>
+        <v>-0.1224059774027743</v>
       </c>
       <c r="M92" s="19" t="n">
-        <v>-0.2449908543316808</v>
+        <v>-0.2357448453683059</v>
       </c>
       <c r="N92" s="20" t="n">
         <v>0</v>
@@ -6923,12 +6927,12 @@
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>SAC @ EMU</t>
+          <t>WES @ KENN</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 22:30</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D93" s="22" t="n">
@@ -6941,42 +6945,46 @@
       </c>
       <c r="F93" s="12" t="inlineStr">
         <is>
-          <t>Under 52.5</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="G93" s="23" t="n">
-        <v>52.5</v>
+        <v>51.5</v>
       </c>
       <c r="H93" s="13" t="n">
-        <v>-115</v>
+        <v>-112</v>
       </c>
       <c r="I93" s="15" t="n">
-        <v>0.407892734181457</v>
+        <v>0.4028929855258536</v>
       </c>
       <c r="J93" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K93" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L93" s="14" t="n">
-        <v>-0.1269909867487755</v>
+        <v>-0.1254089012665992</v>
       </c>
       <c r="M93" s="14" t="n">
-        <v>-0.2374179317477109</v>
+        <v>-0.2373811345403485</v>
       </c>
       <c r="N93" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O93" s="24" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="P93" s="12" t="inlineStr">
         <is>
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q93" s="12" t="n"/>
+      <c r="Q93" s="12" t="inlineStr">
+        <is>
+          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="17" t="inlineStr">
@@ -6986,7 +6994,7 @@
       </c>
       <c r="B94" s="17" t="inlineStr">
         <is>
-          <t>UAPB @ MIZ</t>
+          <t>COLO @ GT</t>
         </is>
       </c>
       <c r="C94" s="17" t="inlineStr">
@@ -7004,29 +7012,29 @@
       </c>
       <c r="F94" s="17" t="inlineStr">
         <is>
-          <t>Over 60.5</t>
+          <t>Under 50.5</t>
         </is>
       </c>
       <c r="G94" s="26" t="n">
-        <v>60.5</v>
+        <v>50.5</v>
       </c>
       <c r="H94" s="18" t="n">
-        <v>-112</v>
+        <v>-105</v>
       </c>
       <c r="I94" s="20" t="n">
-        <v>0.3977053958774506</v>
+        <v>0.3867120014398708</v>
       </c>
       <c r="J94" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K94" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L94" s="19" t="n">
-        <v>-0.1305964909150022</v>
+        <v>-0.1254831205113487</v>
       </c>
       <c r="M94" s="19" t="n">
-        <v>-0.2472005006605399</v>
+        <v>-0.2449908543316808</v>
       </c>
       <c r="N94" s="20" t="n">
         <v>0</v>
@@ -7039,11 +7047,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q94" s="17" t="inlineStr">
-        <is>
-          <t>UAPB isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q94" s="17" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="12" t="inlineStr">
@@ -7053,12 +7057,12 @@
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>SAC @ EMU</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-08-29 22:30</t>
         </is>
       </c>
       <c r="D95" s="22" t="n">
@@ -7066,22 +7070,22 @@
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F95" s="12" t="inlineStr">
         <is>
-          <t>TCU -7.5</t>
+          <t>Under 52.5</t>
         </is>
       </c>
       <c r="G95" s="23" t="n">
-        <v>-7.5</v>
+        <v>52.5</v>
       </c>
       <c r="H95" s="13" t="n">
         <v>-115</v>
       </c>
       <c r="I95" s="15" t="n">
-        <v>0.4039442568628988</v>
+        <v>0.407892734181457</v>
       </c>
       <c r="J95" s="15" t="n">
         <v>0.5108342361863488</v>
@@ -7090,10 +7094,10 @@
         <v>0.5348837209302325</v>
       </c>
       <c r="L95" s="14" t="n">
-        <v>-0.1309394640673337</v>
+        <v>-0.1269909867487755</v>
       </c>
       <c r="M95" s="14" t="n">
-        <v>-0.2447998676041457</v>
+        <v>-0.2374179317477109</v>
       </c>
       <c r="N95" s="15" t="n">
         <v>0</v>
@@ -7116,12 +7120,12 @@
       </c>
       <c r="B96" s="17" t="inlineStr">
         <is>
-          <t>NCAT @ GAST</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C96" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 23:00</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D96" s="25" t="n">
@@ -7129,34 +7133,34 @@
       </c>
       <c r="E96" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F96" s="17" t="inlineStr">
         <is>
-          <t>Over 63.5</t>
+          <t>TCU -7.5</t>
         </is>
       </c>
       <c r="G96" s="26" t="n">
-        <v>63.5</v>
+        <v>-7.5</v>
       </c>
       <c r="H96" s="18" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>0.3882730035558194</v>
+        <v>0.4006920158047088</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L96" s="19" t="n">
-        <v>-0.1309577656749499</v>
+        <v>-0.127609870987744</v>
       </c>
       <c r="M96" s="19" t="n">
-        <v>-0.2522149561147182</v>
+        <v>-0.2415472557982298</v>
       </c>
       <c r="N96" s="20" t="n">
         <v>0</v>
@@ -7169,11 +7173,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q96" s="17" t="inlineStr">
-        <is>
-          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q96" s="17" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="12" t="inlineStr">
@@ -7201,29 +7201,29 @@
       </c>
       <c r="F97" s="12" t="inlineStr">
         <is>
-          <t>Under 48.5</t>
+          <t>Under 49.5</t>
         </is>
       </c>
       <c r="G97" s="23" t="n">
-        <v>48.5</v>
+        <v>49.5</v>
       </c>
       <c r="H97" s="13" t="n">
-        <v>-108</v>
+        <v>-115</v>
       </c>
       <c r="I97" s="15" t="n">
-        <v>0.3799657943704541</v>
+        <v>0.4044067869561538</v>
       </c>
       <c r="J97" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K97" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L97" s="14" t="n">
-        <v>-0.1392649748603152</v>
+        <v>-0.1304769339740787</v>
       </c>
       <c r="M97" s="14" t="n">
-        <v>-0.2682140256569032</v>
+        <v>-0.2439351374297994</v>
       </c>
       <c r="N97" s="15" t="n">
         <v>0</v>
@@ -7246,12 +7246,12 @@
       </c>
       <c r="B98" s="17" t="inlineStr">
         <is>
-          <t>SAC @ EMU</t>
+          <t>UAPB @ MIZ</t>
         </is>
       </c>
       <c r="C98" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 22:30</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D98" s="25" t="n">
@@ -7259,32 +7259,34 @@
       </c>
       <c r="E98" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F98" s="17" t="inlineStr">
         <is>
-          <t>EMU ML</t>
-        </is>
-      </c>
-      <c r="G98" s="26" t="n"/>
+          <t>Over 60.5</t>
+        </is>
+      </c>
+      <c r="G98" s="26" t="n">
+        <v>60.5</v>
+      </c>
       <c r="H98" s="18" t="n">
-        <v>-355</v>
+        <v>-112</v>
       </c>
       <c r="I98" s="20" t="n">
-        <v>0.6313778129495795</v>
+        <v>0.3977053958774506</v>
       </c>
       <c r="J98" s="20" t="n">
-        <v>0.7477827050997783</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K98" s="20" t="n">
-        <v>0.7802197802197802</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L98" s="19" t="n">
-        <v>-0.1488419672702007</v>
+        <v>-0.1305964909150022</v>
       </c>
       <c r="M98" s="19" t="n">
-        <v>-0.1907692819942009</v>
+        <v>-0.2472005006605399</v>
       </c>
       <c r="N98" s="20" t="n">
         <v>0</v>
@@ -7297,7 +7299,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q98" s="17" t="n"/>
+      <c r="Q98" s="17" t="inlineStr">
+        <is>
+          <t>UAPB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="12" t="inlineStr">
@@ -7307,12 +7313,12 @@
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>ALB @ BUFF</t>
+          <t>NCAT @ GAST</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-04 23:00</t>
         </is>
       </c>
       <c r="D99" s="22" t="n">
@@ -7325,29 +7331,29 @@
       </c>
       <c r="F99" s="12" t="inlineStr">
         <is>
-          <t>Under 48.5</t>
+          <t>Over 63.5</t>
         </is>
       </c>
       <c r="G99" s="23" t="n">
-        <v>48.5</v>
+        <v>63.5</v>
       </c>
       <c r="H99" s="13" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="I99" s="15" t="n">
-        <v>0.3794983449651635</v>
+        <v>0.3882730035558194</v>
       </c>
       <c r="J99" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K99" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L99" s="14" t="n">
-        <v>-0.155385375965069</v>
+        <v>-0.1309577656749499</v>
       </c>
       <c r="M99" s="14" t="n">
-        <v>-0.2905030941955639</v>
+        <v>-0.2522149561147182</v>
       </c>
       <c r="N99" s="15" t="n">
         <v>0</v>
@@ -7362,7 +7368,7 @@
       </c>
       <c r="Q99" s="12" t="inlineStr">
         <is>
-          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7380,12 @@
       </c>
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>SAC @ EMU</t>
+          <t>ALB @ BUFF</t>
         </is>
       </c>
       <c r="C100" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 22:30</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D100" s="25" t="n">
@@ -7387,34 +7393,34 @@
       </c>
       <c r="E100" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F100" s="17" t="inlineStr">
         <is>
-          <t>EMU -9.5</t>
+          <t>Under 48.5</t>
         </is>
       </c>
       <c r="G100" s="26" t="n">
-        <v>-9.5</v>
+        <v>48.5</v>
       </c>
       <c r="H100" s="18" t="n">
-        <v>-115</v>
+        <v>-112</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>0.3681129091825526</v>
+        <v>0.3762461039069736</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L100" s="19" t="n">
-        <v>-0.1667708117476799</v>
+        <v>-0.1520557828854793</v>
       </c>
       <c r="M100" s="19" t="n">
-        <v>-0.3117889089195756</v>
+        <v>-0.2878198747475144</v>
       </c>
       <c r="N100" s="20" t="n">
         <v>0</v>
@@ -7429,7 +7435,7 @@
       </c>
       <c r="Q100" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7447,12 @@
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>JVST @ NDSU</t>
+          <t>SAC @ EMU</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30</t>
+          <t>2026-08-29 22:30</t>
         </is>
       </c>
       <c r="D101" s="22" t="n">
@@ -7454,34 +7460,32 @@
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F101" s="12" t="inlineStr">
         <is>
-          <t>Under 46.5</t>
-        </is>
-      </c>
-      <c r="G101" s="23" t="n">
-        <v>46.5</v>
-      </c>
+          <t>EMU ML</t>
+        </is>
+      </c>
+      <c r="G101" s="23" t="n"/>
       <c r="H101" s="13" t="n">
-        <v>-108</v>
+        <v>-380</v>
       </c>
       <c r="I101" s="15" t="n">
-        <v>0.3425002548836977</v>
+        <v>0.6374864603996904</v>
       </c>
       <c r="J101" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.7600000000000001</v>
       </c>
       <c r="K101" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="L101" s="14" t="n">
-        <v>-0.1767305143470715</v>
+        <v>-0.1541802062669763</v>
       </c>
       <c r="M101" s="14" t="n">
-        <v>-0.3403698794832488</v>
+        <v>-0.1947539447582859</v>
       </c>
       <c r="N101" s="15" t="n">
         <v>0</v>
@@ -7494,11 +7498,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q101" s="12" t="inlineStr">
-        <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
-        </is>
-      </c>
+      <c r="Q101" s="12" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="17" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>MASS @ RUTG</t>
+          <t>SAC @ EMU</t>
         </is>
       </c>
       <c r="C102" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 22:00</t>
+          <t>2026-08-29 22:30</t>
         </is>
       </c>
       <c r="D102" s="25" t="n">
@@ -7521,35 +7521,37 @@
       </c>
       <c r="E102" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F102" s="17" t="inlineStr">
         <is>
-          <t>RUTG ML</t>
-        </is>
-      </c>
-      <c r="G102" s="26" t="n"/>
+          <t>EMU -10</t>
+        </is>
+      </c>
+      <c r="G102" s="26" t="n">
+        <v>-10</v>
+      </c>
       <c r="H102" s="18" t="n">
-        <v>-6500</v>
+        <v>-110</v>
       </c>
       <c r="I102" s="20" t="n">
-        <v>0.8036923684058288</v>
+        <v>0.3503913906579027</v>
       </c>
       <c r="J102" s="20" t="n">
-        <v>0.9538784067085954</v>
+        <v>0.5</v>
       </c>
       <c r="K102" s="20" t="n">
-        <v>0.9848484848484849</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L102" s="19" t="n">
-        <v>-0.1811561164426561</v>
+        <v>-0.1734181331516211</v>
       </c>
       <c r="M102" s="19" t="n">
-        <v>-0.183943133618697</v>
+        <v>-0.3208769320138066</v>
       </c>
       <c r="N102" s="20" t="n">
-        <v>0</v>
+        <v>0.0308</v>
       </c>
       <c r="O102" s="27" t="n">
         <v>0.45</v>
@@ -7561,7 +7563,7 @@
       </c>
       <c r="Q102" s="17" t="inlineStr">
         <is>
-          <t>price outside allowed range</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -7573,12 +7575,12 @@
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>IDHO @ UTAH</t>
+          <t>JVST @ NDSU</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 01:00</t>
+          <t>2026-08-29 21:30</t>
         </is>
       </c>
       <c r="D103" s="22" t="n">
@@ -7586,32 +7588,34 @@
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F103" s="12" t="inlineStr">
         <is>
-          <t>UTAH ML</t>
-        </is>
-      </c>
-      <c r="G103" s="23" t="n"/>
+          <t>Under 46.5</t>
+        </is>
+      </c>
+      <c r="G103" s="23" t="n">
+        <v>46.5</v>
+      </c>
       <c r="H103" s="13" t="n">
-        <v>-10000</v>
+        <v>-108</v>
       </c>
       <c r="I103" s="15" t="n">
-        <v>0.8084273455958602</v>
+        <v>0.3425002548836977</v>
       </c>
       <c r="J103" s="15" t="n">
-        <v>0.9684473601999376</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K103" s="15" t="n">
-        <v>0.9900990099009901</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L103" s="14" t="n">
-        <v>-0.1816716643051299</v>
+        <v>-0.1767305143470715</v>
       </c>
       <c r="M103" s="14" t="n">
-        <v>-0.1834883809481812</v>
+        <v>-0.3403698794832488</v>
       </c>
       <c r="N103" s="15" t="n">
         <v>0</v>
@@ -7626,7 +7630,7 @@
       </c>
       <c r="Q103" s="12" t="inlineStr">
         <is>
-          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -7638,12 +7642,12 @@
       </c>
       <c r="B104" s="17" t="inlineStr">
         <is>
-          <t>UAB @ ILL</t>
+          <t>MASS @ RUTG</t>
         </is>
       </c>
       <c r="C104" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 01:00</t>
+          <t>2026-09-03 22:00</t>
         </is>
       </c>
       <c r="D104" s="25" t="n">
@@ -7656,27 +7660,27 @@
       </c>
       <c r="F104" s="17" t="inlineStr">
         <is>
-          <t>ILL ML</t>
+          <t>RUTG ML</t>
         </is>
       </c>
       <c r="G104" s="26" t="n"/>
       <c r="H104" s="18" t="n">
-        <v>-10000</v>
+        <v>-6500</v>
       </c>
       <c r="I104" s="20" t="n">
-        <v>0.8035624619687695</v>
+        <v>0.8036923684058288</v>
       </c>
       <c r="J104" s="20" t="n">
-        <v>0.9684473601999376</v>
+        <v>0.9538784067085954</v>
       </c>
       <c r="K104" s="20" t="n">
-        <v>0.9900990099009901</v>
+        <v>0.9848484848484849</v>
       </c>
       <c r="L104" s="19" t="n">
-        <v>-0.1865365479322206</v>
+        <v>-0.1811561164426561</v>
       </c>
       <c r="M104" s="19" t="n">
-        <v>-0.1884019134115428</v>
+        <v>-0.183943133618697</v>
       </c>
       <c r="N104" s="20" t="n">
         <v>0</v>
@@ -7703,12 +7707,12 @@
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>AKR @ WAKE</t>
+          <t>IDHO @ UTAH</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D105" s="22" t="n">
@@ -7721,27 +7725,27 @@
       </c>
       <c r="F105" s="12" t="inlineStr">
         <is>
-          <t>WAKE ML</t>
+          <t>UTAH ML</t>
         </is>
       </c>
       <c r="G105" s="23" t="n"/>
       <c r="H105" s="13" t="n">
-        <v>-2800</v>
+        <v>-10000</v>
       </c>
       <c r="I105" s="15" t="n">
-        <v>0.7689464432363347</v>
+        <v>0.8084273455958602</v>
       </c>
       <c r="J105" s="15" t="n">
-        <v>0.9311163895486935</v>
+        <v>0.9684473601999376</v>
       </c>
       <c r="K105" s="15" t="n">
-        <v>0.9655172413793104</v>
+        <v>0.9900990099009901</v>
       </c>
       <c r="L105" s="14" t="n">
-        <v>-0.1965707981429757</v>
+        <v>-0.1816716643051299</v>
       </c>
       <c r="M105" s="14" t="n">
-        <v>-0.203591183790939</v>
+        <v>-0.1834883809481812</v>
       </c>
       <c r="N105" s="15" t="n">
         <v>0</v>
@@ -7756,7 +7760,7 @@
       </c>
       <c r="Q105" s="12" t="inlineStr">
         <is>
-          <t>price outside allowed range</t>
+          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -7768,12 +7772,12 @@
       </c>
       <c r="B106" s="17" t="inlineStr">
         <is>
-          <t>NMSU @ FSU</t>
+          <t>UAB @ ILL</t>
         </is>
       </c>
       <c r="C106" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D106" s="25" t="n">
@@ -7786,27 +7790,27 @@
       </c>
       <c r="F106" s="17" t="inlineStr">
         <is>
-          <t>FSU ML</t>
+          <t>ILL ML</t>
         </is>
       </c>
       <c r="G106" s="26" t="n"/>
       <c r="H106" s="18" t="n">
-        <v>-6500</v>
+        <v>-8000</v>
       </c>
       <c r="I106" s="20" t="n">
-        <v>0.7810227846843814</v>
+        <v>0.7982560124778584</v>
       </c>
       <c r="J106" s="20" t="n">
-        <v>0.9538784067085954</v>
+        <v>0.9578344612181156</v>
       </c>
       <c r="K106" s="20" t="n">
-        <v>0.9848484848484849</v>
+        <v>0.9876543209876543</v>
       </c>
       <c r="L106" s="19" t="n">
-        <v>-0.2038257001641035</v>
+        <v>-0.1893983085097959</v>
       </c>
       <c r="M106" s="19" t="n">
-        <v>-0.2069614801666282</v>
+        <v>-0.1917657873661684</v>
       </c>
       <c r="N106" s="20" t="n">
         <v>0</v>
@@ -7833,7 +7837,7 @@
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>WES @ KENN</t>
+          <t>AKR @ WAKE</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
@@ -7851,33 +7855,33 @@
       </c>
       <c r="F107" s="12" t="inlineStr">
         <is>
-          <t>KENN ML</t>
+          <t>WAKE ML</t>
         </is>
       </c>
       <c r="G107" s="23" t="n"/>
       <c r="H107" s="13" t="n">
-        <v>-3600</v>
+        <v>-3200</v>
       </c>
       <c r="I107" s="15" t="n">
-        <v>0.7629882523168648</v>
+        <v>0.7712245057719294</v>
       </c>
       <c r="J107" s="15" t="n">
-        <v>0.9396411092985318</v>
+        <v>0.9356725146198831</v>
       </c>
       <c r="K107" s="15" t="n">
-        <v>0.972972972972973</v>
+        <v>0.9696969696969697</v>
       </c>
       <c r="L107" s="14" t="n">
-        <v>-0.2099847206561082</v>
+        <v>-0.1984724639250404</v>
       </c>
       <c r="M107" s="14" t="n">
-        <v>-0.2158176295632223</v>
+        <v>-0.2046747284226978</v>
       </c>
       <c r="N107" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O107" s="24" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="P107" s="12" t="inlineStr">
         <is>
@@ -7886,7 +7890,7 @@
       </c>
       <c r="Q107" s="12" t="inlineStr">
         <is>
-          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>price outside allowed range</t>
         </is>
       </c>
     </row>
@@ -7898,12 +7902,12 @@
       </c>
       <c r="B108" s="17" t="inlineStr">
         <is>
-          <t>MRMK @ DEL</t>
+          <t>NMSU @ FSU</t>
         </is>
       </c>
       <c r="C108" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D108" s="25" t="n">
@@ -7916,27 +7920,27 @@
       </c>
       <c r="F108" s="17" t="inlineStr">
         <is>
-          <t>DEL ML</t>
+          <t>FSU ML</t>
         </is>
       </c>
       <c r="G108" s="26" t="n"/>
       <c r="H108" s="18" t="n">
-        <v>-10000</v>
+        <v>-8000</v>
       </c>
       <c r="I108" s="20" t="n">
-        <v>0.7657797338257375</v>
+        <v>0.7830008119391415</v>
       </c>
       <c r="J108" s="20" t="n">
-        <v>0.9684473601999376</v>
+        <v>0.9578344612181156</v>
       </c>
       <c r="K108" s="20" t="n">
-        <v>0.9900990099009901</v>
+        <v>0.9876543209876543</v>
       </c>
       <c r="L108" s="19" t="n">
-        <v>-0.2243192760752526</v>
+        <v>-0.2046535090485128</v>
       </c>
       <c r="M108" s="19" t="n">
-        <v>-0.2265624688360051</v>
+        <v>-0.2072116779116193</v>
       </c>
       <c r="N108" s="20" t="n">
         <v>0</v>
@@ -7951,7 +7955,7 @@
       </c>
       <c r="Q108" s="17" t="inlineStr">
         <is>
-          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>price outside allowed range</t>
         </is>
       </c>
     </row>
@@ -7963,7 +7967,7 @@
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>ALB @ BUFF</t>
+          <t>WES @ KENN</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
@@ -7981,33 +7985,33 @@
       </c>
       <c r="F109" s="12" t="inlineStr">
         <is>
-          <t>BUFF ML</t>
+          <t>KENN ML</t>
         </is>
       </c>
       <c r="G109" s="23" t="n"/>
       <c r="H109" s="13" t="n">
-        <v>-8000</v>
+        <v>-3600</v>
       </c>
       <c r="I109" s="15" t="n">
-        <v>0.7599039260434692</v>
+        <v>0.7629882523168648</v>
       </c>
       <c r="J109" s="15" t="n">
-        <v>0.9578344612181156</v>
+        <v>0.9396411092985318</v>
       </c>
       <c r="K109" s="15" t="n">
-        <v>0.9876543209876543</v>
+        <v>0.972972972972973</v>
       </c>
       <c r="L109" s="14" t="n">
-        <v>-0.227750394944185</v>
+        <v>-0.2099847206561082</v>
       </c>
       <c r="M109" s="14" t="n">
-        <v>-0.2305972748809874</v>
+        <v>-0.2158176295632223</v>
       </c>
       <c r="N109" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O109" s="24" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="P109" s="12" t="inlineStr">
         <is>
@@ -8016,7 +8020,7 @@
       </c>
       <c r="Q109" s="12" t="inlineStr">
         <is>
-          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -8028,7 +8032,7 @@
       </c>
       <c r="B110" s="17" t="inlineStr">
         <is>
-          <t>WES @ KENN</t>
+          <t>MRMK @ DEL</t>
         </is>
       </c>
       <c r="C110" s="17" t="inlineStr">
@@ -8041,40 +8045,38 @@
       </c>
       <c r="E110" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F110" s="17" t="inlineStr">
         <is>
-          <t>KENN -22.5</t>
-        </is>
-      </c>
-      <c r="G110" s="26" t="n">
-        <v>-22.5</v>
-      </c>
+          <t>DEL ML</t>
+        </is>
+      </c>
+      <c r="G110" s="26" t="n"/>
       <c r="H110" s="18" t="n">
-        <v>-105</v>
+        <v>-20000</v>
       </c>
       <c r="I110" s="20" t="n">
-        <v>0.2726533482579036</v>
+        <v>0.7679768076779374</v>
       </c>
       <c r="J110" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.9728415079043372</v>
       </c>
       <c r="K110" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.9950248756218906</v>
       </c>
       <c r="L110" s="19" t="n">
-        <v>-0.2395417736933159</v>
+        <v>-0.2270480679439532</v>
       </c>
       <c r="M110" s="19" t="n">
-        <v>-0.4676767962583787</v>
+        <v>-0.228183308283673</v>
       </c>
       <c r="N110" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O110" s="27" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="P110" s="17" t="inlineStr">
         <is>
@@ -8083,7 +8085,7 @@
       </c>
       <c r="Q110" s="17" t="inlineStr">
         <is>
-          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -8095,12 +8097,12 @@
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>NCAT @ GAST</t>
+          <t>ALB @ BUFF</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 23:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D111" s="22" t="n">
@@ -8113,27 +8115,27 @@
       </c>
       <c r="F111" s="12" t="inlineStr">
         <is>
-          <t>GAST ML</t>
+          <t>BUFF ML</t>
         </is>
       </c>
       <c r="G111" s="23" t="n"/>
       <c r="H111" s="13" t="n">
-        <v>-5000</v>
+        <v>-8000</v>
       </c>
       <c r="I111" s="15" t="n">
-        <v>0.7344577690680144</v>
+        <v>0.7599039260434692</v>
       </c>
       <c r="J111" s="15" t="n">
-        <v>0.949050949050949</v>
+        <v>0.9578344612181156</v>
       </c>
       <c r="K111" s="15" t="n">
-        <v>0.9803921568627451</v>
+        <v>0.9876543209876543</v>
       </c>
       <c r="L111" s="14" t="n">
-        <v>-0.2459343877947306</v>
+        <v>-0.227750394944185</v>
       </c>
       <c r="M111" s="14" t="n">
-        <v>-0.2508530755506253</v>
+        <v>-0.2305972748809874</v>
       </c>
       <c r="N111" s="15" t="n">
         <v>0</v>
@@ -8148,7 +8150,7 @@
       </c>
       <c r="Q111" s="12" t="inlineStr">
         <is>
-          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -8160,7 +8162,7 @@
       </c>
       <c r="B112" s="17" t="inlineStr">
         <is>
-          <t>AKR @ WAKE</t>
+          <t>WES @ KENN</t>
         </is>
       </c>
       <c r="C112" s="17" t="inlineStr">
@@ -8178,35 +8180,35 @@
       </c>
       <c r="F112" s="17" t="inlineStr">
         <is>
-          <t>WAKE -23.5</t>
+          <t>KENN -22.5</t>
         </is>
       </c>
       <c r="G112" s="26" t="n">
-        <v>-23.5</v>
+        <v>-22.5</v>
       </c>
       <c r="H112" s="18" t="n">
-        <v>-112</v>
+        <v>-105</v>
       </c>
       <c r="I112" s="20" t="n">
-        <v>0.279786024178475</v>
+        <v>0.2726533482579036</v>
       </c>
       <c r="J112" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K112" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L112" s="19" t="n">
-        <v>-0.2485158626139778</v>
+        <v>-0.2395417736933159</v>
       </c>
       <c r="M112" s="19" t="n">
-        <v>-0.4704050256621722</v>
+        <v>-0.4676767962583787</v>
       </c>
       <c r="N112" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O112" s="27" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="P112" s="17" t="inlineStr">
         <is>
@@ -8215,7 +8217,7 @@
       </c>
       <c r="Q112" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -8227,12 +8229,12 @@
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>UAB @ ILL</t>
+          <t>NCAT @ GAST</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 01:00</t>
+          <t>2026-09-04 23:00</t>
         </is>
       </c>
       <c r="D113" s="22" t="n">
@@ -8240,34 +8242,32 @@
       </c>
       <c r="E113" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
-          <t>ILL -28.5</t>
-        </is>
-      </c>
-      <c r="G113" s="23" t="n">
-        <v>-28.5</v>
-      </c>
+          <t>GAST ML</t>
+        </is>
+      </c>
+      <c r="G113" s="23" t="n"/>
       <c r="H113" s="13" t="n">
-        <v>-102</v>
+        <v>-5000</v>
       </c>
       <c r="I113" s="15" t="n">
-        <v>0.2561903984522976</v>
+        <v>0.7344577690680144</v>
       </c>
       <c r="J113" s="15" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.949050949050949</v>
       </c>
       <c r="K113" s="15" t="n">
-        <v>0.504950495049505</v>
+        <v>0.9803921568627451</v>
       </c>
       <c r="L113" s="14" t="n">
-        <v>-0.2487600965972073</v>
+        <v>-0.2459343877947306</v>
       </c>
       <c r="M113" s="14" t="n">
-        <v>-0.4926425442415282</v>
+        <v>-0.2508530755506253</v>
       </c>
       <c r="N113" s="15" t="n">
         <v>0</v>
@@ -8282,7 +8282,7 @@
       </c>
       <c r="Q113" s="12" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="B114" s="17" t="inlineStr">
         <is>
-          <t>ALB @ BUFF</t>
+          <t>AKR @ WAKE</t>
         </is>
       </c>
       <c r="C114" s="17" t="inlineStr">
@@ -8312,29 +8312,29 @@
       </c>
       <c r="F114" s="17" t="inlineStr">
         <is>
-          <t>BUFF -24.5</t>
+          <t>WAKE -23.5</t>
         </is>
       </c>
       <c r="G114" s="26" t="n">
-        <v>-24.5</v>
+        <v>-23.5</v>
       </c>
       <c r="H114" s="18" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I114" s="20" t="n">
-        <v>0.2657449776111079</v>
+        <v>0.279786024178475</v>
       </c>
       <c r="J114" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K114" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L114" s="19" t="n">
-        <v>-0.2534857916196613</v>
+        <v>-0.2485158626139778</v>
       </c>
       <c r="M114" s="19" t="n">
-        <v>-0.4881948579341625</v>
+        <v>-0.4704050256621722</v>
       </c>
       <c r="N114" s="20" t="n">
         <v>0</v>
@@ -8349,7 +8349,7 @@
       </c>
       <c r="Q114" s="17" t="inlineStr">
         <is>
-          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -8361,12 +8361,12 @@
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>UAB @ ILL</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D115" s="22" t="n">
@@ -8379,29 +8379,29 @@
       </c>
       <c r="F115" s="12" t="inlineStr">
         <is>
-          <t>USC -38.5</t>
+          <t>ILL -28.5</t>
         </is>
       </c>
       <c r="G115" s="23" t="n">
-        <v>-38.5</v>
+        <v>-28.5</v>
       </c>
       <c r="H115" s="13" t="n">
-        <v>100</v>
+        <v>-102</v>
       </c>
       <c r="I115" s="15" t="n">
-        <v>0.2414515187338134</v>
+        <v>0.2561903984522976</v>
       </c>
       <c r="J115" s="15" t="n">
-        <v>0.4782608695652174</v>
+        <v>0.4826358742837298</v>
       </c>
       <c r="K115" s="15" t="n">
-        <v>0.5</v>
+        <v>0.504950495049505</v>
       </c>
       <c r="L115" s="14" t="n">
-        <v>-0.2585484812661866</v>
+        <v>-0.2487600965972073</v>
       </c>
       <c r="M115" s="14" t="n">
-        <v>-0.5170969625323734</v>
+        <v>-0.4926425442415282</v>
       </c>
       <c r="N115" s="15" t="n">
         <v>0</v>
@@ -8428,12 +8428,12 @@
       </c>
       <c r="B116" s="17" t="inlineStr">
         <is>
-          <t>NMSU @ FSU</t>
+          <t>ALB @ BUFF</t>
         </is>
       </c>
       <c r="C116" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D116" s="25" t="n">
@@ -8446,29 +8446,29 @@
       </c>
       <c r="F116" s="17" t="inlineStr">
         <is>
-          <t>FSU -31.5</t>
+          <t>BUFF -24.5</t>
         </is>
       </c>
       <c r="G116" s="26" t="n">
-        <v>-31.5</v>
+        <v>-24.5</v>
       </c>
       <c r="H116" s="18" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="I116" s="20" t="n">
-        <v>0.2515947455243119</v>
+        <v>0.2679098546460923</v>
       </c>
       <c r="J116" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5</v>
       </c>
       <c r="K116" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L116" s="19" t="n">
-        <v>-0.2606003764269076</v>
+        <v>-0.2558996691634315</v>
       </c>
       <c r="M116" s="19" t="n">
-        <v>-0.5087912111192006</v>
+        <v>-0.4885357320392782</v>
       </c>
       <c r="N116" s="20" t="n">
         <v>0</v>
@@ -8483,7 +8483,7 @@
       </c>
       <c r="Q116" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>MASS @ RUTG</t>
+          <t>NMSU @ FSU</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 22:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D117" s="22" t="n">
@@ -8513,29 +8513,29 @@
       </c>
       <c r="F117" s="12" t="inlineStr">
         <is>
-          <t>RUTG -30.5</t>
+          <t>FSU -31.5</t>
         </is>
       </c>
       <c r="G117" s="23" t="n">
-        <v>-30.5</v>
+        <v>-31.5</v>
       </c>
       <c r="H117" s="13" t="n">
-        <v>-112</v>
+        <v>-105</v>
       </c>
       <c r="I117" s="15" t="n">
-        <v>0.2637706885532299</v>
+        <v>0.2515947455243119</v>
       </c>
       <c r="J117" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K117" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L117" s="14" t="n">
-        <v>-0.2645311982392229</v>
+        <v>-0.2606003764269076</v>
       </c>
       <c r="M117" s="14" t="n">
-        <v>-0.5007197680956719</v>
+        <v>-0.5087912111192006</v>
       </c>
       <c r="N117" s="15" t="n">
         <v>0</v>
@@ -8562,12 +8562,12 @@
       </c>
       <c r="B118" s="17" t="inlineStr">
         <is>
-          <t>MRMK @ DEL</t>
+          <t>MASS @ RUTG</t>
         </is>
       </c>
       <c r="C118" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-03 22:00</t>
         </is>
       </c>
       <c r="D118" s="25" t="n">
@@ -8580,17 +8580,17 @@
       </c>
       <c r="F118" s="17" t="inlineStr">
         <is>
-          <t>DEL -28.5</t>
+          <t>RUTG -30.5</t>
         </is>
       </c>
       <c r="G118" s="26" t="n">
-        <v>-28.5</v>
+        <v>-30.5</v>
       </c>
       <c r="H118" s="18" t="n">
         <v>-112</v>
       </c>
       <c r="I118" s="20" t="n">
-        <v>0.2613150626201174</v>
+        <v>0.2637706885532299</v>
       </c>
       <c r="J118" s="20" t="n">
         <v>0.5043297540699688</v>
@@ -8599,10 +8599,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L118" s="19" t="n">
-        <v>-0.2669868241723354</v>
+        <v>-0.2645311982392229</v>
       </c>
       <c r="M118" s="19" t="n">
-        <v>-0.5053679171833493</v>
+        <v>-0.5007197680956719</v>
       </c>
       <c r="N118" s="20" t="n">
         <v>0</v>
@@ -8617,7 +8617,7 @@
       </c>
       <c r="Q118" s="17" t="inlineStr">
         <is>
-          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -8654,22 +8654,22 @@
         <v>-28.5</v>
       </c>
       <c r="H119" s="13" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I119" s="15" t="n">
-        <v>0.2590431225556397</v>
+        <v>0.2568782455206553</v>
       </c>
       <c r="J119" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K119" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L119" s="14" t="n">
-        <v>-0.2692587642368131</v>
+        <v>-0.2669312782888685</v>
       </c>
       <c r="M119" s="14" t="n">
-        <v>-0.509668375162539</v>
+        <v>-0.5095960767332944</v>
       </c>
       <c r="N119" s="15" t="n">
         <v>0</v>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="B120" s="17" t="inlineStr">
         <is>
-          <t>IDHO @ UTAH</t>
+          <t>MRMK @ DEL</t>
         </is>
       </c>
       <c r="C120" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 01:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D120" s="25" t="n">
@@ -8714,17 +8714,17 @@
       </c>
       <c r="F120" s="17" t="inlineStr">
         <is>
-          <t>UTAH -33.5</t>
+          <t>DEL -28.5</t>
         </is>
       </c>
       <c r="G120" s="26" t="n">
-        <v>-33.5</v>
+        <v>-28.5</v>
       </c>
       <c r="H120" s="18" t="n">
         <v>-112</v>
       </c>
       <c r="I120" s="20" t="n">
-        <v>0.2585208472473556</v>
+        <v>0.2613150626201174</v>
       </c>
       <c r="J120" s="20" t="n">
         <v>0.5043297540699688</v>
@@ -8733,10 +8733,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L120" s="19" t="n">
-        <v>-0.2697810395450972</v>
+        <v>-0.2669868241723354</v>
       </c>
       <c r="M120" s="19" t="n">
-        <v>-0.5106569677103627</v>
+        <v>-0.5053679171833493</v>
       </c>
       <c r="N120" s="20" t="n">
         <v>0</v>
@@ -8751,7 +8751,7 @@
       </c>
       <c r="Q120" s="17" t="inlineStr">
         <is>
-          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -8788,22 +8788,22 @@
         <v>-42.5</v>
       </c>
       <c r="H121" s="13" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="I121" s="15" t="n">
-        <v>0.2482518098143184</v>
+        <v>0.2449995687561283</v>
       </c>
       <c r="J121" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K121" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L121" s="14" t="n">
-        <v>-0.2709789594164509</v>
+        <v>-0.2671955531950912</v>
       </c>
       <c r="M121" s="14" t="n">
-        <v>-0.521885403320572</v>
+        <v>-0.5216675086189875</v>
       </c>
       <c r="N121" s="15" t="n">
         <v>0</v>
@@ -8830,12 +8830,12 @@
       </c>
       <c r="B122" s="17" t="inlineStr">
         <is>
-          <t>UAPB @ MIZ</t>
+          <t>IDHO @ UTAH</t>
         </is>
       </c>
       <c r="C122" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D122" s="25" t="n">
@@ -8848,17 +8848,17 @@
       </c>
       <c r="F122" s="17" t="inlineStr">
         <is>
-          <t>MIZ -54.5</t>
+          <t>UTAH -33.5</t>
         </is>
       </c>
       <c r="G122" s="26" t="n">
-        <v>-54.5</v>
+        <v>-33.5</v>
       </c>
       <c r="H122" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I122" s="20" t="n">
-        <v>0.250018047672936</v>
+        <v>0.2563559702123712</v>
       </c>
       <c r="J122" s="20" t="n">
         <v>0.5</v>
@@ -8867,10 +8867,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L122" s="19" t="n">
-        <v>-0.2737914761365878</v>
+        <v>-0.2674535535971527</v>
       </c>
       <c r="M122" s="19" t="n">
-        <v>-0.5226928180789403</v>
+        <v>-0.5105931477763822</v>
       </c>
       <c r="N122" s="20" t="n">
         <v>0</v>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="Q122" s="17" t="inlineStr">
         <is>
-          <t>UAPB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -8897,12 +8897,12 @@
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>INST @ PUR</t>
+          <t>UAPB @ MIZ</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 23:00</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D123" s="22" t="n">
@@ -8915,29 +8915,29 @@
       </c>
       <c r="F123" s="12" t="inlineStr">
         <is>
-          <t>PUR -35.5</t>
+          <t>MIZ -54.5</t>
         </is>
       </c>
       <c r="G123" s="23" t="n">
-        <v>-35.5</v>
+        <v>-54.5</v>
       </c>
       <c r="H123" s="13" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="I123" s="15" t="n">
-        <v>0.2539608529598711</v>
+        <v>0.2478531706379516</v>
       </c>
       <c r="J123" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K123" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L123" s="14" t="n">
-        <v>-0.2743410338325817</v>
+        <v>-0.2713775985928176</v>
       </c>
       <c r="M123" s="14" t="n">
-        <v>-0.5192883854688154</v>
+        <v>-0.5226531528454265</v>
       </c>
       <c r="N123" s="15" t="n">
         <v>0</v>
@@ -8952,7 +8952,7 @@
       </c>
       <c r="Q123" s="12" t="inlineStr">
         <is>
-          <t>INST isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>UAPB isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -8964,12 +8964,12 @@
       </c>
       <c r="B124" s="17" t="inlineStr">
         <is>
-          <t>EIU @ MINN</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C124" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D124" s="25" t="n">
@@ -8982,29 +8982,29 @@
       </c>
       <c r="F124" s="17" t="inlineStr">
         <is>
-          <t>MINN -43.5</t>
+          <t>USC -38.5</t>
         </is>
       </c>
       <c r="G124" s="26" t="n">
-        <v>-43.5</v>
+        <v>-38.5</v>
       </c>
       <c r="H124" s="18" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I124" s="20" t="n">
-        <v>0.2525065802931694</v>
+        <v>0.2523210839512047</v>
       </c>
       <c r="J124" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K124" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L124" s="19" t="n">
-        <v>-0.2757953064992834</v>
+        <v>-0.2714884398583192</v>
       </c>
       <c r="M124" s="19" t="n">
-        <v>-0.5220411158736437</v>
+        <v>-0.5182961124567911</v>
       </c>
       <c r="N124" s="20" t="n">
         <v>0</v>
@@ -9019,7 +9019,141 @@
       </c>
       <c r="Q124" s="17" t="inlineStr">
         <is>
+          <t>raw model/market disagreement exceeds the safety limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B125" s="12" t="inlineStr">
+        <is>
+          <t>EIU @ MINN</t>
+        </is>
+      </c>
+      <c r="C125" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-04 00:00</t>
+        </is>
+      </c>
+      <c r="D125" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" s="12" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="F125" s="12" t="inlineStr">
+        <is>
+          <t>MINN -43.5</t>
+        </is>
+      </c>
+      <c r="G125" s="23" t="n">
+        <v>-43.5</v>
+      </c>
+      <c r="H125" s="13" t="n">
+        <v>-110</v>
+      </c>
+      <c r="I125" s="15" t="n">
+        <v>0.250341703258185</v>
+      </c>
+      <c r="J125" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K125" s="15" t="n">
+        <v>0.5238095238095238</v>
+      </c>
+      <c r="L125" s="14" t="n">
+        <v>-0.2734678205513388</v>
+      </c>
+      <c r="M125" s="14" t="n">
+        <v>-0.5220749301434651</v>
+      </c>
+      <c r="N125" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P125" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q125" s="12" t="inlineStr">
+        <is>
           <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B126" s="17" t="inlineStr">
+        <is>
+          <t>INST @ PUR</t>
+        </is>
+      </c>
+      <c r="C126" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-04 23:00</t>
+        </is>
+      </c>
+      <c r="D126" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" s="17" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="F126" s="17" t="inlineStr">
+        <is>
+          <t>PUR -35.5</t>
+        </is>
+      </c>
+      <c r="G126" s="26" t="n">
+        <v>-35.5</v>
+      </c>
+      <c r="H126" s="18" t="n">
+        <v>-112</v>
+      </c>
+      <c r="I126" s="20" t="n">
+        <v>0.2539608529598711</v>
+      </c>
+      <c r="J126" s="20" t="n">
+        <v>0.5043297540699688</v>
+      </c>
+      <c r="K126" s="20" t="n">
+        <v>0.5283018867924528</v>
+      </c>
+      <c r="L126" s="19" t="n">
+        <v>-0.2743410338325817</v>
+      </c>
+      <c r="M126" s="19" t="n">
+        <v>-0.5192883854688154</v>
+      </c>
+      <c r="N126" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P126" s="17" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+      <c r="Q126" s="17" t="inlineStr">
+        <is>
+          <t>INST isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -15996,10 +16130,10 @@
         <v>47.5</v>
       </c>
       <c r="K5" s="13" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="L5" s="13" t="n">
-        <v>-298</v>
+        <v>-310</v>
       </c>
       <c r="M5" s="12" t="inlineStr">
         <is>
@@ -16042,7 +16176,7 @@
         <v>-38.5</v>
       </c>
       <c r="J6" s="30" t="n">
-        <v>59.5</v>
+        <v>60.5</v>
       </c>
       <c r="K6" s="18" t="n"/>
       <c r="L6" s="18" t="n"/>
@@ -16090,10 +16224,10 @@
         <v>53.5</v>
       </c>
       <c r="K7" s="13" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>-218</v>
+        <v>-225</v>
       </c>
       <c r="M7" s="12" t="inlineStr">
         <is>
@@ -16182,16 +16316,16 @@
       </c>
       <c r="H9" s="12" t="inlineStr"/>
       <c r="I9" s="23" t="n">
-        <v>-9.5</v>
+        <v>-10</v>
       </c>
       <c r="J9" s="29" t="n">
         <v>52.5</v>
       </c>
       <c r="K9" s="13" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>-355</v>
+        <v>-380</v>
       </c>
       <c r="M9" s="12" t="inlineStr">
         <is>
@@ -16234,7 +16368,7 @@
         <v>-4</v>
       </c>
       <c r="J10" s="30" t="n">
-        <v>48.5</v>
+        <v>49.5</v>
       </c>
       <c r="K10" s="18" t="n">
         <v>154</v>
@@ -16286,10 +16420,10 @@
         <v>53.5</v>
       </c>
       <c r="K11" s="13" t="n">
-        <v>2000</v>
+        <v>2200</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>-6500</v>
+        <v>-8000</v>
       </c>
       <c r="M11" s="12" t="inlineStr">
         <is>
@@ -16478,10 +16612,10 @@
         <v>49.5</v>
       </c>
       <c r="K15" s="13" t="n">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>-2800</v>
+        <v>-3200</v>
       </c>
       <c r="M15" s="12" t="inlineStr">
         <is>
@@ -16527,10 +16661,10 @@
         <v>55.5</v>
       </c>
       <c r="K16" s="18" t="n">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="L16" s="18" t="n">
-        <v>-10000</v>
+        <v>-20000</v>
       </c>
       <c r="M16" s="17" t="inlineStr">
         <is>
@@ -16764,7 +16898,9 @@
       <c r="I21" s="23" t="n">
         <v>-43.5</v>
       </c>
-      <c r="J21" s="29" t="n"/>
+      <c r="J21" s="29" t="n">
+        <v>51.5</v>
+      </c>
       <c r="K21" s="13" t="n"/>
       <c r="L21" s="13" t="n"/>
       <c r="M21" s="12" t="inlineStr">
@@ -16860,10 +16996,10 @@
         <v>56.5</v>
       </c>
       <c r="K23" s="13" t="n">
-        <v>3000</v>
+        <v>2200</v>
       </c>
       <c r="L23" s="13" t="n">
-        <v>-10000</v>
+        <v>-8000</v>
       </c>
       <c r="M23" s="12" t="inlineStr">
         <is>
@@ -51997,7 +52133,7 @@
         </is>
       </c>
       <c r="B4" s="39" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5">
@@ -52017,7 +52153,7 @@
         </is>
       </c>
       <c r="B6" s="39" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7">

--- a/NCAAF_Edge_Model.xlsx
+++ b/NCAAF_Edge_Model.xlsx
@@ -640,7 +640,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-25T15:27:48+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
+          <t>Generated 2026-08-25T18:02:02+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>Settings!B5+SUMIF('Bet Ledger'!$G$6:$G$9,"&lt;&gt;Pending",'Bet Ledger'!$H$6:$H$9)</f>
+        <f>Settings!B5+SUMIF('Bet Ledger'!$G$6:$G$10,"&lt;&gt;Pending",'Bet Ledger'!$H$6:$H$10)</f>
         <v/>
       </c>
     </row>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>SUMIF('Bet Ledger'!$G$6:$G$9,"&lt;&gt;Pending",'Bet Ledger'!$F$6:$F$9)</f>
+        <f>SUMIF('Bet Ledger'!$G$6:$G$10,"&lt;&gt;Pending",'Bet Ledger'!$F$6:$F$10)</f>
         <v/>
       </c>
     </row>
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>SUMIF('Bet Ledger'!$G$6:$G$9,"&lt;&gt;Pending",'Bet Ledger'!$H$6:$H$9)</f>
+        <f>SUMIF('Bet Ledger'!$G$6:$G$10,"&lt;&gt;Pending",'Bet Ledger'!$H$6:$H$10)</f>
         <v/>
       </c>
     </row>
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="B9" s="7">
-        <f>COUNTIFS('Bet Ledger'!$G$6:$G$9,"&lt;&gt;Pending",'Bet Ledger'!$G$6:$G$9,"&lt;&gt;")</f>
+        <f>COUNTIFS('Bet Ledger'!$G$6:$G$10,"&lt;&gt;Pending",'Bet Ledger'!$G$6:$G$10,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>COUNTIF('Bet Ledger'!$G$6:$G$9,"Win")</f>
+        <f>COUNTIF('Bet Ledger'!$G$6:$G$10,"Win")</f>
         <v/>
       </c>
     </row>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>COUNTIF('Bet Ledger'!$G$6:$G$9,"Loss")</f>
+        <f>COUNTIF('Bet Ledger'!$G$6:$G$10,"Loss")</f>
         <v/>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B12" s="7">
-        <f>COUNTIF('Bet Ledger'!$G$6:$G$9,"Push")</f>
+        <f>COUNTIF('Bet Ledger'!$G$6:$G$10,"Push")</f>
         <v/>
       </c>
     </row>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="B14" s="7">
-        <f>COUNTIF('Bet Ledger'!$G$6:$G$9,"Pending")</f>
+        <f>COUNTIF('Bet Ledger'!$G$6:$G$10,"Pending")</f>
         <v/>
       </c>
     </row>
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -1036,17 +1036,17 @@
       </c>
       <c r="D22" s="17" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E22" s="18" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>0.08339809109262664</v>
+        <v>0.09405980478503773</v>
       </c>
       <c r="G22" s="20" t="n">
-        <v>0.5955932130438462</v>
+        <v>0.6178693285945616</v>
       </c>
       <c r="H22" s="21" t="n"/>
       <c r="I22" s="17" t="inlineStr">
@@ -1063,32 +1063,32 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>AKR @ WAKE</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>UNC +7.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E23" s="13" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0.08007721496452191</v>
+        <v>0.0917323188370931</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0.5993079841952912</v>
+        <v>0.6200342056295459</v>
       </c>
       <c r="H23" s="16" t="n"/>
       <c r="I23" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
     </row>
@@ -1100,30 +1100,67 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>COLO @ GT</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D24" s="17" t="inlineStr">
         <is>
-          <t>Over 50.5</t>
+          <t>UNC +7.5</t>
         </is>
       </c>
       <c r="E24" s="18" t="n">
-        <v>-115</v>
+        <v>-105</v>
       </c>
       <c r="F24" s="19" t="n">
-        <v>0.07840427762989666</v>
+        <v>0.08386062118588167</v>
       </c>
       <c r="G24" s="20" t="n">
-        <v>0.6132879985601292</v>
+        <v>0.5960557431371012</v>
       </c>
       <c r="H24" s="21" t="n"/>
       <c r="I24" s="17" t="inlineStr">
+        <is>
+          <t>2026-08-29 16:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>LEAN</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>COLO @ GT</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>Over 50.5</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>-115</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>0.07840427762989666</v>
+      </c>
+      <c r="G25" s="15" t="n">
+        <v>0.6132879985601292</v>
+      </c>
+      <c r="H25" s="16" t="n"/>
+      <c r="I25" s="12" t="inlineStr">
         <is>
           <t>2026-09-04 00:00</t>
         </is>
@@ -1350,29 +1387,29 @@
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="G6" s="26" t="n">
-        <v>49.5</v>
+        <v>48.5</v>
       </c>
       <c r="H6" s="18" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="I6" s="20" t="n">
-        <v>0.5955932130438462</v>
+        <v>0.6178693285945616</v>
       </c>
       <c r="J6" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5</v>
       </c>
       <c r="K6" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L6" s="19" t="n">
-        <v>0.08339809109262664</v>
+        <v>0.09405980478503773</v>
       </c>
       <c r="M6" s="19" t="n">
-        <v>0.1628248445141758</v>
+        <v>0.1795687182259812</v>
       </c>
       <c r="N6" s="20" t="n">
         <v>0</v>
@@ -1395,12 +1432,12 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>AKR @ WAKE</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D7" s="22" t="n">
@@ -1408,34 +1445,34 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>UNC +7.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="G7" s="23" t="n">
-        <v>-7.5</v>
+        <v>48.5</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>0.5993079841952912</v>
+        <v>0.6200342056295459</v>
       </c>
       <c r="J7" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K7" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L7" s="14" t="n">
-        <v>0.08007721496452191</v>
+        <v>0.0917323188370931</v>
       </c>
       <c r="M7" s="14" t="n">
-        <v>0.1542227843761165</v>
+        <v>0.1736361749416404</v>
       </c>
       <c r="N7" s="15" t="n">
         <v>0</v>
@@ -1458,12 +1495,12 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>COLO @ GT</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D8" s="25" t="n">
@@ -1471,34 +1508,34 @@
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t>Over 50.5</t>
+          <t>UNC +7.5</t>
         </is>
       </c>
       <c r="G8" s="26" t="n">
-        <v>50.5</v>
+        <v>-7.5</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>-115</v>
+        <v>-105</v>
       </c>
       <c r="I8" s="20" t="n">
-        <v>0.6132879985601292</v>
+        <v>0.5960557431371012</v>
       </c>
       <c r="J8" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K8" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L8" s="19" t="n">
-        <v>0.07840427762989666</v>
+        <v>0.08386062118588167</v>
       </c>
       <c r="M8" s="19" t="n">
-        <v>0.1465819103515458</v>
+        <v>0.1637278794581499</v>
       </c>
       <c r="N8" s="20" t="n">
         <v>0</v>
@@ -1516,17 +1553,17 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>INST @ PUR</t>
+          <t>COLO @ GT</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 23:00</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D9" s="22" t="n">
@@ -1534,34 +1571,34 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>INST +35.5</t>
+          <t>Over 50.5</t>
         </is>
       </c>
       <c r="G9" s="23" t="n">
-        <v>-35.5</v>
+        <v>50.5</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>-108</v>
+        <v>-115</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>0.7460391470401289</v>
+        <v>0.6132879985601292</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K9" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L9" s="14" t="n">
-        <v>0.2268083778093596</v>
+        <v>0.07840427762989666</v>
       </c>
       <c r="M9" s="14" t="n">
-        <v>0.4368161350402483</v>
+        <v>0.1465819103515458</v>
       </c>
       <c r="N9" s="15" t="n">
         <v>0</v>
@@ -1574,11 +1611,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q9" s="12" t="inlineStr">
-        <is>
-          <t>INST isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
@@ -1588,12 +1621,12 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>EIU @ MINN</t>
+          <t>INST @ PUR</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-09-04 23:00</t>
         </is>
       </c>
       <c r="D10" s="25" t="n">
@@ -1606,29 +1639,29 @@
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t>EIU +43.5</t>
+          <t>INST +35.5</t>
         </is>
       </c>
       <c r="G10" s="26" t="n">
-        <v>-43.5</v>
+        <v>-35.5</v>
       </c>
       <c r="H10" s="18" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I10" s="20" t="n">
-        <v>0.7496582967418151</v>
+        <v>0.7471065701681774</v>
       </c>
       <c r="J10" s="20" t="n">
-        <v>0.5</v>
+        <v>0.4978050921861282</v>
       </c>
       <c r="K10" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L10" s="19" t="n">
-        <v>0.2258487729322912</v>
+        <v>0.2278758009374081</v>
       </c>
       <c r="M10" s="19" t="n">
-        <v>0.4311658392343742</v>
+        <v>0.4388719129164899</v>
       </c>
       <c r="N10" s="20" t="n">
         <v>0</v>
@@ -1643,7 +1676,7 @@
       </c>
       <c r="Q10" s="17" t="inlineStr">
         <is>
-          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>INST isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -1655,12 +1688,12 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>BCU @ UCF</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D11" s="22" t="n">
@@ -1673,17 +1706,17 @@
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>SJSU +38.5</t>
+          <t>BCU +42.5</t>
         </is>
       </c>
       <c r="G11" s="23" t="n">
-        <v>-38.5</v>
+        <v>-42.5</v>
       </c>
       <c r="H11" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>0.7476789160487953</v>
+        <v>0.7495833131506973</v>
       </c>
       <c r="J11" s="15" t="n">
         <v>0.5</v>
@@ -1692,10 +1725,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L11" s="14" t="n">
-        <v>0.2238693922392715</v>
+        <v>0.2257737893411734</v>
       </c>
       <c r="M11" s="14" t="n">
-        <v>0.4273870215477003</v>
+        <v>0.4310226887422403</v>
       </c>
       <c r="N11" s="15" t="n">
         <v>0</v>
@@ -1710,7 +1743,7 @@
       </c>
       <c r="Q11" s="12" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -1789,12 +1822,12 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>BCU @ UCF</t>
+          <t>EIU @ MINN</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D13" s="22" t="n">
@@ -1807,29 +1840,29 @@
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>BCU +42.5</t>
+          <t>EIU +43.5</t>
         </is>
       </c>
       <c r="G13" s="23" t="n">
-        <v>-42.5</v>
+        <v>-43.5</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>-115</v>
+        <v>-112</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>0.7550004312438716</v>
+        <v>0.7518231737767994</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L13" s="14" t="n">
-        <v>0.2201167103136391</v>
+        <v>0.2235212869843466</v>
       </c>
       <c r="M13" s="14" t="n">
-        <v>0.4115225453689773</v>
+        <v>0.4230938646489417</v>
       </c>
       <c r="N13" s="15" t="n">
         <v>0</v>
@@ -1844,7 +1877,7 @@
       </c>
       <c r="Q13" s="12" t="inlineStr">
         <is>
-          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -1990,12 +2023,12 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>NCAT @ GAST</t>
+          <t>MASS @ RUTG</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 23:00</t>
+          <t>2026-09-03 22:00</t>
         </is>
       </c>
       <c r="D16" s="25" t="n">
@@ -2008,29 +2041,29 @@
       </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
-          <t>NCAT +28.5</t>
+          <t>MASS +29.5</t>
         </is>
       </c>
       <c r="G16" s="26" t="n">
-        <v>-28.5</v>
+        <v>-29.5</v>
       </c>
       <c r="H16" s="18" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="I16" s="20" t="n">
-        <v>0.7431217544793447</v>
+        <v>0.7307755149318647</v>
       </c>
       <c r="J16" s="20" t="n">
-        <v>0.5</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K16" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L16" s="19" t="n">
-        <v>0.2193122306698209</v>
+        <v>0.2185803929806451</v>
       </c>
       <c r="M16" s="19" t="n">
-        <v>0.4186869858242036</v>
+        <v>0.4267521958193548</v>
       </c>
       <c r="N16" s="20" t="n">
         <v>0</v>
@@ -2045,7 +2078,7 @@
       </c>
       <c r="Q16" s="17" t="inlineStr">
         <is>
-          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -2057,12 +2090,12 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>MASS @ RUTG</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 22:00</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D17" s="22" t="n">
@@ -2075,29 +2108,29 @@
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>MASS +30.5</t>
+          <t>SJSU +38.5</t>
         </is>
       </c>
       <c r="G17" s="23" t="n">
-        <v>-30.5</v>
+        <v>-38.5</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>-108</v>
+        <v>-115</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>0.7362293114467701</v>
+        <v>0.7530960341419698</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K17" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L17" s="14" t="n">
-        <v>0.2169985422160008</v>
+        <v>0.2182123132117373</v>
       </c>
       <c r="M17" s="14" t="n">
-        <v>0.4179231183419276</v>
+        <v>0.4079621507871608</v>
       </c>
       <c r="N17" s="15" t="n">
         <v>0</v>
@@ -2124,12 +2157,12 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>NMSU @ FSU</t>
+          <t>NCAT @ GAST</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-04 23:00</t>
         </is>
       </c>
       <c r="D18" s="25" t="n">
@@ -2142,29 +2175,29 @@
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>NMSU +31.5</t>
+          <t>NCAT +28.5</t>
         </is>
       </c>
       <c r="G18" s="26" t="n">
-        <v>-31.5</v>
+        <v>-28.5</v>
       </c>
       <c r="H18" s="18" t="n">
-        <v>-115</v>
+        <v>-112</v>
       </c>
       <c r="I18" s="20" t="n">
-        <v>0.7484052544756881</v>
+        <v>0.7452866315143292</v>
       </c>
       <c r="J18" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K18" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L18" s="19" t="n">
-        <v>0.2135215335454556</v>
+        <v>0.2169847447218763</v>
       </c>
       <c r="M18" s="19" t="n">
-        <v>0.3991924322806341</v>
+        <v>0.4107211239378373</v>
       </c>
       <c r="N18" s="20" t="n">
         <v>0</v>
@@ -2179,7 +2212,7 @@
       </c>
       <c r="Q18" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -2191,12 +2224,12 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>NCAT @ GAST</t>
+          <t>NMSU @ FSU</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 23:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D19" s="22" t="n">
@@ -2204,32 +2237,34 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>NCAT ML</t>
-        </is>
-      </c>
-      <c r="G19" s="23" t="n"/>
+          <t>NMSU +31.5</t>
+        </is>
+      </c>
+      <c r="G19" s="23" t="n">
+        <v>-31.5</v>
+      </c>
       <c r="H19" s="13" t="n">
-        <v>1800</v>
+        <v>-115</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>0.2655422309319856</v>
+        <v>0.7484052544756881</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>0.05094905094905094</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K19" s="15" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L19" s="14" t="n">
-        <v>0.2129106519846172</v>
+        <v>0.2135215335454556</v>
       </c>
       <c r="M19" s="14" t="n">
-        <v>4.045302387707726</v>
+        <v>0.3991924322806341</v>
       </c>
       <c r="N19" s="15" t="n">
         <v>0</v>
@@ -2244,7 +2279,7 @@
       </c>
       <c r="Q19" s="12" t="inlineStr">
         <is>
-          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -2256,12 +2291,12 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>ALB @ BUFF</t>
+          <t>NCAT @ GAST</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-04 23:00</t>
         </is>
       </c>
       <c r="D20" s="25" t="n">
@@ -2269,34 +2304,32 @@
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F20" s="17" t="inlineStr">
         <is>
-          <t>ALB +24.5</t>
-        </is>
-      </c>
-      <c r="G20" s="26" t="n">
-        <v>-24.5</v>
-      </c>
+          <t>NCAT ML</t>
+        </is>
+      </c>
+      <c r="G20" s="26" t="n"/>
       <c r="H20" s="18" t="n">
-        <v>-110</v>
+        <v>1700</v>
       </c>
       <c r="I20" s="20" t="n">
-        <v>0.7320901453539077</v>
+        <v>0.2669368643359646</v>
       </c>
       <c r="J20" s="20" t="n">
-        <v>0.5</v>
+        <v>0.05373831775700934</v>
       </c>
       <c r="K20" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.05555555555555555</v>
       </c>
       <c r="L20" s="19" t="n">
-        <v>0.2082806215443839</v>
+        <v>0.2113813087804091</v>
       </c>
       <c r="M20" s="19" t="n">
-        <v>0.3976266411301875</v>
+        <v>3.804863558047364</v>
       </c>
       <c r="N20" s="20" t="n">
         <v>0</v>
@@ -2311,7 +2344,7 @@
       </c>
       <c r="Q20" s="17" t="inlineStr">
         <is>
-          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2356,7 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>MRMK @ DEL</t>
+          <t>ALB @ BUFF</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
@@ -2336,32 +2369,34 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>MRMK ML</t>
-        </is>
-      </c>
-      <c r="G21" s="23" t="n"/>
+          <t>ALB +24.5</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="n">
+        <v>-24.5</v>
+      </c>
       <c r="H21" s="13" t="n">
-        <v>3500</v>
+        <v>-108</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>0.2320231923220626</v>
+        <v>0.7299252683189232</v>
       </c>
       <c r="J21" s="15" t="n">
-        <v>0.02715849209566274</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K21" s="15" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L21" s="14" t="n">
-        <v>0.2042454145442848</v>
+        <v>0.210694499088154</v>
       </c>
       <c r="M21" s="14" t="n">
-        <v>7.352834923594253</v>
+        <v>0.4057819982438522</v>
       </c>
       <c r="N21" s="15" t="n">
         <v>0</v>
@@ -2376,7 +2411,7 @@
       </c>
       <c r="Q21" s="12" t="inlineStr">
         <is>
-          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -2413,22 +2448,22 @@
         <v>-28.5</v>
       </c>
       <c r="H22" s="18" t="n">
-        <v>-118</v>
+        <v>-112</v>
       </c>
       <c r="I22" s="20" t="n">
-        <v>0.7438096015477024</v>
+        <v>0.7372924157245517</v>
       </c>
       <c r="J22" s="20" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K22" s="20" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L22" s="19" t="n">
-        <v>0.2025251978779776</v>
+        <v>0.2089905289320989</v>
       </c>
       <c r="M22" s="19" t="n">
-        <v>0.3741567215033823</v>
+        <v>0.3955892154786157</v>
       </c>
       <c r="N22" s="20" t="n">
         <v>0</v>
@@ -2480,22 +2515,22 @@
         <v>-23.5</v>
       </c>
       <c r="H23" s="13" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>0.7202139758215249</v>
+        <v>0.716961734763335</v>
       </c>
       <c r="J23" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K23" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L23" s="14" t="n">
-        <v>0.2009832065907556</v>
+        <v>0.2047666128121155</v>
       </c>
       <c r="M23" s="14" t="n">
-        <v>0.3870787682488629</v>
+        <v>0.3997824345379398</v>
       </c>
       <c r="N23" s="15" t="n">
         <v>0</v>
@@ -2522,7 +2557,7 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>ALB @ BUFF</t>
+          <t>MRMK @ DEL</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
@@ -2540,27 +2575,27 @@
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>ALB ML</t>
+          <t>MRMK ML</t>
         </is>
       </c>
       <c r="G24" s="26" t="n"/>
       <c r="H24" s="18" t="n">
-        <v>2200</v>
+        <v>3000</v>
       </c>
       <c r="I24" s="20" t="n">
-        <v>0.2400960739565308</v>
+        <v>0.2342202661742625</v>
       </c>
       <c r="J24" s="20" t="n">
-        <v>0.04216553878188443</v>
+        <v>0.03155263980006248</v>
       </c>
       <c r="K24" s="20" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="L24" s="19" t="n">
-        <v>0.1966178130869655</v>
+        <v>0.2019622016581335</v>
       </c>
       <c r="M24" s="19" t="n">
-        <v>4.522209701000207</v>
+        <v>6.260828251402137</v>
       </c>
       <c r="N24" s="20" t="n">
         <v>0</v>
@@ -2575,7 +2610,7 @@
       </c>
       <c r="Q24" s="17" t="inlineStr">
         <is>
-          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -2587,7 +2622,7 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>WES @ KENN</t>
+          <t>ALB @ BUFF</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
@@ -2600,40 +2635,38 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>WES +22.5</t>
-        </is>
-      </c>
-      <c r="G25" s="23" t="n">
-        <v>-22.5</v>
-      </c>
+          <t>ALB ML</t>
+        </is>
+      </c>
+      <c r="G25" s="23" t="n"/>
       <c r="H25" s="13" t="n">
-        <v>-115</v>
+        <v>2200</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>0.7273466517420963</v>
+        <v>0.2400960739565308</v>
       </c>
       <c r="J25" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.04216553878188443</v>
       </c>
       <c r="K25" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="L25" s="14" t="n">
-        <v>0.1924629308118638</v>
+        <v>0.1966178130869655</v>
       </c>
       <c r="M25" s="14" t="n">
-        <v>0.3598220010830496</v>
+        <v>4.522209701000207</v>
       </c>
       <c r="N25" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O25" s="24" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="P25" s="12" t="inlineStr">
         <is>
@@ -2642,7 +2675,7 @@
       </c>
       <c r="Q25" s="12" t="inlineStr">
         <is>
-          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -2667,32 +2700,34 @@
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>WES ML</t>
-        </is>
-      </c>
-      <c r="G26" s="26" t="n"/>
+          <t>WES +22.5</t>
+        </is>
+      </c>
+      <c r="G26" s="26" t="n">
+        <v>-22.5</v>
+      </c>
       <c r="H26" s="18" t="n">
-        <v>1500</v>
+        <v>-115</v>
       </c>
       <c r="I26" s="20" t="n">
-        <v>0.2370117476831352</v>
+        <v>0.7273466517420963</v>
       </c>
       <c r="J26" s="20" t="n">
-        <v>0.06035889070146819</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K26" s="20" t="n">
-        <v>0.0625</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L26" s="19" t="n">
-        <v>0.1745117476831352</v>
+        <v>0.1924629308118638</v>
       </c>
       <c r="M26" s="19" t="n">
-        <v>2.792187962930162</v>
+        <v>0.3598220010830496</v>
       </c>
       <c r="N26" s="20" t="n">
         <v>0</v>
@@ -2719,12 +2754,12 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>NMSU @ FSU</t>
+          <t>WES @ KENN</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D27" s="22" t="n">
@@ -2737,33 +2772,33 @@
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>NMSU ML</t>
+          <t>WES ML</t>
         </is>
       </c>
       <c r="G27" s="23" t="n"/>
       <c r="H27" s="13" t="n">
-        <v>2200</v>
+        <v>1500</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>0.2169991880608585</v>
+        <v>0.2370117476831352</v>
       </c>
       <c r="J27" s="15" t="n">
-        <v>0.04216553878188443</v>
+        <v>0.06035889070146819</v>
       </c>
       <c r="K27" s="15" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.0625</v>
       </c>
       <c r="L27" s="14" t="n">
-        <v>0.1735209271912933</v>
+        <v>0.1745117476831352</v>
       </c>
       <c r="M27" s="14" t="n">
-        <v>3.990981325399745</v>
+        <v>2.792187962930162</v>
       </c>
       <c r="N27" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O27" s="24" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="P27" s="12" t="inlineStr">
         <is>
@@ -2772,7 +2807,7 @@
       </c>
       <c r="Q27" s="12" t="inlineStr">
         <is>
-          <t>price outside allowed range</t>
+          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -2784,12 +2819,12 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>AKR @ WAKE</t>
+          <t>NMSU @ FSU</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D28" s="25" t="n">
@@ -2802,27 +2837,27 @@
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>AKR ML</t>
+          <t>NMSU ML</t>
         </is>
       </c>
       <c r="G28" s="26" t="n"/>
       <c r="H28" s="18" t="n">
-        <v>1400</v>
+        <v>2200</v>
       </c>
       <c r="I28" s="20" t="n">
-        <v>0.2287754942280706</v>
+        <v>0.2169991880608585</v>
       </c>
       <c r="J28" s="20" t="n">
-        <v>0.06432748538011696</v>
+        <v>0.04216553878188443</v>
       </c>
       <c r="K28" s="20" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="L28" s="19" t="n">
-        <v>0.162108827561404</v>
+        <v>0.1735209271912933</v>
       </c>
       <c r="M28" s="19" t="n">
-        <v>2.43163241342106</v>
+        <v>3.990981325399745</v>
       </c>
       <c r="N28" s="20" t="n">
         <v>0</v>
@@ -2849,12 +2884,12 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>IDHO @ UTAH</t>
+          <t>AKR @ WAKE</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 01:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D29" s="22" t="n">
@@ -2867,27 +2902,27 @@
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>IDHO ML</t>
+          <t>AKR ML</t>
         </is>
       </c>
       <c r="G29" s="23" t="n"/>
       <c r="H29" s="13" t="n">
-        <v>3000</v>
+        <v>1400</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>0.1915726544041398</v>
+        <v>0.2287754942280706</v>
       </c>
       <c r="J29" s="15" t="n">
-        <v>0.03155263980006248</v>
+        <v>0.06432748538011696</v>
       </c>
       <c r="K29" s="15" t="n">
-        <v>0.03225806451612903</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="L29" s="14" t="n">
-        <v>0.1593145898880108</v>
+        <v>0.162108827561404</v>
       </c>
       <c r="M29" s="14" t="n">
-        <v>4.938752286528335</v>
+        <v>2.43163241342106</v>
       </c>
       <c r="N29" s="15" t="n">
         <v>0</v>
@@ -2902,7 +2937,7 @@
       </c>
       <c r="Q29" s="12" t="inlineStr">
         <is>
-          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>price outside allowed range</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2949,7 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>UAB @ ILL</t>
+          <t>IDHO @ UTAH</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
@@ -2932,27 +2967,27 @@
       </c>
       <c r="F30" s="17" t="inlineStr">
         <is>
-          <t>UAB ML</t>
+          <t>IDHO ML</t>
         </is>
       </c>
       <c r="G30" s="26" t="n"/>
       <c r="H30" s="18" t="n">
-        <v>2200</v>
+        <v>3000</v>
       </c>
       <c r="I30" s="20" t="n">
-        <v>0.2017439875221416</v>
+        <v>0.1915726544041398</v>
       </c>
       <c r="J30" s="20" t="n">
-        <v>0.04216553878188443</v>
+        <v>0.03155263980006248</v>
       </c>
       <c r="K30" s="20" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>0.1582657266525764</v>
+        <v>0.1593145898880108</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>3.640111713009257</v>
+        <v>4.938752286528335</v>
       </c>
       <c r="N30" s="20" t="n">
         <v>0</v>
@@ -2967,7 +3002,7 @@
       </c>
       <c r="Q30" s="17" t="inlineStr">
         <is>
-          <t>price outside allowed range</t>
+          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -2979,12 +3014,12 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>MASS @ RUTG</t>
+          <t>UAB @ ILL</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 22:00</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D31" s="22" t="n">
@@ -2997,27 +3032,27 @@
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>MASS ML</t>
+          <t>UAB ML</t>
         </is>
       </c>
       <c r="G31" s="23" t="n"/>
       <c r="H31" s="13" t="n">
-        <v>2000</v>
+        <v>2200</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>0.1963076315941712</v>
+        <v>0.2017439875221416</v>
       </c>
       <c r="J31" s="15" t="n">
-        <v>0.0461215932914046</v>
+        <v>0.04216553878188443</v>
       </c>
       <c r="K31" s="15" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="L31" s="14" t="n">
-        <v>0.1486885839751236</v>
+        <v>0.1582657266525764</v>
       </c>
       <c r="M31" s="14" t="n">
-        <v>3.122460263477595</v>
+        <v>3.640111713009257</v>
       </c>
       <c r="N31" s="15" t="n">
         <v>0</v>
@@ -3044,12 +3079,12 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>JVST @ NDSU</t>
+          <t>MASS @ RUTG</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30</t>
+          <t>2026-09-03 22:00</t>
         </is>
       </c>
       <c r="D32" s="25" t="n">
@@ -3057,34 +3092,32 @@
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F32" s="17" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
-        </is>
-      </c>
-      <c r="G32" s="26" t="n">
-        <v>46.5</v>
-      </c>
+          <t>MASS ML</t>
+        </is>
+      </c>
+      <c r="G32" s="26" t="n"/>
       <c r="H32" s="18" t="n">
-        <v>-112</v>
+        <v>2000</v>
       </c>
       <c r="I32" s="20" t="n">
-        <v>0.6574997451163023</v>
+        <v>0.1963076315941712</v>
       </c>
       <c r="J32" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.0461215932914046</v>
       </c>
       <c r="K32" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.04761904761904762</v>
       </c>
       <c r="L32" s="19" t="n">
-        <v>0.1291978583238494</v>
+        <v>0.1486885839751236</v>
       </c>
       <c r="M32" s="19" t="n">
-        <v>0.2445530889701435</v>
+        <v>3.122460263477595</v>
       </c>
       <c r="N32" s="20" t="n">
         <v>0</v>
@@ -3099,7 +3132,7 @@
       </c>
       <c r="Q32" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>price outside allowed range</t>
         </is>
       </c>
     </row>
@@ -3111,12 +3144,12 @@
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>SAC @ EMU</t>
+          <t>JVST @ NDSU</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 22:30</t>
+          <t>2026-08-29 21:30</t>
         </is>
       </c>
       <c r="D33" s="22" t="n">
@@ -3124,37 +3157,37 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>SAC +10</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="G33" s="23" t="n">
-        <v>-10</v>
+        <v>46.5</v>
       </c>
       <c r="H33" s="13" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>0.6496086093420973</v>
+        <v>0.6574997451163023</v>
       </c>
       <c r="J33" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K33" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L33" s="14" t="n">
-        <v>0.1257990855325735</v>
+        <v>0.1291978583238494</v>
       </c>
       <c r="M33" s="14" t="n">
-        <v>0.2327670346937839</v>
+        <v>0.2445530889701435</v>
       </c>
       <c r="N33" s="15" t="n">
-        <v>0.0308</v>
+        <v>0</v>
       </c>
       <c r="O33" s="24" t="n">
         <v>0.45</v>
@@ -3178,12 +3211,12 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>ALB @ BUFF</t>
+          <t>SAC @ EMU</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-29 22:30</t>
         </is>
       </c>
       <c r="D34" s="25" t="n">
@@ -3191,37 +3224,37 @@
       </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F34" s="17" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>SAC +10</t>
         </is>
       </c>
       <c r="G34" s="26" t="n">
-        <v>48.5</v>
+        <v>-10</v>
       </c>
       <c r="H34" s="18" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I34" s="20" t="n">
-        <v>0.6237538960930264</v>
+        <v>0.6517734863770817</v>
       </c>
       <c r="J34" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K34" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L34" s="19" t="n">
-        <v>0.1045231268622572</v>
+        <v>0.1234715995846288</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>0.2013037998828658</v>
+        <v>0.2265177781236275</v>
       </c>
       <c r="N34" s="20" t="n">
-        <v>0</v>
+        <v>0.0308</v>
       </c>
       <c r="O34" s="27" t="n">
         <v>0.45</v>
@@ -3233,7 +3266,7 @@
       </c>
       <c r="Q34" s="17" t="inlineStr">
         <is>
-          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3278,12 @@
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>NCAT @ GAST</t>
+          <t>ALB @ BUFF</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 23:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D35" s="22" t="n">
@@ -3263,29 +3296,29 @@
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>Under 63.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="G35" s="23" t="n">
-        <v>63.5</v>
+        <v>48.5</v>
       </c>
       <c r="H35" s="13" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>0.6117269964441806</v>
+        <v>0.6237538960930264</v>
       </c>
       <c r="J35" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K35" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L35" s="14" t="n">
-        <v>0.08342510965172778</v>
+        <v>0.1045231268622572</v>
       </c>
       <c r="M35" s="14" t="n">
-        <v>0.1579118146979133</v>
+        <v>0.2013037998828658</v>
       </c>
       <c r="N35" s="15" t="n">
         <v>0</v>
@@ -3300,7 +3333,7 @@
       </c>
       <c r="Q35" s="12" t="inlineStr">
         <is>
-          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -3312,12 +3345,12 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>UAPB @ MIZ</t>
+          <t>NCAT @ GAST</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-09-04 23:00</t>
         </is>
       </c>
       <c r="D36" s="25" t="n">
@@ -3330,29 +3363,29 @@
       </c>
       <c r="F36" s="17" t="inlineStr">
         <is>
-          <t>Under 60.5</t>
+          <t>Under 63.5</t>
         </is>
       </c>
       <c r="G36" s="26" t="n">
-        <v>60.5</v>
+        <v>63.5</v>
       </c>
       <c r="H36" s="18" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I36" s="20" t="n">
-        <v>0.6022946041225494</v>
+        <v>0.6095621194091961</v>
       </c>
       <c r="J36" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5</v>
       </c>
       <c r="K36" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L36" s="19" t="n">
-        <v>0.08306383489178015</v>
+        <v>0.0857525955996723</v>
       </c>
       <c r="M36" s="19" t="n">
-        <v>0.15997479312491</v>
+        <v>0.1637095006902836</v>
       </c>
       <c r="N36" s="20" t="n">
         <v>0</v>
@@ -3367,7 +3400,7 @@
       </c>
       <c r="Q36" s="17" t="inlineStr">
         <is>
-          <t>UAPB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -3379,12 +3412,12 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>SAC @ EMU</t>
+          <t>UAPB @ MIZ</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 22:30</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D37" s="22" t="n">
@@ -3397,29 +3430,29 @@
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>Over 52.5</t>
+          <t>Under 60.5</t>
         </is>
       </c>
       <c r="G37" s="23" t="n">
-        <v>52.5</v>
+        <v>60.5</v>
       </c>
       <c r="H37" s="13" t="n">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>0.592107265818543</v>
+        <v>0.6022946041225494</v>
       </c>
       <c r="J37" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K37" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L37" s="14" t="n">
-        <v>0.07991214386732348</v>
+        <v>0.08306383489178015</v>
       </c>
       <c r="M37" s="14" t="n">
-        <v>0.1560189475504887</v>
+        <v>0.15997479312491</v>
       </c>
       <c r="N37" s="15" t="n">
         <v>0</v>
@@ -3434,7 +3467,7 @@
       </c>
       <c r="Q37" s="12" t="inlineStr">
         <is>
-          <t>correlated with a stronger play on the same game</t>
+          <t>UAPB isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -3446,12 +3479,12 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>WES @ KENN</t>
+          <t>SAC @ EMU</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-29 22:30</t>
         </is>
       </c>
       <c r="D38" s="25" t="n">
@@ -3464,35 +3497,35 @@
       </c>
       <c r="F38" s="17" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>Over 52.5</t>
         </is>
       </c>
       <c r="G38" s="26" t="n">
-        <v>51.5</v>
+        <v>52.5</v>
       </c>
       <c r="H38" s="18" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="I38" s="20" t="n">
-        <v>0.5971070144741464</v>
+        <v>0.592107265818543</v>
       </c>
       <c r="J38" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K38" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>0.07787624524337711</v>
+        <v>0.07991214386732348</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>0.1499838797279857</v>
+        <v>0.1560189475504887</v>
       </c>
       <c r="N38" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O38" s="27" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="P38" s="17" t="inlineStr">
         <is>
@@ -3501,7 +3534,7 @@
       </c>
       <c r="Q38" s="17" t="inlineStr">
         <is>
-          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>correlated with a stronger play on the same game</t>
         </is>
       </c>
     </row>
@@ -3536,22 +3569,22 @@
       </c>
       <c r="G39" s="23" t="n"/>
       <c r="H39" s="13" t="n">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>0.3621290026789783</v>
+        <v>0.3639656274205685</v>
       </c>
       <c r="J39" s="15" t="n">
-        <v>0.274247491638796</v>
+        <v>0.2779207411219763</v>
       </c>
       <c r="K39" s="15" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2898550724637681</v>
       </c>
       <c r="L39" s="14" t="n">
-        <v>0.0764147169646926</v>
+        <v>0.07411055495680036</v>
       </c>
       <c r="M39" s="14" t="n">
-        <v>0.267451509376424</v>
+        <v>0.2556814146009613</v>
       </c>
       <c r="N39" s="15" t="n">
         <v>0</v>
@@ -3574,7 +3607,7 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>AKR @ WAKE</t>
+          <t>WES @ KENN</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
@@ -3592,17 +3625,17 @@
       </c>
       <c r="F40" s="17" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="G40" s="26" t="n">
-        <v>49.5</v>
+        <v>51.5</v>
       </c>
       <c r="H40" s="18" t="n">
         <v>-112</v>
       </c>
       <c r="I40" s="20" t="n">
-        <v>0.603175208172005</v>
+        <v>0.6014367685441151</v>
       </c>
       <c r="J40" s="20" t="n">
         <v>0.5043297540699688</v>
@@ -3611,23 +3644,27 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L40" s="19" t="n">
-        <v>0.07487332137955216</v>
+        <v>0.07313488175166227</v>
       </c>
       <c r="M40" s="19" t="n">
-        <v>0.1417245011827237</v>
+        <v>0.1384338833156464</v>
       </c>
       <c r="N40" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O40" s="27" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="P40" s="17" t="inlineStr">
         <is>
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q40" s="17" t="n"/>
+      <c r="Q40" s="17" t="inlineStr">
+        <is>
+          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
@@ -3729,22 +3766,22 @@
         <v>53.5</v>
       </c>
       <c r="H42" s="18" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="I42" s="20" t="n">
-        <v>0.5740430549239717</v>
+        <v>0.5686259368307972</v>
       </c>
       <c r="J42" s="20" t="n">
-        <v>0.5</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K42" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L42" s="19" t="n">
-        <v>0.05023353111444784</v>
+        <v>0.05643081487957768</v>
       </c>
       <c r="M42" s="19" t="n">
-        <v>0.09590037758212777</v>
+        <v>0.1101744480982231</v>
       </c>
       <c r="N42" s="20" t="n">
         <v>0</v>
@@ -3767,12 +3804,12 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>EIU @ MINN</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D43" s="22" t="n">
@@ -3785,29 +3822,29 @@
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>Under 60.5</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="G43" s="23" t="n">
-        <v>60.5</v>
+        <v>51.5</v>
       </c>
       <c r="H43" s="13" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>0.5606183297218017</v>
+        <v>0.5627832126788681</v>
       </c>
       <c r="J43" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5</v>
       </c>
       <c r="K43" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L43" s="14" t="n">
-        <v>0.04138756049103243</v>
+        <v>0.03897368886934427</v>
       </c>
       <c r="M43" s="14" t="n">
-        <v>0.07970937576050707</v>
+        <v>0.07440431511420276</v>
       </c>
       <c r="N43" s="15" t="n">
         <v>0</v>
@@ -3820,7 +3857,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q43" s="12" t="n"/>
+      <c r="Q43" s="12" t="inlineStr">
+        <is>
+          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="17" t="inlineStr">
@@ -3830,12 +3871,12 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>HAW @ STAN</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D44" s="25" t="n">
@@ -3843,37 +3884,37 @@
       </c>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F44" s="17" t="inlineStr">
         <is>
-          <t>HAW +4</t>
+          <t>Under 60.5</t>
         </is>
       </c>
       <c r="G44" s="26" t="n">
-        <v>-4</v>
+        <v>60.5</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I44" s="20" t="n">
-        <v>0.5666660811488681</v>
+        <v>0.5627832067567862</v>
       </c>
       <c r="J44" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K44" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L44" s="19" t="n">
-        <v>0.03836419435641525</v>
+        <v>0.03897368294726233</v>
       </c>
       <c r="M44" s="19" t="n">
-        <v>0.07044135577437555</v>
+        <v>0.07440430380841001</v>
       </c>
       <c r="N44" s="20" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="O44" s="27" t="n">
         <v>0.45</v>
@@ -3954,12 +3995,12 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>EIU @ MINN</t>
+          <t>HAW @ STAN</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D46" s="25" t="n">
@@ -3967,37 +4008,37 @@
       </c>
       <c r="E46" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F46" s="17" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>HAW +4</t>
         </is>
       </c>
       <c r="G46" s="26" t="n">
-        <v>51.5</v>
+        <v>-4</v>
       </c>
       <c r="H46" s="18" t="n">
-        <v>-112</v>
+        <v>-115</v>
       </c>
       <c r="I46" s="20" t="n">
-        <v>0.5649480897138526</v>
+        <v>0.5699183222070581</v>
       </c>
       <c r="J46" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K46" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L46" s="19" t="n">
-        <v>0.03664620292139975</v>
+        <v>0.03503460127682556</v>
       </c>
       <c r="M46" s="19" t="n">
-        <v>0.0693660269583638</v>
+        <v>0.06353625082439679</v>
       </c>
       <c r="N46" s="20" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="O46" s="27" t="n">
         <v>0.45</v>
@@ -4007,11 +4048,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q46" s="17" t="inlineStr">
-        <is>
-          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q46" s="17" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
@@ -4084,12 +4121,12 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>NMSU @ FSU</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D48" s="25" t="n">
@@ -4097,32 +4134,34 @@
       </c>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F48" s="17" t="inlineStr">
         <is>
-          <t>MEM ML</t>
-        </is>
-      </c>
-      <c r="G48" s="26" t="n"/>
+          <t>Over 52.5</t>
+        </is>
+      </c>
+      <c r="G48" s="26" t="n">
+        <v>52.5</v>
+      </c>
       <c r="H48" s="18" t="n">
-        <v>180</v>
+        <v>-108</v>
       </c>
       <c r="I48" s="20" t="n">
-        <v>0.383035891688529</v>
+        <v>0.5472084462676521</v>
       </c>
       <c r="J48" s="20" t="n">
-        <v>0.3425247738043947</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K48" s="20" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L48" s="19" t="n">
-        <v>0.02589303454567188</v>
+        <v>0.02797767703688281</v>
       </c>
       <c r="M48" s="19" t="n">
-        <v>0.07250049672788117</v>
+        <v>0.05388293355251517</v>
       </c>
       <c r="N48" s="20" t="n">
         <v>0</v>
@@ -4208,12 +4247,12 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>COLO @ GT</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D50" s="25" t="n">
@@ -4226,29 +4265,29 @@
       </c>
       <c r="F50" s="17" t="inlineStr">
         <is>
-          <t>MEM +5.5</t>
+          <t>COLO +6.5</t>
         </is>
       </c>
       <c r="G50" s="26" t="n">
-        <v>-5.5</v>
+        <v>-6.5</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>-112</v>
+        <v>-105</v>
       </c>
       <c r="I50" s="20" t="n">
-        <v>0.5540130817463144</v>
+        <v>0.5359459352051367</v>
       </c>
       <c r="J50" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K50" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L50" s="19" t="n">
-        <v>0.02571119495386154</v>
+        <v>0.02375081325391715</v>
       </c>
       <c r="M50" s="19" t="n">
-        <v>0.04866761901980932</v>
+        <v>0.0463706354005049</v>
       </c>
       <c r="N50" s="20" t="n">
         <v>0</v>
@@ -4271,12 +4310,12 @@
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>COLO @ GT</t>
+          <t>MRMK @ DEL</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D51" s="22" t="n">
@@ -4284,34 +4323,34 @@
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
         <is>
-          <t>COLO +6.5</t>
+          <t>Over 55.5</t>
         </is>
       </c>
       <c r="G51" s="23" t="n">
-        <v>-6.5</v>
+        <v>55.5</v>
       </c>
       <c r="H51" s="13" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>0.5359459352051367</v>
+        <v>0.5416001704595914</v>
       </c>
       <c r="J51" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5</v>
       </c>
       <c r="K51" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L51" s="14" t="n">
-        <v>0.02375081325391715</v>
+        <v>0.01779064665006758</v>
       </c>
       <c r="M51" s="14" t="n">
-        <v>0.0463706354005049</v>
+        <v>0.03396396178649275</v>
       </c>
       <c r="N51" s="15" t="n">
         <v>0</v>
@@ -4324,7 +4363,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q51" s="12" t="n"/>
+      <c r="Q51" s="12" t="inlineStr">
+        <is>
+          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="17" t="inlineStr">
@@ -4357,22 +4400,22 @@
       </c>
       <c r="G52" s="26" t="n"/>
       <c r="H52" s="18" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="I52" s="20" t="n">
-        <v>0.3714942648294812</v>
+        <v>0.3745807138274095</v>
       </c>
       <c r="J52" s="20" t="n">
-        <v>0.3363518758085381</v>
+        <v>0.3425247738043947</v>
       </c>
       <c r="K52" s="20" t="n">
-        <v>0.3508771929824561</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="L52" s="19" t="n">
-        <v>0.0206170718470251</v>
+        <v>0.01743785668455239</v>
       </c>
       <c r="M52" s="19" t="n">
-        <v>0.05875865476402153</v>
+        <v>0.04882599871674664</v>
       </c>
       <c r="N52" s="20" t="n">
         <v>0</v>
@@ -4395,12 +4438,12 @@
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>MRMK @ DEL</t>
+          <t>SJSU @ EMU</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-04 22:30</t>
         </is>
       </c>
       <c r="D53" s="22" t="n">
@@ -4408,34 +4451,32 @@
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
-          <t>Over 55.5</t>
-        </is>
-      </c>
-      <c r="G53" s="23" t="n">
-        <v>55.5</v>
-      </c>
+          <t>SJSU ML</t>
+        </is>
+      </c>
+      <c r="G53" s="23" t="n"/>
       <c r="H53" s="13" t="n">
-        <v>-110</v>
+        <v>180</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>0.5416001704595914</v>
+        <v>0.3741599606283899</v>
       </c>
       <c r="J53" s="15" t="n">
-        <v>0.5</v>
+        <v>0.3425247738043947</v>
       </c>
       <c r="K53" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="L53" s="14" t="n">
-        <v>0.01779064665006758</v>
+        <v>0.0170171034855327</v>
       </c>
       <c r="M53" s="14" t="n">
-        <v>0.03396396178649275</v>
+        <v>0.04764788975949152</v>
       </c>
       <c r="N53" s="15" t="n">
         <v>0</v>
@@ -4448,11 +4489,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q53" s="12" t="inlineStr">
-        <is>
-          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q53" s="12" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="17" t="inlineStr">
@@ -4462,12 +4499,12 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>SJSU @ EMU</t>
+          <t>COLO @ GT</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 22:30</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D54" s="25" t="n">
@@ -4480,27 +4517,27 @@
       </c>
       <c r="F54" s="17" t="inlineStr">
         <is>
-          <t>SJSU ML</t>
+          <t>COLO ML</t>
         </is>
       </c>
       <c r="G54" s="26" t="n"/>
       <c r="H54" s="18" t="n">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="I54" s="20" t="n">
-        <v>0.3741599606283899</v>
+        <v>0.3446539939839948</v>
       </c>
       <c r="J54" s="20" t="n">
-        <v>0.3425247738043947</v>
+        <v>0.3146067415730336</v>
       </c>
       <c r="K54" s="20" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.3278688524590164</v>
       </c>
       <c r="L54" s="19" t="n">
-        <v>0.0170171034855327</v>
+        <v>0.0167851415249784</v>
       </c>
       <c r="M54" s="19" t="n">
-        <v>0.04764788975949152</v>
+        <v>0.05119468165118402</v>
       </c>
       <c r="N54" s="20" t="n">
         <v>0</v>
@@ -4523,12 +4560,12 @@
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>SJSU @ EMU</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 22:30</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D55" s="22" t="n">
@@ -4541,29 +4578,29 @@
       </c>
       <c r="F55" s="12" t="inlineStr">
         <is>
-          <t>SJSU +5.5</t>
+          <t>MEM +4.5</t>
         </is>
       </c>
       <c r="G55" s="23" t="n">
-        <v>-5.5</v>
+        <v>-4.5</v>
       </c>
       <c r="H55" s="13" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>0.5451972766345791</v>
+        <v>0.5397080135747594</v>
       </c>
       <c r="J55" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K55" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L55" s="14" t="n">
-        <v>0.01689538984212624</v>
+        <v>0.01589848976523556</v>
       </c>
       <c r="M55" s="14" t="n">
-        <v>0.03198055934402461</v>
+        <v>0.03035166227908614</v>
       </c>
       <c r="N55" s="15" t="n">
         <v>0</v>
@@ -4586,12 +4623,12 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>COLO @ GT</t>
+          <t>JVST @ NDSU</t>
         </is>
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-08-29 21:30</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
@@ -4599,35 +4636,37 @@
       </c>
       <c r="E56" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F56" s="17" t="inlineStr">
         <is>
-          <t>COLO ML</t>
-        </is>
-      </c>
-      <c r="G56" s="26" t="n"/>
+          <t>JVST +7</t>
+        </is>
+      </c>
+      <c r="G56" s="26" t="n">
+        <v>-7</v>
+      </c>
       <c r="H56" s="18" t="n">
-        <v>205</v>
+        <v>-115</v>
       </c>
       <c r="I56" s="20" t="n">
-        <v>0.3446539939839948</v>
+        <v>0.5499855318495314</v>
       </c>
       <c r="J56" s="20" t="n">
-        <v>0.3146067415730336</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K56" s="20" t="n">
-        <v>0.3278688524590164</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L56" s="19" t="n">
-        <v>0.0167851415249784</v>
+        <v>0.01510181091929885</v>
       </c>
       <c r="M56" s="19" t="n">
-        <v>0.05119468165118402</v>
+        <v>0.02680803788623665</v>
       </c>
       <c r="N56" s="20" t="n">
-        <v>0</v>
+        <v>0.0505</v>
       </c>
       <c r="O56" s="27" t="n">
         <v>0.45</v>
@@ -4647,12 +4686,12 @@
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>JVST @ NDSU</t>
+          <t>SJSU @ EMU</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30</t>
+          <t>2026-09-04 22:30</t>
         </is>
       </c>
       <c r="D57" s="22" t="n">
@@ -4665,32 +4704,32 @@
       </c>
       <c r="F57" s="12" t="inlineStr">
         <is>
-          <t>JVST +7</t>
+          <t>SJSU +4.5</t>
         </is>
       </c>
       <c r="G57" s="23" t="n">
-        <v>-7</v>
+        <v>-4.5</v>
       </c>
       <c r="H57" s="13" t="n">
-        <v>-115</v>
+        <v>-105</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>0.5499855318495314</v>
+        <v>0.5253691652874209</v>
       </c>
       <c r="J57" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K57" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L57" s="14" t="n">
-        <v>0.01510181091929885</v>
+        <v>0.01317404333620142</v>
       </c>
       <c r="M57" s="14" t="n">
-        <v>0.02680803788623665</v>
+        <v>0.02572075127544082</v>
       </c>
       <c r="N57" s="15" t="n">
-        <v>0.0505</v>
+        <v>0</v>
       </c>
       <c r="O57" s="24" t="n">
         <v>0.45</v>
@@ -4710,12 +4749,12 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
@@ -4723,34 +4762,32 @@
       </c>
       <c r="E58" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F58" s="17" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
-        </is>
-      </c>
-      <c r="G58" s="26" t="n">
-        <v>47.5</v>
-      </c>
+          <t>MEM ML</t>
+        </is>
+      </c>
+      <c r="G58" s="26" t="n"/>
       <c r="H58" s="18" t="n">
-        <v>-110</v>
+        <v>160</v>
       </c>
       <c r="I58" s="20" t="n">
-        <v>0.5376883257015108</v>
+        <v>0.396303332895533</v>
       </c>
       <c r="J58" s="20" t="n">
-        <v>0.5</v>
+        <v>0.3690596562184025</v>
       </c>
       <c r="K58" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="L58" s="19" t="n">
-        <v>0.01387880189198698</v>
+        <v>0.01168794828014835</v>
       </c>
       <c r="M58" s="19" t="n">
-        <v>0.02649589452106615</v>
+        <v>0.03038866552838582</v>
       </c>
       <c r="N58" s="20" t="n">
         <v>0</v>
@@ -4773,12 +4810,12 @@
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>NMSU @ FSU</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D59" s="22" t="n">
@@ -4791,29 +4828,29 @@
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
-          <t>Over 53.5</t>
+          <t>Over 47.5</t>
         </is>
       </c>
       <c r="G59" s="23" t="n">
-        <v>53.5</v>
+        <v>47.5</v>
       </c>
       <c r="H59" s="13" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>0.5276563112932702</v>
+        <v>0.5398532027364953</v>
       </c>
       <c r="J59" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K59" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L59" s="14" t="n">
-        <v>0.008425542062500901</v>
+        <v>0.01155131594404246</v>
       </c>
       <c r="M59" s="14" t="n">
-        <v>0.01622696989815003</v>
+        <v>0.02186499089408034</v>
       </c>
       <c r="N59" s="15" t="n">
         <v>0</v>
@@ -4859,22 +4896,22 @@
       </c>
       <c r="G60" s="26" t="n"/>
       <c r="H60" s="18" t="n">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="I60" s="20" t="n">
-        <v>0.3308036085807733</v>
+        <v>0.3283150740711329</v>
       </c>
       <c r="J60" s="20" t="n">
-        <v>0.3092071169459319</v>
+        <v>0.3042300479266514</v>
       </c>
       <c r="K60" s="20" t="n">
-        <v>0.3225806451612903</v>
+        <v>0.3174603174603174</v>
       </c>
       <c r="L60" s="19" t="n">
-        <v>0.008222963419482976</v>
+        <v>0.01085475661081547</v>
       </c>
       <c r="M60" s="19" t="n">
-        <v>0.02549118660039718</v>
+        <v>0.03419248332406866</v>
       </c>
       <c r="N60" s="20" t="n">
         <v>0</v>
@@ -4897,12 +4934,12 @@
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>IDHO @ UTAH</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 01:00</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D61" s="22" t="n">
@@ -4925,7 +4962,7 @@
         <v>-110</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>0.5278465354893196</v>
+        <v>0.5298211850615678</v>
       </c>
       <c r="J61" s="15" t="n">
         <v>0.5</v>
@@ -4934,10 +4971,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L61" s="14" t="n">
-        <v>0.004037011679795754</v>
+        <v>0.006011661252043998</v>
       </c>
       <c r="M61" s="14" t="n">
-        <v>0.007707022297791966</v>
+        <v>0.01147680784481137</v>
       </c>
       <c r="N61" s="15" t="n">
         <v>0</v>
@@ -4950,11 +4987,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q61" s="12" t="inlineStr">
-        <is>
-          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q61" s="12" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="17" t="inlineStr">
@@ -4964,12 +4997,12 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
@@ -4982,29 +5015,29 @@
       </c>
       <c r="F62" s="17" t="inlineStr">
         <is>
-          <t>Over 56.5</t>
+          <t>Over 53.5</t>
         </is>
       </c>
       <c r="G62" s="26" t="n">
-        <v>56.5</v>
+        <v>53.5</v>
       </c>
       <c r="H62" s="18" t="n">
-        <v>-112</v>
+        <v>-105</v>
       </c>
       <c r="I62" s="20" t="n">
-        <v>0.5319860620965522</v>
+        <v>0.5145050826711687</v>
       </c>
       <c r="J62" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K62" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L62" s="19" t="n">
-        <v>0.003684175304099369</v>
+        <v>0.002309960719949156</v>
       </c>
       <c r="M62" s="19" t="n">
-        <v>0.006973617539902333</v>
+        <v>0.004509923310376918</v>
       </c>
       <c r="N62" s="20" t="n">
         <v>0</v>
@@ -5027,7 +5060,7 @@
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>UAB @ ILL</t>
+          <t>IDHO @ UTAH</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
@@ -5052,22 +5085,22 @@
         <v>56.5</v>
       </c>
       <c r="H63" s="13" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>0.5177573195518956</v>
+        <v>0.5300114125243041</v>
       </c>
       <c r="J63" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K63" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L63" s="14" t="n">
-        <v>-0.00147344967887364</v>
+        <v>0.001709525731851236</v>
       </c>
       <c r="M63" s="14" t="n">
-        <v>-0.00283775493708982</v>
+        <v>0.003235887992432629</v>
       </c>
       <c r="N63" s="15" t="n">
         <v>0</v>
@@ -5080,7 +5113,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q63" s="12" t="n"/>
+      <c r="Q63" s="12" t="inlineStr">
+        <is>
+          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="17" t="inlineStr">
@@ -5090,12 +5127,12 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>UAB @ ILL</t>
         </is>
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D64" s="25" t="n">
@@ -5108,29 +5145,29 @@
       </c>
       <c r="F64" s="17" t="inlineStr">
         <is>
-          <t>Over 53.5</t>
+          <t>Over 56.5</t>
         </is>
       </c>
       <c r="G64" s="26" t="n">
-        <v>53.5</v>
+        <v>56.5</v>
       </c>
       <c r="H64" s="18" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I64" s="20" t="n">
-        <v>0.5199222007643431</v>
+        <v>0.5177573195518956</v>
       </c>
       <c r="J64" s="20" t="n">
-        <v>0.5</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K64" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L64" s="19" t="n">
-        <v>-0.003887323045180691</v>
+        <v>-0.00147344967887364</v>
       </c>
       <c r="M64" s="19" t="n">
-        <v>-0.007421253086253965</v>
+        <v>-0.00283775493708982</v>
       </c>
       <c r="N64" s="20" t="n">
         <v>0</v>
@@ -5287,12 +5324,12 @@
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>UAB @ ILL</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D67" s="22" t="n">
@@ -5305,29 +5342,29 @@
       </c>
       <c r="F67" s="12" t="inlineStr">
         <is>
-          <t>Under 53.5</t>
+          <t>Under 56.5</t>
         </is>
       </c>
       <c r="G67" s="23" t="n">
-        <v>53.5</v>
+        <v>56.5</v>
       </c>
       <c r="H67" s="13" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>0.4800777992356569</v>
+        <v>0.4822426804481044</v>
       </c>
       <c r="J67" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K67" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L67" s="14" t="n">
-        <v>-0.04373172457386698</v>
+        <v>-0.04605920634434846</v>
       </c>
       <c r="M67" s="14" t="n">
-        <v>-0.08348783782283686</v>
+        <v>-0.08718349772323103</v>
       </c>
       <c r="N67" s="15" t="n">
         <v>0</v>
@@ -5350,7 +5387,7 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>UAB @ ILL</t>
+          <t>IDHO @ UTAH</t>
         </is>
       </c>
       <c r="C68" s="17" t="inlineStr">
@@ -5375,22 +5412,22 @@
         <v>56.5</v>
       </c>
       <c r="H68" s="18" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="I68" s="20" t="n">
-        <v>0.4822426804481044</v>
+        <v>0.4699885874756959</v>
       </c>
       <c r="J68" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K68" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L68" s="19" t="n">
-        <v>-0.04605920634434846</v>
+        <v>-0.04924218175507333</v>
       </c>
       <c r="M68" s="19" t="n">
-        <v>-0.08718349772323103</v>
+        <v>-0.09483679449125221</v>
       </c>
       <c r="N68" s="20" t="n">
         <v>0</v>
@@ -5403,7 +5440,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q68" s="17" t="n"/>
+      <c r="Q68" s="17" t="inlineStr">
+        <is>
+          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
@@ -5413,12 +5454,12 @@
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D69" s="22" t="n">
@@ -5431,29 +5472,29 @@
       </c>
       <c r="F69" s="12" t="inlineStr">
         <is>
-          <t>Under 56.5</t>
+          <t>Under 53.5</t>
         </is>
       </c>
       <c r="G69" s="23" t="n">
-        <v>56.5</v>
+        <v>53.5</v>
       </c>
       <c r="H69" s="13" t="n">
-        <v>-108</v>
+        <v>-115</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>0.4680139379034478</v>
+        <v>0.4854949173288313</v>
       </c>
       <c r="J69" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K69" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L69" s="14" t="n">
-        <v>-0.05121683132732147</v>
+        <v>-0.04938880360140119</v>
       </c>
       <c r="M69" s="14" t="n">
-        <v>-0.09863982329706344</v>
+        <v>-0.09233558934175018</v>
       </c>
       <c r="N69" s="15" t="n">
         <v>0</v>
@@ -5476,12 +5517,12 @@
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>JVST @ NDSU</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C70" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D70" s="25" t="n">
@@ -5489,32 +5530,34 @@
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F70" s="17" t="inlineStr">
         <is>
-          <t>NDSU ML</t>
-        </is>
-      </c>
-      <c r="G70" s="26" t="n"/>
+          <t>Under 56.5</t>
+        </is>
+      </c>
+      <c r="G70" s="26" t="n">
+        <v>56.5</v>
+      </c>
       <c r="H70" s="18" t="n">
-        <v>-258</v>
+        <v>-110</v>
       </c>
       <c r="I70" s="20" t="n">
-        <v>0.6691963914192267</v>
+        <v>0.4701788149384322</v>
       </c>
       <c r="J70" s="20" t="n">
-        <v>0.6907928830540681</v>
+        <v>0.5</v>
       </c>
       <c r="K70" s="20" t="n">
-        <v>0.7206703910614525</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L70" s="19" t="n">
-        <v>-0.05147399964222577</v>
+        <v>-0.05363070887109167</v>
       </c>
       <c r="M70" s="19" t="n">
-        <v>-0.07142516229425128</v>
+        <v>-0.1023858987539022</v>
       </c>
       <c r="N70" s="20" t="n">
         <v>0</v>
@@ -5537,12 +5580,12 @@
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>IDHO @ UTAH</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 01:00</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D71" s="22" t="n">
@@ -5550,34 +5593,32 @@
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
         <is>
-          <t>Under 56.5</t>
-        </is>
-      </c>
-      <c r="G71" s="23" t="n">
-        <v>56.5</v>
-      </c>
+          <t>UNLV ML</t>
+        </is>
+      </c>
+      <c r="G71" s="23" t="n"/>
       <c r="H71" s="13" t="n">
-        <v>-110</v>
+        <v>-192</v>
       </c>
       <c r="I71" s="15" t="n">
-        <v>0.4721534645106804</v>
+        <v>0.603696667104467</v>
       </c>
       <c r="J71" s="15" t="n">
-        <v>0.5</v>
+        <v>0.6309403437815976</v>
       </c>
       <c r="K71" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.6575342465753424</v>
       </c>
       <c r="L71" s="14" t="n">
-        <v>-0.05165605929884343</v>
+        <v>-0.05383757947087542</v>
       </c>
       <c r="M71" s="14" t="n">
-        <v>-0.09861611320688279</v>
+        <v>-0.08187798544528968</v>
       </c>
       <c r="N71" s="15" t="n">
         <v>0</v>
@@ -5590,11 +5631,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q71" s="12" t="inlineStr">
-        <is>
-          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q71" s="12" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="17" t="inlineStr">
@@ -5604,12 +5641,12 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>NMSU @ FSU</t>
+          <t>JVST @ NDSU</t>
         </is>
       </c>
       <c r="C72" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-08-29 21:30</t>
         </is>
       </c>
       <c r="D72" s="25" t="n">
@@ -5617,34 +5654,32 @@
       </c>
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F72" s="17" t="inlineStr">
         <is>
-          <t>Under 53.5</t>
-        </is>
-      </c>
-      <c r="G72" s="26" t="n">
-        <v>53.5</v>
-      </c>
+          <t>NDSU ML</t>
+        </is>
+      </c>
+      <c r="G72" s="26" t="n"/>
       <c r="H72" s="18" t="n">
-        <v>-112</v>
+        <v>-265</v>
       </c>
       <c r="I72" s="20" t="n">
-        <v>0.4723436887067298</v>
+        <v>0.6716849259288671</v>
       </c>
       <c r="J72" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.6957699520733487</v>
       </c>
       <c r="K72" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.726027397260274</v>
       </c>
       <c r="L72" s="19" t="n">
-        <v>-0.055958198085723</v>
+        <v>-0.05434247133140691</v>
       </c>
       <c r="M72" s="19" t="n">
-        <v>-0.1059208749479757</v>
+        <v>-0.07484906428665483</v>
       </c>
       <c r="N72" s="20" t="n">
         <v>0</v>
@@ -5728,12 +5763,12 @@
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>SJSU @ EMU</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C74" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 22:30</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D74" s="25" t="n">
@@ -5741,32 +5776,34 @@
       </c>
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F74" s="17" t="inlineStr">
         <is>
-          <t>EMU ML</t>
-        </is>
-      </c>
-      <c r="G74" s="26" t="n"/>
+          <t>Under 47.5</t>
+        </is>
+      </c>
+      <c r="G74" s="26" t="n">
+        <v>47.5</v>
+      </c>
       <c r="H74" s="18" t="n">
-        <v>-218</v>
+        <v>-108</v>
       </c>
       <c r="I74" s="20" t="n">
-        <v>0.6258400393716101</v>
+        <v>0.4601467972635047</v>
       </c>
       <c r="J74" s="20" t="n">
-        <v>0.6574752261956054</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K74" s="20" t="n">
-        <v>0.6855345911949685</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L74" s="19" t="n">
-        <v>-0.05969455182335837</v>
+        <v>-0.05908397196726456</v>
       </c>
       <c r="M74" s="19" t="n">
-        <v>-0.08707737376067881</v>
+        <v>-0.1137913534184353</v>
       </c>
       <c r="N74" s="20" t="n">
         <v>0</v>
@@ -5789,12 +5826,12 @@
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>SJSU @ EMU</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-09-04 22:30</t>
         </is>
       </c>
       <c r="D75" s="22" t="n">
@@ -5802,34 +5839,32 @@
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
-        </is>
-      </c>
-      <c r="G75" s="23" t="n">
-        <v>47.5</v>
-      </c>
+          <t>EMU ML</t>
+        </is>
+      </c>
+      <c r="G75" s="23" t="n"/>
       <c r="H75" s="13" t="n">
-        <v>-110</v>
+        <v>-218</v>
       </c>
       <c r="I75" s="15" t="n">
-        <v>0.4623116742984892</v>
+        <v>0.6258400393716101</v>
       </c>
       <c r="J75" s="15" t="n">
-        <v>0.5</v>
+        <v>0.6574752261956054</v>
       </c>
       <c r="K75" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.6855345911949685</v>
       </c>
       <c r="L75" s="14" t="n">
-        <v>-0.06149784951103465</v>
+        <v>-0.05969455182335837</v>
       </c>
       <c r="M75" s="14" t="n">
-        <v>-0.117404985430157</v>
+        <v>-0.08707737376067881</v>
       </c>
       <c r="N75" s="15" t="n">
         <v>0</v>
@@ -5852,12 +5887,12 @@
       </c>
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>JVST @ NDSU</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C76" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D76" s="25" t="n">
@@ -5865,37 +5900,35 @@
       </c>
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F76" s="17" t="inlineStr">
         <is>
-          <t>NDSU -7</t>
-        </is>
-      </c>
-      <c r="G76" s="26" t="n">
-        <v>-7</v>
-      </c>
+          <t>UVA ML</t>
+        </is>
+      </c>
+      <c r="G76" s="26" t="n"/>
       <c r="H76" s="18" t="n">
-        <v>-105</v>
+        <v>-218</v>
       </c>
       <c r="I76" s="20" t="n">
-        <v>0.4500144681504686</v>
+        <v>0.6254192861725905</v>
       </c>
       <c r="J76" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.6574752261956054</v>
       </c>
       <c r="K76" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.6855345911949685</v>
       </c>
       <c r="L76" s="19" t="n">
-        <v>-0.06218065380075088</v>
+        <v>-0.06011530502237805</v>
       </c>
       <c r="M76" s="19" t="n">
-        <v>-0.1152697169483107</v>
+        <v>-0.08769113301429471</v>
       </c>
       <c r="N76" s="20" t="n">
-        <v>0.0505</v>
+        <v>0</v>
       </c>
       <c r="O76" s="27" t="n">
         <v>0.45</v>
@@ -5915,12 +5948,12 @@
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>SJSU @ EMU</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-09-04 22:30</t>
         </is>
       </c>
       <c r="D77" s="22" t="n">
@@ -5928,32 +5961,34 @@
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
-          <t>UVA ML</t>
-        </is>
-      </c>
-      <c r="G77" s="23" t="n"/>
+          <t>EMU -4.5</t>
+        </is>
+      </c>
+      <c r="G77" s="23" t="n">
+        <v>-4.5</v>
+      </c>
       <c r="H77" s="13" t="n">
-        <v>-225</v>
+        <v>-115</v>
       </c>
       <c r="I77" s="15" t="n">
-        <v>0.6285057351705188</v>
+        <v>0.4746308347125791</v>
       </c>
       <c r="J77" s="15" t="n">
-        <v>0.6636481241914618</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K77" s="15" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L77" s="14" t="n">
-        <v>-0.06380195713717352</v>
+        <v>-0.06025288621765346</v>
       </c>
       <c r="M77" s="14" t="n">
-        <v>-0.0921583825314729</v>
+        <v>-0.112646700319961</v>
       </c>
       <c r="N77" s="15" t="n">
         <v>0</v>
@@ -5976,12 +6011,12 @@
       </c>
       <c r="B78" s="17" t="inlineStr">
         <is>
-          <t>SJSU @ EMU</t>
+          <t>JVST @ NDSU</t>
         </is>
       </c>
       <c r="C78" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 22:30</t>
+          <t>2026-08-29 21:30</t>
         </is>
       </c>
       <c r="D78" s="25" t="n">
@@ -5994,32 +6029,32 @@
       </c>
       <c r="F78" s="17" t="inlineStr">
         <is>
-          <t>EMU -5.5</t>
+          <t>NDSU -7</t>
         </is>
       </c>
       <c r="G78" s="26" t="n">
-        <v>-5.5</v>
+        <v>-7</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="I78" s="20" t="n">
-        <v>0.4548027233654209</v>
+        <v>0.4500144681504686</v>
       </c>
       <c r="J78" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K78" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L78" s="19" t="n">
-        <v>-0.06442804586534834</v>
+        <v>-0.06218065380075088</v>
       </c>
       <c r="M78" s="19" t="n">
-        <v>-0.1240836438888189</v>
+        <v>-0.1152697169483107</v>
       </c>
       <c r="N78" s="20" t="n">
-        <v>0</v>
+        <v>0.0505</v>
       </c>
       <c r="O78" s="27" t="n">
         <v>0.45</v>
@@ -6039,12 +6074,12 @@
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>MRMK @ DEL</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D79" s="22" t="n">
@@ -6052,22 +6087,22 @@
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
-          <t>Under 55.5</t>
+          <t>UNLV -4.5</t>
         </is>
       </c>
       <c r="G79" s="23" t="n">
-        <v>55.5</v>
+        <v>-4.5</v>
       </c>
       <c r="H79" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I79" s="15" t="n">
-        <v>0.4583998295404086</v>
+        <v>0.4602919864252407</v>
       </c>
       <c r="J79" s="15" t="n">
         <v>0.5</v>
@@ -6076,10 +6111,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L79" s="14" t="n">
-        <v>-0.06540969426911525</v>
+        <v>-0.06351753738428317</v>
       </c>
       <c r="M79" s="14" t="n">
-        <v>-0.1248730526955836</v>
+        <v>-0.1212607531881769</v>
       </c>
       <c r="N79" s="15" t="n">
         <v>0</v>
@@ -6092,11 +6127,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q79" s="12" t="inlineStr">
-        <is>
-          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q79" s="12" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="17" t="inlineStr">
@@ -6106,12 +6137,12 @@
       </c>
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>MRMK @ DEL</t>
         </is>
       </c>
       <c r="C80" s="17" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D80" s="25" t="n">
@@ -6119,32 +6150,34 @@
       </c>
       <c r="E80" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F80" s="17" t="inlineStr">
         <is>
-          <t>UNLV ML</t>
-        </is>
-      </c>
-      <c r="G80" s="26" t="n"/>
+          <t>Under 55.5</t>
+        </is>
+      </c>
+      <c r="G80" s="26" t="n">
+        <v>55.5</v>
+      </c>
       <c r="H80" s="18" t="n">
-        <v>-218</v>
+        <v>-110</v>
       </c>
       <c r="I80" s="20" t="n">
-        <v>0.616964108311471</v>
+        <v>0.4583998295404086</v>
       </c>
       <c r="J80" s="20" t="n">
-        <v>0.6574752261956054</v>
+        <v>0.5</v>
       </c>
       <c r="K80" s="20" t="n">
-        <v>0.6855345911949685</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L80" s="19" t="n">
-        <v>-0.06857048288349754</v>
+        <v>-0.06540969426911525</v>
       </c>
       <c r="M80" s="19" t="n">
-        <v>-0.1000248328300561</v>
+        <v>-0.1248730526955836</v>
       </c>
       <c r="N80" s="20" t="n">
         <v>0</v>
@@ -6157,7 +6190,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q80" s="17" t="n"/>
+      <c r="Q80" s="17" t="inlineStr">
+        <is>
+          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="12" t="inlineStr">
@@ -6293,12 +6330,12 @@
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>NMSU @ FSU</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D83" s="22" t="n">
@@ -6306,34 +6343,34 @@
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F83" s="12" t="inlineStr">
         <is>
-          <t>UNLV -5.5</t>
+          <t>Under 52.5</t>
         </is>
       </c>
       <c r="G83" s="23" t="n">
-        <v>-5.5</v>
+        <v>52.5</v>
       </c>
       <c r="H83" s="13" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I83" s="15" t="n">
-        <v>0.4459869182536856</v>
+        <v>0.4527915537323479</v>
       </c>
       <c r="J83" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K83" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L83" s="14" t="n">
-        <v>-0.07324385097708364</v>
+        <v>-0.07551033306010491</v>
       </c>
       <c r="M83" s="14" t="n">
-        <v>-0.1410622315114202</v>
+        <v>-0.1429302732923415</v>
       </c>
       <c r="N83" s="15" t="n">
         <v>0</v>
@@ -6480,12 +6517,12 @@
       </c>
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>EIU @ MINN</t>
+          <t>HAW @ STAN</t>
         </is>
       </c>
       <c r="C86" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D86" s="25" t="n">
@@ -6493,37 +6530,37 @@
       </c>
       <c r="E86" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F86" s="17" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>STAN -4</t>
         </is>
       </c>
       <c r="G86" s="26" t="n">
-        <v>51.5</v>
+        <v>-4</v>
       </c>
       <c r="H86" s="18" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="I86" s="20" t="n">
-        <v>0.4350519102861474</v>
+        <v>0.4300816777929419</v>
       </c>
       <c r="J86" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K86" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L86" s="19" t="n">
-        <v>-0.08417885894462185</v>
+        <v>-0.08211344415827765</v>
       </c>
       <c r="M86" s="19" t="n">
-        <v>-0.1621222468563086</v>
+        <v>-0.1555115377793785</v>
       </c>
       <c r="N86" s="20" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="O86" s="27" t="n">
         <v>0.45</v>
@@ -6533,11 +6570,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q86" s="17" t="inlineStr">
-        <is>
-          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q86" s="17" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="12" t="inlineStr">
@@ -6547,12 +6580,12 @@
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>HAW @ STAN</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D87" s="22" t="n">
@@ -6560,37 +6593,37 @@
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F87" s="12" t="inlineStr">
         <is>
-          <t>STAN -4</t>
+          <t>Over 60.5</t>
         </is>
       </c>
       <c r="G87" s="23" t="n">
-        <v>-4</v>
+        <v>60.5</v>
       </c>
       <c r="H87" s="13" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I87" s="15" t="n">
-        <v>0.4333339188511319</v>
+        <v>0.4372167932432138</v>
       </c>
       <c r="J87" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5</v>
       </c>
       <c r="K87" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L87" s="14" t="n">
-        <v>-0.08589685037963735</v>
+        <v>-0.08659273056631001</v>
       </c>
       <c r="M87" s="14" t="n">
-        <v>-0.1604724948268336</v>
+        <v>-0.1653133947175008</v>
       </c>
       <c r="N87" s="15" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="O87" s="24" t="n">
         <v>0.45</v>
@@ -6610,12 +6643,12 @@
       </c>
       <c r="B88" s="17" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>EIU @ MINN</t>
         </is>
       </c>
       <c r="C88" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D88" s="25" t="n">
@@ -6628,29 +6661,29 @@
       </c>
       <c r="F88" s="17" t="inlineStr">
         <is>
-          <t>Over 60.5</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="G88" s="26" t="n">
-        <v>60.5</v>
+        <v>51.5</v>
       </c>
       <c r="H88" s="18" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I88" s="20" t="n">
-        <v>0.4393816702781982</v>
+        <v>0.4372167873211319</v>
       </c>
       <c r="J88" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K88" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L88" s="19" t="n">
-        <v>-0.08892021651425458</v>
+        <v>-0.08659273648839194</v>
       </c>
       <c r="M88" s="19" t="n">
-        <v>-0.1683132669734104</v>
+        <v>-0.1653134060232936</v>
       </c>
       <c r="N88" s="20" t="n">
         <v>0</v>
@@ -6663,7 +6696,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q88" s="17" t="n"/>
+      <c r="Q88" s="17" t="inlineStr">
+        <is>
+          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="12" t="inlineStr">
@@ -6698,22 +6735,22 @@
         <v>53.5</v>
       </c>
       <c r="H89" s="13" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="I89" s="15" t="n">
-        <v>0.4259569450760283</v>
+        <v>0.4313740631692028</v>
       </c>
       <c r="J89" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K89" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L89" s="14" t="n">
-        <v>-0.09785257873349551</v>
+        <v>-0.1035096577610297</v>
       </c>
       <c r="M89" s="14" t="n">
-        <v>-0.1868094684912186</v>
+        <v>-0.1935180558140992</v>
       </c>
       <c r="N89" s="15" t="n">
         <v>0</v>
@@ -6826,22 +6863,22 @@
       </c>
       <c r="G91" s="23" t="n"/>
       <c r="H91" s="13" t="n">
-        <v>-310</v>
+        <v>-305</v>
       </c>
       <c r="I91" s="15" t="n">
-        <v>0.6378709973210217</v>
+        <v>0.6360343725794315</v>
       </c>
       <c r="J91" s="15" t="n">
-        <v>0.725752508361204</v>
+        <v>0.7220792588780237</v>
       </c>
       <c r="K91" s="15" t="n">
-        <v>0.7560975609756098</v>
+        <v>0.7530864197530864</v>
       </c>
       <c r="L91" s="14" t="n">
-        <v>-0.1182265636545881</v>
+        <v>-0.1170520471736549</v>
       </c>
       <c r="M91" s="14" t="n">
-        <v>-0.1563641648334875</v>
+        <v>-0.1554297675584598</v>
       </c>
       <c r="N91" s="15" t="n">
         <v>0</v>
@@ -6864,7 +6901,7 @@
       </c>
       <c r="B92" s="17" t="inlineStr">
         <is>
-          <t>AKR @ WAKE</t>
+          <t>WES @ KENN</t>
         </is>
       </c>
       <c r="C92" s="17" t="inlineStr">
@@ -6882,17 +6919,17 @@
       </c>
       <c r="F92" s="17" t="inlineStr">
         <is>
-          <t>Under 49.5</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="G92" s="26" t="n">
-        <v>49.5</v>
+        <v>51.5</v>
       </c>
       <c r="H92" s="18" t="n">
         <v>-108</v>
       </c>
       <c r="I92" s="20" t="n">
-        <v>0.396824791827995</v>
+        <v>0.3985632314558849</v>
       </c>
       <c r="J92" s="20" t="n">
         <v>0.4956702459300312</v>
@@ -6901,23 +6938,27 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L92" s="19" t="n">
-        <v>-0.1224059774027743</v>
+        <v>-0.1206675377748844</v>
       </c>
       <c r="M92" s="19" t="n">
-        <v>-0.2357448453683059</v>
+        <v>-0.2323967394182957</v>
       </c>
       <c r="N92" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O92" s="27" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="P92" s="17" t="inlineStr">
         <is>
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q92" s="17" t="n"/>
+      <c r="Q92" s="17" t="inlineStr">
+        <is>
+          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="12" t="inlineStr">
@@ -6927,12 +6968,12 @@
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>WES @ KENN</t>
+          <t>COLO @ GT</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D93" s="22" t="n">
@@ -6945,46 +6986,42 @@
       </c>
       <c r="F93" s="12" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>Under 50.5</t>
         </is>
       </c>
       <c r="G93" s="23" t="n">
-        <v>51.5</v>
+        <v>50.5</v>
       </c>
       <c r="H93" s="13" t="n">
-        <v>-112</v>
+        <v>-105</v>
       </c>
       <c r="I93" s="15" t="n">
-        <v>0.4028929855258536</v>
+        <v>0.3867120014398708</v>
       </c>
       <c r="J93" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K93" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L93" s="14" t="n">
-        <v>-0.1254089012665992</v>
+        <v>-0.1254831205113487</v>
       </c>
       <c r="M93" s="14" t="n">
-        <v>-0.2373811345403485</v>
+        <v>-0.2449908543316808</v>
       </c>
       <c r="N93" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O93" s="24" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="P93" s="12" t="inlineStr">
         <is>
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q93" s="12" t="inlineStr">
-        <is>
-          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q93" s="12" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="17" t="inlineStr">
@@ -6994,12 +7031,12 @@
       </c>
       <c r="B94" s="17" t="inlineStr">
         <is>
-          <t>COLO @ GT</t>
+          <t>SAC @ EMU</t>
         </is>
       </c>
       <c r="C94" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-08-29 22:30</t>
         </is>
       </c>
       <c r="D94" s="25" t="n">
@@ -7012,29 +7049,29 @@
       </c>
       <c r="F94" s="17" t="inlineStr">
         <is>
-          <t>Under 50.5</t>
+          <t>Under 52.5</t>
         </is>
       </c>
       <c r="G94" s="26" t="n">
-        <v>50.5</v>
+        <v>52.5</v>
       </c>
       <c r="H94" s="18" t="n">
-        <v>-105</v>
+        <v>-115</v>
       </c>
       <c r="I94" s="20" t="n">
-        <v>0.3867120014398708</v>
+        <v>0.407892734181457</v>
       </c>
       <c r="J94" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K94" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L94" s="19" t="n">
-        <v>-0.1254831205113487</v>
+        <v>-0.1269909867487755</v>
       </c>
       <c r="M94" s="19" t="n">
-        <v>-0.2449908543316808</v>
+        <v>-0.2374179317477109</v>
       </c>
       <c r="N94" s="20" t="n">
         <v>0</v>
@@ -7057,12 +7094,12 @@
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>SAC @ EMU</t>
+          <t>UAPB @ MIZ</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 22:30</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D95" s="22" t="n">
@@ -7075,29 +7112,29 @@
       </c>
       <c r="F95" s="12" t="inlineStr">
         <is>
-          <t>Under 52.5</t>
+          <t>Over 60.5</t>
         </is>
       </c>
       <c r="G95" s="23" t="n">
-        <v>52.5</v>
+        <v>60.5</v>
       </c>
       <c r="H95" s="13" t="n">
-        <v>-115</v>
+        <v>-112</v>
       </c>
       <c r="I95" s="15" t="n">
-        <v>0.407892734181457</v>
+        <v>0.3977053958774506</v>
       </c>
       <c r="J95" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K95" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L95" s="14" t="n">
-        <v>-0.1269909867487755</v>
+        <v>-0.1305964909150022</v>
       </c>
       <c r="M95" s="14" t="n">
-        <v>-0.2374179317477109</v>
+        <v>-0.2472005006605399</v>
       </c>
       <c r="N95" s="15" t="n">
         <v>0</v>
@@ -7110,7 +7147,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q95" s="12" t="n"/>
+      <c r="Q95" s="12" t="inlineStr">
+        <is>
+          <t>UAPB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="17" t="inlineStr">
@@ -7145,22 +7186,22 @@
         <v>-7.5</v>
       </c>
       <c r="H96" s="18" t="n">
-        <v>-112</v>
+        <v>-115</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>0.4006920158047088</v>
+        <v>0.4039442568628988</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L96" s="19" t="n">
-        <v>-0.127609870987744</v>
+        <v>-0.1309394640673337</v>
       </c>
       <c r="M96" s="19" t="n">
-        <v>-0.2415472557982298</v>
+        <v>-0.2447998676041457</v>
       </c>
       <c r="N96" s="20" t="n">
         <v>0</v>
@@ -7183,12 +7224,12 @@
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>HAW @ STAN</t>
+          <t>NCAT @ GAST</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-04 23:00</t>
         </is>
       </c>
       <c r="D97" s="22" t="n">
@@ -7201,29 +7242,29 @@
       </c>
       <c r="F97" s="12" t="inlineStr">
         <is>
-          <t>Under 49.5</t>
+          <t>Over 63.5</t>
         </is>
       </c>
       <c r="G97" s="23" t="n">
-        <v>49.5</v>
+        <v>63.5</v>
       </c>
       <c r="H97" s="13" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="I97" s="15" t="n">
-        <v>0.4044067869561538</v>
+        <v>0.3904378805908039</v>
       </c>
       <c r="J97" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5</v>
       </c>
       <c r="K97" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L97" s="14" t="n">
-        <v>-0.1304769339740787</v>
+        <v>-0.13337164321872</v>
       </c>
       <c r="M97" s="14" t="n">
-        <v>-0.2439351374297994</v>
+        <v>-0.2546185915993744</v>
       </c>
       <c r="N97" s="15" t="n">
         <v>0</v>
@@ -7236,7 +7277,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q97" s="12" t="n"/>
+      <c r="Q97" s="12" t="inlineStr">
+        <is>
+          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="17" t="inlineStr">
@@ -7246,12 +7291,12 @@
       </c>
       <c r="B98" s="17" t="inlineStr">
         <is>
-          <t>UAPB @ MIZ</t>
+          <t>AKR @ WAKE</t>
         </is>
       </c>
       <c r="C98" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D98" s="25" t="n">
@@ -7264,29 +7309,29 @@
       </c>
       <c r="F98" s="17" t="inlineStr">
         <is>
-          <t>Over 60.5</t>
+          <t>Under 48.5</t>
         </is>
       </c>
       <c r="G98" s="26" t="n">
-        <v>60.5</v>
+        <v>48.5</v>
       </c>
       <c r="H98" s="18" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="I98" s="20" t="n">
-        <v>0.3977053958774506</v>
+        <v>0.3799657943704541</v>
       </c>
       <c r="J98" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K98" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L98" s="19" t="n">
-        <v>-0.1305964909150022</v>
+        <v>-0.1392649748603152</v>
       </c>
       <c r="M98" s="19" t="n">
-        <v>-0.2472005006605399</v>
+        <v>-0.2682140256569032</v>
       </c>
       <c r="N98" s="20" t="n">
         <v>0</v>
@@ -7299,11 +7344,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q98" s="17" t="inlineStr">
-        <is>
-          <t>UAPB isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q98" s="17" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="12" t="inlineStr">
@@ -7313,12 +7354,12 @@
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>NCAT @ GAST</t>
+          <t>HAW @ STAN</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 23:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D99" s="22" t="n">
@@ -7331,29 +7372,29 @@
       </c>
       <c r="F99" s="12" t="inlineStr">
         <is>
-          <t>Over 63.5</t>
+          <t>Under 48.5</t>
         </is>
       </c>
       <c r="G99" s="23" t="n">
-        <v>63.5</v>
+        <v>48.5</v>
       </c>
       <c r="H99" s="13" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I99" s="15" t="n">
-        <v>0.3882730035558194</v>
+        <v>0.3821306714054384</v>
       </c>
       <c r="J99" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5</v>
       </c>
       <c r="K99" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L99" s="14" t="n">
-        <v>-0.1309577656749499</v>
+        <v>-0.1416788524040854</v>
       </c>
       <c r="M99" s="14" t="n">
-        <v>-0.2522149561147182</v>
+        <v>-0.270477809135072</v>
       </c>
       <c r="N99" s="15" t="n">
         <v>0</v>
@@ -7366,11 +7407,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q99" s="12" t="inlineStr">
-        <is>
-          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q99" s="12" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="17" t="inlineStr">
@@ -7533,22 +7570,22 @@
         <v>-10</v>
       </c>
       <c r="H102" s="18" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I102" s="20" t="n">
-        <v>0.3503913906579027</v>
+        <v>0.3482265136229183</v>
       </c>
       <c r="J102" s="20" t="n">
-        <v>0.5</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K102" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L102" s="19" t="n">
-        <v>-0.1734181331516211</v>
+        <v>-0.171004255607851</v>
       </c>
       <c r="M102" s="19" t="n">
-        <v>-0.3208769320138066</v>
+        <v>-0.3192007316465091</v>
       </c>
       <c r="N102" s="20" t="n">
         <v>0.0308</v>
@@ -8055,22 +8092,22 @@
       </c>
       <c r="G110" s="26" t="n"/>
       <c r="H110" s="18" t="n">
-        <v>-20000</v>
+        <v>-10000</v>
       </c>
       <c r="I110" s="20" t="n">
-        <v>0.7679768076779374</v>
+        <v>0.7657797338257375</v>
       </c>
       <c r="J110" s="20" t="n">
-        <v>0.9728415079043372</v>
+        <v>0.9684473601999376</v>
       </c>
       <c r="K110" s="20" t="n">
-        <v>0.9950248756218906</v>
+        <v>0.9900990099009901</v>
       </c>
       <c r="L110" s="19" t="n">
-        <v>-0.2270480679439532</v>
+        <v>-0.2243192760752526</v>
       </c>
       <c r="M110" s="19" t="n">
-        <v>-0.228183308283673</v>
+        <v>-0.2265624688360051</v>
       </c>
       <c r="N110" s="20" t="n">
         <v>0</v>
@@ -8252,22 +8289,22 @@
       </c>
       <c r="G113" s="23" t="n"/>
       <c r="H113" s="13" t="n">
-        <v>-5000</v>
+        <v>-4500</v>
       </c>
       <c r="I113" s="15" t="n">
-        <v>0.7344577690680144</v>
+        <v>0.7330631356640354</v>
       </c>
       <c r="J113" s="15" t="n">
-        <v>0.949050949050949</v>
+        <v>0.9462616822429908</v>
       </c>
       <c r="K113" s="15" t="n">
-        <v>0.9803921568627451</v>
+        <v>0.9782608695652174</v>
       </c>
       <c r="L113" s="14" t="n">
-        <v>-0.2459343877947306</v>
+        <v>-0.245197733901182</v>
       </c>
       <c r="M113" s="14" t="n">
-        <v>-0.2508530755506253</v>
+        <v>-0.2506465724323195</v>
       </c>
       <c r="N113" s="15" t="n">
         <v>0</v>
@@ -8319,22 +8356,22 @@
         <v>-23.5</v>
       </c>
       <c r="H114" s="18" t="n">
-        <v>-112</v>
+        <v>-115</v>
       </c>
       <c r="I114" s="20" t="n">
-        <v>0.279786024178475</v>
+        <v>0.283038265236665</v>
       </c>
       <c r="J114" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K114" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L114" s="19" t="n">
-        <v>-0.2485158626139778</v>
+        <v>-0.2518454556935675</v>
       </c>
       <c r="M114" s="19" t="n">
-        <v>-0.4704050256621722</v>
+        <v>-0.4708415041227568</v>
       </c>
       <c r="N114" s="20" t="n">
         <v>0</v>
@@ -8386,22 +8423,22 @@
         <v>-28.5</v>
       </c>
       <c r="H115" s="13" t="n">
-        <v>-102</v>
+        <v>-108</v>
       </c>
       <c r="I115" s="15" t="n">
-        <v>0.2561903984522976</v>
+        <v>0.2627075842754483</v>
       </c>
       <c r="J115" s="15" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K115" s="15" t="n">
-        <v>0.504950495049505</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L115" s="14" t="n">
-        <v>-0.2487600965972073</v>
+        <v>-0.2565231849553209</v>
       </c>
       <c r="M115" s="14" t="n">
-        <v>-0.4926425442415282</v>
+        <v>-0.494044652506544</v>
       </c>
       <c r="N115" s="15" t="n">
         <v>0</v>
@@ -8453,22 +8490,22 @@
         <v>-24.5</v>
       </c>
       <c r="H116" s="18" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="I116" s="20" t="n">
-        <v>0.2679098546460923</v>
+        <v>0.2700747316810768</v>
       </c>
       <c r="J116" s="20" t="n">
-        <v>0.5</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K116" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L116" s="19" t="n">
-        <v>-0.2558996691634315</v>
+        <v>-0.2582271551113761</v>
       </c>
       <c r="M116" s="19" t="n">
-        <v>-0.4885357320392782</v>
+        <v>-0.4887871150322476</v>
       </c>
       <c r="N116" s="20" t="n">
         <v>0</v>
@@ -8562,12 +8599,12 @@
       </c>
       <c r="B118" s="17" t="inlineStr">
         <is>
-          <t>MASS @ RUTG</t>
+          <t>NCAT @ GAST</t>
         </is>
       </c>
       <c r="C118" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 22:00</t>
+          <t>2026-09-04 23:00</t>
         </is>
       </c>
       <c r="D118" s="25" t="n">
@@ -8580,29 +8617,29 @@
       </c>
       <c r="F118" s="17" t="inlineStr">
         <is>
-          <t>RUTG -30.5</t>
+          <t>GAST -28.5</t>
         </is>
       </c>
       <c r="G118" s="26" t="n">
-        <v>-30.5</v>
+        <v>-28.5</v>
       </c>
       <c r="H118" s="18" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="I118" s="20" t="n">
-        <v>0.2637706885532299</v>
+        <v>0.2547133684856709</v>
       </c>
       <c r="J118" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K118" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L118" s="19" t="n">
-        <v>-0.2645311982392229</v>
+        <v>-0.2645174007450984</v>
       </c>
       <c r="M118" s="19" t="n">
-        <v>-0.5007197680956719</v>
+        <v>-0.5094409199535228</v>
       </c>
       <c r="N118" s="20" t="n">
         <v>0</v>
@@ -8617,7 +8654,7 @@
       </c>
       <c r="Q118" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -8629,12 +8666,12 @@
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>NCAT @ GAST</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 23:00</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D119" s="22" t="n">
@@ -8647,29 +8684,29 @@
       </c>
       <c r="F119" s="12" t="inlineStr">
         <is>
-          <t>GAST -28.5</t>
+          <t>USC -38.5</t>
         </is>
       </c>
       <c r="G119" s="23" t="n">
-        <v>-28.5</v>
+        <v>-38.5</v>
       </c>
       <c r="H119" s="13" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="I119" s="15" t="n">
-        <v>0.2568782455206553</v>
+        <v>0.2469039658580302</v>
       </c>
       <c r="J119" s="15" t="n">
-        <v>0.5</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K119" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L119" s="14" t="n">
-        <v>-0.2669312782888685</v>
+        <v>-0.2652911560931893</v>
       </c>
       <c r="M119" s="14" t="n">
-        <v>-0.5095960767332944</v>
+        <v>-0.5179493999914648</v>
       </c>
       <c r="N119" s="15" t="n">
         <v>0</v>
@@ -8684,7 +8721,7 @@
       </c>
       <c r="Q119" s="12" t="inlineStr">
         <is>
-          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8733,12 @@
       </c>
       <c r="B120" s="17" t="inlineStr">
         <is>
-          <t>MRMK @ DEL</t>
+          <t>MASS @ RUTG</t>
         </is>
       </c>
       <c r="C120" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-03 22:00</t>
         </is>
       </c>
       <c r="D120" s="25" t="n">
@@ -8714,29 +8751,29 @@
       </c>
       <c r="F120" s="17" t="inlineStr">
         <is>
-          <t>DEL -28.5</t>
+          <t>RUTG -29.5</t>
         </is>
       </c>
       <c r="G120" s="26" t="n">
-        <v>-28.5</v>
+        <v>-29.5</v>
       </c>
       <c r="H120" s="18" t="n">
-        <v>-112</v>
+        <v>-115</v>
       </c>
       <c r="I120" s="20" t="n">
-        <v>0.2613150626201174</v>
+        <v>0.2692244850681354</v>
       </c>
       <c r="J120" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K120" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L120" s="19" t="n">
-        <v>-0.2669868241723354</v>
+        <v>-0.2656592358620971</v>
       </c>
       <c r="M120" s="19" t="n">
-        <v>-0.5053679171833493</v>
+        <v>-0.4966672670465295</v>
       </c>
       <c r="N120" s="20" t="n">
         <v>0</v>
@@ -8751,7 +8788,7 @@
       </c>
       <c r="Q120" s="17" t="inlineStr">
         <is>
-          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -8763,7 +8800,7 @@
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>BCU @ UCF</t>
+          <t>MRMK @ DEL</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
@@ -8781,29 +8818,29 @@
       </c>
       <c r="F121" s="12" t="inlineStr">
         <is>
-          <t>UCF -42.5</t>
+          <t>DEL -28.5</t>
         </is>
       </c>
       <c r="G121" s="23" t="n">
-        <v>-42.5</v>
+        <v>-28.5</v>
       </c>
       <c r="H121" s="13" t="n">
-        <v>-105</v>
+        <v>-112</v>
       </c>
       <c r="I121" s="15" t="n">
-        <v>0.2449995687561283</v>
+        <v>0.2613150626201174</v>
       </c>
       <c r="J121" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K121" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L121" s="14" t="n">
-        <v>-0.2671955531950912</v>
+        <v>-0.2669868241723354</v>
       </c>
       <c r="M121" s="14" t="n">
-        <v>-0.5216675086189875</v>
+        <v>-0.5053679171833493</v>
       </c>
       <c r="N121" s="15" t="n">
         <v>0</v>
@@ -8818,7 +8855,7 @@
       </c>
       <c r="Q121" s="12" t="inlineStr">
         <is>
-          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -8897,12 +8934,12 @@
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>UAPB @ MIZ</t>
+          <t>INST @ PUR</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-09-04 23:00</t>
         </is>
       </c>
       <c r="D123" s="22" t="n">
@@ -8915,29 +8952,29 @@
       </c>
       <c r="F123" s="12" t="inlineStr">
         <is>
-          <t>MIZ -54.5</t>
+          <t>PUR -35.5</t>
         </is>
       </c>
       <c r="G123" s="23" t="n">
-        <v>-54.5</v>
+        <v>-35.5</v>
       </c>
       <c r="H123" s="13" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I123" s="15" t="n">
-        <v>0.2478531706379516</v>
+        <v>0.2528934298318226</v>
       </c>
       <c r="J123" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5021949078138718</v>
       </c>
       <c r="K123" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L123" s="14" t="n">
-        <v>-0.2713775985928176</v>
+        <v>-0.2709160939777012</v>
       </c>
       <c r="M123" s="14" t="n">
-        <v>-0.5226531528454265</v>
+        <v>-0.5172034521392477</v>
       </c>
       <c r="N123" s="15" t="n">
         <v>0</v>
@@ -8952,7 +8989,7 @@
       </c>
       <c r="Q123" s="12" t="inlineStr">
         <is>
-          <t>UAPB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>INST isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -8964,12 +9001,12 @@
       </c>
       <c r="B124" s="17" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>EIU @ MINN</t>
         </is>
       </c>
       <c r="C124" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D124" s="25" t="n">
@@ -8982,29 +9019,29 @@
       </c>
       <c r="F124" s="17" t="inlineStr">
         <is>
-          <t>USC -38.5</t>
+          <t>MINN -43.5</t>
         </is>
       </c>
       <c r="G124" s="26" t="n">
-        <v>-38.5</v>
+        <v>-43.5</v>
       </c>
       <c r="H124" s="18" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I124" s="20" t="n">
-        <v>0.2523210839512047</v>
+        <v>0.2481768262232006</v>
       </c>
       <c r="J124" s="20" t="n">
-        <v>0.5</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K124" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L124" s="19" t="n">
-        <v>-0.2714884398583192</v>
+        <v>-0.2710539430075687</v>
       </c>
       <c r="M124" s="19" t="n">
-        <v>-0.5182961124567911</v>
+        <v>-0.5220298161627247</v>
       </c>
       <c r="N124" s="20" t="n">
         <v>0</v>
@@ -9019,7 +9056,7 @@
       </c>
       <c r="Q124" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -9031,7 +9068,7 @@
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>EIU @ MINN</t>
+          <t>UAPB @ MIZ</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
@@ -9049,29 +9086,29 @@
       </c>
       <c r="F125" s="12" t="inlineStr">
         <is>
-          <t>MINN -43.5</t>
+          <t>MIZ -54.5</t>
         </is>
       </c>
       <c r="G125" s="23" t="n">
-        <v>-43.5</v>
+        <v>-54.5</v>
       </c>
       <c r="H125" s="13" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I125" s="15" t="n">
-        <v>0.250341703258185</v>
+        <v>0.2478531706379516</v>
       </c>
       <c r="J125" s="15" t="n">
-        <v>0.5</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K125" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L125" s="14" t="n">
-        <v>-0.2734678205513388</v>
+        <v>-0.2713775985928176</v>
       </c>
       <c r="M125" s="14" t="n">
-        <v>-0.5220749301434651</v>
+        <v>-0.5226531528454265</v>
       </c>
       <c r="N125" s="15" t="n">
         <v>0</v>
@@ -9086,7 +9123,7 @@
       </c>
       <c r="Q125" s="12" t="inlineStr">
         <is>
-          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>UAPB isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -9098,12 +9135,12 @@
       </c>
       <c r="B126" s="17" t="inlineStr">
         <is>
-          <t>INST @ PUR</t>
+          <t>BCU @ UCF</t>
         </is>
       </c>
       <c r="C126" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 23:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D126" s="25" t="n">
@@ -9116,29 +9153,29 @@
       </c>
       <c r="F126" s="17" t="inlineStr">
         <is>
-          <t>PUR -35.5</t>
+          <t>UCF -42.5</t>
         </is>
       </c>
       <c r="G126" s="26" t="n">
-        <v>-35.5</v>
+        <v>-42.5</v>
       </c>
       <c r="H126" s="18" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I126" s="20" t="n">
-        <v>0.2539608529598711</v>
+        <v>0.2504166868493028</v>
       </c>
       <c r="J126" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K126" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L126" s="19" t="n">
-        <v>-0.2743410338325817</v>
+        <v>-0.273392836960221</v>
       </c>
       <c r="M126" s="19" t="n">
-        <v>-0.5192883854688154</v>
+        <v>-0.5219317796513311</v>
       </c>
       <c r="N126" s="20" t="n">
         <v>0</v>
@@ -9153,7 +9190,7 @@
       </c>
       <c r="Q126" s="17" t="inlineStr">
         <is>
-          <t>INST isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -9171,7 +9208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9352,12 +9389,12 @@
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>HAW @ STAN</t>
+          <t>AKR @ WAKE</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
@@ -9367,14 +9404,14 @@
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E7" s="18" t="n">
-        <v>-105</v>
+        <v>-112</v>
       </c>
       <c r="F7" s="21" t="n">
-        <v>21.5</v>
+        <v>24.5</v>
       </c>
       <c r="G7" s="17" t="inlineStr">
         <is>
@@ -9399,13 +9436,13 @@
         </is>
       </c>
       <c r="L7" s="19" t="n">
-        <v>0.0834</v>
+        <v>0.0917</v>
       </c>
       <c r="M7" s="19" t="n"/>
       <c r="N7" s="17" t="n"/>
       <c r="O7" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>
@@ -9417,24 +9454,24 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>SAC @ EMU</t>
+          <t>HAW @ STAN</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>SAC ML</t>
+          <t>Over 49.5</t>
         </is>
       </c>
       <c r="E8" s="13" t="n">
-        <v>280</v>
+        <v>-105</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>18</v>
+        <v>21.5</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -9459,7 +9496,7 @@
         </is>
       </c>
       <c r="L8" s="14" t="n">
-        <v>0.1055</v>
+        <v>0.0834</v>
       </c>
       <c r="M8" s="14" t="n"/>
       <c r="N8" s="12" t="n"/>
@@ -9477,24 +9514,24 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>SAC @ EMU</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>UNC +7.5</t>
+          <t>SAC ML</t>
         </is>
       </c>
       <c r="E9" s="18" t="n">
-        <v>-108</v>
+        <v>280</v>
       </c>
       <c r="F9" s="21" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G9" s="17" t="inlineStr">
         <is>
@@ -9519,11 +9556,71 @@
         </is>
       </c>
       <c r="L9" s="19" t="n">
-        <v>0.0801</v>
+        <v>0.1055</v>
       </c>
       <c r="M9" s="19" t="n"/>
       <c r="N9" s="17" t="n"/>
       <c r="O9" s="17" t="inlineStr">
+        <is>
+          <t>Draft Kings</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>UNC @ TCU</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>UNC +7.5</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>-108</v>
+      </c>
+      <c r="F10" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H10" s="16">
+        <f>IF(OR($G10="",$G10="Pending"),"",ROUND(IF($G10="Win",IF($E10&gt;0,$F10*$E10/100,$F10*100/-$E10),IF($G10="Loss",-$F10,0)),2))</f>
+        <v/>
+      </c>
+      <c r="I10" s="16">
+        <f>Settings!$B$5+SUM($H$6:$H10)</f>
+        <v/>
+      </c>
+      <c r="J10" s="14">
+        <f>IFERROR(SUM($H$6:$H10)/SUMIF($G$6:$G10,"&lt;&gt;Pending",$F$6:$F10),"")</f>
+        <v/>
+      </c>
+      <c r="K10" s="12" t="inlineStr">
+        <is>
+          <t>LEAN</t>
+        </is>
+      </c>
+      <c r="L10" s="14" t="n">
+        <v>0.0801</v>
+      </c>
+      <c r="M10" s="14" t="n"/>
+      <c r="N10" s="12" t="n"/>
+      <c r="O10" s="12" t="inlineStr">
         <is>
           <t>Draft Kings</t>
         </is>
@@ -16130,10 +16227,10 @@
         <v>47.5</v>
       </c>
       <c r="K5" s="13" t="n">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="L5" s="13" t="n">
-        <v>-310</v>
+        <v>-305</v>
       </c>
       <c r="M5" s="12" t="inlineStr">
         <is>
@@ -16224,10 +16321,10 @@
         <v>53.5</v>
       </c>
       <c r="K7" s="13" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>-225</v>
+        <v>-218</v>
       </c>
       <c r="M7" s="12" t="inlineStr">
         <is>
@@ -16273,10 +16370,10 @@
         <v>46.5</v>
       </c>
       <c r="K8" s="18" t="n">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="L8" s="18" t="n">
-        <v>-258</v>
+        <v>-265</v>
       </c>
       <c r="M8" s="17" t="inlineStr">
         <is>
@@ -16368,7 +16465,7 @@
         <v>-4</v>
       </c>
       <c r="J10" s="30" t="n">
-        <v>49.5</v>
+        <v>48.5</v>
       </c>
       <c r="K10" s="18" t="n">
         <v>154</v>
@@ -16417,7 +16514,7 @@
         <v>-31.5</v>
       </c>
       <c r="J11" s="29" t="n">
-        <v>53.5</v>
+        <v>52.5</v>
       </c>
       <c r="K11" s="13" t="n">
         <v>2200</v>
@@ -16463,16 +16560,16 @@
       </c>
       <c r="H12" s="17" t="inlineStr"/>
       <c r="I12" s="26" t="n">
-        <v>-5.5</v>
+        <v>-4.5</v>
       </c>
       <c r="J12" s="30" t="n">
         <v>56.5</v>
       </c>
       <c r="K12" s="18" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="L12" s="18" t="n">
-        <v>-218</v>
+        <v>-192</v>
       </c>
       <c r="M12" s="17" t="inlineStr">
         <is>
@@ -16512,7 +16609,7 @@
       </c>
       <c r="H13" s="12" t="inlineStr"/>
       <c r="I13" s="23" t="n">
-        <v>-30.5</v>
+        <v>-29.5</v>
       </c>
       <c r="J13" s="29" t="n">
         <v>53.5</v>
@@ -16609,7 +16706,7 @@
         <v>-23.5</v>
       </c>
       <c r="J15" s="29" t="n">
-        <v>49.5</v>
+        <v>48.5</v>
       </c>
       <c r="K15" s="13" t="n">
         <v>1400</v>
@@ -16661,10 +16758,10 @@
         <v>55.5</v>
       </c>
       <c r="K16" s="18" t="n">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="L16" s="18" t="n">
-        <v>-20000</v>
+        <v>-10000</v>
       </c>
       <c r="M16" s="17" t="inlineStr">
         <is>
@@ -17039,7 +17136,7 @@
       </c>
       <c r="H24" s="17" t="inlineStr"/>
       <c r="I24" s="26" t="n">
-        <v>-5.5</v>
+        <v>-4.5</v>
       </c>
       <c r="J24" s="30" t="n">
         <v>53.5</v>
@@ -17139,10 +17236,10 @@
         <v>63.5</v>
       </c>
       <c r="K26" s="18" t="n">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="L26" s="18" t="n">
-        <v>-5000</v>
+        <v>-4500</v>
       </c>
       <c r="M26" s="17" t="inlineStr">
         <is>
@@ -17278,10 +17375,10 @@
         <v>49.5</v>
       </c>
       <c r="K29" s="13" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="L29" s="13" t="n">
-        <v>-410</v>
+        <v>-395</v>
       </c>
       <c r="M29" s="12" t="inlineStr">
         <is>
@@ -17376,10 +17473,10 @@
         <v>51.5</v>
       </c>
       <c r="K31" s="13" t="n">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="L31" s="13" t="n">
-        <v>-3200</v>
+        <v>-3600</v>
       </c>
       <c r="M31" s="12" t="inlineStr">
         <is>

--- a/NCAAF_Edge_Model.xlsx
+++ b/NCAAF_Edge_Model.xlsx
@@ -640,7 +640,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-25T18:02:02+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
+          <t>Generated 2026-08-25T21:56:33+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
         </is>
       </c>
     </row>
@@ -1114,13 +1114,13 @@
         </is>
       </c>
       <c r="E24" s="18" t="n">
-        <v>-105</v>
+        <v>-102</v>
       </c>
       <c r="F24" s="19" t="n">
-        <v>0.08386062118588167</v>
+        <v>0.08784030332263559</v>
       </c>
       <c r="G24" s="20" t="n">
-        <v>0.5960557431371012</v>
+        <v>0.5927907983721405</v>
       </c>
       <c r="H24" s="21" t="n"/>
       <c r="I24" s="17" t="inlineStr">
@@ -1520,22 +1520,22 @@
         <v>-7.5</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>-105</v>
+        <v>-102</v>
       </c>
       <c r="I8" s="20" t="n">
-        <v>0.5960557431371012</v>
+        <v>0.5927907983721405</v>
       </c>
       <c r="J8" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.4826358742837298</v>
       </c>
       <c r="K8" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.504950495049505</v>
       </c>
       <c r="L8" s="19" t="n">
-        <v>0.08386062118588167</v>
+        <v>0.08784030332263559</v>
       </c>
       <c r="M8" s="19" t="n">
-        <v>0.1637278794581499</v>
+        <v>0.1739582477565921</v>
       </c>
       <c r="N8" s="20" t="n">
         <v>0</v>
@@ -1688,12 +1688,12 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>BCU @ UCF</t>
+          <t>NMSU @ FSU</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D11" s="22" t="n">
@@ -1706,29 +1706,29 @@
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>BCU +42.5</t>
+          <t>NMSU +30.5</t>
         </is>
       </c>
       <c r="G11" s="23" t="n">
-        <v>-42.5</v>
+        <v>-30.5</v>
       </c>
       <c r="H11" s="13" t="n">
-        <v>-110</v>
+        <v>-102</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>0.7495833131506973</v>
+        <v>0.7327748458688852</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>0.5</v>
+        <v>0.4826358742837298</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.504950495049505</v>
       </c>
       <c r="L11" s="14" t="n">
-        <v>0.2257737893411734</v>
+        <v>0.2278243508193802</v>
       </c>
       <c r="M11" s="14" t="n">
-        <v>0.4310226887422403</v>
+        <v>0.4511815575050472</v>
       </c>
       <c r="N11" s="15" t="n">
         <v>0</v>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="Q11" s="12" t="inlineStr">
         <is>
-          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>UAPB @ MIZ</t>
+          <t>BCU @ UCF</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D12" s="25" t="n">
@@ -1773,29 +1773,29 @@
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>UAPB +54.5</t>
+          <t>BCU +42.5</t>
         </is>
       </c>
       <c r="G12" s="26" t="n">
-        <v>-54.5</v>
+        <v>-42.5</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I12" s="20" t="n">
-        <v>0.7521468293620484</v>
+        <v>0.7495833131506973</v>
       </c>
       <c r="J12" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K12" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L12" s="19" t="n">
-        <v>0.2238449425695955</v>
+        <v>0.2257737893411734</v>
       </c>
       <c r="M12" s="19" t="n">
-        <v>0.4237064984353057</v>
+        <v>0.4310226887422403</v>
       </c>
       <c r="N12" s="20" t="n">
         <v>0</v>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="Q12" s="17" t="inlineStr">
         <is>
-          <t>UAPB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>EIU @ MINN</t>
+          <t>UAPB @ MIZ</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -1840,17 +1840,17 @@
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>EIU +43.5</t>
+          <t>UAPB +54.5</t>
         </is>
       </c>
       <c r="G13" s="23" t="n">
-        <v>-43.5</v>
+        <v>-54.5</v>
       </c>
       <c r="H13" s="13" t="n">
         <v>-112</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>0.7518231737767994</v>
+        <v>0.7521468293620484</v>
       </c>
       <c r="J13" s="15" t="n">
         <v>0.5043297540699688</v>
@@ -1859,10 +1859,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L13" s="14" t="n">
-        <v>0.2235212869843466</v>
+        <v>0.2238449425695955</v>
       </c>
       <c r="M13" s="14" t="n">
-        <v>0.4230938646489417</v>
+        <v>0.4237064984353057</v>
       </c>
       <c r="N13" s="15" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="Q13" s="12" t="inlineStr">
         <is>
-          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>UAPB isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -1889,12 +1889,12 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>IDHO @ UTAH</t>
+          <t>EIU @ MINN</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 01:00</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D14" s="25" t="n">
@@ -1907,29 +1907,29 @@
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t>IDHO +33.5</t>
+          <t>EIU +43.5</t>
         </is>
       </c>
       <c r="G14" s="26" t="n">
-        <v>-33.5</v>
+        <v>-43.5</v>
       </c>
       <c r="H14" s="18" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="I14" s="20" t="n">
-        <v>0.7436440297876288</v>
+        <v>0.7518231737767994</v>
       </c>
       <c r="J14" s="20" t="n">
-        <v>0.5</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K14" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L14" s="19" t="n">
-        <v>0.2198345059781049</v>
+        <v>0.2235212869843466</v>
       </c>
       <c r="M14" s="19" t="n">
-        <v>0.4196840568672914</v>
+        <v>0.4230938646489417</v>
       </c>
       <c r="N14" s="20" t="n">
         <v>0</v>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="Q14" s="17" t="inlineStr">
         <is>
-          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -1956,12 +1956,12 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>MRMK @ DEL</t>
+          <t>IDHO @ UTAH</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D15" s="22" t="n">
@@ -1974,29 +1974,29 @@
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>MRMK +28.5</t>
+          <t>IDHO +33.5</t>
         </is>
       </c>
       <c r="G15" s="23" t="n">
-        <v>-28.5</v>
+        <v>-33.5</v>
       </c>
       <c r="H15" s="13" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>0.7386849373798826</v>
+        <v>0.7436440297876288</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L15" s="14" t="n">
-        <v>0.2194541681491133</v>
+        <v>0.2198345059781049</v>
       </c>
       <c r="M15" s="14" t="n">
-        <v>0.4226524719908851</v>
+        <v>0.4196840568672914</v>
       </c>
       <c r="N15" s="15" t="n">
         <v>0</v>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="Q15" s="12" t="inlineStr">
         <is>
-          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -2023,12 +2023,12 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>MASS @ RUTG</t>
+          <t>MRMK @ DEL</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 22:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D16" s="25" t="n">
@@ -2041,29 +2041,29 @@
       </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
-          <t>MASS +29.5</t>
+          <t>MRMK +28.5</t>
         </is>
       </c>
       <c r="G16" s="26" t="n">
-        <v>-29.5</v>
+        <v>-28.5</v>
       </c>
       <c r="H16" s="18" t="n">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="I16" s="20" t="n">
-        <v>0.7307755149318647</v>
+        <v>0.7386849373798826</v>
       </c>
       <c r="J16" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K16" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L16" s="19" t="n">
-        <v>0.2185803929806451</v>
+        <v>0.2194541681491133</v>
       </c>
       <c r="M16" s="19" t="n">
-        <v>0.4267521958193548</v>
+        <v>0.4226524719908851</v>
       </c>
       <c r="N16" s="20" t="n">
         <v>0</v>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="Q16" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>MASS @ RUTG</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-09-03 22:00</t>
         </is>
       </c>
       <c r="D17" s="22" t="n">
@@ -2108,29 +2108,29 @@
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>SJSU +38.5</t>
+          <t>MASS +29.5</t>
         </is>
       </c>
       <c r="G17" s="23" t="n">
-        <v>-38.5</v>
+        <v>-29.5</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>-115</v>
+        <v>-105</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>0.7530960341419698</v>
+        <v>0.7307755149318647</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K17" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L17" s="14" t="n">
-        <v>0.2182123132117373</v>
+        <v>0.2185803929806451</v>
       </c>
       <c r="M17" s="14" t="n">
-        <v>0.4079621507871608</v>
+        <v>0.4267521958193548</v>
       </c>
       <c r="N17" s="15" t="n">
         <v>0</v>
@@ -2157,12 +2157,12 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>NCAT @ GAST</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 23:00</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D18" s="25" t="n">
@@ -2175,29 +2175,29 @@
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>NCAT +28.5</t>
+          <t>SJSU +38.5</t>
         </is>
       </c>
       <c r="G18" s="26" t="n">
-        <v>-28.5</v>
+        <v>-38.5</v>
       </c>
       <c r="H18" s="18" t="n">
-        <v>-112</v>
+        <v>-115</v>
       </c>
       <c r="I18" s="20" t="n">
-        <v>0.7452866315143292</v>
+        <v>0.7530960341419698</v>
       </c>
       <c r="J18" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K18" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L18" s="19" t="n">
-        <v>0.2169847447218763</v>
+        <v>0.2182123132117373</v>
       </c>
       <c r="M18" s="19" t="n">
-        <v>0.4107211239378373</v>
+        <v>0.4079621507871608</v>
       </c>
       <c r="N18" s="20" t="n">
         <v>0</v>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Q18" s="17" t="inlineStr">
         <is>
-          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -2224,12 +2224,12 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>NMSU @ FSU</t>
+          <t>NCAT @ GAST</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-04 23:00</t>
         </is>
       </c>
       <c r="D19" s="22" t="n">
@@ -2242,29 +2242,29 @@
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>NMSU +31.5</t>
+          <t>NCAT +28.5</t>
         </is>
       </c>
       <c r="G19" s="23" t="n">
-        <v>-31.5</v>
+        <v>-28.5</v>
       </c>
       <c r="H19" s="13" t="n">
-        <v>-115</v>
+        <v>-112</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>0.7484052544756881</v>
+        <v>0.7452866315143292</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K19" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L19" s="14" t="n">
-        <v>0.2135215335454556</v>
+        <v>0.2169847447218763</v>
       </c>
       <c r="M19" s="14" t="n">
-        <v>0.3991924322806341</v>
+        <v>0.4107211239378373</v>
       </c>
       <c r="N19" s="15" t="n">
         <v>0</v>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="Q19" s="12" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -3569,22 +3569,22 @@
       </c>
       <c r="G39" s="23" t="n"/>
       <c r="H39" s="13" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>0.3639656274205685</v>
+        <v>0.3621290026789783</v>
       </c>
       <c r="J39" s="15" t="n">
-        <v>0.2779207411219763</v>
+        <v>0.274247491638796</v>
       </c>
       <c r="K39" s="15" t="n">
-        <v>0.2898550724637681</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="L39" s="14" t="n">
-        <v>0.07411055495680036</v>
+        <v>0.0764147169646926</v>
       </c>
       <c r="M39" s="14" t="n">
-        <v>0.2556814146009613</v>
+        <v>0.267451509376424</v>
       </c>
       <c r="N39" s="15" t="n">
         <v>0</v>
@@ -4121,12 +4121,12 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>NMSU @ FSU</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D48" s="25" t="n">
@@ -4134,34 +4134,34 @@
       </c>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F48" s="17" t="inlineStr">
         <is>
-          <t>Over 52.5</t>
+          <t>NCSU +5.5</t>
         </is>
       </c>
       <c r="G48" s="26" t="n">
-        <v>52.5</v>
+        <v>-5.5</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="I48" s="20" t="n">
-        <v>0.5472084462676521</v>
+        <v>0.5380374278212803</v>
       </c>
       <c r="J48" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K48" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L48" s="19" t="n">
-        <v>0.02797767703688281</v>
+        <v>0.02584230587006076</v>
       </c>
       <c r="M48" s="19" t="n">
-        <v>0.05388293355251517</v>
+        <v>0.05045402574630908</v>
       </c>
       <c r="N48" s="20" t="n">
         <v>0</v>
@@ -4184,12 +4184,12 @@
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>COLO @ GT</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D49" s="22" t="n">
@@ -4202,17 +4202,17 @@
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
-          <t>NCSU +5.5</t>
+          <t>COLO +6.5</t>
         </is>
       </c>
       <c r="G49" s="23" t="n">
-        <v>-5.5</v>
+        <v>-6.5</v>
       </c>
       <c r="H49" s="13" t="n">
         <v>-105</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>0.5380374278212803</v>
+        <v>0.5359459352051367</v>
       </c>
       <c r="J49" s="15" t="n">
         <v>0.4891657638136511</v>
@@ -4221,10 +4221,10 @@
         <v>0.5121951219512195</v>
       </c>
       <c r="L49" s="14" t="n">
-        <v>0.02584230587006076</v>
+        <v>0.02375081325391715</v>
       </c>
       <c r="M49" s="14" t="n">
-        <v>0.05045402574630908</v>
+        <v>0.0463706354005049</v>
       </c>
       <c r="N49" s="15" t="n">
         <v>0</v>
@@ -4247,12 +4247,12 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>COLO @ GT</t>
+          <t>NMSU @ FSU</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D50" s="25" t="n">
@@ -4260,34 +4260,34 @@
       </c>
       <c r="E50" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F50" s="17" t="inlineStr">
         <is>
-          <t>COLO +6.5</t>
+          <t>Over 52.5</t>
         </is>
       </c>
       <c r="G50" s="26" t="n">
-        <v>-6.5</v>
+        <v>52.5</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>-105</v>
+        <v>-112</v>
       </c>
       <c r="I50" s="20" t="n">
-        <v>0.5359459352051367</v>
+        <v>0.5515382003376208</v>
       </c>
       <c r="J50" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K50" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L50" s="19" t="n">
-        <v>0.02375081325391715</v>
+        <v>0.02323631354516797</v>
       </c>
       <c r="M50" s="19" t="n">
-        <v>0.0463706354005049</v>
+        <v>0.04398302206763932</v>
       </c>
       <c r="N50" s="20" t="n">
         <v>0</v>
@@ -4686,12 +4686,12 @@
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>SJSU @ EMU</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 22:30</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D57" s="22" t="n">
@@ -4699,34 +4699,32 @@
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
         <is>
-          <t>SJSU +4.5</t>
-        </is>
-      </c>
-      <c r="G57" s="23" t="n">
-        <v>-4.5</v>
-      </c>
+          <t>MEM ML</t>
+        </is>
+      </c>
+      <c r="G57" s="23" t="n"/>
       <c r="H57" s="13" t="n">
-        <v>-105</v>
+        <v>164</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>0.5253691652874209</v>
+        <v>0.3933214139392706</v>
       </c>
       <c r="J57" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.3630958183058778</v>
       </c>
       <c r="K57" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.3787878787878788</v>
       </c>
       <c r="L57" s="14" t="n">
-        <v>0.01317404333620142</v>
+        <v>0.01453353515139177</v>
       </c>
       <c r="M57" s="14" t="n">
-        <v>0.02572075127544082</v>
+        <v>0.03836853279967412</v>
       </c>
       <c r="N57" s="15" t="n">
         <v>0</v>
@@ -4749,12 +4747,12 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
@@ -4762,32 +4760,34 @@
       </c>
       <c r="E58" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F58" s="17" t="inlineStr">
         <is>
-          <t>MEM ML</t>
-        </is>
-      </c>
-      <c r="G58" s="26" t="n"/>
+          <t>Over 47.5</t>
+        </is>
+      </c>
+      <c r="G58" s="26" t="n">
+        <v>47.5</v>
+      </c>
       <c r="H58" s="18" t="n">
-        <v>160</v>
+        <v>-110</v>
       </c>
       <c r="I58" s="20" t="n">
-        <v>0.396303332895533</v>
+        <v>0.5376883257015108</v>
       </c>
       <c r="J58" s="20" t="n">
-        <v>0.3690596562184025</v>
+        <v>0.5</v>
       </c>
       <c r="K58" s="20" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L58" s="19" t="n">
-        <v>0.01168794828014835</v>
+        <v>0.01387880189198698</v>
       </c>
       <c r="M58" s="19" t="n">
-        <v>0.03038866552838582</v>
+        <v>0.02649589452106615</v>
       </c>
       <c r="N58" s="20" t="n">
         <v>0</v>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>SJSU @ EMU</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-09-04 22:30</t>
         </is>
       </c>
       <c r="D59" s="22" t="n">
@@ -4823,34 +4823,34 @@
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
+          <t>SJSU +4.5</t>
         </is>
       </c>
       <c r="G59" s="23" t="n">
-        <v>47.5</v>
+        <v>-4.5</v>
       </c>
       <c r="H59" s="13" t="n">
-        <v>-112</v>
+        <v>-105</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>0.5398532027364953</v>
+        <v>0.5253691652874209</v>
       </c>
       <c r="J59" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K59" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L59" s="14" t="n">
-        <v>0.01155131594404246</v>
+        <v>0.01317404333620142</v>
       </c>
       <c r="M59" s="14" t="n">
-        <v>0.02186499089408034</v>
+        <v>0.02572075127544082</v>
       </c>
       <c r="N59" s="15" t="n">
         <v>0</v>
@@ -5580,12 +5580,12 @@
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>JVST @ NDSU</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-08-29 21:30</t>
         </is>
       </c>
       <c r="D71" s="22" t="n">
@@ -5598,27 +5598,27 @@
       </c>
       <c r="F71" s="12" t="inlineStr">
         <is>
-          <t>UNLV ML</t>
+          <t>NDSU ML</t>
         </is>
       </c>
       <c r="G71" s="23" t="n"/>
       <c r="H71" s="13" t="n">
-        <v>-192</v>
+        <v>-265</v>
       </c>
       <c r="I71" s="15" t="n">
-        <v>0.603696667104467</v>
+        <v>0.6716849259288671</v>
       </c>
       <c r="J71" s="15" t="n">
-        <v>0.6309403437815976</v>
+        <v>0.6957699520733487</v>
       </c>
       <c r="K71" s="15" t="n">
-        <v>0.6575342465753424</v>
+        <v>0.726027397260274</v>
       </c>
       <c r="L71" s="14" t="n">
-        <v>-0.05383757947087542</v>
+        <v>-0.05434247133140691</v>
       </c>
       <c r="M71" s="14" t="n">
-        <v>-0.08187798544528968</v>
+        <v>-0.07484906428665483</v>
       </c>
       <c r="N71" s="15" t="n">
         <v>0</v>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>JVST @ NDSU</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C72" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D72" s="25" t="n">
@@ -5659,27 +5659,27 @@
       </c>
       <c r="F72" s="17" t="inlineStr">
         <is>
-          <t>NDSU ML</t>
+          <t>UNLV ML</t>
         </is>
       </c>
       <c r="G72" s="26" t="n"/>
       <c r="H72" s="18" t="n">
-        <v>-265</v>
+        <v>-198</v>
       </c>
       <c r="I72" s="20" t="n">
-        <v>0.6716849259288671</v>
+        <v>0.6066785860607294</v>
       </c>
       <c r="J72" s="20" t="n">
-        <v>0.6957699520733487</v>
+        <v>0.6369041816941223</v>
       </c>
       <c r="K72" s="20" t="n">
-        <v>0.726027397260274</v>
+        <v>0.6644295302013423</v>
       </c>
       <c r="L72" s="19" t="n">
-        <v>-0.05434247133140691</v>
+        <v>-0.05775094414061288</v>
       </c>
       <c r="M72" s="19" t="n">
-        <v>-0.07484906428665483</v>
+        <v>-0.08691808764597275</v>
       </c>
       <c r="N72" s="20" t="n">
         <v>0</v>
@@ -5763,12 +5763,12 @@
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>SJSU @ EMU</t>
         </is>
       </c>
       <c r="C74" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-09-04 22:30</t>
         </is>
       </c>
       <c r="D74" s="25" t="n">
@@ -5776,34 +5776,32 @@
       </c>
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F74" s="17" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
-        </is>
-      </c>
-      <c r="G74" s="26" t="n">
-        <v>47.5</v>
-      </c>
+          <t>EMU ML</t>
+        </is>
+      </c>
+      <c r="G74" s="26" t="n"/>
       <c r="H74" s="18" t="n">
-        <v>-108</v>
+        <v>-218</v>
       </c>
       <c r="I74" s="20" t="n">
-        <v>0.4601467972635047</v>
+        <v>0.6258400393716101</v>
       </c>
       <c r="J74" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.6574752261956054</v>
       </c>
       <c r="K74" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.6855345911949685</v>
       </c>
       <c r="L74" s="19" t="n">
-        <v>-0.05908397196726456</v>
+        <v>-0.05969455182335837</v>
       </c>
       <c r="M74" s="19" t="n">
-        <v>-0.1137913534184353</v>
+        <v>-0.08707737376067881</v>
       </c>
       <c r="N74" s="20" t="n">
         <v>0</v>
@@ -5826,12 +5824,12 @@
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>SJSU @ EMU</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 22:30</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D75" s="22" t="n">
@@ -5844,7 +5842,7 @@
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
-          <t>EMU ML</t>
+          <t>UVA ML</t>
         </is>
       </c>
       <c r="G75" s="23" t="n"/>
@@ -5852,7 +5850,7 @@
         <v>-218</v>
       </c>
       <c r="I75" s="15" t="n">
-        <v>0.6258400393716101</v>
+        <v>0.6254192861725905</v>
       </c>
       <c r="J75" s="15" t="n">
         <v>0.6574752261956054</v>
@@ -5861,10 +5859,10 @@
         <v>0.6855345911949685</v>
       </c>
       <c r="L75" s="14" t="n">
-        <v>-0.05969455182335837</v>
+        <v>-0.06011530502237805</v>
       </c>
       <c r="M75" s="14" t="n">
-        <v>-0.08707737376067881</v>
+        <v>-0.08769113301429471</v>
       </c>
       <c r="N75" s="15" t="n">
         <v>0</v>
@@ -5887,12 +5885,12 @@
       </c>
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>SJSU @ EMU</t>
         </is>
       </c>
       <c r="C76" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-09-04 22:30</t>
         </is>
       </c>
       <c r="D76" s="25" t="n">
@@ -5900,32 +5898,34 @@
       </c>
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F76" s="17" t="inlineStr">
         <is>
-          <t>UVA ML</t>
-        </is>
-      </c>
-      <c r="G76" s="26" t="n"/>
+          <t>EMU -4.5</t>
+        </is>
+      </c>
+      <c r="G76" s="26" t="n">
+        <v>-4.5</v>
+      </c>
       <c r="H76" s="18" t="n">
-        <v>-218</v>
+        <v>-115</v>
       </c>
       <c r="I76" s="20" t="n">
-        <v>0.6254192861725905</v>
+        <v>0.4746308347125791</v>
       </c>
       <c r="J76" s="20" t="n">
-        <v>0.6574752261956054</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K76" s="20" t="n">
-        <v>0.6855345911949685</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L76" s="19" t="n">
-        <v>-0.06011530502237805</v>
+        <v>-0.06025288621765346</v>
       </c>
       <c r="M76" s="19" t="n">
-        <v>-0.08769113301429471</v>
+        <v>-0.112646700319961</v>
       </c>
       <c r="N76" s="20" t="n">
         <v>0</v>
@@ -5948,12 +5948,12 @@
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>SJSU @ EMU</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 22:30</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D77" s="22" t="n">
@@ -5961,34 +5961,34 @@
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
-          <t>EMU -4.5</t>
+          <t>Under 47.5</t>
         </is>
       </c>
       <c r="G77" s="23" t="n">
-        <v>-4.5</v>
+        <v>47.5</v>
       </c>
       <c r="H77" s="13" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="I77" s="15" t="n">
-        <v>0.4746308347125791</v>
+        <v>0.4623116742984892</v>
       </c>
       <c r="J77" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5</v>
       </c>
       <c r="K77" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L77" s="14" t="n">
-        <v>-0.06025288621765346</v>
+        <v>-0.06149784951103465</v>
       </c>
       <c r="M77" s="14" t="n">
-        <v>-0.112646700319961</v>
+        <v>-0.117404985430157</v>
       </c>
       <c r="N77" s="15" t="n">
         <v>0</v>
@@ -6204,12 +6204,12 @@
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>COLO @ GT</t>
+          <t>NMSU @ FSU</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D81" s="22" t="n">
@@ -6217,34 +6217,34 @@
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
-          <t>GT -6.5</t>
+          <t>Under 52.5</t>
         </is>
       </c>
       <c r="G81" s="23" t="n">
-        <v>-6.5</v>
+        <v>52.5</v>
       </c>
       <c r="H81" s="13" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="I81" s="15" t="n">
-        <v>0.4640540647948633</v>
+        <v>0.4484617996623792</v>
       </c>
       <c r="J81" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K81" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L81" s="14" t="n">
-        <v>-0.07082965613536918</v>
+        <v>-0.07076896956839007</v>
       </c>
       <c r="M81" s="14" t="n">
-        <v>-0.132420661470473</v>
+        <v>-0.1362957932428252</v>
       </c>
       <c r="N81" s="15" t="n">
         <v>0</v>
@@ -6267,12 +6267,12 @@
       </c>
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>COLO @ GT</t>
         </is>
       </c>
       <c r="C82" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D82" s="25" t="n">
@@ -6285,17 +6285,17 @@
       </c>
       <c r="F82" s="17" t="inlineStr">
         <is>
-          <t>UVA -5.5</t>
+          <t>GT -6.5</t>
         </is>
       </c>
       <c r="G82" s="26" t="n">
-        <v>-5.5</v>
+        <v>-6.5</v>
       </c>
       <c r="H82" s="18" t="n">
         <v>-115</v>
       </c>
       <c r="I82" s="20" t="n">
-        <v>0.4619625721787197</v>
+        <v>0.4640540647948633</v>
       </c>
       <c r="J82" s="20" t="n">
         <v>0.5108342361863488</v>
@@ -6304,10 +6304,10 @@
         <v>0.5348837209302325</v>
       </c>
       <c r="L82" s="19" t="n">
-        <v>-0.07292114875151279</v>
+        <v>-0.07082965613536918</v>
       </c>
       <c r="M82" s="19" t="n">
-        <v>-0.1363308433180458</v>
+        <v>-0.132420661470473</v>
       </c>
       <c r="N82" s="20" t="n">
         <v>0</v>
@@ -6330,12 +6330,12 @@
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>NMSU @ FSU</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D83" s="22" t="n">
@@ -6343,34 +6343,34 @@
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F83" s="12" t="inlineStr">
         <is>
-          <t>Under 52.5</t>
+          <t>UVA -5.5</t>
         </is>
       </c>
       <c r="G83" s="23" t="n">
-        <v>52.5</v>
+        <v>-5.5</v>
       </c>
       <c r="H83" s="13" t="n">
-        <v>-112</v>
+        <v>-115</v>
       </c>
       <c r="I83" s="15" t="n">
-        <v>0.4527915537323479</v>
+        <v>0.4619625721787197</v>
       </c>
       <c r="J83" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K83" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L83" s="14" t="n">
-        <v>-0.07551033306010491</v>
+        <v>-0.07292114875151279</v>
       </c>
       <c r="M83" s="14" t="n">
-        <v>-0.1429302732923415</v>
+        <v>-0.1363308433180458</v>
       </c>
       <c r="N83" s="15" t="n">
         <v>0</v>
@@ -6863,22 +6863,22 @@
       </c>
       <c r="G91" s="23" t="n"/>
       <c r="H91" s="13" t="n">
-        <v>-305</v>
+        <v>-310</v>
       </c>
       <c r="I91" s="15" t="n">
-        <v>0.6360343725794315</v>
+        <v>0.6378709973210217</v>
       </c>
       <c r="J91" s="15" t="n">
-        <v>0.7220792588780237</v>
+        <v>0.725752508361204</v>
       </c>
       <c r="K91" s="15" t="n">
-        <v>0.7530864197530864</v>
+        <v>0.7560975609756098</v>
       </c>
       <c r="L91" s="14" t="n">
-        <v>-0.1170520471736549</v>
+        <v>-0.1182265636545881</v>
       </c>
       <c r="M91" s="14" t="n">
-        <v>-0.1554297675584598</v>
+        <v>-0.1563641648334875</v>
       </c>
       <c r="N91" s="15" t="n">
         <v>0</v>
@@ -7161,12 +7161,12 @@
       </c>
       <c r="B96" s="17" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>NCAT @ GAST</t>
         </is>
       </c>
       <c r="C96" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-09-04 23:00</t>
         </is>
       </c>
       <c r="D96" s="25" t="n">
@@ -7174,34 +7174,34 @@
       </c>
       <c r="E96" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F96" s="17" t="inlineStr">
         <is>
-          <t>TCU -7.5</t>
+          <t>Over 63.5</t>
         </is>
       </c>
       <c r="G96" s="26" t="n">
-        <v>-7.5</v>
+        <v>63.5</v>
       </c>
       <c r="H96" s="18" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>0.4039442568628988</v>
+        <v>0.3904378805908039</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L96" s="19" t="n">
-        <v>-0.1309394640673337</v>
+        <v>-0.13337164321872</v>
       </c>
       <c r="M96" s="19" t="n">
-        <v>-0.2447998676041457</v>
+        <v>-0.2546185915993744</v>
       </c>
       <c r="N96" s="20" t="n">
         <v>0</v>
@@ -7214,7 +7214,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q96" s="17" t="n"/>
+      <c r="Q96" s="17" t="inlineStr">
+        <is>
+          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="12" t="inlineStr">
@@ -7224,12 +7228,12 @@
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>NCAT @ GAST</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 23:00</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D97" s="22" t="n">
@@ -7237,34 +7241,34 @@
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F97" s="12" t="inlineStr">
         <is>
-          <t>Over 63.5</t>
+          <t>TCU -7.5</t>
         </is>
       </c>
       <c r="G97" s="23" t="n">
-        <v>63.5</v>
+        <v>-7.5</v>
       </c>
       <c r="H97" s="13" t="n">
-        <v>-110</v>
+        <v>-118</v>
       </c>
       <c r="I97" s="15" t="n">
-        <v>0.3904378805908039</v>
+        <v>0.4072092016278595</v>
       </c>
       <c r="J97" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5173641257162701</v>
       </c>
       <c r="K97" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5412844036697247</v>
       </c>
       <c r="L97" s="14" t="n">
-        <v>-0.13337164321872</v>
+        <v>-0.1340752020418653</v>
       </c>
       <c r="M97" s="14" t="n">
-        <v>-0.2546185915993744</v>
+        <v>-0.2476982546197173</v>
       </c>
       <c r="N97" s="15" t="n">
         <v>0</v>
@@ -7277,11 +7281,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q97" s="12" t="inlineStr">
-        <is>
-          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q97" s="12" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="17" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>NMSU @ FSU</t>
+          <t>NCAT @ GAST</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-04 23:00</t>
         </is>
       </c>
       <c r="D117" s="22" t="n">
@@ -8550,29 +8550,29 @@
       </c>
       <c r="F117" s="12" t="inlineStr">
         <is>
-          <t>FSU -31.5</t>
+          <t>GAST -28.5</t>
         </is>
       </c>
       <c r="G117" s="23" t="n">
-        <v>-31.5</v>
+        <v>-28.5</v>
       </c>
       <c r="H117" s="13" t="n">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="I117" s="15" t="n">
-        <v>0.2515947455243119</v>
+        <v>0.2547133684856709</v>
       </c>
       <c r="J117" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K117" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L117" s="14" t="n">
-        <v>-0.2606003764269076</v>
+        <v>-0.2645174007450984</v>
       </c>
       <c r="M117" s="14" t="n">
-        <v>-0.5087912111192006</v>
+        <v>-0.5094409199535228</v>
       </c>
       <c r="N117" s="15" t="n">
         <v>0</v>
@@ -8587,7 +8587,7 @@
       </c>
       <c r="Q117" s="12" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -8599,12 +8599,12 @@
       </c>
       <c r="B118" s="17" t="inlineStr">
         <is>
-          <t>NCAT @ GAST</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C118" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 23:00</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D118" s="25" t="n">
@@ -8617,29 +8617,29 @@
       </c>
       <c r="F118" s="17" t="inlineStr">
         <is>
-          <t>GAST -28.5</t>
+          <t>USC -38.5</t>
         </is>
       </c>
       <c r="G118" s="26" t="n">
-        <v>-28.5</v>
+        <v>-38.5</v>
       </c>
       <c r="H118" s="18" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="I118" s="20" t="n">
-        <v>0.2547133684856709</v>
+        <v>0.2469039658580302</v>
       </c>
       <c r="J118" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K118" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L118" s="19" t="n">
-        <v>-0.2645174007450984</v>
+        <v>-0.2652911560931893</v>
       </c>
       <c r="M118" s="19" t="n">
-        <v>-0.5094409199535228</v>
+        <v>-0.5179493999914648</v>
       </c>
       <c r="N118" s="20" t="n">
         <v>0</v>
@@ -8654,7 +8654,7 @@
       </c>
       <c r="Q118" s="17" t="inlineStr">
         <is>
-          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -8666,12 +8666,12 @@
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>MASS @ RUTG</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-09-03 22:00</t>
         </is>
       </c>
       <c r="D119" s="22" t="n">
@@ -8684,29 +8684,29 @@
       </c>
       <c r="F119" s="12" t="inlineStr">
         <is>
-          <t>USC -38.5</t>
+          <t>RUTG -29.5</t>
         </is>
       </c>
       <c r="G119" s="23" t="n">
-        <v>-38.5</v>
+        <v>-29.5</v>
       </c>
       <c r="H119" s="13" t="n">
-        <v>-105</v>
+        <v>-115</v>
       </c>
       <c r="I119" s="15" t="n">
-        <v>0.2469039658580302</v>
+        <v>0.2692244850681354</v>
       </c>
       <c r="J119" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K119" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L119" s="14" t="n">
-        <v>-0.2652911560931893</v>
+        <v>-0.2656592358620971</v>
       </c>
       <c r="M119" s="14" t="n">
-        <v>-0.5179493999914648</v>
+        <v>-0.4966672670465295</v>
       </c>
       <c r="N119" s="15" t="n">
         <v>0</v>
@@ -8733,12 +8733,12 @@
       </c>
       <c r="B120" s="17" t="inlineStr">
         <is>
-          <t>MASS @ RUTG</t>
+          <t>MRMK @ DEL</t>
         </is>
       </c>
       <c r="C120" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 22:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D120" s="25" t="n">
@@ -8751,29 +8751,29 @@
       </c>
       <c r="F120" s="17" t="inlineStr">
         <is>
-          <t>RUTG -29.5</t>
+          <t>DEL -28.5</t>
         </is>
       </c>
       <c r="G120" s="26" t="n">
-        <v>-29.5</v>
+        <v>-28.5</v>
       </c>
       <c r="H120" s="18" t="n">
-        <v>-115</v>
+        <v>-112</v>
       </c>
       <c r="I120" s="20" t="n">
-        <v>0.2692244850681354</v>
+        <v>0.2613150626201174</v>
       </c>
       <c r="J120" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K120" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L120" s="19" t="n">
-        <v>-0.2656592358620971</v>
+        <v>-0.2669868241723354</v>
       </c>
       <c r="M120" s="19" t="n">
-        <v>-0.4966672670465295</v>
+        <v>-0.5053679171833493</v>
       </c>
       <c r="N120" s="20" t="n">
         <v>0</v>
@@ -8788,7 +8788,7 @@
       </c>
       <c r="Q120" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -8800,12 +8800,12 @@
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>MRMK @ DEL</t>
+          <t>IDHO @ UTAH</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D121" s="22" t="n">
@@ -8818,29 +8818,29 @@
       </c>
       <c r="F121" s="12" t="inlineStr">
         <is>
-          <t>DEL -28.5</t>
+          <t>UTAH -33.5</t>
         </is>
       </c>
       <c r="G121" s="23" t="n">
-        <v>-28.5</v>
+        <v>-33.5</v>
       </c>
       <c r="H121" s="13" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I121" s="15" t="n">
-        <v>0.2613150626201174</v>
+        <v>0.2563559702123712</v>
       </c>
       <c r="J121" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K121" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L121" s="14" t="n">
-        <v>-0.2669868241723354</v>
+        <v>-0.2674535535971527</v>
       </c>
       <c r="M121" s="14" t="n">
-        <v>-0.5053679171833493</v>
+        <v>-0.5105931477763822</v>
       </c>
       <c r="N121" s="15" t="n">
         <v>0</v>
@@ -8855,7 +8855,7 @@
       </c>
       <c r="Q121" s="12" t="inlineStr">
         <is>
-          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -8867,12 +8867,12 @@
       </c>
       <c r="B122" s="17" t="inlineStr">
         <is>
-          <t>IDHO @ UTAH</t>
+          <t>INST @ PUR</t>
         </is>
       </c>
       <c r="C122" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 01:00</t>
+          <t>2026-09-04 23:00</t>
         </is>
       </c>
       <c r="D122" s="25" t="n">
@@ -8885,29 +8885,29 @@
       </c>
       <c r="F122" s="17" t="inlineStr">
         <is>
-          <t>UTAH -33.5</t>
+          <t>PUR -35.5</t>
         </is>
       </c>
       <c r="G122" s="26" t="n">
-        <v>-33.5</v>
+        <v>-35.5</v>
       </c>
       <c r="H122" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I122" s="20" t="n">
-        <v>0.2563559702123712</v>
+        <v>0.2528934298318226</v>
       </c>
       <c r="J122" s="20" t="n">
-        <v>0.5</v>
+        <v>0.5021949078138718</v>
       </c>
       <c r="K122" s="20" t="n">
         <v>0.5238095238095238</v>
       </c>
       <c r="L122" s="19" t="n">
-        <v>-0.2674535535971527</v>
+        <v>-0.2709160939777012</v>
       </c>
       <c r="M122" s="19" t="n">
-        <v>-0.5105931477763822</v>
+        <v>-0.5172034521392477</v>
       </c>
       <c r="N122" s="20" t="n">
         <v>0</v>
@@ -8922,7 +8922,7 @@
       </c>
       <c r="Q122" s="17" t="inlineStr">
         <is>
-          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>INST isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -8934,12 +8934,12 @@
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>INST @ PUR</t>
+          <t>EIU @ MINN</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 23:00</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D123" s="22" t="n">
@@ -8952,29 +8952,29 @@
       </c>
       <c r="F123" s="12" t="inlineStr">
         <is>
-          <t>PUR -35.5</t>
+          <t>MINN -43.5</t>
         </is>
       </c>
       <c r="G123" s="23" t="n">
-        <v>-35.5</v>
+        <v>-43.5</v>
       </c>
       <c r="H123" s="13" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I123" s="15" t="n">
-        <v>0.2528934298318226</v>
+        <v>0.2481768262232006</v>
       </c>
       <c r="J123" s="15" t="n">
-        <v>0.5021949078138718</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K123" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L123" s="14" t="n">
-        <v>-0.2709160939777012</v>
+        <v>-0.2710539430075687</v>
       </c>
       <c r="M123" s="14" t="n">
-        <v>-0.5172034521392477</v>
+        <v>-0.5220298161627247</v>
       </c>
       <c r="N123" s="15" t="n">
         <v>0</v>
@@ -8989,7 +8989,7 @@
       </c>
       <c r="Q123" s="12" t="inlineStr">
         <is>
-          <t>INST isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -9001,7 +9001,7 @@
       </c>
       <c r="B124" s="17" t="inlineStr">
         <is>
-          <t>EIU @ MINN</t>
+          <t>UAPB @ MIZ</t>
         </is>
       </c>
       <c r="C124" s="17" t="inlineStr">
@@ -9019,17 +9019,17 @@
       </c>
       <c r="F124" s="17" t="inlineStr">
         <is>
-          <t>MINN -43.5</t>
+          <t>MIZ -54.5</t>
         </is>
       </c>
       <c r="G124" s="26" t="n">
-        <v>-43.5</v>
+        <v>-54.5</v>
       </c>
       <c r="H124" s="18" t="n">
         <v>-108</v>
       </c>
       <c r="I124" s="20" t="n">
-        <v>0.2481768262232006</v>
+        <v>0.2478531706379516</v>
       </c>
       <c r="J124" s="20" t="n">
         <v>0.4956702459300312</v>
@@ -9038,10 +9038,10 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L124" s="19" t="n">
-        <v>-0.2710539430075687</v>
+        <v>-0.2713775985928176</v>
       </c>
       <c r="M124" s="19" t="n">
-        <v>-0.5220298161627247</v>
+        <v>-0.5226531528454265</v>
       </c>
       <c r="N124" s="20" t="n">
         <v>0</v>
@@ -9056,7 +9056,7 @@
       </c>
       <c r="Q124" s="17" t="inlineStr">
         <is>
-          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>UAPB isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -9068,12 +9068,12 @@
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>UAPB @ MIZ</t>
+          <t>BCU @ UCF</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D125" s="22" t="n">
@@ -9086,29 +9086,29 @@
       </c>
       <c r="F125" s="12" t="inlineStr">
         <is>
-          <t>MIZ -54.5</t>
+          <t>UCF -42.5</t>
         </is>
       </c>
       <c r="G125" s="23" t="n">
-        <v>-54.5</v>
+        <v>-42.5</v>
       </c>
       <c r="H125" s="13" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I125" s="15" t="n">
-        <v>0.2478531706379516</v>
+        <v>0.2504166868493028</v>
       </c>
       <c r="J125" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5</v>
       </c>
       <c r="K125" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L125" s="14" t="n">
-        <v>-0.2713775985928176</v>
+        <v>-0.273392836960221</v>
       </c>
       <c r="M125" s="14" t="n">
-        <v>-0.5226531528454265</v>
+        <v>-0.5219317796513311</v>
       </c>
       <c r="N125" s="15" t="n">
         <v>0</v>
@@ -9123,7 +9123,7 @@
       </c>
       <c r="Q125" s="12" t="inlineStr">
         <is>
-          <t>UAPB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -9135,12 +9135,12 @@
       </c>
       <c r="B126" s="17" t="inlineStr">
         <is>
-          <t>BCU @ UCF</t>
+          <t>NMSU @ FSU</t>
         </is>
       </c>
       <c r="C126" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D126" s="25" t="n">
@@ -9153,29 +9153,29 @@
       </c>
       <c r="F126" s="17" t="inlineStr">
         <is>
-          <t>UCF -42.5</t>
+          <t>FSU -30.5</t>
         </is>
       </c>
       <c r="G126" s="26" t="n">
-        <v>-42.5</v>
+        <v>-30.5</v>
       </c>
       <c r="H126" s="18" t="n">
-        <v>-110</v>
+        <v>-118</v>
       </c>
       <c r="I126" s="20" t="n">
-        <v>0.2504166868493028</v>
+        <v>0.2672251541311149</v>
       </c>
       <c r="J126" s="20" t="n">
-        <v>0.5</v>
+        <v>0.5173641257162701</v>
       </c>
       <c r="K126" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5412844036697247</v>
       </c>
       <c r="L126" s="19" t="n">
-        <v>-0.273392836960221</v>
+        <v>-0.2740592495386099</v>
       </c>
       <c r="M126" s="19" t="n">
-        <v>-0.5219317796513311</v>
+        <v>-0.5063128508425166</v>
       </c>
       <c r="N126" s="20" t="n">
         <v>0</v>
@@ -9190,7 +9190,7 @@
       </c>
       <c r="Q126" s="17" t="inlineStr">
         <is>
-          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -16227,10 +16227,10 @@
         <v>47.5</v>
       </c>
       <c r="K5" s="13" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="L5" s="13" t="n">
-        <v>-305</v>
+        <v>-310</v>
       </c>
       <c r="M5" s="12" t="inlineStr">
         <is>
@@ -16511,7 +16511,7 @@
       </c>
       <c r="H11" s="12" t="inlineStr"/>
       <c r="I11" s="23" t="n">
-        <v>-31.5</v>
+        <v>-30.5</v>
       </c>
       <c r="J11" s="29" t="n">
         <v>52.5</v>
@@ -16566,10 +16566,10 @@
         <v>56.5</v>
       </c>
       <c r="K12" s="18" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="L12" s="18" t="n">
-        <v>-192</v>
+        <v>-198</v>
       </c>
       <c r="M12" s="17" t="inlineStr">
         <is>
@@ -17424,10 +17424,10 @@
         <v>48.5</v>
       </c>
       <c r="K30" s="18" t="n">
-        <v>-3200</v>
+        <v>-2800</v>
       </c>
       <c r="L30" s="18" t="n">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="M30" s="17" t="inlineStr">
         <is>

--- a/NCAAF_Edge_Model.xlsx
+++ b/NCAAF_Edge_Model.xlsx
@@ -640,7 +640,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-28T21:13:28+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
+          <t>Generated 2026-08-28T21:58:27+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>Settings!B5+SUMIF('Bet Ledger'!$G$6:$G$19,"&lt;&gt;Pending",'Bet Ledger'!$H$6:$H$19)</f>
+        <f>Settings!B5+SUMIF('Bet Ledger'!$G$6:$G$20,"&lt;&gt;Pending",'Bet Ledger'!$H$6:$H$20)</f>
         <v/>
       </c>
     </row>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>SUMIF('Bet Ledger'!$G$6:$G$19,"&lt;&gt;Pending",'Bet Ledger'!$F$6:$F$19)</f>
+        <f>SUMIF('Bet Ledger'!$G$6:$G$20,"&lt;&gt;Pending",'Bet Ledger'!$F$6:$F$20)</f>
         <v/>
       </c>
     </row>
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>SUMIF('Bet Ledger'!$G$6:$G$19,"&lt;&gt;Pending",'Bet Ledger'!$H$6:$H$19)</f>
+        <f>SUMIF('Bet Ledger'!$G$6:$G$20,"&lt;&gt;Pending",'Bet Ledger'!$H$6:$H$20)</f>
         <v/>
       </c>
     </row>
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="B9" s="7">
-        <f>COUNTIFS('Bet Ledger'!$G$6:$G$19,"&lt;&gt;Pending",'Bet Ledger'!$G$6:$G$19,"&lt;&gt;")</f>
+        <f>COUNTIFS('Bet Ledger'!$G$6:$G$20,"&lt;&gt;Pending",'Bet Ledger'!$G$6:$G$20,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>COUNTIF('Bet Ledger'!$G$6:$G$19,"Win")</f>
+        <f>COUNTIF('Bet Ledger'!$G$6:$G$20,"Win")</f>
         <v/>
       </c>
     </row>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>COUNTIF('Bet Ledger'!$G$6:$G$19,"Loss")</f>
+        <f>COUNTIF('Bet Ledger'!$G$6:$G$20,"Loss")</f>
         <v/>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B12" s="7">
-        <f>COUNTIF('Bet Ledger'!$G$6:$G$19,"Push")</f>
+        <f>COUNTIF('Bet Ledger'!$G$6:$G$20,"Push")</f>
         <v/>
       </c>
     </row>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="B14" s="7">
-        <f>COUNTIF('Bet Ledger'!$G$6:$G$19,"Pending")</f>
+        <f>COUNTIF('Bet Ledger'!$G$6:$G$20,"Pending")</f>
         <v/>
       </c>
     </row>
@@ -1248,32 +1248,32 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>BAY @ AUB</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D28" s="17" t="inlineStr">
         <is>
-          <t>UNC +9.5</t>
+          <t>Under 59.5</t>
         </is>
       </c>
       <c r="E28" s="18" t="n">
-        <v>-112</v>
+        <v>-118</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>0.09744989334789012</v>
+        <v>0.09489433857765461</v>
       </c>
       <c r="G28" s="20" t="n">
-        <v>0.6257517801403429</v>
+        <v>0.6361787422473794</v>
       </c>
       <c r="H28" s="21" t="n"/>
       <c r="I28" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>BAY @ AUB</t>
+          <t>HAW @ STAN</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Under 59.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E29" s="13" t="n">
-        <v>-118</v>
+        <v>-110</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0.09489433857765461</v>
+        <v>0.09405980478503773</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>0.6361787422473794</v>
+        <v>0.6178693285945616</v>
       </c>
       <c r="H29" s="16" t="n"/>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>HAW @ STAN</t>
+          <t>FIU @ USF</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
@@ -1332,22 +1332,22 @@
       </c>
       <c r="D30" s="17" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>Over 53.5</t>
         </is>
       </c>
       <c r="E30" s="18" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>0.09405980478503773</v>
+        <v>0.093264091885228</v>
       </c>
       <c r="G30" s="20" t="n">
-        <v>0.6178693285945616</v>
+        <v>0.6281478128154605</v>
       </c>
       <c r="H30" s="21" t="n"/>
       <c r="I30" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>BAY @ AUB</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D12" s="25" t="n">
@@ -1943,34 +1943,34 @@
       </c>
       <c r="E12" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>UNC +9.5</t>
+          <t>Under 59.5</t>
         </is>
       </c>
       <c r="G12" s="26" t="n">
-        <v>-9.5</v>
+        <v>59.5</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>-112</v>
+        <v>-118</v>
       </c>
       <c r="I12" s="20" t="n">
-        <v>0.6257517801403429</v>
+        <v>0.6361787422473794</v>
       </c>
       <c r="J12" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5173641257162701</v>
       </c>
       <c r="K12" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5412844036697247</v>
       </c>
       <c r="L12" s="19" t="n">
-        <v>0.09744989334789012</v>
+        <v>0.09489433857765461</v>
       </c>
       <c r="M12" s="19" t="n">
-        <v>0.1844587266942205</v>
+        <v>0.175313269575667</v>
       </c>
       <c r="N12" s="20" t="n">
         <v>0</v>
@@ -1993,12 +1993,12 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>BAY @ AUB</t>
+          <t>HAW @ STAN</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D13" s="22" t="n">
@@ -2011,29 +2011,29 @@
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>Under 59.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="G13" s="23" t="n">
-        <v>59.5</v>
+        <v>48.5</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>-118</v>
+        <v>-110</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>0.6361787422473794</v>
+        <v>0.6178693285945616</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.5</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L13" s="14" t="n">
-        <v>0.09489433857765461</v>
+        <v>0.09405980478503773</v>
       </c>
       <c r="M13" s="14" t="n">
-        <v>0.175313269575667</v>
+        <v>0.1795687182259812</v>
       </c>
       <c r="N13" s="15" t="n">
         <v>0</v>
@@ -2056,12 +2056,12 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>HAW @ STAN</t>
+          <t>FIU @ USF</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D14" s="25" t="n">
@@ -2074,29 +2074,29 @@
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>Over 53.5</t>
         </is>
       </c>
       <c r="G14" s="26" t="n">
-        <v>48.5</v>
+        <v>53.5</v>
       </c>
       <c r="H14" s="18" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="I14" s="20" t="n">
-        <v>0.6178693285945616</v>
+        <v>0.6281478128154605</v>
       </c>
       <c r="J14" s="20" t="n">
-        <v>0.5</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K14" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L14" s="19" t="n">
-        <v>0.09405980478503773</v>
+        <v>0.093264091885228</v>
       </c>
       <c r="M14" s="19" t="n">
-        <v>0.1795687182259812</v>
+        <v>0.1743633022202087</v>
       </c>
       <c r="N14" s="20" t="n">
         <v>0</v>
@@ -2318,12 +2318,12 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>NMSU @ FSU</t>
+          <t>UAPB @ MIZ</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D18" s="25" t="n">
@@ -2336,29 +2336,29 @@
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>NMSU +31.5</t>
+          <t>UAPB +54.5</t>
         </is>
       </c>
       <c r="G18" s="26" t="n">
-        <v>-31.5</v>
+        <v>-54.5</v>
       </c>
       <c r="H18" s="18" t="n">
-        <v>-102</v>
+        <v>-108</v>
       </c>
       <c r="I18" s="20" t="n">
-        <v>0.7343060735243786</v>
+        <v>0.7478170752920796</v>
       </c>
       <c r="J18" s="20" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K18" s="20" t="n">
-        <v>0.504950495049505</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L18" s="19" t="n">
-        <v>0.2293555784748736</v>
+        <v>0.2285863060613104</v>
       </c>
       <c r="M18" s="19" t="n">
-        <v>0.4542139887443577</v>
+        <v>0.4402402931551164</v>
       </c>
       <c r="N18" s="20" t="n">
         <v>0</v>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="Q18" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>UAPB isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -2385,12 +2385,12 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>UAPB @ MIZ</t>
+          <t>UTU @ BYU</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-09-06 00:00</t>
         </is>
       </c>
       <c r="D19" s="22" t="n">
@@ -2403,17 +2403,17 @@
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>UAPB +54.5</t>
+          <t>UTU +47.5</t>
         </is>
       </c>
       <c r="G19" s="23" t="n">
-        <v>-54.5</v>
+        <v>-47.5</v>
       </c>
       <c r="H19" s="13" t="n">
         <v>-108</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>0.7478170752920796</v>
+        <v>0.7476589193185947</v>
       </c>
       <c r="J19" s="15" t="n">
         <v>0.4956702459300312</v>
@@ -2422,16 +2422,16 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L19" s="14" t="n">
-        <v>0.2285863060613104</v>
+        <v>0.2284281500878255</v>
       </c>
       <c r="M19" s="14" t="n">
-        <v>0.4402402931551164</v>
+        <v>0.4399356964654418</v>
       </c>
       <c r="N19" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O19" s="24" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="P19" s="12" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="Q19" s="12" t="inlineStr">
         <is>
-          <t>UAPB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>UTU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -2452,12 +2452,12 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>UTU @ BYU</t>
+          <t>INST @ PUR</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00</t>
+          <t>2026-09-04 23:00</t>
         </is>
       </c>
       <c r="D20" s="25" t="n">
@@ -2470,35 +2470,35 @@
       </c>
       <c r="F20" s="17" t="inlineStr">
         <is>
-          <t>UTU +47.5</t>
+          <t>INST +35.5</t>
         </is>
       </c>
       <c r="G20" s="26" t="n">
-        <v>-47.5</v>
+        <v>-35.5</v>
       </c>
       <c r="H20" s="18" t="n">
         <v>-108</v>
       </c>
       <c r="I20" s="20" t="n">
-        <v>0.7476589193185947</v>
+        <v>0.7471065701681774</v>
       </c>
       <c r="J20" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4978050921861282</v>
       </c>
       <c r="K20" s="20" t="n">
         <v>0.5192307692307693</v>
       </c>
       <c r="L20" s="19" t="n">
-        <v>0.2284281500878255</v>
+        <v>0.2278758009374081</v>
       </c>
       <c r="M20" s="19" t="n">
-        <v>0.4399356964654418</v>
+        <v>0.4388719129164899</v>
       </c>
       <c r="N20" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O20" s="27" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="P20" s="17" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="Q20" s="17" t="inlineStr">
         <is>
-          <t>UTU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>INST isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>INST @ PUR</t>
+          <t>NWST @ LT</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 23:00</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D21" s="22" t="n">
@@ -2537,29 +2537,29 @@
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>INST +35.5</t>
+          <t>NWST +41.5</t>
         </is>
       </c>
       <c r="G21" s="23" t="n">
-        <v>-35.5</v>
+        <v>-41.5</v>
       </c>
       <c r="H21" s="13" t="n">
         <v>-108</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>0.7471065701681774</v>
+        <v>0.7470572981808887</v>
       </c>
       <c r="J21" s="15" t="n">
-        <v>0.4978050921861282</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K21" s="15" t="n">
         <v>0.5192307692307693</v>
       </c>
       <c r="L21" s="14" t="n">
-        <v>0.2278758009374081</v>
+        <v>0.2278265289501195</v>
       </c>
       <c r="M21" s="14" t="n">
-        <v>0.4388719129164899</v>
+        <v>0.4387770187187487</v>
       </c>
       <c r="N21" s="15" t="n">
         <v>0</v>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="Q21" s="12" t="inlineStr">
         <is>
-          <t>INST isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>NWST isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -2586,12 +2586,12 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>NWST @ LT</t>
+          <t>NICH @ KSU</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D22" s="25" t="n">
@@ -2604,17 +2604,17 @@
       </c>
       <c r="F22" s="17" t="inlineStr">
         <is>
-          <t>NWST +41.5</t>
+          <t>NICH +40.5</t>
         </is>
       </c>
       <c r="G22" s="26" t="n">
-        <v>-41.5</v>
+        <v>-40.5</v>
       </c>
       <c r="H22" s="18" t="n">
         <v>-108</v>
       </c>
       <c r="I22" s="20" t="n">
-        <v>0.7470572981808887</v>
+        <v>0.7469287042110235</v>
       </c>
       <c r="J22" s="20" t="n">
         <v>0.4956702459300312</v>
@@ -2623,10 +2623,10 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L22" s="19" t="n">
-        <v>0.2278265289501195</v>
+        <v>0.2276979349802543</v>
       </c>
       <c r="M22" s="19" t="n">
-        <v>0.4387770187187487</v>
+        <v>0.4385293562582676</v>
       </c>
       <c r="N22" s="20" t="n">
         <v>0</v>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="Q22" s="17" t="inlineStr">
         <is>
-          <t>NWST isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>NICH isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -2653,12 +2653,12 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>NICH @ KSU</t>
+          <t>UNT @ IU</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D23" s="22" t="n">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>NICH +40.5</t>
+          <t>UNT +40.5</t>
         </is>
       </c>
       <c r="G23" s="23" t="n">
@@ -2681,7 +2681,7 @@
         <v>-108</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>0.7469287042110235</v>
+        <v>0.746723975316852</v>
       </c>
       <c r="J23" s="15" t="n">
         <v>0.4956702459300312</v>
@@ -2690,10 +2690,10 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L23" s="14" t="n">
-        <v>0.2276979349802543</v>
+        <v>0.2274932060860827</v>
       </c>
       <c r="M23" s="14" t="n">
-        <v>0.4385293562582676</v>
+        <v>0.4381350635731964</v>
       </c>
       <c r="N23" s="15" t="n">
         <v>0</v>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="Q23" s="12" t="inlineStr">
         <is>
-          <t>NICH isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -2720,12 +2720,12 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>UNT @ IU</t>
+          <t>ACU @ TTU</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D24" s="25" t="n">
@@ -2738,17 +2738,17 @@
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>UNT +40.5</t>
+          <t>ACU +42.5</t>
         </is>
       </c>
       <c r="G24" s="26" t="n">
-        <v>-40.5</v>
+        <v>-42.5</v>
       </c>
       <c r="H24" s="18" t="n">
         <v>-108</v>
       </c>
       <c r="I24" s="20" t="n">
-        <v>0.746723975316852</v>
+        <v>0.7466897348351318</v>
       </c>
       <c r="J24" s="20" t="n">
         <v>0.4956702459300312</v>
@@ -2757,10 +2757,10 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L24" s="19" t="n">
-        <v>0.2274932060860827</v>
+        <v>0.2274589656043625</v>
       </c>
       <c r="M24" s="19" t="n">
-        <v>0.4381350635731964</v>
+        <v>0.4380691189417354</v>
       </c>
       <c r="N24" s="20" t="n">
         <v>0</v>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="Q24" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>ACU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>ACU @ TTU</t>
+          <t>FUR @ TENN</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D25" s="22" t="n">
@@ -2805,29 +2805,29 @@
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>ACU +42.5</t>
+          <t>FUR +46.5</t>
         </is>
       </c>
       <c r="G25" s="23" t="n">
-        <v>-42.5</v>
+        <v>-46.5</v>
       </c>
       <c r="H25" s="13" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>0.7466897348351318</v>
+        <v>0.7497811250786943</v>
       </c>
       <c r="J25" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5</v>
       </c>
       <c r="K25" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L25" s="14" t="n">
-        <v>0.2274589656043625</v>
+        <v>0.2259716012691705</v>
       </c>
       <c r="M25" s="14" t="n">
-        <v>0.4380691189417354</v>
+        <v>0.4314003296956892</v>
       </c>
       <c r="N25" s="15" t="n">
         <v>0</v>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="Q25" s="12" t="inlineStr">
         <is>
-          <t>ACU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>FUR isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -2854,12 +2854,12 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>FUR @ TENN</t>
+          <t>BCU @ UCF</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D26" s="25" t="n">
@@ -2872,17 +2872,17 @@
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>FUR +46.5</t>
+          <t>BCU +42.5</t>
         </is>
       </c>
       <c r="G26" s="26" t="n">
-        <v>-46.5</v>
+        <v>-42.5</v>
       </c>
       <c r="H26" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I26" s="20" t="n">
-        <v>0.7497811250786943</v>
+        <v>0.7495833131506973</v>
       </c>
       <c r="J26" s="20" t="n">
         <v>0.5</v>
@@ -2891,10 +2891,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L26" s="19" t="n">
-        <v>0.2259716012691705</v>
+        <v>0.2257737893411734</v>
       </c>
       <c r="M26" s="19" t="n">
-        <v>0.4314003296956892</v>
+        <v>0.4310226887422403</v>
       </c>
       <c r="N26" s="20" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="Q26" s="17" t="inlineStr">
         <is>
-          <t>FUR isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -2921,12 +2921,12 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>BCU @ UCF</t>
+          <t>MORG @ ASU</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-06 02:00</t>
         </is>
       </c>
       <c r="D27" s="22" t="n">
@@ -2939,17 +2939,17 @@
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>BCU +42.5</t>
+          <t>MORG +41.5</t>
         </is>
       </c>
       <c r="G27" s="23" t="n">
-        <v>-42.5</v>
+        <v>-41.5</v>
       </c>
       <c r="H27" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>0.7495833131506973</v>
+        <v>0.7493519008122786</v>
       </c>
       <c r="J27" s="15" t="n">
         <v>0.5</v>
@@ -2958,10 +2958,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L27" s="14" t="n">
-        <v>0.2257737893411734</v>
+        <v>0.2255423770027548</v>
       </c>
       <c r="M27" s="14" t="n">
-        <v>0.4310226887422403</v>
+        <v>0.4305809015507138</v>
       </c>
       <c r="N27" s="15" t="n">
         <v>0</v>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="Q27" s="12" t="inlineStr">
         <is>
-          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>MORG isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -2988,12 +2988,12 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>MORG @ ASU</t>
+          <t>NORF @ ODU</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>2026-09-06 02:00</t>
+          <t>2026-09-05 22:00</t>
         </is>
       </c>
       <c r="D28" s="25" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>MORG +41.5</t>
+          <t>NORF +41.5</t>
         </is>
       </c>
       <c r="G28" s="26" t="n">
@@ -3016,7 +3016,7 @@
         <v>-110</v>
       </c>
       <c r="I28" s="20" t="n">
-        <v>0.7493519008122786</v>
+        <v>0.7490055324508147</v>
       </c>
       <c r="J28" s="20" t="n">
         <v>0.5</v>
@@ -3025,10 +3025,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L28" s="19" t="n">
-        <v>0.2255423770027548</v>
+        <v>0.2251960086412909</v>
       </c>
       <c r="M28" s="19" t="n">
-        <v>0.4305809015507138</v>
+        <v>0.4299196528606463</v>
       </c>
       <c r="N28" s="20" t="n">
         <v>0</v>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="Q28" s="17" t="inlineStr">
         <is>
-          <t>MORG isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>NORF isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -3055,12 +3055,12 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>NORF @ ODU</t>
+          <t>LIU @ KU</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 22:00</t>
+          <t>2026-09-05 00:00</t>
         </is>
       </c>
       <c r="D29" s="22" t="n">
@@ -3073,17 +3073,17 @@
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>NORF +41.5</t>
+          <t>LIU +38.5</t>
         </is>
       </c>
       <c r="G29" s="23" t="n">
-        <v>-41.5</v>
+        <v>-38.5</v>
       </c>
       <c r="H29" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>0.7490055324508147</v>
+        <v>0.7488772579251495</v>
       </c>
       <c r="J29" s="15" t="n">
         <v>0.5</v>
@@ -3092,10 +3092,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L29" s="14" t="n">
-        <v>0.2251960086412909</v>
+        <v>0.2250677341156256</v>
       </c>
       <c r="M29" s="14" t="n">
-        <v>0.4299196528606463</v>
+        <v>0.4296747651298308</v>
       </c>
       <c r="N29" s="15" t="n">
         <v>0</v>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="Q29" s="12" t="inlineStr">
         <is>
-          <t>NORF isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>LIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>LIU @ KU</t>
+          <t>PRST @ SDSU</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 00:00</t>
+          <t>2026-09-06 01:30</t>
         </is>
       </c>
       <c r="D30" s="25" t="n">
@@ -3140,17 +3140,17 @@
       </c>
       <c r="F30" s="17" t="inlineStr">
         <is>
-          <t>LIU +38.5</t>
+          <t>PRST +40.5</t>
         </is>
       </c>
       <c r="G30" s="26" t="n">
-        <v>-38.5</v>
+        <v>-40.5</v>
       </c>
       <c r="H30" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I30" s="20" t="n">
-        <v>0.7488772579251495</v>
+        <v>0.7486961049263416</v>
       </c>
       <c r="J30" s="20" t="n">
         <v>0.5</v>
@@ -3159,10 +3159,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>0.2250677341156256</v>
+        <v>0.2248865811168178</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>0.4296747651298308</v>
+        <v>0.4293289275866523</v>
       </c>
       <c r="N30" s="20" t="n">
         <v>0</v>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="Q30" s="17" t="inlineStr">
         <is>
-          <t>LIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>PRST isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -3189,12 +3189,12 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>PRST @ SDSU</t>
+          <t>FOR @ NDSU</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 01:30</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D31" s="22" t="n">
@@ -3207,17 +3207,17 @@
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>PRST +40.5</t>
+          <t>FOR +39.5</t>
         </is>
       </c>
       <c r="G31" s="23" t="n">
-        <v>-40.5</v>
+        <v>-39.5</v>
       </c>
       <c r="H31" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>0.7486961049263416</v>
+        <v>0.747919032112444</v>
       </c>
       <c r="J31" s="15" t="n">
         <v>0.5</v>
@@ -3226,10 +3226,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L31" s="14" t="n">
-        <v>0.2248865811168178</v>
+        <v>0.2241095083029202</v>
       </c>
       <c r="M31" s="14" t="n">
-        <v>0.4293289275866523</v>
+        <v>0.4278454249419387</v>
       </c>
       <c r="N31" s="15" t="n">
         <v>0</v>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="Q31" s="12" t="inlineStr">
         <is>
-          <t>PRST isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>FOR isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -3256,12 +3256,12 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>FOR @ NDSU</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D32" s="25" t="n">
@@ -3274,17 +3274,17 @@
       </c>
       <c r="F32" s="17" t="inlineStr">
         <is>
-          <t>FOR +39.5</t>
+          <t>SJSU +38.5</t>
         </is>
       </c>
       <c r="G32" s="26" t="n">
-        <v>-39.5</v>
+        <v>-38.5</v>
       </c>
       <c r="H32" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I32" s="20" t="n">
-        <v>0.747919032112444</v>
+        <v>0.7476789160487953</v>
       </c>
       <c r="J32" s="20" t="n">
         <v>0.5</v>
@@ -3293,10 +3293,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L32" s="19" t="n">
-        <v>0.2241095083029202</v>
+        <v>0.2238693922392715</v>
       </c>
       <c r="M32" s="19" t="n">
-        <v>0.4278454249419387</v>
+        <v>0.4273870215477003</v>
       </c>
       <c r="N32" s="20" t="n">
         <v>0</v>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="Q32" s="17" t="inlineStr">
         <is>
-          <t>FOR isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -3323,12 +3323,12 @@
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>HAMP @ MD</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-09-06 00:00</t>
         </is>
       </c>
       <c r="D33" s="22" t="n">
@@ -3341,35 +3341,35 @@
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>SJSU +38.5</t>
+          <t>HAMP +45.5</t>
         </is>
       </c>
       <c r="G33" s="23" t="n">
-        <v>-38.5</v>
+        <v>-45.5</v>
       </c>
       <c r="H33" s="13" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>0.7476789160487953</v>
+        <v>0.7520172898132291</v>
       </c>
       <c r="J33" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K33" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L33" s="14" t="n">
-        <v>0.2238693922392715</v>
+        <v>0.2237154030207763</v>
       </c>
       <c r="M33" s="14" t="n">
-        <v>0.4273870215477003</v>
+        <v>0.4234612985750408</v>
       </c>
       <c r="N33" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O33" s="24" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="P33" s="12" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="Q33" s="12" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>HAMP isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -3390,12 +3390,12 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>HAMP @ MD</t>
+          <t>BALL @ OSU</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00</t>
+          <t>2026-09-05 16:30</t>
         </is>
       </c>
       <c r="D34" s="25" t="n">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="F34" s="17" t="inlineStr">
         <is>
-          <t>HAMP +45.5</t>
+          <t>BALL +50.5</t>
         </is>
       </c>
       <c r="G34" s="26" t="n">
-        <v>-45.5</v>
+        <v>-50.5</v>
       </c>
       <c r="H34" s="18" t="n">
         <v>-112</v>
       </c>
       <c r="I34" s="20" t="n">
-        <v>0.7520172898132291</v>
+        <v>0.7519654142724952</v>
       </c>
       <c r="J34" s="20" t="n">
         <v>0.5043297540699688</v>
@@ -3427,16 +3427,16 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L34" s="19" t="n">
-        <v>0.2237154030207763</v>
+        <v>0.2236635274800424</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>0.4234612985750408</v>
+        <v>0.423363105587223</v>
       </c>
       <c r="N34" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O34" s="27" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="P34" s="17" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="Q34" s="17" t="inlineStr">
         <is>
-          <t>HAMP isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>BALL @ OSU</t>
+          <t>EIU @ MINN</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 16:30</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D35" s="22" t="n">
@@ -3475,17 +3475,17 @@
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>BALL +50.5</t>
+          <t>EIU +43.5</t>
         </is>
       </c>
       <c r="G35" s="23" t="n">
-        <v>-50.5</v>
+        <v>-43.5</v>
       </c>
       <c r="H35" s="13" t="n">
         <v>-112</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>0.7519654142724952</v>
+        <v>0.7518231737767994</v>
       </c>
       <c r="J35" s="15" t="n">
         <v>0.5043297540699688</v>
@@ -3494,10 +3494,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L35" s="14" t="n">
-        <v>0.2236635274800424</v>
+        <v>0.2235212869843466</v>
       </c>
       <c r="M35" s="14" t="n">
-        <v>0.423363105587223</v>
+        <v>0.4230938646489417</v>
       </c>
       <c r="N35" s="15" t="n">
         <v>0</v>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Q35" s="12" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -3524,12 +3524,12 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>EIU @ MINN</t>
+          <t>UNA @ ARK</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-09-05 20:15</t>
         </is>
       </c>
       <c r="D36" s="25" t="n">
@@ -3542,17 +3542,17 @@
       </c>
       <c r="F36" s="17" t="inlineStr">
         <is>
-          <t>EIU +43.5</t>
+          <t>UNA +40.5</t>
         </is>
       </c>
       <c r="G36" s="26" t="n">
-        <v>-43.5</v>
+        <v>-40.5</v>
       </c>
       <c r="H36" s="18" t="n">
         <v>-112</v>
       </c>
       <c r="I36" s="20" t="n">
-        <v>0.7518231737767994</v>
+        <v>0.7514996793539089</v>
       </c>
       <c r="J36" s="20" t="n">
         <v>0.5043297540699688</v>
@@ -3561,10 +3561,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L36" s="19" t="n">
-        <v>0.2235212869843466</v>
+        <v>0.2231977925614561</v>
       </c>
       <c r="M36" s="19" t="n">
-        <v>0.4230938646489417</v>
+        <v>0.422481535919899</v>
       </c>
       <c r="N36" s="20" t="n">
         <v>0</v>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="Q36" s="17" t="inlineStr">
         <is>
-          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>UNA isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -3591,12 +3591,12 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>UNA @ ARK</t>
+          <t>WMU @ MICH</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 20:15</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D37" s="22" t="n">
@@ -3609,29 +3609,29 @@
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>UNA +40.5</t>
+          <t>WMU +27.5</t>
         </is>
       </c>
       <c r="G37" s="23" t="n">
-        <v>-40.5</v>
+        <v>-27.5</v>
       </c>
       <c r="H37" s="13" t="n">
-        <v>-112</v>
+        <v>-105</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>0.7514996793539089</v>
+        <v>0.7345065169441323</v>
       </c>
       <c r="J37" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K37" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L37" s="14" t="n">
-        <v>0.2231977925614561</v>
+        <v>0.2223113949929127</v>
       </c>
       <c r="M37" s="14" t="n">
-        <v>0.422481535919899</v>
+        <v>0.4340365330814011</v>
       </c>
       <c r="N37" s="15" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="Q37" s="12" t="inlineStr">
         <is>
-          <t>UNA isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -3658,12 +3658,12 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>WMU @ MICH</t>
+          <t>IDHO @ UTAH</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D38" s="25" t="n">
@@ -3676,29 +3676,29 @@
       </c>
       <c r="F38" s="17" t="inlineStr">
         <is>
-          <t>WMU +27.5</t>
+          <t>IDHO +33.5</t>
         </is>
       </c>
       <c r="G38" s="26" t="n">
-        <v>-27.5</v>
+        <v>-33.5</v>
       </c>
       <c r="H38" s="18" t="n">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="I38" s="20" t="n">
-        <v>0.7345065169441323</v>
+        <v>0.7414791527526444</v>
       </c>
       <c r="J38" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K38" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>0.2223113949929127</v>
+        <v>0.2222483835218751</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>0.4340365330814011</v>
+        <v>0.4280339238199079</v>
       </c>
       <c r="N38" s="20" t="n">
         <v>0</v>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="Q38" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -3725,12 +3725,12 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>IDHO @ UTAH</t>
+          <t>KENT @ SC</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 01:00</t>
+          <t>2026-09-05 16:45</t>
         </is>
       </c>
       <c r="D39" s="22" t="n">
@@ -3743,29 +3743,29 @@
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>IDHO +33.5</t>
+          <t>KENT +36.5</t>
         </is>
       </c>
       <c r="G39" s="23" t="n">
-        <v>-33.5</v>
+        <v>-36.5</v>
       </c>
       <c r="H39" s="13" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>0.7414791527526444</v>
+        <v>0.7500631386431562</v>
       </c>
       <c r="J39" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K39" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L39" s="14" t="n">
-        <v>0.2222483835218751</v>
+        <v>0.2217612518507034</v>
       </c>
       <c r="M39" s="14" t="n">
-        <v>0.4280339238199079</v>
+        <v>0.4197623695745456</v>
       </c>
       <c r="N39" s="15" t="n">
         <v>0</v>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="Q39" s="12" t="inlineStr">
         <is>
-          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -3792,12 +3792,12 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>KENT @ SC</t>
+          <t>BRY @ ARMY</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 16:45</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D40" s="25" t="n">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="F40" s="17" t="inlineStr">
         <is>
-          <t>KENT +36.5</t>
+          <t>BRY +36.5</t>
         </is>
       </c>
       <c r="G40" s="26" t="n">
@@ -3820,7 +3820,7 @@
         <v>-112</v>
       </c>
       <c r="I40" s="20" t="n">
-        <v>0.7500631386431562</v>
+        <v>0.7499321602477051</v>
       </c>
       <c r="J40" s="20" t="n">
         <v>0.5043297540699688</v>
@@ -3829,10 +3829,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L40" s="19" t="n">
-        <v>0.2217612518507034</v>
+        <v>0.2216302734552523</v>
       </c>
       <c r="M40" s="19" t="n">
-        <v>0.4197623695745456</v>
+        <v>0.4195144461831561</v>
       </c>
       <c r="N40" s="20" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
       </c>
       <c r="Q40" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>BRY isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -3859,12 +3859,12 @@
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>BRY @ ARMY</t>
+          <t>ULM @ MSST</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D41" s="22" t="n">
@@ -3877,29 +3877,29 @@
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>BRY +36.5</t>
+          <t>ULM +28.5</t>
         </is>
       </c>
       <c r="G41" s="23" t="n">
-        <v>-36.5</v>
+        <v>-28.5</v>
       </c>
       <c r="H41" s="13" t="n">
-        <v>-112</v>
+        <v>-105</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>0.7499321602477051</v>
+        <v>0.7334330756423124</v>
       </c>
       <c r="J41" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K41" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L41" s="14" t="n">
-        <v>0.2216302734552523</v>
+        <v>0.2212379536910929</v>
       </c>
       <c r="M41" s="14" t="n">
-        <v>0.4195144461831561</v>
+        <v>0.431940766730229</v>
       </c>
       <c r="N41" s="15" t="n">
         <v>0</v>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="Q41" s="12" t="inlineStr">
         <is>
-          <t>BRY isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>ULM @ MSST</t>
+          <t>MVSU @ SAC</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-09-06 02:00</t>
         </is>
       </c>
       <c r="D42" s="25" t="n">
@@ -3944,35 +3944,35 @@
       </c>
       <c r="F42" s="17" t="inlineStr">
         <is>
-          <t>ULM +28.5</t>
+          <t>MVSU +35.5</t>
         </is>
       </c>
       <c r="G42" s="26" t="n">
-        <v>-28.5</v>
+        <v>-35.5</v>
       </c>
       <c r="H42" s="18" t="n">
-        <v>-105</v>
+        <v>-112</v>
       </c>
       <c r="I42" s="20" t="n">
-        <v>0.7334330756423124</v>
+        <v>0.7492254004247646</v>
       </c>
       <c r="J42" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K42" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L42" s="19" t="n">
-        <v>0.2212379536910929</v>
+        <v>0.2209235136323118</v>
       </c>
       <c r="M42" s="19" t="n">
-        <v>0.431940766730229</v>
+        <v>0.4181766508040187</v>
       </c>
       <c r="N42" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O42" s="27" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="P42" s="17" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="Q42" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>MVSU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -3993,12 +3993,12 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>MVSU @ SAC</t>
+          <t>APSU @ VAN</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 02:00</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D43" s="22" t="n">
@@ -4011,35 +4011,35 @@
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>MVSU +35.5</t>
+          <t>APSU +30.5</t>
         </is>
       </c>
       <c r="G43" s="23" t="n">
-        <v>-35.5</v>
+        <v>-30.5</v>
       </c>
       <c r="H43" s="13" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>0.7492254004247646</v>
+        <v>0.7386266152687198</v>
       </c>
       <c r="J43" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K43" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L43" s="14" t="n">
-        <v>0.2209235136323118</v>
+        <v>0.2193958460379505</v>
       </c>
       <c r="M43" s="14" t="n">
-        <v>0.4181766508040187</v>
+        <v>0.4225401479249419</v>
       </c>
       <c r="N43" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O43" s="24" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="P43" s="12" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="Q43" s="12" t="inlineStr">
         <is>
-          <t>MVSU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>APSU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -4060,12 +4060,12 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>APSU @ VAN</t>
+          <t>UNH @ SYR</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D44" s="25" t="n">
@@ -4078,29 +4078,29 @@
       </c>
       <c r="F44" s="17" t="inlineStr">
         <is>
-          <t>APSU +30.5</t>
+          <t>UNH +32.5</t>
         </is>
       </c>
       <c r="G44" s="26" t="n">
-        <v>-30.5</v>
+        <v>-32.5</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>-108</v>
+        <v>-115</v>
       </c>
       <c r="I44" s="20" t="n">
-        <v>0.7386266152687198</v>
+        <v>0.7526000257941813</v>
       </c>
       <c r="J44" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K44" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L44" s="19" t="n">
-        <v>0.2193958460379505</v>
+        <v>0.2177163048639488</v>
       </c>
       <c r="M44" s="19" t="n">
-        <v>0.4225401479249419</v>
+        <v>0.4070348308325997</v>
       </c>
       <c r="N44" s="20" t="n">
         <v>0</v>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="Q44" s="17" t="inlineStr">
         <is>
-          <t>APSU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>UNH isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -4127,12 +4127,12 @@
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>UNH @ SYR</t>
+          <t>TNST @ UGA</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-09-05 19:00</t>
         </is>
       </c>
       <c r="D45" s="22" t="n">
@@ -4145,29 +4145,29 @@
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
-          <t>UNH +32.5</t>
+          <t>TNST +47.5</t>
         </is>
       </c>
       <c r="G45" s="23" t="n">
-        <v>-32.5</v>
+        <v>-47.5</v>
       </c>
       <c r="H45" s="13" t="n">
-        <v>-115</v>
+        <v>-118</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>0.7526000257941813</v>
+        <v>0.7584495775780455</v>
       </c>
       <c r="J45" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5173641257162701</v>
       </c>
       <c r="K45" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5412844036697247</v>
       </c>
       <c r="L45" s="14" t="n">
-        <v>0.2177163048639488</v>
+        <v>0.2171651739083208</v>
       </c>
       <c r="M45" s="14" t="n">
-        <v>0.4070348308325997</v>
+        <v>0.401203456881474</v>
       </c>
       <c r="N45" s="15" t="n">
         <v>0</v>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="Q45" s="12" t="inlineStr">
         <is>
-          <t>UNH isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>TNST isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -4194,12 +4194,12 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>TNST @ UGA</t>
+          <t>NCAT @ GAST</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 19:00</t>
+          <t>2026-09-04 23:00</t>
         </is>
       </c>
       <c r="D46" s="25" t="n">
@@ -4212,29 +4212,29 @@
       </c>
       <c r="F46" s="17" t="inlineStr">
         <is>
-          <t>TNST +47.5</t>
+          <t>NCAT +28.5</t>
         </is>
       </c>
       <c r="G46" s="26" t="n">
-        <v>-47.5</v>
+        <v>-28.5</v>
       </c>
       <c r="H46" s="18" t="n">
-        <v>-118</v>
+        <v>-112</v>
       </c>
       <c r="I46" s="20" t="n">
-        <v>0.7584495775780455</v>
+        <v>0.7452866315143292</v>
       </c>
       <c r="J46" s="20" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K46" s="20" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L46" s="19" t="n">
-        <v>0.2171651739083208</v>
+        <v>0.2169847447218763</v>
       </c>
       <c r="M46" s="19" t="n">
-        <v>0.401203456881474</v>
+        <v>0.4107211239378373</v>
       </c>
       <c r="N46" s="20" t="n">
         <v>0</v>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="Q46" s="17" t="inlineStr">
         <is>
-          <t>TNST isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -4261,12 +4261,12 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>NCAT @ GAST</t>
+          <t>NMSU @ FSU</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 23:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D47" s="22" t="n">
@@ -4279,17 +4279,17 @@
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>NCAT +28.5</t>
+          <t>NMSU +31.5</t>
         </is>
       </c>
       <c r="G47" s="23" t="n">
-        <v>-28.5</v>
+        <v>-31.5</v>
       </c>
       <c r="H47" s="13" t="n">
         <v>-112</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>0.7452866315143292</v>
+        <v>0.7451530134174981</v>
       </c>
       <c r="J47" s="15" t="n">
         <v>0.5043297540699688</v>
@@ -4298,10 +4298,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L47" s="14" t="n">
-        <v>0.2169847447218763</v>
+        <v>0.2168511266250452</v>
       </c>
       <c r="M47" s="14" t="n">
-        <v>0.4107211239378373</v>
+        <v>0.4104682039688355</v>
       </c>
       <c r="N47" s="15" t="n">
         <v>0</v>
@@ -4316,7 +4316,7 @@
       </c>
       <c r="Q47" s="12" t="inlineStr">
         <is>
-          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -7841,12 +7841,12 @@
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>NMSU @ FSU</t>
+          <t>APSU @ VAN</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D101" s="22" t="n">
@@ -7859,27 +7859,27 @@
       </c>
       <c r="F101" s="12" t="inlineStr">
         <is>
-          <t>NMSU ML</t>
+          <t>APSU ML</t>
         </is>
       </c>
       <c r="G101" s="23" t="n"/>
       <c r="H101" s="13" t="n">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="I101" s="15" t="n">
-        <v>0.2094956647177477</v>
+        <v>0.2000025632021549</v>
       </c>
       <c r="J101" s="15" t="n">
-        <v>0.02715849209566274</v>
+        <v>0.01924962981481125</v>
       </c>
       <c r="K101" s="15" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.0196078431372549</v>
       </c>
       <c r="L101" s="14" t="n">
-        <v>0.1817178869399699</v>
+        <v>0.1803947200649</v>
       </c>
       <c r="M101" s="14" t="n">
-        <v>6.541843929838918</v>
+        <v>9.200130723309901</v>
       </c>
       <c r="N101" s="15" t="n">
         <v>0</v>
@@ -7894,7 +7894,7 @@
       </c>
       <c r="Q101" s="12" t="inlineStr">
         <is>
-          <t>price outside allowed range</t>
+          <t>APSU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -7906,12 +7906,12 @@
       </c>
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>APSU @ VAN</t>
+          <t>NMSU @ FSU</t>
         </is>
       </c>
       <c r="C102" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D102" s="25" t="n">
@@ -7924,27 +7924,27 @@
       </c>
       <c r="F102" s="17" t="inlineStr">
         <is>
-          <t>APSU ML</t>
+          <t>NMSU ML</t>
         </is>
       </c>
       <c r="G102" s="26" t="n"/>
       <c r="H102" s="18" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="I102" s="20" t="n">
-        <v>0.2000025632021549</v>
+        <v>0.2116927385699474</v>
       </c>
       <c r="J102" s="20" t="n">
-        <v>0.01924962981481125</v>
+        <v>0.03155263980006248</v>
       </c>
       <c r="K102" s="20" t="n">
-        <v>0.0196078431372549</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="L102" s="19" t="n">
-        <v>0.1803947200649</v>
+        <v>0.1794346740538184</v>
       </c>
       <c r="M102" s="19" t="n">
-        <v>9.200130723309901</v>
+        <v>5.56247489566837</v>
       </c>
       <c r="N102" s="20" t="n">
         <v>0</v>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="Q102" s="17" t="inlineStr">
         <is>
-          <t>APSU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>price outside allowed range</t>
         </is>
       </c>
     </row>
@@ -11330,12 +11330,12 @@
       </c>
       <c r="B154" s="17" t="inlineStr">
         <is>
-          <t>FIU @ USF</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C154" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D154" s="25" t="n">
@@ -11343,34 +11343,34 @@
       </c>
       <c r="E154" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F154" s="17" t="inlineStr">
         <is>
-          <t>Over 53.5</t>
+          <t>UNC +8.5</t>
         </is>
       </c>
       <c r="G154" s="26" t="n">
-        <v>53.5</v>
+        <v>-8.5</v>
       </c>
       <c r="H154" s="18" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="I154" s="20" t="n">
-        <v>0.6281478128154605</v>
+        <v>0.6114350102008398</v>
       </c>
       <c r="J154" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K154" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L154" s="19" t="n">
-        <v>0.093264091885228</v>
+        <v>0.09220424097007052</v>
       </c>
       <c r="M154" s="19" t="n">
-        <v>0.1743633022202087</v>
+        <v>0.1775785381645804</v>
       </c>
       <c r="N154" s="20" t="n">
         <v>0</v>
@@ -11464,12 +11464,12 @@
       </c>
       <c r="B156" s="17" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>FUR @ TENN</t>
         </is>
       </c>
       <c r="C156" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D156" s="25" t="n">
@@ -11477,32 +11477,34 @@
       </c>
       <c r="E156" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F156" s="17" t="inlineStr">
         <is>
-          <t>UNC ML</t>
-        </is>
-      </c>
-      <c r="G156" s="26" t="n"/>
+          <t>Under 66.5</t>
+        </is>
+      </c>
+      <c r="G156" s="26" t="n">
+        <v>66.5</v>
+      </c>
       <c r="H156" s="18" t="n">
-        <v>285</v>
+        <v>-115</v>
       </c>
       <c r="I156" s="20" t="n">
-        <v>0.3495989730025922</v>
+        <v>0.6232864407919079</v>
       </c>
       <c r="J156" s="20" t="n">
-        <v>0.2491874322860238</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K156" s="20" t="n">
-        <v>0.2597402597402597</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L156" s="19" t="n">
-        <v>0.08985871326233252</v>
+        <v>0.08840271986167536</v>
       </c>
       <c r="M156" s="19" t="n">
-        <v>0.3459560460599802</v>
+        <v>0.1652746501761755</v>
       </c>
       <c r="N156" s="20" t="n">
         <v>0</v>
@@ -11517,7 +11519,7 @@
       </c>
       <c r="Q156" s="17" t="inlineStr">
         <is>
-          <t>correlated with a stronger play on the same game</t>
+          <t>FUR isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -11529,7 +11531,7 @@
       </c>
       <c r="B157" s="12" t="inlineStr">
         <is>
-          <t>FUR @ TENN</t>
+          <t>BC @ CIN</t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr">
@@ -11547,29 +11549,29 @@
       </c>
       <c r="F157" s="12" t="inlineStr">
         <is>
-          <t>Under 66.5</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="G157" s="23" t="n">
-        <v>66.5</v>
+        <v>51.5</v>
       </c>
       <c r="H157" s="13" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="I157" s="15" t="n">
-        <v>0.6232864407919079</v>
+        <v>0.6057060023101252</v>
       </c>
       <c r="J157" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K157" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L157" s="14" t="n">
-        <v>0.08840271986167536</v>
+        <v>0.0864752330793559</v>
       </c>
       <c r="M157" s="14" t="n">
-        <v>0.1652746501761755</v>
+        <v>0.1665448933380189</v>
       </c>
       <c r="N157" s="15" t="n">
         <v>0</v>
@@ -11584,7 +11586,7 @@
       </c>
       <c r="Q157" s="12" t="inlineStr">
         <is>
-          <t>FUR isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>outside the top 10 plays for this week</t>
         </is>
       </c>
     </row>
@@ -11596,12 +11598,12 @@
       </c>
       <c r="B158" s="17" t="inlineStr">
         <is>
-          <t>BC @ CIN</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C158" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D158" s="25" t="n">
@@ -11609,34 +11611,32 @@
       </c>
       <c r="E158" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F158" s="17" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
-        </is>
-      </c>
-      <c r="G158" s="26" t="n">
-        <v>51.5</v>
-      </c>
+          <t>UNC ML</t>
+        </is>
+      </c>
+      <c r="G158" s="26" t="n"/>
       <c r="H158" s="18" t="n">
-        <v>-108</v>
+        <v>275</v>
       </c>
       <c r="I158" s="20" t="n">
-        <v>0.6057060023101252</v>
+        <v>0.3529707493110541</v>
       </c>
       <c r="J158" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.2559309849029475</v>
       </c>
       <c r="K158" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="L158" s="19" t="n">
-        <v>0.0864752330793559</v>
+        <v>0.08630408264438744</v>
       </c>
       <c r="M158" s="19" t="n">
-        <v>0.1665448933380189</v>
+        <v>0.3236403099164529</v>
       </c>
       <c r="N158" s="20" t="n">
         <v>0</v>
@@ -11651,7 +11651,7 @@
       </c>
       <c r="Q158" s="17" t="inlineStr">
         <is>
-          <t>outside the top 10 plays for this week</t>
+          <t>correlated with a stronger play on the same game</t>
         </is>
       </c>
     </row>
@@ -13304,12 +13304,12 @@
       </c>
       <c r="B184" s="17" t="inlineStr">
         <is>
-          <t>ACU @ TTU</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C184" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D184" s="25" t="n">
@@ -13322,29 +13322,29 @@
       </c>
       <c r="F184" s="17" t="inlineStr">
         <is>
-          <t>Under 59.5</t>
+          <t>Under 61.5</t>
         </is>
       </c>
       <c r="G184" s="26" t="n">
-        <v>59.5</v>
+        <v>61.5</v>
       </c>
       <c r="H184" s="18" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="I184" s="20" t="n">
-        <v>0.5922733326643557</v>
+        <v>0.57924574575779</v>
       </c>
       <c r="J184" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K184" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L184" s="19" t="n">
-        <v>0.05738961173412316</v>
+        <v>0.0600149765270207</v>
       </c>
       <c r="M184" s="19" t="n">
-        <v>0.1072936219377083</v>
+        <v>0.1155843992372252</v>
       </c>
       <c r="N184" s="20" t="n">
         <v>0</v>
@@ -13357,11 +13357,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q184" s="17" t="inlineStr">
-        <is>
-          <t>ACU isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q184" s="17" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="12" t="inlineStr">
@@ -13371,12 +13367,12 @@
       </c>
       <c r="B185" s="12" t="inlineStr">
         <is>
-          <t>TOL @ MSU</t>
+          <t>ACU @ TTU</t>
         </is>
       </c>
       <c r="C185" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 00:00</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D185" s="22" t="n">
@@ -13389,29 +13385,29 @@
       </c>
       <c r="F185" s="12" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
+          <t>Under 59.5</t>
         </is>
       </c>
       <c r="G185" s="23" t="n">
-        <v>49.5</v>
+        <v>59.5</v>
       </c>
       <c r="H185" s="13" t="n">
-        <v>-108</v>
+        <v>-115</v>
       </c>
       <c r="I185" s="15" t="n">
-        <v>0.5755767191857057</v>
+        <v>0.5922733326643557</v>
       </c>
       <c r="J185" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K185" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L185" s="14" t="n">
-        <v>0.05634594995493647</v>
+        <v>0.05738961173412316</v>
       </c>
       <c r="M185" s="14" t="n">
-        <v>0.108518125839137</v>
+        <v>0.1072936219377083</v>
       </c>
       <c r="N185" s="15" t="n">
         <v>0</v>
@@ -13424,7 +13420,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q185" s="12" t="n"/>
+      <c r="Q185" s="12" t="inlineStr">
+        <is>
+          <t>ACU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="17" t="inlineStr">
@@ -13434,12 +13434,12 @@
       </c>
       <c r="B186" s="17" t="inlineStr">
         <is>
-          <t>BOIS @ ORE</t>
+          <t>TOL @ MSU</t>
         </is>
       </c>
       <c r="C186" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-05 00:00</t>
         </is>
       </c>
       <c r="D186" s="25" t="n">
@@ -13452,29 +13452,29 @@
       </c>
       <c r="F186" s="17" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>Over 49.5</t>
         </is>
       </c>
       <c r="G186" s="26" t="n">
-        <v>51.5</v>
+        <v>49.5</v>
       </c>
       <c r="H186" s="18" t="n">
-        <v>-118</v>
+        <v>-108</v>
       </c>
       <c r="I186" s="20" t="n">
-        <v>0.5973374319201017</v>
+        <v>0.5755767191857057</v>
       </c>
       <c r="J186" s="20" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K186" s="20" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L186" s="19" t="n">
-        <v>0.05605302825037695</v>
+        <v>0.05634594995493647</v>
       </c>
       <c r="M186" s="19" t="n">
-        <v>0.1035555945642557</v>
+        <v>0.108518125839137</v>
       </c>
       <c r="N186" s="20" t="n">
         <v>0</v>
@@ -13497,12 +13497,12 @@
       </c>
       <c r="B187" s="12" t="inlineStr">
         <is>
-          <t>UNLV @ HAW</t>
+          <t>BOIS @ ORE</t>
         </is>
       </c>
       <c r="C187" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 02:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D187" s="22" t="n">
@@ -13510,37 +13510,37 @@
       </c>
       <c r="E187" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F187" s="12" t="inlineStr">
         <is>
-          <t>HAW +3</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="G187" s="23" t="n">
-        <v>3</v>
+        <v>51.5</v>
       </c>
       <c r="H187" s="13" t="n">
-        <v>-108</v>
+        <v>-118</v>
       </c>
       <c r="I187" s="15" t="n">
-        <v>0.5752024326373151</v>
+        <v>0.5973374319201017</v>
       </c>
       <c r="J187" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5173641257162701</v>
       </c>
       <c r="K187" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5412844036697247</v>
       </c>
       <c r="L187" s="14" t="n">
-        <v>0.0559716634065458</v>
+        <v>0.05605302825037695</v>
       </c>
       <c r="M187" s="14" t="n">
-        <v>0.1016809753962156</v>
+        <v>0.1035555945642557</v>
       </c>
       <c r="N187" s="15" t="n">
-        <v>0.0567</v>
+        <v>0</v>
       </c>
       <c r="O187" s="24" t="n">
         <v>0.45</v>
@@ -13560,12 +13560,12 @@
       </c>
       <c r="B188" s="17" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>UNLV @ HAW</t>
         </is>
       </c>
       <c r="C188" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-09-06 02:00</t>
         </is>
       </c>
       <c r="D188" s="25" t="n">
@@ -13573,37 +13573,37 @@
       </c>
       <c r="E188" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F188" s="17" t="inlineStr">
         <is>
-          <t>Under 61.5</t>
+          <t>HAW +3</t>
         </is>
       </c>
       <c r="G188" s="26" t="n">
-        <v>61.5</v>
+        <v>3</v>
       </c>
       <c r="H188" s="18" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="I188" s="20" t="n">
-        <v>0.5835754998277588</v>
+        <v>0.5752024326373151</v>
       </c>
       <c r="J188" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K188" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L188" s="19" t="n">
-        <v>0.05527361303530598</v>
+        <v>0.0559716634065458</v>
       </c>
       <c r="M188" s="19" t="n">
-        <v>0.1046250532454005</v>
+        <v>0.1016809753962156</v>
       </c>
       <c r="N188" s="20" t="n">
-        <v>0</v>
+        <v>0.0567</v>
       </c>
       <c r="O188" s="27" t="n">
         <v>0.45</v>
@@ -14267,29 +14267,29 @@
       </c>
       <c r="F199" s="12" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>Over 50.5</t>
         </is>
       </c>
       <c r="G199" s="23" t="n">
-        <v>51.5</v>
+        <v>50.5</v>
       </c>
       <c r="H199" s="13" t="n">
-        <v>-102</v>
+        <v>-118</v>
       </c>
       <c r="I199" s="15" t="n">
-        <v>0.550297511023865</v>
+        <v>0.5864236544376711</v>
       </c>
       <c r="J199" s="15" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.5173641257162701</v>
       </c>
       <c r="K199" s="15" t="n">
-        <v>0.504950495049505</v>
+        <v>0.5412844036697247</v>
       </c>
       <c r="L199" s="14" t="n">
-        <v>0.04534701597436008</v>
+        <v>0.04513925076794634</v>
       </c>
       <c r="M199" s="14" t="n">
-        <v>0.08980487477275234</v>
+        <v>0.08339285311366351</v>
       </c>
       <c r="N199" s="15" t="n">
         <v>0</v>
@@ -15860,12 +15860,12 @@
       </c>
       <c r="B224" s="17" t="inlineStr">
         <is>
-          <t>COLO @ GT</t>
+          <t>MRSH @ PSU</t>
         </is>
       </c>
       <c r="C224" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D224" s="25" t="n">
@@ -15873,34 +15873,34 @@
       </c>
       <c r="E224" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F224" s="17" t="inlineStr">
         <is>
-          <t>COLO +6.5</t>
+          <t>Over 54.5</t>
         </is>
       </c>
       <c r="G224" s="26" t="n">
-        <v>-6.5</v>
+        <v>54.5</v>
       </c>
       <c r="H224" s="18" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="I224" s="20" t="n">
-        <v>0.5359459352051367</v>
+        <v>0.5454956920521962</v>
       </c>
       <c r="J224" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5</v>
       </c>
       <c r="K224" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L224" s="19" t="n">
-        <v>0.02375081325391715</v>
+        <v>0.02168616824267233</v>
       </c>
       <c r="M224" s="19" t="n">
-        <v>0.0463706354005049</v>
+        <v>0.04140086664510184</v>
       </c>
       <c r="N224" s="20" t="n">
         <v>0</v>
@@ -15923,12 +15923,12 @@
       </c>
       <c r="B225" s="12" t="inlineStr">
         <is>
-          <t>MRSH @ PSU</t>
+          <t>MRMK @ DEL</t>
         </is>
       </c>
       <c r="C225" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D225" s="22" t="n">
@@ -15941,29 +15941,29 @@
       </c>
       <c r="F225" s="12" t="inlineStr">
         <is>
-          <t>Over 54.5</t>
+          <t>Over 55.5</t>
         </is>
       </c>
       <c r="G225" s="23" t="n">
-        <v>54.5</v>
+        <v>55.5</v>
       </c>
       <c r="H225" s="13" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I225" s="15" t="n">
-        <v>0.5454956920521962</v>
+        <v>0.5394352934246071</v>
       </c>
       <c r="J225" s="15" t="n">
-        <v>0.5</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K225" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L225" s="14" t="n">
-        <v>0.02168616824267233</v>
+        <v>0.02020452419383778</v>
       </c>
       <c r="M225" s="14" t="n">
-        <v>0.04140086664510184</v>
+        <v>0.03891241696590997</v>
       </c>
       <c r="N225" s="15" t="n">
         <v>0</v>
@@ -15976,7 +15976,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q225" s="12" t="n"/>
+      <c r="Q225" s="12" t="inlineStr">
+        <is>
+          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="17" t="inlineStr">
@@ -15986,12 +15990,12 @@
       </c>
       <c r="B226" s="17" t="inlineStr">
         <is>
-          <t>MRMK @ DEL</t>
+          <t>SEMO @ ISU</t>
         </is>
       </c>
       <c r="C226" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-05 17:00</t>
         </is>
       </c>
       <c r="D226" s="25" t="n">
@@ -16004,29 +16008,29 @@
       </c>
       <c r="F226" s="17" t="inlineStr">
         <is>
-          <t>Over 55.5</t>
+          <t>Over 53.5</t>
         </is>
       </c>
       <c r="G226" s="26" t="n">
-        <v>55.5</v>
+        <v>53.5</v>
       </c>
       <c r="H226" s="18" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="I226" s="20" t="n">
-        <v>0.5394352934246071</v>
+        <v>0.5322711249079335</v>
       </c>
       <c r="J226" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K226" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L226" s="19" t="n">
-        <v>0.02020452419383778</v>
+        <v>0.02007600295671397</v>
       </c>
       <c r="M226" s="19" t="n">
-        <v>0.03891241696590997</v>
+        <v>0.03919600577263205</v>
       </c>
       <c r="N226" s="20" t="n">
         <v>0</v>
@@ -16041,7 +16045,7 @@
       </c>
       <c r="Q226" s="17" t="inlineStr">
         <is>
-          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>SEMO isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -16053,12 +16057,12 @@
       </c>
       <c r="B227" s="12" t="inlineStr">
         <is>
-          <t>SEMO @ ISU</t>
+          <t>UCLA @ CAL</t>
         </is>
       </c>
       <c r="C227" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 17:00</t>
+          <t>2026-09-06 02:30</t>
         </is>
       </c>
       <c r="D227" s="22" t="n">
@@ -16078,22 +16082,22 @@
         <v>53.5</v>
       </c>
       <c r="H227" s="13" t="n">
-        <v>-105</v>
+        <v>-112</v>
       </c>
       <c r="I227" s="15" t="n">
-        <v>0.5322711249079335</v>
+        <v>0.5476605702507094</v>
       </c>
       <c r="J227" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K227" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L227" s="14" t="n">
-        <v>0.02007600295671397</v>
+        <v>0.01935868345825653</v>
       </c>
       <c r="M227" s="14" t="n">
-        <v>0.03919600577263205</v>
+        <v>0.03664322226027122</v>
       </c>
       <c r="N227" s="15" t="n">
         <v>0</v>
@@ -16106,11 +16110,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q227" s="12" t="inlineStr">
-        <is>
-          <t>SEMO isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q227" s="12" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="17" t="inlineStr">
@@ -16133,32 +16133,34 @@
       </c>
       <c r="E228" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F228" s="17" t="inlineStr">
         <is>
-          <t>COLO ML</t>
-        </is>
-      </c>
-      <c r="G228" s="26" t="n"/>
+          <t>COLO +6.5</t>
+        </is>
+      </c>
+      <c r="G228" s="26" t="n">
+        <v>-6.5</v>
+      </c>
       <c r="H228" s="18" t="n">
-        <v>210</v>
+        <v>-110</v>
       </c>
       <c r="I228" s="20" t="n">
-        <v>0.3419541816704439</v>
+        <v>0.5413630532983111</v>
       </c>
       <c r="J228" s="20" t="n">
-        <v>0.3092071169459319</v>
+        <v>0.5</v>
       </c>
       <c r="K228" s="20" t="n">
-        <v>0.3225806451612903</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L228" s="19" t="n">
-        <v>0.01937353650915358</v>
+        <v>0.0175535294887873</v>
       </c>
       <c r="M228" s="19" t="n">
-        <v>0.06005796317837608</v>
+        <v>0.03351128356950311</v>
       </c>
       <c r="N228" s="20" t="n">
         <v>0</v>
@@ -16181,12 +16183,12 @@
       </c>
       <c r="B229" s="12" t="inlineStr">
         <is>
-          <t>UCLA @ CAL</t>
+          <t>WYO @ CSU</t>
         </is>
       </c>
       <c r="C229" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 02:30</t>
+          <t>2026-09-05 22:00</t>
         </is>
       </c>
       <c r="D229" s="22" t="n">
@@ -16194,34 +16196,32 @@
       </c>
       <c r="E229" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F229" s="12" t="inlineStr">
         <is>
-          <t>Over 53.5</t>
-        </is>
-      </c>
-      <c r="G229" s="23" t="n">
-        <v>53.5</v>
-      </c>
+          <t>WYO ML</t>
+        </is>
+      </c>
+      <c r="G229" s="23" t="n"/>
       <c r="H229" s="13" t="n">
-        <v>-112</v>
+        <v>142</v>
       </c>
       <c r="I229" s="15" t="n">
-        <v>0.5476605702507094</v>
+        <v>0.4304310459370255</v>
       </c>
       <c r="J229" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.3962430290578221</v>
       </c>
       <c r="K229" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.4132231404958678</v>
       </c>
       <c r="L229" s="14" t="n">
-        <v>0.01935868345825653</v>
+        <v>0.01720790544115774</v>
       </c>
       <c r="M229" s="14" t="n">
-        <v>0.03664322226027122</v>
+        <v>0.04164313116760177</v>
       </c>
       <c r="N229" s="15" t="n">
         <v>0</v>
@@ -16244,12 +16244,12 @@
       </c>
       <c r="B230" s="17" t="inlineStr">
         <is>
-          <t>WYO @ CSU</t>
+          <t>SJSU @ EMU</t>
         </is>
       </c>
       <c r="C230" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 22:00</t>
+          <t>2026-09-04 22:30</t>
         </is>
       </c>
       <c r="D230" s="25" t="n">
@@ -16262,27 +16262,27 @@
       </c>
       <c r="F230" s="17" t="inlineStr">
         <is>
-          <t>WYO ML</t>
+          <t>SJSU ML</t>
         </is>
       </c>
       <c r="G230" s="26" t="n"/>
       <c r="H230" s="18" t="n">
-        <v>142</v>
+        <v>180</v>
       </c>
       <c r="I230" s="20" t="n">
-        <v>0.4304310459370255</v>
+        <v>0.3741599606283899</v>
       </c>
       <c r="J230" s="20" t="n">
-        <v>0.3962430290578221</v>
+        <v>0.3425247738043947</v>
       </c>
       <c r="K230" s="20" t="n">
-        <v>0.4132231404958678</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="L230" s="19" t="n">
-        <v>0.01720790544115774</v>
+        <v>0.0170171034855327</v>
       </c>
       <c r="M230" s="19" t="n">
-        <v>0.04164313116760177</v>
+        <v>0.04764788975949152</v>
       </c>
       <c r="N230" s="20" t="n">
         <v>0</v>
@@ -16305,12 +16305,12 @@
       </c>
       <c r="B231" s="12" t="inlineStr">
         <is>
-          <t>SJSU @ EMU</t>
+          <t>WSU @ WASH</t>
         </is>
       </c>
       <c r="C231" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 22:30</t>
+          <t>2026-09-06 20:00</t>
         </is>
       </c>
       <c r="D231" s="22" t="n">
@@ -16318,32 +16318,34 @@
       </c>
       <c r="E231" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F231" s="12" t="inlineStr">
         <is>
-          <t>SJSU ML</t>
-        </is>
-      </c>
-      <c r="G231" s="23" t="n"/>
+          <t>Over 50.5</t>
+        </is>
+      </c>
+      <c r="G231" s="23" t="n">
+        <v>50.5</v>
+      </c>
       <c r="H231" s="13" t="n">
-        <v>180</v>
+        <v>-110</v>
       </c>
       <c r="I231" s="15" t="n">
-        <v>0.3741599606283899</v>
+        <v>0.5376882571623026</v>
       </c>
       <c r="J231" s="15" t="n">
-        <v>0.3425247738043947</v>
+        <v>0.5</v>
       </c>
       <c r="K231" s="15" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L231" s="14" t="n">
-        <v>0.0170171034855327</v>
+        <v>0.01387873335277878</v>
       </c>
       <c r="M231" s="14" t="n">
-        <v>0.04764788975949152</v>
+        <v>0.02649576367348688</v>
       </c>
       <c r="N231" s="15" t="n">
         <v>0</v>
@@ -16366,12 +16368,12 @@
       </c>
       <c r="B232" s="17" t="inlineStr">
         <is>
-          <t>WSU @ WASH</t>
+          <t>WKU @ NEV</t>
         </is>
       </c>
       <c r="C232" s="17" t="inlineStr">
         <is>
-          <t>2026-09-06 20:00</t>
+          <t>2026-09-06 02:30</t>
         </is>
       </c>
       <c r="D232" s="25" t="n">
@@ -16379,34 +16381,34 @@
       </c>
       <c r="E232" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F232" s="17" t="inlineStr">
         <is>
-          <t>Over 50.5</t>
+          <t>NEV +2.5</t>
         </is>
       </c>
       <c r="G232" s="26" t="n">
-        <v>50.5</v>
+        <v>2.5</v>
       </c>
       <c r="H232" s="18" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I232" s="20" t="n">
-        <v>0.5376882571623026</v>
+        <v>0.5326677557018351</v>
       </c>
       <c r="J232" s="20" t="n">
-        <v>0.5</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K232" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L232" s="19" t="n">
-        <v>0.01387873335277878</v>
+        <v>0.01343698647106584</v>
       </c>
       <c r="M232" s="19" t="n">
-        <v>0.02649576367348688</v>
+        <v>0.02587864061094175</v>
       </c>
       <c r="N232" s="20" t="n">
         <v>0</v>
@@ -16429,12 +16431,12 @@
       </c>
       <c r="B233" s="12" t="inlineStr">
         <is>
-          <t>WKU @ NEV</t>
+          <t>SJSU @ EMU</t>
         </is>
       </c>
       <c r="C233" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 02:30</t>
+          <t>2026-09-04 22:30</t>
         </is>
       </c>
       <c r="D233" s="22" t="n">
@@ -16447,29 +16449,29 @@
       </c>
       <c r="F233" s="12" t="inlineStr">
         <is>
-          <t>NEV +2.5</t>
+          <t>SJSU +4.5</t>
         </is>
       </c>
       <c r="G233" s="23" t="n">
-        <v>2.5</v>
+        <v>-4.5</v>
       </c>
       <c r="H233" s="13" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="I233" s="15" t="n">
-        <v>0.5326677557018351</v>
+        <v>0.5253691652874209</v>
       </c>
       <c r="J233" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K233" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L233" s="14" t="n">
-        <v>0.01343698647106584</v>
+        <v>0.01317404333620142</v>
       </c>
       <c r="M233" s="14" t="n">
-        <v>0.02587864061094175</v>
+        <v>0.02572075127544082</v>
       </c>
       <c r="N233" s="15" t="n">
         <v>0</v>
@@ -16492,12 +16494,12 @@
       </c>
       <c r="B234" s="17" t="inlineStr">
         <is>
-          <t>SJSU @ EMU</t>
+          <t>JVST @ NDSU</t>
         </is>
       </c>
       <c r="C234" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 22:30</t>
+          <t>2026-08-29 21:30</t>
         </is>
       </c>
       <c r="D234" s="25" t="n">
@@ -16510,17 +16512,17 @@
       </c>
       <c r="F234" s="17" t="inlineStr">
         <is>
-          <t>SJSU +4.5</t>
+          <t>JVST +6.5</t>
         </is>
       </c>
       <c r="G234" s="26" t="n">
-        <v>-4.5</v>
+        <v>-6.5</v>
       </c>
       <c r="H234" s="18" t="n">
         <v>-105</v>
       </c>
       <c r="I234" s="20" t="n">
-        <v>0.5253691652874209</v>
+        <v>0.5242758558005725</v>
       </c>
       <c r="J234" s="20" t="n">
         <v>0.4891657638136511</v>
@@ -16529,10 +16531,10 @@
         <v>0.5121951219512195</v>
       </c>
       <c r="L234" s="19" t="n">
-        <v>0.01317404333620142</v>
+        <v>0.01208073384935293</v>
       </c>
       <c r="M234" s="19" t="n">
-        <v>0.02572075127544082</v>
+        <v>0.02358619465826051</v>
       </c>
       <c r="N234" s="20" t="n">
         <v>0</v>
@@ -16555,12 +16557,12 @@
       </c>
       <c r="B235" s="12" t="inlineStr">
         <is>
-          <t>JVST @ NDSU</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C235" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D235" s="22" t="n">
@@ -16568,34 +16570,32 @@
       </c>
       <c r="E235" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F235" s="12" t="inlineStr">
         <is>
-          <t>JVST +6.5</t>
-        </is>
-      </c>
-      <c r="G235" s="23" t="n">
-        <v>-6.5</v>
-      </c>
+          <t>MEM ML</t>
+        </is>
+      </c>
+      <c r="G235" s="23" t="n"/>
       <c r="H235" s="13" t="n">
-        <v>-105</v>
+        <v>160</v>
       </c>
       <c r="I235" s="15" t="n">
-        <v>0.5242758558005725</v>
+        <v>0.396303332895533</v>
       </c>
       <c r="J235" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.3690596562184025</v>
       </c>
       <c r="K235" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="L235" s="14" t="n">
-        <v>0.01208073384935293</v>
+        <v>0.01168794828014835</v>
       </c>
       <c r="M235" s="14" t="n">
-        <v>0.02358619465826051</v>
+        <v>0.03038866552838582</v>
       </c>
       <c r="N235" s="15" t="n">
         <v>0</v>
@@ -16618,12 +16618,12 @@
       </c>
       <c r="B236" s="17" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>JVST @ NDSU</t>
         </is>
       </c>
       <c r="C236" s="17" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-08-29 21:30</t>
         </is>
       </c>
       <c r="D236" s="25" t="n">
@@ -16636,27 +16636,27 @@
       </c>
       <c r="F236" s="17" t="inlineStr">
         <is>
-          <t>MEM ML</t>
+          <t>JVST ML</t>
         </is>
       </c>
       <c r="G236" s="26" t="n"/>
       <c r="H236" s="18" t="n">
-        <v>160</v>
+        <v>215</v>
       </c>
       <c r="I236" s="20" t="n">
-        <v>0.396303332895533</v>
+        <v>0.3283150740711329</v>
       </c>
       <c r="J236" s="20" t="n">
-        <v>0.3690596562184025</v>
+        <v>0.3042300479266514</v>
       </c>
       <c r="K236" s="20" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.3174603174603174</v>
       </c>
       <c r="L236" s="19" t="n">
-        <v>0.01168794828014835</v>
+        <v>0.01085475661081547</v>
       </c>
       <c r="M236" s="19" t="n">
-        <v>0.03038866552838582</v>
+        <v>0.03419248332406866</v>
       </c>
       <c r="N236" s="20" t="n">
         <v>0</v>
@@ -16679,12 +16679,12 @@
       </c>
       <c r="B237" s="12" t="inlineStr">
         <is>
-          <t>JVST @ NDSU</t>
+          <t>COLO @ GT</t>
         </is>
       </c>
       <c r="C237" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D237" s="22" t="n">
@@ -16697,27 +16697,27 @@
       </c>
       <c r="F237" s="12" t="inlineStr">
         <is>
-          <t>JVST ML</t>
+          <t>COLO ML</t>
         </is>
       </c>
       <c r="G237" s="23" t="n"/>
       <c r="H237" s="13" t="n">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="I237" s="15" t="n">
-        <v>0.3283150740711329</v>
+        <v>0.3498349996997374</v>
       </c>
       <c r="J237" s="15" t="n">
-        <v>0.3042300479266514</v>
+        <v>0.3249687530045188</v>
       </c>
       <c r="K237" s="15" t="n">
-        <v>0.3174603174603174</v>
+        <v>0.3389830508474576</v>
       </c>
       <c r="L237" s="14" t="n">
-        <v>0.01085475661081547</v>
+        <v>0.0108519488522798</v>
       </c>
       <c r="M237" s="14" t="n">
-        <v>0.03419248332406866</v>
+        <v>0.03201324911422543</v>
       </c>
       <c r="N237" s="15" t="n">
         <v>0</v>
@@ -21386,12 +21386,12 @@
       </c>
       <c r="B310" s="17" t="inlineStr">
         <is>
-          <t>IDHO @ UTAH</t>
+          <t>COLO @ GT</t>
         </is>
       </c>
       <c r="C310" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 01:00</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D310" s="25" t="n">
@@ -21399,34 +21399,32 @@
       </c>
       <c r="E310" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F310" s="17" t="inlineStr">
         <is>
-          <t>Under 56.5</t>
-        </is>
-      </c>
-      <c r="G310" s="26" t="n">
-        <v>56.5</v>
-      </c>
+          <t>GT ML</t>
+        </is>
+      </c>
+      <c r="G310" s="26" t="n"/>
       <c r="H310" s="18" t="n">
-        <v>-112</v>
+        <v>-238</v>
       </c>
       <c r="I310" s="20" t="n">
-        <v>0.4743183415456649</v>
+        <v>0.6501650003002626</v>
       </c>
       <c r="J310" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.6750312469954812</v>
       </c>
       <c r="K310" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.7041420118343196</v>
       </c>
       <c r="L310" s="19" t="n">
-        <v>-0.05398354524678795</v>
+        <v>-0.05397701153405698</v>
       </c>
       <c r="M310" s="19" t="n">
-        <v>-0.1021831392171343</v>
+        <v>-0.07665642814500517</v>
       </c>
       <c r="N310" s="20" t="n">
         <v>0</v>
@@ -21439,11 +21437,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q310" s="17" t="inlineStr">
-        <is>
-          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q310" s="17" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="12" t="inlineStr">
@@ -21453,12 +21447,12 @@
       </c>
       <c r="B311" s="12" t="inlineStr">
         <is>
-          <t>JVST @ NDSU</t>
+          <t>IDHO @ UTAH</t>
         </is>
       </c>
       <c r="C311" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D311" s="22" t="n">
@@ -21466,32 +21460,34 @@
       </c>
       <c r="E311" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F311" s="12" t="inlineStr">
         <is>
-          <t>NDSU ML</t>
-        </is>
-      </c>
-      <c r="G311" s="23" t="n"/>
+          <t>Under 56.5</t>
+        </is>
+      </c>
+      <c r="G311" s="23" t="n">
+        <v>56.5</v>
+      </c>
       <c r="H311" s="13" t="n">
-        <v>-265</v>
+        <v>-112</v>
       </c>
       <c r="I311" s="15" t="n">
-        <v>0.6716849259288671</v>
+        <v>0.4743183415456649</v>
       </c>
       <c r="J311" s="15" t="n">
-        <v>0.6957699520733487</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K311" s="15" t="n">
-        <v>0.726027397260274</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L311" s="14" t="n">
-        <v>-0.05434247133140691</v>
+        <v>-0.05398354524678795</v>
       </c>
       <c r="M311" s="14" t="n">
-        <v>-0.07484906428665483</v>
+        <v>-0.1021831392171343</v>
       </c>
       <c r="N311" s="15" t="n">
         <v>0</v>
@@ -21504,7 +21500,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q311" s="12" t="n"/>
+      <c r="Q311" s="12" t="inlineStr">
+        <is>
+          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="17" t="inlineStr">
@@ -21514,12 +21514,12 @@
       </c>
       <c r="B312" s="17" t="inlineStr">
         <is>
-          <t>WYO @ CSU</t>
+          <t>JVST @ NDSU</t>
         </is>
       </c>
       <c r="C312" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 22:00</t>
+          <t>2026-08-29 21:30</t>
         </is>
       </c>
       <c r="D312" s="25" t="n">
@@ -21527,34 +21527,32 @@
       </c>
       <c r="E312" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F312" s="17" t="inlineStr">
         <is>
-          <t>CSU -3.5</t>
-        </is>
-      </c>
-      <c r="G312" s="26" t="n">
-        <v>-3.5</v>
-      </c>
+          <t>NDSU ML</t>
+        </is>
+      </c>
+      <c r="G312" s="26" t="n"/>
       <c r="H312" s="18" t="n">
-        <v>100</v>
+        <v>-265</v>
       </c>
       <c r="I312" s="20" t="n">
-        <v>0.4445970995073426</v>
+        <v>0.6716849259288671</v>
       </c>
       <c r="J312" s="20" t="n">
-        <v>0.4782608695652174</v>
+        <v>0.6957699520733487</v>
       </c>
       <c r="K312" s="20" t="n">
-        <v>0.5</v>
+        <v>0.726027397260274</v>
       </c>
       <c r="L312" s="19" t="n">
-        <v>-0.05540290049265745</v>
+        <v>-0.05434247133140691</v>
       </c>
       <c r="M312" s="19" t="n">
-        <v>-0.110805800985315</v>
+        <v>-0.07484906428665483</v>
       </c>
       <c r="N312" s="20" t="n">
         <v>0</v>
@@ -21577,12 +21575,12 @@
       </c>
       <c r="B313" s="12" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>WYO @ CSU</t>
         </is>
       </c>
       <c r="C313" s="12" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-09-05 22:00</t>
         </is>
       </c>
       <c r="D313" s="22" t="n">
@@ -21590,34 +21588,34 @@
       </c>
       <c r="E313" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F313" s="12" t="inlineStr">
         <is>
-          <t>Under 56.5</t>
+          <t>CSU -3.5</t>
         </is>
       </c>
       <c r="G313" s="23" t="n">
-        <v>56.5</v>
+        <v>-3.5</v>
       </c>
       <c r="H313" s="13" t="n">
-        <v>-112</v>
+        <v>100</v>
       </c>
       <c r="I313" s="15" t="n">
-        <v>0.4723436919734165</v>
+        <v>0.4445970995073426</v>
       </c>
       <c r="J313" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="K313" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5</v>
       </c>
       <c r="L313" s="14" t="n">
-        <v>-0.0559581948190363</v>
+        <v>-0.05540290049265745</v>
       </c>
       <c r="M313" s="14" t="n">
-        <v>-0.1059208687646045</v>
+        <v>-0.110805800985315</v>
       </c>
       <c r="N313" s="15" t="n">
         <v>0</v>
@@ -21640,12 +21638,12 @@
       </c>
       <c r="B314" s="17" t="inlineStr">
         <is>
-          <t>UNH @ SYR</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C314" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D314" s="25" t="n">
@@ -21658,17 +21656,17 @@
       </c>
       <c r="F314" s="17" t="inlineStr">
         <is>
-          <t>Under 55.5</t>
+          <t>Under 56.5</t>
         </is>
       </c>
       <c r="G314" s="26" t="n">
-        <v>55.5</v>
+        <v>56.5</v>
       </c>
       <c r="H314" s="18" t="n">
         <v>-112</v>
       </c>
       <c r="I314" s="20" t="n">
-        <v>0.472343691420072</v>
+        <v>0.4723436919734165</v>
       </c>
       <c r="J314" s="20" t="n">
         <v>0.5043297540699688</v>
@@ -21677,10 +21675,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L314" s="19" t="n">
-        <v>-0.05595819537238078</v>
+        <v>-0.0559581948190363</v>
       </c>
       <c r="M314" s="19" t="n">
-        <v>-0.1059208698120065</v>
+        <v>-0.1059208687646045</v>
       </c>
       <c r="N314" s="20" t="n">
         <v>0</v>
@@ -21693,11 +21691,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q314" s="17" t="inlineStr">
-        <is>
-          <t>UNH isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q314" s="17" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="12" t="inlineStr">
@@ -21707,12 +21701,12 @@
       </c>
       <c r="B315" s="12" t="inlineStr">
         <is>
-          <t>MVSU @ SAC</t>
+          <t>UNH @ SYR</t>
         </is>
       </c>
       <c r="C315" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 02:00</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D315" s="22" t="n">
@@ -21725,35 +21719,35 @@
       </c>
       <c r="F315" s="12" t="inlineStr">
         <is>
-          <t>Under 56.5</t>
+          <t>Under 55.5</t>
         </is>
       </c>
       <c r="G315" s="23" t="n">
-        <v>56.5</v>
+        <v>55.5</v>
       </c>
       <c r="H315" s="13" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I315" s="15" t="n">
-        <v>0.4621085317490612</v>
+        <v>0.472343691420072</v>
       </c>
       <c r="J315" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K315" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L315" s="14" t="n">
-        <v>-0.05712223748170808</v>
+        <v>-0.05595819537238078</v>
       </c>
       <c r="M315" s="14" t="n">
-        <v>-0.1100131981129192</v>
+        <v>-0.1059208698120065</v>
       </c>
       <c r="N315" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O315" s="24" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="P315" s="12" t="inlineStr">
         <is>
@@ -21762,7 +21756,7 @@
       </c>
       <c r="Q315" s="12" t="inlineStr">
         <is>
-          <t>MVSU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>UNH isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -21774,12 +21768,12 @@
       </c>
       <c r="B316" s="17" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>MVSU @ SAC</t>
         </is>
       </c>
       <c r="C316" s="17" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-09-06 02:00</t>
         </is>
       </c>
       <c r="D316" s="25" t="n">
@@ -21787,47 +21781,51 @@
       </c>
       <c r="E316" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F316" s="17" t="inlineStr">
         <is>
-          <t>UNLV -4.5</t>
+          <t>Under 56.5</t>
         </is>
       </c>
       <c r="G316" s="26" t="n">
-        <v>-4.5</v>
+        <v>56.5</v>
       </c>
       <c r="H316" s="18" t="n">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="I316" s="20" t="n">
-        <v>0.4548748683320663</v>
+        <v>0.4621085317490612</v>
       </c>
       <c r="J316" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K316" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L316" s="19" t="n">
-        <v>-0.05732025361915327</v>
+        <v>-0.05712223748170808</v>
       </c>
       <c r="M316" s="19" t="n">
-        <v>-0.1119109713516802</v>
+        <v>-0.1100131981129192</v>
       </c>
       <c r="N316" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O316" s="27" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="P316" s="17" t="inlineStr">
         <is>
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q316" s="17" t="n"/>
+      <c r="Q316" s="17" t="inlineStr">
+        <is>
+          <t>MVSU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="12" t="inlineStr">
@@ -21837,12 +21835,12 @@
       </c>
       <c r="B317" s="12" t="inlineStr">
         <is>
-          <t>BRY @ ARMY</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C317" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D317" s="22" t="n">
@@ -21850,34 +21848,34 @@
       </c>
       <c r="E317" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F317" s="12" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>UNLV -4.5</t>
         </is>
       </c>
       <c r="G317" s="23" t="n">
-        <v>51.5</v>
+        <v>-4.5</v>
       </c>
       <c r="H317" s="13" t="n">
-        <v>-112</v>
+        <v>-105</v>
       </c>
       <c r="I317" s="15" t="n">
-        <v>0.4703719936573756</v>
+        <v>0.4548748683320663</v>
       </c>
       <c r="J317" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K317" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L317" s="14" t="n">
-        <v>-0.05792989313507724</v>
+        <v>-0.05732025361915327</v>
       </c>
       <c r="M317" s="14" t="n">
-        <v>-0.1096530120056819</v>
+        <v>-0.1119109713516802</v>
       </c>
       <c r="N317" s="15" t="n">
         <v>0</v>
@@ -21890,11 +21888,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q317" s="12" t="inlineStr">
-        <is>
-          <t>BRY isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q317" s="12" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="17" t="inlineStr">
@@ -21904,12 +21898,12 @@
       </c>
       <c r="B318" s="17" t="inlineStr">
         <is>
-          <t>JVST @ NDSU</t>
+          <t>BRY @ ARMY</t>
         </is>
       </c>
       <c r="C318" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D318" s="25" t="n">
@@ -21917,34 +21911,34 @@
       </c>
       <c r="E318" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F318" s="17" t="inlineStr">
         <is>
-          <t>NDSU -6.5</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="G318" s="26" t="n">
-        <v>-6.5</v>
+        <v>51.5</v>
       </c>
       <c r="H318" s="18" t="n">
-        <v>-115</v>
+        <v>-112</v>
       </c>
       <c r="I318" s="20" t="n">
-        <v>0.4757241441994276</v>
+        <v>0.4703719936573756</v>
       </c>
       <c r="J318" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K318" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L318" s="19" t="n">
-        <v>-0.05915957673080491</v>
+        <v>-0.05792989313507724</v>
       </c>
       <c r="M318" s="19" t="n">
-        <v>-0.110602686931505</v>
+        <v>-0.1096530120056819</v>
       </c>
       <c r="N318" s="20" t="n">
         <v>0</v>
@@ -21957,7 +21951,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q318" s="17" t="n"/>
+      <c r="Q318" s="17" t="inlineStr">
+        <is>
+          <t>BRY isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="12" t="inlineStr">
@@ -21967,12 +21965,12 @@
       </c>
       <c r="B319" s="12" t="inlineStr">
         <is>
-          <t>SJSU @ EMU</t>
+          <t>JVST @ NDSU</t>
         </is>
       </c>
       <c r="C319" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 22:30</t>
+          <t>2026-08-29 21:30</t>
         </is>
       </c>
       <c r="D319" s="22" t="n">
@@ -21980,32 +21978,34 @@
       </c>
       <c r="E319" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F319" s="12" t="inlineStr">
         <is>
-          <t>EMU ML</t>
-        </is>
-      </c>
-      <c r="G319" s="23" t="n"/>
+          <t>NDSU -6.5</t>
+        </is>
+      </c>
+      <c r="G319" s="23" t="n">
+        <v>-6.5</v>
+      </c>
       <c r="H319" s="13" t="n">
-        <v>-218</v>
+        <v>-115</v>
       </c>
       <c r="I319" s="15" t="n">
-        <v>0.6258400393716101</v>
+        <v>0.4757241441994276</v>
       </c>
       <c r="J319" s="15" t="n">
-        <v>0.6574752261956054</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K319" s="15" t="n">
-        <v>0.6855345911949685</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L319" s="14" t="n">
-        <v>-0.05969455182335837</v>
+        <v>-0.05915957673080491</v>
       </c>
       <c r="M319" s="14" t="n">
-        <v>-0.08707737376067881</v>
+        <v>-0.110602686931505</v>
       </c>
       <c r="N319" s="15" t="n">
         <v>0</v>
@@ -22028,12 +22028,12 @@
       </c>
       <c r="B320" s="17" t="inlineStr">
         <is>
-          <t>WYO @ CSU</t>
+          <t>SJSU @ EMU</t>
         </is>
       </c>
       <c r="C320" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 22:00</t>
+          <t>2026-09-04 22:30</t>
         </is>
       </c>
       <c r="D320" s="25" t="n">
@@ -22046,27 +22046,27 @@
       </c>
       <c r="F320" s="17" t="inlineStr">
         <is>
-          <t>CSU ML</t>
+          <t>EMU ML</t>
         </is>
       </c>
       <c r="G320" s="26" t="n"/>
       <c r="H320" s="18" t="n">
-        <v>-170</v>
+        <v>-218</v>
       </c>
       <c r="I320" s="20" t="n">
-        <v>0.5695689540629745</v>
+        <v>0.6258400393716101</v>
       </c>
       <c r="J320" s="20" t="n">
-        <v>0.6037569709421778</v>
+        <v>0.6574752261956054</v>
       </c>
       <c r="K320" s="20" t="n">
-        <v>0.6296296296296297</v>
+        <v>0.6855345911949685</v>
       </c>
       <c r="L320" s="19" t="n">
-        <v>-0.06006067556665518</v>
+        <v>-0.05969455182335837</v>
       </c>
       <c r="M320" s="19" t="n">
-        <v>-0.09539048472351103</v>
+        <v>-0.08707737376067881</v>
       </c>
       <c r="N320" s="20" t="n">
         <v>0</v>
@@ -22089,12 +22089,12 @@
       </c>
       <c r="B321" s="12" t="inlineStr">
         <is>
-          <t>SJSU @ EMU</t>
+          <t>WYO @ CSU</t>
         </is>
       </c>
       <c r="C321" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 22:30</t>
+          <t>2026-09-05 22:00</t>
         </is>
       </c>
       <c r="D321" s="22" t="n">
@@ -22102,34 +22102,32 @@
       </c>
       <c r="E321" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F321" s="12" t="inlineStr">
         <is>
-          <t>EMU -4.5</t>
-        </is>
-      </c>
-      <c r="G321" s="23" t="n">
-        <v>-4.5</v>
-      </c>
+          <t>CSU ML</t>
+        </is>
+      </c>
+      <c r="G321" s="23" t="n"/>
       <c r="H321" s="13" t="n">
-        <v>-115</v>
+        <v>-170</v>
       </c>
       <c r="I321" s="15" t="n">
-        <v>0.4746308347125791</v>
+        <v>0.5695689540629745</v>
       </c>
       <c r="J321" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.6037569709421778</v>
       </c>
       <c r="K321" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.6296296296296297</v>
       </c>
       <c r="L321" s="14" t="n">
-        <v>-0.06025288621765346</v>
+        <v>-0.06006067556665518</v>
       </c>
       <c r="M321" s="14" t="n">
-        <v>-0.112646700319961</v>
+        <v>-0.09539048472351103</v>
       </c>
       <c r="N321" s="15" t="n">
         <v>0</v>
@@ -22152,12 +22150,12 @@
       </c>
       <c r="B322" s="17" t="inlineStr">
         <is>
-          <t>WKU @ NEV</t>
+          <t>SJSU @ EMU</t>
         </is>
       </c>
       <c r="C322" s="17" t="inlineStr">
         <is>
-          <t>2026-09-06 02:30</t>
+          <t>2026-09-04 22:30</t>
         </is>
       </c>
       <c r="D322" s="25" t="n">
@@ -22170,29 +22168,29 @@
       </c>
       <c r="F322" s="17" t="inlineStr">
         <is>
-          <t>WKU -2.5</t>
+          <t>EMU -4.5</t>
         </is>
       </c>
       <c r="G322" s="26" t="n">
-        <v>2.5</v>
+        <v>-4.5</v>
       </c>
       <c r="H322" s="18" t="n">
-        <v>-112</v>
+        <v>-115</v>
       </c>
       <c r="I322" s="20" t="n">
-        <v>0.4673322442981649</v>
+        <v>0.4746308347125791</v>
       </c>
       <c r="J322" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K322" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L322" s="19" t="n">
-        <v>-0.06096964249428793</v>
+        <v>-0.06025288621765346</v>
       </c>
       <c r="M322" s="19" t="n">
-        <v>-0.1154068232927594</v>
+        <v>-0.112646700319961</v>
       </c>
       <c r="N322" s="20" t="n">
         <v>0</v>
@@ -22215,12 +22213,12 @@
       </c>
       <c r="B323" s="12" t="inlineStr">
         <is>
-          <t>WSU @ WASH</t>
+          <t>WKU @ NEV</t>
         </is>
       </c>
       <c r="C323" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 20:00</t>
+          <t>2026-09-06 02:30</t>
         </is>
       </c>
       <c r="D323" s="22" t="n">
@@ -22228,34 +22226,34 @@
       </c>
       <c r="E323" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F323" s="12" t="inlineStr">
         <is>
-          <t>Under 50.5</t>
+          <t>WKU -2.5</t>
         </is>
       </c>
       <c r="G323" s="23" t="n">
-        <v>50.5</v>
+        <v>2.5</v>
       </c>
       <c r="H323" s="13" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="I323" s="15" t="n">
-        <v>0.4623117428376974</v>
+        <v>0.4673322442981649</v>
       </c>
       <c r="J323" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K323" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L323" s="14" t="n">
-        <v>-0.06149778097182645</v>
+        <v>-0.06096964249428793</v>
       </c>
       <c r="M323" s="14" t="n">
-        <v>-0.1174048545825777</v>
+        <v>-0.1154068232927594</v>
       </c>
       <c r="N323" s="15" t="n">
         <v>0</v>
@@ -22278,12 +22276,12 @@
       </c>
       <c r="B324" s="17" t="inlineStr">
         <is>
-          <t>COLO @ GT</t>
+          <t>WSU @ WASH</t>
         </is>
       </c>
       <c r="C324" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-09-06 20:00</t>
         </is>
       </c>
       <c r="D324" s="25" t="n">
@@ -22291,32 +22289,34 @@
       </c>
       <c r="E324" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F324" s="17" t="inlineStr">
         <is>
-          <t>GT ML</t>
-        </is>
-      </c>
-      <c r="G324" s="26" t="n"/>
+          <t>Under 50.5</t>
+        </is>
+      </c>
+      <c r="G324" s="26" t="n">
+        <v>50.5</v>
+      </c>
       <c r="H324" s="18" t="n">
-        <v>-258</v>
+        <v>-110</v>
       </c>
       <c r="I324" s="20" t="n">
-        <v>0.6580458183295561</v>
+        <v>0.4623117428376974</v>
       </c>
       <c r="J324" s="20" t="n">
-        <v>0.6907928830540681</v>
+        <v>0.5</v>
       </c>
       <c r="K324" s="20" t="n">
-        <v>0.7206703910614525</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L324" s="19" t="n">
-        <v>-0.06262457273189637</v>
+        <v>-0.06149778097182645</v>
       </c>
       <c r="M324" s="19" t="n">
-        <v>-0.08689766293805778</v>
+        <v>-0.1174048545825777</v>
       </c>
       <c r="N324" s="20" t="n">
         <v>0</v>
@@ -22339,12 +22339,12 @@
       </c>
       <c r="B325" s="12" t="inlineStr">
         <is>
-          <t>UCLA @ CAL</t>
+          <t>COLO @ GT</t>
         </is>
       </c>
       <c r="C325" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 02:30</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D325" s="22" t="n">
@@ -22352,34 +22352,34 @@
       </c>
       <c r="E325" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F325" s="12" t="inlineStr">
         <is>
-          <t>Under 53.5</t>
+          <t>GT -6.5</t>
         </is>
       </c>
       <c r="G325" s="23" t="n">
-        <v>53.5</v>
+        <v>-6.5</v>
       </c>
       <c r="H325" s="13" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I325" s="15" t="n">
-        <v>0.4523394297492906</v>
+        <v>0.4586369467016889</v>
       </c>
       <c r="J325" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5</v>
       </c>
       <c r="K325" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L325" s="14" t="n">
-        <v>-0.06689133948147863</v>
+        <v>-0.06517257710783497</v>
       </c>
       <c r="M325" s="14" t="n">
-        <v>-0.128827764927292</v>
+        <v>-0.1244203744785939</v>
       </c>
       <c r="N325" s="15" t="n">
         <v>0</v>
@@ -22402,12 +22402,12 @@
       </c>
       <c r="B326" s="17" t="inlineStr">
         <is>
-          <t>SEMO @ ISU</t>
+          <t>UCLA @ CAL</t>
         </is>
       </c>
       <c r="C326" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 17:00</t>
+          <t>2026-09-06 02:30</t>
         </is>
       </c>
       <c r="D326" s="25" t="n">
@@ -22427,22 +22427,22 @@
         <v>53.5</v>
       </c>
       <c r="H326" s="18" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="I326" s="20" t="n">
-        <v>0.4677288750920665</v>
+        <v>0.4523394297492906</v>
       </c>
       <c r="J326" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K326" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L326" s="19" t="n">
-        <v>-0.067154845838166</v>
+        <v>-0.06689133948147863</v>
       </c>
       <c r="M326" s="19" t="n">
-        <v>-0.1255503639583105</v>
+        <v>-0.128827764927292</v>
       </c>
       <c r="N326" s="20" t="n">
         <v>0</v>
@@ -22455,11 +22455,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q326" s="17" t="inlineStr">
-        <is>
-          <t>SEMO isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q326" s="17" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="12" t="inlineStr">
@@ -22469,12 +22465,12 @@
       </c>
       <c r="B327" s="12" t="inlineStr">
         <is>
-          <t>MRMK @ DEL</t>
+          <t>SEMO @ ISU</t>
         </is>
       </c>
       <c r="C327" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-05 17:00</t>
         </is>
       </c>
       <c r="D327" s="22" t="n">
@@ -22487,29 +22483,29 @@
       </c>
       <c r="F327" s="12" t="inlineStr">
         <is>
-          <t>Under 55.5</t>
+          <t>Under 53.5</t>
         </is>
       </c>
       <c r="G327" s="23" t="n">
-        <v>55.5</v>
+        <v>53.5</v>
       </c>
       <c r="H327" s="13" t="n">
-        <v>-112</v>
+        <v>-115</v>
       </c>
       <c r="I327" s="15" t="n">
-        <v>0.4605647065753929</v>
+        <v>0.4677288750920665</v>
       </c>
       <c r="J327" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K327" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L327" s="14" t="n">
-        <v>-0.06773718021705988</v>
+        <v>-0.067154845838166</v>
       </c>
       <c r="M327" s="14" t="n">
-        <v>-0.1282168054108634</v>
+        <v>-0.1255503639583105</v>
       </c>
       <c r="N327" s="15" t="n">
         <v>0</v>
@@ -22524,7 +22520,7 @@
       </c>
       <c r="Q327" s="12" t="inlineStr">
         <is>
-          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>SEMO isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -22536,12 +22532,12 @@
       </c>
       <c r="B328" s="17" t="inlineStr">
         <is>
-          <t>MRSH @ PSU</t>
+          <t>MRMK @ DEL</t>
         </is>
       </c>
       <c r="C328" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D328" s="25" t="n">
@@ -22554,29 +22550,29 @@
       </c>
       <c r="F328" s="17" t="inlineStr">
         <is>
-          <t>Under 54.5</t>
+          <t>Under 55.5</t>
         </is>
       </c>
       <c r="G328" s="26" t="n">
-        <v>54.5</v>
+        <v>55.5</v>
       </c>
       <c r="H328" s="18" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="I328" s="20" t="n">
-        <v>0.4545043079478038</v>
+        <v>0.4605647065753929</v>
       </c>
       <c r="J328" s="20" t="n">
-        <v>0.5</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K328" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L328" s="19" t="n">
-        <v>-0.06930521586172</v>
+        <v>-0.06773718021705988</v>
       </c>
       <c r="M328" s="19" t="n">
-        <v>-0.1323099575541927</v>
+        <v>-0.1282168054108634</v>
       </c>
       <c r="N328" s="20" t="n">
         <v>0</v>
@@ -22589,7 +22585,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q328" s="17" t="n"/>
+      <c r="Q328" s="17" t="inlineStr">
+        <is>
+          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="12" t="inlineStr">
@@ -22599,12 +22599,12 @@
       </c>
       <c r="B329" s="12" t="inlineStr">
         <is>
-          <t>COLO @ GT</t>
+          <t>MRSH @ PSU</t>
         </is>
       </c>
       <c r="C329" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D329" s="22" t="n">
@@ -22612,34 +22612,34 @@
       </c>
       <c r="E329" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F329" s="12" t="inlineStr">
         <is>
-          <t>GT -6.5</t>
+          <t>Under 54.5</t>
         </is>
       </c>
       <c r="G329" s="23" t="n">
-        <v>-6.5</v>
+        <v>54.5</v>
       </c>
       <c r="H329" s="13" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="I329" s="15" t="n">
-        <v>0.4640540647948633</v>
+        <v>0.4545043079478038</v>
       </c>
       <c r="J329" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5</v>
       </c>
       <c r="K329" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L329" s="14" t="n">
-        <v>-0.07082965613536918</v>
+        <v>-0.06930521586172</v>
       </c>
       <c r="M329" s="14" t="n">
-        <v>-0.132420661470473</v>
+        <v>-0.1323099575541927</v>
       </c>
       <c r="N329" s="15" t="n">
         <v>0</v>
@@ -24226,29 +24226,29 @@
       </c>
       <c r="F354" s="17" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>Under 50.5</t>
         </is>
       </c>
       <c r="G354" s="26" t="n">
-        <v>51.5</v>
+        <v>50.5</v>
       </c>
       <c r="H354" s="18" t="n">
-        <v>-118</v>
+        <v>-102</v>
       </c>
       <c r="I354" s="20" t="n">
-        <v>0.449702488976135</v>
+        <v>0.4135763455623289</v>
       </c>
       <c r="J354" s="20" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.4826358742837298</v>
       </c>
       <c r="K354" s="20" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.504950495049505</v>
       </c>
       <c r="L354" s="19" t="n">
-        <v>-0.09158191469358978</v>
+        <v>-0.09137414948717604</v>
       </c>
       <c r="M354" s="19" t="n">
-        <v>-0.1691937068068015</v>
+        <v>-0.1809566489844074</v>
       </c>
       <c r="N354" s="20" t="n">
         <v>0</v>
@@ -24962,12 +24962,12 @@
       </c>
       <c r="B366" s="17" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>UNLV @ HAW</t>
         </is>
       </c>
       <c r="C366" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-09-06 02:00</t>
         </is>
       </c>
       <c r="D366" s="25" t="n">
@@ -24975,37 +24975,37 @@
       </c>
       <c r="E366" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F366" s="17" t="inlineStr">
         <is>
-          <t>Over 61.5</t>
+          <t>UNLV -3</t>
         </is>
       </c>
       <c r="G366" s="26" t="n">
-        <v>61.5</v>
+        <v>3</v>
       </c>
       <c r="H366" s="18" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I366" s="20" t="n">
-        <v>0.4164245001722412</v>
+        <v>0.4247975673626849</v>
       </c>
       <c r="J366" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K366" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L366" s="19" t="n">
-        <v>-0.1028062690585281</v>
+        <v>-0.1035043194297679</v>
       </c>
       <c r="M366" s="19" t="n">
-        <v>-0.1979972589275354</v>
+        <v>-0.184802661991996</v>
       </c>
       <c r="N366" s="20" t="n">
-        <v>0</v>
+        <v>0.0567</v>
       </c>
       <c r="O366" s="27" t="n">
         <v>0.45</v>
@@ -25025,12 +25025,12 @@
       </c>
       <c r="B367" s="12" t="inlineStr">
         <is>
-          <t>UNLV @ HAW</t>
+          <t>TOL @ MSU</t>
         </is>
       </c>
       <c r="C367" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 02:00</t>
+          <t>2026-09-05 00:00</t>
         </is>
       </c>
       <c r="D367" s="22" t="n">
@@ -25038,22 +25038,22 @@
       </c>
       <c r="E367" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F367" s="12" t="inlineStr">
         <is>
-          <t>UNLV -3</t>
+          <t>Under 49.5</t>
         </is>
       </c>
       <c r="G367" s="23" t="n">
-        <v>3</v>
+        <v>49.5</v>
       </c>
       <c r="H367" s="13" t="n">
         <v>-112</v>
       </c>
       <c r="I367" s="15" t="n">
-        <v>0.4247975673626849</v>
+        <v>0.4244232808142943</v>
       </c>
       <c r="J367" s="15" t="n">
         <v>0.5043297540699688</v>
@@ -25062,13 +25062,13 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L367" s="14" t="n">
-        <v>-0.1035043194297679</v>
+        <v>-0.1038786059781586</v>
       </c>
       <c r="M367" s="14" t="n">
-        <v>-0.184802661991996</v>
+        <v>-0.1966273613158002</v>
       </c>
       <c r="N367" s="15" t="n">
-        <v>0.0567</v>
+        <v>0</v>
       </c>
       <c r="O367" s="24" t="n">
         <v>0.45</v>
@@ -25088,12 +25088,12 @@
       </c>
       <c r="B368" s="17" t="inlineStr">
         <is>
-          <t>TOL @ MSU</t>
+          <t>ACU @ TTU</t>
         </is>
       </c>
       <c r="C368" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 00:00</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D368" s="25" t="n">
@@ -25106,29 +25106,29 @@
       </c>
       <c r="F368" s="17" t="inlineStr">
         <is>
-          <t>Under 49.5</t>
+          <t>Over 59.5</t>
         </is>
       </c>
       <c r="G368" s="26" t="n">
-        <v>49.5</v>
+        <v>59.5</v>
       </c>
       <c r="H368" s="18" t="n">
-        <v>-112</v>
+        <v>-105</v>
       </c>
       <c r="I368" s="20" t="n">
-        <v>0.4244232808142943</v>
+        <v>0.4077266673356444</v>
       </c>
       <c r="J368" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K368" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L368" s="19" t="n">
-        <v>-0.1038786059781586</v>
+        <v>-0.1044684546155751</v>
       </c>
       <c r="M368" s="19" t="n">
-        <v>-0.1966273613158002</v>
+        <v>-0.2039622209161229</v>
       </c>
       <c r="N368" s="20" t="n">
         <v>0</v>
@@ -25141,7 +25141,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q368" s="17" t="n"/>
+      <c r="Q368" s="17" t="inlineStr">
+        <is>
+          <t>ACU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="12" t="inlineStr">
@@ -25151,12 +25155,12 @@
       </c>
       <c r="B369" s="12" t="inlineStr">
         <is>
-          <t>ACU @ TTU</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C369" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D369" s="22" t="n">
@@ -25169,29 +25173,29 @@
       </c>
       <c r="F369" s="12" t="inlineStr">
         <is>
-          <t>Over 59.5</t>
+          <t>Over 61.5</t>
         </is>
       </c>
       <c r="G369" s="23" t="n">
-        <v>59.5</v>
+        <v>61.5</v>
       </c>
       <c r="H369" s="13" t="n">
-        <v>-105</v>
+        <v>-112</v>
       </c>
       <c r="I369" s="15" t="n">
-        <v>0.4077266673356444</v>
+        <v>0.42075425424221</v>
       </c>
       <c r="J369" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K369" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L369" s="14" t="n">
-        <v>-0.1044684546155751</v>
+        <v>-0.1075476325502428</v>
       </c>
       <c r="M369" s="14" t="n">
-        <v>-0.2039622209161229</v>
+        <v>-0.2035723044701025</v>
       </c>
       <c r="N369" s="15" t="n">
         <v>0</v>
@@ -25204,11 +25208,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q369" s="12" t="inlineStr">
-        <is>
-          <t>ACU isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q369" s="12" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="17" t="inlineStr">
@@ -26567,12 +26567,12 @@
       </c>
       <c r="B391" s="12" t="inlineStr">
         <is>
-          <t>UNT @ IU</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C391" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D391" s="22" t="n">
@@ -26580,34 +26580,32 @@
       </c>
       <c r="E391" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F391" s="12" t="inlineStr">
         <is>
-          <t>Under 55.5</t>
-        </is>
-      </c>
-      <c r="G391" s="23" t="n">
-        <v>55.5</v>
-      </c>
+          <t>TCU ML</t>
+        </is>
+      </c>
+      <c r="G391" s="23" t="n"/>
       <c r="H391" s="13" t="n">
-        <v>-105</v>
+        <v>-345</v>
       </c>
       <c r="I391" s="15" t="n">
-        <v>0.3833393089817336</v>
+        <v>0.6470292506889459</v>
       </c>
       <c r="J391" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.7440690150970525</v>
       </c>
       <c r="K391" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.7752808988764045</v>
       </c>
       <c r="L391" s="14" t="n">
-        <v>-0.1288558129694859</v>
+        <v>-0.1282516481874586</v>
       </c>
       <c r="M391" s="14" t="n">
-        <v>-0.2515756348451867</v>
+        <v>-0.1654260389664321</v>
       </c>
       <c r="N391" s="15" t="n">
         <v>0</v>
@@ -26630,12 +26628,12 @@
       </c>
       <c r="B392" s="17" t="inlineStr">
         <is>
-          <t>TULN @ DUKE</t>
+          <t>UNT @ IU</t>
         </is>
       </c>
       <c r="C392" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D392" s="25" t="n">
@@ -26643,34 +26641,34 @@
       </c>
       <c r="E392" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F392" s="17" t="inlineStr">
         <is>
-          <t>DUKE -9.5</t>
+          <t>Under 55.5</t>
         </is>
       </c>
       <c r="G392" s="26" t="n">
-        <v>-9.5</v>
+        <v>55.5</v>
       </c>
       <c r="H392" s="18" t="n">
-        <v>-102</v>
+        <v>-105</v>
       </c>
       <c r="I392" s="20" t="n">
-        <v>0.3756363052637322</v>
+        <v>0.3833393089817336</v>
       </c>
       <c r="J392" s="20" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K392" s="20" t="n">
-        <v>0.504950495049505</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L392" s="19" t="n">
-        <v>-0.1293141897857728</v>
+        <v>-0.1288558129694859</v>
       </c>
       <c r="M392" s="19" t="n">
-        <v>-0.2560928072228049</v>
+        <v>-0.2515756348451867</v>
       </c>
       <c r="N392" s="20" t="n">
         <v>0</v>
@@ -26693,7 +26691,7 @@
       </c>
       <c r="B393" s="12" t="inlineStr">
         <is>
-          <t>BAY @ AUB</t>
+          <t>TULN @ DUKE</t>
         </is>
       </c>
       <c r="C393" s="12" t="inlineStr">
@@ -26711,32 +26709,32 @@
       </c>
       <c r="F393" s="12" t="inlineStr">
         <is>
-          <t>AUB -7</t>
+          <t>DUKE -9.5</t>
         </is>
       </c>
       <c r="G393" s="23" t="n">
-        <v>-7</v>
+        <v>-9.5</v>
       </c>
       <c r="H393" s="13" t="n">
-        <v>-112</v>
+        <v>-102</v>
       </c>
       <c r="I393" s="15" t="n">
-        <v>0.3980834043538695</v>
+        <v>0.3756363052637322</v>
       </c>
       <c r="J393" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4826358742837298</v>
       </c>
       <c r="K393" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.504950495049505</v>
       </c>
       <c r="L393" s="14" t="n">
-        <v>-0.1302184824385834</v>
+        <v>-0.1293141897857728</v>
       </c>
       <c r="M393" s="14" t="n">
-        <v>-0.2352885379987043</v>
+        <v>-0.2560928072228049</v>
       </c>
       <c r="N393" s="15" t="n">
-        <v>0.0454</v>
+        <v>0</v>
       </c>
       <c r="O393" s="24" t="n">
         <v>0.45</v>
@@ -26756,12 +26754,12 @@
       </c>
       <c r="B394" s="17" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>BAY @ AUB</t>
         </is>
       </c>
       <c r="C394" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D394" s="25" t="n">
@@ -26769,35 +26767,37 @@
       </c>
       <c r="E394" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F394" s="17" t="inlineStr">
         <is>
-          <t>TCU ML</t>
-        </is>
-      </c>
-      <c r="G394" s="26" t="n"/>
+          <t>AUB -7</t>
+        </is>
+      </c>
+      <c r="G394" s="26" t="n">
+        <v>-7</v>
+      </c>
       <c r="H394" s="18" t="n">
-        <v>-360</v>
+        <v>-112</v>
       </c>
       <c r="I394" s="20" t="n">
-        <v>0.6504010269974078</v>
+        <v>0.3980834043538695</v>
       </c>
       <c r="J394" s="20" t="n">
-        <v>0.7508125677139762</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K394" s="20" t="n">
-        <v>0.7826086956521739</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L394" s="19" t="n">
-        <v>-0.1322076686547662</v>
+        <v>-0.1302184824385834</v>
       </c>
       <c r="M394" s="19" t="n">
-        <v>-0.1689320210588679</v>
+        <v>-0.2352885379987043</v>
       </c>
       <c r="N394" s="20" t="n">
-        <v>0</v>
+        <v>0.0454</v>
       </c>
       <c r="O394" s="27" t="n">
         <v>0.45</v>
@@ -27081,12 +27081,12 @@
       </c>
       <c r="B399" s="12" t="inlineStr">
         <is>
-          <t>CLEM @ LSU</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C399" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D399" s="22" t="n">
@@ -27094,32 +27094,34 @@
       </c>
       <c r="E399" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F399" s="12" t="inlineStr">
         <is>
-          <t>LSU ML</t>
-        </is>
-      </c>
-      <c r="G399" s="23" t="n"/>
+          <t>TCU -8.5</t>
+        </is>
+      </c>
+      <c r="G399" s="23" t="n">
+        <v>-8.5</v>
+      </c>
       <c r="H399" s="13" t="n">
-        <v>-380</v>
+        <v>-112</v>
       </c>
       <c r="I399" s="15" t="n">
-        <v>0.6517040235225773</v>
+        <v>0.3885649897991602</v>
       </c>
       <c r="J399" s="15" t="n">
-        <v>0.7600000000000001</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K399" s="15" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L399" s="14" t="n">
-        <v>-0.1399626431440893</v>
+        <v>-0.1397368969932926</v>
       </c>
       <c r="M399" s="14" t="n">
-        <v>-0.1767949176556919</v>
+        <v>-0.2645019835944468</v>
       </c>
       <c r="N399" s="15" t="n">
         <v>0</v>
@@ -27142,12 +27144,12 @@
       </c>
       <c r="B400" s="17" t="inlineStr">
         <is>
-          <t>FIU @ USF</t>
+          <t>CLEM @ LSU</t>
         </is>
       </c>
       <c r="C400" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D400" s="25" t="n">
@@ -27155,34 +27157,32 @@
       </c>
       <c r="E400" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F400" s="17" t="inlineStr">
         <is>
-          <t>Under 53.5</t>
-        </is>
-      </c>
-      <c r="G400" s="26" t="n">
-        <v>53.5</v>
-      </c>
+          <t>LSU ML</t>
+        </is>
+      </c>
+      <c r="G400" s="26" t="n"/>
       <c r="H400" s="18" t="n">
-        <v>-105</v>
+        <v>-380</v>
       </c>
       <c r="I400" s="20" t="n">
-        <v>0.3718521871845395</v>
+        <v>0.6517040235225773</v>
       </c>
       <c r="J400" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.7600000000000001</v>
       </c>
       <c r="K400" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="L400" s="19" t="n">
-        <v>-0.14034293476668</v>
+        <v>-0.1399626431440893</v>
       </c>
       <c r="M400" s="19" t="n">
-        <v>-0.2740028726397086</v>
+        <v>-0.1767949176556919</v>
       </c>
       <c r="N400" s="20" t="n">
         <v>0</v>
@@ -27205,12 +27205,12 @@
       </c>
       <c r="B401" s="12" t="inlineStr">
         <is>
-          <t>BAY @ AUB</t>
+          <t>FIU @ USF</t>
         </is>
       </c>
       <c r="C401" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D401" s="22" t="n">
@@ -27223,29 +27223,29 @@
       </c>
       <c r="F401" s="12" t="inlineStr">
         <is>
-          <t>Over 59.5</t>
+          <t>Under 53.5</t>
         </is>
       </c>
       <c r="G401" s="23" t="n">
-        <v>59.5</v>
+        <v>53.5</v>
       </c>
       <c r="H401" s="13" t="n">
-        <v>-102</v>
+        <v>-105</v>
       </c>
       <c r="I401" s="15" t="n">
-        <v>0.3638212577526206</v>
+        <v>0.3718521871845395</v>
       </c>
       <c r="J401" s="15" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K401" s="15" t="n">
-        <v>0.504950495049505</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L401" s="14" t="n">
-        <v>-0.1411292372968843</v>
+        <v>-0.14034293476668</v>
       </c>
       <c r="M401" s="14" t="n">
-        <v>-0.2794912346467708</v>
+        <v>-0.2740028726397086</v>
       </c>
       <c r="N401" s="15" t="n">
         <v>0</v>
@@ -27268,12 +27268,12 @@
       </c>
       <c r="B402" s="17" t="inlineStr">
         <is>
-          <t>HAW @ STAN</t>
+          <t>BAY @ AUB</t>
         </is>
       </c>
       <c r="C402" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D402" s="25" t="n">
@@ -27286,29 +27286,29 @@
       </c>
       <c r="F402" s="17" t="inlineStr">
         <is>
-          <t>Under 48.5</t>
+          <t>Over 59.5</t>
         </is>
       </c>
       <c r="G402" s="26" t="n">
-        <v>48.5</v>
+        <v>59.5</v>
       </c>
       <c r="H402" s="18" t="n">
-        <v>-110</v>
+        <v>-102</v>
       </c>
       <c r="I402" s="20" t="n">
-        <v>0.3821306714054384</v>
+        <v>0.3638212577526206</v>
       </c>
       <c r="J402" s="20" t="n">
-        <v>0.5</v>
+        <v>0.4826358742837298</v>
       </c>
       <c r="K402" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.504950495049505</v>
       </c>
       <c r="L402" s="19" t="n">
-        <v>-0.1416788524040854</v>
+        <v>-0.1411292372968843</v>
       </c>
       <c r="M402" s="19" t="n">
-        <v>-0.270477809135072</v>
+        <v>-0.2794912346467708</v>
       </c>
       <c r="N402" s="20" t="n">
         <v>0</v>
@@ -27331,12 +27331,12 @@
       </c>
       <c r="B403" s="12" t="inlineStr">
         <is>
-          <t>YSU @ UK</t>
+          <t>HAW @ STAN</t>
         </is>
       </c>
       <c r="C403" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 17:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D403" s="22" t="n">
@@ -27349,17 +27349,17 @@
       </c>
       <c r="F403" s="12" t="inlineStr">
         <is>
-          <t>Over 62.5</t>
+          <t>Under 48.5</t>
         </is>
       </c>
       <c r="G403" s="23" t="n">
-        <v>62.5</v>
+        <v>48.5</v>
       </c>
       <c r="H403" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I403" s="15" t="n">
-        <v>0.3788792876661868</v>
+        <v>0.3821306714054384</v>
       </c>
       <c r="J403" s="15" t="n">
         <v>0.5</v>
@@ -27368,10 +27368,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L403" s="14" t="n">
-        <v>-0.144930236143337</v>
+        <v>-0.1416788524040854</v>
       </c>
       <c r="M403" s="14" t="n">
-        <v>-0.2766849962736433</v>
+        <v>-0.270477809135072</v>
       </c>
       <c r="N403" s="15" t="n">
         <v>0</v>
@@ -27384,11 +27384,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q403" s="12" t="inlineStr">
-        <is>
-          <t>YSU isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q403" s="12" t="n"/>
     </row>
     <row r="404">
       <c r="A404" s="17" t="inlineStr">
@@ -27398,12 +27394,12 @@
       </c>
       <c r="B404" s="17" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>YSU @ UK</t>
         </is>
       </c>
       <c r="C404" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-09-05 17:00</t>
         </is>
       </c>
       <c r="D404" s="25" t="n">
@@ -27411,34 +27407,34 @@
       </c>
       <c r="E404" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F404" s="17" t="inlineStr">
         <is>
-          <t>TCU -9.5</t>
+          <t>Over 62.5</t>
         </is>
       </c>
       <c r="G404" s="26" t="n">
-        <v>-9.5</v>
+        <v>62.5</v>
       </c>
       <c r="H404" s="18" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I404" s="20" t="n">
-        <v>0.3742482198596571</v>
+        <v>0.3788792876661868</v>
       </c>
       <c r="J404" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5</v>
       </c>
       <c r="K404" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L404" s="19" t="n">
-        <v>-0.1449825493711122</v>
+        <v>-0.144930236143337</v>
       </c>
       <c r="M404" s="19" t="n">
-        <v>-0.2792256506406604</v>
+        <v>-0.2766849962736433</v>
       </c>
       <c r="N404" s="20" t="n">
         <v>0</v>
@@ -27451,7 +27447,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q404" s="17" t="n"/>
+      <c r="Q404" s="17" t="inlineStr">
+        <is>
+          <t>YSU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="12" t="inlineStr">
@@ -30429,22 +30429,22 @@
       </c>
       <c r="G450" s="26" t="n"/>
       <c r="H450" s="18" t="n">
-        <v>-20000</v>
+        <v>-10000</v>
       </c>
       <c r="I450" s="20" t="n">
-        <v>0.7905043352822523</v>
+        <v>0.7883072614300526</v>
       </c>
       <c r="J450" s="20" t="n">
-        <v>0.9728415079043372</v>
+        <v>0.9684473601999376</v>
       </c>
       <c r="K450" s="20" t="n">
-        <v>0.9950248756218906</v>
+        <v>0.9900990099009901</v>
       </c>
       <c r="L450" s="19" t="n">
-        <v>-0.2045205403396383</v>
+        <v>-0.2017917484709375</v>
       </c>
       <c r="M450" s="19" t="n">
-        <v>-0.2055431430413365</v>
+        <v>-0.2038096659556469</v>
       </c>
       <c r="N450" s="20" t="n">
         <v>0</v>
@@ -34904,12 +34904,12 @@
       </c>
       <c r="B518" s="17" t="inlineStr">
         <is>
-          <t>NCAT @ GAST</t>
+          <t>NMSU @ FSU</t>
         </is>
       </c>
       <c r="C518" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 23:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D518" s="25" t="n">
@@ -34922,17 +34922,17 @@
       </c>
       <c r="F518" s="17" t="inlineStr">
         <is>
-          <t>GAST -28.5</t>
+          <t>FSU -31.5</t>
         </is>
       </c>
       <c r="G518" s="26" t="n">
-        <v>-28.5</v>
+        <v>-31.5</v>
       </c>
       <c r="H518" s="18" t="n">
         <v>-108</v>
       </c>
       <c r="I518" s="20" t="n">
-        <v>0.2547133684856709</v>
+        <v>0.2548469865825019</v>
       </c>
       <c r="J518" s="20" t="n">
         <v>0.4956702459300312</v>
@@ -34941,10 +34941,10 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L518" s="19" t="n">
-        <v>-0.2645174007450984</v>
+        <v>-0.2643837826482673</v>
       </c>
       <c r="M518" s="19" t="n">
-        <v>-0.5094409199535228</v>
+        <v>-0.509183581396663</v>
       </c>
       <c r="N518" s="20" t="n">
         <v>0</v>
@@ -34959,7 +34959,7 @@
       </c>
       <c r="Q518" s="17" t="inlineStr">
         <is>
-          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -34971,12 +34971,12 @@
       </c>
       <c r="B519" s="12" t="inlineStr">
         <is>
-          <t>UNH @ SYR</t>
+          <t>NCAT @ GAST</t>
         </is>
       </c>
       <c r="C519" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-09-04 23:00</t>
         </is>
       </c>
       <c r="D519" s="22" t="n">
@@ -34989,29 +34989,29 @@
       </c>
       <c r="F519" s="12" t="inlineStr">
         <is>
-          <t>SYR -32.5</t>
+          <t>GAST -28.5</t>
         </is>
       </c>
       <c r="G519" s="23" t="n">
-        <v>-32.5</v>
+        <v>-28.5</v>
       </c>
       <c r="H519" s="13" t="n">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="I519" s="15" t="n">
-        <v>0.2473999742058187</v>
+        <v>0.2547133684856709</v>
       </c>
       <c r="J519" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K519" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L519" s="14" t="n">
-        <v>-0.2647951477454008</v>
+        <v>-0.2645174007450984</v>
       </c>
       <c r="M519" s="14" t="n">
-        <v>-0.5169810027410207</v>
+        <v>-0.5094409199535228</v>
       </c>
       <c r="N519" s="15" t="n">
         <v>0</v>
@@ -35026,7 +35026,7 @@
       </c>
       <c r="Q519" s="12" t="inlineStr">
         <is>
-          <t>UNH isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -35038,12 +35038,12 @@
       </c>
       <c r="B520" s="17" t="inlineStr">
         <is>
-          <t>APSU @ VAN</t>
+          <t>UNH @ SYR</t>
         </is>
       </c>
       <c r="C520" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D520" s="25" t="n">
@@ -35056,29 +35056,29 @@
       </c>
       <c r="F520" s="17" t="inlineStr">
         <is>
-          <t>VAN -30.5</t>
+          <t>SYR -32.5</t>
         </is>
       </c>
       <c r="G520" s="26" t="n">
-        <v>-30.5</v>
+        <v>-32.5</v>
       </c>
       <c r="H520" s="18" t="n">
-        <v>-112</v>
+        <v>-105</v>
       </c>
       <c r="I520" s="20" t="n">
-        <v>0.2613733847312802</v>
+        <v>0.2473999742058187</v>
       </c>
       <c r="J520" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K520" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L520" s="19" t="n">
-        <v>-0.2669285020611726</v>
+        <v>-0.2647951477454008</v>
       </c>
       <c r="M520" s="19" t="n">
-        <v>-0.5052575217586481</v>
+        <v>-0.5169810027410207</v>
       </c>
       <c r="N520" s="20" t="n">
         <v>0</v>
@@ -35093,7 +35093,7 @@
       </c>
       <c r="Q520" s="17" t="inlineStr">
         <is>
-          <t>APSU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>UNH isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -35105,12 +35105,12 @@
       </c>
       <c r="B521" s="12" t="inlineStr">
         <is>
-          <t>ULM @ MSST</t>
+          <t>APSU @ VAN</t>
         </is>
       </c>
       <c r="C521" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D521" s="22" t="n">
@@ -35123,29 +35123,29 @@
       </c>
       <c r="F521" s="12" t="inlineStr">
         <is>
-          <t>MSST -28.5</t>
+          <t>VAN -30.5</t>
         </is>
       </c>
       <c r="G521" s="23" t="n">
-        <v>-28.5</v>
+        <v>-30.5</v>
       </c>
       <c r="H521" s="13" t="n">
-        <v>-115</v>
+        <v>-112</v>
       </c>
       <c r="I521" s="15" t="n">
-        <v>0.2665669243576875</v>
+        <v>0.2613733847312802</v>
       </c>
       <c r="J521" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K521" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L521" s="14" t="n">
-        <v>-0.268316796572545</v>
+        <v>-0.2669285020611726</v>
       </c>
       <c r="M521" s="14" t="n">
-        <v>-0.5016357501138885</v>
+        <v>-0.5052575217586481</v>
       </c>
       <c r="N521" s="15" t="n">
         <v>0</v>
@@ -35160,7 +35160,7 @@
       </c>
       <c r="Q521" s="12" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>APSU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -35172,12 +35172,12 @@
       </c>
       <c r="B522" s="17" t="inlineStr">
         <is>
-          <t>MVSU @ SAC</t>
+          <t>ULM @ MSST</t>
         </is>
       </c>
       <c r="C522" s="17" t="inlineStr">
         <is>
-          <t>2026-09-06 02:00</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D522" s="25" t="n">
@@ -35190,35 +35190,35 @@
       </c>
       <c r="F522" s="17" t="inlineStr">
         <is>
-          <t>SAC -35.5</t>
+          <t>MSST -28.5</t>
         </is>
       </c>
       <c r="G522" s="26" t="n">
-        <v>-35.5</v>
+        <v>-28.5</v>
       </c>
       <c r="H522" s="18" t="n">
-        <v>-108</v>
+        <v>-115</v>
       </c>
       <c r="I522" s="20" t="n">
-        <v>0.2507745995752354</v>
+        <v>0.2665669243576875</v>
       </c>
       <c r="J522" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K522" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L522" s="19" t="n">
-        <v>-0.2684561696555339</v>
+        <v>-0.268316796572545</v>
       </c>
       <c r="M522" s="19" t="n">
-        <v>-0.5170266971143614</v>
+        <v>-0.5016357501138885</v>
       </c>
       <c r="N522" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O522" s="27" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="P522" s="17" t="inlineStr">
         <is>
@@ -35227,7 +35227,7 @@
       </c>
       <c r="Q522" s="17" t="inlineStr">
         <is>
-          <t>MVSU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -35239,12 +35239,12 @@
       </c>
       <c r="B523" s="12" t="inlineStr">
         <is>
-          <t>BRY @ ARMY</t>
+          <t>MVSU @ SAC</t>
         </is>
       </c>
       <c r="C523" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-09-06 02:00</t>
         </is>
       </c>
       <c r="D523" s="22" t="n">
@@ -35257,17 +35257,17 @@
       </c>
       <c r="F523" s="12" t="inlineStr">
         <is>
-          <t>ARMY -36.5</t>
+          <t>SAC -35.5</t>
         </is>
       </c>
       <c r="G523" s="23" t="n">
-        <v>-36.5</v>
+        <v>-35.5</v>
       </c>
       <c r="H523" s="13" t="n">
         <v>-108</v>
       </c>
       <c r="I523" s="15" t="n">
-        <v>0.2500678397522949</v>
+        <v>0.2507745995752354</v>
       </c>
       <c r="J523" s="15" t="n">
         <v>0.4956702459300312</v>
@@ -35276,16 +35276,16 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L523" s="14" t="n">
-        <v>-0.2691629294784744</v>
+        <v>-0.2684561696555339</v>
       </c>
       <c r="M523" s="14" t="n">
-        <v>-0.5183878641807653</v>
+        <v>-0.5170266971143614</v>
       </c>
       <c r="N523" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O523" s="24" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="P523" s="12" t="inlineStr">
         <is>
@@ -35294,7 +35294,7 @@
       </c>
       <c r="Q523" s="12" t="inlineStr">
         <is>
-          <t>BRY isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>MVSU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -35306,12 +35306,12 @@
       </c>
       <c r="B524" s="17" t="inlineStr">
         <is>
-          <t>KENT @ SC</t>
+          <t>BRY @ ARMY</t>
         </is>
       </c>
       <c r="C524" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 16:45</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D524" s="25" t="n">
@@ -35324,7 +35324,7 @@
       </c>
       <c r="F524" s="17" t="inlineStr">
         <is>
-          <t>SC -36.5</t>
+          <t>ARMY -36.5</t>
         </is>
       </c>
       <c r="G524" s="26" t="n">
@@ -35334,7 +35334,7 @@
         <v>-108</v>
       </c>
       <c r="I524" s="20" t="n">
-        <v>0.2499368613568438</v>
+        <v>0.2500678397522949</v>
       </c>
       <c r="J524" s="20" t="n">
         <v>0.4956702459300312</v>
@@ -35343,10 +35343,10 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L524" s="19" t="n">
-        <v>-0.2692939078739255</v>
+        <v>-0.2691629294784744</v>
       </c>
       <c r="M524" s="19" t="n">
-        <v>-0.5186401188683007</v>
+        <v>-0.5183878641807653</v>
       </c>
       <c r="N524" s="20" t="n">
         <v>0</v>
@@ -35361,7 +35361,7 @@
       </c>
       <c r="Q524" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>BRY isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -35373,12 +35373,12 @@
       </c>
       <c r="B525" s="12" t="inlineStr">
         <is>
-          <t>WMU @ MICH</t>
+          <t>KENT @ SC</t>
         </is>
       </c>
       <c r="C525" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-09-05 16:45</t>
         </is>
       </c>
       <c r="D525" s="22" t="n">
@@ -35391,29 +35391,29 @@
       </c>
       <c r="F525" s="12" t="inlineStr">
         <is>
-          <t>MICH -27.5</t>
+          <t>SC -36.5</t>
         </is>
       </c>
       <c r="G525" s="23" t="n">
-        <v>-27.5</v>
+        <v>-36.5</v>
       </c>
       <c r="H525" s="13" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="I525" s="15" t="n">
-        <v>0.2654934830558677</v>
+        <v>0.2499368613568438</v>
       </c>
       <c r="J525" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K525" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L525" s="14" t="n">
-        <v>-0.2693902378743648</v>
+        <v>-0.2692939078739255</v>
       </c>
       <c r="M525" s="14" t="n">
-        <v>-0.5036426186346822</v>
+        <v>-0.5186401188683007</v>
       </c>
       <c r="N525" s="15" t="n">
         <v>0</v>
@@ -35440,12 +35440,12 @@
       </c>
       <c r="B526" s="17" t="inlineStr">
         <is>
-          <t>IDHO @ UTAH</t>
+          <t>WMU @ MICH</t>
         </is>
       </c>
       <c r="C526" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 01:00</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D526" s="25" t="n">
@@ -35458,29 +35458,29 @@
       </c>
       <c r="F526" s="17" t="inlineStr">
         <is>
-          <t>UTAH -33.5</t>
+          <t>MICH -27.5</t>
         </is>
       </c>
       <c r="G526" s="26" t="n">
-        <v>-33.5</v>
+        <v>-27.5</v>
       </c>
       <c r="H526" s="18" t="n">
-        <v>-112</v>
+        <v>-115</v>
       </c>
       <c r="I526" s="20" t="n">
-        <v>0.2585208472473556</v>
+        <v>0.2654934830558677</v>
       </c>
       <c r="J526" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K526" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L526" s="19" t="n">
-        <v>-0.2697810395450972</v>
+        <v>-0.2693902378743648</v>
       </c>
       <c r="M526" s="19" t="n">
-        <v>-0.5106569677103627</v>
+        <v>-0.5036426186346822</v>
       </c>
       <c r="N526" s="20" t="n">
         <v>0</v>
@@ -35495,7 +35495,7 @@
       </c>
       <c r="Q526" s="17" t="inlineStr">
         <is>
-          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -35507,12 +35507,12 @@
       </c>
       <c r="B527" s="12" t="inlineStr">
         <is>
-          <t>UNA @ ARK</t>
+          <t>IDHO @ UTAH</t>
         </is>
       </c>
       <c r="C527" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 20:15</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D527" s="22" t="n">
@@ -35525,29 +35525,29 @@
       </c>
       <c r="F527" s="12" t="inlineStr">
         <is>
-          <t>ARK -40.5</t>
+          <t>UTAH -33.5</t>
         </is>
       </c>
       <c r="G527" s="23" t="n">
-        <v>-40.5</v>
+        <v>-33.5</v>
       </c>
       <c r="H527" s="13" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I527" s="15" t="n">
-        <v>0.2485003206460911</v>
+        <v>0.2585208472473556</v>
       </c>
       <c r="J527" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K527" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L527" s="14" t="n">
-        <v>-0.2707304485846782</v>
+        <v>-0.2697810395450972</v>
       </c>
       <c r="M527" s="14" t="n">
-        <v>-0.5214067898667876</v>
+        <v>-0.5106569677103627</v>
       </c>
       <c r="N527" s="15" t="n">
         <v>0</v>
@@ -35562,7 +35562,7 @@
       </c>
       <c r="Q527" s="12" t="inlineStr">
         <is>
-          <t>UNA isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -35574,12 +35574,12 @@
       </c>
       <c r="B528" s="17" t="inlineStr">
         <is>
-          <t>INST @ PUR</t>
+          <t>UNA @ ARK</t>
         </is>
       </c>
       <c r="C528" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 23:00</t>
+          <t>2026-09-05 20:15</t>
         </is>
       </c>
       <c r="D528" s="25" t="n">
@@ -35592,29 +35592,29 @@
       </c>
       <c r="F528" s="17" t="inlineStr">
         <is>
-          <t>PUR -35.5</t>
+          <t>ARK -40.5</t>
         </is>
       </c>
       <c r="G528" s="26" t="n">
-        <v>-35.5</v>
+        <v>-40.5</v>
       </c>
       <c r="H528" s="18" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I528" s="20" t="n">
-        <v>0.2528934298318226</v>
+        <v>0.2485003206460911</v>
       </c>
       <c r="J528" s="20" t="n">
-        <v>0.5021949078138718</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K528" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L528" s="19" t="n">
-        <v>-0.2709160939777012</v>
+        <v>-0.2707304485846782</v>
       </c>
       <c r="M528" s="19" t="n">
-        <v>-0.5172034521392477</v>
+        <v>-0.5214067898667876</v>
       </c>
       <c r="N528" s="20" t="n">
         <v>0</v>
@@ -35629,7 +35629,7 @@
       </c>
       <c r="Q528" s="17" t="inlineStr">
         <is>
-          <t>INST isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>UNA isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -35641,12 +35641,12 @@
       </c>
       <c r="B529" s="12" t="inlineStr">
         <is>
-          <t>EIU @ MINN</t>
+          <t>INST @ PUR</t>
         </is>
       </c>
       <c r="C529" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-09-04 23:00</t>
         </is>
       </c>
       <c r="D529" s="22" t="n">
@@ -35659,29 +35659,29 @@
       </c>
       <c r="F529" s="12" t="inlineStr">
         <is>
-          <t>MINN -43.5</t>
+          <t>PUR -35.5</t>
         </is>
       </c>
       <c r="G529" s="23" t="n">
-        <v>-43.5</v>
+        <v>-35.5</v>
       </c>
       <c r="H529" s="13" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I529" s="15" t="n">
-        <v>0.2481768262232006</v>
+        <v>0.2528934298318226</v>
       </c>
       <c r="J529" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5021949078138718</v>
       </c>
       <c r="K529" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L529" s="14" t="n">
-        <v>-0.2710539430075687</v>
+        <v>-0.2709160939777012</v>
       </c>
       <c r="M529" s="14" t="n">
-        <v>-0.5220298161627247</v>
+        <v>-0.5172034521392477</v>
       </c>
       <c r="N529" s="15" t="n">
         <v>0</v>
@@ -35696,7 +35696,7 @@
       </c>
       <c r="Q529" s="12" t="inlineStr">
         <is>
-          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>INST isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -35708,12 +35708,12 @@
       </c>
       <c r="B530" s="17" t="inlineStr">
         <is>
-          <t>BALL @ OSU</t>
+          <t>EIU @ MINN</t>
         </is>
       </c>
       <c r="C530" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 16:30</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D530" s="25" t="n">
@@ -35726,17 +35726,17 @@
       </c>
       <c r="F530" s="17" t="inlineStr">
         <is>
-          <t>OSU -50.5</t>
+          <t>MINN -43.5</t>
         </is>
       </c>
       <c r="G530" s="26" t="n">
-        <v>-50.5</v>
+        <v>-43.5</v>
       </c>
       <c r="H530" s="18" t="n">
         <v>-108</v>
       </c>
       <c r="I530" s="20" t="n">
-        <v>0.2480345857275048</v>
+        <v>0.2481768262232006</v>
       </c>
       <c r="J530" s="20" t="n">
         <v>0.4956702459300312</v>
@@ -35745,10 +35745,10 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L530" s="19" t="n">
-        <v>-0.2711961835032645</v>
+        <v>-0.2710539430075687</v>
       </c>
       <c r="M530" s="19" t="n">
-        <v>-0.5223037608211019</v>
+        <v>-0.5220298161627247</v>
       </c>
       <c r="N530" s="20" t="n">
         <v>0</v>
@@ -35763,7 +35763,7 @@
       </c>
       <c r="Q530" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -35775,12 +35775,12 @@
       </c>
       <c r="B531" s="12" t="inlineStr">
         <is>
-          <t>HAMP @ MD</t>
+          <t>BALL @ OSU</t>
         </is>
       </c>
       <c r="C531" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00</t>
+          <t>2026-09-05 16:30</t>
         </is>
       </c>
       <c r="D531" s="22" t="n">
@@ -35793,17 +35793,17 @@
       </c>
       <c r="F531" s="12" t="inlineStr">
         <is>
-          <t>MD -45.5</t>
+          <t>OSU -50.5</t>
         </is>
       </c>
       <c r="G531" s="23" t="n">
-        <v>-45.5</v>
+        <v>-50.5</v>
       </c>
       <c r="H531" s="13" t="n">
         <v>-108</v>
       </c>
       <c r="I531" s="15" t="n">
-        <v>0.2479827101867709</v>
+        <v>0.2480345857275048</v>
       </c>
       <c r="J531" s="15" t="n">
         <v>0.4956702459300312</v>
@@ -35812,16 +35812,16 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L531" s="14" t="n">
-        <v>-0.2712480590439984</v>
+        <v>-0.2711961835032645</v>
       </c>
       <c r="M531" s="14" t="n">
-        <v>-0.5224036692699228</v>
+        <v>-0.5223037608211019</v>
       </c>
       <c r="N531" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O531" s="24" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="P531" s="12" t="inlineStr">
         <is>
@@ -35830,7 +35830,7 @@
       </c>
       <c r="Q531" s="12" t="inlineStr">
         <is>
-          <t>HAMP isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -35842,12 +35842,12 @@
       </c>
       <c r="B532" s="17" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>HAMP @ MD</t>
         </is>
       </c>
       <c r="C532" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-09-06 00:00</t>
         </is>
       </c>
       <c r="D532" s="25" t="n">
@@ -35860,35 +35860,35 @@
       </c>
       <c r="F532" s="17" t="inlineStr">
         <is>
-          <t>USC -38.5</t>
+          <t>MD -45.5</t>
         </is>
       </c>
       <c r="G532" s="26" t="n">
-        <v>-38.5</v>
+        <v>-45.5</v>
       </c>
       <c r="H532" s="18" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I532" s="20" t="n">
-        <v>0.2523210839512047</v>
+        <v>0.2479827101867709</v>
       </c>
       <c r="J532" s="20" t="n">
-        <v>0.5</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K532" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L532" s="19" t="n">
-        <v>-0.2714884398583192</v>
+        <v>-0.2712480590439984</v>
       </c>
       <c r="M532" s="19" t="n">
-        <v>-0.5182961124567911</v>
+        <v>-0.5224036692699228</v>
       </c>
       <c r="N532" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O532" s="27" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="P532" s="17" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
       </c>
       <c r="Q532" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>HAMP isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -35909,12 +35909,12 @@
       </c>
       <c r="B533" s="12" t="inlineStr">
         <is>
-          <t>FOR @ NDSU</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C533" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D533" s="22" t="n">
@@ -35927,17 +35927,17 @@
       </c>
       <c r="F533" s="12" t="inlineStr">
         <is>
-          <t>NDSU -39.5</t>
+          <t>USC -38.5</t>
         </is>
       </c>
       <c r="G533" s="23" t="n">
-        <v>-39.5</v>
+        <v>-38.5</v>
       </c>
       <c r="H533" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I533" s="15" t="n">
-        <v>0.252080967887556</v>
+        <v>0.2523210839512047</v>
       </c>
       <c r="J533" s="15" t="n">
         <v>0.5</v>
@@ -35946,10 +35946,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L533" s="14" t="n">
-        <v>-0.2717285559219679</v>
+        <v>-0.2714884398583192</v>
       </c>
       <c r="M533" s="14" t="n">
-        <v>-0.5187545158510295</v>
+        <v>-0.5182961124567911</v>
       </c>
       <c r="N533" s="15" t="n">
         <v>0</v>
@@ -35964,7 +35964,7 @@
       </c>
       <c r="Q533" s="12" t="inlineStr">
         <is>
-          <t>FOR isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -35976,12 +35976,12 @@
       </c>
       <c r="B534" s="17" t="inlineStr">
         <is>
-          <t>PRST @ SDSU</t>
+          <t>FOR @ NDSU</t>
         </is>
       </c>
       <c r="C534" s="17" t="inlineStr">
         <is>
-          <t>2026-09-06 01:30</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D534" s="25" t="n">
@@ -35994,17 +35994,17 @@
       </c>
       <c r="F534" s="17" t="inlineStr">
         <is>
-          <t>SDSU -40.5</t>
+          <t>NDSU -39.5</t>
         </is>
       </c>
       <c r="G534" s="26" t="n">
-        <v>-40.5</v>
+        <v>-39.5</v>
       </c>
       <c r="H534" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I534" s="20" t="n">
-        <v>0.2513038950736583</v>
+        <v>0.252080967887556</v>
       </c>
       <c r="J534" s="20" t="n">
         <v>0.5</v>
@@ -36013,10 +36013,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L534" s="19" t="n">
-        <v>-0.2725056287358655</v>
+        <v>-0.2717285559219679</v>
       </c>
       <c r="M534" s="19" t="n">
-        <v>-0.5202380184957431</v>
+        <v>-0.5187545158510295</v>
       </c>
       <c r="N534" s="20" t="n">
         <v>0</v>
@@ -36031,7 +36031,7 @@
       </c>
       <c r="Q534" s="17" t="inlineStr">
         <is>
-          <t>PRST isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>FOR isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -36043,12 +36043,12 @@
       </c>
       <c r="B535" s="12" t="inlineStr">
         <is>
-          <t>LIU @ KU</t>
+          <t>PRST @ SDSU</t>
         </is>
       </c>
       <c r="C535" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 00:00</t>
+          <t>2026-09-06 01:30</t>
         </is>
       </c>
       <c r="D535" s="22" t="n">
@@ -36061,17 +36061,17 @@
       </c>
       <c r="F535" s="12" t="inlineStr">
         <is>
-          <t>KU -38.5</t>
+          <t>SDSU -40.5</t>
         </is>
       </c>
       <c r="G535" s="23" t="n">
-        <v>-38.5</v>
+        <v>-40.5</v>
       </c>
       <c r="H535" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I535" s="15" t="n">
-        <v>0.2511227420748506</v>
+        <v>0.2513038950736583</v>
       </c>
       <c r="J535" s="15" t="n">
         <v>0.5</v>
@@ -36080,10 +36080,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L535" s="14" t="n">
-        <v>-0.2726867817346733</v>
+        <v>-0.2725056287358655</v>
       </c>
       <c r="M535" s="14" t="n">
-        <v>-0.5205838560389217</v>
+        <v>-0.5202380184957431</v>
       </c>
       <c r="N535" s="15" t="n">
         <v>0</v>
@@ -36098,7 +36098,7 @@
       </c>
       <c r="Q535" s="12" t="inlineStr">
         <is>
-          <t>LIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>PRST isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -36110,12 +36110,12 @@
       </c>
       <c r="B536" s="17" t="inlineStr">
         <is>
-          <t>NORF @ ODU</t>
+          <t>LIU @ KU</t>
         </is>
       </c>
       <c r="C536" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 22:00</t>
+          <t>2026-09-05 00:00</t>
         </is>
       </c>
       <c r="D536" s="25" t="n">
@@ -36128,17 +36128,17 @@
       </c>
       <c r="F536" s="17" t="inlineStr">
         <is>
-          <t>ODU -41.5</t>
+          <t>KU -38.5</t>
         </is>
       </c>
       <c r="G536" s="26" t="n">
-        <v>-41.5</v>
+        <v>-38.5</v>
       </c>
       <c r="H536" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I536" s="20" t="n">
-        <v>0.2509944675491853</v>
+        <v>0.2511227420748506</v>
       </c>
       <c r="J536" s="20" t="n">
         <v>0.5</v>
@@ -36147,10 +36147,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L536" s="19" t="n">
-        <v>-0.2728150562603385</v>
+        <v>-0.2726867817346733</v>
       </c>
       <c r="M536" s="19" t="n">
-        <v>-0.5208287437697371</v>
+        <v>-0.5205838560389217</v>
       </c>
       <c r="N536" s="20" t="n">
         <v>0</v>
@@ -36165,7 +36165,7 @@
       </c>
       <c r="Q536" s="17" t="inlineStr">
         <is>
-          <t>NORF isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>LIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -36177,12 +36177,12 @@
       </c>
       <c r="B537" s="12" t="inlineStr">
         <is>
-          <t>MORG @ ASU</t>
+          <t>NORF @ ODU</t>
         </is>
       </c>
       <c r="C537" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 02:00</t>
+          <t>2026-09-05 22:00</t>
         </is>
       </c>
       <c r="D537" s="22" t="n">
@@ -36195,7 +36195,7 @@
       </c>
       <c r="F537" s="12" t="inlineStr">
         <is>
-          <t>ASU -41.5</t>
+          <t>ODU -41.5</t>
         </is>
       </c>
       <c r="G537" s="23" t="n">
@@ -36205,7 +36205,7 @@
         <v>-110</v>
       </c>
       <c r="I537" s="15" t="n">
-        <v>0.2506480991877214</v>
+        <v>0.2509944675491853</v>
       </c>
       <c r="J537" s="15" t="n">
         <v>0.5</v>
@@ -36214,10 +36214,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L537" s="14" t="n">
-        <v>-0.2731614246218025</v>
+        <v>-0.2728150562603385</v>
       </c>
       <c r="M537" s="14" t="n">
-        <v>-0.5214899924598047</v>
+        <v>-0.5208287437697371</v>
       </c>
       <c r="N537" s="15" t="n">
         <v>0</v>
@@ -36232,7 +36232,7 @@
       </c>
       <c r="Q537" s="12" t="inlineStr">
         <is>
-          <t>MORG isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>NORF isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -36244,12 +36244,12 @@
       </c>
       <c r="B538" s="17" t="inlineStr">
         <is>
-          <t>BCU @ UCF</t>
+          <t>MORG @ ASU</t>
         </is>
       </c>
       <c r="C538" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-06 02:00</t>
         </is>
       </c>
       <c r="D538" s="25" t="n">
@@ -36262,17 +36262,17 @@
       </c>
       <c r="F538" s="17" t="inlineStr">
         <is>
-          <t>UCF -42.5</t>
+          <t>ASU -41.5</t>
         </is>
       </c>
       <c r="G538" s="26" t="n">
-        <v>-42.5</v>
+        <v>-41.5</v>
       </c>
       <c r="H538" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I538" s="20" t="n">
-        <v>0.2504166868493028</v>
+        <v>0.2506480991877214</v>
       </c>
       <c r="J538" s="20" t="n">
         <v>0.5</v>
@@ -36281,10 +36281,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L538" s="19" t="n">
-        <v>-0.273392836960221</v>
+        <v>-0.2731614246218025</v>
       </c>
       <c r="M538" s="19" t="n">
-        <v>-0.5219317796513311</v>
+        <v>-0.5214899924598047</v>
       </c>
       <c r="N538" s="20" t="n">
         <v>0</v>
@@ -36299,7 +36299,7 @@
       </c>
       <c r="Q538" s="17" t="inlineStr">
         <is>
-          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>MORG isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -36311,12 +36311,12 @@
       </c>
       <c r="B539" s="12" t="inlineStr">
         <is>
-          <t>FUR @ TENN</t>
+          <t>BCU @ UCF</t>
         </is>
       </c>
       <c r="C539" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D539" s="22" t="n">
@@ -36329,17 +36329,17 @@
       </c>
       <c r="F539" s="12" t="inlineStr">
         <is>
-          <t>TENN -46.5</t>
+          <t>UCF -42.5</t>
         </is>
       </c>
       <c r="G539" s="23" t="n">
-        <v>-46.5</v>
+        <v>-42.5</v>
       </c>
       <c r="H539" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I539" s="15" t="n">
-        <v>0.2502188749213057</v>
+        <v>0.2504166868493028</v>
       </c>
       <c r="J539" s="15" t="n">
         <v>0.5</v>
@@ -36348,10 +36348,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L539" s="14" t="n">
-        <v>-0.2735906488882182</v>
+        <v>-0.273392836960221</v>
       </c>
       <c r="M539" s="14" t="n">
-        <v>-0.52230942060478</v>
+        <v>-0.5219317796513311</v>
       </c>
       <c r="N539" s="15" t="n">
         <v>0</v>
@@ -36366,7 +36366,7 @@
       </c>
       <c r="Q539" s="12" t="inlineStr">
         <is>
-          <t>FUR isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -36378,12 +36378,12 @@
       </c>
       <c r="B540" s="17" t="inlineStr">
         <is>
-          <t>ACU @ TTU</t>
+          <t>FUR @ TENN</t>
         </is>
       </c>
       <c r="C540" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D540" s="25" t="n">
@@ -36396,29 +36396,29 @@
       </c>
       <c r="F540" s="17" t="inlineStr">
         <is>
-          <t>TTU -42.5</t>
+          <t>TENN -46.5</t>
         </is>
       </c>
       <c r="G540" s="26" t="n">
-        <v>-42.5</v>
+        <v>-46.5</v>
       </c>
       <c r="H540" s="18" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I540" s="20" t="n">
-        <v>0.2533102651648682</v>
+        <v>0.2502188749213057</v>
       </c>
       <c r="J540" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K540" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L540" s="19" t="n">
-        <v>-0.2749916216275847</v>
+        <v>-0.2735906488882182</v>
       </c>
       <c r="M540" s="19" t="n">
-        <v>-0.5205198552236424</v>
+        <v>-0.52230942060478</v>
       </c>
       <c r="N540" s="20" t="n">
         <v>0</v>
@@ -36433,7 +36433,7 @@
       </c>
       <c r="Q540" s="17" t="inlineStr">
         <is>
-          <t>ACU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>FUR isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -36445,12 +36445,12 @@
       </c>
       <c r="B541" s="12" t="inlineStr">
         <is>
-          <t>UNT @ IU</t>
+          <t>ACU @ TTU</t>
         </is>
       </c>
       <c r="C541" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D541" s="22" t="n">
@@ -36463,17 +36463,17 @@
       </c>
       <c r="F541" s="12" t="inlineStr">
         <is>
-          <t>IU -40.5</t>
+          <t>TTU -42.5</t>
         </is>
       </c>
       <c r="G541" s="23" t="n">
-        <v>-40.5</v>
+        <v>-42.5</v>
       </c>
       <c r="H541" s="13" t="n">
         <v>-112</v>
       </c>
       <c r="I541" s="15" t="n">
-        <v>0.253276024683148</v>
+        <v>0.2533102651648682</v>
       </c>
       <c r="J541" s="15" t="n">
         <v>0.5043297540699688</v>
@@ -36482,10 +36482,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L541" s="14" t="n">
-        <v>-0.2750258621093048</v>
+        <v>-0.2749916216275847</v>
       </c>
       <c r="M541" s="14" t="n">
-        <v>-0.5205846675640413</v>
+        <v>-0.5205198552236424</v>
       </c>
       <c r="N541" s="15" t="n">
         <v>0</v>
@@ -36500,7 +36500,7 @@
       </c>
       <c r="Q541" s="12" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>ACU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -36512,12 +36512,12 @@
       </c>
       <c r="B542" s="17" t="inlineStr">
         <is>
-          <t>NICH @ KSU</t>
+          <t>UNT @ IU</t>
         </is>
       </c>
       <c r="C542" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D542" s="25" t="n">
@@ -36530,7 +36530,7 @@
       </c>
       <c r="F542" s="17" t="inlineStr">
         <is>
-          <t>KSU -40.5</t>
+          <t>IU -40.5</t>
         </is>
       </c>
       <c r="G542" s="26" t="n">
@@ -36540,7 +36540,7 @@
         <v>-112</v>
       </c>
       <c r="I542" s="20" t="n">
-        <v>0.2530712957889765</v>
+        <v>0.253276024683148</v>
       </c>
       <c r="J542" s="20" t="n">
         <v>0.5043297540699688</v>
@@ -36549,10 +36549,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L542" s="19" t="n">
-        <v>-0.2752305910034764</v>
+        <v>-0.2750258621093048</v>
       </c>
       <c r="M542" s="19" t="n">
-        <v>-0.5209721901137231</v>
+        <v>-0.5205846675640413</v>
       </c>
       <c r="N542" s="20" t="n">
         <v>0</v>
@@ -36567,7 +36567,7 @@
       </c>
       <c r="Q542" s="17" t="inlineStr">
         <is>
-          <t>NICH isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -36579,12 +36579,12 @@
       </c>
       <c r="B543" s="12" t="inlineStr">
         <is>
-          <t>NWST @ LT</t>
+          <t>NICH @ KSU</t>
         </is>
       </c>
       <c r="C543" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D543" s="22" t="n">
@@ -36597,17 +36597,17 @@
       </c>
       <c r="F543" s="12" t="inlineStr">
         <is>
-          <t>LT -41.5</t>
+          <t>KSU -40.5</t>
         </is>
       </c>
       <c r="G543" s="23" t="n">
-        <v>-41.5</v>
+        <v>-40.5</v>
       </c>
       <c r="H543" s="13" t="n">
         <v>-112</v>
       </c>
       <c r="I543" s="15" t="n">
-        <v>0.2529427018191113</v>
+        <v>0.2530712957889765</v>
       </c>
       <c r="J543" s="15" t="n">
         <v>0.5043297540699688</v>
@@ -36616,10 +36616,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L543" s="14" t="n">
-        <v>-0.2753591849733415</v>
+        <v>-0.2752305910034764</v>
       </c>
       <c r="M543" s="14" t="n">
-        <v>-0.5212156001281107</v>
+        <v>-0.5209721901137231</v>
       </c>
       <c r="N543" s="15" t="n">
         <v>0</v>
@@ -36634,7 +36634,7 @@
       </c>
       <c r="Q543" s="12" t="inlineStr">
         <is>
-          <t>NWST isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>NICH isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -36646,12 +36646,12 @@
       </c>
       <c r="B544" s="17" t="inlineStr">
         <is>
-          <t>NMSU @ FSU</t>
+          <t>NWST @ LT</t>
         </is>
       </c>
       <c r="C544" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D544" s="25" t="n">
@@ -36664,29 +36664,29 @@
       </c>
       <c r="F544" s="17" t="inlineStr">
         <is>
-          <t>FSU -31.5</t>
+          <t>LT -41.5</t>
         </is>
       </c>
       <c r="G544" s="26" t="n">
-        <v>-31.5</v>
+        <v>-41.5</v>
       </c>
       <c r="H544" s="18" t="n">
-        <v>-118</v>
+        <v>-112</v>
       </c>
       <c r="I544" s="20" t="n">
-        <v>0.2656939264756214</v>
+        <v>0.2529427018191113</v>
       </c>
       <c r="J544" s="20" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K544" s="20" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L544" s="19" t="n">
-        <v>-0.2755904771941033</v>
+        <v>-0.2753591849733415</v>
       </c>
       <c r="M544" s="19" t="n">
-        <v>-0.509141729053513</v>
+        <v>-0.5212156001281107</v>
       </c>
       <c r="N544" s="20" t="n">
         <v>0</v>
@@ -36701,7 +36701,7 @@
       </c>
       <c r="Q544" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>NWST isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -36987,7 +36987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -37233,7 +37233,7 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>OKST @ TLSA</t>
+          <t>FIU @ USF</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -37243,11 +37243,11 @@
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Under 60.5</t>
+          <t>Over 53.5</t>
         </is>
       </c>
       <c r="E8" s="13" t="n">
-        <v>-102</v>
+        <v>-115</v>
       </c>
       <c r="F8" s="16" t="n">
         <v>25</v>
@@ -37275,7 +37275,7 @@
         </is>
       </c>
       <c r="L8" s="14" t="n">
-        <v>0.1091</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="M8" s="14" t="n"/>
       <c r="N8" s="12" t="n"/>
@@ -37293,7 +37293,7 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>BAY @ AUB</t>
+          <t>OKST @ TLSA</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
@@ -37303,11 +37303,11 @@
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>Under 59.5</t>
+          <t>Under 60.5</t>
         </is>
       </c>
       <c r="E9" s="18" t="n">
-        <v>-115</v>
+        <v>-102</v>
       </c>
       <c r="F9" s="21" t="n">
         <v>25</v>
@@ -37335,7 +37335,7 @@
         </is>
       </c>
       <c r="L9" s="19" t="n">
-        <v>0.098</v>
+        <v>0.1091</v>
       </c>
       <c r="M9" s="19" t="n"/>
       <c r="N9" s="17" t="n"/>
@@ -37353,7 +37353,7 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>TULN @ DUKE</t>
+          <t>BAY @ AUB</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
@@ -37363,11 +37363,11 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>Under 59.5</t>
         </is>
       </c>
       <c r="E10" s="13" t="n">
-        <v>-108</v>
+        <v>-115</v>
       </c>
       <c r="F10" s="16" t="n">
         <v>25</v>
@@ -37395,7 +37395,7 @@
         </is>
       </c>
       <c r="L10" s="14" t="n">
-        <v>0.1029</v>
+        <v>0.098</v>
       </c>
       <c r="M10" s="14" t="n"/>
       <c r="N10" s="12" t="n"/>
@@ -37413,24 +37413,24 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>M-OH @ PITT</t>
+          <t>TULN @ DUKE</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t>M-OH ML</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="E11" s="18" t="n">
-        <v>550</v>
+        <v>-108</v>
       </c>
       <c r="F11" s="21" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G11" s="17" t="inlineStr">
         <is>
@@ -37451,11 +37451,11 @@
       </c>
       <c r="K11" s="17" t="inlineStr">
         <is>
-          <t>GOOD</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="L11" s="19" t="n">
-        <v>0.1283</v>
+        <v>0.1029</v>
       </c>
       <c r="M11" s="19" t="n"/>
       <c r="N11" s="17" t="n"/>
@@ -37473,24 +37473,24 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>BALL @ OSU</t>
+          <t>M-OH @ PITT</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Under 56.5</t>
+          <t>M-OH ML</t>
         </is>
       </c>
       <c r="E12" s="13" t="n">
-        <v>-105</v>
+        <v>550</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>22.5</v>
+        <v>19</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
@@ -37511,11 +37511,11 @@
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>LEAN</t>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="L12" s="14" t="n">
-        <v>0.0886</v>
+        <v>0.1283</v>
       </c>
       <c r="M12" s="14" t="n"/>
       <c r="N12" s="12" t="n"/>
@@ -37533,7 +37533,7 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>UNT @ IU</t>
+          <t>BALL @ OSU</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
@@ -37543,14 +37543,14 @@
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>Over 55.5</t>
+          <t>Under 56.5</t>
         </is>
       </c>
       <c r="E13" s="18" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="F13" s="21" t="n">
-        <v>23.5</v>
+        <v>22.5</v>
       </c>
       <c r="G13" s="17" t="inlineStr">
         <is>
@@ -37575,7 +37575,7 @@
         </is>
       </c>
       <c r="L13" s="19" t="n">
-        <v>0.0898</v>
+        <v>0.0886</v>
       </c>
       <c r="M13" s="19" t="n"/>
       <c r="N13" s="17" t="n"/>
@@ -37593,7 +37593,7 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>OHIO @ NEB</t>
+          <t>UNT @ IU</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -37603,14 +37603,14 @@
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
+          <t>Over 55.5</t>
         </is>
       </c>
       <c r="E14" s="13" t="n">
         <v>-108</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>25</v>
+        <v>23.5</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -37635,7 +37635,7 @@
         </is>
       </c>
       <c r="L14" s="14" t="n">
-        <v>0.1092</v>
+        <v>0.0898</v>
       </c>
       <c r="M14" s="14" t="n"/>
       <c r="N14" s="12" t="n"/>
@@ -37648,12 +37648,12 @@
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>COLO @ GT</t>
+          <t>OHIO @ NEB</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
@@ -37663,14 +37663,14 @@
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
-          <t>Over 50.5</t>
+          <t>Over 47.5</t>
         </is>
       </c>
       <c r="E15" s="18" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="F15" s="21" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G15" s="17" t="inlineStr">
         <is>
@@ -37695,7 +37695,7 @@
         </is>
       </c>
       <c r="L15" s="19" t="n">
-        <v>0.0784</v>
+        <v>0.1092</v>
       </c>
       <c r="M15" s="19" t="n"/>
       <c r="N15" s="17" t="n"/>
@@ -37708,12 +37708,12 @@
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>AKR @ WAKE</t>
+          <t>COLO @ GT</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
@@ -37723,14 +37723,14 @@
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>Over 50.5</t>
         </is>
       </c>
       <c r="E16" s="13" t="n">
-        <v>-112</v>
+        <v>-115</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>24.5</v>
+        <v>21</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -37755,7 +37755,7 @@
         </is>
       </c>
       <c r="L16" s="14" t="n">
-        <v>0.0917</v>
+        <v>0.0784</v>
       </c>
       <c r="M16" s="14" t="n"/>
       <c r="N16" s="12" t="n"/>
@@ -37768,12 +37768,12 @@
     <row r="17">
       <c r="A17" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>HAW @ STAN</t>
+          <t>AKR @ WAKE</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
@@ -37783,14 +37783,14 @@
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E17" s="18" t="n">
-        <v>-105</v>
+        <v>-112</v>
       </c>
       <c r="F17" s="21" t="n">
-        <v>21.5</v>
+        <v>24.5</v>
       </c>
       <c r="G17" s="17" t="inlineStr">
         <is>
@@ -37815,13 +37815,13 @@
         </is>
       </c>
       <c r="L17" s="19" t="n">
-        <v>0.0834</v>
+        <v>0.0917</v>
       </c>
       <c r="M17" s="19" t="n"/>
       <c r="N17" s="17" t="n"/>
       <c r="O17" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>
@@ -37833,24 +37833,24 @@
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>SAC @ EMU</t>
+          <t>HAW @ STAN</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>SAC ML</t>
+          <t>Over 49.5</t>
         </is>
       </c>
       <c r="E18" s="13" t="n">
-        <v>280</v>
+        <v>-105</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>18</v>
+        <v>21.5</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -37875,7 +37875,7 @@
         </is>
       </c>
       <c r="L18" s="14" t="n">
-        <v>0.1055</v>
+        <v>0.0834</v>
       </c>
       <c r="M18" s="14" t="n"/>
       <c r="N18" s="12" t="n"/>
@@ -37893,24 +37893,24 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>SAC @ EMU</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D19" s="17" t="inlineStr">
         <is>
-          <t>UNC +7.5</t>
+          <t>SAC ML</t>
         </is>
       </c>
       <c r="E19" s="18" t="n">
-        <v>-108</v>
+        <v>280</v>
       </c>
       <c r="F19" s="21" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G19" s="17" t="inlineStr">
         <is>
@@ -37935,11 +37935,71 @@
         </is>
       </c>
       <c r="L19" s="19" t="n">
-        <v>0.0801</v>
+        <v>0.1055</v>
       </c>
       <c r="M19" s="19" t="n"/>
       <c r="N19" s="17" t="n"/>
       <c r="O19" s="17" t="inlineStr">
+        <is>
+          <t>Draft Kings</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>UNC @ TCU</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>UNC +7.5</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="n">
+        <v>-108</v>
+      </c>
+      <c r="F20" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H20" s="16">
+        <f>IF(OR($G20="",$G20="Pending"),"",ROUND(IF($G20="Win",IF($E20&gt;0,$F20*$E20/100,$F20*100/-$E20),IF($G20="Loss",-$F20,0)),2))</f>
+        <v/>
+      </c>
+      <c r="I20" s="16">
+        <f>Settings!$B$5+SUM($H$6:$H20)</f>
+        <v/>
+      </c>
+      <c r="J20" s="14">
+        <f>IFERROR(SUM($H$6:$H20)/SUMIF($G$6:$G20,"&lt;&gt;Pending",$F$6:$F20),"")</f>
+        <v/>
+      </c>
+      <c r="K20" s="12" t="inlineStr">
+        <is>
+          <t>LEAN</t>
+        </is>
+      </c>
+      <c r="L20" s="14" t="n">
+        <v>0.0801</v>
+      </c>
+      <c r="M20" s="14" t="n"/>
+      <c r="N20" s="12" t="n"/>
+      <c r="O20" s="12" t="inlineStr">
         <is>
           <t>Draft Kings</t>
         </is>
@@ -44540,16 +44600,16 @@
         </is>
       </c>
       <c r="I5" s="23" t="n">
-        <v>-9.5</v>
+        <v>-8.5</v>
       </c>
       <c r="J5" s="29" t="n">
         <v>46.5</v>
       </c>
       <c r="K5" s="13" t="n">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="L5" s="13" t="n">
-        <v>-360</v>
+        <v>-345</v>
       </c>
       <c r="M5" s="12" t="inlineStr">
         <is>
@@ -44637,7 +44697,7 @@
         <v>-4</v>
       </c>
       <c r="J7" s="29" t="n">
-        <v>51.5</v>
+        <v>50.5</v>
       </c>
       <c r="K7" s="13" t="n">
         <v>150</v>
@@ -44836,10 +44896,10 @@
         <v>53.5</v>
       </c>
       <c r="K11" s="13" t="n">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>-20000</v>
+        <v>-10000</v>
       </c>
       <c r="M11" s="12" t="inlineStr">
         <is>
@@ -45269,10 +45329,10 @@
         <v>50.5</v>
       </c>
       <c r="K20" s="18" t="n">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="L20" s="18" t="n">
-        <v>-258</v>
+        <v>-238</v>
       </c>
       <c r="M20" s="17" t="inlineStr">
         <is>

--- a/NCAAF_Edge_Model.xlsx
+++ b/NCAAF_Edge_Model.xlsx
@@ -640,7 +640,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-28T21:58:27+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
+          <t>Generated 2026-08-29T03:02:44+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>HAW @ STAN</t>
+          <t>FIU @ USF</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>Over 53.5</t>
         </is>
       </c>
       <c r="E29" s="13" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0.09405980478503773</v>
+        <v>0.093264091885228</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>0.6178693285945616</v>
+        <v>0.6281478128154605</v>
       </c>
       <c r="H29" s="16" t="n"/>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
     </row>
@@ -1322,32 +1322,32 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>FIU @ USF</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D30" s="17" t="inlineStr">
         <is>
-          <t>Over 53.5</t>
+          <t>UNC +8.5</t>
         </is>
       </c>
       <c r="E30" s="18" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>0.093264091885228</v>
+        <v>0.08979036342630042</v>
       </c>
       <c r="G30" s="20" t="n">
-        <v>0.6281478128154605</v>
+        <v>0.6135998872358243</v>
       </c>
       <c r="H30" s="21" t="n"/>
       <c r="I30" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
     </row>
@@ -1993,12 +1993,12 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>HAW @ STAN</t>
+          <t>FIU @ USF</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D13" s="22" t="n">
@@ -2011,29 +2011,29 @@
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>Over 53.5</t>
         </is>
       </c>
       <c r="G13" s="23" t="n">
-        <v>48.5</v>
+        <v>53.5</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>0.6178693285945616</v>
+        <v>0.6281478128154605</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L13" s="14" t="n">
-        <v>0.09405980478503773</v>
+        <v>0.093264091885228</v>
       </c>
       <c r="M13" s="14" t="n">
-        <v>0.1795687182259812</v>
+        <v>0.1743633022202087</v>
       </c>
       <c r="N13" s="15" t="n">
         <v>0</v>
@@ -2056,12 +2056,12 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>FIU @ USF</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D14" s="25" t="n">
@@ -2069,34 +2069,34 @@
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t>Over 53.5</t>
+          <t>UNC +8.5</t>
         </is>
       </c>
       <c r="G14" s="26" t="n">
-        <v>53.5</v>
+        <v>-8.5</v>
       </c>
       <c r="H14" s="18" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="I14" s="20" t="n">
-        <v>0.6281478128154605</v>
+        <v>0.6135998872358243</v>
       </c>
       <c r="J14" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5</v>
       </c>
       <c r="K14" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L14" s="19" t="n">
-        <v>0.093264091885228</v>
+        <v>0.08979036342630042</v>
       </c>
       <c r="M14" s="19" t="n">
-        <v>0.1743633022202087</v>
+        <v>0.1714179665411191</v>
       </c>
       <c r="N14" s="20" t="n">
         <v>0</v>
@@ -3256,12 +3256,12 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>HAMP @ MD</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-09-06 00:00</t>
         </is>
       </c>
       <c r="D32" s="25" t="n">
@@ -3274,35 +3274,35 @@
       </c>
       <c r="F32" s="17" t="inlineStr">
         <is>
-          <t>SJSU +38.5</t>
+          <t>HAMP +45.5</t>
         </is>
       </c>
       <c r="G32" s="26" t="n">
-        <v>-38.5</v>
+        <v>-45.5</v>
       </c>
       <c r="H32" s="18" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="I32" s="20" t="n">
-        <v>0.7476789160487953</v>
+        <v>0.7520172898132291</v>
       </c>
       <c r="J32" s="20" t="n">
-        <v>0.5</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K32" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L32" s="19" t="n">
-        <v>0.2238693922392715</v>
+        <v>0.2237154030207763</v>
       </c>
       <c r="M32" s="19" t="n">
-        <v>0.4273870215477003</v>
+        <v>0.4234612985750408</v>
       </c>
       <c r="N32" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O32" s="27" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="P32" s="17" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="Q32" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>HAMP isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -3323,12 +3323,12 @@
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>HAMP @ MD</t>
+          <t>BALL @ OSU</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00</t>
+          <t>2026-09-05 16:30</t>
         </is>
       </c>
       <c r="D33" s="22" t="n">
@@ -3341,17 +3341,17 @@
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>HAMP +45.5</t>
+          <t>BALL +50.5</t>
         </is>
       </c>
       <c r="G33" s="23" t="n">
-        <v>-45.5</v>
+        <v>-50.5</v>
       </c>
       <c r="H33" s="13" t="n">
         <v>-112</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>0.7520172898132291</v>
+        <v>0.7519654142724952</v>
       </c>
       <c r="J33" s="15" t="n">
         <v>0.5043297540699688</v>
@@ -3360,16 +3360,16 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L33" s="14" t="n">
-        <v>0.2237154030207763</v>
+        <v>0.2236635274800424</v>
       </c>
       <c r="M33" s="14" t="n">
-        <v>0.4234612985750408</v>
+        <v>0.423363105587223</v>
       </c>
       <c r="N33" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O33" s="24" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="P33" s="12" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="Q33" s="12" t="inlineStr">
         <is>
-          <t>HAMP isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -3390,12 +3390,12 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>BALL @ OSU</t>
+          <t>EIU @ MINN</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 16:30</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D34" s="25" t="n">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="F34" s="17" t="inlineStr">
         <is>
-          <t>BALL +50.5</t>
+          <t>EIU +43.5</t>
         </is>
       </c>
       <c r="G34" s="26" t="n">
-        <v>-50.5</v>
+        <v>-43.5</v>
       </c>
       <c r="H34" s="18" t="n">
         <v>-112</v>
       </c>
       <c r="I34" s="20" t="n">
-        <v>0.7519654142724952</v>
+        <v>0.7518231737767994</v>
       </c>
       <c r="J34" s="20" t="n">
         <v>0.5043297540699688</v>
@@ -3427,10 +3427,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L34" s="19" t="n">
-        <v>0.2236635274800424</v>
+        <v>0.2235212869843466</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>0.423363105587223</v>
+        <v>0.4230938646489417</v>
       </c>
       <c r="N34" s="20" t="n">
         <v>0</v>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="Q34" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>EIU @ MINN</t>
+          <t>UNA @ ARK</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-09-05 20:15</t>
         </is>
       </c>
       <c r="D35" s="22" t="n">
@@ -3475,17 +3475,17 @@
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>EIU +43.5</t>
+          <t>UNA +40.5</t>
         </is>
       </c>
       <c r="G35" s="23" t="n">
-        <v>-43.5</v>
+        <v>-40.5</v>
       </c>
       <c r="H35" s="13" t="n">
         <v>-112</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>0.7518231737767994</v>
+        <v>0.7514996793539089</v>
       </c>
       <c r="J35" s="15" t="n">
         <v>0.5043297540699688</v>
@@ -3494,10 +3494,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L35" s="14" t="n">
-        <v>0.2235212869843466</v>
+        <v>0.2231977925614561</v>
       </c>
       <c r="M35" s="14" t="n">
-        <v>0.4230938646489417</v>
+        <v>0.422481535919899</v>
       </c>
       <c r="N35" s="15" t="n">
         <v>0</v>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Q35" s="12" t="inlineStr">
         <is>
-          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>UNA isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -3524,12 +3524,12 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>UNA @ ARK</t>
+          <t>WMU @ MICH</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 20:15</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D36" s="25" t="n">
@@ -3542,29 +3542,29 @@
       </c>
       <c r="F36" s="17" t="inlineStr">
         <is>
-          <t>UNA +40.5</t>
+          <t>WMU +27.5</t>
         </is>
       </c>
       <c r="G36" s="26" t="n">
-        <v>-40.5</v>
+        <v>-27.5</v>
       </c>
       <c r="H36" s="18" t="n">
-        <v>-112</v>
+        <v>-105</v>
       </c>
       <c r="I36" s="20" t="n">
-        <v>0.7514996793539089</v>
+        <v>0.7345065169441323</v>
       </c>
       <c r="J36" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K36" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L36" s="19" t="n">
-        <v>0.2231977925614561</v>
+        <v>0.2223113949929127</v>
       </c>
       <c r="M36" s="19" t="n">
-        <v>0.422481535919899</v>
+        <v>0.4340365330814011</v>
       </c>
       <c r="N36" s="20" t="n">
         <v>0</v>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="Q36" s="17" t="inlineStr">
         <is>
-          <t>UNA isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -3591,12 +3591,12 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>WMU @ MICH</t>
+          <t>IDHO @ UTAH</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D37" s="22" t="n">
@@ -3609,29 +3609,29 @@
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>WMU +27.5</t>
+          <t>IDHO +33.5</t>
         </is>
       </c>
       <c r="G37" s="23" t="n">
-        <v>-27.5</v>
+        <v>-33.5</v>
       </c>
       <c r="H37" s="13" t="n">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>0.7345065169441323</v>
+        <v>0.7414791527526444</v>
       </c>
       <c r="J37" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K37" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L37" s="14" t="n">
-        <v>0.2223113949929127</v>
+        <v>0.2222483835218751</v>
       </c>
       <c r="M37" s="14" t="n">
-        <v>0.4340365330814011</v>
+        <v>0.4280339238199079</v>
       </c>
       <c r="N37" s="15" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="Q37" s="12" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -3658,12 +3658,12 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>IDHO @ UTAH</t>
+          <t>KENT @ SC</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 01:00</t>
+          <t>2026-09-05 16:45</t>
         </is>
       </c>
       <c r="D38" s="25" t="n">
@@ -3676,29 +3676,29 @@
       </c>
       <c r="F38" s="17" t="inlineStr">
         <is>
-          <t>IDHO +33.5</t>
+          <t>KENT +36.5</t>
         </is>
       </c>
       <c r="G38" s="26" t="n">
-        <v>-33.5</v>
+        <v>-36.5</v>
       </c>
       <c r="H38" s="18" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I38" s="20" t="n">
-        <v>0.7414791527526444</v>
+        <v>0.7500631386431562</v>
       </c>
       <c r="J38" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K38" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>0.2222483835218751</v>
+        <v>0.2217612518507034</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>0.4280339238199079</v>
+        <v>0.4197623695745456</v>
       </c>
       <c r="N38" s="20" t="n">
         <v>0</v>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="Q38" s="17" t="inlineStr">
         <is>
-          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -3725,12 +3725,12 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>KENT @ SC</t>
+          <t>BRY @ ARMY</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 16:45</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D39" s="22" t="n">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>KENT +36.5</t>
+          <t>BRY +36.5</t>
         </is>
       </c>
       <c r="G39" s="23" t="n">
@@ -3753,7 +3753,7 @@
         <v>-112</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>0.7500631386431562</v>
+        <v>0.7499321602477051</v>
       </c>
       <c r="J39" s="15" t="n">
         <v>0.5043297540699688</v>
@@ -3762,10 +3762,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L39" s="14" t="n">
-        <v>0.2217612518507034</v>
+        <v>0.2216302734552523</v>
       </c>
       <c r="M39" s="14" t="n">
-        <v>0.4197623695745456</v>
+        <v>0.4195144461831561</v>
       </c>
       <c r="N39" s="15" t="n">
         <v>0</v>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="Q39" s="12" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>BRY isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -3792,12 +3792,12 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>BRY @ ARMY</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D40" s="25" t="n">
@@ -3810,17 +3810,17 @@
       </c>
       <c r="F40" s="17" t="inlineStr">
         <is>
-          <t>BRY +36.5</t>
+          <t>SJSU +38.5</t>
         </is>
       </c>
       <c r="G40" s="26" t="n">
-        <v>-36.5</v>
+        <v>-38.5</v>
       </c>
       <c r="H40" s="18" t="n">
         <v>-112</v>
       </c>
       <c r="I40" s="20" t="n">
-        <v>0.7499321602477051</v>
+        <v>0.7498437930837798</v>
       </c>
       <c r="J40" s="20" t="n">
         <v>0.5043297540699688</v>
@@ -3829,10 +3829,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L40" s="19" t="n">
-        <v>0.2216302734552523</v>
+        <v>0.221541906291327</v>
       </c>
       <c r="M40" s="19" t="n">
-        <v>0.4195144461831561</v>
+        <v>0.419347179765726</v>
       </c>
       <c r="N40" s="20" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
       </c>
       <c r="Q40" s="17" t="inlineStr">
         <is>
-          <t>BRY isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -10467,12 +10467,12 @@
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t>CLEM @ LSU</t>
+          <t>URI @ TEM</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-09-05 18:00</t>
         </is>
       </c>
       <c r="D141" s="22" t="n">
@@ -10480,34 +10480,32 @@
       </c>
       <c r="E141" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F141" s="12" t="inlineStr">
         <is>
-          <t>CLEM +10.5</t>
-        </is>
-      </c>
-      <c r="G141" s="23" t="n">
-        <v>-10.5</v>
-      </c>
+          <t>URI ML</t>
+        </is>
+      </c>
+      <c r="G141" s="23" t="n"/>
       <c r="H141" s="13" t="n">
-        <v>-110</v>
+        <v>410</v>
       </c>
       <c r="I141" s="15" t="n">
-        <v>0.6424786609670081</v>
+        <v>0.3160728518625565</v>
       </c>
       <c r="J141" s="15" t="n">
-        <v>0.5</v>
+        <v>0.1881331403762663</v>
       </c>
       <c r="K141" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.196078431372549</v>
       </c>
       <c r="L141" s="14" t="n">
-        <v>0.1186691371574843</v>
+        <v>0.1199944204900075</v>
       </c>
       <c r="M141" s="14" t="n">
-        <v>0.2265501709370156</v>
+        <v>0.611971544499038</v>
       </c>
       <c r="N141" s="15" t="n">
         <v>0</v>
@@ -10522,7 +10520,7 @@
       </c>
       <c r="Q141" s="12" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>URI isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -10534,12 +10532,12 @@
       </c>
       <c r="B142" s="17" t="inlineStr">
         <is>
-          <t>SDST @ NU</t>
+          <t>CLEM @ LSU</t>
         </is>
       </c>
       <c r="C142" s="17" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D142" s="25" t="n">
@@ -10547,32 +10545,34 @@
       </c>
       <c r="E142" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F142" s="17" t="inlineStr">
         <is>
-          <t>SDST ML</t>
-        </is>
-      </c>
-      <c r="G142" s="26" t="n"/>
+          <t>CLEM +10.5</t>
+        </is>
+      </c>
+      <c r="G142" s="26" t="n">
+        <v>-10.5</v>
+      </c>
       <c r="H142" s="18" t="n">
-        <v>500</v>
+        <v>-110</v>
       </c>
       <c r="I142" s="20" t="n">
-        <v>0.2841604384822952</v>
+        <v>0.6424786609670081</v>
       </c>
       <c r="J142" s="20" t="n">
-        <v>0.16</v>
+        <v>0.5</v>
       </c>
       <c r="K142" s="20" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L142" s="19" t="n">
-        <v>0.1174937718156286</v>
+        <v>0.1186691371574843</v>
       </c>
       <c r="M142" s="19" t="n">
-        <v>0.7049626308937714</v>
+        <v>0.2265501709370156</v>
       </c>
       <c r="N142" s="20" t="n">
         <v>0</v>
@@ -10587,7 +10587,7 @@
       </c>
       <c r="Q142" s="17" t="inlineStr">
         <is>
-          <t>SDST isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -10599,12 +10599,12 @@
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t>SAC @ EMU</t>
+          <t>SDST @ NU</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 22:30</t>
+          <t>2026-09-06 00:00</t>
         </is>
       </c>
       <c r="D143" s="22" t="n">
@@ -10612,34 +10612,32 @@
       </c>
       <c r="E143" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F143" s="12" t="inlineStr">
         <is>
-          <t>SAC +9.5</t>
-        </is>
-      </c>
-      <c r="G143" s="23" t="n">
-        <v>-9.5</v>
-      </c>
+          <t>SDST ML</t>
+        </is>
+      </c>
+      <c r="G143" s="23" t="n"/>
       <c r="H143" s="13" t="n">
-        <v>-108</v>
+        <v>500</v>
       </c>
       <c r="I143" s="15" t="n">
-        <v>0.6351393318756373</v>
+        <v>0.2841604384822952</v>
       </c>
       <c r="J143" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.16</v>
       </c>
       <c r="K143" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="L143" s="14" t="n">
-        <v>0.115908562644868</v>
+        <v>0.1174937718156286</v>
       </c>
       <c r="M143" s="14" t="n">
-        <v>0.2232313058345609</v>
+        <v>0.7049626308937714</v>
       </c>
       <c r="N143" s="15" t="n">
         <v>0</v>
@@ -10654,7 +10652,7 @@
       </c>
       <c r="Q143" s="12" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>SDST isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -10798,12 +10796,12 @@
       </c>
       <c r="B146" s="17" t="inlineStr">
         <is>
-          <t>IDST @ USU</t>
+          <t>URI @ TEM</t>
         </is>
       </c>
       <c r="C146" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-05 18:00</t>
         </is>
       </c>
       <c r="D146" s="25" t="n">
@@ -10811,32 +10809,34 @@
       </c>
       <c r="E146" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F146" s="17" t="inlineStr">
         <is>
-          <t>IDST ML</t>
-        </is>
-      </c>
-      <c r="G146" s="26" t="n"/>
+          <t>URI +10.5</t>
+        </is>
+      </c>
+      <c r="G146" s="26" t="n">
+        <v>-10.5</v>
+      </c>
       <c r="H146" s="18" t="n">
-        <v>410</v>
+        <v>-112</v>
       </c>
       <c r="I146" s="20" t="n">
-        <v>0.3069727771901823</v>
+        <v>0.6399010968538523</v>
       </c>
       <c r="J146" s="20" t="n">
-        <v>0.1881331403762663</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K146" s="20" t="n">
-        <v>0.196078431372549</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L146" s="19" t="n">
-        <v>0.1108943458176333</v>
+        <v>0.1115992100613995</v>
       </c>
       <c r="M146" s="19" t="n">
-        <v>0.5655611636699299</v>
+        <v>0.2112413619019348</v>
       </c>
       <c r="N146" s="20" t="n">
         <v>0</v>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="Q146" s="17" t="inlineStr">
         <is>
-          <t>IDST isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>URI isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -10863,12 +10863,12 @@
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t>URI @ TEM</t>
+          <t>IDST @ USU</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 18:00</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D147" s="22" t="n">
@@ -10881,27 +10881,27 @@
       </c>
       <c r="F147" s="12" t="inlineStr">
         <is>
-          <t>URI ML</t>
+          <t>IDST ML</t>
         </is>
       </c>
       <c r="G147" s="23" t="n"/>
       <c r="H147" s="13" t="n">
-        <v>360</v>
+        <v>410</v>
       </c>
       <c r="I147" s="15" t="n">
-        <v>0.3263254617622711</v>
+        <v>0.3069727771901823</v>
       </c>
       <c r="J147" s="15" t="n">
-        <v>0.2086383601756955</v>
+        <v>0.1881331403762663</v>
       </c>
       <c r="K147" s="15" t="n">
-        <v>0.2173913043478261</v>
+        <v>0.196078431372549</v>
       </c>
       <c r="L147" s="14" t="n">
-        <v>0.108934157414445</v>
+        <v>0.1108943458176333</v>
       </c>
       <c r="M147" s="14" t="n">
-        <v>0.5010971241064468</v>
+        <v>0.5655611636699299</v>
       </c>
       <c r="N147" s="15" t="n">
         <v>0</v>
@@ -10916,7 +10916,7 @@
       </c>
       <c r="Q147" s="12" t="inlineStr">
         <is>
-          <t>URI isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>IDST isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -10995,12 +10995,12 @@
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t>URI @ TEM</t>
+          <t>SAC @ EMU</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 18:00</t>
+          <t>2026-08-29 22:30</t>
         </is>
       </c>
       <c r="D149" s="22" t="n">
@@ -11013,32 +11013,32 @@
       </c>
       <c r="F149" s="12" t="inlineStr">
         <is>
-          <t>URI +10</t>
+          <t>SAC +9.5</t>
         </is>
       </c>
       <c r="G149" s="23" t="n">
-        <v>-10</v>
+        <v>-9.5</v>
       </c>
       <c r="H149" s="13" t="n">
-        <v>-112</v>
+        <v>-115</v>
       </c>
       <c r="I149" s="15" t="n">
-        <v>0.6360461103075994</v>
+        <v>0.6427213270037963</v>
       </c>
       <c r="J149" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K149" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L149" s="14" t="n">
-        <v>0.1077442235151466</v>
+        <v>0.1078376060735637</v>
       </c>
       <c r="M149" s="14" t="n">
-        <v>0.1971737431196206</v>
+        <v>0.2016094374418799</v>
       </c>
       <c r="N149" s="15" t="n">
-        <v>0.0332</v>
+        <v>0</v>
       </c>
       <c r="O149" s="24" t="n">
         <v>0.45</v>
@@ -11050,7 +11050,7 @@
       </c>
       <c r="Q149" s="12" t="inlineStr">
         <is>
-          <t>URI isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>model and market are too far apart for a reliable early-season play</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="B152" s="17" t="inlineStr">
         <is>
-          <t>ALCN @ USM</t>
+          <t>URI @ TEM</t>
         </is>
       </c>
       <c r="C152" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 21:00</t>
+          <t>2026-09-05 18:00</t>
         </is>
       </c>
       <c r="D152" s="25" t="n">
@@ -11214,29 +11214,29 @@
       </c>
       <c r="F152" s="17" t="inlineStr">
         <is>
-          <t>Over 50.5</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="G152" s="26" t="n">
-        <v>50.5</v>
+        <v>51.5</v>
       </c>
       <c r="H152" s="18" t="n">
-        <v>-112</v>
+        <v>-105</v>
       </c>
       <c r="I152" s="20" t="n">
-        <v>0.6264949544829508</v>
+        <v>0.6124522056927323</v>
       </c>
       <c r="J152" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K152" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L152" s="19" t="n">
-        <v>0.09819306769049796</v>
+        <v>0.1002570837415128</v>
       </c>
       <c r="M152" s="19" t="n">
-        <v>0.1858654495570139</v>
+        <v>0.1957400206381916</v>
       </c>
       <c r="N152" s="20" t="n">
         <v>0</v>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="Q152" s="17" t="inlineStr">
         <is>
-          <t>ALCN isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>URI isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -11263,12 +11263,12 @@
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t>YSU @ UK</t>
+          <t>ALCN @ USM</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 17:00</t>
+          <t>2026-09-05 21:00</t>
         </is>
       </c>
       <c r="D153" s="22" t="n">
@@ -11281,29 +11281,29 @@
       </c>
       <c r="F153" s="12" t="inlineStr">
         <is>
-          <t>Under 62.5</t>
+          <t>Over 50.5</t>
         </is>
       </c>
       <c r="G153" s="23" t="n">
-        <v>62.5</v>
+        <v>50.5</v>
       </c>
       <c r="H153" s="13" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="I153" s="15" t="n">
-        <v>0.6211207123338132</v>
+        <v>0.6264949544829508</v>
       </c>
       <c r="J153" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K153" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L153" s="14" t="n">
-        <v>0.09731118852428933</v>
+        <v>0.09819306769049796</v>
       </c>
       <c r="M153" s="14" t="n">
-        <v>0.1857759053645525</v>
+        <v>0.1858654495570139</v>
       </c>
       <c r="N153" s="15" t="n">
         <v>0</v>
@@ -11318,7 +11318,7 @@
       </c>
       <c r="Q153" s="12" t="inlineStr">
         <is>
-          <t>YSU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>ALCN isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -11330,12 +11330,12 @@
       </c>
       <c r="B154" s="17" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>YSU @ UK</t>
         </is>
       </c>
       <c r="C154" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-09-05 17:00</t>
         </is>
       </c>
       <c r="D154" s="25" t="n">
@@ -11343,34 +11343,34 @@
       </c>
       <c r="E154" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F154" s="17" t="inlineStr">
         <is>
-          <t>UNC +8.5</t>
+          <t>Under 62.5</t>
         </is>
       </c>
       <c r="G154" s="26" t="n">
-        <v>-8.5</v>
+        <v>62.5</v>
       </c>
       <c r="H154" s="18" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I154" s="20" t="n">
-        <v>0.6114350102008398</v>
+        <v>0.6211207123338132</v>
       </c>
       <c r="J154" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5</v>
       </c>
       <c r="K154" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L154" s="19" t="n">
-        <v>0.09220424097007052</v>
+        <v>0.09731118852428933</v>
       </c>
       <c r="M154" s="19" t="n">
-        <v>0.1775785381645804</v>
+        <v>0.1857759053645525</v>
       </c>
       <c r="N154" s="20" t="n">
         <v>0</v>
@@ -11385,7 +11385,7 @@
       </c>
       <c r="Q154" s="17" t="inlineStr">
         <is>
-          <t>outside the top 10 plays for this week</t>
+          <t>YSU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -11397,12 +11397,12 @@
       </c>
       <c r="B155" s="12" t="inlineStr">
         <is>
-          <t>URI @ TEM</t>
+          <t>HAW @ STAN</t>
         </is>
       </c>
       <c r="C155" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 18:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D155" s="22" t="n">
@@ -11415,29 +11415,29 @@
       </c>
       <c r="F155" s="12" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="G155" s="23" t="n">
-        <v>51.5</v>
+        <v>48.5</v>
       </c>
       <c r="H155" s="13" t="n">
-        <v>-112</v>
+        <v>-115</v>
       </c>
       <c r="I155" s="15" t="n">
-        <v>0.6200342008208912</v>
+        <v>0.6232864466877359</v>
       </c>
       <c r="J155" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K155" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L155" s="14" t="n">
-        <v>0.0917323140284384</v>
+        <v>0.08840272575750341</v>
       </c>
       <c r="M155" s="14" t="n">
-        <v>0.1736361658395441</v>
+        <v>0.1652746611988105</v>
       </c>
       <c r="N155" s="15" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="Q155" s="12" t="inlineStr">
         <is>
-          <t>URI isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>outside the top 10 plays for this week</t>
         </is>
       </c>
     </row>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="B158" s="17" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>NCAT @ GAST</t>
         </is>
       </c>
       <c r="C158" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-09-04 23:00</t>
         </is>
       </c>
       <c r="D158" s="25" t="n">
@@ -11611,32 +11611,34 @@
       </c>
       <c r="E158" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F158" s="17" t="inlineStr">
         <is>
-          <t>UNC ML</t>
-        </is>
-      </c>
-      <c r="G158" s="26" t="n"/>
+          <t>Under 63.5</t>
+        </is>
+      </c>
+      <c r="G158" s="26" t="n">
+        <v>63.5</v>
+      </c>
       <c r="H158" s="18" t="n">
-        <v>275</v>
+        <v>-110</v>
       </c>
       <c r="I158" s="20" t="n">
-        <v>0.3529707493110541</v>
+        <v>0.6095621194091961</v>
       </c>
       <c r="J158" s="20" t="n">
-        <v>0.2559309849029475</v>
+        <v>0.5</v>
       </c>
       <c r="K158" s="20" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L158" s="19" t="n">
-        <v>0.08630408264438744</v>
+        <v>0.0857525955996723</v>
       </c>
       <c r="M158" s="19" t="n">
-        <v>0.3236403099164529</v>
+        <v>0.1637095006902836</v>
       </c>
       <c r="N158" s="20" t="n">
         <v>0</v>
@@ -11651,7 +11653,7 @@
       </c>
       <c r="Q158" s="17" t="inlineStr">
         <is>
-          <t>correlated with a stronger play on the same game</t>
+          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -11663,12 +11665,12 @@
       </c>
       <c r="B159" s="12" t="inlineStr">
         <is>
-          <t>NCAT @ GAST</t>
+          <t>TULN @ DUKE</t>
         </is>
       </c>
       <c r="C159" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 23:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D159" s="22" t="n">
@@ -11676,34 +11678,32 @@
       </c>
       <c r="E159" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F159" s="12" t="inlineStr">
         <is>
-          <t>Under 63.5</t>
-        </is>
-      </c>
-      <c r="G159" s="23" t="n">
-        <v>63.5</v>
-      </c>
+          <t>TULN ML</t>
+        </is>
+      </c>
+      <c r="G159" s="23" t="n"/>
       <c r="H159" s="13" t="n">
-        <v>-110</v>
+        <v>300</v>
       </c>
       <c r="I159" s="15" t="n">
-        <v>0.6095621194091961</v>
+        <v>0.3354589358801325</v>
       </c>
       <c r="J159" s="15" t="n">
-        <v>0.5</v>
+        <v>0.24</v>
       </c>
       <c r="K159" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.25</v>
       </c>
       <c r="L159" s="14" t="n">
-        <v>0.0857525955996723</v>
+        <v>0.08545893588013254</v>
       </c>
       <c r="M159" s="14" t="n">
-        <v>0.1637095006902836</v>
+        <v>0.3418357435205301</v>
       </c>
       <c r="N159" s="15" t="n">
         <v>0</v>
@@ -11718,7 +11718,7 @@
       </c>
       <c r="Q159" s="12" t="inlineStr">
         <is>
-          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>correlated with a stronger play on the same game</t>
         </is>
       </c>
     </row>
@@ -11730,12 +11730,12 @@
       </c>
       <c r="B160" s="17" t="inlineStr">
         <is>
-          <t>TULN @ DUKE</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C160" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D160" s="25" t="n">
@@ -11748,27 +11748,27 @@
       </c>
       <c r="F160" s="17" t="inlineStr">
         <is>
-          <t>TULN ML</t>
+          <t>UNC ML</t>
         </is>
       </c>
       <c r="G160" s="26" t="n"/>
       <c r="H160" s="18" t="n">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="I160" s="20" t="n">
-        <v>0.3354589358801325</v>
+        <v>0.3545694500280139</v>
       </c>
       <c r="J160" s="20" t="n">
-        <v>0.24</v>
+        <v>0.2591283863368669</v>
       </c>
       <c r="K160" s="20" t="n">
-        <v>0.25</v>
+        <v>0.2702702702702703</v>
       </c>
       <c r="L160" s="19" t="n">
-        <v>0.08545893588013254</v>
+        <v>0.08429917975774359</v>
       </c>
       <c r="M160" s="19" t="n">
-        <v>0.3418357435205301</v>
+        <v>0.3119069651036515</v>
       </c>
       <c r="N160" s="20" t="n">
         <v>0</v>
@@ -13304,12 +13304,12 @@
       </c>
       <c r="B184" s="17" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>ACU @ TTU</t>
         </is>
       </c>
       <c r="C184" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D184" s="25" t="n">
@@ -13322,29 +13322,29 @@
       </c>
       <c r="F184" s="17" t="inlineStr">
         <is>
-          <t>Under 61.5</t>
+          <t>Under 59.5</t>
         </is>
       </c>
       <c r="G184" s="26" t="n">
-        <v>61.5</v>
+        <v>59.5</v>
       </c>
       <c r="H184" s="18" t="n">
-        <v>-108</v>
+        <v>-115</v>
       </c>
       <c r="I184" s="20" t="n">
-        <v>0.57924574575779</v>
+        <v>0.5922733326643557</v>
       </c>
       <c r="J184" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K184" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L184" s="19" t="n">
-        <v>0.0600149765270207</v>
+        <v>0.05738961173412316</v>
       </c>
       <c r="M184" s="19" t="n">
-        <v>0.1155843992372252</v>
+        <v>0.1072936219377083</v>
       </c>
       <c r="N184" s="20" t="n">
         <v>0</v>
@@ -13357,7 +13357,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q184" s="17" t="n"/>
+      <c r="Q184" s="17" t="inlineStr">
+        <is>
+          <t>ACU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="12" t="inlineStr">
@@ -13367,12 +13371,12 @@
       </c>
       <c r="B185" s="12" t="inlineStr">
         <is>
-          <t>ACU @ TTU</t>
+          <t>TOL @ MSU</t>
         </is>
       </c>
       <c r="C185" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-05 00:00</t>
         </is>
       </c>
       <c r="D185" s="22" t="n">
@@ -13385,29 +13389,29 @@
       </c>
       <c r="F185" s="12" t="inlineStr">
         <is>
-          <t>Under 59.5</t>
+          <t>Over 49.5</t>
         </is>
       </c>
       <c r="G185" s="23" t="n">
-        <v>59.5</v>
+        <v>49.5</v>
       </c>
       <c r="H185" s="13" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="I185" s="15" t="n">
-        <v>0.5922733326643557</v>
+        <v>0.5755767191857057</v>
       </c>
       <c r="J185" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K185" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L185" s="14" t="n">
-        <v>0.05738961173412316</v>
+        <v>0.05634594995493647</v>
       </c>
       <c r="M185" s="14" t="n">
-        <v>0.1072936219377083</v>
+        <v>0.108518125839137</v>
       </c>
       <c r="N185" s="15" t="n">
         <v>0</v>
@@ -13420,11 +13424,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q185" s="12" t="inlineStr">
-        <is>
-          <t>ACU isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q185" s="12" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="17" t="inlineStr">
@@ -13434,12 +13434,12 @@
       </c>
       <c r="B186" s="17" t="inlineStr">
         <is>
-          <t>TOL @ MSU</t>
+          <t>BOIS @ ORE</t>
         </is>
       </c>
       <c r="C186" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 00:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D186" s="25" t="n">
@@ -13452,29 +13452,29 @@
       </c>
       <c r="F186" s="17" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="G186" s="26" t="n">
-        <v>49.5</v>
+        <v>51.5</v>
       </c>
       <c r="H186" s="18" t="n">
-        <v>-108</v>
+        <v>-118</v>
       </c>
       <c r="I186" s="20" t="n">
-        <v>0.5755767191857057</v>
+        <v>0.5973374319201017</v>
       </c>
       <c r="J186" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5173641257162701</v>
       </c>
       <c r="K186" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5412844036697247</v>
       </c>
       <c r="L186" s="19" t="n">
-        <v>0.05634594995493647</v>
+        <v>0.05605302825037695</v>
       </c>
       <c r="M186" s="19" t="n">
-        <v>0.108518125839137</v>
+        <v>0.1035555945642557</v>
       </c>
       <c r="N186" s="20" t="n">
         <v>0</v>
@@ -13497,12 +13497,12 @@
       </c>
       <c r="B187" s="12" t="inlineStr">
         <is>
-          <t>BOIS @ ORE</t>
+          <t>UNLV @ HAW</t>
         </is>
       </c>
       <c r="C187" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-06 02:00</t>
         </is>
       </c>
       <c r="D187" s="22" t="n">
@@ -13510,37 +13510,37 @@
       </c>
       <c r="E187" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F187" s="12" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>HAW +3</t>
         </is>
       </c>
       <c r="G187" s="23" t="n">
-        <v>51.5</v>
+        <v>3</v>
       </c>
       <c r="H187" s="13" t="n">
-        <v>-118</v>
+        <v>-108</v>
       </c>
       <c r="I187" s="15" t="n">
-        <v>0.5973374319201017</v>
+        <v>0.5752024326373151</v>
       </c>
       <c r="J187" s="15" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K187" s="15" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L187" s="14" t="n">
-        <v>0.05605302825037695</v>
+        <v>0.0559716634065458</v>
       </c>
       <c r="M187" s="14" t="n">
-        <v>0.1035555945642557</v>
+        <v>0.1016809753962156</v>
       </c>
       <c r="N187" s="15" t="n">
-        <v>0</v>
+        <v>0.0567</v>
       </c>
       <c r="O187" s="24" t="n">
         <v>0.45</v>
@@ -13560,12 +13560,12 @@
       </c>
       <c r="B188" s="17" t="inlineStr">
         <is>
-          <t>UNLV @ HAW</t>
+          <t>ARST @ MEM</t>
         </is>
       </c>
       <c r="C188" s="17" t="inlineStr">
         <is>
-          <t>2026-09-06 02:00</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D188" s="25" t="n">
@@ -13573,37 +13573,35 @@
       </c>
       <c r="E188" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F188" s="17" t="inlineStr">
         <is>
-          <t>HAW +3</t>
-        </is>
-      </c>
-      <c r="G188" s="26" t="n">
-        <v>3</v>
-      </c>
+          <t>ARST ML</t>
+        </is>
+      </c>
+      <c r="G188" s="26" t="n"/>
       <c r="H188" s="18" t="n">
-        <v>-108</v>
+        <v>250</v>
       </c>
       <c r="I188" s="20" t="n">
-        <v>0.5752024326373151</v>
+        <v>0.3401615480236082</v>
       </c>
       <c r="J188" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.274247491638796</v>
       </c>
       <c r="K188" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="L188" s="19" t="n">
-        <v>0.0559716634065458</v>
+        <v>0.05444726230932251</v>
       </c>
       <c r="M188" s="19" t="n">
-        <v>0.1016809753962156</v>
+        <v>0.1905654180826287</v>
       </c>
       <c r="N188" s="20" t="n">
-        <v>0.0567</v>
+        <v>0</v>
       </c>
       <c r="O188" s="27" t="n">
         <v>0.45</v>
@@ -13623,12 +13621,12 @@
       </c>
       <c r="B189" s="12" t="inlineStr">
         <is>
-          <t>ARST @ MEM</t>
+          <t>BC @ CIN</t>
         </is>
       </c>
       <c r="C189" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D189" s="22" t="n">
@@ -13636,32 +13634,34 @@
       </c>
       <c r="E189" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F189" s="12" t="inlineStr">
         <is>
-          <t>ARST ML</t>
-        </is>
-      </c>
-      <c r="G189" s="23" t="n"/>
+          <t>BC +7.5</t>
+        </is>
+      </c>
+      <c r="G189" s="23" t="n">
+        <v>-7.5</v>
+      </c>
       <c r="H189" s="13" t="n">
-        <v>250</v>
+        <v>-112</v>
       </c>
       <c r="I189" s="15" t="n">
-        <v>0.3401615480236082</v>
+        <v>0.5824793144711614</v>
       </c>
       <c r="J189" s="15" t="n">
-        <v>0.274247491638796</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K189" s="15" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L189" s="14" t="n">
-        <v>0.05444726230932251</v>
+        <v>0.05417742767870859</v>
       </c>
       <c r="M189" s="14" t="n">
-        <v>0.1905654180826287</v>
+        <v>0.1025501309632698</v>
       </c>
       <c r="N189" s="15" t="n">
         <v>0</v>
@@ -13697,34 +13697,32 @@
       </c>
       <c r="E190" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F190" s="17" t="inlineStr">
         <is>
-          <t>BC +7.5</t>
-        </is>
-      </c>
-      <c r="G190" s="26" t="n">
-        <v>-7.5</v>
-      </c>
+          <t>BC ML</t>
+        </is>
+      </c>
+      <c r="G190" s="26" t="n"/>
       <c r="H190" s="18" t="n">
-        <v>-112</v>
+        <v>250</v>
       </c>
       <c r="I190" s="20" t="n">
-        <v>0.5824793144711614</v>
+        <v>0.3389003135487954</v>
       </c>
       <c r="J190" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.274247491638796</v>
       </c>
       <c r="K190" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="L190" s="19" t="n">
-        <v>0.05417742767870859</v>
+        <v>0.05318602783450965</v>
       </c>
       <c r="M190" s="19" t="n">
-        <v>0.1025501309632698</v>
+        <v>0.1861510974207837</v>
       </c>
       <c r="N190" s="20" t="n">
         <v>0</v>
@@ -13747,12 +13745,12 @@
       </c>
       <c r="B191" s="12" t="inlineStr">
         <is>
-          <t>BC @ CIN</t>
+          <t>WMU @ MICH</t>
         </is>
       </c>
       <c r="C191" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D191" s="22" t="n">
@@ -13760,32 +13758,34 @@
       </c>
       <c r="E191" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F191" s="12" t="inlineStr">
         <is>
-          <t>BC ML</t>
-        </is>
-      </c>
-      <c r="G191" s="23" t="n"/>
+          <t>Over 47.5</t>
+        </is>
+      </c>
+      <c r="G191" s="23" t="n">
+        <v>47.5</v>
+      </c>
       <c r="H191" s="13" t="n">
-        <v>250</v>
+        <v>-115</v>
       </c>
       <c r="I191" s="15" t="n">
-        <v>0.3389003135487954</v>
+        <v>0.5868277708093877</v>
       </c>
       <c r="J191" s="15" t="n">
-        <v>0.274247491638796</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K191" s="15" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L191" s="14" t="n">
-        <v>0.05318602783450965</v>
+        <v>0.05194404987915524</v>
       </c>
       <c r="M191" s="14" t="n">
-        <v>0.1861510974207837</v>
+        <v>0.09711278890450747</v>
       </c>
       <c r="N191" s="15" t="n">
         <v>0</v>
@@ -13808,12 +13808,12 @@
       </c>
       <c r="B192" s="17" t="inlineStr">
         <is>
-          <t>WMU @ MICH</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C192" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D192" s="25" t="n">
@@ -13826,17 +13826,17 @@
       </c>
       <c r="F192" s="17" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
+          <t>Under 61.5</t>
         </is>
       </c>
       <c r="G192" s="26" t="n">
-        <v>47.5</v>
+        <v>61.5</v>
       </c>
       <c r="H192" s="18" t="n">
         <v>-115</v>
       </c>
       <c r="I192" s="20" t="n">
-        <v>0.5868277708093877</v>
+        <v>0.5868277408859488</v>
       </c>
       <c r="J192" s="20" t="n">
         <v>0.5108342361863488</v>
@@ -13845,10 +13845,10 @@
         <v>0.5348837209302325</v>
       </c>
       <c r="L192" s="19" t="n">
-        <v>0.05194404987915524</v>
+        <v>0.05194401995571629</v>
       </c>
       <c r="M192" s="19" t="n">
-        <v>0.09711278890450747</v>
+        <v>0.09711273296068679</v>
       </c>
       <c r="N192" s="20" t="n">
         <v>0</v>
@@ -14188,12 +14188,12 @@
       </c>
       <c r="B198" s="17" t="inlineStr">
         <is>
-          <t>HAW @ STAN</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C198" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D198" s="25" t="n">
@@ -14201,32 +14201,34 @@
       </c>
       <c r="E198" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F198" s="17" t="inlineStr">
         <is>
-          <t>HAW ML</t>
-        </is>
-      </c>
-      <c r="G198" s="26" t="n"/>
+          <t>Over 51.5</t>
+        </is>
+      </c>
+      <c r="G198" s="26" t="n">
+        <v>51.5</v>
+      </c>
       <c r="H198" s="18" t="n">
-        <v>164</v>
+        <v>-102</v>
       </c>
       <c r="I198" s="20" t="n">
-        <v>0.4247810281571975</v>
+        <v>0.550297511023865</v>
       </c>
       <c r="J198" s="20" t="n">
-        <v>0.3630958183058778</v>
+        <v>0.4826358742837298</v>
       </c>
       <c r="K198" s="20" t="n">
-        <v>0.3787878787878788</v>
+        <v>0.504950495049505</v>
       </c>
       <c r="L198" s="19" t="n">
-        <v>0.04599314936931875</v>
+        <v>0.04534701597436008</v>
       </c>
       <c r="M198" s="19" t="n">
-        <v>0.1214219143350014</v>
+        <v>0.08980487477275234</v>
       </c>
       <c r="N198" s="20" t="n">
         <v>0</v>
@@ -14249,12 +14251,12 @@
       </c>
       <c r="B199" s="12" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>MOST @ TA&amp;M</t>
         </is>
       </c>
       <c r="C199" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D199" s="22" t="n">
@@ -14267,29 +14269,29 @@
       </c>
       <c r="F199" s="12" t="inlineStr">
         <is>
-          <t>Over 50.5</t>
+          <t>Over 52.5</t>
         </is>
       </c>
       <c r="G199" s="23" t="n">
-        <v>50.5</v>
+        <v>52.5</v>
       </c>
       <c r="H199" s="13" t="n">
-        <v>-118</v>
+        <v>-110</v>
       </c>
       <c r="I199" s="15" t="n">
-        <v>0.5864236544376711</v>
+        <v>0.5684427123756473</v>
       </c>
       <c r="J199" s="15" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.5</v>
       </c>
       <c r="K199" s="15" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L199" s="14" t="n">
-        <v>0.04513925076794634</v>
+        <v>0.04463318856612342</v>
       </c>
       <c r="M199" s="14" t="n">
-        <v>0.08339285311366351</v>
+        <v>0.08520881453532658</v>
       </c>
       <c r="N199" s="15" t="n">
         <v>0</v>
@@ -14312,12 +14314,12 @@
       </c>
       <c r="B200" s="17" t="inlineStr">
         <is>
-          <t>MOST @ TA&amp;M</t>
+          <t>NWST @ LT</t>
         </is>
       </c>
       <c r="C200" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D200" s="25" t="n">
@@ -14337,22 +14339,22 @@
         <v>52.5</v>
       </c>
       <c r="H200" s="18" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I200" s="20" t="n">
-        <v>0.5684427123756473</v>
+        <v>0.5625111309589089</v>
       </c>
       <c r="J200" s="20" t="n">
-        <v>0.5</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K200" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L200" s="19" t="n">
-        <v>0.04463318856612342</v>
+        <v>0.04328036172813965</v>
       </c>
       <c r="M200" s="19" t="n">
-        <v>0.08520881453532658</v>
+        <v>0.08335477073567654</v>
       </c>
       <c r="N200" s="20" t="n">
         <v>0</v>
@@ -14365,7 +14367,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q200" s="17" t="n"/>
+      <c r="Q200" s="17" t="inlineStr">
+        <is>
+          <t>NWST isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="12" t="inlineStr">
@@ -14375,12 +14381,12 @@
       </c>
       <c r="B201" s="12" t="inlineStr">
         <is>
-          <t>NWST @ LT</t>
+          <t>TOW @ NAVY</t>
         </is>
       </c>
       <c r="C201" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D201" s="22" t="n">
@@ -14393,17 +14399,17 @@
       </c>
       <c r="F201" s="12" t="inlineStr">
         <is>
-          <t>Over 52.5</t>
+          <t>Over 53.5</t>
         </is>
       </c>
       <c r="G201" s="23" t="n">
-        <v>52.5</v>
+        <v>53.5</v>
       </c>
       <c r="H201" s="13" t="n">
         <v>-108</v>
       </c>
       <c r="I201" s="15" t="n">
-        <v>0.5625111309589089</v>
+        <v>0.5625111297198597</v>
       </c>
       <c r="J201" s="15" t="n">
         <v>0.4956702459300312</v>
@@ -14412,10 +14418,10 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L201" s="14" t="n">
-        <v>0.04328036172813965</v>
+        <v>0.04328036048909045</v>
       </c>
       <c r="M201" s="14" t="n">
-        <v>0.08335477073567654</v>
+        <v>0.08335476834935951</v>
       </c>
       <c r="N201" s="15" t="n">
         <v>0</v>
@@ -14430,7 +14436,7 @@
       </c>
       <c r="Q201" s="12" t="inlineStr">
         <is>
-          <t>NWST isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>TOW isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -14442,12 +14448,12 @@
       </c>
       <c r="B202" s="17" t="inlineStr">
         <is>
-          <t>TOW @ NAVY</t>
+          <t>LIU @ KU</t>
         </is>
       </c>
       <c r="C202" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-05 00:00</t>
         </is>
       </c>
       <c r="D202" s="25" t="n">
@@ -14467,22 +14473,22 @@
         <v>53.5</v>
       </c>
       <c r="H202" s="18" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I202" s="20" t="n">
-        <v>0.5625111297198597</v>
+        <v>0.5706075882916188</v>
       </c>
       <c r="J202" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K202" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L202" s="19" t="n">
-        <v>0.04328036048909045</v>
+        <v>0.04230570149916602</v>
       </c>
       <c r="M202" s="19" t="n">
-        <v>0.08335476834935951</v>
+        <v>0.0800786492662785</v>
       </c>
       <c r="N202" s="20" t="n">
         <v>0</v>
@@ -14497,7 +14503,7 @@
       </c>
       <c r="Q202" s="17" t="inlineStr">
         <is>
-          <t>TOW isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>LIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -14509,12 +14515,12 @@
       </c>
       <c r="B203" s="12" t="inlineStr">
         <is>
-          <t>HAW @ STAN</t>
+          <t>UCLA @ CAL</t>
         </is>
       </c>
       <c r="C203" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-06 02:30</t>
         </is>
       </c>
       <c r="D203" s="22" t="n">
@@ -14522,37 +14528,35 @@
       </c>
       <c r="E203" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F203" s="12" t="inlineStr">
         <is>
-          <t>HAW +4</t>
-        </is>
-      </c>
-      <c r="G203" s="23" t="n">
-        <v>-4</v>
-      </c>
+          <t>CAL ML</t>
+        </is>
+      </c>
+      <c r="G203" s="23" t="n"/>
       <c r="H203" s="13" t="n">
-        <v>-108</v>
+        <v>100</v>
       </c>
       <c r="I203" s="15" t="n">
-        <v>0.5623363270788992</v>
+        <v>0.5412654769965314</v>
       </c>
       <c r="J203" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="K203" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5</v>
       </c>
       <c r="L203" s="14" t="n">
-        <v>0.04310555784812997</v>
+        <v>0.04126547699653138</v>
       </c>
       <c r="M203" s="14" t="n">
-        <v>0.08052980264374909</v>
+        <v>0.08253095399306276</v>
       </c>
       <c r="N203" s="15" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="O203" s="24" t="n">
         <v>0.45</v>
@@ -14572,12 +14576,12 @@
       </c>
       <c r="B204" s="17" t="inlineStr">
         <is>
-          <t>LIU @ KU</t>
+          <t>HAW @ STAN</t>
         </is>
       </c>
       <c r="C204" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 00:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D204" s="25" t="n">
@@ -14585,37 +14589,37 @@
       </c>
       <c r="E204" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F204" s="17" t="inlineStr">
         <is>
-          <t>Over 53.5</t>
+          <t>HAW +4</t>
         </is>
       </c>
       <c r="G204" s="26" t="n">
-        <v>53.5</v>
+        <v>-4</v>
       </c>
       <c r="H204" s="18" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I204" s="20" t="n">
-        <v>0.5706075882916188</v>
+        <v>0.5645012041138837</v>
       </c>
       <c r="J204" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K204" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L204" s="19" t="n">
-        <v>0.04230570149916602</v>
+        <v>0.04069168030435988</v>
       </c>
       <c r="M204" s="19" t="n">
-        <v>0.0800786492662785</v>
+        <v>0.07535568443760798</v>
       </c>
       <c r="N204" s="20" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="O204" s="27" t="n">
         <v>0.45</v>
@@ -14625,11 +14629,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q204" s="17" t="inlineStr">
-        <is>
-          <t>LIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q204" s="17" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="12" t="inlineStr">
@@ -14639,12 +14639,12 @@
       </c>
       <c r="B205" s="12" t="inlineStr">
         <is>
-          <t>UCLA @ CAL</t>
+          <t>MORG @ ASU</t>
         </is>
       </c>
       <c r="C205" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 02:30</t>
+          <t>2026-09-06 02:00</t>
         </is>
       </c>
       <c r="D205" s="22" t="n">
@@ -14652,32 +14652,34 @@
       </c>
       <c r="E205" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F205" s="12" t="inlineStr">
         <is>
-          <t>CAL ML</t>
-        </is>
-      </c>
-      <c r="G205" s="23" t="n"/>
+          <t>Over 52.5</t>
+        </is>
+      </c>
+      <c r="G205" s="23" t="n">
+        <v>52.5</v>
+      </c>
       <c r="H205" s="13" t="n">
-        <v>100</v>
+        <v>-112</v>
       </c>
       <c r="I205" s="15" t="n">
-        <v>0.5412654769965314</v>
+        <v>0.5687274415570815</v>
       </c>
       <c r="J205" s="15" t="n">
-        <v>0.4782608695652174</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K205" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L205" s="14" t="n">
-        <v>0.04126547699653138</v>
+        <v>0.04042555476462872</v>
       </c>
       <c r="M205" s="14" t="n">
-        <v>0.08253095399306276</v>
+        <v>0.07651980009018999</v>
       </c>
       <c r="N205" s="15" t="n">
         <v>0</v>
@@ -14690,7 +14692,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q205" s="12" t="n"/>
+      <c r="Q205" s="12" t="inlineStr">
+        <is>
+          <t>MORG isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="17" t="inlineStr">
@@ -14700,12 +14706,12 @@
       </c>
       <c r="B206" s="17" t="inlineStr">
         <is>
-          <t>MORG @ ASU</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C206" s="17" t="inlineStr">
         <is>
-          <t>2026-09-06 02:00</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D206" s="25" t="n">
@@ -14718,29 +14724,29 @@
       </c>
       <c r="F206" s="17" t="inlineStr">
         <is>
-          <t>Over 52.5</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="G206" s="26" t="n">
-        <v>52.5</v>
+        <v>46.5</v>
       </c>
       <c r="H206" s="18" t="n">
-        <v>-112</v>
+        <v>-105</v>
       </c>
       <c r="I206" s="20" t="n">
-        <v>0.5687274415570815</v>
+        <v>0.5516520441530162</v>
       </c>
       <c r="J206" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K206" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L206" s="19" t="n">
-        <v>0.04042555476462872</v>
+        <v>0.03945692220179664</v>
       </c>
       <c r="M206" s="19" t="n">
-        <v>0.07651980009018999</v>
+        <v>0.07703494334636485</v>
       </c>
       <c r="N206" s="20" t="n">
         <v>0</v>
@@ -14753,11 +14759,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q206" s="17" t="inlineStr">
-        <is>
-          <t>MORG isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q206" s="17" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="12" t="inlineStr">
@@ -15157,12 +15159,12 @@
       </c>
       <c r="B213" s="12" t="inlineStr">
         <is>
-          <t>SMU @ FSU</t>
+          <t>HAW @ STAN</t>
         </is>
       </c>
       <c r="C213" s="12" t="inlineStr">
         <is>
-          <t>2026-09-07 23:30</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D213" s="22" t="n">
@@ -15175,27 +15177,27 @@
       </c>
       <c r="F213" s="12" t="inlineStr">
         <is>
-          <t>FSU ML</t>
+          <t>HAW ML</t>
         </is>
       </c>
       <c r="G213" s="23" t="n"/>
       <c r="H213" s="13" t="n">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="I213" s="15" t="n">
-        <v>0.4707366622168365</v>
+        <v>0.4319998430736718</v>
       </c>
       <c r="J213" s="15" t="n">
-        <v>0.4170073589533933</v>
+        <v>0.3775334481388264</v>
       </c>
       <c r="K213" s="15" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.3937007874015748</v>
       </c>
       <c r="L213" s="14" t="n">
-        <v>0.03595405352118436</v>
+        <v>0.03829905567209696</v>
       </c>
       <c r="M213" s="14" t="n">
-        <v>0.08269432309872393</v>
+        <v>0.09727960140712633</v>
       </c>
       <c r="N213" s="15" t="n">
         <v>0</v>
@@ -15218,12 +15220,12 @@
       </c>
       <c r="B214" s="17" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>SMU @ FSU</t>
         </is>
       </c>
       <c r="C214" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-09-07 23:30</t>
         </is>
       </c>
       <c r="D214" s="25" t="n">
@@ -15231,34 +15233,32 @@
       </c>
       <c r="E214" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F214" s="17" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
-        </is>
-      </c>
-      <c r="G214" s="26" t="n">
-        <v>46.5</v>
-      </c>
+          <t>FSU ML</t>
+        </is>
+      </c>
+      <c r="G214" s="26" t="n"/>
       <c r="H214" s="18" t="n">
-        <v>-108</v>
+        <v>130</v>
       </c>
       <c r="I214" s="20" t="n">
-        <v>0.5549042852112063</v>
+        <v>0.4707366622168365</v>
       </c>
       <c r="J214" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4170073589533933</v>
       </c>
       <c r="K214" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="L214" s="19" t="n">
-        <v>0.035673515980437</v>
+        <v>0.03595405352118436</v>
       </c>
       <c r="M214" s="19" t="n">
-        <v>0.06870454929565661</v>
+        <v>0.08269432309872393</v>
       </c>
       <c r="N214" s="20" t="n">
         <v>0</v>
@@ -16618,12 +16618,12 @@
       </c>
       <c r="B236" s="17" t="inlineStr">
         <is>
-          <t>JVST @ NDSU</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C236" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D236" s="25" t="n">
@@ -16631,35 +16631,37 @@
       </c>
       <c r="E236" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F236" s="17" t="inlineStr">
         <is>
-          <t>JVST ML</t>
-        </is>
-      </c>
-      <c r="G236" s="26" t="n"/>
+          <t>MEM +4</t>
+        </is>
+      </c>
+      <c r="G236" s="26" t="n">
+        <v>-4</v>
+      </c>
       <c r="H236" s="18" t="n">
-        <v>215</v>
+        <v>-108</v>
       </c>
       <c r="I236" s="20" t="n">
-        <v>0.3283150740711329</v>
+        <v>0.5308146628888071</v>
       </c>
       <c r="J236" s="20" t="n">
-        <v>0.3042300479266514</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K236" s="20" t="n">
-        <v>0.3174603174603174</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L236" s="19" t="n">
-        <v>0.01085475661081547</v>
+        <v>0.0115838936580378</v>
       </c>
       <c r="M236" s="19" t="n">
-        <v>0.03419248332406866</v>
+        <v>0.02161803347527169</v>
       </c>
       <c r="N236" s="20" t="n">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="O236" s="27" t="n">
         <v>0.45</v>
@@ -16679,12 +16681,12 @@
       </c>
       <c r="B237" s="12" t="inlineStr">
         <is>
-          <t>COLO @ GT</t>
+          <t>JVST @ NDSU</t>
         </is>
       </c>
       <c r="C237" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-08-29 21:30</t>
         </is>
       </c>
       <c r="D237" s="22" t="n">
@@ -16697,27 +16699,27 @@
       </c>
       <c r="F237" s="12" t="inlineStr">
         <is>
-          <t>COLO ML</t>
+          <t>JVST ML</t>
         </is>
       </c>
       <c r="G237" s="23" t="n"/>
       <c r="H237" s="13" t="n">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="I237" s="15" t="n">
-        <v>0.3498349996997374</v>
+        <v>0.3283150740711329</v>
       </c>
       <c r="J237" s="15" t="n">
-        <v>0.3249687530045188</v>
+        <v>0.3042300479266514</v>
       </c>
       <c r="K237" s="15" t="n">
-        <v>0.3389830508474576</v>
+        <v>0.3174603174603174</v>
       </c>
       <c r="L237" s="14" t="n">
-        <v>0.0108519488522798</v>
+        <v>0.01085475661081547</v>
       </c>
       <c r="M237" s="14" t="n">
-        <v>0.03201324911422543</v>
+        <v>0.03419248332406866</v>
       </c>
       <c r="N237" s="15" t="n">
         <v>0</v>
@@ -16740,12 +16742,12 @@
       </c>
       <c r="B238" s="17" t="inlineStr">
         <is>
-          <t>BRY @ ARMY</t>
+          <t>COLO @ GT</t>
         </is>
       </c>
       <c r="C238" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D238" s="25" t="n">
@@ -16753,34 +16755,32 @@
       </c>
       <c r="E238" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F238" s="17" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
-        </is>
-      </c>
-      <c r="G238" s="26" t="n">
-        <v>51.5</v>
-      </c>
+          <t>COLO ML</t>
+        </is>
+      </c>
+      <c r="G238" s="26" t="n"/>
       <c r="H238" s="18" t="n">
-        <v>-108</v>
+        <v>195</v>
       </c>
       <c r="I238" s="20" t="n">
-        <v>0.5296280063426244</v>
+        <v>0.3498349996997374</v>
       </c>
       <c r="J238" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.3249687530045188</v>
       </c>
       <c r="K238" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.3389830508474576</v>
       </c>
       <c r="L238" s="19" t="n">
-        <v>0.01039723711185514</v>
+        <v>0.0108519488522798</v>
       </c>
       <c r="M238" s="19" t="n">
-        <v>0.02002430851172116</v>
+        <v>0.03201324911422543</v>
       </c>
       <c r="N238" s="20" t="n">
         <v>0</v>
@@ -16793,11 +16793,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q238" s="17" t="inlineStr">
-        <is>
-          <t>BRY isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q238" s="17" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="12" t="inlineStr">
@@ -16807,12 +16803,12 @@
       </c>
       <c r="B239" s="12" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>BRY @ ARMY</t>
         </is>
       </c>
       <c r="C239" s="12" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D239" s="22" t="n">
@@ -16820,34 +16816,34 @@
       </c>
       <c r="E239" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F239" s="12" t="inlineStr">
         <is>
-          <t>MEM +4.5</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="G239" s="23" t="n">
-        <v>-4.5</v>
+        <v>51.5</v>
       </c>
       <c r="H239" s="13" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="I239" s="15" t="n">
-        <v>0.5451251316679337</v>
+        <v>0.5296280063426244</v>
       </c>
       <c r="J239" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K239" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L239" s="14" t="n">
-        <v>0.01024141073770124</v>
+        <v>0.01039723711185514</v>
       </c>
       <c r="M239" s="14" t="n">
-        <v>0.01914698529222392</v>
+        <v>0.02002430851172116</v>
       </c>
       <c r="N239" s="15" t="n">
         <v>0</v>
@@ -16860,7 +16856,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q239" s="12" t="n"/>
+      <c r="Q239" s="12" t="inlineStr">
+        <is>
+          <t>BRY isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="17" t="inlineStr">
@@ -21835,12 +21835,12 @@
       </c>
       <c r="B317" s="12" t="inlineStr">
         <is>
-          <t>MEM @ UNLV</t>
+          <t>BRY @ ARMY</t>
         </is>
       </c>
       <c r="C317" s="12" t="inlineStr">
         <is>
-          <t>2026-08-30 02:00</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D317" s="22" t="n">
@@ -21848,34 +21848,34 @@
       </c>
       <c r="E317" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F317" s="12" t="inlineStr">
         <is>
-          <t>UNLV -4.5</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="G317" s="23" t="n">
-        <v>-4.5</v>
+        <v>51.5</v>
       </c>
       <c r="H317" s="13" t="n">
-        <v>-105</v>
+        <v>-112</v>
       </c>
       <c r="I317" s="15" t="n">
-        <v>0.4548748683320663</v>
+        <v>0.4703719936573756</v>
       </c>
       <c r="J317" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K317" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L317" s="14" t="n">
-        <v>-0.05732025361915327</v>
+        <v>-0.05792989313507724</v>
       </c>
       <c r="M317" s="14" t="n">
-        <v>-0.1119109713516802</v>
+        <v>-0.1096530120056819</v>
       </c>
       <c r="N317" s="15" t="n">
         <v>0</v>
@@ -21888,7 +21888,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q317" s="12" t="n"/>
+      <c r="Q317" s="12" t="inlineStr">
+        <is>
+          <t>BRY isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="17" t="inlineStr">
@@ -21898,12 +21902,12 @@
       </c>
       <c r="B318" s="17" t="inlineStr">
         <is>
-          <t>BRY @ ARMY</t>
+          <t>MEM @ UNLV</t>
         </is>
       </c>
       <c r="C318" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-08-30 02:00</t>
         </is>
       </c>
       <c r="D318" s="25" t="n">
@@ -21911,22 +21915,22 @@
       </c>
       <c r="E318" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F318" s="17" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>UNLV -4</t>
         </is>
       </c>
       <c r="G318" s="26" t="n">
-        <v>51.5</v>
+        <v>-4</v>
       </c>
       <c r="H318" s="18" t="n">
         <v>-112</v>
       </c>
       <c r="I318" s="20" t="n">
-        <v>0.4703719936573756</v>
+        <v>0.4691853371111929</v>
       </c>
       <c r="J318" s="20" t="n">
         <v>0.5043297540699688</v>
@@ -21935,13 +21939,13 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L318" s="19" t="n">
-        <v>-0.05792989313507724</v>
+        <v>-0.0591165496812599</v>
       </c>
       <c r="M318" s="19" t="n">
-        <v>-0.1096530120056819</v>
+        <v>-0.1084298758401122</v>
       </c>
       <c r="N318" s="20" t="n">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="O318" s="27" t="n">
         <v>0.45</v>
@@ -21951,11 +21955,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q318" s="17" t="inlineStr">
-        <is>
-          <t>BRY isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q318" s="17" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="12" t="inlineStr">
@@ -23172,12 +23172,12 @@
       </c>
       <c r="B338" s="17" t="inlineStr">
         <is>
-          <t>APSU @ VAN</t>
+          <t>HAW @ STAN</t>
         </is>
       </c>
       <c r="C338" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D338" s="25" t="n">
@@ -23185,34 +23185,32 @@
       </c>
       <c r="E338" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F338" s="17" t="inlineStr">
         <is>
-          <t>Over 61.5</t>
-        </is>
-      </c>
-      <c r="G338" s="26" t="n">
-        <v>61.5</v>
-      </c>
+          <t>STAN ML</t>
+        </is>
+      </c>
+      <c r="G338" s="26" t="n"/>
       <c r="H338" s="18" t="n">
-        <v>-108</v>
+        <v>-185</v>
       </c>
       <c r="I338" s="20" t="n">
-        <v>0.4369507853031964</v>
+        <v>0.5680001569263282</v>
       </c>
       <c r="J338" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.6224665518611737</v>
       </c>
       <c r="K338" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.6491228070175439</v>
       </c>
       <c r="L338" s="19" t="n">
-        <v>-0.08227998392757285</v>
+        <v>-0.08112265009121566</v>
       </c>
       <c r="M338" s="19" t="n">
-        <v>-0.1584651542308809</v>
+        <v>-0.1249727312216025</v>
       </c>
       <c r="N338" s="20" t="n">
         <v>0</v>
@@ -23225,11 +23223,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q338" s="17" t="inlineStr">
-        <is>
-          <t>APSU isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q338" s="17" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="12" t="inlineStr">
@@ -23239,12 +23233,12 @@
       </c>
       <c r="B339" s="12" t="inlineStr">
         <is>
-          <t>UTEP @ OU</t>
+          <t>APSU @ VAN</t>
         </is>
       </c>
       <c r="C339" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 00:00</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D339" s="22" t="n">
@@ -23257,29 +23251,29 @@
       </c>
       <c r="F339" s="12" t="inlineStr">
         <is>
-          <t>Under 50.5</t>
+          <t>Over 61.5</t>
         </is>
       </c>
       <c r="G339" s="23" t="n">
-        <v>50.5</v>
+        <v>61.5</v>
       </c>
       <c r="H339" s="13" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="I339" s="15" t="n">
-        <v>0.4450957958169039</v>
+        <v>0.4369507853031964</v>
       </c>
       <c r="J339" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K339" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L339" s="14" t="n">
-        <v>-0.08320609097554887</v>
+        <v>-0.08227998392757285</v>
       </c>
       <c r="M339" s="14" t="n">
-        <v>-0.157497243632289</v>
+        <v>-0.1584651542308809</v>
       </c>
       <c r="N339" s="15" t="n">
         <v>0</v>
@@ -23292,7 +23286,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q339" s="12" t="n"/>
+      <c r="Q339" s="12" t="inlineStr">
+        <is>
+          <t>APSU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="17" t="inlineStr">
@@ -23302,12 +23300,12 @@
       </c>
       <c r="B340" s="17" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>UTEP @ OU</t>
         </is>
       </c>
       <c r="C340" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-09-05 00:00</t>
         </is>
       </c>
       <c r="D340" s="25" t="n">
@@ -23320,17 +23318,17 @@
       </c>
       <c r="F340" s="17" t="inlineStr">
         <is>
-          <t>Under 46.5</t>
+          <t>Under 50.5</t>
         </is>
       </c>
       <c r="G340" s="26" t="n">
-        <v>46.5</v>
+        <v>50.5</v>
       </c>
       <c r="H340" s="18" t="n">
         <v>-112</v>
       </c>
       <c r="I340" s="20" t="n">
-        <v>0.4450957147887937</v>
+        <v>0.4450957958169039</v>
       </c>
       <c r="J340" s="20" t="n">
         <v>0.5043297540699688</v>
@@ -23339,10 +23337,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L340" s="19" t="n">
-        <v>-0.0832061720036591</v>
+        <v>-0.08320609097554887</v>
       </c>
       <c r="M340" s="19" t="n">
-        <v>-0.1574973970069262</v>
+        <v>-0.157497243632289</v>
       </c>
       <c r="N340" s="20" t="n">
         <v>0</v>
@@ -23688,12 +23686,12 @@
       </c>
       <c r="B346" s="17" t="inlineStr">
         <is>
-          <t>EIU @ MINN</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C346" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D346" s="25" t="n">
@@ -23706,29 +23704,29 @@
       </c>
       <c r="F346" s="17" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>Under 46.5</t>
         </is>
       </c>
       <c r="G346" s="26" t="n">
-        <v>51.5</v>
+        <v>46.5</v>
       </c>
       <c r="H346" s="18" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="I346" s="20" t="n">
-        <v>0.4372167873211319</v>
+        <v>0.4483479558469838</v>
       </c>
       <c r="J346" s="20" t="n">
-        <v>0.5</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K346" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L346" s="19" t="n">
-        <v>-0.08659273648839194</v>
+        <v>-0.08653576508324867</v>
       </c>
       <c r="M346" s="19" t="n">
-        <v>-0.1653134060232936</v>
+        <v>-0.1617842564599868</v>
       </c>
       <c r="N346" s="20" t="n">
         <v>0</v>
@@ -23741,11 +23739,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q346" s="17" t="inlineStr">
-        <is>
-          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q346" s="17" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="12" t="inlineStr">
@@ -23755,12 +23749,12 @@
       </c>
       <c r="B347" s="12" t="inlineStr">
         <is>
-          <t>UCLA @ CAL</t>
+          <t>EIU @ MINN</t>
         </is>
       </c>
       <c r="C347" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 02:30</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D347" s="22" t="n">
@@ -23768,32 +23762,34 @@
       </c>
       <c r="E347" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F347" s="12" t="inlineStr">
         <is>
-          <t>UCLA ML</t>
-        </is>
-      </c>
-      <c r="G347" s="23" t="n"/>
+          <t>Under 51.5</t>
+        </is>
+      </c>
+      <c r="G347" s="23" t="n">
+        <v>51.5</v>
+      </c>
       <c r="H347" s="13" t="n">
-        <v>-120</v>
+        <v>-110</v>
       </c>
       <c r="I347" s="15" t="n">
-        <v>0.4587345230034686</v>
+        <v>0.4372167873211319</v>
       </c>
       <c r="J347" s="15" t="n">
-        <v>0.5217391304347826</v>
+        <v>0.5</v>
       </c>
       <c r="K347" s="15" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L347" s="14" t="n">
-        <v>-0.08672002245107679</v>
+        <v>-0.08659273648839194</v>
       </c>
       <c r="M347" s="14" t="n">
-        <v>-0.1589867078269741</v>
+        <v>-0.1653134060232936</v>
       </c>
       <c r="N347" s="15" t="n">
         <v>0</v>
@@ -23806,7 +23802,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q347" s="12" t="n"/>
+      <c r="Q347" s="12" t="inlineStr">
+        <is>
+          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="17" t="inlineStr">
@@ -23816,12 +23816,12 @@
       </c>
       <c r="B348" s="17" t="inlineStr">
         <is>
-          <t>MORG @ ASU</t>
+          <t>UCLA @ CAL</t>
         </is>
       </c>
       <c r="C348" s="17" t="inlineStr">
         <is>
-          <t>2026-09-06 02:00</t>
+          <t>2026-09-06 02:30</t>
         </is>
       </c>
       <c r="D348" s="25" t="n">
@@ -23829,34 +23829,32 @@
       </c>
       <c r="E348" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F348" s="17" t="inlineStr">
         <is>
-          <t>Under 52.5</t>
-        </is>
-      </c>
-      <c r="G348" s="26" t="n">
-        <v>52.5</v>
-      </c>
+          <t>UCLA ML</t>
+        </is>
+      </c>
+      <c r="G348" s="26" t="n"/>
       <c r="H348" s="18" t="n">
-        <v>-108</v>
+        <v>-120</v>
       </c>
       <c r="I348" s="20" t="n">
-        <v>0.4312725584429185</v>
+        <v>0.4587345230034686</v>
       </c>
       <c r="J348" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="K348" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="L348" s="19" t="n">
-        <v>-0.08795821078785082</v>
+        <v>-0.08672002245107679</v>
       </c>
       <c r="M348" s="19" t="n">
-        <v>-0.1694009985543792</v>
+        <v>-0.1589867078269741</v>
       </c>
       <c r="N348" s="20" t="n">
         <v>0</v>
@@ -23869,11 +23867,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q348" s="17" t="inlineStr">
-        <is>
-          <t>MORG isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q348" s="17" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="12" t="inlineStr">
@@ -23883,12 +23877,12 @@
       </c>
       <c r="B349" s="12" t="inlineStr">
         <is>
-          <t>HAW @ STAN</t>
+          <t>MORG @ ASU</t>
         </is>
       </c>
       <c r="C349" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-06 02:00</t>
         </is>
       </c>
       <c r="D349" s="22" t="n">
@@ -23896,32 +23890,34 @@
       </c>
       <c r="E349" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F349" s="12" t="inlineStr">
         <is>
-          <t>STAN ML</t>
-        </is>
-      </c>
-      <c r="G349" s="23" t="n"/>
+          <t>Under 52.5</t>
+        </is>
+      </c>
+      <c r="G349" s="23" t="n">
+        <v>52.5</v>
+      </c>
       <c r="H349" s="13" t="n">
-        <v>-198</v>
+        <v>-108</v>
       </c>
       <c r="I349" s="15" t="n">
-        <v>0.5752189718428025</v>
+        <v>0.4312725584429185</v>
       </c>
       <c r="J349" s="15" t="n">
-        <v>0.6369041816941223</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K349" s="15" t="n">
-        <v>0.6644295302013423</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L349" s="14" t="n">
-        <v>-0.08921055835853986</v>
+        <v>-0.08795821078785082</v>
       </c>
       <c r="M349" s="14" t="n">
-        <v>-0.1342663959133578</v>
+        <v>-0.1694009985543792</v>
       </c>
       <c r="N349" s="15" t="n">
         <v>0</v>
@@ -23934,7 +23930,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q349" s="12" t="n"/>
+      <c r="Q349" s="12" t="inlineStr">
+        <is>
+          <t>MORG isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="17" t="inlineStr">
@@ -23944,12 +23944,12 @@
       </c>
       <c r="B350" s="17" t="inlineStr">
         <is>
-          <t>LIU @ KU</t>
+          <t>HAW @ STAN</t>
         </is>
       </c>
       <c r="C350" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 00:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D350" s="25" t="n">
@@ -23957,37 +23957,37 @@
       </c>
       <c r="E350" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F350" s="17" t="inlineStr">
         <is>
-          <t>Under 53.5</t>
+          <t>STAN -4</t>
         </is>
       </c>
       <c r="G350" s="26" t="n">
-        <v>53.5</v>
+        <v>-4</v>
       </c>
       <c r="H350" s="18" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I350" s="20" t="n">
-        <v>0.4293924117083812</v>
+        <v>0.4354987958861163</v>
       </c>
       <c r="J350" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5</v>
       </c>
       <c r="K350" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L350" s="19" t="n">
-        <v>-0.08983835752238811</v>
+        <v>-0.08831072792340755</v>
       </c>
       <c r="M350" s="19" t="n">
-        <v>-0.1730220218949696</v>
+        <v>-0.1635399495935468</v>
       </c>
       <c r="N350" s="20" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="O350" s="27" t="n">
         <v>0.45</v>
@@ -23997,11 +23997,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q350" s="17" t="inlineStr">
-        <is>
-          <t>LIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q350" s="17" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="12" t="inlineStr">
@@ -24011,12 +24007,12 @@
       </c>
       <c r="B351" s="12" t="inlineStr">
         <is>
-          <t>HAW @ STAN</t>
+          <t>LIU @ KU</t>
         </is>
       </c>
       <c r="C351" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-05 00:00</t>
         </is>
       </c>
       <c r="D351" s="22" t="n">
@@ -24024,37 +24020,37 @@
       </c>
       <c r="E351" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F351" s="12" t="inlineStr">
         <is>
-          <t>STAN -4</t>
+          <t>Under 53.5</t>
         </is>
       </c>
       <c r="G351" s="23" t="n">
-        <v>-4</v>
+        <v>53.5</v>
       </c>
       <c r="H351" s="13" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="I351" s="15" t="n">
-        <v>0.4376636729211008</v>
+        <v>0.4293924117083812</v>
       </c>
       <c r="J351" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K351" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L351" s="14" t="n">
-        <v>-0.09063821387135207</v>
+        <v>-0.08983835752238811</v>
       </c>
       <c r="M351" s="14" t="n">
-        <v>-0.1664228527973303</v>
+        <v>-0.1730220218949696</v>
       </c>
       <c r="N351" s="15" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="O351" s="24" t="n">
         <v>0.45</v>
@@ -24064,7 +24060,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q351" s="12" t="n"/>
+      <c r="Q351" s="12" t="inlineStr">
+        <is>
+          <t>LIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="17" t="inlineStr">
@@ -24226,29 +24226,29 @@
       </c>
       <c r="F354" s="17" t="inlineStr">
         <is>
-          <t>Under 50.5</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="G354" s="26" t="n">
-        <v>50.5</v>
+        <v>51.5</v>
       </c>
       <c r="H354" s="18" t="n">
-        <v>-102</v>
+        <v>-118</v>
       </c>
       <c r="I354" s="20" t="n">
-        <v>0.4135763455623289</v>
+        <v>0.449702488976135</v>
       </c>
       <c r="J354" s="20" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.5173641257162701</v>
       </c>
       <c r="K354" s="20" t="n">
-        <v>0.504950495049505</v>
+        <v>0.5412844036697247</v>
       </c>
       <c r="L354" s="19" t="n">
-        <v>-0.09137414948717604</v>
+        <v>-0.09158191469358978</v>
       </c>
       <c r="M354" s="19" t="n">
-        <v>-0.1809566489844074</v>
+        <v>-0.1691937068068015</v>
       </c>
       <c r="N354" s="20" t="n">
         <v>0</v>
@@ -24773,12 +24773,12 @@
       </c>
       <c r="B363" s="12" t="inlineStr">
         <is>
-          <t>WMU @ MICH</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C363" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D363" s="22" t="n">
@@ -24791,17 +24791,17 @@
       </c>
       <c r="F363" s="12" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
+          <t>Over 61.5</t>
         </is>
       </c>
       <c r="G363" s="23" t="n">
-        <v>47.5</v>
+        <v>61.5</v>
       </c>
       <c r="H363" s="13" t="n">
         <v>-105</v>
       </c>
       <c r="I363" s="15" t="n">
-        <v>0.4131722291906123</v>
+        <v>0.4131722591140512</v>
       </c>
       <c r="J363" s="15" t="n">
         <v>0.4891657638136511</v>
@@ -24810,10 +24810,10 @@
         <v>0.5121951219512195</v>
       </c>
       <c r="L363" s="14" t="n">
-        <v>-0.09902289276060727</v>
+        <v>-0.09902286283716832</v>
       </c>
       <c r="M363" s="14" t="n">
-        <v>-0.1933304096754713</v>
+        <v>-0.1933303512535191</v>
       </c>
       <c r="N363" s="15" t="n">
         <v>0</v>
@@ -24836,12 +24836,12 @@
       </c>
       <c r="B364" s="17" t="inlineStr">
         <is>
-          <t>BC @ CIN</t>
+          <t>WMU @ MICH</t>
         </is>
       </c>
       <c r="C364" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D364" s="25" t="n">
@@ -24849,34 +24849,34 @@
       </c>
       <c r="E364" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F364" s="17" t="inlineStr">
         <is>
-          <t>CIN -7.5</t>
+          <t>Under 47.5</t>
         </is>
       </c>
       <c r="G364" s="26" t="n">
-        <v>-7.5</v>
+        <v>47.5</v>
       </c>
       <c r="H364" s="18" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="I364" s="20" t="n">
-        <v>0.4175206855288386</v>
+        <v>0.4131722291906123</v>
       </c>
       <c r="J364" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K364" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L364" s="19" t="n">
-        <v>-0.1017100837019307</v>
+        <v>-0.09902289276060727</v>
       </c>
       <c r="M364" s="19" t="n">
-        <v>-0.1958860871296442</v>
+        <v>-0.1933304096754713</v>
       </c>
       <c r="N364" s="20" t="n">
         <v>0</v>
@@ -24899,7 +24899,7 @@
       </c>
       <c r="B365" s="12" t="inlineStr">
         <is>
-          <t>BOIS @ ORE</t>
+          <t>BC @ CIN</t>
         </is>
       </c>
       <c r="C365" s="12" t="inlineStr">
@@ -24912,34 +24912,34 @@
       </c>
       <c r="E365" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F365" s="12" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>CIN -7.5</t>
         </is>
       </c>
       <c r="G365" s="23" t="n">
-        <v>51.5</v>
+        <v>-7.5</v>
       </c>
       <c r="H365" s="13" t="n">
-        <v>-102</v>
+        <v>-108</v>
       </c>
       <c r="I365" s="15" t="n">
-        <v>0.4026625680798983</v>
+        <v>0.4175206855288386</v>
       </c>
       <c r="J365" s="15" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K365" s="15" t="n">
-        <v>0.504950495049505</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L365" s="14" t="n">
-        <v>-0.1022879269696066</v>
+        <v>-0.1017100837019307</v>
       </c>
       <c r="M365" s="14" t="n">
-        <v>-0.2025702083123582</v>
+        <v>-0.1958860871296442</v>
       </c>
       <c r="N365" s="15" t="n">
         <v>0</v>
@@ -24962,12 +24962,12 @@
       </c>
       <c r="B366" s="17" t="inlineStr">
         <is>
-          <t>UNLV @ HAW</t>
+          <t>BOIS @ ORE</t>
         </is>
       </c>
       <c r="C366" s="17" t="inlineStr">
         <is>
-          <t>2026-09-06 02:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D366" s="25" t="n">
@@ -24975,37 +24975,37 @@
       </c>
       <c r="E366" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F366" s="17" t="inlineStr">
         <is>
-          <t>UNLV -3</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="G366" s="26" t="n">
-        <v>3</v>
+        <v>51.5</v>
       </c>
       <c r="H366" s="18" t="n">
-        <v>-112</v>
+        <v>-102</v>
       </c>
       <c r="I366" s="20" t="n">
-        <v>0.4247975673626849</v>
+        <v>0.4026625680798983</v>
       </c>
       <c r="J366" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4826358742837298</v>
       </c>
       <c r="K366" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.504950495049505</v>
       </c>
       <c r="L366" s="19" t="n">
-        <v>-0.1035043194297679</v>
+        <v>-0.1022879269696066</v>
       </c>
       <c r="M366" s="19" t="n">
-        <v>-0.184802661991996</v>
+        <v>-0.2025702083123582</v>
       </c>
       <c r="N366" s="20" t="n">
-        <v>0.0567</v>
+        <v>0</v>
       </c>
       <c r="O366" s="27" t="n">
         <v>0.45</v>
@@ -25025,12 +25025,12 @@
       </c>
       <c r="B367" s="12" t="inlineStr">
         <is>
-          <t>TOL @ MSU</t>
+          <t>UNLV @ HAW</t>
         </is>
       </c>
       <c r="C367" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 00:00</t>
+          <t>2026-09-06 02:00</t>
         </is>
       </c>
       <c r="D367" s="22" t="n">
@@ -25038,22 +25038,22 @@
       </c>
       <c r="E367" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F367" s="12" t="inlineStr">
         <is>
-          <t>Under 49.5</t>
+          <t>UNLV -3</t>
         </is>
       </c>
       <c r="G367" s="23" t="n">
-        <v>49.5</v>
+        <v>3</v>
       </c>
       <c r="H367" s="13" t="n">
         <v>-112</v>
       </c>
       <c r="I367" s="15" t="n">
-        <v>0.4244232808142943</v>
+        <v>0.4247975673626849</v>
       </c>
       <c r="J367" s="15" t="n">
         <v>0.5043297540699688</v>
@@ -25062,13 +25062,13 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L367" s="14" t="n">
-        <v>-0.1038786059781586</v>
+        <v>-0.1035043194297679</v>
       </c>
       <c r="M367" s="14" t="n">
-        <v>-0.1966273613158002</v>
+        <v>-0.184802661991996</v>
       </c>
       <c r="N367" s="15" t="n">
-        <v>0</v>
+        <v>0.0567</v>
       </c>
       <c r="O367" s="24" t="n">
         <v>0.45</v>
@@ -25088,12 +25088,12 @@
       </c>
       <c r="B368" s="17" t="inlineStr">
         <is>
-          <t>ACU @ TTU</t>
+          <t>TOL @ MSU</t>
         </is>
       </c>
       <c r="C368" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-05 00:00</t>
         </is>
       </c>
       <c r="D368" s="25" t="n">
@@ -25106,29 +25106,29 @@
       </c>
       <c r="F368" s="17" t="inlineStr">
         <is>
-          <t>Over 59.5</t>
+          <t>Under 49.5</t>
         </is>
       </c>
       <c r="G368" s="26" t="n">
-        <v>59.5</v>
+        <v>49.5</v>
       </c>
       <c r="H368" s="18" t="n">
-        <v>-105</v>
+        <v>-112</v>
       </c>
       <c r="I368" s="20" t="n">
-        <v>0.4077266673356444</v>
+        <v>0.4244232808142943</v>
       </c>
       <c r="J368" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K368" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L368" s="19" t="n">
-        <v>-0.1044684546155751</v>
+        <v>-0.1038786059781586</v>
       </c>
       <c r="M368" s="19" t="n">
-        <v>-0.2039622209161229</v>
+        <v>-0.1966273613158002</v>
       </c>
       <c r="N368" s="20" t="n">
         <v>0</v>
@@ -25141,11 +25141,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q368" s="17" t="inlineStr">
-        <is>
-          <t>ACU isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q368" s="17" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="12" t="inlineStr">
@@ -25155,12 +25151,12 @@
       </c>
       <c r="B369" s="12" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>ACU @ TTU</t>
         </is>
       </c>
       <c r="C369" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D369" s="22" t="n">
@@ -25173,29 +25169,29 @@
       </c>
       <c r="F369" s="12" t="inlineStr">
         <is>
-          <t>Over 61.5</t>
+          <t>Over 59.5</t>
         </is>
       </c>
       <c r="G369" s="23" t="n">
-        <v>61.5</v>
+        <v>59.5</v>
       </c>
       <c r="H369" s="13" t="n">
-        <v>-112</v>
+        <v>-105</v>
       </c>
       <c r="I369" s="15" t="n">
-        <v>0.42075425424221</v>
+        <v>0.4077266673356444</v>
       </c>
       <c r="J369" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K369" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L369" s="14" t="n">
-        <v>-0.1075476325502428</v>
+        <v>-0.1044684546155751</v>
       </c>
       <c r="M369" s="14" t="n">
-        <v>-0.2035723044701025</v>
+        <v>-0.2039622209161229</v>
       </c>
       <c r="N369" s="15" t="n">
         <v>0</v>
@@ -25208,7 +25204,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q369" s="12" t="n"/>
+      <c r="Q369" s="12" t="inlineStr">
+        <is>
+          <t>ACU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="17" t="inlineStr">
@@ -26500,12 +26500,12 @@
       </c>
       <c r="B390" s="17" t="inlineStr">
         <is>
-          <t>MERC @ NMSU</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C390" s="17" t="inlineStr">
         <is>
-          <t>2026-09-06 01:00</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D390" s="25" t="n">
@@ -26513,34 +26513,32 @@
       </c>
       <c r="E390" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F390" s="17" t="inlineStr">
         <is>
-          <t>Under 50.5</t>
-        </is>
-      </c>
-      <c r="G390" s="26" t="n">
-        <v>50.5</v>
-      </c>
+          <t>TCU ML</t>
+        </is>
+      </c>
+      <c r="G390" s="26" t="n"/>
       <c r="H390" s="18" t="n">
-        <v>-108</v>
+        <v>-340</v>
       </c>
       <c r="I390" s="20" t="n">
-        <v>0.3916651598428054</v>
+        <v>0.6454305499719861</v>
       </c>
       <c r="J390" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.740871613663133</v>
       </c>
       <c r="K390" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="L390" s="19" t="n">
-        <v>-0.1275656093879639</v>
+        <v>-0.1272967227552866</v>
       </c>
       <c r="M390" s="19" t="n">
-        <v>-0.2456819143768192</v>
+        <v>-0.1647369353303709</v>
       </c>
       <c r="N390" s="20" t="n">
         <v>0</v>
@@ -26553,11 +26551,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q390" s="17" t="inlineStr">
-        <is>
-          <t>MERC isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q390" s="17" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="12" t="inlineStr">
@@ -26567,12 +26561,12 @@
       </c>
       <c r="B391" s="12" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>MERC @ NMSU</t>
         </is>
       </c>
       <c r="C391" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-09-06 01:00</t>
         </is>
       </c>
       <c r="D391" s="22" t="n">
@@ -26580,32 +26574,34 @@
       </c>
       <c r="E391" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F391" s="12" t="inlineStr">
         <is>
-          <t>TCU ML</t>
-        </is>
-      </c>
-      <c r="G391" s="23" t="n"/>
+          <t>Under 50.5</t>
+        </is>
+      </c>
+      <c r="G391" s="23" t="n">
+        <v>50.5</v>
+      </c>
       <c r="H391" s="13" t="n">
-        <v>-345</v>
+        <v>-108</v>
       </c>
       <c r="I391" s="15" t="n">
-        <v>0.6470292506889459</v>
+        <v>0.3916651598428054</v>
       </c>
       <c r="J391" s="15" t="n">
-        <v>0.7440690150970525</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K391" s="15" t="n">
-        <v>0.7752808988764045</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L391" s="14" t="n">
-        <v>-0.1282516481874586</v>
+        <v>-0.1275656093879639</v>
       </c>
       <c r="M391" s="14" t="n">
-        <v>-0.1654260389664321</v>
+        <v>-0.2456819143768192</v>
       </c>
       <c r="N391" s="15" t="n">
         <v>0</v>
@@ -26618,7 +26614,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q391" s="12" t="n"/>
+      <c r="Q391" s="12" t="inlineStr">
+        <is>
+          <t>MERC isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="17" t="inlineStr">
@@ -27014,12 +27014,12 @@
       </c>
       <c r="B398" s="17" t="inlineStr">
         <is>
-          <t>URI @ TEM</t>
+          <t>HAW @ STAN</t>
         </is>
       </c>
       <c r="C398" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 18:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D398" s="25" t="n">
@@ -27032,29 +27032,29 @@
       </c>
       <c r="F398" s="17" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>Under 48.5</t>
         </is>
       </c>
       <c r="G398" s="26" t="n">
-        <v>51.5</v>
+        <v>48.5</v>
       </c>
       <c r="H398" s="18" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="I398" s="20" t="n">
-        <v>0.3799657991791088</v>
+        <v>0.3767135533122641</v>
       </c>
       <c r="J398" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K398" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L398" s="19" t="n">
-        <v>-0.1392649700516605</v>
+        <v>-0.1354815686389554</v>
       </c>
       <c r="M398" s="19" t="n">
-        <v>-0.2682140163957905</v>
+        <v>-0.2645116340093892</v>
       </c>
       <c r="N398" s="20" t="n">
         <v>0</v>
@@ -27067,11 +27067,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q398" s="17" t="inlineStr">
-        <is>
-          <t>URI isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q398" s="17" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="12" t="inlineStr">
@@ -27106,22 +27102,22 @@
         <v>-8.5</v>
       </c>
       <c r="H399" s="13" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I399" s="15" t="n">
-        <v>0.3885649897991602</v>
+        <v>0.3864001127641757</v>
       </c>
       <c r="J399" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K399" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L399" s="14" t="n">
-        <v>-0.1397368969932926</v>
+        <v>-0.1374094110453481</v>
       </c>
       <c r="M399" s="14" t="n">
-        <v>-0.2645019835944468</v>
+        <v>-0.2623270574502099</v>
       </c>
       <c r="N399" s="15" t="n">
         <v>0</v>
@@ -27331,12 +27327,12 @@
       </c>
       <c r="B403" s="12" t="inlineStr">
         <is>
-          <t>HAW @ STAN</t>
+          <t>YSU @ UK</t>
         </is>
       </c>
       <c r="C403" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-05 17:00</t>
         </is>
       </c>
       <c r="D403" s="22" t="n">
@@ -27349,17 +27345,17 @@
       </c>
       <c r="F403" s="12" t="inlineStr">
         <is>
-          <t>Under 48.5</t>
+          <t>Over 62.5</t>
         </is>
       </c>
       <c r="G403" s="23" t="n">
-        <v>48.5</v>
+        <v>62.5</v>
       </c>
       <c r="H403" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I403" s="15" t="n">
-        <v>0.3821306714054384</v>
+        <v>0.3788792876661868</v>
       </c>
       <c r="J403" s="15" t="n">
         <v>0.5</v>
@@ -27368,10 +27364,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L403" s="14" t="n">
-        <v>-0.1416788524040854</v>
+        <v>-0.144930236143337</v>
       </c>
       <c r="M403" s="14" t="n">
-        <v>-0.270477809135072</v>
+        <v>-0.2766849962736433</v>
       </c>
       <c r="N403" s="15" t="n">
         <v>0</v>
@@ -27384,7 +27380,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q403" s="12" t="n"/>
+      <c r="Q403" s="12" t="inlineStr">
+        <is>
+          <t>YSU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="17" t="inlineStr">
@@ -27394,12 +27394,12 @@
       </c>
       <c r="B404" s="17" t="inlineStr">
         <is>
-          <t>YSU @ UK</t>
+          <t>ALCN @ USM</t>
         </is>
       </c>
       <c r="C404" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 17:00</t>
+          <t>2026-09-05 21:00</t>
         </is>
       </c>
       <c r="D404" s="25" t="n">
@@ -27412,29 +27412,29 @@
       </c>
       <c r="F404" s="17" t="inlineStr">
         <is>
-          <t>Over 62.5</t>
+          <t>Under 50.5</t>
         </is>
       </c>
       <c r="G404" s="26" t="n">
-        <v>62.5</v>
+        <v>50.5</v>
       </c>
       <c r="H404" s="18" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I404" s="20" t="n">
-        <v>0.3788792876661868</v>
+        <v>0.3735050455170492</v>
       </c>
       <c r="J404" s="20" t="n">
-        <v>0.5</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K404" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L404" s="19" t="n">
-        <v>-0.144930236143337</v>
+        <v>-0.1457257237137201</v>
       </c>
       <c r="M404" s="19" t="n">
-        <v>-0.2766849962736433</v>
+        <v>-0.2806569493745719</v>
       </c>
       <c r="N404" s="20" t="n">
         <v>0</v>
@@ -27449,7 +27449,7 @@
       </c>
       <c r="Q404" s="17" t="inlineStr">
         <is>
-          <t>YSU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>ALCN isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -27461,12 +27461,12 @@
       </c>
       <c r="B405" s="12" t="inlineStr">
         <is>
-          <t>ALCN @ USM</t>
+          <t>SAC @ EMU</t>
         </is>
       </c>
       <c r="C405" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 21:00</t>
+          <t>2026-08-29 22:30</t>
         </is>
       </c>
       <c r="D405" s="22" t="n">
@@ -27474,34 +27474,32 @@
       </c>
       <c r="E405" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F405" s="12" t="inlineStr">
         <is>
-          <t>Under 50.5</t>
-        </is>
-      </c>
-      <c r="G405" s="23" t="n">
-        <v>50.5</v>
-      </c>
+          <t>EMU ML</t>
+        </is>
+      </c>
+      <c r="G405" s="23" t="n"/>
       <c r="H405" s="13" t="n">
-        <v>-108</v>
+        <v>-345</v>
       </c>
       <c r="I405" s="15" t="n">
-        <v>0.3735050455170492</v>
+        <v>0.6295209679482165</v>
       </c>
       <c r="J405" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.7440690150970525</v>
       </c>
       <c r="K405" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.7752808988764045</v>
       </c>
       <c r="L405" s="14" t="n">
-        <v>-0.1457257237137201</v>
+        <v>-0.145759930928188</v>
       </c>
       <c r="M405" s="14" t="n">
-        <v>-0.2806569493745719</v>
+        <v>-0.1880091862696917</v>
       </c>
       <c r="N405" s="15" t="n">
         <v>0</v>
@@ -27514,11 +27512,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q405" s="12" t="inlineStr">
-        <is>
-          <t>ALCN isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q405" s="12" t="n"/>
     </row>
     <row r="406">
       <c r="A406" s="17" t="inlineStr">
@@ -27528,12 +27522,12 @@
       </c>
       <c r="B406" s="17" t="inlineStr">
         <is>
-          <t>SAC @ EMU</t>
+          <t>CMU @ UNM</t>
         </is>
       </c>
       <c r="C406" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 22:30</t>
+          <t>2026-09-06 02:00</t>
         </is>
       </c>
       <c r="D406" s="25" t="n">
@@ -27541,32 +27535,34 @@
       </c>
       <c r="E406" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F406" s="17" t="inlineStr">
         <is>
-          <t>EMU ML</t>
-        </is>
-      </c>
-      <c r="G406" s="26" t="n"/>
+          <t>UNM -10.5</t>
+        </is>
+      </c>
+      <c r="G406" s="26" t="n">
+        <v>-10.5</v>
+      </c>
       <c r="H406" s="18" t="n">
-        <v>-345</v>
+        <v>-108</v>
       </c>
       <c r="I406" s="20" t="n">
-        <v>0.6295209679482165</v>
+        <v>0.3729452075758831</v>
       </c>
       <c r="J406" s="20" t="n">
-        <v>0.7440690150970525</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K406" s="20" t="n">
-        <v>0.7752808988764045</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L406" s="19" t="n">
-        <v>-0.145759930928188</v>
+        <v>-0.1462855616548862</v>
       </c>
       <c r="M406" s="19" t="n">
-        <v>-0.1880091862696917</v>
+        <v>-0.2817351557797806</v>
       </c>
       <c r="N406" s="20" t="n">
         <v>0</v>
@@ -27589,12 +27585,12 @@
       </c>
       <c r="B407" s="12" t="inlineStr">
         <is>
-          <t>CMU @ UNM</t>
+          <t>URI @ TEM</t>
         </is>
       </c>
       <c r="C407" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 02:00</t>
+          <t>2026-09-05 18:00</t>
         </is>
       </c>
       <c r="D407" s="22" t="n">
@@ -27602,34 +27598,34 @@
       </c>
       <c r="E407" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F407" s="12" t="inlineStr">
         <is>
-          <t>UNM -10.5</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="G407" s="23" t="n">
-        <v>-10.5</v>
+        <v>51.5</v>
       </c>
       <c r="H407" s="13" t="n">
-        <v>-108</v>
+        <v>-115</v>
       </c>
       <c r="I407" s="15" t="n">
-        <v>0.3729452075758831</v>
+        <v>0.3875477943072677</v>
       </c>
       <c r="J407" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K407" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L407" s="14" t="n">
-        <v>-0.1462855616548862</v>
+        <v>-0.1473359266229648</v>
       </c>
       <c r="M407" s="14" t="n">
-        <v>-0.2817351557797806</v>
+        <v>-0.2754541236864126</v>
       </c>
       <c r="N407" s="15" t="n">
         <v>0</v>
@@ -27642,7 +27638,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q407" s="12" t="n"/>
+      <c r="Q407" s="12" t="inlineStr">
+        <is>
+          <t>URI isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="17" t="inlineStr">
@@ -27845,12 +27845,12 @@
       </c>
       <c r="B411" s="12" t="inlineStr">
         <is>
-          <t>URI @ TEM</t>
+          <t>ALB @ BUFF</t>
         </is>
       </c>
       <c r="C411" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 18:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D411" s="22" t="n">
@@ -27858,32 +27858,34 @@
       </c>
       <c r="E411" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F411" s="12" t="inlineStr">
         <is>
-          <t>TEM ML</t>
-        </is>
-      </c>
-      <c r="G411" s="23" t="n"/>
+          <t>Under 48.5</t>
+        </is>
+      </c>
+      <c r="G411" s="23" t="n">
+        <v>48.5</v>
+      </c>
       <c r="H411" s="13" t="n">
-        <v>-470</v>
+        <v>-112</v>
       </c>
       <c r="I411" s="15" t="n">
-        <v>0.6736745382377289</v>
+        <v>0.3762461039069736</v>
       </c>
       <c r="J411" s="15" t="n">
-        <v>0.7913616398243045</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K411" s="15" t="n">
-        <v>0.8245614035087719</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L411" s="14" t="n">
-        <v>-0.150886865271043</v>
+        <v>-0.1520557828854793</v>
       </c>
       <c r="M411" s="14" t="n">
-        <v>-0.182990453626584</v>
+        <v>-0.2878198747475144</v>
       </c>
       <c r="N411" s="15" t="n">
         <v>0</v>
@@ -27898,7 +27900,7 @@
       </c>
       <c r="Q411" s="12" t="inlineStr">
         <is>
-          <t>URI isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -27910,12 +27912,12 @@
       </c>
       <c r="B412" s="17" t="inlineStr">
         <is>
-          <t>ALB @ BUFF</t>
+          <t>IDST @ USU</t>
         </is>
       </c>
       <c r="C412" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D412" s="25" t="n">
@@ -27923,34 +27925,32 @@
       </c>
       <c r="E412" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F412" s="17" t="inlineStr">
         <is>
-          <t>Under 48.5</t>
-        </is>
-      </c>
-      <c r="G412" s="26" t="n">
-        <v>48.5</v>
-      </c>
+          <t>USU ML</t>
+        </is>
+      </c>
+      <c r="G412" s="26" t="n"/>
       <c r="H412" s="18" t="n">
-        <v>-112</v>
+        <v>-550</v>
       </c>
       <c r="I412" s="20" t="n">
-        <v>0.3762461039069736</v>
+        <v>0.6930272228098177</v>
       </c>
       <c r="J412" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.8118668596237336</v>
       </c>
       <c r="K412" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="L412" s="19" t="n">
-        <v>-0.1520557828854793</v>
+        <v>-0.1531266233440285</v>
       </c>
       <c r="M412" s="19" t="n">
-        <v>-0.2878198747475144</v>
+        <v>-0.1809678275883973</v>
       </c>
       <c r="N412" s="20" t="n">
         <v>0</v>
@@ -27965,7 +27965,7 @@
       </c>
       <c r="Q412" s="17" t="inlineStr">
         <is>
-          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>IDST isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -27977,12 +27977,12 @@
       </c>
       <c r="B413" s="12" t="inlineStr">
         <is>
-          <t>IDST @ USU</t>
+          <t>SAC @ EMU</t>
         </is>
       </c>
       <c r="C413" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-08-29 22:30</t>
         </is>
       </c>
       <c r="D413" s="22" t="n">
@@ -27990,32 +27990,34 @@
       </c>
       <c r="E413" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F413" s="12" t="inlineStr">
         <is>
-          <t>USU ML</t>
-        </is>
-      </c>
-      <c r="G413" s="23" t="n"/>
+          <t>EMU -9.5</t>
+        </is>
+      </c>
+      <c r="G413" s="23" t="n">
+        <v>-9.5</v>
+      </c>
       <c r="H413" s="13" t="n">
-        <v>-550</v>
+        <v>-105</v>
       </c>
       <c r="I413" s="15" t="n">
-        <v>0.6930272228098177</v>
+        <v>0.3572786729962037</v>
       </c>
       <c r="J413" s="15" t="n">
-        <v>0.8118668596237336</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K413" s="15" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L413" s="14" t="n">
-        <v>-0.1531266233440285</v>
+        <v>-0.1549164489550158</v>
       </c>
       <c r="M413" s="14" t="n">
-        <v>-0.1809678275883973</v>
+        <v>-0.3024559241502689</v>
       </c>
       <c r="N413" s="15" t="n">
         <v>0</v>
@@ -28030,7 +28032,7 @@
       </c>
       <c r="Q413" s="12" t="inlineStr">
         <is>
-          <t>IDST isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>model and market are too far apart for a reliable early-season play</t>
         </is>
       </c>
     </row>
@@ -28042,12 +28044,12 @@
       </c>
       <c r="B414" s="17" t="inlineStr">
         <is>
-          <t>URI @ TEM</t>
+          <t>SHSU @ TROY</t>
         </is>
       </c>
       <c r="C414" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 18:00</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D414" s="25" t="n">
@@ -28055,37 +28057,35 @@
       </c>
       <c r="E414" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F414" s="17" t="inlineStr">
         <is>
-          <t>TEM -10</t>
-        </is>
-      </c>
-      <c r="G414" s="26" t="n">
-        <v>-10</v>
-      </c>
+          <t>TROY ML</t>
+        </is>
+      </c>
+      <c r="G414" s="26" t="n"/>
       <c r="H414" s="18" t="n">
-        <v>-108</v>
+        <v>-1000</v>
       </c>
       <c r="I414" s="20" t="n">
-        <v>0.3639538896924006</v>
+        <v>0.7537540812733499</v>
       </c>
       <c r="J414" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.8720930232558138</v>
       </c>
       <c r="K414" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="L414" s="19" t="n">
-        <v>-0.1552768795383687</v>
+        <v>-0.1553368278175592</v>
       </c>
       <c r="M414" s="19" t="n">
-        <v>-0.2891236523750743</v>
+        <v>-0.1708705105993151</v>
       </c>
       <c r="N414" s="20" t="n">
-        <v>0.0332</v>
+        <v>0</v>
       </c>
       <c r="O414" s="27" t="n">
         <v>0.45</v>
@@ -28097,7 +28097,7 @@
       </c>
       <c r="Q414" s="17" t="inlineStr">
         <is>
-          <t>URI isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>price outside allowed range</t>
         </is>
       </c>
     </row>
@@ -28109,12 +28109,12 @@
       </c>
       <c r="B415" s="12" t="inlineStr">
         <is>
-          <t>SHSU @ TROY</t>
+          <t>TAR @ BGSU</t>
         </is>
       </c>
       <c r="C415" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D415" s="22" t="n">
@@ -28122,32 +28122,34 @@
       </c>
       <c r="E415" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F415" s="12" t="inlineStr">
         <is>
-          <t>TROY ML</t>
-        </is>
-      </c>
-      <c r="G415" s="23" t="n"/>
+          <t>Under 47.5</t>
+        </is>
+      </c>
+      <c r="G415" s="23" t="n">
+        <v>47.5</v>
+      </c>
       <c r="H415" s="13" t="n">
-        <v>-1000</v>
+        <v>-110</v>
       </c>
       <c r="I415" s="15" t="n">
-        <v>0.7537540812733499</v>
+        <v>0.3678350313477137</v>
       </c>
       <c r="J415" s="15" t="n">
-        <v>0.8720930232558138</v>
+        <v>0.5</v>
       </c>
       <c r="K415" s="15" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L415" s="14" t="n">
-        <v>-0.1553368278175592</v>
+        <v>-0.1559744924618102</v>
       </c>
       <c r="M415" s="14" t="n">
-        <v>-0.1708705105993151</v>
+        <v>-0.2977694856089103</v>
       </c>
       <c r="N415" s="15" t="n">
         <v>0</v>
@@ -28162,7 +28164,7 @@
       </c>
       <c r="Q415" s="12" t="inlineStr">
         <is>
-          <t>price outside allowed range</t>
+          <t>TAR isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28176,7 @@
       </c>
       <c r="B416" s="17" t="inlineStr">
         <is>
-          <t>TAR @ BGSU</t>
+          <t>OHIO @ NEB</t>
         </is>
       </c>
       <c r="C416" s="17" t="inlineStr">
@@ -28199,22 +28201,22 @@
         <v>47.5</v>
       </c>
       <c r="H416" s="18" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="I416" s="20" t="n">
-        <v>0.3678350313477137</v>
+        <v>0.3715450078325325</v>
       </c>
       <c r="J416" s="20" t="n">
-        <v>0.5</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K416" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L416" s="19" t="n">
-        <v>-0.1559744924618102</v>
+        <v>-0.1567568789599203</v>
       </c>
       <c r="M416" s="19" t="n">
-        <v>-0.2977694856089103</v>
+        <v>-0.2967183780312778</v>
       </c>
       <c r="N416" s="20" t="n">
         <v>0</v>
@@ -28227,11 +28229,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q416" s="17" t="inlineStr">
-        <is>
-          <t>TAR isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q416" s="17" t="n"/>
     </row>
     <row r="417">
       <c r="A417" s="12" t="inlineStr">
@@ -28241,12 +28239,12 @@
       </c>
       <c r="B417" s="12" t="inlineStr">
         <is>
-          <t>OHIO @ NEB</t>
+          <t>TULN @ DUKE</t>
         </is>
       </c>
       <c r="C417" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D417" s="22" t="n">
@@ -28259,29 +28257,29 @@
       </c>
       <c r="F417" s="12" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
+          <t>Under 50.5</t>
         </is>
       </c>
       <c r="G417" s="23" t="n">
-        <v>47.5</v>
+        <v>50.5</v>
       </c>
       <c r="H417" s="13" t="n">
-        <v>-112</v>
+        <v>-105</v>
       </c>
       <c r="I417" s="15" t="n">
-        <v>0.3715450078325325</v>
+        <v>0.3548602420613127</v>
       </c>
       <c r="J417" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K417" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L417" s="14" t="n">
-        <v>-0.1567568789599203</v>
+        <v>-0.1573348798899068</v>
       </c>
       <c r="M417" s="14" t="n">
-        <v>-0.2967183780312778</v>
+        <v>-0.307177622642199</v>
       </c>
       <c r="N417" s="15" t="n">
         <v>0</v>
@@ -28304,12 +28302,12 @@
       </c>
       <c r="B418" s="17" t="inlineStr">
         <is>
-          <t>TULN @ DUKE</t>
+          <t>URI @ TEM</t>
         </is>
       </c>
       <c r="C418" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-05 18:00</t>
         </is>
       </c>
       <c r="D418" s="25" t="n">
@@ -28317,34 +28315,34 @@
       </c>
       <c r="E418" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F418" s="17" t="inlineStr">
         <is>
-          <t>Under 50.5</t>
+          <t>TEM -10.5</t>
         </is>
       </c>
       <c r="G418" s="26" t="n">
-        <v>50.5</v>
+        <v>-10.5</v>
       </c>
       <c r="H418" s="18" t="n">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="I418" s="20" t="n">
-        <v>0.3548602420613127</v>
+        <v>0.3600989031461477</v>
       </c>
       <c r="J418" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K418" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L418" s="19" t="n">
-        <v>-0.1573348798899068</v>
+        <v>-0.1591318660846216</v>
       </c>
       <c r="M418" s="19" t="n">
-        <v>-0.307177622642199</v>
+        <v>-0.3064761865333452</v>
       </c>
       <c r="N418" s="20" t="n">
         <v>0</v>
@@ -28357,7 +28355,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q418" s="17" t="n"/>
+      <c r="Q418" s="17" t="inlineStr">
+        <is>
+          <t>URI isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="12" t="inlineStr">
@@ -28499,12 +28501,12 @@
       </c>
       <c r="B421" s="12" t="inlineStr">
         <is>
-          <t>SELA @ USA</t>
+          <t>URI @ TEM</t>
         </is>
       </c>
       <c r="C421" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-05 18:00</t>
         </is>
       </c>
       <c r="D421" s="22" t="n">
@@ -28517,27 +28519,27 @@
       </c>
       <c r="F421" s="12" t="inlineStr">
         <is>
-          <t>USA ML</t>
+          <t>TEM ML</t>
         </is>
       </c>
       <c r="G421" s="23" t="n"/>
       <c r="H421" s="13" t="n">
-        <v>-600</v>
+        <v>-550</v>
       </c>
       <c r="I421" s="15" t="n">
-        <v>0.6945722663174285</v>
+        <v>0.6839271481374435</v>
       </c>
       <c r="J421" s="15" t="n">
-        <v>0.8223350253807106</v>
+        <v>0.8118668596237336</v>
       </c>
       <c r="K421" s="15" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="L421" s="14" t="n">
-        <v>-0.1625705908254286</v>
+        <v>-0.1622266980164027</v>
       </c>
       <c r="M421" s="14" t="n">
-        <v>-0.1896656892963333</v>
+        <v>-0.1917224612921122</v>
       </c>
       <c r="N421" s="15" t="n">
         <v>0</v>
@@ -28552,7 +28554,7 @@
       </c>
       <c r="Q421" s="12" t="inlineStr">
         <is>
-          <t>SELA isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>URI isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -28564,12 +28566,12 @@
       </c>
       <c r="B422" s="17" t="inlineStr">
         <is>
-          <t>SAC @ EMU</t>
+          <t>SELA @ USA</t>
         </is>
       </c>
       <c r="C422" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 22:30</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D422" s="25" t="n">
@@ -28577,34 +28579,32 @@
       </c>
       <c r="E422" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F422" s="17" t="inlineStr">
         <is>
-          <t>EMU -9.5</t>
-        </is>
-      </c>
-      <c r="G422" s="26" t="n">
-        <v>-9.5</v>
-      </c>
+          <t>USA ML</t>
+        </is>
+      </c>
+      <c r="G422" s="26" t="n"/>
       <c r="H422" s="18" t="n">
-        <v>-112</v>
+        <v>-600</v>
       </c>
       <c r="I422" s="20" t="n">
-        <v>0.3648606681243626</v>
+        <v>0.6945722663174285</v>
       </c>
       <c r="J422" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.8223350253807106</v>
       </c>
       <c r="K422" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="L422" s="19" t="n">
-        <v>-0.1634412186680902</v>
+        <v>-0.1625705908254286</v>
       </c>
       <c r="M422" s="19" t="n">
-        <v>-0.3093708781931707</v>
+        <v>-0.1896656892963333</v>
       </c>
       <c r="N422" s="20" t="n">
         <v>0</v>
@@ -28619,7 +28619,7 @@
       </c>
       <c r="Q422" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>SELA isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -35306,12 +35306,12 @@
       </c>
       <c r="B524" s="17" t="inlineStr">
         <is>
-          <t>BRY @ ARMY</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C524" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D524" s="25" t="n">
@@ -35324,17 +35324,17 @@
       </c>
       <c r="F524" s="17" t="inlineStr">
         <is>
-          <t>ARMY -36.5</t>
+          <t>USC -38.5</t>
         </is>
       </c>
       <c r="G524" s="26" t="n">
-        <v>-36.5</v>
+        <v>-38.5</v>
       </c>
       <c r="H524" s="18" t="n">
         <v>-108</v>
       </c>
       <c r="I524" s="20" t="n">
-        <v>0.2500678397522949</v>
+        <v>0.2501562069162203</v>
       </c>
       <c r="J524" s="20" t="n">
         <v>0.4956702459300312</v>
@@ -35343,10 +35343,10 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L524" s="19" t="n">
-        <v>-0.2691629294784744</v>
+        <v>-0.269074562314549</v>
       </c>
       <c r="M524" s="19" t="n">
-        <v>-0.5183878641807653</v>
+        <v>-0.518217675568761</v>
       </c>
       <c r="N524" s="20" t="n">
         <v>0</v>
@@ -35361,7 +35361,7 @@
       </c>
       <c r="Q524" s="17" t="inlineStr">
         <is>
-          <t>BRY isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -35373,12 +35373,12 @@
       </c>
       <c r="B525" s="12" t="inlineStr">
         <is>
-          <t>KENT @ SC</t>
+          <t>BRY @ ARMY</t>
         </is>
       </c>
       <c r="C525" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 16:45</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D525" s="22" t="n">
@@ -35391,7 +35391,7 @@
       </c>
       <c r="F525" s="12" t="inlineStr">
         <is>
-          <t>SC -36.5</t>
+          <t>ARMY -36.5</t>
         </is>
       </c>
       <c r="G525" s="23" t="n">
@@ -35401,7 +35401,7 @@
         <v>-108</v>
       </c>
       <c r="I525" s="15" t="n">
-        <v>0.2499368613568438</v>
+        <v>0.2500678397522949</v>
       </c>
       <c r="J525" s="15" t="n">
         <v>0.4956702459300312</v>
@@ -35410,10 +35410,10 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L525" s="14" t="n">
-        <v>-0.2692939078739255</v>
+        <v>-0.2691629294784744</v>
       </c>
       <c r="M525" s="14" t="n">
-        <v>-0.5186401188683007</v>
+        <v>-0.5183878641807653</v>
       </c>
       <c r="N525" s="15" t="n">
         <v>0</v>
@@ -35428,7 +35428,7 @@
       </c>
       <c r="Q525" s="12" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>BRY isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -35440,12 +35440,12 @@
       </c>
       <c r="B526" s="17" t="inlineStr">
         <is>
-          <t>WMU @ MICH</t>
+          <t>KENT @ SC</t>
         </is>
       </c>
       <c r="C526" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-09-05 16:45</t>
         </is>
       </c>
       <c r="D526" s="25" t="n">
@@ -35458,29 +35458,29 @@
       </c>
       <c r="F526" s="17" t="inlineStr">
         <is>
-          <t>MICH -27.5</t>
+          <t>SC -36.5</t>
         </is>
       </c>
       <c r="G526" s="26" t="n">
-        <v>-27.5</v>
+        <v>-36.5</v>
       </c>
       <c r="H526" s="18" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="I526" s="20" t="n">
-        <v>0.2654934830558677</v>
+        <v>0.2499368613568438</v>
       </c>
       <c r="J526" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K526" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L526" s="19" t="n">
-        <v>-0.2693902378743648</v>
+        <v>-0.2692939078739255</v>
       </c>
       <c r="M526" s="19" t="n">
-        <v>-0.5036426186346822</v>
+        <v>-0.5186401188683007</v>
       </c>
       <c r="N526" s="20" t="n">
         <v>0</v>
@@ -35507,12 +35507,12 @@
       </c>
       <c r="B527" s="12" t="inlineStr">
         <is>
-          <t>IDHO @ UTAH</t>
+          <t>WMU @ MICH</t>
         </is>
       </c>
       <c r="C527" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 01:00</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D527" s="22" t="n">
@@ -35525,29 +35525,29 @@
       </c>
       <c r="F527" s="12" t="inlineStr">
         <is>
-          <t>UTAH -33.5</t>
+          <t>MICH -27.5</t>
         </is>
       </c>
       <c r="G527" s="23" t="n">
-        <v>-33.5</v>
+        <v>-27.5</v>
       </c>
       <c r="H527" s="13" t="n">
-        <v>-112</v>
+        <v>-115</v>
       </c>
       <c r="I527" s="15" t="n">
-        <v>0.2585208472473556</v>
+        <v>0.2654934830558677</v>
       </c>
       <c r="J527" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K527" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L527" s="14" t="n">
-        <v>-0.2697810395450972</v>
+        <v>-0.2693902378743648</v>
       </c>
       <c r="M527" s="14" t="n">
-        <v>-0.5106569677103627</v>
+        <v>-0.5036426186346822</v>
       </c>
       <c r="N527" s="15" t="n">
         <v>0</v>
@@ -35562,7 +35562,7 @@
       </c>
       <c r="Q527" s="12" t="inlineStr">
         <is>
-          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -35574,12 +35574,12 @@
       </c>
       <c r="B528" s="17" t="inlineStr">
         <is>
-          <t>UNA @ ARK</t>
+          <t>IDHO @ UTAH</t>
         </is>
       </c>
       <c r="C528" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 20:15</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D528" s="25" t="n">
@@ -35592,29 +35592,29 @@
       </c>
       <c r="F528" s="17" t="inlineStr">
         <is>
-          <t>ARK -40.5</t>
+          <t>UTAH -33.5</t>
         </is>
       </c>
       <c r="G528" s="26" t="n">
-        <v>-40.5</v>
+        <v>-33.5</v>
       </c>
       <c r="H528" s="18" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I528" s="20" t="n">
-        <v>0.2485003206460911</v>
+        <v>0.2585208472473556</v>
       </c>
       <c r="J528" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K528" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L528" s="19" t="n">
-        <v>-0.2707304485846782</v>
+        <v>-0.2697810395450972</v>
       </c>
       <c r="M528" s="19" t="n">
-        <v>-0.5214067898667876</v>
+        <v>-0.5106569677103627</v>
       </c>
       <c r="N528" s="20" t="n">
         <v>0</v>
@@ -35629,7 +35629,7 @@
       </c>
       <c r="Q528" s="17" t="inlineStr">
         <is>
-          <t>UNA isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -35641,12 +35641,12 @@
       </c>
       <c r="B529" s="12" t="inlineStr">
         <is>
-          <t>INST @ PUR</t>
+          <t>UNA @ ARK</t>
         </is>
       </c>
       <c r="C529" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 23:00</t>
+          <t>2026-09-05 20:15</t>
         </is>
       </c>
       <c r="D529" s="22" t="n">
@@ -35659,29 +35659,29 @@
       </c>
       <c r="F529" s="12" t="inlineStr">
         <is>
-          <t>PUR -35.5</t>
+          <t>ARK -40.5</t>
         </is>
       </c>
       <c r="G529" s="23" t="n">
-        <v>-35.5</v>
+        <v>-40.5</v>
       </c>
       <c r="H529" s="13" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I529" s="15" t="n">
-        <v>0.2528934298318226</v>
+        <v>0.2485003206460911</v>
       </c>
       <c r="J529" s="15" t="n">
-        <v>0.5021949078138718</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K529" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L529" s="14" t="n">
-        <v>-0.2709160939777012</v>
+        <v>-0.2707304485846782</v>
       </c>
       <c r="M529" s="14" t="n">
-        <v>-0.5172034521392477</v>
+        <v>-0.5214067898667876</v>
       </c>
       <c r="N529" s="15" t="n">
         <v>0</v>
@@ -35696,7 +35696,7 @@
       </c>
       <c r="Q529" s="12" t="inlineStr">
         <is>
-          <t>INST isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>UNA isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -35708,12 +35708,12 @@
       </c>
       <c r="B530" s="17" t="inlineStr">
         <is>
-          <t>EIU @ MINN</t>
+          <t>INST @ PUR</t>
         </is>
       </c>
       <c r="C530" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-09-04 23:00</t>
         </is>
       </c>
       <c r="D530" s="25" t="n">
@@ -35726,29 +35726,29 @@
       </c>
       <c r="F530" s="17" t="inlineStr">
         <is>
-          <t>MINN -43.5</t>
+          <t>PUR -35.5</t>
         </is>
       </c>
       <c r="G530" s="26" t="n">
-        <v>-43.5</v>
+        <v>-35.5</v>
       </c>
       <c r="H530" s="18" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I530" s="20" t="n">
-        <v>0.2481768262232006</v>
+        <v>0.2528934298318226</v>
       </c>
       <c r="J530" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5021949078138718</v>
       </c>
       <c r="K530" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L530" s="19" t="n">
-        <v>-0.2710539430075687</v>
+        <v>-0.2709160939777012</v>
       </c>
       <c r="M530" s="19" t="n">
-        <v>-0.5220298161627247</v>
+        <v>-0.5172034521392477</v>
       </c>
       <c r="N530" s="20" t="n">
         <v>0</v>
@@ -35763,7 +35763,7 @@
       </c>
       <c r="Q530" s="17" t="inlineStr">
         <is>
-          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>INST isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -35775,12 +35775,12 @@
       </c>
       <c r="B531" s="12" t="inlineStr">
         <is>
-          <t>BALL @ OSU</t>
+          <t>EIU @ MINN</t>
         </is>
       </c>
       <c r="C531" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 16:30</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D531" s="22" t="n">
@@ -35793,17 +35793,17 @@
       </c>
       <c r="F531" s="12" t="inlineStr">
         <is>
-          <t>OSU -50.5</t>
+          <t>MINN -43.5</t>
         </is>
       </c>
       <c r="G531" s="23" t="n">
-        <v>-50.5</v>
+        <v>-43.5</v>
       </c>
       <c r="H531" s="13" t="n">
         <v>-108</v>
       </c>
       <c r="I531" s="15" t="n">
-        <v>0.2480345857275048</v>
+        <v>0.2481768262232006</v>
       </c>
       <c r="J531" s="15" t="n">
         <v>0.4956702459300312</v>
@@ -35812,10 +35812,10 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L531" s="14" t="n">
-        <v>-0.2711961835032645</v>
+        <v>-0.2710539430075687</v>
       </c>
       <c r="M531" s="14" t="n">
-        <v>-0.5223037608211019</v>
+        <v>-0.5220298161627247</v>
       </c>
       <c r="N531" s="15" t="n">
         <v>0</v>
@@ -35830,7 +35830,7 @@
       </c>
       <c r="Q531" s="12" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -35842,12 +35842,12 @@
       </c>
       <c r="B532" s="17" t="inlineStr">
         <is>
-          <t>HAMP @ MD</t>
+          <t>BALL @ OSU</t>
         </is>
       </c>
       <c r="C532" s="17" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00</t>
+          <t>2026-09-05 16:30</t>
         </is>
       </c>
       <c r="D532" s="25" t="n">
@@ -35860,17 +35860,17 @@
       </c>
       <c r="F532" s="17" t="inlineStr">
         <is>
-          <t>MD -45.5</t>
+          <t>OSU -50.5</t>
         </is>
       </c>
       <c r="G532" s="26" t="n">
-        <v>-45.5</v>
+        <v>-50.5</v>
       </c>
       <c r="H532" s="18" t="n">
         <v>-108</v>
       </c>
       <c r="I532" s="20" t="n">
-        <v>0.2479827101867709</v>
+        <v>0.2480345857275048</v>
       </c>
       <c r="J532" s="20" t="n">
         <v>0.4956702459300312</v>
@@ -35879,16 +35879,16 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L532" s="19" t="n">
-        <v>-0.2712480590439984</v>
+        <v>-0.2711961835032645</v>
       </c>
       <c r="M532" s="19" t="n">
-        <v>-0.5224036692699228</v>
+        <v>-0.5223037608211019</v>
       </c>
       <c r="N532" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O532" s="27" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="P532" s="17" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
       </c>
       <c r="Q532" s="17" t="inlineStr">
         <is>
-          <t>HAMP isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -35909,12 +35909,12 @@
       </c>
       <c r="B533" s="12" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>HAMP @ MD</t>
         </is>
       </c>
       <c r="C533" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-09-06 00:00</t>
         </is>
       </c>
       <c r="D533" s="22" t="n">
@@ -35927,35 +35927,35 @@
       </c>
       <c r="F533" s="12" t="inlineStr">
         <is>
-          <t>USC -38.5</t>
+          <t>MD -45.5</t>
         </is>
       </c>
       <c r="G533" s="23" t="n">
-        <v>-38.5</v>
+        <v>-45.5</v>
       </c>
       <c r="H533" s="13" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I533" s="15" t="n">
-        <v>0.2523210839512047</v>
+        <v>0.2479827101867709</v>
       </c>
       <c r="J533" s="15" t="n">
-        <v>0.5</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K533" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L533" s="14" t="n">
-        <v>-0.2714884398583192</v>
+        <v>-0.2712480590439984</v>
       </c>
       <c r="M533" s="14" t="n">
-        <v>-0.5182961124567911</v>
+        <v>-0.5224036692699228</v>
       </c>
       <c r="N533" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O533" s="24" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="P533" s="12" t="inlineStr">
         <is>
@@ -35964,7 +35964,7 @@
       </c>
       <c r="Q533" s="12" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>HAMP isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -44606,10 +44606,10 @@
         <v>46.5</v>
       </c>
       <c r="K5" s="13" t="n">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="L5" s="13" t="n">
-        <v>-345</v>
+        <v>-340</v>
       </c>
       <c r="M5" s="12" t="inlineStr">
         <is>
@@ -44697,7 +44697,7 @@
         <v>-4</v>
       </c>
       <c r="J7" s="29" t="n">
-        <v>50.5</v>
+        <v>51.5</v>
       </c>
       <c r="K7" s="13" t="n">
         <v>150</v>
@@ -44847,10 +44847,10 @@
         <v>48.5</v>
       </c>
       <c r="K10" s="18" t="n">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="L10" s="18" t="n">
-        <v>-198</v>
+        <v>-185</v>
       </c>
       <c r="M10" s="17" t="inlineStr">
         <is>
@@ -44939,7 +44939,7 @@
       </c>
       <c r="H12" s="17" t="inlineStr"/>
       <c r="I12" s="26" t="n">
-        <v>-4.5</v>
+        <v>-4</v>
       </c>
       <c r="J12" s="30" t="n">
         <v>56.5</v>
@@ -46667,16 +46667,16 @@
       </c>
       <c r="H48" s="17" t="inlineStr"/>
       <c r="I48" s="26" t="n">
-        <v>-10</v>
+        <v>-10.5</v>
       </c>
       <c r="J48" s="30" t="n">
         <v>51.5</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>360</v>
+        <v>410</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>-470</v>
+        <v>-550</v>
       </c>
       <c r="M48" s="17" t="inlineStr">
         <is>

--- a/NCAAF_Edge_Model.xlsx
+++ b/NCAAF_Edge_Model.xlsx
@@ -640,7 +640,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-29T03:02:44+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
+          <t>Generated 2026-08-29T13:04:38+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>Settings!B5+SUMIF('Bet Ledger'!$G$6:$G$20,"&lt;&gt;Pending",'Bet Ledger'!$H$6:$H$20)</f>
+        <f>Settings!B5+SUMIF('Bet Ledger'!$G$6:$G$21,"&lt;&gt;Pending",'Bet Ledger'!$H$6:$H$21)</f>
         <v/>
       </c>
     </row>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>SUMIF('Bet Ledger'!$G$6:$G$20,"&lt;&gt;Pending",'Bet Ledger'!$F$6:$F$20)</f>
+        <f>SUMIF('Bet Ledger'!$G$6:$G$21,"&lt;&gt;Pending",'Bet Ledger'!$F$6:$F$21)</f>
         <v/>
       </c>
     </row>
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>SUMIF('Bet Ledger'!$G$6:$G$20,"&lt;&gt;Pending",'Bet Ledger'!$H$6:$H$20)</f>
+        <f>SUMIF('Bet Ledger'!$G$6:$G$21,"&lt;&gt;Pending",'Bet Ledger'!$H$6:$H$21)</f>
         <v/>
       </c>
     </row>
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="B9" s="7">
-        <f>COUNTIFS('Bet Ledger'!$G$6:$G$20,"&lt;&gt;Pending",'Bet Ledger'!$G$6:$G$20,"&lt;&gt;")</f>
+        <f>COUNTIFS('Bet Ledger'!$G$6:$G$21,"&lt;&gt;Pending",'Bet Ledger'!$G$6:$G$21,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>COUNTIF('Bet Ledger'!$G$6:$G$20,"Win")</f>
+        <f>COUNTIF('Bet Ledger'!$G$6:$G$21,"Win")</f>
         <v/>
       </c>
     </row>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>COUNTIF('Bet Ledger'!$G$6:$G$20,"Loss")</f>
+        <f>COUNTIF('Bet Ledger'!$G$6:$G$21,"Loss")</f>
         <v/>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B12" s="7">
-        <f>COUNTIF('Bet Ledger'!$G$6:$G$20,"Push")</f>
+        <f>COUNTIF('Bet Ledger'!$G$6:$G$21,"Push")</f>
         <v/>
       </c>
     </row>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="B14" s="7">
-        <f>COUNTIF('Bet Ledger'!$G$6:$G$20,"Pending")</f>
+        <f>COUNTIF('Bet Ledger'!$G$6:$G$21,"Pending")</f>
         <v/>
       </c>
     </row>
@@ -1068,22 +1068,22 @@
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>SAC ML</t>
+          <t>SAC +8.5</t>
         </is>
       </c>
       <c r="E23" s="13" t="n">
-        <v>275</v>
+        <v>-108</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0.1038123653851168</v>
+        <v>0.1064813533659181</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0.3704790320517835</v>
+        <v>0.6257121225966874</v>
       </c>
       <c r="H23" s="16" t="n"/>
       <c r="I23" s="12" t="inlineStr">
@@ -1322,32 +1322,32 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>HAW @ STAN</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D30" s="17" t="inlineStr">
         <is>
-          <t>UNC +8.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E30" s="18" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>0.08979036342630042</v>
+        <v>0.08840272575750341</v>
       </c>
       <c r="G30" s="20" t="n">
-        <v>0.6135998872358243</v>
+        <v>0.6232864466877359</v>
       </c>
       <c r="H30" s="21" t="n"/>
       <c r="I30" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
     </row>
@@ -1632,32 +1632,34 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>SAC ML</t>
-        </is>
-      </c>
-      <c r="G7" s="23" t="n"/>
+          <t>SAC +8.5</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="n">
+        <v>-8.5</v>
+      </c>
       <c r="H7" s="13" t="n">
-        <v>275</v>
+        <v>-108</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>0.3704790320517835</v>
+        <v>0.6257121225966874</v>
       </c>
       <c r="J7" s="15" t="n">
-        <v>0.2559309849029475</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K7" s="15" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L7" s="14" t="n">
-        <v>0.1038123653851168</v>
+        <v>0.1064813533659181</v>
       </c>
       <c r="M7" s="14" t="n">
-        <v>0.3892963701941881</v>
+        <v>0.2050751990751017</v>
       </c>
       <c r="N7" s="15" t="n">
         <v>0</v>
@@ -2056,12 +2058,12 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>HAW @ STAN</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D14" s="25" t="n">
@@ -2069,34 +2071,34 @@
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t>UNC +8.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="G14" s="26" t="n">
-        <v>-8.5</v>
+        <v>48.5</v>
       </c>
       <c r="H14" s="18" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="I14" s="20" t="n">
-        <v>0.6135998872358243</v>
+        <v>0.6232864466877359</v>
       </c>
       <c r="J14" s="20" t="n">
-        <v>0.5</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K14" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L14" s="19" t="n">
-        <v>0.08979036342630042</v>
+        <v>0.08840272575750341</v>
       </c>
       <c r="M14" s="19" t="n">
-        <v>0.1714179665411191</v>
+        <v>0.1652746611988105</v>
       </c>
       <c r="N14" s="20" t="n">
         <v>0</v>
@@ -2144,22 +2146,22 @@
         <v>-41.5</v>
       </c>
       <c r="H15" s="13" t="n">
-        <v>105</v>
+        <v>-102</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>0.7327885682520831</v>
+        <v>0.7403402716277143</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>0.4675324675324675</v>
+        <v>0.4826358742837298</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>0.4878048780487805</v>
+        <v>0.504950495049505</v>
       </c>
       <c r="L15" s="14" t="n">
-        <v>0.2449836902033026</v>
+        <v>0.2353897765782094</v>
       </c>
       <c r="M15" s="14" t="n">
-        <v>0.5022165649167701</v>
+        <v>0.4661640673411598</v>
       </c>
       <c r="N15" s="15" t="n">
         <v>0</v>
@@ -3256,12 +3258,12 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>HAMP @ MD</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D32" s="25" t="n">
@@ -3274,35 +3276,35 @@
       </c>
       <c r="F32" s="17" t="inlineStr">
         <is>
-          <t>HAMP +45.5</t>
+          <t>SJSU +38.5</t>
         </is>
       </c>
       <c r="G32" s="26" t="n">
-        <v>-45.5</v>
+        <v>-38.5</v>
       </c>
       <c r="H32" s="18" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I32" s="20" t="n">
-        <v>0.7520172898132291</v>
+        <v>0.7476789160487953</v>
       </c>
       <c r="J32" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K32" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L32" s="19" t="n">
-        <v>0.2237154030207763</v>
+        <v>0.2238693922392715</v>
       </c>
       <c r="M32" s="19" t="n">
-        <v>0.4234612985750408</v>
+        <v>0.4273870215477003</v>
       </c>
       <c r="N32" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O32" s="27" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="P32" s="17" t="inlineStr">
         <is>
@@ -3311,7 +3313,7 @@
       </c>
       <c r="Q32" s="17" t="inlineStr">
         <is>
-          <t>HAMP isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -3323,12 +3325,12 @@
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>BALL @ OSU</t>
+          <t>HAMP @ MD</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 16:30</t>
+          <t>2026-09-06 00:00</t>
         </is>
       </c>
       <c r="D33" s="22" t="n">
@@ -3341,17 +3343,17 @@
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>BALL +50.5</t>
+          <t>HAMP +45.5</t>
         </is>
       </c>
       <c r="G33" s="23" t="n">
-        <v>-50.5</v>
+        <v>-45.5</v>
       </c>
       <c r="H33" s="13" t="n">
         <v>-112</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>0.7519654142724952</v>
+        <v>0.7520172898132291</v>
       </c>
       <c r="J33" s="15" t="n">
         <v>0.5043297540699688</v>
@@ -3360,16 +3362,16 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L33" s="14" t="n">
-        <v>0.2236635274800424</v>
+        <v>0.2237154030207763</v>
       </c>
       <c r="M33" s="14" t="n">
-        <v>0.423363105587223</v>
+        <v>0.4234612985750408</v>
       </c>
       <c r="N33" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O33" s="24" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="P33" s="12" t="inlineStr">
         <is>
@@ -3378,7 +3380,7 @@
       </c>
       <c r="Q33" s="12" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>HAMP isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -3390,12 +3392,12 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>EIU @ MINN</t>
+          <t>BALL @ OSU</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-09-05 16:30</t>
         </is>
       </c>
       <c r="D34" s="25" t="n">
@@ -3408,17 +3410,17 @@
       </c>
       <c r="F34" s="17" t="inlineStr">
         <is>
-          <t>EIU +43.5</t>
+          <t>BALL +50.5</t>
         </is>
       </c>
       <c r="G34" s="26" t="n">
-        <v>-43.5</v>
+        <v>-50.5</v>
       </c>
       <c r="H34" s="18" t="n">
         <v>-112</v>
       </c>
       <c r="I34" s="20" t="n">
-        <v>0.7518231737767994</v>
+        <v>0.7519654142724952</v>
       </c>
       <c r="J34" s="20" t="n">
         <v>0.5043297540699688</v>
@@ -3427,10 +3429,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L34" s="19" t="n">
-        <v>0.2235212869843466</v>
+        <v>0.2236635274800424</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>0.4230938646489417</v>
+        <v>0.423363105587223</v>
       </c>
       <c r="N34" s="20" t="n">
         <v>0</v>
@@ -3445,7 +3447,7 @@
       </c>
       <c r="Q34" s="17" t="inlineStr">
         <is>
-          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3459,12 @@
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>UNA @ ARK</t>
+          <t>EIU @ MINN</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 20:15</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D35" s="22" t="n">
@@ -3475,17 +3477,17 @@
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>UNA +40.5</t>
+          <t>EIU +43.5</t>
         </is>
       </c>
       <c r="G35" s="23" t="n">
-        <v>-40.5</v>
+        <v>-43.5</v>
       </c>
       <c r="H35" s="13" t="n">
         <v>-112</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>0.7514996793539089</v>
+        <v>0.7518231737767994</v>
       </c>
       <c r="J35" s="15" t="n">
         <v>0.5043297540699688</v>
@@ -3494,10 +3496,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L35" s="14" t="n">
-        <v>0.2231977925614561</v>
+        <v>0.2235212869843466</v>
       </c>
       <c r="M35" s="14" t="n">
-        <v>0.422481535919899</v>
+        <v>0.4230938646489417</v>
       </c>
       <c r="N35" s="15" t="n">
         <v>0</v>
@@ -3512,7 +3514,7 @@
       </c>
       <c r="Q35" s="12" t="inlineStr">
         <is>
-          <t>UNA isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -3524,12 +3526,12 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>WMU @ MICH</t>
+          <t>UNA @ ARK</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-09-05 20:15</t>
         </is>
       </c>
       <c r="D36" s="25" t="n">
@@ -3542,29 +3544,29 @@
       </c>
       <c r="F36" s="17" t="inlineStr">
         <is>
-          <t>WMU +27.5</t>
+          <t>UNA +40.5</t>
         </is>
       </c>
       <c r="G36" s="26" t="n">
-        <v>-27.5</v>
+        <v>-40.5</v>
       </c>
       <c r="H36" s="18" t="n">
-        <v>-105</v>
+        <v>-112</v>
       </c>
       <c r="I36" s="20" t="n">
-        <v>0.7345065169441323</v>
+        <v>0.7514996793539089</v>
       </c>
       <c r="J36" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K36" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L36" s="19" t="n">
-        <v>0.2223113949929127</v>
+        <v>0.2231977925614561</v>
       </c>
       <c r="M36" s="19" t="n">
-        <v>0.4340365330814011</v>
+        <v>0.422481535919899</v>
       </c>
       <c r="N36" s="20" t="n">
         <v>0</v>
@@ -3579,7 +3581,7 @@
       </c>
       <c r="Q36" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>UNA isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -3591,12 +3593,12 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>IDHO @ UTAH</t>
+          <t>WMU @ MICH</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 01:00</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D37" s="22" t="n">
@@ -3609,29 +3611,29 @@
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>IDHO +33.5</t>
+          <t>WMU +27.5</t>
         </is>
       </c>
       <c r="G37" s="23" t="n">
-        <v>-33.5</v>
+        <v>-27.5</v>
       </c>
       <c r="H37" s="13" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>0.7414791527526444</v>
+        <v>0.7345065169441323</v>
       </c>
       <c r="J37" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K37" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L37" s="14" t="n">
-        <v>0.2222483835218751</v>
+        <v>0.2223113949929127</v>
       </c>
       <c r="M37" s="14" t="n">
-        <v>0.4280339238199079</v>
+        <v>0.4340365330814011</v>
       </c>
       <c r="N37" s="15" t="n">
         <v>0</v>
@@ -3646,7 +3648,7 @@
       </c>
       <c r="Q37" s="12" t="inlineStr">
         <is>
-          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -3658,12 +3660,12 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>KENT @ SC</t>
+          <t>IDHO @ UTAH</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 16:45</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D38" s="25" t="n">
@@ -3676,29 +3678,29 @@
       </c>
       <c r="F38" s="17" t="inlineStr">
         <is>
-          <t>KENT +36.5</t>
+          <t>IDHO +33.5</t>
         </is>
       </c>
       <c r="G38" s="26" t="n">
-        <v>-36.5</v>
+        <v>-33.5</v>
       </c>
       <c r="H38" s="18" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="I38" s="20" t="n">
-        <v>0.7500631386431562</v>
+        <v>0.7414791527526444</v>
       </c>
       <c r="J38" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K38" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>0.2217612518507034</v>
+        <v>0.2222483835218751</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>0.4197623695745456</v>
+        <v>0.4280339238199079</v>
       </c>
       <c r="N38" s="20" t="n">
         <v>0</v>
@@ -3713,7 +3715,7 @@
       </c>
       <c r="Q38" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -3725,12 +3727,12 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>BRY @ ARMY</t>
+          <t>KENT @ SC</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-09-05 16:45</t>
         </is>
       </c>
       <c r="D39" s="22" t="n">
@@ -3743,7 +3745,7 @@
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>BRY +36.5</t>
+          <t>KENT +36.5</t>
         </is>
       </c>
       <c r="G39" s="23" t="n">
@@ -3753,7 +3755,7 @@
         <v>-112</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>0.7499321602477051</v>
+        <v>0.7500631386431562</v>
       </c>
       <c r="J39" s="15" t="n">
         <v>0.5043297540699688</v>
@@ -3762,10 +3764,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L39" s="14" t="n">
-        <v>0.2216302734552523</v>
+        <v>0.2217612518507034</v>
       </c>
       <c r="M39" s="14" t="n">
-        <v>0.4195144461831561</v>
+        <v>0.4197623695745456</v>
       </c>
       <c r="N39" s="15" t="n">
         <v>0</v>
@@ -3780,7 +3782,7 @@
       </c>
       <c r="Q39" s="12" t="inlineStr">
         <is>
-          <t>BRY isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -3792,12 +3794,12 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>BRY @ ARMY</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D40" s="25" t="n">
@@ -3810,17 +3812,17 @@
       </c>
       <c r="F40" s="17" t="inlineStr">
         <is>
-          <t>SJSU +38.5</t>
+          <t>BRY +36.5</t>
         </is>
       </c>
       <c r="G40" s="26" t="n">
-        <v>-38.5</v>
+        <v>-36.5</v>
       </c>
       <c r="H40" s="18" t="n">
         <v>-112</v>
       </c>
       <c r="I40" s="20" t="n">
-        <v>0.7498437930837798</v>
+        <v>0.7499321602477051</v>
       </c>
       <c r="J40" s="20" t="n">
         <v>0.5043297540699688</v>
@@ -3829,10 +3831,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L40" s="19" t="n">
-        <v>0.221541906291327</v>
+        <v>0.2216302734552523</v>
       </c>
       <c r="M40" s="19" t="n">
-        <v>0.419347179765726</v>
+        <v>0.4195144461831561</v>
       </c>
       <c r="N40" s="20" t="n">
         <v>0</v>
@@ -3847,7 +3849,7 @@
       </c>
       <c r="Q40" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>BRY isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -5530,12 +5532,12 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>ECU @ ALA</t>
+          <t>MIA @ STAN</t>
         </is>
       </c>
       <c r="C66" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-09-05 01:00</t>
         </is>
       </c>
       <c r="D66" s="25" t="n">
@@ -5543,32 +5545,34 @@
       </c>
       <c r="E66" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F66" s="17" t="inlineStr">
         <is>
-          <t>ECU ML</t>
-        </is>
-      </c>
-      <c r="G66" s="26" t="n"/>
+          <t>STAN +23.5</t>
+        </is>
+      </c>
+      <c r="G66" s="26" t="n">
+        <v>23.5</v>
+      </c>
       <c r="H66" s="18" t="n">
-        <v>3000</v>
+        <v>-108</v>
       </c>
       <c r="I66" s="20" t="n">
-        <v>0.2383533919565171</v>
+        <v>0.7263894656063076</v>
       </c>
       <c r="J66" s="20" t="n">
-        <v>0.03155263980006248</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K66" s="20" t="n">
-        <v>0.03225806451612903</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L66" s="19" t="n">
-        <v>0.206095327440388</v>
+        <v>0.2071586963755383</v>
       </c>
       <c r="M66" s="19" t="n">
-        <v>6.388955150652029</v>
+        <v>0.3989723041306665</v>
       </c>
       <c r="N66" s="20" t="n">
         <v>0</v>
@@ -5583,7 +5587,7 @@
       </c>
       <c r="Q66" s="17" t="inlineStr">
         <is>
-          <t>price outside allowed range</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -5595,12 +5599,12 @@
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>ALB @ BUFF</t>
+          <t>ECU @ ALA</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D67" s="22" t="n">
@@ -5608,34 +5612,32 @@
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
         <is>
-          <t>ALB +24.5</t>
-        </is>
-      </c>
-      <c r="G67" s="23" t="n">
-        <v>-24.5</v>
-      </c>
+          <t>ECU ML</t>
+        </is>
+      </c>
+      <c r="G67" s="23" t="n"/>
       <c r="H67" s="13" t="n">
-        <v>-112</v>
+        <v>3000</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>0.7342550223888921</v>
+        <v>0.2383533919565171</v>
       </c>
       <c r="J67" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.03155263980006248</v>
       </c>
       <c r="K67" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="L67" s="14" t="n">
-        <v>0.2059531355964392</v>
+        <v>0.206095327440388</v>
       </c>
       <c r="M67" s="14" t="n">
-        <v>0.3898398638075457</v>
+        <v>6.388955150652029</v>
       </c>
       <c r="N67" s="15" t="n">
         <v>0</v>
@@ -5650,7 +5652,7 @@
       </c>
       <c r="Q67" s="12" t="inlineStr">
         <is>
-          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>price outside allowed range</t>
         </is>
       </c>
     </row>
@@ -5662,7 +5664,7 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>MRMK @ DEL</t>
+          <t>ALB @ BUFF</t>
         </is>
       </c>
       <c r="C68" s="17" t="inlineStr">
@@ -5675,32 +5677,34 @@
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F68" s="17" t="inlineStr">
         <is>
-          <t>MRMK ML</t>
-        </is>
-      </c>
-      <c r="G68" s="26" t="n"/>
+          <t>ALB +24.5</t>
+        </is>
+      </c>
+      <c r="G68" s="26" t="n">
+        <v>-24.5</v>
+      </c>
       <c r="H68" s="18" t="n">
-        <v>3500</v>
+        <v>-112</v>
       </c>
       <c r="I68" s="20" t="n">
-        <v>0.2320231923220626</v>
+        <v>0.7342550223888921</v>
       </c>
       <c r="J68" s="20" t="n">
-        <v>0.02715849209566274</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K68" s="20" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L68" s="19" t="n">
-        <v>0.2042454145442848</v>
+        <v>0.2059531355964392</v>
       </c>
       <c r="M68" s="19" t="n">
-        <v>7.352834923594253</v>
+        <v>0.3898398638075457</v>
       </c>
       <c r="N68" s="20" t="n">
         <v>0</v>
@@ -5715,7 +5719,7 @@
       </c>
       <c r="Q68" s="17" t="inlineStr">
         <is>
-          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -5727,12 +5731,12 @@
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>HCU @ RICE</t>
+          <t>MRMK @ DEL</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D69" s="22" t="n">
@@ -5740,34 +5744,32 @@
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
         <is>
-          <t>HCU +24.5</t>
-        </is>
-      </c>
-      <c r="G69" s="23" t="n">
-        <v>-24.5</v>
-      </c>
+          <t>MRMK ML</t>
+        </is>
+      </c>
+      <c r="G69" s="23" t="n"/>
       <c r="H69" s="13" t="n">
-        <v>-118</v>
+        <v>3500</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>0.7450679751245244</v>
+        <v>0.2320231923220626</v>
       </c>
       <c r="J69" s="15" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.02715849209566274</v>
       </c>
       <c r="K69" s="15" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="L69" s="14" t="n">
-        <v>0.2037835714547996</v>
+        <v>0.2042454145442848</v>
       </c>
       <c r="M69" s="14" t="n">
-        <v>0.3764815133656467</v>
+        <v>7.352834923594253</v>
       </c>
       <c r="N69" s="15" t="n">
         <v>0</v>
@@ -5782,7 +5784,7 @@
       </c>
       <c r="Q69" s="12" t="inlineStr">
         <is>
-          <t>HCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>MRMK isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -5794,12 +5796,12 @@
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>WSU @ WASH</t>
+          <t>HCU @ RICE</t>
         </is>
       </c>
       <c r="C70" s="17" t="inlineStr">
         <is>
-          <t>2026-09-06 20:00</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D70" s="25" t="n">
@@ -5812,29 +5814,29 @@
       </c>
       <c r="F70" s="17" t="inlineStr">
         <is>
-          <t>WSU +23.5</t>
+          <t>HCU +24.5</t>
         </is>
       </c>
       <c r="G70" s="26" t="n">
-        <v>-23.5</v>
+        <v>-24.5</v>
       </c>
       <c r="H70" s="18" t="n">
-        <v>-108</v>
+        <v>-118</v>
       </c>
       <c r="I70" s="20" t="n">
-        <v>0.7230006966275496</v>
+        <v>0.7450679751245244</v>
       </c>
       <c r="J70" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5173641257162701</v>
       </c>
       <c r="K70" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5412844036697247</v>
       </c>
       <c r="L70" s="19" t="n">
-        <v>0.2037699273967803</v>
+        <v>0.2037835714547996</v>
       </c>
       <c r="M70" s="19" t="n">
-        <v>0.392445786097503</v>
+        <v>0.3764815133656467</v>
       </c>
       <c r="N70" s="20" t="n">
         <v>0</v>
@@ -5849,7 +5851,7 @@
       </c>
       <c r="Q70" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>HCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -5861,12 +5863,12 @@
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>MRSH @ PSU</t>
+          <t>WSU @ WASH</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-06 20:00</t>
         </is>
       </c>
       <c r="D71" s="22" t="n">
@@ -5879,29 +5881,29 @@
       </c>
       <c r="F71" s="12" t="inlineStr">
         <is>
-          <t>MRSH +24.5</t>
+          <t>WSU +23.5</t>
         </is>
       </c>
       <c r="G71" s="23" t="n">
-        <v>-24.5</v>
+        <v>-23.5</v>
       </c>
       <c r="H71" s="13" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I71" s="15" t="n">
-        <v>0.7270469160318935</v>
+        <v>0.7230006966275496</v>
       </c>
       <c r="J71" s="15" t="n">
-        <v>0.5</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K71" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L71" s="14" t="n">
-        <v>0.2032373922223697</v>
+        <v>0.2037699273967803</v>
       </c>
       <c r="M71" s="14" t="n">
-        <v>0.3879986578790695</v>
+        <v>0.392445786097503</v>
       </c>
       <c r="N71" s="15" t="n">
         <v>0</v>
@@ -5928,12 +5930,12 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>MIA @ STAN</t>
+          <t>MRSH @ PSU</t>
         </is>
       </c>
       <c r="C72" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 01:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D72" s="25" t="n">
@@ -5946,29 +5948,29 @@
       </c>
       <c r="F72" s="17" t="inlineStr">
         <is>
-          <t>STAN +24.5</t>
+          <t>MRSH +24.5</t>
         </is>
       </c>
       <c r="G72" s="26" t="n">
-        <v>24.5</v>
+        <v>-24.5</v>
       </c>
       <c r="H72" s="18" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="I72" s="20" t="n">
-        <v>0.7375960622734384</v>
+        <v>0.7270469160318935</v>
       </c>
       <c r="J72" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5</v>
       </c>
       <c r="K72" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L72" s="19" t="n">
-        <v>0.2027123413432059</v>
+        <v>0.2032373922223697</v>
       </c>
       <c r="M72" s="19" t="n">
-        <v>0.3789839425112109</v>
+        <v>0.3879986578790695</v>
       </c>
       <c r="N72" s="20" t="n">
         <v>0</v>
@@ -7250,12 +7252,12 @@
       </c>
       <c r="B92" s="17" t="inlineStr">
         <is>
-          <t>MIA @ STAN</t>
+          <t>CIT @ CLT</t>
         </is>
       </c>
       <c r="C92" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 01:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D92" s="25" t="n">
@@ -7268,27 +7270,27 @@
       </c>
       <c r="F92" s="17" t="inlineStr">
         <is>
-          <t>STAN ML</t>
+          <t>CIT ML</t>
         </is>
       </c>
       <c r="G92" s="26" t="n"/>
       <c r="H92" s="18" t="n">
-        <v>1600</v>
+        <v>700</v>
       </c>
       <c r="I92" s="20" t="n">
-        <v>0.247873213749308</v>
+        <v>0.3117280046500647</v>
       </c>
       <c r="J92" s="20" t="n">
-        <v>0.05686546463245493</v>
+        <v>0.12</v>
       </c>
       <c r="K92" s="20" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.125</v>
       </c>
       <c r="L92" s="19" t="n">
-        <v>0.1890496843375433</v>
+        <v>0.1867280046500647</v>
       </c>
       <c r="M92" s="19" t="n">
-        <v>3.213844633738237</v>
+        <v>1.493824037200517</v>
       </c>
       <c r="N92" s="20" t="n">
         <v>0</v>
@@ -7303,7 +7305,7 @@
       </c>
       <c r="Q92" s="17" t="inlineStr">
         <is>
-          <t>price outside allowed range</t>
+          <t>CIT isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -7315,7 +7317,7 @@
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>CIT @ CLT</t>
+          <t>ME @ APP</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
@@ -7328,32 +7330,34 @@
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F93" s="12" t="inlineStr">
         <is>
-          <t>CIT ML</t>
-        </is>
-      </c>
-      <c r="G93" s="23" t="n"/>
+          <t>ME +18.5</t>
+        </is>
+      </c>
+      <c r="G93" s="23" t="n">
+        <v>-18.5</v>
+      </c>
       <c r="H93" s="13" t="n">
-        <v>700</v>
+        <v>-108</v>
       </c>
       <c r="I93" s="15" t="n">
-        <v>0.3117280046500647</v>
+        <v>0.7057228774337212</v>
       </c>
       <c r="J93" s="15" t="n">
-        <v>0.12</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K93" s="15" t="n">
-        <v>0.125</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L93" s="14" t="n">
-        <v>0.1867280046500647</v>
+        <v>0.1864921082029519</v>
       </c>
       <c r="M93" s="14" t="n">
-        <v>1.493824037200517</v>
+        <v>0.3591699861686483</v>
       </c>
       <c r="N93" s="15" t="n">
         <v>0</v>
@@ -7368,7 +7372,7 @@
       </c>
       <c r="Q93" s="12" t="inlineStr">
         <is>
-          <t>CIT isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>ME isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -7380,12 +7384,12 @@
       </c>
       <c r="B94" s="17" t="inlineStr">
         <is>
-          <t>ME @ APP</t>
+          <t>CHSO @ GASO</t>
         </is>
       </c>
       <c r="C94" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D94" s="25" t="n">
@@ -7393,34 +7397,32 @@
       </c>
       <c r="E94" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F94" s="17" t="inlineStr">
         <is>
-          <t>ME +18.5</t>
-        </is>
-      </c>
-      <c r="G94" s="26" t="n">
-        <v>-18.5</v>
-      </c>
+          <t>CHSO ML</t>
+        </is>
+      </c>
+      <c r="G94" s="26" t="n"/>
       <c r="H94" s="18" t="n">
-        <v>-108</v>
+        <v>1700</v>
       </c>
       <c r="I94" s="20" t="n">
-        <v>0.7057228774337212</v>
+        <v>0.2411928555709533</v>
       </c>
       <c r="J94" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.05373831775700934</v>
       </c>
       <c r="K94" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.05555555555555555</v>
       </c>
       <c r="L94" s="19" t="n">
-        <v>0.1864921082029519</v>
+        <v>0.1856373000153977</v>
       </c>
       <c r="M94" s="19" t="n">
-        <v>0.3591699861686483</v>
+        <v>3.341471400277159</v>
       </c>
       <c r="N94" s="20" t="n">
         <v>0</v>
@@ -7435,7 +7437,7 @@
       </c>
       <c r="Q94" s="17" t="inlineStr">
         <is>
-          <t>ME isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>CHSO isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -7447,12 +7449,12 @@
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>CHSO @ GASO</t>
+          <t>SEMO @ ISU</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-05 17:00</t>
         </is>
       </c>
       <c r="D95" s="22" t="n">
@@ -7465,27 +7467,27 @@
       </c>
       <c r="F95" s="12" t="inlineStr">
         <is>
-          <t>CHSO ML</t>
+          <t>SEMO ML</t>
         </is>
       </c>
       <c r="G95" s="23" t="n"/>
       <c r="H95" s="13" t="n">
-        <v>1700</v>
+        <v>3500</v>
       </c>
       <c r="I95" s="15" t="n">
-        <v>0.2411928555709533</v>
+        <v>0.2129786473780797</v>
       </c>
       <c r="J95" s="15" t="n">
-        <v>0.05373831775700934</v>
+        <v>0.02715849209566274</v>
       </c>
       <c r="K95" s="15" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="L95" s="14" t="n">
-        <v>0.1856373000153977</v>
+        <v>0.1852008696003019</v>
       </c>
       <c r="M95" s="14" t="n">
-        <v>3.341471400277159</v>
+        <v>6.667231305610869</v>
       </c>
       <c r="N95" s="15" t="n">
         <v>0</v>
@@ -7500,7 +7502,7 @@
       </c>
       <c r="Q95" s="12" t="inlineStr">
         <is>
-          <t>CHSO isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>SEMO isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -7512,12 +7514,12 @@
       </c>
       <c r="B96" s="17" t="inlineStr">
         <is>
-          <t>SEMO @ ISU</t>
+          <t>WIS @ ND</t>
         </is>
       </c>
       <c r="C96" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 17:00</t>
+          <t>2026-09-06 23:30</t>
         </is>
       </c>
       <c r="D96" s="25" t="n">
@@ -7525,32 +7527,34 @@
       </c>
       <c r="E96" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F96" s="17" t="inlineStr">
         <is>
-          <t>SEMO ML</t>
-        </is>
-      </c>
-      <c r="G96" s="26" t="n"/>
+          <t>WIS +20.5</t>
+        </is>
+      </c>
+      <c r="G96" s="26" t="n">
+        <v>-20.5</v>
+      </c>
       <c r="H96" s="18" t="n">
-        <v>3500</v>
+        <v>-108</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>0.2129786473780797</v>
+        <v>0.7022807671560833</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>0.02715849209566274</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L96" s="19" t="n">
-        <v>0.1852008696003019</v>
+        <v>0.1830499979253141</v>
       </c>
       <c r="M96" s="19" t="n">
-        <v>6.667231305610869</v>
+        <v>0.3525407367450495</v>
       </c>
       <c r="N96" s="20" t="n">
         <v>0</v>
@@ -7565,7 +7569,7 @@
       </c>
       <c r="Q96" s="17" t="inlineStr">
         <is>
-          <t>SEMO isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -7577,12 +7581,12 @@
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>WIS @ ND</t>
+          <t>ORST @ HOU</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 23:30</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D97" s="22" t="n">
@@ -7595,29 +7599,29 @@
       </c>
       <c r="F97" s="12" t="inlineStr">
         <is>
-          <t>WIS +20.5</t>
+          <t>ORST +20.5</t>
         </is>
       </c>
       <c r="G97" s="23" t="n">
         <v>-20.5</v>
       </c>
       <c r="H97" s="13" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="I97" s="15" t="n">
-        <v>0.7022807671560833</v>
+        <v>0.6950888924217836</v>
       </c>
       <c r="J97" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K97" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L97" s="14" t="n">
-        <v>0.1830499979253141</v>
+        <v>0.1828937704705641</v>
       </c>
       <c r="M97" s="14" t="n">
-        <v>0.3525407367450495</v>
+        <v>0.3570783137758632</v>
       </c>
       <c r="N97" s="15" t="n">
         <v>0</v>
@@ -7644,12 +7648,12 @@
       </c>
       <c r="B98" s="17" t="inlineStr">
         <is>
-          <t>ORST @ HOU</t>
+          <t>FAU @ FLA</t>
         </is>
       </c>
       <c r="C98" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-09-05 23:45</t>
         </is>
       </c>
       <c r="D98" s="25" t="n">
@@ -7657,34 +7661,32 @@
       </c>
       <c r="E98" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F98" s="17" t="inlineStr">
         <is>
-          <t>ORST +20.5</t>
-        </is>
-      </c>
-      <c r="G98" s="26" t="n">
-        <v>-20.5</v>
-      </c>
+          <t>FAU ML</t>
+        </is>
+      </c>
+      <c r="G98" s="26" t="n"/>
       <c r="H98" s="18" t="n">
-        <v>-105</v>
+        <v>1800</v>
       </c>
       <c r="I98" s="20" t="n">
-        <v>0.6950888924217836</v>
+        <v>0.235268670017273</v>
       </c>
       <c r="J98" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.05094905094905094</v>
       </c>
       <c r="K98" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L98" s="19" t="n">
-        <v>0.1828937704705641</v>
+        <v>0.1826370910699046</v>
       </c>
       <c r="M98" s="19" t="n">
-        <v>0.3570783137758632</v>
+        <v>3.470104730328188</v>
       </c>
       <c r="N98" s="20" t="n">
         <v>0</v>
@@ -7699,7 +7701,7 @@
       </c>
       <c r="Q98" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>price outside allowed range</t>
         </is>
       </c>
     </row>
@@ -7711,12 +7713,12 @@
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>FAU @ FLA</t>
+          <t>MIA @ STAN</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:45</t>
+          <t>2026-09-05 01:00</t>
         </is>
       </c>
       <c r="D99" s="22" t="n">
@@ -7729,27 +7731,27 @@
       </c>
       <c r="F99" s="12" t="inlineStr">
         <is>
-          <t>FAU ML</t>
+          <t>STAN ML</t>
         </is>
       </c>
       <c r="G99" s="23" t="n"/>
       <c r="H99" s="13" t="n">
-        <v>1800</v>
+        <v>1300</v>
       </c>
       <c r="I99" s="15" t="n">
-        <v>0.235268670017273</v>
+        <v>0.2538822866587337</v>
       </c>
       <c r="J99" s="15" t="n">
-        <v>0.05094905094905094</v>
+        <v>0.06888361045130641</v>
       </c>
       <c r="K99" s="15" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="L99" s="14" t="n">
-        <v>0.1826370910699046</v>
+        <v>0.1824537152301623</v>
       </c>
       <c r="M99" s="14" t="n">
-        <v>3.470104730328188</v>
+        <v>2.554352013222273</v>
       </c>
       <c r="N99" s="15" t="n">
         <v>0</v>
@@ -10995,12 +10997,12 @@
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t>SAC @ EMU</t>
+          <t>ALB @ BUFF</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 22:30</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D149" s="22" t="n">
@@ -11008,34 +11010,34 @@
       </c>
       <c r="E149" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F149" s="12" t="inlineStr">
         <is>
-          <t>SAC +9.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="G149" s="23" t="n">
-        <v>-9.5</v>
+        <v>48.5</v>
       </c>
       <c r="H149" s="13" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="I149" s="15" t="n">
-        <v>0.6427213270037963</v>
+        <v>0.6237538960930264</v>
       </c>
       <c r="J149" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K149" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L149" s="14" t="n">
-        <v>0.1078376060735637</v>
+        <v>0.1045231268622572</v>
       </c>
       <c r="M149" s="14" t="n">
-        <v>0.2016094374418799</v>
+        <v>0.2013037998828658</v>
       </c>
       <c r="N149" s="15" t="n">
         <v>0</v>
@@ -11050,7 +11052,7 @@
       </c>
       <c r="Q149" s="12" t="inlineStr">
         <is>
-          <t>model and market are too far apart for a reliable early-season play</t>
+          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -11062,12 +11064,12 @@
       </c>
       <c r="B150" s="17" t="inlineStr">
         <is>
-          <t>ALB @ BUFF</t>
+          <t>SAC @ EMU</t>
         </is>
       </c>
       <c r="C150" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-08-29 22:30</t>
         </is>
       </c>
       <c r="D150" s="25" t="n">
@@ -11075,34 +11077,32 @@
       </c>
       <c r="E150" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F150" s="17" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
-        </is>
-      </c>
-      <c r="G150" s="26" t="n">
-        <v>48.5</v>
-      </c>
+          <t>SAC ML</t>
+        </is>
+      </c>
+      <c r="G150" s="26" t="n"/>
       <c r="H150" s="18" t="n">
-        <v>-108</v>
+        <v>275</v>
       </c>
       <c r="I150" s="20" t="n">
-        <v>0.6237538960930264</v>
+        <v>0.3704790320517835</v>
       </c>
       <c r="J150" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.2559309849029475</v>
       </c>
       <c r="K150" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="L150" s="19" t="n">
-        <v>0.1045231268622572</v>
+        <v>0.1038123653851168</v>
       </c>
       <c r="M150" s="19" t="n">
-        <v>0.2013037998828658</v>
+        <v>0.3892963701941881</v>
       </c>
       <c r="N150" s="20" t="n">
         <v>0</v>
@@ -11117,7 +11117,7 @@
       </c>
       <c r="Q150" s="17" t="inlineStr">
         <is>
-          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>correlated with a stronger play on the same game</t>
         </is>
       </c>
     </row>
@@ -11397,12 +11397,12 @@
       </c>
       <c r="B155" s="12" t="inlineStr">
         <is>
-          <t>HAW @ STAN</t>
+          <t>FUR @ TENN</t>
         </is>
       </c>
       <c r="C155" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D155" s="22" t="n">
@@ -11415,17 +11415,17 @@
       </c>
       <c r="F155" s="12" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>Under 66.5</t>
         </is>
       </c>
       <c r="G155" s="23" t="n">
-        <v>48.5</v>
+        <v>66.5</v>
       </c>
       <c r="H155" s="13" t="n">
         <v>-115</v>
       </c>
       <c r="I155" s="15" t="n">
-        <v>0.6232864466877359</v>
+        <v>0.6232864407919079</v>
       </c>
       <c r="J155" s="15" t="n">
         <v>0.5108342361863488</v>
@@ -11434,10 +11434,10 @@
         <v>0.5348837209302325</v>
       </c>
       <c r="L155" s="14" t="n">
-        <v>0.08840272575750341</v>
+        <v>0.08840271986167536</v>
       </c>
       <c r="M155" s="14" t="n">
-        <v>0.1652746611988105</v>
+        <v>0.1652746501761755</v>
       </c>
       <c r="N155" s="15" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="Q155" s="12" t="inlineStr">
         <is>
-          <t>outside the top 10 plays for this week</t>
+          <t>FUR isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
       </c>
       <c r="B156" s="17" t="inlineStr">
         <is>
-          <t>FUR @ TENN</t>
+          <t>BC @ CIN</t>
         </is>
       </c>
       <c r="C156" s="17" t="inlineStr">
@@ -11482,29 +11482,29 @@
       </c>
       <c r="F156" s="17" t="inlineStr">
         <is>
-          <t>Under 66.5</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="G156" s="26" t="n">
-        <v>66.5</v>
+        <v>51.5</v>
       </c>
       <c r="H156" s="18" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="I156" s="20" t="n">
-        <v>0.6232864407919079</v>
+        <v>0.6057060023101252</v>
       </c>
       <c r="J156" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K156" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L156" s="19" t="n">
-        <v>0.08840271986167536</v>
+        <v>0.0864752330793559</v>
       </c>
       <c r="M156" s="19" t="n">
-        <v>0.1652746501761755</v>
+        <v>0.1665448933380189</v>
       </c>
       <c r="N156" s="20" t="n">
         <v>0</v>
@@ -11519,7 +11519,7 @@
       </c>
       <c r="Q156" s="17" t="inlineStr">
         <is>
-          <t>FUR isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>outside the top 10 plays for this week</t>
         </is>
       </c>
     </row>
@@ -11531,12 +11531,12 @@
       </c>
       <c r="B157" s="12" t="inlineStr">
         <is>
-          <t>BC @ CIN</t>
+          <t>NCAT @ GAST</t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-04 23:00</t>
         </is>
       </c>
       <c r="D157" s="22" t="n">
@@ -11549,29 +11549,29 @@
       </c>
       <c r="F157" s="12" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>Under 63.5</t>
         </is>
       </c>
       <c r="G157" s="23" t="n">
-        <v>51.5</v>
+        <v>63.5</v>
       </c>
       <c r="H157" s="13" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I157" s="15" t="n">
-        <v>0.6057060023101252</v>
+        <v>0.6095621194091961</v>
       </c>
       <c r="J157" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5</v>
       </c>
       <c r="K157" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L157" s="14" t="n">
-        <v>0.0864752330793559</v>
+        <v>0.0857525955996723</v>
       </c>
       <c r="M157" s="14" t="n">
-        <v>0.1665448933380189</v>
+        <v>0.1637095006902836</v>
       </c>
       <c r="N157" s="15" t="n">
         <v>0</v>
@@ -11586,7 +11586,7 @@
       </c>
       <c r="Q157" s="12" t="inlineStr">
         <is>
-          <t>outside the top 10 plays for this week</t>
+          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="B158" s="17" t="inlineStr">
         <is>
-          <t>NCAT @ GAST</t>
+          <t>TULN @ DUKE</t>
         </is>
       </c>
       <c r="C158" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 23:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D158" s="25" t="n">
@@ -11611,34 +11611,32 @@
       </c>
       <c r="E158" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F158" s="17" t="inlineStr">
         <is>
-          <t>Under 63.5</t>
-        </is>
-      </c>
-      <c r="G158" s="26" t="n">
-        <v>63.5</v>
-      </c>
+          <t>TULN ML</t>
+        </is>
+      </c>
+      <c r="G158" s="26" t="n"/>
       <c r="H158" s="18" t="n">
-        <v>-110</v>
+        <v>300</v>
       </c>
       <c r="I158" s="20" t="n">
-        <v>0.6095621194091961</v>
+        <v>0.3354589358801325</v>
       </c>
       <c r="J158" s="20" t="n">
-        <v>0.5</v>
+        <v>0.24</v>
       </c>
       <c r="K158" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.25</v>
       </c>
       <c r="L158" s="19" t="n">
-        <v>0.0857525955996723</v>
+        <v>0.08545893588013254</v>
       </c>
       <c r="M158" s="19" t="n">
-        <v>0.1637095006902836</v>
+        <v>0.3418357435205301</v>
       </c>
       <c r="N158" s="20" t="n">
         <v>0</v>
@@ -11653,7 +11651,7 @@
       </c>
       <c r="Q158" s="17" t="inlineStr">
         <is>
-          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>correlated with a stronger play on the same game</t>
         </is>
       </c>
     </row>
@@ -11665,12 +11663,12 @@
       </c>
       <c r="B159" s="12" t="inlineStr">
         <is>
-          <t>TULN @ DUKE</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C159" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D159" s="22" t="n">
@@ -11678,32 +11676,34 @@
       </c>
       <c r="E159" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F159" s="12" t="inlineStr">
         <is>
-          <t>TULN ML</t>
-        </is>
-      </c>
-      <c r="G159" s="23" t="n"/>
+          <t>UNC +8.5</t>
+        </is>
+      </c>
+      <c r="G159" s="23" t="n">
+        <v>-8.5</v>
+      </c>
       <c r="H159" s="13" t="n">
-        <v>300</v>
+        <v>-115</v>
       </c>
       <c r="I159" s="15" t="n">
-        <v>0.3354589358801325</v>
+        <v>0.6190170053289987</v>
       </c>
       <c r="J159" s="15" t="n">
-        <v>0.24</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K159" s="15" t="n">
-        <v>0.25</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L159" s="14" t="n">
-        <v>0.08545893588013254</v>
+        <v>0.08413328439876622</v>
       </c>
       <c r="M159" s="14" t="n">
-        <v>0.3418357435205301</v>
+        <v>0.1572926621368236</v>
       </c>
       <c r="N159" s="15" t="n">
         <v>0</v>
@@ -11718,7 +11718,7 @@
       </c>
       <c r="Q159" s="12" t="inlineStr">
         <is>
-          <t>correlated with a stronger play on the same game</t>
+          <t>outside the top 10 plays for this week</t>
         </is>
       </c>
     </row>
@@ -11730,12 +11730,12 @@
       </c>
       <c r="B160" s="17" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>TULN @ DUKE</t>
         </is>
       </c>
       <c r="C160" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D160" s="25" t="n">
@@ -11743,32 +11743,34 @@
       </c>
       <c r="E160" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F160" s="17" t="inlineStr">
         <is>
-          <t>UNC ML</t>
-        </is>
-      </c>
-      <c r="G160" s="26" t="n"/>
+          <t>TULN +9.5</t>
+        </is>
+      </c>
+      <c r="G160" s="26" t="n">
+        <v>-9.5</v>
+      </c>
       <c r="H160" s="18" t="n">
-        <v>270</v>
+        <v>-118</v>
       </c>
       <c r="I160" s="20" t="n">
-        <v>0.3545694500280139</v>
+        <v>0.6243636947362678</v>
       </c>
       <c r="J160" s="20" t="n">
-        <v>0.2591283863368669</v>
+        <v>0.5173641257162701</v>
       </c>
       <c r="K160" s="20" t="n">
-        <v>0.2702702702702703</v>
+        <v>0.5412844036697247</v>
       </c>
       <c r="L160" s="19" t="n">
-        <v>0.08429917975774359</v>
+        <v>0.0830792910665431</v>
       </c>
       <c r="M160" s="19" t="n">
-        <v>0.3119069651036515</v>
+        <v>0.1534854699364948</v>
       </c>
       <c r="N160" s="20" t="n">
         <v>0</v>
@@ -11795,12 +11797,12 @@
       </c>
       <c r="B161" s="12" t="inlineStr">
         <is>
-          <t>TULN @ DUKE</t>
+          <t>FIU @ USF</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D161" s="22" t="n">
@@ -11808,34 +11810,32 @@
       </c>
       <c r="E161" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F161" s="12" t="inlineStr">
         <is>
-          <t>TULN +9.5</t>
-        </is>
-      </c>
-      <c r="G161" s="23" t="n">
-        <v>-9.5</v>
-      </c>
+          <t>FIU ML</t>
+        </is>
+      </c>
+      <c r="G161" s="23" t="n"/>
       <c r="H161" s="13" t="n">
-        <v>-118</v>
+        <v>425</v>
       </c>
       <c r="I161" s="15" t="n">
-        <v>0.6243636947362678</v>
+        <v>0.2735268764959096</v>
       </c>
       <c r="J161" s="15" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.182741116751269</v>
       </c>
       <c r="K161" s="15" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="L161" s="14" t="n">
-        <v>0.0830792910665431</v>
+        <v>0.0830506860197191</v>
       </c>
       <c r="M161" s="14" t="n">
-        <v>0.1534854699364948</v>
+        <v>0.4360161016035251</v>
       </c>
       <c r="N161" s="15" t="n">
         <v>0</v>
@@ -11862,12 +11862,12 @@
       </c>
       <c r="B162" s="17" t="inlineStr">
         <is>
-          <t>FIU @ USF</t>
+          <t>BAY @ AUB</t>
         </is>
       </c>
       <c r="C162" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D162" s="25" t="n">
@@ -11875,35 +11875,37 @@
       </c>
       <c r="E162" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F162" s="17" t="inlineStr">
         <is>
-          <t>FIU ML</t>
-        </is>
-      </c>
-      <c r="G162" s="26" t="n"/>
+          <t>BAY +7</t>
+        </is>
+      </c>
+      <c r="G162" s="26" t="n">
+        <v>-7</v>
+      </c>
       <c r="H162" s="18" t="n">
-        <v>425</v>
+        <v>-108</v>
       </c>
       <c r="I162" s="20" t="n">
-        <v>0.2735268764959096</v>
+        <v>0.6019165956461305</v>
       </c>
       <c r="J162" s="20" t="n">
-        <v>0.182741116751269</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K162" s="20" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L162" s="19" t="n">
-        <v>0.0830506860197191</v>
+        <v>0.08268582641536126</v>
       </c>
       <c r="M162" s="19" t="n">
-        <v>0.4360161016035251</v>
+        <v>0.1520130784139129</v>
       </c>
       <c r="N162" s="20" t="n">
-        <v>0</v>
+        <v>0.0454</v>
       </c>
       <c r="O162" s="27" t="n">
         <v>0.45</v>
@@ -11940,37 +11942,35 @@
       </c>
       <c r="E163" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F163" s="12" t="inlineStr">
         <is>
-          <t>BAY +7</t>
-        </is>
-      </c>
-      <c r="G163" s="23" t="n">
-        <v>-7</v>
-      </c>
+          <t>BAY ML</t>
+        </is>
+      </c>
+      <c r="G163" s="23" t="n"/>
       <c r="H163" s="13" t="n">
-        <v>-108</v>
+        <v>240</v>
       </c>
       <c r="I163" s="15" t="n">
-        <v>0.6019165956461305</v>
+        <v>0.3767698976814278</v>
       </c>
       <c r="J163" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.2820294784580499</v>
       </c>
       <c r="K163" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="L163" s="14" t="n">
-        <v>0.08268582641536126</v>
+        <v>0.08265225062260423</v>
       </c>
       <c r="M163" s="14" t="n">
-        <v>0.1520130784139129</v>
+        <v>0.2810176521168544</v>
       </c>
       <c r="N163" s="15" t="n">
-        <v>0.0454</v>
+        <v>0</v>
       </c>
       <c r="O163" s="24" t="n">
         <v>0.45</v>
@@ -11994,12 +11994,12 @@
       </c>
       <c r="B164" s="17" t="inlineStr">
         <is>
-          <t>BAY @ AUB</t>
+          <t>CMU @ UNM</t>
         </is>
       </c>
       <c r="C164" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-06 02:00</t>
         </is>
       </c>
       <c r="D164" s="25" t="n">
@@ -12012,27 +12012,27 @@
       </c>
       <c r="F164" s="17" t="inlineStr">
         <is>
-          <t>BAY ML</t>
+          <t>CMU ML</t>
         </is>
       </c>
       <c r="G164" s="26" t="n"/>
       <c r="H164" s="18" t="n">
-        <v>240</v>
+        <v>320</v>
       </c>
       <c r="I164" s="20" t="n">
-        <v>0.3767698976814278</v>
+        <v>0.3200943443355193</v>
       </c>
       <c r="J164" s="20" t="n">
-        <v>0.2820294784580499</v>
+        <v>0.2284946236559139</v>
       </c>
       <c r="K164" s="20" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="L164" s="19" t="n">
-        <v>0.08265225062260423</v>
+        <v>0.08199910624028123</v>
       </c>
       <c r="M164" s="19" t="n">
-        <v>0.2810176521168544</v>
+        <v>0.3443962462091812</v>
       </c>
       <c r="N164" s="20" t="n">
         <v>0</v>
@@ -12059,12 +12059,12 @@
       </c>
       <c r="B165" s="12" t="inlineStr">
         <is>
-          <t>CMU @ UNM</t>
+          <t>UNT @ IU</t>
         </is>
       </c>
       <c r="C165" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 02:00</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D165" s="22" t="n">
@@ -12072,32 +12072,34 @@
       </c>
       <c r="E165" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F165" s="12" t="inlineStr">
         <is>
-          <t>CMU ML</t>
-        </is>
-      </c>
-      <c r="G165" s="23" t="n"/>
+          <t>Over 55.5</t>
+        </is>
+      </c>
+      <c r="G165" s="23" t="n">
+        <v>55.5</v>
+      </c>
       <c r="H165" s="13" t="n">
-        <v>320</v>
+        <v>-115</v>
       </c>
       <c r="I165" s="15" t="n">
-        <v>0.3200943443355193</v>
+        <v>0.6166606910182664</v>
       </c>
       <c r="J165" s="15" t="n">
-        <v>0.2284946236559139</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K165" s="15" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L165" s="14" t="n">
-        <v>0.08199910624028123</v>
+        <v>0.08177697008803386</v>
       </c>
       <c r="M165" s="14" t="n">
-        <v>0.3443962462091812</v>
+        <v>0.1528873788602371</v>
       </c>
       <c r="N165" s="15" t="n">
         <v>0</v>
@@ -12112,7 +12114,7 @@
       </c>
       <c r="Q165" s="12" t="inlineStr">
         <is>
-          <t>correlated with a stronger play on the same game</t>
+          <t>outside the top 10 plays for this week</t>
         </is>
       </c>
     </row>
@@ -12124,12 +12126,12 @@
       </c>
       <c r="B166" s="17" t="inlineStr">
         <is>
-          <t>UNT @ IU</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C166" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D166" s="25" t="n">
@@ -12137,34 +12139,32 @@
       </c>
       <c r="E166" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F166" s="17" t="inlineStr">
         <is>
-          <t>Over 55.5</t>
-        </is>
-      </c>
-      <c r="G166" s="26" t="n">
-        <v>55.5</v>
-      </c>
+          <t>UNC ML</t>
+        </is>
+      </c>
+      <c r="G166" s="26" t="n"/>
       <c r="H166" s="18" t="n">
-        <v>-115</v>
+        <v>260</v>
       </c>
       <c r="I166" s="20" t="n">
-        <v>0.6166606910182664</v>
+        <v>0.3582340969849722</v>
       </c>
       <c r="J166" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.2664576802507838</v>
       </c>
       <c r="K166" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="L166" s="19" t="n">
-        <v>0.08177697008803386</v>
+        <v>0.08045631920719443</v>
       </c>
       <c r="M166" s="19" t="n">
-        <v>0.1528873788602371</v>
+        <v>0.2896427491459</v>
       </c>
       <c r="N166" s="20" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="Q166" s="17" t="inlineStr">
         <is>
-          <t>outside the top 10 plays for this week</t>
+          <t>correlated with a stronger play on the same game</t>
         </is>
       </c>
     </row>
@@ -13304,12 +13304,12 @@
       </c>
       <c r="B184" s="17" t="inlineStr">
         <is>
-          <t>ACU @ TTU</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C184" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D184" s="25" t="n">
@@ -13322,29 +13322,29 @@
       </c>
       <c r="F184" s="17" t="inlineStr">
         <is>
-          <t>Under 59.5</t>
+          <t>Under 61.5</t>
         </is>
       </c>
       <c r="G184" s="26" t="n">
-        <v>59.5</v>
+        <v>61.5</v>
       </c>
       <c r="H184" s="18" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="I184" s="20" t="n">
-        <v>0.5922733326643557</v>
+        <v>0.57924574575779</v>
       </c>
       <c r="J184" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K184" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L184" s="19" t="n">
-        <v>0.05738961173412316</v>
+        <v>0.0600149765270207</v>
       </c>
       <c r="M184" s="19" t="n">
-        <v>0.1072936219377083</v>
+        <v>0.1155843992372252</v>
       </c>
       <c r="N184" s="20" t="n">
         <v>0</v>
@@ -13357,11 +13357,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q184" s="17" t="inlineStr">
-        <is>
-          <t>ACU isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q184" s="17" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="12" t="inlineStr">
@@ -13371,12 +13367,12 @@
       </c>
       <c r="B185" s="12" t="inlineStr">
         <is>
-          <t>TOL @ MSU</t>
+          <t>ACU @ TTU</t>
         </is>
       </c>
       <c r="C185" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 00:00</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D185" s="22" t="n">
@@ -13389,29 +13385,29 @@
       </c>
       <c r="F185" s="12" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
+          <t>Under 59.5</t>
         </is>
       </c>
       <c r="G185" s="23" t="n">
-        <v>49.5</v>
+        <v>59.5</v>
       </c>
       <c r="H185" s="13" t="n">
-        <v>-108</v>
+        <v>-115</v>
       </c>
       <c r="I185" s="15" t="n">
-        <v>0.5755767191857057</v>
+        <v>0.5922733326643557</v>
       </c>
       <c r="J185" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K185" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L185" s="14" t="n">
-        <v>0.05634594995493647</v>
+        <v>0.05738961173412316</v>
       </c>
       <c r="M185" s="14" t="n">
-        <v>0.108518125839137</v>
+        <v>0.1072936219377083</v>
       </c>
       <c r="N185" s="15" t="n">
         <v>0</v>
@@ -13424,7 +13420,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q185" s="12" t="n"/>
+      <c r="Q185" s="12" t="inlineStr">
+        <is>
+          <t>ACU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="17" t="inlineStr">
@@ -13434,12 +13434,12 @@
       </c>
       <c r="B186" s="17" t="inlineStr">
         <is>
-          <t>BOIS @ ORE</t>
+          <t>TOL @ MSU</t>
         </is>
       </c>
       <c r="C186" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-05 00:00</t>
         </is>
       </c>
       <c r="D186" s="25" t="n">
@@ -13452,29 +13452,29 @@
       </c>
       <c r="F186" s="17" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>Over 49.5</t>
         </is>
       </c>
       <c r="G186" s="26" t="n">
-        <v>51.5</v>
+        <v>49.5</v>
       </c>
       <c r="H186" s="18" t="n">
-        <v>-118</v>
+        <v>-108</v>
       </c>
       <c r="I186" s="20" t="n">
-        <v>0.5973374319201017</v>
+        <v>0.5755767191857057</v>
       </c>
       <c r="J186" s="20" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K186" s="20" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L186" s="19" t="n">
-        <v>0.05605302825037695</v>
+        <v>0.05634594995493647</v>
       </c>
       <c r="M186" s="19" t="n">
-        <v>0.1035555945642557</v>
+        <v>0.108518125839137</v>
       </c>
       <c r="N186" s="20" t="n">
         <v>0</v>
@@ -13497,12 +13497,12 @@
       </c>
       <c r="B187" s="12" t="inlineStr">
         <is>
-          <t>UNLV @ HAW</t>
+          <t>BOIS @ ORE</t>
         </is>
       </c>
       <c r="C187" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 02:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D187" s="22" t="n">
@@ -13510,37 +13510,37 @@
       </c>
       <c r="E187" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F187" s="12" t="inlineStr">
         <is>
-          <t>HAW +3</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="G187" s="23" t="n">
-        <v>3</v>
+        <v>51.5</v>
       </c>
       <c r="H187" s="13" t="n">
-        <v>-108</v>
+        <v>-118</v>
       </c>
       <c r="I187" s="15" t="n">
-        <v>0.5752024326373151</v>
+        <v>0.5973374319201017</v>
       </c>
       <c r="J187" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5173641257162701</v>
       </c>
       <c r="K187" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5412844036697247</v>
       </c>
       <c r="L187" s="14" t="n">
-        <v>0.0559716634065458</v>
+        <v>0.05605302825037695</v>
       </c>
       <c r="M187" s="14" t="n">
-        <v>0.1016809753962156</v>
+        <v>0.1035555945642557</v>
       </c>
       <c r="N187" s="15" t="n">
-        <v>0.0567</v>
+        <v>0</v>
       </c>
       <c r="O187" s="24" t="n">
         <v>0.45</v>
@@ -13560,12 +13560,12 @@
       </c>
       <c r="B188" s="17" t="inlineStr">
         <is>
-          <t>ARST @ MEM</t>
+          <t>UNLV @ HAW</t>
         </is>
       </c>
       <c r="C188" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-06 02:00</t>
         </is>
       </c>
       <c r="D188" s="25" t="n">
@@ -13573,35 +13573,37 @@
       </c>
       <c r="E188" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F188" s="17" t="inlineStr">
         <is>
-          <t>ARST ML</t>
-        </is>
-      </c>
-      <c r="G188" s="26" t="n"/>
+          <t>HAW +3</t>
+        </is>
+      </c>
+      <c r="G188" s="26" t="n">
+        <v>3</v>
+      </c>
       <c r="H188" s="18" t="n">
-        <v>250</v>
+        <v>-108</v>
       </c>
       <c r="I188" s="20" t="n">
-        <v>0.3401615480236082</v>
+        <v>0.5752024326373151</v>
       </c>
       <c r="J188" s="20" t="n">
-        <v>0.274247491638796</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K188" s="20" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L188" s="19" t="n">
-        <v>0.05444726230932251</v>
+        <v>0.0559716634065458</v>
       </c>
       <c r="M188" s="19" t="n">
-        <v>0.1905654180826287</v>
+        <v>0.1016809753962156</v>
       </c>
       <c r="N188" s="20" t="n">
-        <v>0</v>
+        <v>0.0567</v>
       </c>
       <c r="O188" s="27" t="n">
         <v>0.45</v>
@@ -13621,12 +13623,12 @@
       </c>
       <c r="B189" s="12" t="inlineStr">
         <is>
-          <t>BC @ CIN</t>
+          <t>ARST @ MEM</t>
         </is>
       </c>
       <c r="C189" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D189" s="22" t="n">
@@ -13634,34 +13636,32 @@
       </c>
       <c r="E189" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F189" s="12" t="inlineStr">
         <is>
-          <t>BC +7.5</t>
-        </is>
-      </c>
-      <c r="G189" s="23" t="n">
-        <v>-7.5</v>
-      </c>
+          <t>ARST ML</t>
+        </is>
+      </c>
+      <c r="G189" s="23" t="n"/>
       <c r="H189" s="13" t="n">
-        <v>-112</v>
+        <v>250</v>
       </c>
       <c r="I189" s="15" t="n">
-        <v>0.5824793144711614</v>
+        <v>0.3401615480236082</v>
       </c>
       <c r="J189" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.274247491638796</v>
       </c>
       <c r="K189" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="L189" s="14" t="n">
-        <v>0.05417742767870859</v>
+        <v>0.05444726230932251</v>
       </c>
       <c r="M189" s="14" t="n">
-        <v>0.1025501309632698</v>
+        <v>0.1905654180826287</v>
       </c>
       <c r="N189" s="15" t="n">
         <v>0</v>
@@ -13697,32 +13697,34 @@
       </c>
       <c r="E190" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F190" s="17" t="inlineStr">
         <is>
-          <t>BC ML</t>
-        </is>
-      </c>
-      <c r="G190" s="26" t="n"/>
+          <t>BC +7.5</t>
+        </is>
+      </c>
+      <c r="G190" s="26" t="n">
+        <v>-7.5</v>
+      </c>
       <c r="H190" s="18" t="n">
-        <v>250</v>
+        <v>-112</v>
       </c>
       <c r="I190" s="20" t="n">
-        <v>0.3389003135487954</v>
+        <v>0.5824793144711614</v>
       </c>
       <c r="J190" s="20" t="n">
-        <v>0.274247491638796</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K190" s="20" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L190" s="19" t="n">
-        <v>0.05318602783450965</v>
+        <v>0.05417742767870859</v>
       </c>
       <c r="M190" s="19" t="n">
-        <v>0.1861510974207837</v>
+        <v>0.1025501309632698</v>
       </c>
       <c r="N190" s="20" t="n">
         <v>0</v>
@@ -13745,12 +13747,12 @@
       </c>
       <c r="B191" s="12" t="inlineStr">
         <is>
-          <t>WMU @ MICH</t>
+          <t>BC @ CIN</t>
         </is>
       </c>
       <c r="C191" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D191" s="22" t="n">
@@ -13758,34 +13760,32 @@
       </c>
       <c r="E191" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F191" s="12" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
-        </is>
-      </c>
-      <c r="G191" s="23" t="n">
-        <v>47.5</v>
-      </c>
+          <t>BC ML</t>
+        </is>
+      </c>
+      <c r="G191" s="23" t="n"/>
       <c r="H191" s="13" t="n">
-        <v>-115</v>
+        <v>250</v>
       </c>
       <c r="I191" s="15" t="n">
-        <v>0.5868277708093877</v>
+        <v>0.3389003135487954</v>
       </c>
       <c r="J191" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.274247491638796</v>
       </c>
       <c r="K191" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="L191" s="14" t="n">
-        <v>0.05194404987915524</v>
+        <v>0.05318602783450965</v>
       </c>
       <c r="M191" s="14" t="n">
-        <v>0.09711278890450747</v>
+        <v>0.1861510974207837</v>
       </c>
       <c r="N191" s="15" t="n">
         <v>0</v>
@@ -13808,12 +13808,12 @@
       </c>
       <c r="B192" s="17" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>WMU @ MICH</t>
         </is>
       </c>
       <c r="C192" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D192" s="25" t="n">
@@ -13826,17 +13826,17 @@
       </c>
       <c r="F192" s="17" t="inlineStr">
         <is>
-          <t>Under 61.5</t>
+          <t>Over 47.5</t>
         </is>
       </c>
       <c r="G192" s="26" t="n">
-        <v>61.5</v>
+        <v>47.5</v>
       </c>
       <c r="H192" s="18" t="n">
         <v>-115</v>
       </c>
       <c r="I192" s="20" t="n">
-        <v>0.5868277408859488</v>
+        <v>0.5868277708093877</v>
       </c>
       <c r="J192" s="20" t="n">
         <v>0.5108342361863488</v>
@@ -13845,10 +13845,10 @@
         <v>0.5348837209302325</v>
       </c>
       <c r="L192" s="19" t="n">
-        <v>0.05194401995571629</v>
+        <v>0.05194404987915524</v>
       </c>
       <c r="M192" s="19" t="n">
-        <v>0.09711273296068679</v>
+        <v>0.09711278890450747</v>
       </c>
       <c r="N192" s="20" t="n">
         <v>0</v>
@@ -13932,12 +13932,12 @@
       </c>
       <c r="B194" s="17" t="inlineStr">
         <is>
-          <t>SAC @ EMU</t>
+          <t>MIA @ STAN</t>
         </is>
       </c>
       <c r="C194" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 22:30</t>
+          <t>2026-09-05 01:00</t>
         </is>
       </c>
       <c r="D194" s="25" t="n">
@@ -13950,29 +13950,29 @@
       </c>
       <c r="F194" s="17" t="inlineStr">
         <is>
-          <t>Over 53.5</t>
+          <t>Over 47.5</t>
         </is>
       </c>
       <c r="G194" s="26" t="n">
-        <v>53.5</v>
+        <v>47.5</v>
       </c>
       <c r="H194" s="18" t="n">
-        <v>-115</v>
+        <v>-112</v>
       </c>
       <c r="I194" s="20" t="n">
-        <v>0.5849969873979599</v>
+        <v>0.5780608395330034</v>
       </c>
       <c r="J194" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K194" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L194" s="19" t="n">
-        <v>0.0501132664677274</v>
+        <v>0.04975895274055053</v>
       </c>
       <c r="M194" s="19" t="n">
-        <v>0.09369001991792503</v>
+        <v>0.09418658911604205</v>
       </c>
       <c r="N194" s="20" t="n">
         <v>0</v>
@@ -14125,12 +14125,12 @@
       </c>
       <c r="B197" s="12" t="inlineStr">
         <is>
-          <t>MIA @ STAN</t>
+          <t>MOST @ TA&amp;M</t>
         </is>
       </c>
       <c r="C197" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 01:00</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D197" s="22" t="n">
@@ -14143,29 +14143,29 @@
       </c>
       <c r="F197" s="12" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
+          <t>Over 52.5</t>
         </is>
       </c>
       <c r="G197" s="23" t="n">
-        <v>47.5</v>
+        <v>52.5</v>
       </c>
       <c r="H197" s="13" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="I197" s="15" t="n">
-        <v>0.5813130805911932</v>
+        <v>0.5684427123756473</v>
       </c>
       <c r="J197" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5</v>
       </c>
       <c r="K197" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L197" s="14" t="n">
-        <v>0.04642935966096073</v>
+        <v>0.04463318856612342</v>
       </c>
       <c r="M197" s="14" t="n">
-        <v>0.08680271588788291</v>
+        <v>0.08520881453532658</v>
       </c>
       <c r="N197" s="15" t="n">
         <v>0</v>
@@ -14188,12 +14188,12 @@
       </c>
       <c r="B198" s="17" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>NWST @ LT</t>
         </is>
       </c>
       <c r="C198" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D198" s="25" t="n">
@@ -14206,29 +14206,29 @@
       </c>
       <c r="F198" s="17" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>Over 52.5</t>
         </is>
       </c>
       <c r="G198" s="26" t="n">
-        <v>51.5</v>
+        <v>52.5</v>
       </c>
       <c r="H198" s="18" t="n">
-        <v>-102</v>
+        <v>-108</v>
       </c>
       <c r="I198" s="20" t="n">
-        <v>0.550297511023865</v>
+        <v>0.5625111309589089</v>
       </c>
       <c r="J198" s="20" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K198" s="20" t="n">
-        <v>0.504950495049505</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L198" s="19" t="n">
-        <v>0.04534701597436008</v>
+        <v>0.04328036172813965</v>
       </c>
       <c r="M198" s="19" t="n">
-        <v>0.08980487477275234</v>
+        <v>0.08335477073567654</v>
       </c>
       <c r="N198" s="20" t="n">
         <v>0</v>
@@ -14241,7 +14241,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q198" s="17" t="n"/>
+      <c r="Q198" s="17" t="inlineStr">
+        <is>
+          <t>NWST isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="12" t="inlineStr">
@@ -14251,12 +14255,12 @@
       </c>
       <c r="B199" s="12" t="inlineStr">
         <is>
-          <t>MOST @ TA&amp;M</t>
+          <t>TOW @ NAVY</t>
         </is>
       </c>
       <c r="C199" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D199" s="22" t="n">
@@ -14269,29 +14273,29 @@
       </c>
       <c r="F199" s="12" t="inlineStr">
         <is>
-          <t>Over 52.5</t>
+          <t>Over 53.5</t>
         </is>
       </c>
       <c r="G199" s="23" t="n">
-        <v>52.5</v>
+        <v>53.5</v>
       </c>
       <c r="H199" s="13" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I199" s="15" t="n">
-        <v>0.5684427123756473</v>
+        <v>0.5625111297198597</v>
       </c>
       <c r="J199" s="15" t="n">
-        <v>0.5</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K199" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L199" s="14" t="n">
-        <v>0.04463318856612342</v>
+        <v>0.04328036048909045</v>
       </c>
       <c r="M199" s="14" t="n">
-        <v>0.08520881453532658</v>
+        <v>0.08335476834935951</v>
       </c>
       <c r="N199" s="15" t="n">
         <v>0</v>
@@ -14304,7 +14308,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q199" s="12" t="n"/>
+      <c r="Q199" s="12" t="inlineStr">
+        <is>
+          <t>TOW isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="17" t="inlineStr">
@@ -14314,12 +14322,12 @@
       </c>
       <c r="B200" s="17" t="inlineStr">
         <is>
-          <t>NWST @ LT</t>
+          <t>SAC @ EMU</t>
         </is>
       </c>
       <c r="C200" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-08-29 22:30</t>
         </is>
       </c>
       <c r="D200" s="25" t="n">
@@ -14332,29 +14340,29 @@
       </c>
       <c r="F200" s="17" t="inlineStr">
         <is>
-          <t>Over 52.5</t>
+          <t>Over 54.5</t>
         </is>
       </c>
       <c r="G200" s="26" t="n">
-        <v>52.5</v>
+        <v>54.5</v>
       </c>
       <c r="H200" s="18" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="I200" s="20" t="n">
-        <v>0.5625111309589089</v>
+        <v>0.5554672208853876</v>
       </c>
       <c r="J200" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K200" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L200" s="19" t="n">
-        <v>0.04328036172813965</v>
+        <v>0.04327209893416806</v>
       </c>
       <c r="M200" s="19" t="n">
-        <v>0.08335477073567654</v>
+        <v>0.08448362172861379</v>
       </c>
       <c r="N200" s="20" t="n">
         <v>0</v>
@@ -14367,11 +14375,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q200" s="17" t="inlineStr">
-        <is>
-          <t>NWST isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q200" s="17" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="12" t="inlineStr">
@@ -14381,12 +14385,12 @@
       </c>
       <c r="B201" s="12" t="inlineStr">
         <is>
-          <t>TOW @ NAVY</t>
+          <t>LIU @ KU</t>
         </is>
       </c>
       <c r="C201" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-05 00:00</t>
         </is>
       </c>
       <c r="D201" s="22" t="n">
@@ -14406,22 +14410,22 @@
         <v>53.5</v>
       </c>
       <c r="H201" s="13" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I201" s="15" t="n">
-        <v>0.5625111297198597</v>
+        <v>0.5706075882916188</v>
       </c>
       <c r="J201" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K201" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L201" s="14" t="n">
-        <v>0.04328036048909045</v>
+        <v>0.04230570149916602</v>
       </c>
       <c r="M201" s="14" t="n">
-        <v>0.08335476834935951</v>
+        <v>0.0800786492662785</v>
       </c>
       <c r="N201" s="15" t="n">
         <v>0</v>
@@ -14436,7 +14440,7 @@
       </c>
       <c r="Q201" s="12" t="inlineStr">
         <is>
-          <t>TOW isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>LIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -14448,12 +14452,12 @@
       </c>
       <c r="B202" s="17" t="inlineStr">
         <is>
-          <t>LIU @ KU</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C202" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 00:00</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D202" s="25" t="n">
@@ -14466,29 +14470,29 @@
       </c>
       <c r="F202" s="17" t="inlineStr">
         <is>
-          <t>Over 53.5</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="G202" s="26" t="n">
-        <v>53.5</v>
+        <v>51.5</v>
       </c>
       <c r="H202" s="18" t="n">
-        <v>-112</v>
+        <v>-105</v>
       </c>
       <c r="I202" s="20" t="n">
-        <v>0.5706075882916188</v>
+        <v>0.5535624557888257</v>
       </c>
       <c r="J202" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K202" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L202" s="19" t="n">
-        <v>0.04230570149916602</v>
+        <v>0.04136733383760616</v>
       </c>
       <c r="M202" s="19" t="n">
-        <v>0.0800786492662785</v>
+        <v>0.08076479463532626</v>
       </c>
       <c r="N202" s="20" t="n">
         <v>0</v>
@@ -14501,11 +14505,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q202" s="17" t="inlineStr">
-        <is>
-          <t>LIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q202" s="17" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="12" t="inlineStr">
@@ -14706,12 +14706,12 @@
       </c>
       <c r="B206" s="17" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>ORST @ HOU</t>
         </is>
       </c>
       <c r="C206" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D206" s="25" t="n">
@@ -14724,17 +14724,17 @@
       </c>
       <c r="F206" s="17" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="G206" s="26" t="n">
-        <v>46.5</v>
+        <v>51.5</v>
       </c>
       <c r="H206" s="18" t="n">
         <v>-105</v>
       </c>
       <c r="I206" s="20" t="n">
-        <v>0.5516520441530162</v>
+        <v>0.55165195853316</v>
       </c>
       <c r="J206" s="20" t="n">
         <v>0.4891657638136511</v>
@@ -14743,10 +14743,10 @@
         <v>0.5121951219512195</v>
       </c>
       <c r="L206" s="19" t="n">
-        <v>0.03945692220179664</v>
+        <v>0.03945683658194044</v>
       </c>
       <c r="M206" s="19" t="n">
-        <v>0.07703494334636485</v>
+        <v>0.07703477618378851</v>
       </c>
       <c r="N206" s="20" t="n">
         <v>0</v>
@@ -14769,12 +14769,12 @@
       </c>
       <c r="B207" s="12" t="inlineStr">
         <is>
-          <t>ORST @ HOU</t>
+          <t>UNA @ ARK</t>
         </is>
       </c>
       <c r="C207" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-09-05 20:15</t>
         </is>
       </c>
       <c r="D207" s="22" t="n">
@@ -14787,29 +14787,29 @@
       </c>
       <c r="F207" s="12" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>Under 63.5</t>
         </is>
       </c>
       <c r="G207" s="23" t="n">
-        <v>51.5</v>
+        <v>63.5</v>
       </c>
       <c r="H207" s="13" t="n">
-        <v>-105</v>
+        <v>-115</v>
       </c>
       <c r="I207" s="15" t="n">
-        <v>0.55165195853316</v>
+        <v>0.573859827819978</v>
       </c>
       <c r="J207" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K207" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L207" s="14" t="n">
-        <v>0.03945683658194044</v>
+        <v>0.03897610688974551</v>
       </c>
       <c r="M207" s="14" t="n">
-        <v>0.07703477618378851</v>
+        <v>0.07286837375039362</v>
       </c>
       <c r="N207" s="15" t="n">
         <v>0</v>
@@ -14822,7 +14822,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q207" s="12" t="n"/>
+      <c r="Q207" s="12" t="inlineStr">
+        <is>
+          <t>UNA isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="17" t="inlineStr">
@@ -14832,12 +14836,12 @@
       </c>
       <c r="B208" s="17" t="inlineStr">
         <is>
-          <t>UNA @ ARK</t>
+          <t>PRST @ SDSU</t>
         </is>
       </c>
       <c r="C208" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 20:15</t>
+          <t>2026-09-06 01:30</t>
         </is>
       </c>
       <c r="D208" s="25" t="n">
@@ -14850,17 +14854,17 @@
       </c>
       <c r="F208" s="17" t="inlineStr">
         <is>
-          <t>Under 63.5</t>
+          <t>Under 57.5</t>
         </is>
       </c>
       <c r="G208" s="26" t="n">
-        <v>63.5</v>
+        <v>57.5</v>
       </c>
       <c r="H208" s="18" t="n">
         <v>-115</v>
       </c>
       <c r="I208" s="20" t="n">
-        <v>0.573859827819978</v>
+        <v>0.5738598234342943</v>
       </c>
       <c r="J208" s="20" t="n">
         <v>0.5108342361863488</v>
@@ -14869,10 +14873,10 @@
         <v>0.5348837209302325</v>
       </c>
       <c r="L208" s="19" t="n">
-        <v>0.03897610688974551</v>
+        <v>0.0389761025040618</v>
       </c>
       <c r="M208" s="19" t="n">
-        <v>0.07286837375039362</v>
+        <v>0.0728683655510719</v>
       </c>
       <c r="N208" s="20" t="n">
         <v>0</v>
@@ -14887,7 +14891,7 @@
       </c>
       <c r="Q208" s="17" t="inlineStr">
         <is>
-          <t>UNA isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>PRST isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -14899,12 +14903,12 @@
       </c>
       <c r="B209" s="12" t="inlineStr">
         <is>
-          <t>PRST @ SDSU</t>
+          <t>EIU @ MINN</t>
         </is>
       </c>
       <c r="C209" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 01:30</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D209" s="22" t="n">
@@ -14917,29 +14921,29 @@
       </c>
       <c r="F209" s="12" t="inlineStr">
         <is>
-          <t>Under 57.5</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="G209" s="23" t="n">
-        <v>57.5</v>
+        <v>51.5</v>
       </c>
       <c r="H209" s="13" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="I209" s="15" t="n">
-        <v>0.5738598234342943</v>
+        <v>0.5627832126788681</v>
       </c>
       <c r="J209" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5</v>
       </c>
       <c r="K209" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L209" s="14" t="n">
-        <v>0.0389761025040618</v>
+        <v>0.03897368886934427</v>
       </c>
       <c r="M209" s="14" t="n">
-        <v>0.0728683655510719</v>
+        <v>0.07440431511420276</v>
       </c>
       <c r="N209" s="15" t="n">
         <v>0</v>
@@ -14954,7 +14958,7 @@
       </c>
       <c r="Q209" s="12" t="inlineStr">
         <is>
-          <t>PRST isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -14966,12 +14970,12 @@
       </c>
       <c r="B210" s="17" t="inlineStr">
         <is>
-          <t>EIU @ MINN</t>
+          <t>WYO @ CSU</t>
         </is>
       </c>
       <c r="C210" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-09-05 22:00</t>
         </is>
       </c>
       <c r="D210" s="25" t="n">
@@ -14984,29 +14988,29 @@
       </c>
       <c r="F210" s="17" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>Over 47.5</t>
         </is>
       </c>
       <c r="G210" s="26" t="n">
-        <v>51.5</v>
+        <v>47.5</v>
       </c>
       <c r="H210" s="18" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="I210" s="20" t="n">
-        <v>0.5627832126788681</v>
+        <v>0.5668409273050667</v>
       </c>
       <c r="J210" s="20" t="n">
-        <v>0.5</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K210" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L210" s="19" t="n">
-        <v>0.03897368886934427</v>
+        <v>0.03853904051261392</v>
       </c>
       <c r="M210" s="19" t="n">
-        <v>0.07440431511420276</v>
+        <v>0.07294889811316196</v>
       </c>
       <c r="N210" s="20" t="n">
         <v>0</v>
@@ -15019,11 +15023,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q210" s="17" t="inlineStr">
-        <is>
-          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q210" s="17" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="12" t="inlineStr">
@@ -15033,12 +15033,12 @@
       </c>
       <c r="B211" s="12" t="inlineStr">
         <is>
-          <t>WYO @ CSU</t>
+          <t>LOU @ MISS</t>
         </is>
       </c>
       <c r="C211" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 22:00</t>
+          <t>2026-09-06 23:30</t>
         </is>
       </c>
       <c r="D211" s="22" t="n">
@@ -15051,17 +15051,17 @@
       </c>
       <c r="F211" s="12" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
+          <t>Under 55.5</t>
         </is>
       </c>
       <c r="G211" s="23" t="n">
-        <v>47.5</v>
+        <v>55.5</v>
       </c>
       <c r="H211" s="13" t="n">
         <v>-112</v>
       </c>
       <c r="I211" s="15" t="n">
-        <v>0.5668409273050667</v>
+        <v>0.5668408697405979</v>
       </c>
       <c r="J211" s="15" t="n">
         <v>0.5043297540699688</v>
@@ -15070,10 +15070,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L211" s="14" t="n">
-        <v>0.03853904051261392</v>
+        <v>0.03853898294814506</v>
       </c>
       <c r="M211" s="14" t="n">
-        <v>0.07294889811316196</v>
+        <v>0.07294878915184599</v>
       </c>
       <c r="N211" s="15" t="n">
         <v>0</v>
@@ -15096,12 +15096,12 @@
       </c>
       <c r="B212" s="17" t="inlineStr">
         <is>
-          <t>LOU @ MISS</t>
+          <t>HAW @ STAN</t>
         </is>
       </c>
       <c r="C212" s="17" t="inlineStr">
         <is>
-          <t>2026-09-06 23:30</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D212" s="25" t="n">
@@ -15109,34 +15109,32 @@
       </c>
       <c r="E212" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F212" s="17" t="inlineStr">
         <is>
-          <t>Under 55.5</t>
-        </is>
-      </c>
-      <c r="G212" s="26" t="n">
-        <v>55.5</v>
-      </c>
+          <t>HAW ML</t>
+        </is>
+      </c>
+      <c r="G212" s="26" t="n"/>
       <c r="H212" s="18" t="n">
-        <v>-112</v>
+        <v>154</v>
       </c>
       <c r="I212" s="20" t="n">
-        <v>0.5668408697405979</v>
+        <v>0.4319998430736718</v>
       </c>
       <c r="J212" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.3775334481388264</v>
       </c>
       <c r="K212" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.3937007874015748</v>
       </c>
       <c r="L212" s="19" t="n">
-        <v>0.03853898294814506</v>
+        <v>0.03829905567209696</v>
       </c>
       <c r="M212" s="19" t="n">
-        <v>0.07294878915184599</v>
+        <v>0.09727960140712633</v>
       </c>
       <c r="N212" s="20" t="n">
         <v>0</v>
@@ -15159,12 +15157,12 @@
       </c>
       <c r="B213" s="12" t="inlineStr">
         <is>
-          <t>HAW @ STAN</t>
+          <t>SMU @ FSU</t>
         </is>
       </c>
       <c r="C213" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-07 23:30</t>
         </is>
       </c>
       <c r="D213" s="22" t="n">
@@ -15177,27 +15175,27 @@
       </c>
       <c r="F213" s="12" t="inlineStr">
         <is>
-          <t>HAW ML</t>
+          <t>FSU ML</t>
         </is>
       </c>
       <c r="G213" s="23" t="n"/>
       <c r="H213" s="13" t="n">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="I213" s="15" t="n">
-        <v>0.4319998430736718</v>
+        <v>0.4707366622168365</v>
       </c>
       <c r="J213" s="15" t="n">
-        <v>0.3775334481388264</v>
+        <v>0.4170073589533933</v>
       </c>
       <c r="K213" s="15" t="n">
-        <v>0.3937007874015748</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="L213" s="14" t="n">
-        <v>0.03829905567209696</v>
+        <v>0.03595405352118436</v>
       </c>
       <c r="M213" s="14" t="n">
-        <v>0.09727960140712633</v>
+        <v>0.08269432309872393</v>
       </c>
       <c r="N213" s="15" t="n">
         <v>0</v>
@@ -15220,12 +15218,12 @@
       </c>
       <c r="B214" s="17" t="inlineStr">
         <is>
-          <t>SMU @ FSU</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C214" s="17" t="inlineStr">
         <is>
-          <t>2026-09-07 23:30</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D214" s="25" t="n">
@@ -15233,32 +15231,34 @@
       </c>
       <c r="E214" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F214" s="17" t="inlineStr">
         <is>
-          <t>FSU ML</t>
-        </is>
-      </c>
-      <c r="G214" s="26" t="n"/>
+          <t>Over 46.5</t>
+        </is>
+      </c>
+      <c r="G214" s="26" t="n">
+        <v>46.5</v>
+      </c>
       <c r="H214" s="18" t="n">
-        <v>130</v>
+        <v>-108</v>
       </c>
       <c r="I214" s="20" t="n">
-        <v>0.4707366622168365</v>
+        <v>0.5549042852112063</v>
       </c>
       <c r="J214" s="20" t="n">
-        <v>0.4170073589533933</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K214" s="20" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L214" s="19" t="n">
-        <v>0.03595405352118436</v>
+        <v>0.035673515980437</v>
       </c>
       <c r="M214" s="19" t="n">
-        <v>0.08269432309872393</v>
+        <v>0.06870454929565661</v>
       </c>
       <c r="N214" s="20" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="B253" s="12" t="inlineStr">
         <is>
-          <t>VMI @ VT</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C253" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D253" s="22" t="n">
@@ -17718,37 +17718,37 @@
       </c>
       <c r="E253" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F253" s="12" t="inlineStr">
         <is>
-          <t>Under 57.5</t>
+          <t>NCSU +4</t>
         </is>
       </c>
       <c r="G253" s="23" t="n">
-        <v>57.5</v>
+        <v>-4</v>
       </c>
       <c r="H253" s="13" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="I253" s="15" t="n">
-        <v>0.5312862329478931</v>
+        <v>0.5241780718311789</v>
       </c>
       <c r="J253" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5</v>
       </c>
       <c r="K253" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L253" s="14" t="n">
-        <v>-0.003597487982339387</v>
+        <v>0.0003685480216550907</v>
       </c>
       <c r="M253" s="14" t="n">
-        <v>-0.006725738401765102</v>
+        <v>0.0006816732875316034</v>
       </c>
       <c r="N253" s="15" t="n">
-        <v>0</v>
+        <v>0.0312</v>
       </c>
       <c r="O253" s="24" t="n">
         <v>0.45</v>
@@ -17758,11 +17758,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q253" s="12" t="inlineStr">
-        <is>
-          <t>VMI isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q253" s="12" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="17" t="inlineStr">
@@ -17795,22 +17791,22 @@
       </c>
       <c r="G254" s="26" t="n"/>
       <c r="H254" s="18" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="I254" s="20" t="n">
-        <v>0.3950991488430204</v>
+        <v>0.3920850509946253</v>
       </c>
       <c r="J254" s="20" t="n">
-        <v>0.3835616438356164</v>
+        <v>0.3775334481388264</v>
       </c>
       <c r="K254" s="20" t="n">
-        <v>0.4</v>
+        <v>0.3937007874015748</v>
       </c>
       <c r="L254" s="19" t="n">
-        <v>-0.00490085115697958</v>
+        <v>-0.001615736406949508</v>
       </c>
       <c r="M254" s="19" t="n">
-        <v>-0.01225212789244889</v>
+        <v>-0.00410397047365163</v>
       </c>
       <c r="N254" s="20" t="n">
         <v>0</v>
@@ -17833,12 +17829,12 @@
       </c>
       <c r="B255" s="12" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>VMI @ VT</t>
         </is>
       </c>
       <c r="C255" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D255" s="22" t="n">
@@ -17846,22 +17842,22 @@
       </c>
       <c r="E255" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F255" s="12" t="inlineStr">
         <is>
-          <t>NCSU +4</t>
+          <t>Under 57.5</t>
         </is>
       </c>
       <c r="G255" s="23" t="n">
-        <v>-4</v>
+        <v>57.5</v>
       </c>
       <c r="H255" s="13" t="n">
         <v>-115</v>
       </c>
       <c r="I255" s="15" t="n">
-        <v>0.5295951899243534</v>
+        <v>0.5312862329478931</v>
       </c>
       <c r="J255" s="15" t="n">
         <v>0.5108342361863488</v>
@@ -17870,13 +17866,13 @@
         <v>0.5348837209302325</v>
       </c>
       <c r="L255" s="14" t="n">
-        <v>-0.005288531005879116</v>
+        <v>-0.003597487982339387</v>
       </c>
       <c r="M255" s="14" t="n">
-        <v>-0.009579244458339131</v>
+        <v>-0.006725738401765102</v>
       </c>
       <c r="N255" s="15" t="n">
-        <v>0.0312</v>
+        <v>0</v>
       </c>
       <c r="O255" s="24" t="n">
         <v>0.45</v>
@@ -17886,7 +17882,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q255" s="12" t="n"/>
+      <c r="Q255" s="12" t="inlineStr">
+        <is>
+          <t>VMI isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="17" t="inlineStr">
@@ -20437,12 +20437,12 @@
       </c>
       <c r="B295" s="12" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>SHSU @ TROY</t>
         </is>
       </c>
       <c r="C295" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D295" s="22" t="n">
@@ -20450,32 +20450,34 @@
       </c>
       <c r="E295" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F295" s="12" t="inlineStr">
         <is>
-          <t>UVA ML</t>
-        </is>
-      </c>
-      <c r="G295" s="23" t="n"/>
+          <t>Under 53.5</t>
+        </is>
+      </c>
+      <c r="G295" s="23" t="n">
+        <v>53.5</v>
+      </c>
       <c r="H295" s="13" t="n">
-        <v>-180</v>
+        <v>-115</v>
       </c>
       <c r="I295" s="15" t="n">
-        <v>0.6049008511569796</v>
+        <v>0.4954435546186861</v>
       </c>
       <c r="J295" s="15" t="n">
-        <v>0.6164383561643836</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K295" s="15" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L295" s="14" t="n">
-        <v>-0.03795629170016335</v>
+        <v>-0.03944016631154645</v>
       </c>
       <c r="M295" s="14" t="n">
-        <v>-0.05904312042247623</v>
+        <v>-0.07373596310419572</v>
       </c>
       <c r="N295" s="15" t="n">
         <v>0</v>
@@ -20498,12 +20500,12 @@
       </c>
       <c r="B296" s="17" t="inlineStr">
         <is>
-          <t>SHSU @ TROY</t>
+          <t>TXST @ TEX</t>
         </is>
       </c>
       <c r="C296" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D296" s="25" t="n">
@@ -20516,29 +20518,29 @@
       </c>
       <c r="F296" s="17" t="inlineStr">
         <is>
-          <t>Under 53.5</t>
+          <t>Over 59.5</t>
         </is>
       </c>
       <c r="G296" s="26" t="n">
-        <v>53.5</v>
+        <v>59.5</v>
       </c>
       <c r="H296" s="18" t="n">
-        <v>-115</v>
+        <v>-112</v>
       </c>
       <c r="I296" s="20" t="n">
-        <v>0.4954435546186861</v>
+        <v>0.488207483548292</v>
       </c>
       <c r="J296" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K296" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L296" s="19" t="n">
-        <v>-0.03944016631154645</v>
+        <v>-0.0400944032441608</v>
       </c>
       <c r="M296" s="19" t="n">
-        <v>-0.07373596310419572</v>
+        <v>-0.07589297756930441</v>
       </c>
       <c r="N296" s="20" t="n">
         <v>0</v>
@@ -20561,12 +20563,12 @@
       </c>
       <c r="B297" s="12" t="inlineStr">
         <is>
-          <t>TXST @ TEX</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C297" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D297" s="22" t="n">
@@ -20574,34 +20576,32 @@
       </c>
       <c r="E297" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F297" s="12" t="inlineStr">
         <is>
-          <t>Over 59.5</t>
-        </is>
-      </c>
-      <c r="G297" s="23" t="n">
-        <v>59.5</v>
-      </c>
+          <t>UVA ML</t>
+        </is>
+      </c>
+      <c r="G297" s="23" t="n"/>
       <c r="H297" s="13" t="n">
-        <v>-112</v>
+        <v>-185</v>
       </c>
       <c r="I297" s="15" t="n">
-        <v>0.488207483548292</v>
+        <v>0.6079149490053747</v>
       </c>
       <c r="J297" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.6224665518611737</v>
       </c>
       <c r="K297" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.6491228070175439</v>
       </c>
       <c r="L297" s="14" t="n">
-        <v>-0.0400944032441608</v>
+        <v>-0.0412078580121692</v>
       </c>
       <c r="M297" s="14" t="n">
-        <v>-0.07589297756930441</v>
+        <v>-0.06348237585658495</v>
       </c>
       <c r="N297" s="15" t="n">
         <v>0</v>
@@ -20687,12 +20687,12 @@
       </c>
       <c r="B299" s="12" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>VMI @ VT</t>
         </is>
       </c>
       <c r="C299" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D299" s="22" t="n">
@@ -20700,22 +20700,22 @@
       </c>
       <c r="E299" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F299" s="12" t="inlineStr">
         <is>
-          <t>UVA -4</t>
+          <t>Over 57.5</t>
         </is>
       </c>
       <c r="G299" s="23" t="n">
-        <v>-4</v>
+        <v>57.5</v>
       </c>
       <c r="H299" s="13" t="n">
         <v>-105</v>
       </c>
       <c r="I299" s="15" t="n">
-        <v>0.4704048100756466</v>
+        <v>0.4687137670521069</v>
       </c>
       <c r="J299" s="15" t="n">
         <v>0.4891657638136511</v>
@@ -20724,13 +20724,13 @@
         <v>0.5121951219512195</v>
       </c>
       <c r="L299" s="14" t="n">
-        <v>-0.04179031187557292</v>
+        <v>-0.04348135489911265</v>
       </c>
       <c r="M299" s="14" t="n">
-        <v>-0.07904888639661339</v>
+        <v>-0.08489216908874375</v>
       </c>
       <c r="N299" s="15" t="n">
-        <v>0.0312</v>
+        <v>0</v>
       </c>
       <c r="O299" s="24" t="n">
         <v>0.45</v>
@@ -20740,7 +20740,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q299" s="12" t="n"/>
+      <c r="Q299" s="12" t="inlineStr">
+        <is>
+          <t>VMI isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="17" t="inlineStr">
@@ -20750,12 +20754,12 @@
       </c>
       <c r="B300" s="17" t="inlineStr">
         <is>
-          <t>VMI @ VT</t>
+          <t>LIB @ JMU</t>
         </is>
       </c>
       <c r="C300" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D300" s="25" t="n">
@@ -20763,34 +20767,32 @@
       </c>
       <c r="E300" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F300" s="17" t="inlineStr">
         <is>
-          <t>Over 57.5</t>
-        </is>
-      </c>
-      <c r="G300" s="26" t="n">
-        <v>57.5</v>
-      </c>
+          <t>JMU ML</t>
+        </is>
+      </c>
+      <c r="G300" s="26" t="n"/>
       <c r="H300" s="18" t="n">
-        <v>-105</v>
+        <v>-245</v>
       </c>
       <c r="I300" s="20" t="n">
-        <v>0.4687137670521069</v>
+        <v>0.6636736992451751</v>
       </c>
       <c r="J300" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.6805555555555556</v>
       </c>
       <c r="K300" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.7101449275362319</v>
       </c>
       <c r="L300" s="19" t="n">
-        <v>-0.04348135489911265</v>
+        <v>-0.04647122829105688</v>
       </c>
       <c r="M300" s="19" t="n">
-        <v>-0.08489216908874375</v>
+        <v>-0.06543907657312081</v>
       </c>
       <c r="N300" s="20" t="n">
         <v>0</v>
@@ -20803,11 +20805,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q300" s="17" t="inlineStr">
-        <is>
-          <t>VMI isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q300" s="17" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="12" t="inlineStr">
@@ -20817,12 +20815,12 @@
       </c>
       <c r="B301" s="12" t="inlineStr">
         <is>
-          <t>LIB @ JMU</t>
+          <t>WKU @ NEV</t>
         </is>
       </c>
       <c r="C301" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-09-06 02:30</t>
         </is>
       </c>
       <c r="D301" s="22" t="n">
@@ -20835,27 +20833,27 @@
       </c>
       <c r="F301" s="12" t="inlineStr">
         <is>
-          <t>JMU ML</t>
+          <t>WKU ML</t>
         </is>
       </c>
       <c r="G301" s="23" t="n"/>
       <c r="H301" s="13" t="n">
-        <v>-245</v>
+        <v>-130</v>
       </c>
       <c r="I301" s="15" t="n">
-        <v>0.6636736992451751</v>
+        <v>0.5183478343346938</v>
       </c>
       <c r="J301" s="15" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.5427435387673957</v>
       </c>
       <c r="K301" s="15" t="n">
-        <v>0.7101449275362319</v>
+        <v>0.5652173913043478</v>
       </c>
       <c r="L301" s="14" t="n">
-        <v>-0.04647122829105688</v>
+        <v>-0.046869556969654</v>
       </c>
       <c r="M301" s="14" t="n">
-        <v>-0.06543907657312081</v>
+        <v>-0.08292306233092644</v>
       </c>
       <c r="N301" s="15" t="n">
         <v>0</v>
@@ -20878,12 +20876,12 @@
       </c>
       <c r="B302" s="17" t="inlineStr">
         <is>
-          <t>WKU @ NEV</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C302" s="17" t="inlineStr">
         <is>
-          <t>2026-09-06 02:30</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D302" s="25" t="n">
@@ -20891,35 +20889,37 @@
       </c>
       <c r="E302" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F302" s="17" t="inlineStr">
         <is>
-          <t>WKU ML</t>
-        </is>
-      </c>
-      <c r="G302" s="26" t="n"/>
+          <t>UVA -4</t>
+        </is>
+      </c>
+      <c r="G302" s="26" t="n">
+        <v>-4</v>
+      </c>
       <c r="H302" s="18" t="n">
-        <v>-130</v>
+        <v>-110</v>
       </c>
       <c r="I302" s="20" t="n">
-        <v>0.5183478343346938</v>
+        <v>0.4758219281688211</v>
       </c>
       <c r="J302" s="20" t="n">
-        <v>0.5427435387673957</v>
+        <v>0.5</v>
       </c>
       <c r="K302" s="20" t="n">
-        <v>0.5652173913043478</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L302" s="19" t="n">
-        <v>-0.046869556969654</v>
+        <v>-0.04798759564070276</v>
       </c>
       <c r="M302" s="19" t="n">
-        <v>-0.08292306233092644</v>
+        <v>-0.08875875098781161</v>
       </c>
       <c r="N302" s="20" t="n">
-        <v>0</v>
+        <v>0.0312</v>
       </c>
       <c r="O302" s="27" t="n">
         <v>0.45</v>
@@ -23363,12 +23363,12 @@
       </c>
       <c r="B341" s="12" t="inlineStr">
         <is>
-          <t>PRST @ SDSU</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C341" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 01:30</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D341" s="22" t="n">
@@ -23381,29 +23381,29 @@
       </c>
       <c r="F341" s="12" t="inlineStr">
         <is>
-          <t>Over 57.5</t>
+          <t>Under 46.5</t>
         </is>
       </c>
       <c r="G341" s="23" t="n">
-        <v>57.5</v>
+        <v>46.5</v>
       </c>
       <c r="H341" s="13" t="n">
-        <v>-105</v>
+        <v>-112</v>
       </c>
       <c r="I341" s="15" t="n">
-        <v>0.4261401765657057</v>
+        <v>0.4450957147887937</v>
       </c>
       <c r="J341" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K341" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L341" s="14" t="n">
-        <v>-0.08605494538551384</v>
+        <v>-0.0832061720036591</v>
       </c>
       <c r="M341" s="14" t="n">
-        <v>-0.1680120362288604</v>
+        <v>-0.1574973970069262</v>
       </c>
       <c r="N341" s="15" t="n">
         <v>0</v>
@@ -23416,11 +23416,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q341" s="12" t="inlineStr">
-        <is>
-          <t>PRST isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q341" s="12" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="17" t="inlineStr">
@@ -23430,12 +23426,12 @@
       </c>
       <c r="B342" s="17" t="inlineStr">
         <is>
-          <t>UNA @ ARK</t>
+          <t>PRST @ SDSU</t>
         </is>
       </c>
       <c r="C342" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 20:15</t>
+          <t>2026-09-06 01:30</t>
         </is>
       </c>
       <c r="D342" s="25" t="n">
@@ -23448,17 +23444,17 @@
       </c>
       <c r="F342" s="17" t="inlineStr">
         <is>
-          <t>Over 63.5</t>
+          <t>Over 57.5</t>
         </is>
       </c>
       <c r="G342" s="26" t="n">
-        <v>63.5</v>
+        <v>57.5</v>
       </c>
       <c r="H342" s="18" t="n">
         <v>-105</v>
       </c>
       <c r="I342" s="20" t="n">
-        <v>0.4261401721800219</v>
+        <v>0.4261401765657057</v>
       </c>
       <c r="J342" s="20" t="n">
         <v>0.4891657638136511</v>
@@ -23467,10 +23463,10 @@
         <v>0.5121951219512195</v>
       </c>
       <c r="L342" s="19" t="n">
-        <v>-0.0860549497711976</v>
+        <v>-0.08605494538551384</v>
       </c>
       <c r="M342" s="19" t="n">
-        <v>-0.1680120447913857</v>
+        <v>-0.1680120362288604</v>
       </c>
       <c r="N342" s="20" t="n">
         <v>0</v>
@@ -23485,7 +23481,7 @@
       </c>
       <c r="Q342" s="17" t="inlineStr">
         <is>
-          <t>UNA isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>PRST isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -23497,12 +23493,12 @@
       </c>
       <c r="B343" s="12" t="inlineStr">
         <is>
-          <t>LOU @ MISS</t>
+          <t>UNA @ ARK</t>
         </is>
       </c>
       <c r="C343" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 23:30</t>
+          <t>2026-09-05 20:15</t>
         </is>
       </c>
       <c r="D343" s="22" t="n">
@@ -23515,29 +23511,29 @@
       </c>
       <c r="F343" s="12" t="inlineStr">
         <is>
-          <t>Over 55.5</t>
+          <t>Over 63.5</t>
         </is>
       </c>
       <c r="G343" s="23" t="n">
-        <v>55.5</v>
+        <v>63.5</v>
       </c>
       <c r="H343" s="13" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="I343" s="15" t="n">
-        <v>0.4331591302594021</v>
+        <v>0.4261401721800219</v>
       </c>
       <c r="J343" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K343" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L343" s="14" t="n">
-        <v>-0.08607163897136716</v>
+        <v>-0.0860549497711976</v>
       </c>
       <c r="M343" s="14" t="n">
-        <v>-0.1657676009818922</v>
+        <v>-0.1680120447913857</v>
       </c>
       <c r="N343" s="15" t="n">
         <v>0</v>
@@ -23550,7 +23546,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q343" s="12" t="n"/>
+      <c r="Q343" s="12" t="inlineStr">
+        <is>
+          <t>UNA isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="17" t="inlineStr">
@@ -23560,12 +23560,12 @@
       </c>
       <c r="B344" s="17" t="inlineStr">
         <is>
-          <t>WYO @ CSU</t>
+          <t>LOU @ MISS</t>
         </is>
       </c>
       <c r="C344" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 22:00</t>
+          <t>2026-09-06 23:30</t>
         </is>
       </c>
       <c r="D344" s="25" t="n">
@@ -23578,17 +23578,17 @@
       </c>
       <c r="F344" s="17" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
+          <t>Over 55.5</t>
         </is>
       </c>
       <c r="G344" s="26" t="n">
-        <v>47.5</v>
+        <v>55.5</v>
       </c>
       <c r="H344" s="18" t="n">
         <v>-108</v>
       </c>
       <c r="I344" s="20" t="n">
-        <v>0.4331590726949333</v>
+        <v>0.4331591302594021</v>
       </c>
       <c r="J344" s="20" t="n">
         <v>0.4956702459300312</v>
@@ -23597,10 +23597,10 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L344" s="19" t="n">
-        <v>-0.08607169653583602</v>
+        <v>-0.08607163897136716</v>
       </c>
       <c r="M344" s="19" t="n">
-        <v>-0.1657677118467952</v>
+        <v>-0.1657676009818922</v>
       </c>
       <c r="N344" s="20" t="n">
         <v>0</v>
@@ -23623,12 +23623,12 @@
       </c>
       <c r="B345" s="12" t="inlineStr">
         <is>
-          <t>ORST @ HOU</t>
+          <t>WYO @ CSU</t>
         </is>
       </c>
       <c r="C345" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-09-05 22:00</t>
         </is>
       </c>
       <c r="D345" s="22" t="n">
@@ -23641,29 +23641,29 @@
       </c>
       <c r="F345" s="12" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>Under 47.5</t>
         </is>
       </c>
       <c r="G345" s="23" t="n">
-        <v>51.5</v>
+        <v>47.5</v>
       </c>
       <c r="H345" s="13" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="I345" s="15" t="n">
-        <v>0.44834804146684</v>
+        <v>0.4331590726949333</v>
       </c>
       <c r="J345" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K345" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L345" s="14" t="n">
-        <v>-0.08653567946339247</v>
+        <v>-0.08607169653583602</v>
       </c>
       <c r="M345" s="14" t="n">
-        <v>-0.1617840963880817</v>
+        <v>-0.1657677118467952</v>
       </c>
       <c r="N345" s="15" t="n">
         <v>0</v>
@@ -23686,12 +23686,12 @@
       </c>
       <c r="B346" s="17" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>ORST @ HOU</t>
         </is>
       </c>
       <c r="C346" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D346" s="25" t="n">
@@ -23704,17 +23704,17 @@
       </c>
       <c r="F346" s="17" t="inlineStr">
         <is>
-          <t>Under 46.5</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="G346" s="26" t="n">
-        <v>46.5</v>
+        <v>51.5</v>
       </c>
       <c r="H346" s="18" t="n">
         <v>-115</v>
       </c>
       <c r="I346" s="20" t="n">
-        <v>0.4483479558469838</v>
+        <v>0.44834804146684</v>
       </c>
       <c r="J346" s="20" t="n">
         <v>0.5108342361863488</v>
@@ -23723,10 +23723,10 @@
         <v>0.5348837209302325</v>
       </c>
       <c r="L346" s="19" t="n">
-        <v>-0.08653576508324867</v>
+        <v>-0.08653567946339247</v>
       </c>
       <c r="M346" s="19" t="n">
-        <v>-0.1617842564599868</v>
+        <v>-0.1617840963880817</v>
       </c>
       <c r="N346" s="20" t="n">
         <v>0</v>
@@ -24007,12 +24007,12 @@
       </c>
       <c r="B351" s="12" t="inlineStr">
         <is>
-          <t>LIU @ KU</t>
+          <t>NCSU @ UVA</t>
         </is>
       </c>
       <c r="C351" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 00:00</t>
+          <t>2026-08-29 19:30</t>
         </is>
       </c>
       <c r="D351" s="22" t="n">
@@ -24025,29 +24025,29 @@
       </c>
       <c r="F351" s="12" t="inlineStr">
         <is>
-          <t>Under 53.5</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="G351" s="23" t="n">
-        <v>53.5</v>
+        <v>51.5</v>
       </c>
       <c r="H351" s="13" t="n">
-        <v>-108</v>
+        <v>-115</v>
       </c>
       <c r="I351" s="15" t="n">
-        <v>0.4293924117083812</v>
+        <v>0.4464375442111743</v>
       </c>
       <c r="J351" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K351" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L351" s="14" t="n">
-        <v>-0.08983835752238811</v>
+        <v>-0.08844617671905819</v>
       </c>
       <c r="M351" s="14" t="n">
-        <v>-0.1730220218949696</v>
+        <v>-0.1653558956051959</v>
       </c>
       <c r="N351" s="15" t="n">
         <v>0</v>
@@ -24060,11 +24060,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q351" s="12" t="inlineStr">
-        <is>
-          <t>LIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q351" s="12" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="17" t="inlineStr">
@@ -24074,12 +24070,12 @@
       </c>
       <c r="B352" s="17" t="inlineStr">
         <is>
-          <t>TOW @ NAVY</t>
+          <t>LIU @ KU</t>
         </is>
       </c>
       <c r="C352" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-05 00:00</t>
         </is>
       </c>
       <c r="D352" s="25" t="n">
@@ -24099,22 +24095,22 @@
         <v>53.5</v>
       </c>
       <c r="H352" s="18" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="I352" s="20" t="n">
-        <v>0.4374888702801403</v>
+        <v>0.4293924117083812</v>
       </c>
       <c r="J352" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K352" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L352" s="19" t="n">
-        <v>-0.09081301651231255</v>
+        <v>-0.08983835752238811</v>
       </c>
       <c r="M352" s="19" t="n">
-        <v>-0.1718960669697345</v>
+        <v>-0.1730220218949696</v>
       </c>
       <c r="N352" s="20" t="n">
         <v>0</v>
@@ -24129,7 +24125,7 @@
       </c>
       <c r="Q352" s="17" t="inlineStr">
         <is>
-          <t>TOW isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>LIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -24141,12 +24137,12 @@
       </c>
       <c r="B353" s="12" t="inlineStr">
         <is>
-          <t>NWST @ LT</t>
+          <t>SAC @ EMU</t>
         </is>
       </c>
       <c r="C353" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-08-29 22:30</t>
         </is>
       </c>
       <c r="D353" s="22" t="n">
@@ -24159,29 +24155,29 @@
       </c>
       <c r="F353" s="12" t="inlineStr">
         <is>
-          <t>Under 52.5</t>
+          <t>Under 54.5</t>
         </is>
       </c>
       <c r="G353" s="23" t="n">
-        <v>52.5</v>
+        <v>54.5</v>
       </c>
       <c r="H353" s="13" t="n">
-        <v>-112</v>
+        <v>-115</v>
       </c>
       <c r="I353" s="15" t="n">
-        <v>0.4374888690410911</v>
+        <v>0.4445327791146124</v>
       </c>
       <c r="J353" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K353" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L353" s="14" t="n">
-        <v>-0.09081301775136175</v>
+        <v>-0.09035094181562009</v>
       </c>
       <c r="M353" s="14" t="n">
-        <v>-0.1718960693150776</v>
+        <v>-0.168916978177029</v>
       </c>
       <c r="N353" s="15" t="n">
         <v>0</v>
@@ -24194,11 +24190,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q353" s="12" t="inlineStr">
-        <is>
-          <t>NWST isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q353" s="12" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="17" t="inlineStr">
@@ -24208,12 +24200,12 @@
       </c>
       <c r="B354" s="17" t="inlineStr">
         <is>
-          <t>NCSU @ UVA</t>
+          <t>TOW @ NAVY</t>
         </is>
       </c>
       <c r="C354" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D354" s="25" t="n">
@@ -24226,29 +24218,29 @@
       </c>
       <c r="F354" s="17" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>Under 53.5</t>
         </is>
       </c>
       <c r="G354" s="26" t="n">
-        <v>51.5</v>
+        <v>53.5</v>
       </c>
       <c r="H354" s="18" t="n">
-        <v>-118</v>
+        <v>-112</v>
       </c>
       <c r="I354" s="20" t="n">
-        <v>0.449702488976135</v>
+        <v>0.4374888702801403</v>
       </c>
       <c r="J354" s="20" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K354" s="20" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L354" s="19" t="n">
-        <v>-0.09158191469358978</v>
+        <v>-0.09081301651231255</v>
       </c>
       <c r="M354" s="19" t="n">
-        <v>-0.1691937068068015</v>
+        <v>-0.1718960669697345</v>
       </c>
       <c r="N354" s="20" t="n">
         <v>0</v>
@@ -24261,7 +24253,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q354" s="17" t="n"/>
+      <c r="Q354" s="17" t="inlineStr">
+        <is>
+          <t>TOW isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="12" t="inlineStr">
@@ -24271,12 +24267,12 @@
       </c>
       <c r="B355" s="12" t="inlineStr">
         <is>
-          <t>MOST @ TA&amp;M</t>
+          <t>NWST @ LT</t>
         </is>
       </c>
       <c r="C355" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D355" s="22" t="n">
@@ -24296,22 +24292,22 @@
         <v>52.5</v>
       </c>
       <c r="H355" s="13" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="I355" s="15" t="n">
-        <v>0.4315572876243527</v>
+        <v>0.4374888690410911</v>
       </c>
       <c r="J355" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K355" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L355" s="14" t="n">
-        <v>-0.09225223618517109</v>
+        <v>-0.09081301775136175</v>
       </c>
       <c r="M355" s="14" t="n">
-        <v>-0.1761179054444175</v>
+        <v>-0.1718960693150776</v>
       </c>
       <c r="N355" s="15" t="n">
         <v>0</v>
@@ -24324,7 +24320,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q355" s="12" t="n"/>
+      <c r="Q355" s="12" t="inlineStr">
+        <is>
+          <t>NWST isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="17" t="inlineStr">
@@ -24334,12 +24334,12 @@
       </c>
       <c r="B356" s="17" t="inlineStr">
         <is>
-          <t>MIA @ STAN</t>
+          <t>MOST @ TA&amp;M</t>
         </is>
       </c>
       <c r="C356" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 01:00</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D356" s="25" t="n">
@@ -24352,29 +24352,29 @@
       </c>
       <c r="F356" s="17" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
+          <t>Under 52.5</t>
         </is>
       </c>
       <c r="G356" s="26" t="n">
-        <v>47.5</v>
+        <v>52.5</v>
       </c>
       <c r="H356" s="18" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="I356" s="20" t="n">
-        <v>0.4186869194088068</v>
+        <v>0.4315572876243527</v>
       </c>
       <c r="J356" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5</v>
       </c>
       <c r="K356" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L356" s="19" t="n">
-        <v>-0.09350820254241277</v>
+        <v>-0.09225223618517109</v>
       </c>
       <c r="M356" s="19" t="n">
-        <v>-0.1825636335351868</v>
+        <v>-0.1761179054444175</v>
       </c>
       <c r="N356" s="20" t="n">
         <v>0</v>
@@ -24710,12 +24710,12 @@
       </c>
       <c r="B362" s="17" t="inlineStr">
         <is>
-          <t>SAC @ EMU</t>
+          <t>MIA @ STAN</t>
         </is>
       </c>
       <c r="C362" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 22:30</t>
+          <t>2026-09-05 01:00</t>
         </is>
       </c>
       <c r="D362" s="25" t="n">
@@ -24728,29 +24728,29 @@
       </c>
       <c r="F362" s="17" t="inlineStr">
         <is>
-          <t>Under 53.5</t>
+          <t>Under 47.5</t>
         </is>
       </c>
       <c r="G362" s="26" t="n">
-        <v>53.5</v>
+        <v>47.5</v>
       </c>
       <c r="H362" s="18" t="n">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="I362" s="20" t="n">
-        <v>0.4150030126020401</v>
+        <v>0.4219391604669966</v>
       </c>
       <c r="J362" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K362" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L362" s="19" t="n">
-        <v>-0.09719210934917943</v>
+        <v>-0.09729160876377263</v>
       </c>
       <c r="M362" s="19" t="n">
-        <v>-0.1897560230150646</v>
+        <v>-0.1873764316931916</v>
       </c>
       <c r="N362" s="20" t="n">
         <v>0</v>
@@ -24773,12 +24773,12 @@
       </c>
       <c r="B363" s="12" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>WMU @ MICH</t>
         </is>
       </c>
       <c r="C363" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D363" s="22" t="n">
@@ -24791,17 +24791,17 @@
       </c>
       <c r="F363" s="12" t="inlineStr">
         <is>
-          <t>Over 61.5</t>
+          <t>Under 47.5</t>
         </is>
       </c>
       <c r="G363" s="23" t="n">
-        <v>61.5</v>
+        <v>47.5</v>
       </c>
       <c r="H363" s="13" t="n">
         <v>-105</v>
       </c>
       <c r="I363" s="15" t="n">
-        <v>0.4131722591140512</v>
+        <v>0.4131722291906123</v>
       </c>
       <c r="J363" s="15" t="n">
         <v>0.4891657638136511</v>
@@ -24810,10 +24810,10 @@
         <v>0.5121951219512195</v>
       </c>
       <c r="L363" s="14" t="n">
-        <v>-0.09902286283716832</v>
+        <v>-0.09902289276060727</v>
       </c>
       <c r="M363" s="14" t="n">
-        <v>-0.1933303512535191</v>
+        <v>-0.1933304096754713</v>
       </c>
       <c r="N363" s="15" t="n">
         <v>0</v>
@@ -24836,12 +24836,12 @@
       </c>
       <c r="B364" s="17" t="inlineStr">
         <is>
-          <t>WMU @ MICH</t>
+          <t>BC @ CIN</t>
         </is>
       </c>
       <c r="C364" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D364" s="25" t="n">
@@ -24849,34 +24849,34 @@
       </c>
       <c r="E364" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F364" s="17" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
+          <t>CIN -7.5</t>
         </is>
       </c>
       <c r="G364" s="26" t="n">
-        <v>47.5</v>
+        <v>-7.5</v>
       </c>
       <c r="H364" s="18" t="n">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="I364" s="20" t="n">
-        <v>0.4131722291906123</v>
+        <v>0.4175206855288386</v>
       </c>
       <c r="J364" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K364" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L364" s="19" t="n">
-        <v>-0.09902289276060727</v>
+        <v>-0.1017100837019307</v>
       </c>
       <c r="M364" s="19" t="n">
-        <v>-0.1933304096754713</v>
+        <v>-0.1958860871296442</v>
       </c>
       <c r="N364" s="20" t="n">
         <v>0</v>
@@ -24899,7 +24899,7 @@
       </c>
       <c r="B365" s="12" t="inlineStr">
         <is>
-          <t>BC @ CIN</t>
+          <t>BOIS @ ORE</t>
         </is>
       </c>
       <c r="C365" s="12" t="inlineStr">
@@ -24912,34 +24912,34 @@
       </c>
       <c r="E365" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F365" s="12" t="inlineStr">
         <is>
-          <t>CIN -7.5</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="G365" s="23" t="n">
-        <v>-7.5</v>
+        <v>51.5</v>
       </c>
       <c r="H365" s="13" t="n">
-        <v>-108</v>
+        <v>-102</v>
       </c>
       <c r="I365" s="15" t="n">
-        <v>0.4175206855288386</v>
+        <v>0.4026625680798983</v>
       </c>
       <c r="J365" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4826358742837298</v>
       </c>
       <c r="K365" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.504950495049505</v>
       </c>
       <c r="L365" s="14" t="n">
-        <v>-0.1017100837019307</v>
+        <v>-0.1022879269696066</v>
       </c>
       <c r="M365" s="14" t="n">
-        <v>-0.1958860871296442</v>
+        <v>-0.2025702083123582</v>
       </c>
       <c r="N365" s="15" t="n">
         <v>0</v>
@@ -24962,12 +24962,12 @@
       </c>
       <c r="B366" s="17" t="inlineStr">
         <is>
-          <t>BOIS @ ORE</t>
+          <t>UNLV @ HAW</t>
         </is>
       </c>
       <c r="C366" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-06 02:00</t>
         </is>
       </c>
       <c r="D366" s="25" t="n">
@@ -24975,37 +24975,37 @@
       </c>
       <c r="E366" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F366" s="17" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>UNLV -3</t>
         </is>
       </c>
       <c r="G366" s="26" t="n">
-        <v>51.5</v>
+        <v>3</v>
       </c>
       <c r="H366" s="18" t="n">
-        <v>-102</v>
+        <v>-112</v>
       </c>
       <c r="I366" s="20" t="n">
-        <v>0.4026625680798983</v>
+        <v>0.4247975673626849</v>
       </c>
       <c r="J366" s="20" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K366" s="20" t="n">
-        <v>0.504950495049505</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L366" s="19" t="n">
-        <v>-0.1022879269696066</v>
+        <v>-0.1035043194297679</v>
       </c>
       <c r="M366" s="19" t="n">
-        <v>-0.2025702083123582</v>
+        <v>-0.184802661991996</v>
       </c>
       <c r="N366" s="20" t="n">
-        <v>0</v>
+        <v>0.0567</v>
       </c>
       <c r="O366" s="27" t="n">
         <v>0.45</v>
@@ -25025,12 +25025,12 @@
       </c>
       <c r="B367" s="12" t="inlineStr">
         <is>
-          <t>UNLV @ HAW</t>
+          <t>TOL @ MSU</t>
         </is>
       </c>
       <c r="C367" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 02:00</t>
+          <t>2026-09-05 00:00</t>
         </is>
       </c>
       <c r="D367" s="22" t="n">
@@ -25038,22 +25038,22 @@
       </c>
       <c r="E367" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F367" s="12" t="inlineStr">
         <is>
-          <t>UNLV -3</t>
+          <t>Under 49.5</t>
         </is>
       </c>
       <c r="G367" s="23" t="n">
-        <v>3</v>
+        <v>49.5</v>
       </c>
       <c r="H367" s="13" t="n">
         <v>-112</v>
       </c>
       <c r="I367" s="15" t="n">
-        <v>0.4247975673626849</v>
+        <v>0.4244232808142943</v>
       </c>
       <c r="J367" s="15" t="n">
         <v>0.5043297540699688</v>
@@ -25062,13 +25062,13 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L367" s="14" t="n">
-        <v>-0.1035043194297679</v>
+        <v>-0.1038786059781586</v>
       </c>
       <c r="M367" s="14" t="n">
-        <v>-0.184802661991996</v>
+        <v>-0.1966273613158002</v>
       </c>
       <c r="N367" s="15" t="n">
-        <v>0.0567</v>
+        <v>0</v>
       </c>
       <c r="O367" s="24" t="n">
         <v>0.45</v>
@@ -25088,12 +25088,12 @@
       </c>
       <c r="B368" s="17" t="inlineStr">
         <is>
-          <t>TOL @ MSU</t>
+          <t>ACU @ TTU</t>
         </is>
       </c>
       <c r="C368" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 00:00</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D368" s="25" t="n">
@@ -25106,29 +25106,29 @@
       </c>
       <c r="F368" s="17" t="inlineStr">
         <is>
-          <t>Under 49.5</t>
+          <t>Over 59.5</t>
         </is>
       </c>
       <c r="G368" s="26" t="n">
-        <v>49.5</v>
+        <v>59.5</v>
       </c>
       <c r="H368" s="18" t="n">
-        <v>-112</v>
+        <v>-105</v>
       </c>
       <c r="I368" s="20" t="n">
-        <v>0.4244232808142943</v>
+        <v>0.4077266673356444</v>
       </c>
       <c r="J368" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K368" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L368" s="19" t="n">
-        <v>-0.1038786059781586</v>
+        <v>-0.1044684546155751</v>
       </c>
       <c r="M368" s="19" t="n">
-        <v>-0.1966273613158002</v>
+        <v>-0.2039622209161229</v>
       </c>
       <c r="N368" s="20" t="n">
         <v>0</v>
@@ -25141,7 +25141,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q368" s="17" t="n"/>
+      <c r="Q368" s="17" t="inlineStr">
+        <is>
+          <t>ACU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="12" t="inlineStr">
@@ -25151,12 +25155,12 @@
       </c>
       <c r="B369" s="12" t="inlineStr">
         <is>
-          <t>ACU @ TTU</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C369" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D369" s="22" t="n">
@@ -25169,29 +25173,29 @@
       </c>
       <c r="F369" s="12" t="inlineStr">
         <is>
-          <t>Over 59.5</t>
+          <t>Over 61.5</t>
         </is>
       </c>
       <c r="G369" s="23" t="n">
-        <v>59.5</v>
+        <v>61.5</v>
       </c>
       <c r="H369" s="13" t="n">
-        <v>-105</v>
+        <v>-112</v>
       </c>
       <c r="I369" s="15" t="n">
-        <v>0.4077266673356444</v>
+        <v>0.42075425424221</v>
       </c>
       <c r="J369" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K369" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L369" s="14" t="n">
-        <v>-0.1044684546155751</v>
+        <v>-0.1075476325502428</v>
       </c>
       <c r="M369" s="14" t="n">
-        <v>-0.2039622209161229</v>
+        <v>-0.2035723044701025</v>
       </c>
       <c r="N369" s="15" t="n">
         <v>0</v>
@@ -25204,11 +25208,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q369" s="12" t="inlineStr">
-        <is>
-          <t>ACU isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q369" s="12" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="17" t="inlineStr">
@@ -25795,12 +25795,12 @@
       </c>
       <c r="B379" s="12" t="inlineStr">
         <is>
-          <t>BALL @ OSU</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C379" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 16:30</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D379" s="22" t="n">
@@ -25808,34 +25808,32 @@
       </c>
       <c r="E379" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F379" s="12" t="inlineStr">
         <is>
-          <t>Over 56.5</t>
-        </is>
-      </c>
-      <c r="G379" s="23" t="n">
-        <v>56.5</v>
-      </c>
+          <t>TCU ML</t>
+        </is>
+      </c>
+      <c r="G379" s="23" t="n"/>
       <c r="H379" s="13" t="n">
-        <v>-105</v>
+        <v>-325</v>
       </c>
       <c r="I379" s="15" t="n">
-        <v>0.3884129409777476</v>
+        <v>0.6417659030150278</v>
       </c>
       <c r="J379" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.7335423197492164</v>
       </c>
       <c r="K379" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="L379" s="14" t="n">
-        <v>-0.1237821809734719</v>
+        <v>-0.1229399793379133</v>
       </c>
       <c r="M379" s="14" t="n">
-        <v>-0.2416699723767786</v>
+        <v>-0.1607676652880406</v>
       </c>
       <c r="N379" s="15" t="n">
         <v>0</v>
@@ -25858,12 +25856,12 @@
       </c>
       <c r="B380" s="17" t="inlineStr">
         <is>
-          <t>CMU @ UNM</t>
+          <t>BALL @ OSU</t>
         </is>
       </c>
       <c r="C380" s="17" t="inlineStr">
         <is>
-          <t>2026-09-06 02:00</t>
+          <t>2026-09-05 16:30</t>
         </is>
       </c>
       <c r="D380" s="25" t="n">
@@ -25876,17 +25874,17 @@
       </c>
       <c r="F380" s="17" t="inlineStr">
         <is>
-          <t>Under 46.5</t>
+          <t>Over 56.5</t>
         </is>
       </c>
       <c r="G380" s="26" t="n">
-        <v>46.5</v>
+        <v>56.5</v>
       </c>
       <c r="H380" s="18" t="n">
         <v>-105</v>
       </c>
       <c r="I380" s="20" t="n">
-        <v>0.3884128960930728</v>
+        <v>0.3884129409777476</v>
       </c>
       <c r="J380" s="20" t="n">
         <v>0.4891657638136511</v>
@@ -25895,10 +25893,10 @@
         <v>0.5121951219512195</v>
       </c>
       <c r="L380" s="19" t="n">
-        <v>-0.1237822258581467</v>
+        <v>-0.1237821809734719</v>
       </c>
       <c r="M380" s="19" t="n">
-        <v>-0.2416700600087626</v>
+        <v>-0.2416699723767786</v>
       </c>
       <c r="N380" s="20" t="n">
         <v>0</v>
@@ -25934,32 +25932,34 @@
       </c>
       <c r="E381" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F381" s="12" t="inlineStr">
         <is>
-          <t>UNM ML</t>
-        </is>
-      </c>
-      <c r="G381" s="23" t="n"/>
+          <t>Under 46.5</t>
+        </is>
+      </c>
+      <c r="G381" s="23" t="n">
+        <v>46.5</v>
+      </c>
       <c r="H381" s="13" t="n">
-        <v>-410</v>
+        <v>-105</v>
       </c>
       <c r="I381" s="15" t="n">
-        <v>0.6799056556644807</v>
+        <v>0.3884128960930728</v>
       </c>
       <c r="J381" s="15" t="n">
-        <v>0.771505376344086</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K381" s="15" t="n">
-        <v>0.803921568627451</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L381" s="14" t="n">
-        <v>-0.1240159129629703</v>
+        <v>-0.1237822258581467</v>
       </c>
       <c r="M381" s="14" t="n">
-        <v>-0.1542636966124752</v>
+        <v>-0.2416700600087626</v>
       </c>
       <c r="N381" s="15" t="n">
         <v>0</v>
@@ -25972,11 +25972,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q381" s="12" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+      <c r="Q381" s="12" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="17" t="inlineStr">
@@ -25986,12 +25982,12 @@
       </c>
       <c r="B382" s="17" t="inlineStr">
         <is>
-          <t>NIU @ IOWA</t>
+          <t>CMU @ UNM</t>
         </is>
       </c>
       <c r="C382" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 20:15</t>
+          <t>2026-09-06 02:00</t>
         </is>
       </c>
       <c r="D382" s="25" t="n">
@@ -25999,34 +25995,32 @@
       </c>
       <c r="E382" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F382" s="17" t="inlineStr">
         <is>
-          <t>Under 45.5</t>
-        </is>
-      </c>
-      <c r="G382" s="26" t="n">
-        <v>45.5</v>
-      </c>
+          <t>UNM ML</t>
+        </is>
+      </c>
+      <c r="G382" s="26" t="n"/>
       <c r="H382" s="18" t="n">
-        <v>-102</v>
+        <v>-410</v>
       </c>
       <c r="I382" s="20" t="n">
-        <v>0.3800743267773889</v>
+        <v>0.6799056556644807</v>
       </c>
       <c r="J382" s="20" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.771505376344086</v>
       </c>
       <c r="K382" s="20" t="n">
-        <v>0.504950495049505</v>
+        <v>0.803921568627451</v>
       </c>
       <c r="L382" s="19" t="n">
-        <v>-0.124876168272116</v>
+        <v>-0.1240159129629703</v>
       </c>
       <c r="M382" s="19" t="n">
-        <v>-0.2473037842251709</v>
+        <v>-0.1542636966124752</v>
       </c>
       <c r="N382" s="20" t="n">
         <v>0</v>
@@ -26039,7 +26033,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q382" s="17" t="n"/>
+      <c r="Q382" s="17" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="12" t="inlineStr">
@@ -26049,12 +26047,12 @@
       </c>
       <c r="B383" s="12" t="inlineStr">
         <is>
-          <t>FIU @ USF</t>
+          <t>NIU @ IOWA</t>
         </is>
       </c>
       <c r="C383" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-05 20:15</t>
         </is>
       </c>
       <c r="D383" s="22" t="n">
@@ -26062,32 +26060,34 @@
       </c>
       <c r="E383" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F383" s="12" t="inlineStr">
         <is>
-          <t>USF ML</t>
-        </is>
-      </c>
-      <c r="G383" s="23" t="n"/>
+          <t>Under 45.5</t>
+        </is>
+      </c>
+      <c r="G383" s="23" t="n">
+        <v>45.5</v>
+      </c>
       <c r="H383" s="13" t="n">
-        <v>-575</v>
+        <v>-102</v>
       </c>
       <c r="I383" s="15" t="n">
-        <v>0.7264731235040904</v>
+        <v>0.3800743267773889</v>
       </c>
       <c r="J383" s="15" t="n">
-        <v>0.817258883248731</v>
+        <v>0.4826358742837298</v>
       </c>
       <c r="K383" s="15" t="n">
-        <v>0.8518518518518519</v>
+        <v>0.504950495049505</v>
       </c>
       <c r="L383" s="14" t="n">
-        <v>-0.1253787283477614</v>
+        <v>-0.124876168272116</v>
       </c>
       <c r="M383" s="14" t="n">
-        <v>-0.1471837245821548</v>
+        <v>-0.2473037842251709</v>
       </c>
       <c r="N383" s="15" t="n">
         <v>0</v>
@@ -26100,11 +26100,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q383" s="12" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+      <c r="Q383" s="12" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="17" t="inlineStr">
@@ -26114,12 +26110,12 @@
       </c>
       <c r="B384" s="17" t="inlineStr">
         <is>
-          <t>COLO @ GT</t>
+          <t>FIU @ USF</t>
         </is>
       </c>
       <c r="C384" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D384" s="25" t="n">
@@ -26127,34 +26123,32 @@
       </c>
       <c r="E384" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F384" s="17" t="inlineStr">
         <is>
-          <t>Under 50.5</t>
-        </is>
-      </c>
-      <c r="G384" s="26" t="n">
-        <v>50.5</v>
-      </c>
+          <t>USF ML</t>
+        </is>
+      </c>
+      <c r="G384" s="26" t="n"/>
       <c r="H384" s="18" t="n">
-        <v>-105</v>
+        <v>-575</v>
       </c>
       <c r="I384" s="20" t="n">
-        <v>0.3867120014398708</v>
+        <v>0.7264731235040904</v>
       </c>
       <c r="J384" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.817258883248731</v>
       </c>
       <c r="K384" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="L384" s="19" t="n">
-        <v>-0.1254831205113487</v>
+        <v>-0.1253787283477614</v>
       </c>
       <c r="M384" s="19" t="n">
-        <v>-0.2449908543316808</v>
+        <v>-0.1471837245821548</v>
       </c>
       <c r="N384" s="20" t="n">
         <v>0</v>
@@ -26167,7 +26161,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q384" s="17" t="n"/>
+      <c r="Q384" s="17" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="12" t="inlineStr">
@@ -26177,12 +26175,12 @@
       </c>
       <c r="B385" s="12" t="inlineStr">
         <is>
-          <t>BAY @ AUB</t>
+          <t>COLO @ GT</t>
         </is>
       </c>
       <c r="C385" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D385" s="22" t="n">
@@ -26190,32 +26188,34 @@
       </c>
       <c r="E385" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F385" s="12" t="inlineStr">
         <is>
-          <t>AUB ML</t>
-        </is>
-      </c>
-      <c r="G385" s="23" t="n"/>
+          <t>Under 50.5</t>
+        </is>
+      </c>
+      <c r="G385" s="23" t="n">
+        <v>50.5</v>
+      </c>
       <c r="H385" s="13" t="n">
-        <v>-298</v>
+        <v>-105</v>
       </c>
       <c r="I385" s="15" t="n">
-        <v>0.6232301023185722</v>
+        <v>0.3867120014398708</v>
       </c>
       <c r="J385" s="15" t="n">
-        <v>0.7179705215419501</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K385" s="15" t="n">
-        <v>0.7487437185929648</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L385" s="14" t="n">
-        <v>-0.1255136162743926</v>
+        <v>-0.1254831205113487</v>
       </c>
       <c r="M385" s="14" t="n">
-        <v>-0.167632279453719</v>
+        <v>-0.2449908543316808</v>
       </c>
       <c r="N385" s="15" t="n">
         <v>0</v>
@@ -26238,12 +26238,12 @@
       </c>
       <c r="B386" s="17" t="inlineStr">
         <is>
-          <t>UAPB @ MIZ</t>
+          <t>BAY @ AUB</t>
         </is>
       </c>
       <c r="C386" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D386" s="25" t="n">
@@ -26251,34 +26251,32 @@
       </c>
       <c r="E386" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F386" s="17" t="inlineStr">
         <is>
-          <t>Over 60.5</t>
-        </is>
-      </c>
-      <c r="G386" s="26" t="n">
-        <v>60.5</v>
-      </c>
+          <t>AUB ML</t>
+        </is>
+      </c>
+      <c r="G386" s="26" t="n"/>
       <c r="H386" s="18" t="n">
-        <v>-108</v>
+        <v>-298</v>
       </c>
       <c r="I386" s="20" t="n">
-        <v>0.3933756418074818</v>
+        <v>0.6232301023185722</v>
       </c>
       <c r="J386" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.7179705215419501</v>
       </c>
       <c r="K386" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.7487437185929648</v>
       </c>
       <c r="L386" s="19" t="n">
-        <v>-0.1258551274232875</v>
+        <v>-0.1255136162743926</v>
       </c>
       <c r="M386" s="19" t="n">
-        <v>-0.2423876528152201</v>
+        <v>-0.167632279453719</v>
       </c>
       <c r="N386" s="20" t="n">
         <v>0</v>
@@ -26291,11 +26289,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q386" s="17" t="inlineStr">
-        <is>
-          <t>UAPB isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q386" s="17" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="12" t="inlineStr">
@@ -26305,12 +26299,12 @@
       </c>
       <c r="B387" s="12" t="inlineStr">
         <is>
-          <t>TULN @ DUKE</t>
+          <t>UAPB @ MIZ</t>
         </is>
       </c>
       <c r="C387" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D387" s="22" t="n">
@@ -26318,32 +26312,34 @@
       </c>
       <c r="E387" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F387" s="12" t="inlineStr">
         <is>
-          <t>DUKE ML</t>
-        </is>
-      </c>
-      <c r="G387" s="23" t="n"/>
+          <t>Over 60.5</t>
+        </is>
+      </c>
+      <c r="G387" s="23" t="n">
+        <v>60.5</v>
+      </c>
       <c r="H387" s="13" t="n">
-        <v>-380</v>
+        <v>-108</v>
       </c>
       <c r="I387" s="15" t="n">
-        <v>0.6645410641198675</v>
+        <v>0.3933756418074818</v>
       </c>
       <c r="J387" s="15" t="n">
-        <v>0.7600000000000001</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K387" s="15" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L387" s="14" t="n">
-        <v>-0.1271256025467992</v>
+        <v>-0.1258551274232875</v>
       </c>
       <c r="M387" s="14" t="n">
-        <v>-0.1605797084801674</v>
+        <v>-0.2423876528152201</v>
       </c>
       <c r="N387" s="15" t="n">
         <v>0</v>
@@ -26356,7 +26352,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q387" s="12" t="n"/>
+      <c r="Q387" s="12" t="inlineStr">
+        <is>
+          <t>UAPB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="17" t="inlineStr">
@@ -26366,12 +26366,12 @@
       </c>
       <c r="B388" s="17" t="inlineStr">
         <is>
-          <t>IDST @ USU</t>
+          <t>TULN @ DUKE</t>
         </is>
       </c>
       <c r="C388" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D388" s="25" t="n">
@@ -26379,34 +26379,32 @@
       </c>
       <c r="E388" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F388" s="17" t="inlineStr">
         <is>
-          <t>Over 63.5</t>
-        </is>
-      </c>
-      <c r="G388" s="26" t="n">
-        <v>63.5</v>
-      </c>
+          <t>DUKE ML</t>
+        </is>
+      </c>
+      <c r="G388" s="26" t="n"/>
       <c r="H388" s="18" t="n">
-        <v>-112</v>
+        <v>-380</v>
       </c>
       <c r="I388" s="20" t="n">
-        <v>0.4011545517646687</v>
+        <v>0.6645410641198675</v>
       </c>
       <c r="J388" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.7600000000000001</v>
       </c>
       <c r="K388" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="L388" s="19" t="n">
-        <v>-0.1271473350277841</v>
+        <v>-0.1271256025467992</v>
       </c>
       <c r="M388" s="19" t="n">
-        <v>-0.2406717413025913</v>
+        <v>-0.1605797084801674</v>
       </c>
       <c r="N388" s="20" t="n">
         <v>0</v>
@@ -26419,11 +26417,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q388" s="17" t="inlineStr">
-        <is>
-          <t>IDST isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q388" s="17" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="12" t="inlineStr">
@@ -26433,7 +26427,7 @@
       </c>
       <c r="B389" s="12" t="inlineStr">
         <is>
-          <t>CHSO @ GASO</t>
+          <t>IDST @ USU</t>
         </is>
       </c>
       <c r="C389" s="12" t="inlineStr">
@@ -26451,17 +26445,17 @@
       </c>
       <c r="F389" s="12" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>Over 63.5</t>
         </is>
       </c>
       <c r="G389" s="23" t="n">
-        <v>51.5</v>
+        <v>63.5</v>
       </c>
       <c r="H389" s="13" t="n">
         <v>-112</v>
       </c>
       <c r="I389" s="15" t="n">
-        <v>0.4011545497069526</v>
+        <v>0.4011545517646687</v>
       </c>
       <c r="J389" s="15" t="n">
         <v>0.5043297540699688</v>
@@ -26470,10 +26464,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L389" s="14" t="n">
-        <v>-0.1271473370855002</v>
+        <v>-0.1271473350277841</v>
       </c>
       <c r="M389" s="14" t="n">
-        <v>-0.240671745197554</v>
+        <v>-0.2406717413025913</v>
       </c>
       <c r="N389" s="15" t="n">
         <v>0</v>
@@ -26488,7 +26482,7 @@
       </c>
       <c r="Q389" s="12" t="inlineStr">
         <is>
-          <t>CHSO isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>IDST isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -26500,12 +26494,12 @@
       </c>
       <c r="B390" s="17" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>CHSO @ GASO</t>
         </is>
       </c>
       <c r="C390" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D390" s="25" t="n">
@@ -26513,32 +26507,34 @@
       </c>
       <c r="E390" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F390" s="17" t="inlineStr">
         <is>
-          <t>TCU ML</t>
-        </is>
-      </c>
-      <c r="G390" s="26" t="n"/>
+          <t>Under 51.5</t>
+        </is>
+      </c>
+      <c r="G390" s="26" t="n">
+        <v>51.5</v>
+      </c>
       <c r="H390" s="18" t="n">
-        <v>-340</v>
+        <v>-112</v>
       </c>
       <c r="I390" s="20" t="n">
-        <v>0.6454305499719861</v>
+        <v>0.4011545497069526</v>
       </c>
       <c r="J390" s="20" t="n">
-        <v>0.740871613663133</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K390" s="20" t="n">
-        <v>0.7727272727272727</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L390" s="19" t="n">
-        <v>-0.1272967227552866</v>
+        <v>-0.1271473370855002</v>
       </c>
       <c r="M390" s="19" t="n">
-        <v>-0.1647369353303709</v>
+        <v>-0.240671745197554</v>
       </c>
       <c r="N390" s="20" t="n">
         <v>0</v>
@@ -26551,7 +26547,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q390" s="17" t="n"/>
+      <c r="Q390" s="17" t="inlineStr">
+        <is>
+          <t>CHSO isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="12" t="inlineStr">
@@ -26817,12 +26817,12 @@
       </c>
       <c r="B395" s="12" t="inlineStr">
         <is>
-          <t>NCAT @ GAST</t>
+          <t>UNC @ TCU</t>
         </is>
       </c>
       <c r="C395" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 23:00</t>
+          <t>2026-08-29 16:00</t>
         </is>
       </c>
       <c r="D395" s="22" t="n">
@@ -26830,34 +26830,34 @@
       </c>
       <c r="E395" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F395" s="12" t="inlineStr">
         <is>
-          <t>Over 63.5</t>
+          <t>TCU -8.5</t>
         </is>
       </c>
       <c r="G395" s="23" t="n">
-        <v>63.5</v>
+        <v>-8.5</v>
       </c>
       <c r="H395" s="13" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="I395" s="15" t="n">
-        <v>0.3904378805908039</v>
+        <v>0.3809829946710013</v>
       </c>
       <c r="J395" s="15" t="n">
-        <v>0.5</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K395" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L395" s="14" t="n">
-        <v>-0.13337164321872</v>
+        <v>-0.1312121272802182</v>
       </c>
       <c r="M395" s="14" t="n">
-        <v>-0.2546185915993744</v>
+        <v>-0.2561760580232832</v>
       </c>
       <c r="N395" s="15" t="n">
         <v>0</v>
@@ -26870,11 +26870,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q395" s="12" t="inlineStr">
-        <is>
-          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q395" s="12" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="17" t="inlineStr">
@@ -26884,12 +26880,12 @@
       </c>
       <c r="B396" s="17" t="inlineStr">
         <is>
-          <t>BC @ CIN</t>
+          <t>NCAT @ GAST</t>
         </is>
       </c>
       <c r="C396" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-04 23:00</t>
         </is>
       </c>
       <c r="D396" s="25" t="n">
@@ -26902,29 +26898,29 @@
       </c>
       <c r="F396" s="17" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>Over 63.5</t>
         </is>
       </c>
       <c r="G396" s="26" t="n">
-        <v>51.5</v>
+        <v>63.5</v>
       </c>
       <c r="H396" s="18" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I396" s="20" t="n">
-        <v>0.3942939976898748</v>
+        <v>0.3904378805908039</v>
       </c>
       <c r="J396" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K396" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L396" s="19" t="n">
-        <v>-0.134007889102578</v>
+        <v>-0.13337164321872</v>
       </c>
       <c r="M396" s="19" t="n">
-        <v>-0.2536577900870227</v>
+        <v>-0.2546185915993744</v>
       </c>
       <c r="N396" s="20" t="n">
         <v>0</v>
@@ -26937,7 +26933,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q396" s="17" t="n"/>
+      <c r="Q396" s="17" t="inlineStr">
+        <is>
+          <t>NCAT isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="12" t="inlineStr">
@@ -26947,7 +26947,7 @@
       </c>
       <c r="B397" s="12" t="inlineStr">
         <is>
-          <t>FUR @ TENN</t>
+          <t>BC @ CIN</t>
         </is>
       </c>
       <c r="C397" s="12" t="inlineStr">
@@ -26965,29 +26965,29 @@
       </c>
       <c r="F397" s="12" t="inlineStr">
         <is>
-          <t>Over 66.5</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="G397" s="23" t="n">
-        <v>66.5</v>
+        <v>51.5</v>
       </c>
       <c r="H397" s="13" t="n">
-        <v>-105</v>
+        <v>-112</v>
       </c>
       <c r="I397" s="15" t="n">
-        <v>0.3767135592080921</v>
+        <v>0.3942939976898748</v>
       </c>
       <c r="J397" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K397" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L397" s="14" t="n">
-        <v>-0.1354815627431274</v>
+        <v>-0.134007889102578</v>
       </c>
       <c r="M397" s="14" t="n">
-        <v>-0.2645116224984869</v>
+        <v>-0.2536577900870227</v>
       </c>
       <c r="N397" s="15" t="n">
         <v>0</v>
@@ -27000,11 +27000,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q397" s="12" t="inlineStr">
-        <is>
-          <t>FUR isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q397" s="12" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="17" t="inlineStr">
@@ -27014,12 +27010,12 @@
       </c>
       <c r="B398" s="17" t="inlineStr">
         <is>
-          <t>HAW @ STAN</t>
+          <t>FUR @ TENN</t>
         </is>
       </c>
       <c r="C398" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D398" s="25" t="n">
@@ -27032,17 +27028,17 @@
       </c>
       <c r="F398" s="17" t="inlineStr">
         <is>
-          <t>Under 48.5</t>
+          <t>Over 66.5</t>
         </is>
       </c>
       <c r="G398" s="26" t="n">
-        <v>48.5</v>
+        <v>66.5</v>
       </c>
       <c r="H398" s="18" t="n">
         <v>-105</v>
       </c>
       <c r="I398" s="20" t="n">
-        <v>0.3767135533122641</v>
+        <v>0.3767135592080921</v>
       </c>
       <c r="J398" s="20" t="n">
         <v>0.4891657638136511</v>
@@ -27051,10 +27047,10 @@
         <v>0.5121951219512195</v>
       </c>
       <c r="L398" s="19" t="n">
-        <v>-0.1354815686389554</v>
+        <v>-0.1354815627431274</v>
       </c>
       <c r="M398" s="19" t="n">
-        <v>-0.2645116340093892</v>
+        <v>-0.2645116224984869</v>
       </c>
       <c r="N398" s="20" t="n">
         <v>0</v>
@@ -27067,7 +27063,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q398" s="17" t="n"/>
+      <c r="Q398" s="17" t="inlineStr">
+        <is>
+          <t>FUR isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="12" t="inlineStr">
@@ -27077,12 +27077,12 @@
       </c>
       <c r="B399" s="12" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>HAW @ STAN</t>
         </is>
       </c>
       <c r="C399" s="12" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00</t>
+          <t>2026-08-29 23:00</t>
         </is>
       </c>
       <c r="D399" s="22" t="n">
@@ -27090,34 +27090,34 @@
       </c>
       <c r="E399" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F399" s="12" t="inlineStr">
         <is>
-          <t>TCU -8.5</t>
+          <t>Under 48.5</t>
         </is>
       </c>
       <c r="G399" s="23" t="n">
-        <v>-8.5</v>
+        <v>48.5</v>
       </c>
       <c r="H399" s="13" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="I399" s="15" t="n">
-        <v>0.3864001127641757</v>
+        <v>0.3767135533122641</v>
       </c>
       <c r="J399" s="15" t="n">
-        <v>0.5</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K399" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L399" s="14" t="n">
-        <v>-0.1374094110453481</v>
+        <v>-0.1354815686389554</v>
       </c>
       <c r="M399" s="14" t="n">
-        <v>-0.2623270574502099</v>
+        <v>-0.2645116340093892</v>
       </c>
       <c r="N399" s="15" t="n">
         <v>0</v>
@@ -27995,29 +27995,29 @@
       </c>
       <c r="F413" s="12" t="inlineStr">
         <is>
-          <t>EMU -9.5</t>
+          <t>EMU -8.5</t>
         </is>
       </c>
       <c r="G413" s="23" t="n">
-        <v>-9.5</v>
+        <v>-8.5</v>
       </c>
       <c r="H413" s="13" t="n">
-        <v>-105</v>
+        <v>-112</v>
       </c>
       <c r="I413" s="15" t="n">
-        <v>0.3572786729962037</v>
+        <v>0.3742878774033126</v>
       </c>
       <c r="J413" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K413" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L413" s="14" t="n">
-        <v>-0.1549164489550158</v>
+        <v>-0.1540140093891402</v>
       </c>
       <c r="M413" s="14" t="n">
-        <v>-0.3024559241502689</v>
+        <v>-0.2915265177723012</v>
       </c>
       <c r="N413" s="15" t="n">
         <v>0</v>
@@ -28030,11 +28030,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q413" s="12" t="inlineStr">
-        <is>
-          <t>model and market are too far apart for a reliable early-season play</t>
-        </is>
-      </c>
+      <c r="Q413" s="12" t="n"/>
     </row>
     <row r="414">
       <c r="A414" s="17" t="inlineStr">
@@ -31383,12 +31379,12 @@
       </c>
       <c r="B465" s="12" t="inlineStr">
         <is>
-          <t>CHSO @ GASO</t>
+          <t>MIA @ STAN</t>
         </is>
       </c>
       <c r="C465" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-05 01:00</t>
         </is>
       </c>
       <c r="D465" s="22" t="n">
@@ -31401,27 +31397,27 @@
       </c>
       <c r="F465" s="12" t="inlineStr">
         <is>
-          <t>GASO ML</t>
+          <t>MIA ML</t>
         </is>
       </c>
       <c r="G465" s="23" t="n"/>
       <c r="H465" s="13" t="n">
-        <v>-4500</v>
+        <v>-2800</v>
       </c>
       <c r="I465" s="15" t="n">
-        <v>0.7588071444290467</v>
+        <v>0.7461177133412662</v>
       </c>
       <c r="J465" s="15" t="n">
-        <v>0.9462616822429908</v>
+        <v>0.9311163895486935</v>
       </c>
       <c r="K465" s="15" t="n">
-        <v>0.9782608695652174</v>
+        <v>0.9655172413793104</v>
       </c>
       <c r="L465" s="14" t="n">
-        <v>-0.2194537251361707</v>
+        <v>-0.2193995280380442</v>
       </c>
       <c r="M465" s="14" t="n">
-        <v>-0.2243304745836412</v>
+        <v>-0.2272352254679742</v>
       </c>
       <c r="N465" s="15" t="n">
         <v>0</v>
@@ -31436,7 +31432,7 @@
       </c>
       <c r="Q465" s="12" t="inlineStr">
         <is>
-          <t>CHSO isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>price outside allowed range</t>
         </is>
       </c>
     </row>
@@ -31448,12 +31444,12 @@
       </c>
       <c r="B466" s="17" t="inlineStr">
         <is>
-          <t>LAF @ CONN</t>
+          <t>CHSO @ GASO</t>
         </is>
       </c>
       <c r="C466" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D466" s="25" t="n">
@@ -31461,34 +31457,32 @@
       </c>
       <c r="E466" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F466" s="17" t="inlineStr">
         <is>
-          <t>CONN -19.5</t>
-        </is>
-      </c>
-      <c r="G466" s="26" t="n">
-        <v>-19.5</v>
-      </c>
+          <t>GASO ML</t>
+        </is>
+      </c>
+      <c r="G466" s="26" t="n"/>
       <c r="H466" s="18" t="n">
-        <v>-105</v>
+        <v>-4500</v>
       </c>
       <c r="I466" s="20" t="n">
-        <v>0.2915778949562172</v>
+        <v>0.7588071444290467</v>
       </c>
       <c r="J466" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.9462616822429908</v>
       </c>
       <c r="K466" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.9782608695652174</v>
       </c>
       <c r="L466" s="19" t="n">
-        <v>-0.2206172269950023</v>
+        <v>-0.2194537251361707</v>
       </c>
       <c r="M466" s="19" t="n">
-        <v>-0.4307288717521474</v>
+        <v>-0.2243304745836412</v>
       </c>
       <c r="N466" s="20" t="n">
         <v>0</v>
@@ -31503,7 +31497,7 @@
       </c>
       <c r="Q466" s="17" t="inlineStr">
         <is>
-          <t>LAF isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>CHSO isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -31515,12 +31509,12 @@
       </c>
       <c r="B467" s="12" t="inlineStr">
         <is>
-          <t>TXST @ TEX</t>
+          <t>LAF @ CONN</t>
         </is>
       </c>
       <c r="C467" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D467" s="22" t="n">
@@ -31528,32 +31522,34 @@
       </c>
       <c r="E467" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F467" s="12" t="inlineStr">
         <is>
-          <t>TEX ML</t>
-        </is>
-      </c>
-      <c r="G467" s="23" t="n"/>
+          <t>CONN -19.5</t>
+        </is>
+      </c>
+      <c r="G467" s="23" t="n">
+        <v>-19.5</v>
+      </c>
       <c r="H467" s="13" t="n">
-        <v>-10000</v>
+        <v>-105</v>
       </c>
       <c r="I467" s="15" t="n">
-        <v>0.7669177110759291</v>
+        <v>0.2915778949562172</v>
       </c>
       <c r="J467" s="15" t="n">
-        <v>0.9684473601999376</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K467" s="15" t="n">
-        <v>0.9900990099009901</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L467" s="14" t="n">
-        <v>-0.223181298825061</v>
+        <v>-0.2206172269950023</v>
       </c>
       <c r="M467" s="14" t="n">
-        <v>-0.2254131118133116</v>
+        <v>-0.4307288717521474</v>
       </c>
       <c r="N467" s="15" t="n">
         <v>0</v>
@@ -31568,7 +31564,7 @@
       </c>
       <c r="Q467" s="12" t="inlineStr">
         <is>
-          <t>price outside allowed range</t>
+          <t>LAF isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -31580,12 +31576,12 @@
       </c>
       <c r="B468" s="17" t="inlineStr">
         <is>
-          <t>MIA @ STAN</t>
+          <t>TXST @ TEX</t>
         </is>
       </c>
       <c r="C468" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 01:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D468" s="25" t="n">
@@ -31598,27 +31594,27 @@
       </c>
       <c r="F468" s="17" t="inlineStr">
         <is>
-          <t>MIA ML</t>
+          <t>TEX ML</t>
         </is>
       </c>
       <c r="G468" s="26" t="n"/>
       <c r="H468" s="18" t="n">
-        <v>-4000</v>
+        <v>-10000</v>
       </c>
       <c r="I468" s="20" t="n">
-        <v>0.752126786250692</v>
+        <v>0.7669177110759291</v>
       </c>
       <c r="J468" s="20" t="n">
-        <v>0.9431345353675451</v>
+        <v>0.9684473601999376</v>
       </c>
       <c r="K468" s="20" t="n">
-        <v>0.975609756097561</v>
+        <v>0.9900990099009901</v>
       </c>
       <c r="L468" s="19" t="n">
-        <v>-0.223482969846869</v>
+        <v>-0.223181298825061</v>
       </c>
       <c r="M468" s="19" t="n">
-        <v>-0.2290700440930408</v>
+        <v>-0.2254131118133116</v>
       </c>
       <c r="N468" s="20" t="n">
         <v>0</v>
@@ -33300,12 +33296,12 @@
       </c>
       <c r="B494" s="17" t="inlineStr">
         <is>
-          <t>MIA @ STAN</t>
+          <t>HCU @ RICE</t>
         </is>
       </c>
       <c r="C494" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 01:00</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D494" s="25" t="n">
@@ -33318,29 +33314,29 @@
       </c>
       <c r="F494" s="17" t="inlineStr">
         <is>
-          <t>MIA -24.5</t>
+          <t>RICE -24.5</t>
         </is>
       </c>
       <c r="G494" s="26" t="n">
-        <v>24.5</v>
+        <v>-24.5</v>
       </c>
       <c r="H494" s="18" t="n">
-        <v>-105</v>
+        <v>-102</v>
       </c>
       <c r="I494" s="20" t="n">
-        <v>0.2624039377265616</v>
+        <v>0.2549320248754756</v>
       </c>
       <c r="J494" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.4826358742837298</v>
       </c>
       <c r="K494" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.504950495049505</v>
       </c>
       <c r="L494" s="19" t="n">
-        <v>-0.249791184224658</v>
+        <v>-0.2500184701740294</v>
       </c>
       <c r="M494" s="19" t="n">
-        <v>-0.4876875501529037</v>
+        <v>-0.4951346174034699</v>
       </c>
       <c r="N494" s="20" t="n">
         <v>0</v>
@@ -33355,7 +33351,7 @@
       </c>
       <c r="Q494" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>HCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -33367,12 +33363,12 @@
       </c>
       <c r="B495" s="12" t="inlineStr">
         <is>
-          <t>HCU @ RICE</t>
+          <t>MRSH @ PSU</t>
         </is>
       </c>
       <c r="C495" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D495" s="22" t="n">
@@ -33385,29 +33381,29 @@
       </c>
       <c r="F495" s="12" t="inlineStr">
         <is>
-          <t>RICE -24.5</t>
+          <t>PSU -24.5</t>
         </is>
       </c>
       <c r="G495" s="23" t="n">
         <v>-24.5</v>
       </c>
       <c r="H495" s="13" t="n">
-        <v>-102</v>
+        <v>-110</v>
       </c>
       <c r="I495" s="15" t="n">
-        <v>0.2549320248754756</v>
+        <v>0.2729530839681064</v>
       </c>
       <c r="J495" s="15" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.5</v>
       </c>
       <c r="K495" s="15" t="n">
-        <v>0.504950495049505</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L495" s="14" t="n">
-        <v>-0.2500184701740294</v>
+        <v>-0.2508564398414174</v>
       </c>
       <c r="M495" s="14" t="n">
-        <v>-0.4951346174034699</v>
+        <v>-0.4789077487881604</v>
       </c>
       <c r="N495" s="15" t="n">
         <v>0</v>
@@ -33422,7 +33418,7 @@
       </c>
       <c r="Q495" s="12" t="inlineStr">
         <is>
-          <t>HCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -33434,12 +33430,12 @@
       </c>
       <c r="B496" s="17" t="inlineStr">
         <is>
-          <t>MRSH @ PSU</t>
+          <t>WSU @ WASH</t>
         </is>
       </c>
       <c r="C496" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-06 20:00</t>
         </is>
       </c>
       <c r="D496" s="25" t="n">
@@ -33452,29 +33448,29 @@
       </c>
       <c r="F496" s="17" t="inlineStr">
         <is>
-          <t>PSU -24.5</t>
+          <t>WASH -23.5</t>
         </is>
       </c>
       <c r="G496" s="26" t="n">
-        <v>-24.5</v>
+        <v>-23.5</v>
       </c>
       <c r="H496" s="18" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="I496" s="20" t="n">
-        <v>0.2729530839681064</v>
+        <v>0.2769993033724504</v>
       </c>
       <c r="J496" s="20" t="n">
-        <v>0.5</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K496" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L496" s="19" t="n">
-        <v>-0.2508564398414174</v>
+        <v>-0.2513025834200024</v>
       </c>
       <c r="M496" s="19" t="n">
-        <v>-0.4789077487881604</v>
+        <v>-0.4756798900450047</v>
       </c>
       <c r="N496" s="20" t="n">
         <v>0</v>
@@ -33501,12 +33497,12 @@
       </c>
       <c r="B497" s="12" t="inlineStr">
         <is>
-          <t>WSU @ WASH</t>
+          <t>ALB @ BUFF</t>
         </is>
       </c>
       <c r="C497" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 20:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D497" s="22" t="n">
@@ -33519,29 +33515,29 @@
       </c>
       <c r="F497" s="12" t="inlineStr">
         <is>
-          <t>WASH -23.5</t>
+          <t>BUFF -24.5</t>
         </is>
       </c>
       <c r="G497" s="23" t="n">
-        <v>-23.5</v>
+        <v>-24.5</v>
       </c>
       <c r="H497" s="13" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="I497" s="15" t="n">
-        <v>0.2769993033724504</v>
+        <v>0.2657449776111079</v>
       </c>
       <c r="J497" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K497" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L497" s="14" t="n">
-        <v>-0.2513025834200024</v>
+        <v>-0.2534857916196613</v>
       </c>
       <c r="M497" s="14" t="n">
-        <v>-0.4756798900450047</v>
+        <v>-0.4881948579341625</v>
       </c>
       <c r="N497" s="15" t="n">
         <v>0</v>
@@ -33556,7 +33552,7 @@
       </c>
       <c r="Q497" s="12" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -33568,12 +33564,12 @@
       </c>
       <c r="B498" s="17" t="inlineStr">
         <is>
-          <t>ALB @ BUFF</t>
+          <t>UNH @ SYR</t>
         </is>
       </c>
       <c r="C498" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D498" s="25" t="n">
@@ -33581,34 +33577,32 @@
       </c>
       <c r="E498" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F498" s="17" t="inlineStr">
         <is>
-          <t>BUFF -24.5</t>
-        </is>
-      </c>
-      <c r="G498" s="26" t="n">
-        <v>-24.5</v>
-      </c>
+          <t>SYR ML</t>
+        </is>
+      </c>
+      <c r="G498" s="26" t="n"/>
       <c r="H498" s="18" t="n">
-        <v>-108</v>
+        <v>-100000</v>
       </c>
       <c r="I498" s="20" t="n">
-        <v>0.2657449776111079</v>
+        <v>0.7452707950740558</v>
       </c>
       <c r="J498" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.9807503701851887</v>
       </c>
       <c r="K498" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.999000999000999</v>
       </c>
       <c r="L498" s="19" t="n">
-        <v>-0.2534857916196613</v>
+        <v>-0.2537302039269432</v>
       </c>
       <c r="M498" s="19" t="n">
-        <v>-0.4881948579341625</v>
+        <v>-0.2539839341308702</v>
       </c>
       <c r="N498" s="20" t="n">
         <v>0</v>
@@ -33623,7 +33617,7 @@
       </c>
       <c r="Q498" s="17" t="inlineStr">
         <is>
-          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>UNH isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -33635,12 +33629,12 @@
       </c>
       <c r="B499" s="12" t="inlineStr">
         <is>
-          <t>UNH @ SYR</t>
+          <t>MIA @ STAN</t>
         </is>
       </c>
       <c r="C499" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-09-05 01:00</t>
         </is>
       </c>
       <c r="D499" s="22" t="n">
@@ -33648,32 +33642,34 @@
       </c>
       <c r="E499" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F499" s="12" t="inlineStr">
         <is>
-          <t>SYR ML</t>
-        </is>
-      </c>
-      <c r="G499" s="23" t="n"/>
+          <t>MIA -23.5</t>
+        </is>
+      </c>
+      <c r="G499" s="23" t="n">
+        <v>23.5</v>
+      </c>
       <c r="H499" s="13" t="n">
-        <v>-100000</v>
+        <v>-112</v>
       </c>
       <c r="I499" s="15" t="n">
-        <v>0.7452707950740558</v>
+        <v>0.2736105343936924</v>
       </c>
       <c r="J499" s="15" t="n">
-        <v>0.9807503701851887</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K499" s="15" t="n">
-        <v>0.999000999000999</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L499" s="14" t="n">
-        <v>-0.2537302039269432</v>
+        <v>-0.2546913523987604</v>
       </c>
       <c r="M499" s="14" t="n">
-        <v>-0.2539839341308702</v>
+        <v>-0.4820943456119393</v>
       </c>
       <c r="N499" s="15" t="n">
         <v>0</v>
@@ -33688,7 +33684,7 @@
       </c>
       <c r="Q499" s="12" t="inlineStr">
         <is>
-          <t>UNH isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -35306,12 +35302,12 @@
       </c>
       <c r="B524" s="17" t="inlineStr">
         <is>
-          <t>SJSU @ USC</t>
+          <t>BRY @ ARMY</t>
         </is>
       </c>
       <c r="C524" s="17" t="inlineStr">
         <is>
-          <t>2026-08-29 19:00</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D524" s="25" t="n">
@@ -35324,17 +35320,17 @@
       </c>
       <c r="F524" s="17" t="inlineStr">
         <is>
-          <t>USC -38.5</t>
+          <t>ARMY -36.5</t>
         </is>
       </c>
       <c r="G524" s="26" t="n">
-        <v>-38.5</v>
+        <v>-36.5</v>
       </c>
       <c r="H524" s="18" t="n">
         <v>-108</v>
       </c>
       <c r="I524" s="20" t="n">
-        <v>0.2501562069162203</v>
+        <v>0.2500678397522949</v>
       </c>
       <c r="J524" s="20" t="n">
         <v>0.4956702459300312</v>
@@ -35343,10 +35339,10 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L524" s="19" t="n">
-        <v>-0.269074562314549</v>
+        <v>-0.2691629294784744</v>
       </c>
       <c r="M524" s="19" t="n">
-        <v>-0.518217675568761</v>
+        <v>-0.5183878641807653</v>
       </c>
       <c r="N524" s="20" t="n">
         <v>0</v>
@@ -35361,7 +35357,7 @@
       </c>
       <c r="Q524" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>BRY isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -35373,12 +35369,12 @@
       </c>
       <c r="B525" s="12" t="inlineStr">
         <is>
-          <t>BRY @ ARMY</t>
+          <t>KENT @ SC</t>
         </is>
       </c>
       <c r="C525" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-09-05 16:45</t>
         </is>
       </c>
       <c r="D525" s="22" t="n">
@@ -35391,7 +35387,7 @@
       </c>
       <c r="F525" s="12" t="inlineStr">
         <is>
-          <t>ARMY -36.5</t>
+          <t>SC -36.5</t>
         </is>
       </c>
       <c r="G525" s="23" t="n">
@@ -35401,7 +35397,7 @@
         <v>-108</v>
       </c>
       <c r="I525" s="15" t="n">
-        <v>0.2500678397522949</v>
+        <v>0.2499368613568438</v>
       </c>
       <c r="J525" s="15" t="n">
         <v>0.4956702459300312</v>
@@ -35410,10 +35406,10 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L525" s="14" t="n">
-        <v>-0.2691629294784744</v>
+        <v>-0.2692939078739255</v>
       </c>
       <c r="M525" s="14" t="n">
-        <v>-0.5183878641807653</v>
+        <v>-0.5186401188683007</v>
       </c>
       <c r="N525" s="15" t="n">
         <v>0</v>
@@ -35428,7 +35424,7 @@
       </c>
       <c r="Q525" s="12" t="inlineStr">
         <is>
-          <t>BRY isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -35440,12 +35436,12 @@
       </c>
       <c r="B526" s="17" t="inlineStr">
         <is>
-          <t>KENT @ SC</t>
+          <t>WMU @ MICH</t>
         </is>
       </c>
       <c r="C526" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 16:45</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D526" s="25" t="n">
@@ -35458,29 +35454,29 @@
       </c>
       <c r="F526" s="17" t="inlineStr">
         <is>
-          <t>SC -36.5</t>
+          <t>MICH -27.5</t>
         </is>
       </c>
       <c r="G526" s="26" t="n">
-        <v>-36.5</v>
+        <v>-27.5</v>
       </c>
       <c r="H526" s="18" t="n">
-        <v>-108</v>
+        <v>-115</v>
       </c>
       <c r="I526" s="20" t="n">
-        <v>0.2499368613568438</v>
+        <v>0.2654934830558677</v>
       </c>
       <c r="J526" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K526" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L526" s="19" t="n">
-        <v>-0.2692939078739255</v>
+        <v>-0.2693902378743648</v>
       </c>
       <c r="M526" s="19" t="n">
-        <v>-0.5186401188683007</v>
+        <v>-0.5036426186346822</v>
       </c>
       <c r="N526" s="20" t="n">
         <v>0</v>
@@ -35507,12 +35503,12 @@
       </c>
       <c r="B527" s="12" t="inlineStr">
         <is>
-          <t>WMU @ MICH</t>
+          <t>IDHO @ UTAH</t>
         </is>
       </c>
       <c r="C527" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D527" s="22" t="n">
@@ -35525,29 +35521,29 @@
       </c>
       <c r="F527" s="12" t="inlineStr">
         <is>
-          <t>MICH -27.5</t>
+          <t>UTAH -33.5</t>
         </is>
       </c>
       <c r="G527" s="23" t="n">
-        <v>-27.5</v>
+        <v>-33.5</v>
       </c>
       <c r="H527" s="13" t="n">
-        <v>-115</v>
+        <v>-112</v>
       </c>
       <c r="I527" s="15" t="n">
-        <v>0.2654934830558677</v>
+        <v>0.2585208472473556</v>
       </c>
       <c r="J527" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K527" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L527" s="14" t="n">
-        <v>-0.2693902378743648</v>
+        <v>-0.2697810395450972</v>
       </c>
       <c r="M527" s="14" t="n">
-        <v>-0.5036426186346822</v>
+        <v>-0.5106569677103627</v>
       </c>
       <c r="N527" s="15" t="n">
         <v>0</v>
@@ -35562,7 +35558,7 @@
       </c>
       <c r="Q527" s="12" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -35574,12 +35570,12 @@
       </c>
       <c r="B528" s="17" t="inlineStr">
         <is>
-          <t>IDHO @ UTAH</t>
+          <t>UNA @ ARK</t>
         </is>
       </c>
       <c r="C528" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 01:00</t>
+          <t>2026-09-05 20:15</t>
         </is>
       </c>
       <c r="D528" s="25" t="n">
@@ -35592,29 +35588,29 @@
       </c>
       <c r="F528" s="17" t="inlineStr">
         <is>
-          <t>UTAH -33.5</t>
+          <t>ARK -40.5</t>
         </is>
       </c>
       <c r="G528" s="26" t="n">
-        <v>-33.5</v>
+        <v>-40.5</v>
       </c>
       <c r="H528" s="18" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="I528" s="20" t="n">
-        <v>0.2585208472473556</v>
+        <v>0.2485003206460911</v>
       </c>
       <c r="J528" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K528" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L528" s="19" t="n">
-        <v>-0.2697810395450972</v>
+        <v>-0.2707304485846782</v>
       </c>
       <c r="M528" s="19" t="n">
-        <v>-0.5106569677103627</v>
+        <v>-0.5214067898667876</v>
       </c>
       <c r="N528" s="20" t="n">
         <v>0</v>
@@ -35629,7 +35625,7 @@
       </c>
       <c r="Q528" s="17" t="inlineStr">
         <is>
-          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>UNA isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -35641,12 +35637,12 @@
       </c>
       <c r="B529" s="12" t="inlineStr">
         <is>
-          <t>UNA @ ARK</t>
+          <t>INST @ PUR</t>
         </is>
       </c>
       <c r="C529" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 20:15</t>
+          <t>2026-09-04 23:00</t>
         </is>
       </c>
       <c r="D529" s="22" t="n">
@@ -35659,29 +35655,29 @@
       </c>
       <c r="F529" s="12" t="inlineStr">
         <is>
-          <t>ARK -40.5</t>
+          <t>PUR -35.5</t>
         </is>
       </c>
       <c r="G529" s="23" t="n">
-        <v>-40.5</v>
+        <v>-35.5</v>
       </c>
       <c r="H529" s="13" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I529" s="15" t="n">
-        <v>0.2485003206460911</v>
+        <v>0.2528934298318226</v>
       </c>
       <c r="J529" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5021949078138718</v>
       </c>
       <c r="K529" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L529" s="14" t="n">
-        <v>-0.2707304485846782</v>
+        <v>-0.2709160939777012</v>
       </c>
       <c r="M529" s="14" t="n">
-        <v>-0.5214067898667876</v>
+        <v>-0.5172034521392477</v>
       </c>
       <c r="N529" s="15" t="n">
         <v>0</v>
@@ -35696,7 +35692,7 @@
       </c>
       <c r="Q529" s="12" t="inlineStr">
         <is>
-          <t>UNA isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>INST isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -35708,12 +35704,12 @@
       </c>
       <c r="B530" s="17" t="inlineStr">
         <is>
-          <t>INST @ PUR</t>
+          <t>EIU @ MINN</t>
         </is>
       </c>
       <c r="C530" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 23:00</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D530" s="25" t="n">
@@ -35726,29 +35722,29 @@
       </c>
       <c r="F530" s="17" t="inlineStr">
         <is>
-          <t>PUR -35.5</t>
+          <t>MINN -43.5</t>
         </is>
       </c>
       <c r="G530" s="26" t="n">
-        <v>-35.5</v>
+        <v>-43.5</v>
       </c>
       <c r="H530" s="18" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I530" s="20" t="n">
-        <v>0.2528934298318226</v>
+        <v>0.2481768262232006</v>
       </c>
       <c r="J530" s="20" t="n">
-        <v>0.5021949078138718</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K530" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L530" s="19" t="n">
-        <v>-0.2709160939777012</v>
+        <v>-0.2710539430075687</v>
       </c>
       <c r="M530" s="19" t="n">
-        <v>-0.5172034521392477</v>
+        <v>-0.5220298161627247</v>
       </c>
       <c r="N530" s="20" t="n">
         <v>0</v>
@@ -35763,7 +35759,7 @@
       </c>
       <c r="Q530" s="17" t="inlineStr">
         <is>
-          <t>INST isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -35775,12 +35771,12 @@
       </c>
       <c r="B531" s="12" t="inlineStr">
         <is>
-          <t>EIU @ MINN</t>
+          <t>BALL @ OSU</t>
         </is>
       </c>
       <c r="C531" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-09-05 16:30</t>
         </is>
       </c>
       <c r="D531" s="22" t="n">
@@ -35793,17 +35789,17 @@
       </c>
       <c r="F531" s="12" t="inlineStr">
         <is>
-          <t>MINN -43.5</t>
+          <t>OSU -50.5</t>
         </is>
       </c>
       <c r="G531" s="23" t="n">
-        <v>-43.5</v>
+        <v>-50.5</v>
       </c>
       <c r="H531" s="13" t="n">
         <v>-108</v>
       </c>
       <c r="I531" s="15" t="n">
-        <v>0.2481768262232006</v>
+        <v>0.2480345857275048</v>
       </c>
       <c r="J531" s="15" t="n">
         <v>0.4956702459300312</v>
@@ -35812,10 +35808,10 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L531" s="14" t="n">
-        <v>-0.2710539430075687</v>
+        <v>-0.2711961835032645</v>
       </c>
       <c r="M531" s="14" t="n">
-        <v>-0.5220298161627247</v>
+        <v>-0.5223037608211019</v>
       </c>
       <c r="N531" s="15" t="n">
         <v>0</v>
@@ -35830,7 +35826,7 @@
       </c>
       <c r="Q531" s="12" t="inlineStr">
         <is>
-          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -35842,12 +35838,12 @@
       </c>
       <c r="B532" s="17" t="inlineStr">
         <is>
-          <t>BALL @ OSU</t>
+          <t>HAMP @ MD</t>
         </is>
       </c>
       <c r="C532" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 16:30</t>
+          <t>2026-09-06 00:00</t>
         </is>
       </c>
       <c r="D532" s="25" t="n">
@@ -35860,17 +35856,17 @@
       </c>
       <c r="F532" s="17" t="inlineStr">
         <is>
-          <t>OSU -50.5</t>
+          <t>MD -45.5</t>
         </is>
       </c>
       <c r="G532" s="26" t="n">
-        <v>-50.5</v>
+        <v>-45.5</v>
       </c>
       <c r="H532" s="18" t="n">
         <v>-108</v>
       </c>
       <c r="I532" s="20" t="n">
-        <v>0.2480345857275048</v>
+        <v>0.2479827101867709</v>
       </c>
       <c r="J532" s="20" t="n">
         <v>0.4956702459300312</v>
@@ -35879,16 +35875,16 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L532" s="19" t="n">
-        <v>-0.2711961835032645</v>
+        <v>-0.2712480590439984</v>
       </c>
       <c r="M532" s="19" t="n">
-        <v>-0.5223037608211019</v>
+        <v>-0.5224036692699228</v>
       </c>
       <c r="N532" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O532" s="27" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="P532" s="17" t="inlineStr">
         <is>
@@ -35897,7 +35893,7 @@
       </c>
       <c r="Q532" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>HAMP isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -35909,12 +35905,12 @@
       </c>
       <c r="B533" s="12" t="inlineStr">
         <is>
-          <t>HAMP @ MD</t>
+          <t>SJSU @ USC</t>
         </is>
       </c>
       <c r="C533" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00</t>
+          <t>2026-08-29 19:00</t>
         </is>
       </c>
       <c r="D533" s="22" t="n">
@@ -35927,35 +35923,35 @@
       </c>
       <c r="F533" s="12" t="inlineStr">
         <is>
-          <t>MD -45.5</t>
+          <t>USC -38.5</t>
         </is>
       </c>
       <c r="G533" s="23" t="n">
-        <v>-45.5</v>
+        <v>-38.5</v>
       </c>
       <c r="H533" s="13" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I533" s="15" t="n">
-        <v>0.2479827101867709</v>
+        <v>0.2523210839512047</v>
       </c>
       <c r="J533" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5</v>
       </c>
       <c r="K533" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L533" s="14" t="n">
-        <v>-0.2712480590439984</v>
+        <v>-0.2714884398583192</v>
       </c>
       <c r="M533" s="14" t="n">
-        <v>-0.5224036692699228</v>
+        <v>-0.5182961124567911</v>
       </c>
       <c r="N533" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O533" s="24" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="P533" s="12" t="inlineStr">
         <is>
@@ -35964,7 +35960,7 @@
       </c>
       <c r="Q533" s="12" t="inlineStr">
         <is>
-          <t>HAMP isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -36939,22 +36935,22 @@
         <v>-41.5</v>
       </c>
       <c r="H548" s="18" t="n">
-        <v>-125</v>
+        <v>-118</v>
       </c>
       <c r="I548" s="20" t="n">
-        <v>0.2672114317479169</v>
+        <v>0.2596597283722857</v>
       </c>
       <c r="J548" s="20" t="n">
-        <v>0.5324675324675325</v>
+        <v>0.5173641257162701</v>
       </c>
       <c r="K548" s="20" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5412844036697247</v>
       </c>
       <c r="L548" s="19" t="n">
-        <v>-0.2883441238076386</v>
+        <v>-0.281624675297439</v>
       </c>
       <c r="M548" s="19" t="n">
-        <v>-0.5190194228537495</v>
+        <v>-0.5202896543630654</v>
       </c>
       <c r="N548" s="20" t="n">
         <v>0</v>
@@ -36987,7 +36983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -37953,7 +37949,7 @@
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>UNC @ TCU</t>
+          <t>SAC @ EMU</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
@@ -37963,14 +37959,14 @@
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>UNC +7.5</t>
+          <t>SAC +8.5</t>
         </is>
       </c>
       <c r="E20" s="13" t="n">
         <v>-108</v>
       </c>
       <c r="F20" s="16" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -37995,11 +37991,71 @@
         </is>
       </c>
       <c r="L20" s="14" t="n">
-        <v>0.0801</v>
+        <v>0.1065</v>
       </c>
       <c r="M20" s="14" t="n"/>
       <c r="N20" s="12" t="n"/>
       <c r="O20" s="12" t="inlineStr">
+        <is>
+          <t>DraftKings</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>UNC @ TCU</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>UNC +7.5</t>
+        </is>
+      </c>
+      <c r="E21" s="18" t="n">
+        <v>-108</v>
+      </c>
+      <c r="F21" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="G21" s="17" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H21" s="21">
+        <f>IF(OR($G21="",$G21="Pending"),"",ROUND(IF($G21="Win",IF($E21&gt;0,$F21*$E21/100,$F21*100/-$E21),IF($G21="Loss",-$F21,0)),2))</f>
+        <v/>
+      </c>
+      <c r="I21" s="21">
+        <f>Settings!$B$5+SUM($H$6:$H21)</f>
+        <v/>
+      </c>
+      <c r="J21" s="19">
+        <f>IFERROR(SUM($H$6:$H21)/SUMIF($G$6:$G21,"&lt;&gt;Pending",$F$6:$F21),"")</f>
+        <v/>
+      </c>
+      <c r="K21" s="17" t="inlineStr">
+        <is>
+          <t>LEAN</t>
+        </is>
+      </c>
+      <c r="L21" s="19" t="n">
+        <v>0.0801</v>
+      </c>
+      <c r="M21" s="19" t="n"/>
+      <c r="N21" s="17" t="n"/>
+      <c r="O21" s="17" t="inlineStr">
         <is>
           <t>Draft Kings</t>
         </is>
@@ -44606,10 +44662,10 @@
         <v>46.5</v>
       </c>
       <c r="K5" s="13" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="L5" s="13" t="n">
-        <v>-340</v>
+        <v>-325</v>
       </c>
       <c r="M5" s="12" t="inlineStr">
         <is>
@@ -44700,10 +44756,10 @@
         <v>51.5</v>
       </c>
       <c r="K7" s="13" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>-180</v>
+        <v>-185</v>
       </c>
       <c r="M7" s="12" t="inlineStr">
         <is>
@@ -44792,10 +44848,10 @@
       </c>
       <c r="H9" s="12" t="inlineStr"/>
       <c r="I9" s="23" t="n">
-        <v>-9.5</v>
+        <v>-8.5</v>
       </c>
       <c r="J9" s="29" t="n">
-        <v>53.5</v>
+        <v>54.5</v>
       </c>
       <c r="K9" s="13" t="n">
         <v>275</v>
@@ -45797,16 +45853,16 @@
       </c>
       <c r="H30" s="17" t="inlineStr"/>
       <c r="I30" s="26" t="n">
-        <v>24.5</v>
+        <v>23.5</v>
       </c>
       <c r="J30" s="30" t="n">
         <v>47.5</v>
       </c>
       <c r="K30" s="18" t="n">
-        <v>-4000</v>
+        <v>-2800</v>
       </c>
       <c r="L30" s="18" t="n">
-        <v>1600</v>
+        <v>1300</v>
       </c>
       <c r="M30" s="17" t="inlineStr">
         <is>

--- a/NCAAF_Edge_Model.xlsx
+++ b/NCAAF_Edge_Model.xlsx
@@ -642,7 +642,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-30T17:04:44+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
+          <t>Generated 2026-08-30T21:04:32+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
         </is>
       </c>
     </row>
@@ -2255,12 +2255,12 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>VMI @ VT</t>
+          <t>UTU @ BYU</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-09-06 00:00</t>
         </is>
       </c>
       <c r="D17" s="22" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>VMI +50.5</t>
+          <t>UTU +50.5</t>
         </is>
       </c>
       <c r="G17" s="23" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="Q17" s="12" t="inlineStr">
         <is>
-          <t>VMI isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>UTU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -2590,12 +2590,12 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>FUR @ TENN</t>
+          <t>VMI @ VT</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D22" s="25" t="n">
@@ -2608,17 +2608,17 @@
       </c>
       <c r="F22" s="17" t="inlineStr">
         <is>
-          <t>FUR +46.5</t>
+          <t>VMI +51.5</t>
         </is>
       </c>
       <c r="G22" s="26" t="n">
-        <v>-46.5</v>
+        <v>-51.5</v>
       </c>
       <c r="H22" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I22" s="20" t="n">
-        <v>0.749830435516865</v>
+        <v>0.7499606332961088</v>
       </c>
       <c r="J22" s="20" t="n">
         <v>0.5</v>
@@ -2627,10 +2627,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L22" s="19" t="n">
-        <v>0.2260209117073412</v>
+        <v>0.226151109486585</v>
       </c>
       <c r="M22" s="19" t="n">
-        <v>0.4314944678049242</v>
+        <v>0.4317430272016624</v>
       </c>
       <c r="N22" s="20" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="Q22" s="17" t="inlineStr">
         <is>
-          <t>FUR isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>VMI isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -2657,12 +2657,12 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>MVSU @ SAC</t>
+          <t>FUR @ TENN</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 02:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D23" s="22" t="n">
@@ -2675,29 +2675,29 @@
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>MVSU +35.5</t>
+          <t>FUR +46.5</t>
         </is>
       </c>
       <c r="G23" s="23" t="n">
-        <v>-35.5</v>
+        <v>-46.5</v>
       </c>
       <c r="H23" s="13" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>0.7451524021600664</v>
+        <v>0.749830435516865</v>
       </c>
       <c r="J23" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5</v>
       </c>
       <c r="K23" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L23" s="14" t="n">
-        <v>0.2259216329292971</v>
+        <v>0.2260209117073412</v>
       </c>
       <c r="M23" s="14" t="n">
-        <v>0.4351083300860539</v>
+        <v>0.4314944678049242</v>
       </c>
       <c r="N23" s="15" t="n">
         <v>0</v>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="Q23" s="12" t="inlineStr">
         <is>
-          <t>MVSU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>FUR isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -2724,12 +2724,12 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>BCU @ UCF</t>
+          <t>MVSU @ SAC</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-06 02:00</t>
         </is>
       </c>
       <c r="D24" s="25" t="n">
@@ -2742,29 +2742,29 @@
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>BCU +42.5</t>
+          <t>MVSU +35.5</t>
         </is>
       </c>
       <c r="G24" s="26" t="n">
-        <v>-42.5</v>
+        <v>-35.5</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I24" s="20" t="n">
-        <v>0.7495068449117334</v>
+        <v>0.7451524021600664</v>
       </c>
       <c r="J24" s="20" t="n">
-        <v>0.5</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K24" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L24" s="19" t="n">
-        <v>0.2256973211022095</v>
+        <v>0.2259216329292971</v>
       </c>
       <c r="M24" s="19" t="n">
-        <v>0.4308767039224001</v>
+        <v>0.4351083300860539</v>
       </c>
       <c r="N24" s="20" t="n">
         <v>0</v>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="Q24" s="17" t="inlineStr">
         <is>
-          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>MVSU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>NORF @ ODU</t>
+          <t>BCU @ UCF</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 22:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D25" s="22" t="n">
@@ -2809,17 +2809,17 @@
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>NORF +41.5</t>
+          <t>BCU +42.5</t>
         </is>
       </c>
       <c r="G25" s="23" t="n">
-        <v>-41.5</v>
+        <v>-42.5</v>
       </c>
       <c r="H25" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>0.74936483176334</v>
+        <v>0.7495068449117334</v>
       </c>
       <c r="J25" s="15" t="n">
         <v>0.5</v>
@@ -2828,10 +2828,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L25" s="14" t="n">
-        <v>0.2255553079538162</v>
+        <v>0.2256973211022095</v>
       </c>
       <c r="M25" s="14" t="n">
-        <v>0.430605587911831</v>
+        <v>0.4308767039224001</v>
       </c>
       <c r="N25" s="15" t="n">
         <v>0</v>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="Q25" s="12" t="inlineStr">
         <is>
-          <t>NORF isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -2858,12 +2858,12 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>MORG @ ASU</t>
+          <t>NORF @ ODU</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>2026-09-06 02:00</t>
+          <t>2026-09-05 22:00</t>
         </is>
       </c>
       <c r="D26" s="25" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>MORG +41.5</t>
+          <t>NORF +41.5</t>
         </is>
       </c>
       <c r="G26" s="26" t="n">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="Q26" s="17" t="inlineStr">
         <is>
-          <t>MORG isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>NORF isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -2925,12 +2925,12 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>PRST @ SDSU</t>
+          <t>MORG @ ASU</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 01:30</t>
+          <t>2026-09-06 02:00</t>
         </is>
       </c>
       <c r="D27" s="22" t="n">
@@ -2943,17 +2943,17 @@
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>PRST +40.5</t>
+          <t>MORG +41.5</t>
         </is>
       </c>
       <c r="G27" s="23" t="n">
-        <v>-40.5</v>
+        <v>-41.5</v>
       </c>
       <c r="H27" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>0.7491864110178605</v>
+        <v>0.74936483176334</v>
       </c>
       <c r="J27" s="15" t="n">
         <v>0.5</v>
@@ -2962,10 +2962,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L27" s="14" t="n">
-        <v>0.2253768872083367</v>
+        <v>0.2255553079538162</v>
       </c>
       <c r="M27" s="14" t="n">
-        <v>0.4302649664886429</v>
+        <v>0.430605587911831</v>
       </c>
       <c r="N27" s="15" t="n">
         <v>0</v>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="Q27" s="12" t="inlineStr">
         <is>
-          <t>PRST isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>MORG isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -2992,12 +2992,12 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>LIU @ KU</t>
+          <t>PRST @ SDSU</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 00:00</t>
+          <t>2026-09-06 01:30</t>
         </is>
       </c>
       <c r="D28" s="25" t="n">
@@ -3010,17 +3010,17 @@
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>LIU +38.5</t>
+          <t>PRST +40.5</t>
         </is>
       </c>
       <c r="G28" s="26" t="n">
-        <v>-38.5</v>
+        <v>-40.5</v>
       </c>
       <c r="H28" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I28" s="20" t="n">
-        <v>0.7486868966497979</v>
+        <v>0.7491864110178605</v>
       </c>
       <c r="J28" s="20" t="n">
         <v>0.5</v>
@@ -3029,10 +3029,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L28" s="19" t="n">
-        <v>0.2248773728402741</v>
+        <v>0.2253768872083367</v>
       </c>
       <c r="M28" s="19" t="n">
-        <v>0.4293113481496142</v>
+        <v>0.4302649664886429</v>
       </c>
       <c r="N28" s="20" t="n">
         <v>0</v>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="Q28" s="17" t="inlineStr">
         <is>
-          <t>LIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>PRST isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -3059,12 +3059,12 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>IDHO @ UTAH</t>
+          <t>LIU @ KU</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 01:00</t>
+          <t>2026-09-05 00:00</t>
         </is>
       </c>
       <c r="D29" s="22" t="n">
@@ -3077,29 +3077,29 @@
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>IDHO +33.5</t>
+          <t>LIU +38.5</t>
         </is>
       </c>
       <c r="G29" s="23" t="n">
-        <v>-33.5</v>
+        <v>-38.5</v>
       </c>
       <c r="H29" s="13" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>0.7438837790634202</v>
+        <v>0.7486868966497979</v>
       </c>
       <c r="J29" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5</v>
       </c>
       <c r="K29" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L29" s="14" t="n">
-        <v>0.2246530098326509</v>
+        <v>0.2248773728402741</v>
       </c>
       <c r="M29" s="14" t="n">
-        <v>0.4326650559739945</v>
+        <v>0.4293113481496142</v>
       </c>
       <c r="N29" s="15" t="n">
         <v>0</v>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="Q29" s="12" t="inlineStr">
         <is>
-          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>LIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>BALL @ OSU</t>
+          <t>IDHO @ UTAH</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 16:30</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D30" s="25" t="n">
@@ -3144,29 +3144,29 @@
       </c>
       <c r="F30" s="17" t="inlineStr">
         <is>
-          <t>BALL +50.5</t>
+          <t>IDHO +33.5</t>
         </is>
       </c>
       <c r="G30" s="26" t="n">
-        <v>-50.5</v>
+        <v>-33.5</v>
       </c>
       <c r="H30" s="18" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="I30" s="20" t="n">
-        <v>0.7521115583182229</v>
+        <v>0.7438837790634202</v>
       </c>
       <c r="J30" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K30" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>0.22380967152577</v>
+        <v>0.2246530098326509</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>0.4236397353880647</v>
+        <v>0.4326650559739945</v>
       </c>
       <c r="N30" s="20" t="n">
         <v>0</v>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="Q30" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -3193,12 +3193,12 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>UTU @ BYU</t>
+          <t>BALL @ OSU</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00</t>
+          <t>2026-09-05 16:30</t>
         </is>
       </c>
       <c r="D31" s="22" t="n">
@@ -3211,17 +3211,17 @@
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>UTU +49.5</t>
+          <t>BALL +50.5</t>
         </is>
       </c>
       <c r="G31" s="23" t="n">
-        <v>-49.5</v>
+        <v>-50.5</v>
       </c>
       <c r="H31" s="13" t="n">
         <v>-112</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>0.7520930706656717</v>
+        <v>0.7521115583182229</v>
       </c>
       <c r="J31" s="15" t="n">
         <v>0.5043297540699688</v>
@@ -3230,10 +3230,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L31" s="14" t="n">
-        <v>0.2237911838732188</v>
+        <v>0.22380967152577</v>
       </c>
       <c r="M31" s="14" t="n">
-        <v>0.4236047409028785</v>
+        <v>0.4236397353880647</v>
       </c>
       <c r="N31" s="15" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="Q31" s="12" t="inlineStr">
         <is>
-          <t>UTU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -4131,12 +4131,12 @@
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>WMU @ MICH</t>
+          <t>NAU @ ARIZ</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-09-06 01:30</t>
         </is>
       </c>
       <c r="D45" s="22" t="n">
@@ -4149,29 +4149,29 @@
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
-          <t>WMU +27.5</t>
+          <t>NAU +31.5</t>
         </is>
       </c>
       <c r="G45" s="23" t="n">
-        <v>-27.5</v>
+        <v>-31.5</v>
       </c>
       <c r="H45" s="13" t="n">
-        <v>-105</v>
+        <v>-112</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>0.7317915953656452</v>
+        <v>0.7462521995675839</v>
       </c>
       <c r="J45" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K45" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L45" s="14" t="n">
-        <v>0.2195964734144257</v>
+        <v>0.2179503127751311</v>
       </c>
       <c r="M45" s="14" t="n">
-        <v>0.4287359719043549</v>
+        <v>0.4125488063243552</v>
       </c>
       <c r="N45" s="15" t="n">
         <v>0</v>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="Q45" s="12" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>NAU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -4198,12 +4198,12 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>NAU @ ARIZ</t>
+          <t>MASS @ RUTG</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>2026-09-06 01:30</t>
+          <t>2026-09-03 22:00</t>
         </is>
       </c>
       <c r="D46" s="25" t="n">
@@ -4216,29 +4216,29 @@
       </c>
       <c r="F46" s="17" t="inlineStr">
         <is>
-          <t>NAU +31.5</t>
+          <t>MASS +29.5</t>
         </is>
       </c>
       <c r="G46" s="26" t="n">
-        <v>-31.5</v>
+        <v>-29.5</v>
       </c>
       <c r="H46" s="18" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I46" s="20" t="n">
-        <v>0.7462521995675839</v>
+        <v>0.7412752050592825</v>
       </c>
       <c r="J46" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K46" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L46" s="19" t="n">
-        <v>0.2179503127751311</v>
+        <v>0.2174656812497586</v>
       </c>
       <c r="M46" s="19" t="n">
-        <v>0.4125488063243552</v>
+        <v>0.4151617551131757</v>
       </c>
       <c r="N46" s="20" t="n">
         <v>0</v>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="Q46" s="17" t="inlineStr">
         <is>
-          <t>NAU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -4265,12 +4265,12 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>MASS @ RUTG</t>
+          <t>MOST @ TA&amp;M</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 22:00</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D47" s="22" t="n">
@@ -4283,29 +4283,29 @@
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>MASS +29.5</t>
+          <t>MOST +41.5</t>
         </is>
       </c>
       <c r="G47" s="23" t="n">
-        <v>-29.5</v>
+        <v>-41.5</v>
       </c>
       <c r="H47" s="13" t="n">
-        <v>-110</v>
+        <v>-118</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>0.7412752050592825</v>
+        <v>0.7580468946214751</v>
       </c>
       <c r="J47" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5173641257162701</v>
       </c>
       <c r="K47" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5412844036697247</v>
       </c>
       <c r="L47" s="14" t="n">
-        <v>0.2174656812497586</v>
+        <v>0.2167624909517504</v>
       </c>
       <c r="M47" s="14" t="n">
-        <v>0.4151617551131757</v>
+        <v>0.4004595171820472</v>
       </c>
       <c r="N47" s="15" t="n">
         <v>0</v>
@@ -4332,12 +4332,12 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>MOST @ TA&amp;M</t>
+          <t>DUQ @ AFA</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-05 17:00</t>
         </is>
       </c>
       <c r="D48" s="25" t="n">
@@ -4350,29 +4350,29 @@
       </c>
       <c r="F48" s="17" t="inlineStr">
         <is>
-          <t>MOST +41.5</t>
+          <t>DUQ +30.5</t>
         </is>
       </c>
       <c r="G48" s="26" t="n">
-        <v>-41.5</v>
+        <v>-30.5</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>-118</v>
+        <v>-112</v>
       </c>
       <c r="I48" s="20" t="n">
-        <v>0.7580468946214751</v>
+        <v>0.7449264419026254</v>
       </c>
       <c r="J48" s="20" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K48" s="20" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L48" s="19" t="n">
-        <v>0.2167624909517504</v>
+        <v>0.2166245551101725</v>
       </c>
       <c r="M48" s="19" t="n">
-        <v>0.4004595171820472</v>
+        <v>0.4100393364585408</v>
       </c>
       <c r="N48" s="20" t="n">
         <v>0</v>
@@ -4387,7 +4387,7 @@
       </c>
       <c r="Q48" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>DUQ isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>DUQ @ AFA</t>
+          <t>TOW @ NAVY</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 17:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D49" s="22" t="n">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
-          <t>DUQ +30.5</t>
+          <t>TOW +30.5</t>
         </is>
       </c>
       <c r="G49" s="23" t="n">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="Q49" s="12" t="inlineStr">
         <is>
-          <t>DUQ isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>TOW isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -4466,12 +4466,12 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>TOW @ NAVY</t>
+          <t>WMU @ MICH</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D50" s="25" t="n">
@@ -4484,29 +4484,29 @@
       </c>
       <c r="F50" s="17" t="inlineStr">
         <is>
-          <t>TOW +30.5</t>
+          <t>WMU +27.5</t>
         </is>
       </c>
       <c r="G50" s="26" t="n">
-        <v>-30.5</v>
+        <v>-27.5</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="I50" s="20" t="n">
-        <v>0.7449264419026254</v>
+        <v>0.7350438364238352</v>
       </c>
       <c r="J50" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K50" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L50" s="19" t="n">
-        <v>0.2166245551101725</v>
+        <v>0.2158130671930659</v>
       </c>
       <c r="M50" s="19" t="n">
-        <v>0.4100393364585408</v>
+        <v>0.4156399812607198</v>
       </c>
       <c r="N50" s="20" t="n">
         <v>0</v>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="Q50" s="17" t="inlineStr">
         <is>
-          <t>TOW isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -7711,12 +7711,12 @@
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>WMU @ MICH</t>
+          <t>ALB @ BUFF</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D99" s="22" t="n">
@@ -7729,27 +7729,27 @@
       </c>
       <c r="F99" s="12" t="inlineStr">
         <is>
-          <t>WMU ML</t>
+          <t>ALB ML</t>
         </is>
       </c>
       <c r="G99" s="23" t="n"/>
       <c r="H99" s="13" t="n">
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="I99" s="15" t="n">
-        <v>0.2311613710114301</v>
+        <v>0.2335750998402533</v>
       </c>
       <c r="J99" s="15" t="n">
-        <v>0.0461215932914046</v>
+        <v>0.05094905094905094</v>
       </c>
       <c r="K99" s="15" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L99" s="14" t="n">
-        <v>0.1835423233923825</v>
+        <v>0.1809435208928848</v>
       </c>
       <c r="M99" s="14" t="n">
-        <v>3.854388791240032</v>
+        <v>3.437926896964813</v>
       </c>
       <c r="N99" s="15" t="n">
         <v>0</v>
@@ -7764,7 +7764,7 @@
       </c>
       <c r="Q99" s="12" t="inlineStr">
         <is>
-          <t>price outside allowed range</t>
+          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -7776,12 +7776,12 @@
       </c>
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>ALB @ BUFF</t>
+          <t>WMU @ MICH</t>
         </is>
       </c>
       <c r="C100" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D100" s="25" t="n">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="F100" s="17" t="inlineStr">
         <is>
-          <t>ALB ML</t>
+          <t>WMU ML</t>
         </is>
       </c>
       <c r="G100" s="26" t="n"/>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="Q100" s="17" t="inlineStr">
         <is>
-          <t>ALB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>price outside allowed range</t>
         </is>
       </c>
     </row>
@@ -11273,7 +11273,7 @@
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t>TULN @ DUKE</t>
+          <t>BAY @ AUB</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
@@ -11291,29 +11291,29 @@
       </c>
       <c r="F153" s="12" t="inlineStr">
         <is>
-          <t>Over 50.5</t>
+          <t>Under 58.5</t>
         </is>
       </c>
       <c r="G153" s="23" t="n">
-        <v>50.5</v>
+        <v>58.5</v>
       </c>
       <c r="H153" s="13" t="n">
-        <v>-115</v>
+        <v>-102</v>
       </c>
       <c r="I153" s="15" t="n">
-        <v>0.6281478141114352</v>
+        <v>0.5991888081938934</v>
       </c>
       <c r="J153" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4826358742837298</v>
       </c>
       <c r="K153" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.504950495049505</v>
       </c>
       <c r="L153" s="14" t="n">
-        <v>0.09326409318120266</v>
+        <v>0.09423831314438846</v>
       </c>
       <c r="M153" s="14" t="n">
-        <v>0.1743633046431178</v>
+        <v>0.1866288162271224</v>
       </c>
       <c r="N153" s="15" t="n">
         <v>0</v>
@@ -11328,7 +11328,7 @@
       </c>
       <c r="Q153" s="12" t="inlineStr">
         <is>
-          <t>outside the top 10 plays for this week</t>
+          <t>correlated with a stronger play on the same game</t>
         </is>
       </c>
     </row>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="B154" s="17" t="inlineStr">
         <is>
-          <t>BAY @ AUB</t>
+          <t>TULN @ DUKE</t>
         </is>
       </c>
       <c r="C154" s="17" t="inlineStr">
@@ -11358,29 +11358,29 @@
       </c>
       <c r="F154" s="17" t="inlineStr">
         <is>
-          <t>Under 59.5</t>
+          <t>Over 50.5</t>
         </is>
       </c>
       <c r="G154" s="26" t="n">
-        <v>59.5</v>
+        <v>50.5</v>
       </c>
       <c r="H154" s="18" t="n">
-        <v>-118</v>
+        <v>-115</v>
       </c>
       <c r="I154" s="20" t="n">
-        <v>0.6330121327471427</v>
+        <v>0.6281478141114352</v>
       </c>
       <c r="J154" s="20" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K154" s="20" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L154" s="19" t="n">
-        <v>0.091727729077418</v>
+        <v>0.09326409318120266</v>
       </c>
       <c r="M154" s="19" t="n">
-        <v>0.1694630927023484</v>
+        <v>0.1743633046431178</v>
       </c>
       <c r="N154" s="20" t="n">
         <v>0</v>
@@ -11395,7 +11395,7 @@
       </c>
       <c r="Q154" s="17" t="inlineStr">
         <is>
-          <t>correlated with a stronger play on the same game</t>
+          <t>outside the top 10 plays for this week</t>
         </is>
       </c>
     </row>
@@ -12555,12 +12555,12 @@
       </c>
       <c r="B173" s="12" t="inlineStr">
         <is>
-          <t>WSU @ WASH</t>
+          <t>ARST @ MEM</t>
         </is>
       </c>
       <c r="C173" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 20:00</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D173" s="22" t="n">
@@ -12568,34 +12568,34 @@
       </c>
       <c r="E173" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F173" s="12" t="inlineStr">
         <is>
-          <t>Over 50.5</t>
+          <t>ARST +9.5</t>
         </is>
       </c>
       <c r="G173" s="23" t="n">
-        <v>50.5</v>
+        <v>-9.5</v>
       </c>
       <c r="H173" s="13" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="I173" s="15" t="n">
-        <v>0.5940026766005383</v>
+        <v>0.5989918223865158</v>
       </c>
       <c r="J173" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K173" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L173" s="14" t="n">
-        <v>0.07019315279101446</v>
+        <v>0.070689935594063</v>
       </c>
       <c r="M173" s="14" t="n">
-        <v>0.134005109873755</v>
+        <v>0.1338059495173335</v>
       </c>
       <c r="N173" s="15" t="n">
         <v>0</v>
@@ -12618,12 +12618,12 @@
       </c>
       <c r="B174" s="17" t="inlineStr">
         <is>
-          <t>ORST @ HOU</t>
+          <t>WSU @ WASH</t>
         </is>
       </c>
       <c r="C174" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-09-06 20:00</t>
         </is>
       </c>
       <c r="D174" s="25" t="n">
@@ -12636,29 +12636,29 @@
       </c>
       <c r="F174" s="17" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>Over 50.5</t>
         </is>
       </c>
       <c r="G174" s="26" t="n">
-        <v>51.5</v>
+        <v>50.5</v>
       </c>
       <c r="H174" s="18" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="I174" s="20" t="n">
-        <v>0.581439101443355</v>
+        <v>0.5940026766005383</v>
       </c>
       <c r="J174" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5</v>
       </c>
       <c r="K174" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L174" s="19" t="n">
-        <v>0.06924397949213545</v>
+        <v>0.07019315279101446</v>
       </c>
       <c r="M174" s="19" t="n">
-        <v>0.1351906266275026</v>
+        <v>0.134005109873755</v>
       </c>
       <c r="N174" s="20" t="n">
         <v>0</v>
@@ -12681,12 +12681,12 @@
       </c>
       <c r="B175" s="12" t="inlineStr">
         <is>
-          <t>FRES @ USC</t>
+          <t>ORST @ HOU</t>
         </is>
       </c>
       <c r="C175" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 01:00</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D175" s="22" t="n">
@@ -12706,22 +12706,22 @@
         <v>51.5</v>
       </c>
       <c r="H175" s="13" t="n">
-        <v>-115</v>
+        <v>-105</v>
       </c>
       <c r="I175" s="15" t="n">
-        <v>0.5994197929950476</v>
+        <v>0.581439101443355</v>
       </c>
       <c r="J175" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K175" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L175" s="14" t="n">
-        <v>0.06453607206481504</v>
+        <v>0.06924397949213545</v>
       </c>
       <c r="M175" s="14" t="n">
-        <v>0.1206543955994367</v>
+        <v>0.1351906266275026</v>
       </c>
       <c r="N175" s="15" t="n">
         <v>0</v>
@@ -12744,12 +12744,12 @@
       </c>
       <c r="B176" s="17" t="inlineStr">
         <is>
-          <t>SMU @ FSU</t>
+          <t>FRES @ USC</t>
         </is>
       </c>
       <c r="C176" s="17" t="inlineStr">
         <is>
-          <t>2026-09-07 23:30</t>
+          <t>2026-09-05 01:00</t>
         </is>
       </c>
       <c r="D176" s="25" t="n">
@@ -12757,22 +12757,22 @@
       </c>
       <c r="E176" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F176" s="17" t="inlineStr">
         <is>
-          <t>FSU +3</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="G176" s="26" t="n">
-        <v>3</v>
+        <v>51.5</v>
       </c>
       <c r="H176" s="18" t="n">
         <v>-115</v>
       </c>
       <c r="I176" s="20" t="n">
-        <v>0.5982923347975395</v>
+        <v>0.5994197929950476</v>
       </c>
       <c r="J176" s="20" t="n">
         <v>0.5108342361863488</v>
@@ -12781,13 +12781,13 @@
         <v>0.5348837209302325</v>
       </c>
       <c r="L176" s="19" t="n">
-        <v>0.06340861386730701</v>
+        <v>0.06453607206481504</v>
       </c>
       <c r="M176" s="19" t="n">
-        <v>0.1120514957648113</v>
+        <v>0.1206543955994367</v>
       </c>
       <c r="N176" s="20" t="n">
-        <v>0.0548</v>
+        <v>0</v>
       </c>
       <c r="O176" s="27" t="n">
         <v>0.4</v>
@@ -12807,12 +12807,12 @@
       </c>
       <c r="B177" s="12" t="inlineStr">
         <is>
-          <t>EIU @ MINN</t>
+          <t>SMU @ FSU</t>
         </is>
       </c>
       <c r="C177" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-09-07 23:30</t>
         </is>
       </c>
       <c r="D177" s="22" t="n">
@@ -12820,37 +12820,37 @@
       </c>
       <c r="E177" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F177" s="12" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>FSU +3</t>
         </is>
       </c>
       <c r="G177" s="23" t="n">
-        <v>51.5</v>
+        <v>3</v>
       </c>
       <c r="H177" s="13" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="I177" s="15" t="n">
-        <v>0.5868562195365294</v>
+        <v>0.5982923347975395</v>
       </c>
       <c r="J177" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K177" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L177" s="14" t="n">
-        <v>0.06304669572700561</v>
+        <v>0.06340861386730701</v>
       </c>
       <c r="M177" s="14" t="n">
-        <v>0.1203618736606472</v>
+        <v>0.1120514957648113</v>
       </c>
       <c r="N177" s="15" t="n">
-        <v>0</v>
+        <v>0.0548</v>
       </c>
       <c r="O177" s="24" t="n">
         <v>0.4</v>
@@ -12860,11 +12860,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q177" s="12" t="inlineStr">
-        <is>
-          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q177" s="12" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="17" t="inlineStr">
@@ -12874,12 +12870,12 @@
       </c>
       <c r="B178" s="17" t="inlineStr">
         <is>
-          <t>OKST @ TLSA</t>
+          <t>EIU @ MINN</t>
         </is>
       </c>
       <c r="C178" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 19:45</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D178" s="25" t="n">
@@ -12892,29 +12888,29 @@
       </c>
       <c r="F178" s="17" t="inlineStr">
         <is>
-          <t>Under 60.5</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="G178" s="26" t="n">
-        <v>60.5</v>
+        <v>51.5</v>
       </c>
       <c r="H178" s="18" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I178" s="20" t="n">
-        <v>0.5908202422154937</v>
+        <v>0.5868562195365294</v>
       </c>
       <c r="J178" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K178" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L178" s="19" t="n">
-        <v>0.06251835542304085</v>
+        <v>0.06304669572700561</v>
       </c>
       <c r="M178" s="19" t="n">
-        <v>0.1183383156221844</v>
+        <v>0.1203618736606472</v>
       </c>
       <c r="N178" s="20" t="n">
         <v>0</v>
@@ -12927,7 +12923,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q178" s="17" t="n"/>
+      <c r="Q178" s="17" t="inlineStr">
+        <is>
+          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="12" t="inlineStr">
@@ -12937,12 +12937,12 @@
       </c>
       <c r="B179" s="12" t="inlineStr">
         <is>
-          <t>BRY @ ARMY</t>
+          <t>OKST @ TLSA</t>
         </is>
       </c>
       <c r="C179" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-09-05 19:45</t>
         </is>
       </c>
       <c r="D179" s="22" t="n">
@@ -12955,29 +12955,29 @@
       </c>
       <c r="F179" s="12" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>Under 60.5</t>
         </is>
       </c>
       <c r="G179" s="23" t="n">
-        <v>51.5</v>
+        <v>60.5</v>
       </c>
       <c r="H179" s="13" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I179" s="15" t="n">
-        <v>0.5810688250918421</v>
+        <v>0.5908202422154937</v>
       </c>
       <c r="J179" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K179" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L179" s="14" t="n">
-        <v>0.06183805586107283</v>
+        <v>0.06251835542304085</v>
       </c>
       <c r="M179" s="14" t="n">
-        <v>0.119095514991696</v>
+        <v>0.1183383156221844</v>
       </c>
       <c r="N179" s="15" t="n">
         <v>0</v>
@@ -12990,11 +12990,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q179" s="12" t="inlineStr">
-        <is>
-          <t>BRY isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q179" s="12" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="17" t="inlineStr">
@@ -13004,12 +13000,12 @@
       </c>
       <c r="B180" s="17" t="inlineStr">
         <is>
-          <t>SELA @ USA</t>
+          <t>BRY @ ARMY</t>
         </is>
       </c>
       <c r="C180" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D180" s="25" t="n">
@@ -13022,17 +13018,17 @@
       </c>
       <c r="F180" s="17" t="inlineStr">
         <is>
-          <t>Over 52.5</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="G180" s="26" t="n">
-        <v>52.5</v>
+        <v>51.5</v>
       </c>
       <c r="H180" s="18" t="n">
         <v>-108</v>
       </c>
       <c r="I180" s="20" t="n">
-        <v>0.581068823779724</v>
+        <v>0.5810688250918421</v>
       </c>
       <c r="J180" s="20" t="n">
         <v>0.4956702459300312</v>
@@ -13041,10 +13037,10 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L180" s="19" t="n">
-        <v>0.06183805454895475</v>
+        <v>0.06183805586107283</v>
       </c>
       <c r="M180" s="19" t="n">
-        <v>0.1190955124646538</v>
+        <v>0.119095514991696</v>
       </c>
       <c r="N180" s="20" t="n">
         <v>0</v>
@@ -13059,7 +13055,7 @@
       </c>
       <c r="Q180" s="17" t="inlineStr">
         <is>
-          <t>SELA isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>BRY isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -13071,12 +13067,12 @@
       </c>
       <c r="B181" s="12" t="inlineStr">
         <is>
-          <t>BOIS @ ORE</t>
+          <t>SELA @ USA</t>
         </is>
       </c>
       <c r="C181" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D181" s="22" t="n">
@@ -13089,29 +13085,29 @@
       </c>
       <c r="F181" s="12" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>Over 52.5</t>
         </is>
       </c>
       <c r="G181" s="23" t="n">
-        <v>51.5</v>
+        <v>52.5</v>
       </c>
       <c r="H181" s="13" t="n">
-        <v>-118</v>
+        <v>-108</v>
       </c>
       <c r="I181" s="15" t="n">
-        <v>0.6026847377600082</v>
+        <v>0.581068823779724</v>
       </c>
       <c r="J181" s="15" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K181" s="15" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L181" s="14" t="n">
-        <v>0.06140033409028345</v>
+        <v>0.06183805454895475</v>
       </c>
       <c r="M181" s="14" t="n">
-        <v>0.113434515522727</v>
+        <v>0.1190955124646538</v>
       </c>
       <c r="N181" s="15" t="n">
         <v>0</v>
@@ -13124,7 +13120,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q181" s="12" t="n"/>
+      <c r="Q181" s="12" t="inlineStr">
+        <is>
+          <t>SELA isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="17" t="inlineStr">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="B182" s="17" t="inlineStr">
         <is>
-          <t>BC @ CIN</t>
+          <t>BOIS @ ORE</t>
         </is>
       </c>
       <c r="C182" s="17" t="inlineStr">
@@ -13147,34 +13147,34 @@
       </c>
       <c r="E182" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F182" s="17" t="inlineStr">
         <is>
-          <t>BC +7.5</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="G182" s="26" t="n">
-        <v>-7.5</v>
+        <v>51.5</v>
       </c>
       <c r="H182" s="18" t="n">
-        <v>-112</v>
+        <v>-118</v>
       </c>
       <c r="I182" s="20" t="n">
-        <v>0.588408591423813</v>
+        <v>0.6026847377600082</v>
       </c>
       <c r="J182" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5173641257162701</v>
       </c>
       <c r="K182" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5412844036697247</v>
       </c>
       <c r="L182" s="19" t="n">
-        <v>0.06010670463136014</v>
+        <v>0.06140033409028345</v>
       </c>
       <c r="M182" s="19" t="n">
-        <v>0.1137734051950745</v>
+        <v>0.113434515522727</v>
       </c>
       <c r="N182" s="20" t="n">
         <v>0</v>
@@ -13210,32 +13210,34 @@
       </c>
       <c r="E183" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F183" s="12" t="inlineStr">
         <is>
-          <t>BC ML</t>
-        </is>
-      </c>
-      <c r="G183" s="23" t="n"/>
+          <t>BC +7.5</t>
+        </is>
+      </c>
+      <c r="G183" s="23" t="n">
+        <v>-7.5</v>
+      </c>
       <c r="H183" s="13" t="n">
-        <v>250</v>
+        <v>-112</v>
       </c>
       <c r="I183" s="15" t="n">
-        <v>0.3452243201851257</v>
+        <v>0.588408591423813</v>
       </c>
       <c r="J183" s="15" t="n">
-        <v>0.274247491638796</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K183" s="15" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L183" s="14" t="n">
-        <v>0.05951003447084002</v>
+        <v>0.06010670463136014</v>
       </c>
       <c r="M183" s="14" t="n">
-        <v>0.20828512064794</v>
+        <v>0.1137734051950745</v>
       </c>
       <c r="N183" s="15" t="n">
         <v>0</v>
@@ -13258,12 +13260,12 @@
       </c>
       <c r="B184" s="17" t="inlineStr">
         <is>
-          <t>APSU @ VAN</t>
+          <t>BC @ CIN</t>
         </is>
       </c>
       <c r="C184" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D184" s="25" t="n">
@@ -13271,34 +13273,32 @@
       </c>
       <c r="E184" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F184" s="17" t="inlineStr">
         <is>
-          <t>Under 61.5</t>
-        </is>
-      </c>
-      <c r="G184" s="26" t="n">
-        <v>61.5</v>
-      </c>
+          <t>BC ML</t>
+        </is>
+      </c>
+      <c r="G184" s="26" t="n"/>
       <c r="H184" s="18" t="n">
-        <v>-112</v>
+        <v>250</v>
       </c>
       <c r="I184" s="20" t="n">
-        <v>0.5872138224236385</v>
+        <v>0.3452243201851257</v>
       </c>
       <c r="J184" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.274247491638796</v>
       </c>
       <c r="K184" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="L184" s="19" t="n">
-        <v>0.05891193563118569</v>
+        <v>0.05951003447084002</v>
       </c>
       <c r="M184" s="19" t="n">
-        <v>0.11151187815903</v>
+        <v>0.20828512064794</v>
       </c>
       <c r="N184" s="20" t="n">
         <v>0</v>
@@ -13311,11 +13311,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q184" s="17" t="inlineStr">
-        <is>
-          <t>APSU isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q184" s="17" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="12" t="inlineStr">
@@ -13325,12 +13321,12 @@
       </c>
       <c r="B185" s="12" t="inlineStr">
         <is>
-          <t>CLEM @ LSU</t>
+          <t>APSU @ VAN</t>
         </is>
       </c>
       <c r="C185" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D185" s="22" t="n">
@@ -13343,29 +13339,29 @@
       </c>
       <c r="F185" s="12" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>Under 61.5</t>
         </is>
       </c>
       <c r="G185" s="23" t="n">
-        <v>51.5</v>
+        <v>61.5</v>
       </c>
       <c r="H185" s="13" t="n">
-        <v>-102</v>
+        <v>-112</v>
       </c>
       <c r="I185" s="15" t="n">
-        <v>0.5635010598689705</v>
+        <v>0.5872138224236385</v>
       </c>
       <c r="J185" s="15" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K185" s="15" t="n">
-        <v>0.504950495049505</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L185" s="14" t="n">
-        <v>0.05855056481946552</v>
+        <v>0.05891193563118569</v>
       </c>
       <c r="M185" s="14" t="n">
-        <v>0.1159530793483533</v>
+        <v>0.11151187815903</v>
       </c>
       <c r="N185" s="15" t="n">
         <v>0</v>
@@ -13378,7 +13374,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q185" s="12" t="n"/>
+      <c r="Q185" s="12" t="inlineStr">
+        <is>
+          <t>APSU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="17" t="inlineStr">
@@ -13388,12 +13388,12 @@
       </c>
       <c r="B186" s="17" t="inlineStr">
         <is>
-          <t>UAPB @ MIZ</t>
+          <t>CLEM @ LSU</t>
         </is>
       </c>
       <c r="C186" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D186" s="25" t="n">
@@ -13406,29 +13406,29 @@
       </c>
       <c r="F186" s="17" t="inlineStr">
         <is>
-          <t>Under 60.5</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="G186" s="26" t="n">
-        <v>60.5</v>
+        <v>51.5</v>
       </c>
       <c r="H186" s="18" t="n">
-        <v>-112</v>
+        <v>-102</v>
       </c>
       <c r="I186" s="20" t="n">
-        <v>0.5853985750253541</v>
+        <v>0.5635010598689705</v>
       </c>
       <c r="J186" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4826358742837298</v>
       </c>
       <c r="K186" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.504950495049505</v>
       </c>
       <c r="L186" s="19" t="n">
-        <v>0.05709668823290126</v>
+        <v>0.05855056481946552</v>
       </c>
       <c r="M186" s="19" t="n">
-        <v>0.1080758741551345</v>
+        <v>0.1159530793483533</v>
       </c>
       <c r="N186" s="20" t="n">
         <v>0</v>
@@ -13441,11 +13441,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q186" s="17" t="inlineStr">
-        <is>
-          <t>UAPB isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q186" s="17" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="12" t="inlineStr">
@@ -13455,12 +13451,12 @@
       </c>
       <c r="B187" s="12" t="inlineStr">
         <is>
-          <t>ARST @ MEM</t>
+          <t>UAPB @ MIZ</t>
         </is>
       </c>
       <c r="C187" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D187" s="22" t="n">
@@ -13468,34 +13464,34 @@
       </c>
       <c r="E187" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F187" s="12" t="inlineStr">
         <is>
-          <t>ARST +8.5</t>
+          <t>Under 60.5</t>
         </is>
       </c>
       <c r="G187" s="23" t="n">
-        <v>-8.5</v>
+        <v>60.5</v>
       </c>
       <c r="H187" s="13" t="n">
-        <v>-115</v>
+        <v>-112</v>
       </c>
       <c r="I187" s="15" t="n">
-        <v>0.5913843940444081</v>
+        <v>0.5853985750253541</v>
       </c>
       <c r="J187" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K187" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L187" s="14" t="n">
-        <v>0.05650067311417561</v>
+        <v>0.05709668823290126</v>
       </c>
       <c r="M187" s="14" t="n">
-        <v>0.1056316932134586</v>
+        <v>0.1080758741551345</v>
       </c>
       <c r="N187" s="15" t="n">
         <v>0</v>
@@ -13508,7 +13504,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q187" s="12" t="n"/>
+      <c r="Q187" s="12" t="inlineStr">
+        <is>
+          <t>UAPB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="17" t="inlineStr">
@@ -13707,7 +13707,7 @@
       </c>
       <c r="B191" s="12" t="inlineStr">
         <is>
-          <t>MOST @ TA&amp;M</t>
+          <t>ARST @ MEM</t>
         </is>
       </c>
       <c r="C191" s="12" t="inlineStr">
@@ -13720,34 +13720,32 @@
       </c>
       <c r="E191" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F191" s="12" t="inlineStr">
         <is>
-          <t>Over 52.5</t>
-        </is>
-      </c>
-      <c r="G191" s="23" t="n">
-        <v>52.5</v>
-      </c>
+          <t>ARST ML</t>
+        </is>
+      </c>
+      <c r="G191" s="23" t="n"/>
       <c r="H191" s="13" t="n">
-        <v>-110</v>
+        <v>270</v>
       </c>
       <c r="I191" s="15" t="n">
-        <v>0.575895930667786</v>
+        <v>0.3236757984270614</v>
       </c>
       <c r="J191" s="15" t="n">
-        <v>0.5</v>
+        <v>0.2591283863368669</v>
       </c>
       <c r="K191" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.2702702702702703</v>
       </c>
       <c r="L191" s="14" t="n">
-        <v>0.05208640685826216</v>
+        <v>0.05340552815679112</v>
       </c>
       <c r="M191" s="14" t="n">
-        <v>0.09943768582031876</v>
+        <v>0.1976004541801273</v>
       </c>
       <c r="N191" s="15" t="n">
         <v>0</v>
@@ -13770,12 +13768,12 @@
       </c>
       <c r="B192" s="17" t="inlineStr">
         <is>
-          <t>MORG @ ASU</t>
+          <t>MOST @ TA&amp;M</t>
         </is>
       </c>
       <c r="C192" s="17" t="inlineStr">
         <is>
-          <t>2026-09-06 02:00</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D192" s="25" t="n">
@@ -13795,22 +13793,22 @@
         <v>52.5</v>
       </c>
       <c r="H192" s="18" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I192" s="20" t="n">
-        <v>0.5799064644072576</v>
+        <v>0.575895930667786</v>
       </c>
       <c r="J192" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K192" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L192" s="19" t="n">
-        <v>0.05160457761480475</v>
+        <v>0.05208640685826216</v>
       </c>
       <c r="M192" s="19" t="n">
-        <v>0.09768009334230898</v>
+        <v>0.09943768582031876</v>
       </c>
       <c r="N192" s="20" t="n">
         <v>0</v>
@@ -13823,11 +13821,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q192" s="17" t="inlineStr">
-        <is>
-          <t>MORG isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q192" s="17" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="12" t="inlineStr">
@@ -13837,12 +13831,12 @@
       </c>
       <c r="B193" s="12" t="inlineStr">
         <is>
-          <t>WKU @ NEV</t>
+          <t>MORG @ ASU</t>
         </is>
       </c>
       <c r="C193" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 02:30</t>
+          <t>2026-09-06 02:00</t>
         </is>
       </c>
       <c r="D193" s="22" t="n">
@@ -13850,34 +13844,34 @@
       </c>
       <c r="E193" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F193" s="12" t="inlineStr">
         <is>
-          <t>NEV +2.5</t>
+          <t>Over 52.5</t>
         </is>
       </c>
       <c r="G193" s="23" t="n">
-        <v>2.5</v>
+        <v>52.5</v>
       </c>
       <c r="H193" s="13" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I193" s="15" t="n">
-        <v>0.5701862551785175</v>
+        <v>0.5799064644072576</v>
       </c>
       <c r="J193" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K193" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L193" s="14" t="n">
-        <v>0.05095548594774824</v>
+        <v>0.05160457761480475</v>
       </c>
       <c r="M193" s="14" t="n">
-        <v>0.09813649145492265</v>
+        <v>0.09768009334230898</v>
       </c>
       <c r="N193" s="15" t="n">
         <v>0</v>
@@ -13890,7 +13884,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q193" s="12" t="n"/>
+      <c r="Q193" s="12" t="inlineStr">
+        <is>
+          <t>MORG isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="17" t="inlineStr">
@@ -13900,12 +13898,12 @@
       </c>
       <c r="B194" s="17" t="inlineStr">
         <is>
-          <t>FIU @ USF</t>
+          <t>WKU @ NEV</t>
         </is>
       </c>
       <c r="C194" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-06 02:30</t>
         </is>
       </c>
       <c r="D194" s="25" t="n">
@@ -13913,34 +13911,34 @@
       </c>
       <c r="E194" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F194" s="17" t="inlineStr">
         <is>
-          <t>Over 53.5</t>
+          <t>NEV +2.5</t>
         </is>
       </c>
       <c r="G194" s="26" t="n">
-        <v>53.5</v>
+        <v>2.5</v>
       </c>
       <c r="H194" s="18" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="I194" s="20" t="n">
-        <v>0.5849969873979599</v>
+        <v>0.5701862551785175</v>
       </c>
       <c r="J194" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K194" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L194" s="19" t="n">
-        <v>0.0501132664677274</v>
+        <v>0.05095548594774824</v>
       </c>
       <c r="M194" s="19" t="n">
-        <v>0.09369001991792503</v>
+        <v>0.09813649145492265</v>
       </c>
       <c r="N194" s="20" t="n">
         <v>0</v>
@@ -13963,12 +13961,12 @@
       </c>
       <c r="B195" s="12" t="inlineStr">
         <is>
-          <t>NWST @ LT</t>
+          <t>FIU @ USF</t>
         </is>
       </c>
       <c r="C195" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D195" s="22" t="n">
@@ -13981,29 +13979,29 @@
       </c>
       <c r="F195" s="12" t="inlineStr">
         <is>
-          <t>Over 52.5</t>
+          <t>Over 53.5</t>
         </is>
       </c>
       <c r="G195" s="23" t="n">
-        <v>52.5</v>
+        <v>53.5</v>
       </c>
       <c r="H195" s="13" t="n">
-        <v>-112</v>
+        <v>-115</v>
       </c>
       <c r="I195" s="15" t="n">
-        <v>0.5780608077027705</v>
+        <v>0.5849969873979599</v>
       </c>
       <c r="J195" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K195" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L195" s="14" t="n">
-        <v>0.04975892091031764</v>
+        <v>0.0501132664677274</v>
       </c>
       <c r="M195" s="14" t="n">
-        <v>0.09418652886595835</v>
+        <v>0.09369001991792503</v>
       </c>
       <c r="N195" s="15" t="n">
         <v>0</v>
@@ -14016,11 +14014,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q195" s="12" t="inlineStr">
-        <is>
-          <t>NWST isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q195" s="12" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="17" t="inlineStr">
@@ -14030,12 +14024,12 @@
       </c>
       <c r="B196" s="17" t="inlineStr">
         <is>
-          <t>LIB @ JMU</t>
+          <t>NWST @ LT</t>
         </is>
       </c>
       <c r="C196" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D196" s="25" t="n">
@@ -14043,34 +14037,34 @@
       </c>
       <c r="E196" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F196" s="17" t="inlineStr">
         <is>
-          <t>LIB +6.5</t>
+          <t>Over 52.5</t>
         </is>
       </c>
       <c r="G196" s="26" t="n">
-        <v>-6.5</v>
+        <v>52.5</v>
       </c>
       <c r="H196" s="18" t="n">
-        <v>-105</v>
+        <v>-112</v>
       </c>
       <c r="I196" s="20" t="n">
-        <v>0.5567038915037148</v>
+        <v>0.5780608077027705</v>
       </c>
       <c r="J196" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K196" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L196" s="19" t="n">
-        <v>0.04450876955249528</v>
+        <v>0.04975892091031764</v>
       </c>
       <c r="M196" s="19" t="n">
-        <v>0.08689807388820503</v>
+        <v>0.09418652886595835</v>
       </c>
       <c r="N196" s="20" t="n">
         <v>0</v>
@@ -14083,7 +14077,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q196" s="17" t="n"/>
+      <c r="Q196" s="17" t="inlineStr">
+        <is>
+          <t>NWST isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="12" t="inlineStr">
@@ -14093,12 +14091,12 @@
       </c>
       <c r="B197" s="12" t="inlineStr">
         <is>
-          <t>WKU @ NEV</t>
+          <t>LIB @ JMU</t>
         </is>
       </c>
       <c r="C197" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 02:30</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D197" s="22" t="n">
@@ -14106,32 +14104,34 @@
       </c>
       <c r="E197" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F197" s="12" t="inlineStr">
         <is>
-          <t>NEV ML</t>
-        </is>
-      </c>
-      <c r="G197" s="23" t="n"/>
+          <t>LIB +6.5</t>
+        </is>
+      </c>
+      <c r="G197" s="23" t="n">
+        <v>-6.5</v>
+      </c>
       <c r="H197" s="13" t="n">
-        <v>110</v>
+        <v>-105</v>
       </c>
       <c r="I197" s="15" t="n">
-        <v>0.5205276562505744</v>
+        <v>0.5567038915037148</v>
       </c>
       <c r="J197" s="15" t="n">
-        <v>0.4572564612326044</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K197" s="15" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L197" s="14" t="n">
-        <v>0.04433718006009824</v>
+        <v>0.04450876955249528</v>
       </c>
       <c r="M197" s="14" t="n">
-        <v>0.09310807812620625</v>
+        <v>0.08689807388820503</v>
       </c>
       <c r="N197" s="15" t="n">
         <v>0</v>
@@ -14154,12 +14154,12 @@
       </c>
       <c r="B198" s="17" t="inlineStr">
         <is>
-          <t>BCU @ UCF</t>
+          <t>WKU @ NEV</t>
         </is>
       </c>
       <c r="C198" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-06 02:30</t>
         </is>
       </c>
       <c r="D198" s="25" t="n">
@@ -14167,34 +14167,32 @@
       </c>
       <c r="E198" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F198" s="17" t="inlineStr">
         <is>
-          <t>Under 59.5</t>
-        </is>
-      </c>
-      <c r="G198" s="26" t="n">
-        <v>59.5</v>
-      </c>
+          <t>NEV ML</t>
+        </is>
+      </c>
+      <c r="G198" s="26" t="n"/>
       <c r="H198" s="18" t="n">
-        <v>-108</v>
+        <v>110</v>
       </c>
       <c r="I198" s="20" t="n">
-        <v>0.5625111268567219</v>
+        <v>0.5205276562505744</v>
       </c>
       <c r="J198" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4572564612326044</v>
       </c>
       <c r="K198" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="L198" s="19" t="n">
-        <v>0.04328035762595261</v>
+        <v>0.04433718006009824</v>
       </c>
       <c r="M198" s="19" t="n">
-        <v>0.08335476283516818</v>
+        <v>0.09310807812620625</v>
       </c>
       <c r="N198" s="20" t="n">
         <v>0</v>
@@ -14207,11 +14205,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q198" s="17" t="inlineStr">
-        <is>
-          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q198" s="17" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="12" t="inlineStr">
@@ -14221,12 +14215,12 @@
       </c>
       <c r="B199" s="12" t="inlineStr">
         <is>
-          <t>ARST @ MEM</t>
+          <t>BCU @ UCF</t>
         </is>
       </c>
       <c r="C199" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D199" s="22" t="n">
@@ -14234,32 +14228,34 @@
       </c>
       <c r="E199" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F199" s="12" t="inlineStr">
         <is>
-          <t>ARST ML</t>
-        </is>
-      </c>
-      <c r="G199" s="23" t="n"/>
+          <t>Under 59.5</t>
+        </is>
+      </c>
+      <c r="G199" s="23" t="n">
+        <v>59.5</v>
+      </c>
       <c r="H199" s="13" t="n">
-        <v>245</v>
+        <v>-108</v>
       </c>
       <c r="I199" s="15" t="n">
-        <v>0.3330719758196161</v>
+        <v>0.5625111268567219</v>
       </c>
       <c r="J199" s="15" t="n">
-        <v>0.2779207411219763</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K199" s="15" t="n">
-        <v>0.2898550724637681</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L199" s="14" t="n">
-        <v>0.04321690335584799</v>
+        <v>0.04328035762595261</v>
       </c>
       <c r="M199" s="14" t="n">
-        <v>0.1490983165776757</v>
+        <v>0.08335476283516818</v>
       </c>
       <c r="N199" s="15" t="n">
         <v>0</v>
@@ -14272,7 +14268,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q199" s="12" t="n"/>
+      <c r="Q199" s="12" t="inlineStr">
+        <is>
+          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="17" t="inlineStr">
@@ -16665,12 +16665,12 @@
       </c>
       <c r="B237" s="12" t="inlineStr">
         <is>
-          <t>UAB @ ILL</t>
+          <t>VMI @ VT</t>
         </is>
       </c>
       <c r="C237" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 01:00</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D237" s="22" t="n">
@@ -16683,29 +16683,29 @@
       </c>
       <c r="F237" s="12" t="inlineStr">
         <is>
-          <t>Over 55.5</t>
+          <t>Under 57.5</t>
         </is>
       </c>
       <c r="G237" s="23" t="n">
-        <v>55.5</v>
+        <v>57.5</v>
       </c>
       <c r="H237" s="13" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="I237" s="15" t="n">
-        <v>0.5332636541647089</v>
+        <v>0.5177573173105776</v>
       </c>
       <c r="J237" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K237" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L237" s="14" t="n">
-        <v>-0.00162006676552362</v>
+        <v>-0.00147345192019166</v>
       </c>
       <c r="M237" s="14" t="n">
-        <v>-0.003028820474674732</v>
+        <v>-0.002837759253702332</v>
       </c>
       <c r="N237" s="15" t="n">
         <v>0</v>
@@ -16718,7 +16718,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q237" s="12" t="n"/>
+      <c r="Q237" s="12" t="inlineStr">
+        <is>
+          <t>VMI isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="17" t="inlineStr">
@@ -16728,12 +16732,12 @@
       </c>
       <c r="B238" s="17" t="inlineStr">
         <is>
-          <t>NORF @ ODU</t>
+          <t>UAB @ ILL</t>
         </is>
       </c>
       <c r="C238" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 22:00</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D238" s="25" t="n">
@@ -16753,22 +16757,22 @@
         <v>55.5</v>
       </c>
       <c r="H238" s="18" t="n">
-        <v>-105</v>
+        <v>-115</v>
       </c>
       <c r="I238" s="20" t="n">
-        <v>0.5105302032699688</v>
+        <v>0.5332636541647089</v>
       </c>
       <c r="J238" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K238" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L238" s="19" t="n">
-        <v>-0.001664918681250738</v>
+        <v>-0.00162006676552362</v>
       </c>
       <c r="M238" s="19" t="n">
-        <v>-0.003250555520537157</v>
+        <v>-0.003028820474674732</v>
       </c>
       <c r="N238" s="20" t="n">
         <v>0</v>
@@ -16781,11 +16785,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q238" s="17" t="inlineStr">
-        <is>
-          <t>NORF isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q238" s="17" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="12" t="inlineStr">
@@ -16795,12 +16795,12 @@
       </c>
       <c r="B239" s="12" t="inlineStr">
         <is>
-          <t>LAF @ CONN</t>
+          <t>NORF @ ODU</t>
         </is>
       </c>
       <c r="C239" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-09-05 22:00</t>
         </is>
       </c>
       <c r="D239" s="22" t="n">
@@ -16813,29 +16813,29 @@
       </c>
       <c r="F239" s="12" t="inlineStr">
         <is>
-          <t>Under 58.5</t>
+          <t>Over 55.5</t>
         </is>
       </c>
       <c r="G239" s="23" t="n">
-        <v>58.5</v>
+        <v>55.5</v>
       </c>
       <c r="H239" s="13" t="n">
-        <v>-115</v>
+        <v>-105</v>
       </c>
       <c r="I239" s="15" t="n">
-        <v>0.5312862336505164</v>
+        <v>0.5105302032699688</v>
       </c>
       <c r="J239" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K239" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L239" s="14" t="n">
-        <v>-0.003597487279716094</v>
+        <v>-0.001664918681250738</v>
       </c>
       <c r="M239" s="14" t="n">
-        <v>-0.00672573708816504</v>
+        <v>-0.003250555520537157</v>
       </c>
       <c r="N239" s="15" t="n">
         <v>0</v>
@@ -16850,7 +16850,7 @@
       </c>
       <c r="Q239" s="12" t="inlineStr">
         <is>
-          <t>LAF isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>NORF isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -16862,7 +16862,7 @@
       </c>
       <c r="B240" s="17" t="inlineStr">
         <is>
-          <t>TAR @ BGSU</t>
+          <t>LAF @ CONN</t>
         </is>
       </c>
       <c r="C240" s="17" t="inlineStr">
@@ -16875,32 +16875,34 @@
       </c>
       <c r="E240" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F240" s="17" t="inlineStr">
         <is>
-          <t>BGSU ML</t>
-        </is>
-      </c>
-      <c r="G240" s="26" t="n"/>
+          <t>Under 58.5</t>
+        </is>
+      </c>
+      <c r="G240" s="26" t="n">
+        <v>58.5</v>
+      </c>
       <c r="H240" s="18" t="n">
-        <v>-135</v>
+        <v>-115</v>
       </c>
       <c r="I240" s="20" t="n">
-        <v>0.5676199829925468</v>
+        <v>0.5312862336505164</v>
       </c>
       <c r="J240" s="20" t="n">
-        <v>0.551441114716549</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K240" s="20" t="n">
-        <v>0.574468085106383</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L240" s="19" t="n">
-        <v>-0.006848102113836241</v>
+        <v>-0.003597487279716094</v>
       </c>
       <c r="M240" s="19" t="n">
-        <v>-0.01192077034630745</v>
+        <v>-0.00672573708816504</v>
       </c>
       <c r="N240" s="20" t="n">
         <v>0</v>
@@ -16915,7 +16917,7 @@
       </c>
       <c r="Q240" s="17" t="inlineStr">
         <is>
-          <t>TAR isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>LAF isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -16927,12 +16929,12 @@
       </c>
       <c r="B241" s="12" t="inlineStr">
         <is>
-          <t>WYO @ CSU</t>
+          <t>TAR @ BGSU</t>
         </is>
       </c>
       <c r="C241" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 22:00</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D241" s="22" t="n">
@@ -16945,27 +16947,27 @@
       </c>
       <c r="F241" s="12" t="inlineStr">
         <is>
-          <t>WYO ML</t>
+          <t>BGSU ML</t>
         </is>
       </c>
       <c r="G241" s="23" t="n"/>
       <c r="H241" s="13" t="n">
-        <v>142</v>
+        <v>-135</v>
       </c>
       <c r="I241" s="15" t="n">
-        <v>0.4062220888946388</v>
+        <v>0.5676199829925468</v>
       </c>
       <c r="J241" s="15" t="n">
-        <v>0.3962430290578221</v>
+        <v>0.551441114716549</v>
       </c>
       <c r="K241" s="15" t="n">
-        <v>0.4132231404958678</v>
+        <v>0.574468085106383</v>
       </c>
       <c r="L241" s="14" t="n">
-        <v>-0.007001051601228936</v>
+        <v>-0.006848102113836241</v>
       </c>
       <c r="M241" s="14" t="n">
-        <v>-0.01694254487497404</v>
+        <v>-0.01192077034630745</v>
       </c>
       <c r="N241" s="15" t="n">
         <v>0</v>
@@ -16978,7 +16980,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q241" s="12" t="n"/>
+      <c r="Q241" s="12" t="inlineStr">
+        <is>
+          <t>TAR isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="17" t="inlineStr">
@@ -16988,12 +16994,12 @@
       </c>
       <c r="B242" s="17" t="inlineStr">
         <is>
-          <t>VMI @ VT</t>
+          <t>WYO @ CSU</t>
         </is>
       </c>
       <c r="C242" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-09-05 22:00</t>
         </is>
       </c>
       <c r="D242" s="25" t="n">
@@ -17001,34 +17007,32 @@
       </c>
       <c r="E242" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F242" s="17" t="inlineStr">
         <is>
-          <t>Under 57.5</t>
-        </is>
-      </c>
-      <c r="G242" s="26" t="n">
-        <v>57.5</v>
-      </c>
+          <t>WYO ML</t>
+        </is>
+      </c>
+      <c r="G242" s="26" t="n"/>
       <c r="H242" s="18" t="n">
-        <v>-115</v>
+        <v>142</v>
       </c>
       <c r="I242" s="20" t="n">
-        <v>0.5253393124387365</v>
+        <v>0.4062220888946388</v>
       </c>
       <c r="J242" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.3962430290578221</v>
       </c>
       <c r="K242" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.4132231404958678</v>
       </c>
       <c r="L242" s="19" t="n">
-        <v>-0.009544408491495959</v>
+        <v>-0.007001051601228936</v>
       </c>
       <c r="M242" s="19" t="n">
-        <v>-0.01784389413627524</v>
+        <v>-0.01694254487497404</v>
       </c>
       <c r="N242" s="20" t="n">
         <v>0</v>
@@ -17041,11 +17045,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q242" s="17" t="inlineStr">
-        <is>
-          <t>VMI isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q242" s="17" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="12" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="B243" s="12" t="inlineStr">
         <is>
-          <t>IDHO @ UTAH</t>
+          <t>WYO @ CSU</t>
         </is>
       </c>
       <c r="C243" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 01:00</t>
+          <t>2026-09-05 22:00</t>
         </is>
       </c>
       <c r="D243" s="22" t="n">
@@ -17068,37 +17068,37 @@
       </c>
       <c r="E243" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F243" s="12" t="inlineStr">
         <is>
-          <t>Over 56.5</t>
+          <t>WYO +3</t>
         </is>
       </c>
       <c r="G243" s="23" t="n">
-        <v>56.5</v>
+        <v>-3</v>
       </c>
       <c r="H243" s="13" t="n">
-        <v>-108</v>
+        <v>-102</v>
       </c>
       <c r="I243" s="15" t="n">
-        <v>0.5078086811187539</v>
+        <v>0.4968911314192193</v>
       </c>
       <c r="J243" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4826358742837298</v>
       </c>
       <c r="K243" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.504950495049505</v>
       </c>
       <c r="L243" s="14" t="n">
-        <v>-0.01142208811201539</v>
+        <v>-0.008059363630285699</v>
       </c>
       <c r="M243" s="14" t="n">
-        <v>-0.02199809562314065</v>
+        <v>-0.0149861170161561</v>
       </c>
       <c r="N243" s="15" t="n">
-        <v>0</v>
+        <v>0.0611</v>
       </c>
       <c r="O243" s="24" t="n">
         <v>0.4</v>
@@ -17108,11 +17108,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q243" s="12" t="inlineStr">
-        <is>
-          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q243" s="12" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="17" t="inlineStr">
@@ -17122,12 +17118,12 @@
       </c>
       <c r="B244" s="17" t="inlineStr">
         <is>
-          <t>ULM @ MSST</t>
+          <t>IDHO @ UTAH</t>
         </is>
       </c>
       <c r="C244" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D244" s="25" t="n">
@@ -17147,22 +17143,22 @@
         <v>56.5</v>
       </c>
       <c r="H244" s="18" t="n">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="I244" s="20" t="n">
-        <v>0.4985737034822255</v>
+        <v>0.5078086811187539</v>
       </c>
       <c r="J244" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K244" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L244" s="19" t="n">
-        <v>-0.01362141846899401</v>
+        <v>-0.01142208811201539</v>
       </c>
       <c r="M244" s="19" t="n">
-        <v>-0.026594197963274</v>
+        <v>-0.02199809562314065</v>
       </c>
       <c r="N244" s="20" t="n">
         <v>0</v>
@@ -17175,7 +17171,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q244" s="17" t="n"/>
+      <c r="Q244" s="17" t="inlineStr">
+        <is>
+          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="12" t="inlineStr">
@@ -17185,12 +17185,12 @@
       </c>
       <c r="B245" s="12" t="inlineStr">
         <is>
-          <t>WYO @ CSU</t>
+          <t>ULM @ MSST</t>
         </is>
       </c>
       <c r="C245" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 22:00</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D245" s="22" t="n">
@@ -17198,34 +17198,34 @@
       </c>
       <c r="E245" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F245" s="12" t="inlineStr">
         <is>
-          <t>WYO +3.5</t>
+          <t>Over 56.5</t>
         </is>
       </c>
       <c r="G245" s="23" t="n">
-        <v>-3.5</v>
+        <v>56.5</v>
       </c>
       <c r="H245" s="13" t="n">
-        <v>-120</v>
+        <v>-105</v>
       </c>
       <c r="I245" s="15" t="n">
-        <v>0.5313678145122812</v>
+        <v>0.4985737034822255</v>
       </c>
       <c r="J245" s="15" t="n">
-        <v>0.5217391304347826</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K245" s="15" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L245" s="14" t="n">
-        <v>-0.0140867309422642</v>
+        <v>-0.01362141846899401</v>
       </c>
       <c r="M245" s="14" t="n">
-        <v>-0.02582567339415104</v>
+        <v>-0.026594197963274</v>
       </c>
       <c r="N245" s="15" t="n">
         <v>0</v>
@@ -18111,12 +18111,12 @@
       </c>
       <c r="B259" s="12" t="inlineStr">
         <is>
-          <t>WYO @ CSU</t>
+          <t>TAR @ BGSU</t>
         </is>
       </c>
       <c r="C259" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 22:00</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D259" s="22" t="n">
@@ -18129,29 +18129,29 @@
       </c>
       <c r="F259" s="12" t="inlineStr">
         <is>
-          <t>CSU -3.5</t>
+          <t>TAR +2.5</t>
         </is>
       </c>
       <c r="G259" s="23" t="n">
-        <v>-3.5</v>
+        <v>-2.5</v>
       </c>
       <c r="H259" s="13" t="n">
-        <v>100</v>
+        <v>-108</v>
       </c>
       <c r="I259" s="15" t="n">
-        <v>0.4686321854877188</v>
+        <v>0.4878026475846601</v>
       </c>
       <c r="J259" s="15" t="n">
-        <v>0.4782608695652174</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K259" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L259" s="14" t="n">
-        <v>-0.03136781451228121</v>
+        <v>-0.0314281216461092</v>
       </c>
       <c r="M259" s="14" t="n">
-        <v>-0.06273562902456242</v>
+        <v>-0.06052823428139537</v>
       </c>
       <c r="N259" s="15" t="n">
         <v>0</v>
@@ -18164,7 +18164,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q259" s="12" t="n"/>
+      <c r="Q259" s="12" t="inlineStr">
+        <is>
+          <t>TAR isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="17" t="inlineStr">
@@ -18174,12 +18178,12 @@
       </c>
       <c r="B260" s="17" t="inlineStr">
         <is>
-          <t>TAR @ BGSU</t>
+          <t>ULM @ MSST</t>
         </is>
       </c>
       <c r="C260" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D260" s="25" t="n">
@@ -18187,34 +18191,34 @@
       </c>
       <c r="E260" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F260" s="17" t="inlineStr">
         <is>
-          <t>TAR +2.5</t>
+          <t>Under 56.5</t>
         </is>
       </c>
       <c r="G260" s="26" t="n">
-        <v>-2.5</v>
+        <v>56.5</v>
       </c>
       <c r="H260" s="18" t="n">
-        <v>-108</v>
+        <v>-115</v>
       </c>
       <c r="I260" s="20" t="n">
-        <v>0.4878026475846601</v>
+        <v>0.5014262965177745</v>
       </c>
       <c r="J260" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K260" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L260" s="19" t="n">
-        <v>-0.0314281216461092</v>
+        <v>-0.03345742441245803</v>
       </c>
       <c r="M260" s="19" t="n">
-        <v>-0.06052823428139537</v>
+        <v>-0.06255083694503039</v>
       </c>
       <c r="N260" s="20" t="n">
         <v>0</v>
@@ -18227,11 +18231,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q260" s="17" t="inlineStr">
-        <is>
-          <t>TAR isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q260" s="17" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="12" t="inlineStr">
@@ -18241,12 +18241,12 @@
       </c>
       <c r="B261" s="12" t="inlineStr">
         <is>
-          <t>ULM @ MSST</t>
+          <t>TAR @ BGSU</t>
         </is>
       </c>
       <c r="C261" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D261" s="22" t="n">
@@ -18254,34 +18254,32 @@
       </c>
       <c r="E261" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F261" s="12" t="inlineStr">
         <is>
-          <t>Under 56.5</t>
-        </is>
-      </c>
-      <c r="G261" s="23" t="n">
-        <v>56.5</v>
-      </c>
+          <t>TAR ML</t>
+        </is>
+      </c>
+      <c r="G261" s="23" t="n"/>
       <c r="H261" s="13" t="n">
-        <v>-115</v>
+        <v>114</v>
       </c>
       <c r="I261" s="15" t="n">
-        <v>0.5014262965177745</v>
+        <v>0.4323800170074532</v>
       </c>
       <c r="J261" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.448558885283451</v>
       </c>
       <c r="K261" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.4672897196261682</v>
       </c>
       <c r="L261" s="14" t="n">
-        <v>-0.03345742441245803</v>
+        <v>-0.03490970261871501</v>
       </c>
       <c r="M261" s="14" t="n">
-        <v>-0.06255083694503039</v>
+        <v>-0.07470676360405026</v>
       </c>
       <c r="N261" s="15" t="n">
         <v>0</v>
@@ -18294,7 +18292,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q261" s="12" t="n"/>
+      <c r="Q261" s="12" t="inlineStr">
+        <is>
+          <t>TAR isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="17" t="inlineStr">
@@ -18304,12 +18306,12 @@
       </c>
       <c r="B262" s="17" t="inlineStr">
         <is>
-          <t>TAR @ BGSU</t>
+          <t>WYO @ CSU</t>
         </is>
       </c>
       <c r="C262" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-09-05 22:00</t>
         </is>
       </c>
       <c r="D262" s="25" t="n">
@@ -18322,27 +18324,27 @@
       </c>
       <c r="F262" s="17" t="inlineStr">
         <is>
-          <t>TAR ML</t>
+          <t>CSU ML</t>
         </is>
       </c>
       <c r="G262" s="26" t="n"/>
       <c r="H262" s="18" t="n">
-        <v>114</v>
+        <v>-170</v>
       </c>
       <c r="I262" s="20" t="n">
-        <v>0.4323800170074532</v>
+        <v>0.5937779111053612</v>
       </c>
       <c r="J262" s="20" t="n">
-        <v>0.448558885283451</v>
+        <v>0.6037569709421778</v>
       </c>
       <c r="K262" s="20" t="n">
-        <v>0.4672897196261682</v>
+        <v>0.6296296296296297</v>
       </c>
       <c r="L262" s="19" t="n">
-        <v>-0.03490970261871501</v>
+        <v>-0.03585171852426849</v>
       </c>
       <c r="M262" s="19" t="n">
-        <v>-0.07470676360405026</v>
+        <v>-0.05694096471501453</v>
       </c>
       <c r="N262" s="20" t="n">
         <v>0</v>
@@ -18355,11 +18357,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q262" s="17" t="inlineStr">
-        <is>
-          <t>TAR isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q262" s="17" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="12" t="inlineStr">
@@ -18369,12 +18367,12 @@
       </c>
       <c r="B263" s="12" t="inlineStr">
         <is>
-          <t>WYO @ CSU</t>
+          <t>IDHO @ UTAH</t>
         </is>
       </c>
       <c r="C263" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 22:00</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D263" s="22" t="n">
@@ -18382,32 +18380,34 @@
       </c>
       <c r="E263" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F263" s="12" t="inlineStr">
         <is>
-          <t>CSU ML</t>
-        </is>
-      </c>
-      <c r="G263" s="23" t="n"/>
+          <t>Under 56.5</t>
+        </is>
+      </c>
+      <c r="G263" s="23" t="n">
+        <v>56.5</v>
+      </c>
       <c r="H263" s="13" t="n">
-        <v>-170</v>
+        <v>-112</v>
       </c>
       <c r="I263" s="15" t="n">
-        <v>0.5937779111053612</v>
+        <v>0.4921913188812461</v>
       </c>
       <c r="J263" s="15" t="n">
-        <v>0.6037569709421778</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K263" s="15" t="n">
-        <v>0.6296296296296297</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L263" s="14" t="n">
-        <v>-0.03585171852426849</v>
+        <v>-0.0361105679112067</v>
       </c>
       <c r="M263" s="14" t="n">
-        <v>-0.05694096471501453</v>
+        <v>-0.06835214640335557</v>
       </c>
       <c r="N263" s="15" t="n">
         <v>0</v>
@@ -18420,7 +18420,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q263" s="12" t="n"/>
+      <c r="Q263" s="12" t="inlineStr">
+        <is>
+          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="17" t="inlineStr">
@@ -18430,12 +18434,12 @@
       </c>
       <c r="B264" s="17" t="inlineStr">
         <is>
-          <t>IDHO @ UTAH</t>
+          <t>WYO @ CSU</t>
         </is>
       </c>
       <c r="C264" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 01:00</t>
+          <t>2026-09-05 22:00</t>
         </is>
       </c>
       <c r="D264" s="25" t="n">
@@ -18443,37 +18447,37 @@
       </c>
       <c r="E264" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F264" s="17" t="inlineStr">
         <is>
-          <t>Under 56.5</t>
+          <t>CSU -3</t>
         </is>
       </c>
       <c r="G264" s="26" t="n">
-        <v>56.5</v>
+        <v>-3</v>
       </c>
       <c r="H264" s="18" t="n">
-        <v>-112</v>
+        <v>-118</v>
       </c>
       <c r="I264" s="20" t="n">
-        <v>0.4921913188812461</v>
+        <v>0.5031088685807807</v>
       </c>
       <c r="J264" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5173641257162701</v>
       </c>
       <c r="K264" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5412844036697247</v>
       </c>
       <c r="L264" s="19" t="n">
-        <v>-0.0361105679112067</v>
+        <v>-0.038175535088944</v>
       </c>
       <c r="M264" s="19" t="n">
-        <v>-0.06835214640335557</v>
+        <v>-0.06622116089743058</v>
       </c>
       <c r="N264" s="20" t="n">
-        <v>0</v>
+        <v>0.0611</v>
       </c>
       <c r="O264" s="27" t="n">
         <v>0.4</v>
@@ -18483,11 +18487,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q264" s="17" t="inlineStr">
-        <is>
-          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q264" s="17" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="12" t="inlineStr">
@@ -18497,12 +18497,12 @@
       </c>
       <c r="B265" s="12" t="inlineStr">
         <is>
-          <t>VMI @ VT</t>
+          <t>LAF @ CONN</t>
         </is>
       </c>
       <c r="C265" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D265" s="22" t="n">
@@ -18515,17 +18515,17 @@
       </c>
       <c r="F265" s="12" t="inlineStr">
         <is>
-          <t>Over 57.5</t>
+          <t>Over 58.5</t>
         </is>
       </c>
       <c r="G265" s="23" t="n">
-        <v>57.5</v>
+        <v>58.5</v>
       </c>
       <c r="H265" s="13" t="n">
         <v>-105</v>
       </c>
       <c r="I265" s="15" t="n">
-        <v>0.4746606875612635</v>
+        <v>0.4687137663494835</v>
       </c>
       <c r="J265" s="15" t="n">
         <v>0.4891657638136511</v>
@@ -18534,10 +18534,10 @@
         <v>0.5121951219512195</v>
       </c>
       <c r="L265" s="14" t="n">
-        <v>-0.03753443438995607</v>
+        <v>-0.04348135560173599</v>
       </c>
       <c r="M265" s="14" t="n">
-        <v>-0.07328151476134281</v>
+        <v>-0.0848921704605321</v>
       </c>
       <c r="N265" s="15" t="n">
         <v>0</v>
@@ -18552,7 +18552,7 @@
       </c>
       <c r="Q265" s="12" t="inlineStr">
         <is>
-          <t>VMI isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>LAF isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -18564,12 +18564,12 @@
       </c>
       <c r="B266" s="17" t="inlineStr">
         <is>
-          <t>LAF @ CONN</t>
+          <t>NORF @ ODU</t>
         </is>
       </c>
       <c r="C266" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-09-05 22:00</t>
         </is>
       </c>
       <c r="D266" s="25" t="n">
@@ -18582,29 +18582,29 @@
       </c>
       <c r="F266" s="17" t="inlineStr">
         <is>
-          <t>Over 58.5</t>
+          <t>Under 55.5</t>
         </is>
       </c>
       <c r="G266" s="26" t="n">
-        <v>58.5</v>
+        <v>55.5</v>
       </c>
       <c r="H266" s="18" t="n">
-        <v>-105</v>
+        <v>-115</v>
       </c>
       <c r="I266" s="20" t="n">
-        <v>0.4687137663494835</v>
+        <v>0.4894697967300312</v>
       </c>
       <c r="J266" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K266" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L266" s="19" t="n">
-        <v>-0.04348135560173599</v>
+        <v>-0.04541392420020129</v>
       </c>
       <c r="M266" s="19" t="n">
-        <v>-0.0848921704605321</v>
+        <v>-0.08490429306994168</v>
       </c>
       <c r="N266" s="20" t="n">
         <v>0</v>
@@ -18619,7 +18619,7 @@
       </c>
       <c r="Q266" s="17" t="inlineStr">
         <is>
-          <t>LAF isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>NORF isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -18631,12 +18631,12 @@
       </c>
       <c r="B267" s="12" t="inlineStr">
         <is>
-          <t>NORF @ ODU</t>
+          <t>UAB @ ILL</t>
         </is>
       </c>
       <c r="C267" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 22:00</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D267" s="22" t="n">
@@ -18656,22 +18656,22 @@
         <v>55.5</v>
       </c>
       <c r="H267" s="13" t="n">
-        <v>-115</v>
+        <v>-105</v>
       </c>
       <c r="I267" s="15" t="n">
-        <v>0.4894697967300312</v>
+        <v>0.4667363458352911</v>
       </c>
       <c r="J267" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K267" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L267" s="14" t="n">
-        <v>-0.04541392420020129</v>
+        <v>-0.04545877611592841</v>
       </c>
       <c r="M267" s="14" t="n">
-        <v>-0.08490429306994168</v>
+        <v>-0.08875284860728883</v>
       </c>
       <c r="N267" s="15" t="n">
         <v>0</v>
@@ -18684,11 +18684,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q267" s="12" t="inlineStr">
-        <is>
-          <t>NORF isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q267" s="12" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="17" t="inlineStr">
@@ -18698,12 +18694,12 @@
       </c>
       <c r="B268" s="17" t="inlineStr">
         <is>
-          <t>UAB @ ILL</t>
+          <t>VMI @ VT</t>
         </is>
       </c>
       <c r="C268" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 01:00</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D268" s="25" t="n">
@@ -18716,29 +18712,29 @@
       </c>
       <c r="F268" s="17" t="inlineStr">
         <is>
-          <t>Under 55.5</t>
+          <t>Over 57.5</t>
         </is>
       </c>
       <c r="G268" s="26" t="n">
-        <v>55.5</v>
+        <v>57.5</v>
       </c>
       <c r="H268" s="18" t="n">
-        <v>-105</v>
+        <v>-112</v>
       </c>
       <c r="I268" s="20" t="n">
-        <v>0.4667363458352911</v>
+        <v>0.4822426826894223</v>
       </c>
       <c r="J268" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K268" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L268" s="19" t="n">
-        <v>-0.04545877611592841</v>
+        <v>-0.04605920410303049</v>
       </c>
       <c r="M268" s="19" t="n">
-        <v>-0.08875284860728883</v>
+        <v>-0.08718349348073628</v>
       </c>
       <c r="N268" s="20" t="n">
         <v>0</v>
@@ -18751,7 +18747,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q268" s="17" t="n"/>
+      <c r="Q268" s="17" t="inlineStr">
+        <is>
+          <t>VMI isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="12" t="inlineStr">
@@ -21077,12 +21077,12 @@
       </c>
       <c r="B305" s="12" t="inlineStr">
         <is>
-          <t>ARST @ MEM</t>
+          <t>LIB @ JMU</t>
         </is>
       </c>
       <c r="C305" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D305" s="22" t="n">
@@ -21095,27 +21095,27 @@
       </c>
       <c r="F305" s="12" t="inlineStr">
         <is>
-          <t>MEM ML</t>
+          <t>JMU ML</t>
         </is>
       </c>
       <c r="G305" s="23" t="n"/>
       <c r="H305" s="13" t="n">
-        <v>-305</v>
+        <v>-265</v>
       </c>
       <c r="I305" s="15" t="n">
-        <v>0.6669280241803839</v>
+        <v>0.6397844016709466</v>
       </c>
       <c r="J305" s="15" t="n">
-        <v>0.7220792588780237</v>
+        <v>0.6957699520733487</v>
       </c>
       <c r="K305" s="15" t="n">
-        <v>0.7530864197530864</v>
+        <v>0.726027397260274</v>
       </c>
       <c r="L305" s="14" t="n">
-        <v>-0.08615839557270255</v>
+        <v>-0.08624299558932735</v>
       </c>
       <c r="M305" s="14" t="n">
-        <v>-0.1144070498588346</v>
+        <v>-0.1187875222268094</v>
       </c>
       <c r="N305" s="15" t="n">
         <v>0</v>
@@ -21138,12 +21138,12 @@
       </c>
       <c r="B306" s="17" t="inlineStr">
         <is>
-          <t>LIB @ JMU</t>
+          <t>TOW @ NAVY</t>
         </is>
       </c>
       <c r="C306" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D306" s="25" t="n">
@@ -21151,32 +21151,34 @@
       </c>
       <c r="E306" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F306" s="17" t="inlineStr">
         <is>
-          <t>JMU ML</t>
-        </is>
-      </c>
-      <c r="G306" s="26" t="n"/>
+          <t>Under 53.5</t>
+        </is>
+      </c>
+      <c r="G306" s="26" t="n">
+        <v>53.5</v>
+      </c>
       <c r="H306" s="18" t="n">
-        <v>-265</v>
+        <v>-112</v>
       </c>
       <c r="I306" s="20" t="n">
-        <v>0.6397844016709466</v>
+        <v>0.4393816679461898</v>
       </c>
       <c r="J306" s="20" t="n">
-        <v>0.6957699520733487</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K306" s="20" t="n">
-        <v>0.726027397260274</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L306" s="19" t="n">
-        <v>-0.08624299558932735</v>
+        <v>-0.088920218846263</v>
       </c>
       <c r="M306" s="19" t="n">
-        <v>-0.1187875222268094</v>
+        <v>-0.1683132713875693</v>
       </c>
       <c r="N306" s="20" t="n">
         <v>0</v>
@@ -21189,7 +21191,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q306" s="17" t="n"/>
+      <c r="Q306" s="17" t="inlineStr">
+        <is>
+          <t>TOW isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="12" t="inlineStr">
@@ -21199,12 +21205,12 @@
       </c>
       <c r="B307" s="12" t="inlineStr">
         <is>
-          <t>TOW @ NAVY</t>
+          <t>BCU @ UCF</t>
         </is>
       </c>
       <c r="C307" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D307" s="22" t="n">
@@ -21217,17 +21223,17 @@
       </c>
       <c r="F307" s="12" t="inlineStr">
         <is>
-          <t>Under 53.5</t>
+          <t>Over 59.5</t>
         </is>
       </c>
       <c r="G307" s="23" t="n">
-        <v>53.5</v>
+        <v>59.5</v>
       </c>
       <c r="H307" s="13" t="n">
         <v>-112</v>
       </c>
       <c r="I307" s="15" t="n">
-        <v>0.4393816679461898</v>
+        <v>0.4374888731432781</v>
       </c>
       <c r="J307" s="15" t="n">
         <v>0.5043297540699688</v>
@@ -21236,10 +21242,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L307" s="14" t="n">
-        <v>-0.088920218846263</v>
+        <v>-0.09081301364917471</v>
       </c>
       <c r="M307" s="14" t="n">
-        <v>-0.1683132713875693</v>
+        <v>-0.1718960615502236</v>
       </c>
       <c r="N307" s="15" t="n">
         <v>0</v>
@@ -21254,7 +21260,7 @@
       </c>
       <c r="Q307" s="12" t="inlineStr">
         <is>
-          <t>TOW isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -21266,12 +21272,12 @@
       </c>
       <c r="B308" s="17" t="inlineStr">
         <is>
-          <t>BCU @ UCF</t>
+          <t>LIB @ JMU</t>
         </is>
       </c>
       <c r="C308" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D308" s="25" t="n">
@@ -21279,34 +21285,34 @@
       </c>
       <c r="E308" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F308" s="17" t="inlineStr">
         <is>
-          <t>Over 59.5</t>
+          <t>JMU -6.5</t>
         </is>
       </c>
       <c r="G308" s="26" t="n">
-        <v>59.5</v>
+        <v>-6.5</v>
       </c>
       <c r="H308" s="18" t="n">
-        <v>-112</v>
+        <v>-115</v>
       </c>
       <c r="I308" s="20" t="n">
-        <v>0.4374888731432781</v>
+        <v>0.4432961084962852</v>
       </c>
       <c r="J308" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K308" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L308" s="19" t="n">
-        <v>-0.09081301364917471</v>
+        <v>-0.09158761243394731</v>
       </c>
       <c r="M308" s="19" t="n">
-        <v>-0.1718960615502236</v>
+        <v>-0.1712290145504234</v>
       </c>
       <c r="N308" s="20" t="n">
         <v>0</v>
@@ -21319,11 +21325,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q308" s="17" t="inlineStr">
-        <is>
-          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q308" s="17" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="12" t="inlineStr">
@@ -21333,12 +21335,12 @@
       </c>
       <c r="B309" s="12" t="inlineStr">
         <is>
-          <t>LIB @ JMU</t>
+          <t>ARST @ MEM</t>
         </is>
       </c>
       <c r="C309" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D309" s="22" t="n">
@@ -21346,34 +21348,32 @@
       </c>
       <c r="E309" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F309" s="12" t="inlineStr">
         <is>
-          <t>JMU -6.5</t>
-        </is>
-      </c>
-      <c r="G309" s="23" t="n">
-        <v>-6.5</v>
-      </c>
+          <t>MEM ML</t>
+        </is>
+      </c>
+      <c r="G309" s="23" t="n"/>
       <c r="H309" s="13" t="n">
-        <v>-115</v>
+        <v>-340</v>
       </c>
       <c r="I309" s="15" t="n">
-        <v>0.4432961084962852</v>
+        <v>0.6763242015729386</v>
       </c>
       <c r="J309" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.740871613663133</v>
       </c>
       <c r="K309" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="L309" s="14" t="n">
-        <v>-0.09158761243394731</v>
+        <v>-0.09640307115433411</v>
       </c>
       <c r="M309" s="14" t="n">
-        <v>-0.1712290145504234</v>
+        <v>-0.1247569156114912</v>
       </c>
       <c r="N309" s="15" t="n">
         <v>0</v>
@@ -21969,12 +21969,12 @@
       </c>
       <c r="B319" s="12" t="inlineStr">
         <is>
-          <t>ARST @ MEM</t>
+          <t>UAPB @ MIZ</t>
         </is>
       </c>
       <c r="C319" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D319" s="22" t="n">
@@ -21982,34 +21982,34 @@
       </c>
       <c r="E319" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F319" s="12" t="inlineStr">
         <is>
-          <t>MEM -8.5</t>
+          <t>Over 60.5</t>
         </is>
       </c>
       <c r="G319" s="23" t="n">
-        <v>-8.5</v>
+        <v>60.5</v>
       </c>
       <c r="H319" s="13" t="n">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="I319" s="15" t="n">
-        <v>0.4086156059555919</v>
+        <v>0.4146014249746459</v>
       </c>
       <c r="J319" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K319" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L319" s="14" t="n">
-        <v>-0.1035795159956276</v>
+        <v>-0.1046293442561234</v>
       </c>
       <c r="M319" s="14" t="n">
-        <v>-0.2022266740867016</v>
+        <v>-0.2015083667154967</v>
       </c>
       <c r="N319" s="15" t="n">
         <v>0</v>
@@ -22022,7 +22022,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q319" s="12" t="n"/>
+      <c r="Q319" s="12" t="inlineStr">
+        <is>
+          <t>UAPB isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="17" t="inlineStr">
@@ -22032,12 +22036,12 @@
       </c>
       <c r="B320" s="17" t="inlineStr">
         <is>
-          <t>UAPB @ MIZ</t>
+          <t>CLEM @ LSU</t>
         </is>
       </c>
       <c r="C320" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D320" s="25" t="n">
@@ -22050,29 +22054,29 @@
       </c>
       <c r="F320" s="17" t="inlineStr">
         <is>
-          <t>Over 60.5</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="G320" s="26" t="n">
-        <v>60.5</v>
+        <v>51.5</v>
       </c>
       <c r="H320" s="18" t="n">
-        <v>-108</v>
+        <v>-118</v>
       </c>
       <c r="I320" s="20" t="n">
-        <v>0.4146014249746459</v>
+        <v>0.4364989401310295</v>
       </c>
       <c r="J320" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5173641257162701</v>
       </c>
       <c r="K320" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5412844036697247</v>
       </c>
       <c r="L320" s="19" t="n">
-        <v>-0.1046293442561234</v>
+        <v>-0.1047854635386952</v>
       </c>
       <c r="M320" s="19" t="n">
-        <v>-0.2015083667154967</v>
+        <v>-0.1935867038257251</v>
       </c>
       <c r="N320" s="20" t="n">
         <v>0</v>
@@ -22085,11 +22089,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q320" s="17" t="inlineStr">
-        <is>
-          <t>UAPB isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q320" s="17" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="12" t="inlineStr">
@@ -22099,12 +22099,12 @@
       </c>
       <c r="B321" s="12" t="inlineStr">
         <is>
-          <t>CLEM @ LSU</t>
+          <t>APSU @ VAN</t>
         </is>
       </c>
       <c r="C321" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D321" s="22" t="n">
@@ -22117,29 +22117,29 @@
       </c>
       <c r="F321" s="12" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>Over 61.5</t>
         </is>
       </c>
       <c r="G321" s="23" t="n">
-        <v>51.5</v>
+        <v>61.5</v>
       </c>
       <c r="H321" s="13" t="n">
-        <v>-118</v>
+        <v>-108</v>
       </c>
       <c r="I321" s="15" t="n">
-        <v>0.4364989401310295</v>
+        <v>0.4127861775763615</v>
       </c>
       <c r="J321" s="15" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K321" s="15" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L321" s="14" t="n">
-        <v>-0.1047854635386952</v>
+        <v>-0.1064445916544078</v>
       </c>
       <c r="M321" s="14" t="n">
-        <v>-0.1935867038257251</v>
+        <v>-0.2050043987418222</v>
       </c>
       <c r="N321" s="15" t="n">
         <v>0</v>
@@ -22152,7 +22152,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q321" s="12" t="n"/>
+      <c r="Q321" s="12" t="inlineStr">
+        <is>
+          <t>APSU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="17" t="inlineStr">
@@ -22162,12 +22166,12 @@
       </c>
       <c r="B322" s="17" t="inlineStr">
         <is>
-          <t>APSU @ VAN</t>
+          <t>BOIS @ ORE</t>
         </is>
       </c>
       <c r="C322" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D322" s="25" t="n">
@@ -22180,29 +22184,29 @@
       </c>
       <c r="F322" s="17" t="inlineStr">
         <is>
-          <t>Over 61.5</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="G322" s="26" t="n">
-        <v>61.5</v>
+        <v>51.5</v>
       </c>
       <c r="H322" s="18" t="n">
-        <v>-108</v>
+        <v>-102</v>
       </c>
       <c r="I322" s="20" t="n">
-        <v>0.4127861775763615</v>
+        <v>0.3973152622399918</v>
       </c>
       <c r="J322" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4826358742837298</v>
       </c>
       <c r="K322" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.504950495049505</v>
       </c>
       <c r="L322" s="19" t="n">
-        <v>-0.1064445916544078</v>
+        <v>-0.1076352328095131</v>
       </c>
       <c r="M322" s="19" t="n">
-        <v>-0.2050043987418222</v>
+        <v>-0.2131599708580554</v>
       </c>
       <c r="N322" s="20" t="n">
         <v>0</v>
@@ -22215,11 +22219,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q322" s="17" t="inlineStr">
-        <is>
-          <t>APSU isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q322" s="17" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="12" t="inlineStr">
@@ -22229,7 +22229,7 @@
       </c>
       <c r="B323" s="12" t="inlineStr">
         <is>
-          <t>BOIS @ ORE</t>
+          <t>BC @ CIN</t>
         </is>
       </c>
       <c r="C323" s="12" t="inlineStr">
@@ -22242,34 +22242,34 @@
       </c>
       <c r="E323" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F323" s="12" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>CIN -7.5</t>
         </is>
       </c>
       <c r="G323" s="23" t="n">
-        <v>51.5</v>
+        <v>-7.5</v>
       </c>
       <c r="H323" s="13" t="n">
-        <v>-102</v>
+        <v>-108</v>
       </c>
       <c r="I323" s="15" t="n">
-        <v>0.3973152622399918</v>
+        <v>0.411591408576187</v>
       </c>
       <c r="J323" s="15" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K323" s="15" t="n">
-        <v>0.504950495049505</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L323" s="14" t="n">
-        <v>-0.1076352328095131</v>
+        <v>-0.1076393606545822</v>
       </c>
       <c r="M323" s="14" t="n">
-        <v>-0.2131599708580554</v>
+        <v>-0.2073054353347509</v>
       </c>
       <c r="N323" s="15" t="n">
         <v>0</v>
@@ -22292,12 +22292,12 @@
       </c>
       <c r="B324" s="17" t="inlineStr">
         <is>
-          <t>BC @ CIN</t>
+          <t>SELA @ USA</t>
         </is>
       </c>
       <c r="C324" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D324" s="25" t="n">
@@ -22305,34 +22305,34 @@
       </c>
       <c r="E324" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F324" s="17" t="inlineStr">
         <is>
-          <t>CIN -7.5</t>
+          <t>Under 52.5</t>
         </is>
       </c>
       <c r="G324" s="26" t="n">
-        <v>-7.5</v>
+        <v>52.5</v>
       </c>
       <c r="H324" s="18" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I324" s="20" t="n">
-        <v>0.411591408576187</v>
+        <v>0.418931176220276</v>
       </c>
       <c r="J324" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K324" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L324" s="19" t="n">
-        <v>-0.1076393606545822</v>
+        <v>-0.1093707105721768</v>
       </c>
       <c r="M324" s="19" t="n">
-        <v>-0.2073054353347509</v>
+        <v>-0.2070231307259062</v>
       </c>
       <c r="N324" s="20" t="n">
         <v>0</v>
@@ -22345,7 +22345,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q324" s="17" t="n"/>
+      <c r="Q324" s="17" t="inlineStr">
+        <is>
+          <t>SELA isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="12" t="inlineStr">
@@ -22355,12 +22359,12 @@
       </c>
       <c r="B325" s="12" t="inlineStr">
         <is>
-          <t>SELA @ USA</t>
+          <t>BRY @ ARMY</t>
         </is>
       </c>
       <c r="C325" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D325" s="22" t="n">
@@ -22373,17 +22377,17 @@
       </c>
       <c r="F325" s="12" t="inlineStr">
         <is>
-          <t>Under 52.5</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="G325" s="23" t="n">
-        <v>52.5</v>
+        <v>51.5</v>
       </c>
       <c r="H325" s="13" t="n">
         <v>-112</v>
       </c>
       <c r="I325" s="15" t="n">
-        <v>0.418931176220276</v>
+        <v>0.4189311749081579</v>
       </c>
       <c r="J325" s="15" t="n">
         <v>0.5043297540699688</v>
@@ -22392,10 +22396,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L325" s="14" t="n">
-        <v>-0.1093707105721768</v>
+        <v>-0.1093707118842949</v>
       </c>
       <c r="M325" s="14" t="n">
-        <v>-0.2070231307259062</v>
+        <v>-0.2070231332095583</v>
       </c>
       <c r="N325" s="15" t="n">
         <v>0</v>
@@ -22410,7 +22414,7 @@
       </c>
       <c r="Q325" s="12" t="inlineStr">
         <is>
-          <t>SELA isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>BRY isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -22422,12 +22426,12 @@
       </c>
       <c r="B326" s="17" t="inlineStr">
         <is>
-          <t>BRY @ ARMY</t>
+          <t>OKST @ TLSA</t>
         </is>
       </c>
       <c r="C326" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-09-05 19:45</t>
         </is>
       </c>
       <c r="D326" s="25" t="n">
@@ -22440,29 +22444,29 @@
       </c>
       <c r="F326" s="17" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>Over 60.5</t>
         </is>
       </c>
       <c r="G326" s="26" t="n">
-        <v>51.5</v>
+        <v>60.5</v>
       </c>
       <c r="H326" s="18" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="I326" s="20" t="n">
-        <v>0.4189311749081579</v>
+        <v>0.4091797577845063</v>
       </c>
       <c r="J326" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K326" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L326" s="19" t="n">
-        <v>-0.1093707118842949</v>
+        <v>-0.1100510114462629</v>
       </c>
       <c r="M326" s="19" t="n">
-        <v>-0.2070231332095583</v>
+        <v>-0.2119500961187285</v>
       </c>
       <c r="N326" s="20" t="n">
         <v>0</v>
@@ -22475,11 +22479,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q326" s="17" t="inlineStr">
-        <is>
-          <t>BRY isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q326" s="17" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="12" t="inlineStr">
@@ -22489,12 +22489,12 @@
       </c>
       <c r="B327" s="12" t="inlineStr">
         <is>
-          <t>OKST @ TLSA</t>
+          <t>SMU @ FSU</t>
         </is>
       </c>
       <c r="C327" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 19:45</t>
+          <t>2026-09-07 23:30</t>
         </is>
       </c>
       <c r="D327" s="22" t="n">
@@ -22502,37 +22502,37 @@
       </c>
       <c r="E327" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F327" s="12" t="inlineStr">
         <is>
-          <t>Over 60.5</t>
+          <t>SMU -3</t>
         </is>
       </c>
       <c r="G327" s="23" t="n">
-        <v>60.5</v>
+        <v>3</v>
       </c>
       <c r="H327" s="13" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="I327" s="15" t="n">
-        <v>0.4091797577845063</v>
+        <v>0.4017076652024605</v>
       </c>
       <c r="J327" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K327" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L327" s="14" t="n">
-        <v>-0.1100510114462629</v>
+        <v>-0.110487456748759</v>
       </c>
       <c r="M327" s="14" t="n">
-        <v>-0.2119500961187285</v>
+        <v>-0.2038948789479926</v>
       </c>
       <c r="N327" s="15" t="n">
-        <v>0</v>
+        <v>0.0548</v>
       </c>
       <c r="O327" s="24" t="n">
         <v>0.4</v>
@@ -22552,12 +22552,12 @@
       </c>
       <c r="B328" s="17" t="inlineStr">
         <is>
-          <t>SMU @ FSU</t>
+          <t>EIU @ MINN</t>
         </is>
       </c>
       <c r="C328" s="17" t="inlineStr">
         <is>
-          <t>2026-09-07 23:30</t>
+          <t>2026-09-04 00:00</t>
         </is>
       </c>
       <c r="D328" s="25" t="n">
@@ -22565,37 +22565,37 @@
       </c>
       <c r="E328" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F328" s="17" t="inlineStr">
         <is>
-          <t>SMU -3</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="G328" s="26" t="n">
-        <v>3</v>
+        <v>51.5</v>
       </c>
       <c r="H328" s="18" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="I328" s="20" t="n">
-        <v>0.4017076652024605</v>
+        <v>0.4131437804634706</v>
       </c>
       <c r="J328" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5</v>
       </c>
       <c r="K328" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L328" s="19" t="n">
-        <v>-0.110487456748759</v>
+        <v>-0.1106657433460533</v>
       </c>
       <c r="M328" s="19" t="n">
-        <v>-0.2038948789479926</v>
+        <v>-0.211270964569738</v>
       </c>
       <c r="N328" s="20" t="n">
-        <v>0.0548</v>
+        <v>0</v>
       </c>
       <c r="O328" s="27" t="n">
         <v>0.4</v>
@@ -22605,7 +22605,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q328" s="17" t="n"/>
+      <c r="Q328" s="17" t="inlineStr">
+        <is>
+          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="12" t="inlineStr">
@@ -22615,12 +22619,12 @@
       </c>
       <c r="B329" s="12" t="inlineStr">
         <is>
-          <t>EIU @ MINN</t>
+          <t>FRES @ USC</t>
         </is>
       </c>
       <c r="C329" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 00:00</t>
+          <t>2026-09-05 01:00</t>
         </is>
       </c>
       <c r="D329" s="22" t="n">
@@ -22640,22 +22644,22 @@
         <v>51.5</v>
       </c>
       <c r="H329" s="13" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="I329" s="15" t="n">
-        <v>0.4131437804634706</v>
+        <v>0.4005802070049524</v>
       </c>
       <c r="J329" s="15" t="n">
-        <v>0.5</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K329" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L329" s="14" t="n">
-        <v>-0.1106657433460533</v>
+        <v>-0.1116149149462671</v>
       </c>
       <c r="M329" s="14" t="n">
-        <v>-0.211270964569738</v>
+        <v>-0.2179148339427119</v>
       </c>
       <c r="N329" s="15" t="n">
         <v>0</v>
@@ -22668,11 +22672,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q329" s="12" t="inlineStr">
-        <is>
-          <t>EIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q329" s="12" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="17" t="inlineStr">
@@ -22682,12 +22682,12 @@
       </c>
       <c r="B330" s="17" t="inlineStr">
         <is>
-          <t>FRES @ USC</t>
+          <t>SMU @ FSU</t>
         </is>
       </c>
       <c r="C330" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 01:00</t>
+          <t>2026-09-07 23:30</t>
         </is>
       </c>
       <c r="D330" s="25" t="n">
@@ -22695,34 +22695,32 @@
       </c>
       <c r="E330" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F330" s="17" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
-        </is>
-      </c>
-      <c r="G330" s="26" t="n">
-        <v>51.5</v>
-      </c>
+          <t>SMU ML</t>
+        </is>
+      </c>
+      <c r="G330" s="26" t="n"/>
       <c r="H330" s="18" t="n">
-        <v>-105</v>
+        <v>-162</v>
       </c>
       <c r="I330" s="20" t="n">
-        <v>0.4005802070049524</v>
+        <v>0.5029540416479457</v>
       </c>
       <c r="J330" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5933697541594239</v>
       </c>
       <c r="K330" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.6183206106870229</v>
       </c>
       <c r="L330" s="19" t="n">
-        <v>-0.1116149149462671</v>
+        <v>-0.1153665690390773</v>
       </c>
       <c r="M330" s="19" t="n">
-        <v>-0.2179148339427119</v>
+        <v>-0.1865805005446804</v>
       </c>
       <c r="N330" s="20" t="n">
         <v>0</v>
@@ -22745,12 +22743,12 @@
       </c>
       <c r="B331" s="12" t="inlineStr">
         <is>
-          <t>SMU @ FSU</t>
+          <t>ORST @ HOU</t>
         </is>
       </c>
       <c r="C331" s="12" t="inlineStr">
         <is>
-          <t>2026-09-07 23:30</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D331" s="22" t="n">
@@ -22758,32 +22756,34 @@
       </c>
       <c r="E331" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F331" s="12" t="inlineStr">
         <is>
-          <t>SMU ML</t>
-        </is>
-      </c>
-      <c r="G331" s="23" t="n"/>
+          <t>Under 51.5</t>
+        </is>
+      </c>
+      <c r="G331" s="23" t="n">
+        <v>51.5</v>
+      </c>
       <c r="H331" s="13" t="n">
-        <v>-162</v>
+        <v>-115</v>
       </c>
       <c r="I331" s="15" t="n">
-        <v>0.5029540416479457</v>
+        <v>0.418560898556645</v>
       </c>
       <c r="J331" s="15" t="n">
-        <v>0.5933697541594239</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K331" s="15" t="n">
-        <v>0.6183206106870229</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L331" s="14" t="n">
-        <v>-0.1153665690390773</v>
+        <v>-0.1163228223735875</v>
       </c>
       <c r="M331" s="14" t="n">
-        <v>-0.1865805005446804</v>
+        <v>-0.2174731026984463</v>
       </c>
       <c r="N331" s="15" t="n">
         <v>0</v>
@@ -22806,12 +22806,12 @@
       </c>
       <c r="B332" s="17" t="inlineStr">
         <is>
-          <t>ORST @ HOU</t>
+          <t>WSU @ WASH</t>
         </is>
       </c>
       <c r="C332" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-09-06 20:00</t>
         </is>
       </c>
       <c r="D332" s="25" t="n">
@@ -22824,29 +22824,29 @@
       </c>
       <c r="F332" s="17" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>Under 50.5</t>
         </is>
       </c>
       <c r="G332" s="26" t="n">
-        <v>51.5</v>
+        <v>50.5</v>
       </c>
       <c r="H332" s="18" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="I332" s="20" t="n">
-        <v>0.418560898556645</v>
+        <v>0.4059973233994617</v>
       </c>
       <c r="J332" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5</v>
       </c>
       <c r="K332" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L332" s="19" t="n">
-        <v>-0.1163228223735875</v>
+        <v>-0.1178122004100621</v>
       </c>
       <c r="M332" s="19" t="n">
-        <v>-0.2174731026984463</v>
+        <v>-0.2249142007828458</v>
       </c>
       <c r="N332" s="20" t="n">
         <v>0</v>
@@ -22869,12 +22869,12 @@
       </c>
       <c r="B333" s="12" t="inlineStr">
         <is>
-          <t>WSU @ WASH</t>
+          <t>ARST @ MEM</t>
         </is>
       </c>
       <c r="C333" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 20:00</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D333" s="22" t="n">
@@ -22882,34 +22882,34 @@
       </c>
       <c r="E333" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F333" s="12" t="inlineStr">
         <is>
-          <t>Under 50.5</t>
+          <t>MEM -9.5</t>
         </is>
       </c>
       <c r="G333" s="23" t="n">
-        <v>50.5</v>
+        <v>-9.5</v>
       </c>
       <c r="H333" s="13" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I333" s="15" t="n">
-        <v>0.4059973233994617</v>
+        <v>0.4010081776134841</v>
       </c>
       <c r="J333" s="15" t="n">
-        <v>0.5</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K333" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L333" s="14" t="n">
-        <v>-0.1178122004100621</v>
+        <v>-0.1182225916172852</v>
       </c>
       <c r="M333" s="14" t="n">
-        <v>-0.2249142007828458</v>
+        <v>-0.2276879542258823</v>
       </c>
       <c r="N333" s="15" t="n">
         <v>0</v>
@@ -24015,12 +24015,12 @@
       </c>
       <c r="B351" s="12" t="inlineStr">
         <is>
-          <t>BAY @ AUB</t>
+          <t>YSU @ UK</t>
         </is>
       </c>
       <c r="C351" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-05 17:00</t>
         </is>
       </c>
       <c r="D351" s="22" t="n">
@@ -24033,29 +24033,29 @@
       </c>
       <c r="F351" s="12" t="inlineStr">
         <is>
-          <t>Over 59.5</t>
+          <t>Over 62.5</t>
         </is>
       </c>
       <c r="G351" s="23" t="n">
-        <v>59.5</v>
+        <v>62.5</v>
       </c>
       <c r="H351" s="13" t="n">
-        <v>-102</v>
+        <v>-110</v>
       </c>
       <c r="I351" s="15" t="n">
-        <v>0.3669878672528573</v>
+        <v>0.3854233285750168</v>
       </c>
       <c r="J351" s="15" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.5</v>
       </c>
       <c r="K351" s="15" t="n">
-        <v>0.504950495049505</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L351" s="14" t="n">
-        <v>-0.1379626277966477</v>
+        <v>-0.1383861952345071</v>
       </c>
       <c r="M351" s="14" t="n">
-        <v>-0.2732201060286552</v>
+        <v>-0.264191827265877</v>
       </c>
       <c r="N351" s="15" t="n">
         <v>0</v>
@@ -24068,7 +24068,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q351" s="12" t="n"/>
+      <c r="Q351" s="12" t="inlineStr">
+        <is>
+          <t>YSU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="17" t="inlineStr">
@@ -24078,12 +24082,12 @@
       </c>
       <c r="B352" s="17" t="inlineStr">
         <is>
-          <t>YSU @ UK</t>
+          <t>BAY @ AUB</t>
         </is>
       </c>
       <c r="C352" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 17:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D352" s="25" t="n">
@@ -24091,34 +24095,32 @@
       </c>
       <c r="E352" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F352" s="17" t="inlineStr">
         <is>
-          <t>Over 62.5</t>
-        </is>
-      </c>
-      <c r="G352" s="26" t="n">
-        <v>62.5</v>
-      </c>
+          <t>AUB ML</t>
+        </is>
+      </c>
+      <c r="G352" s="26" t="n"/>
       <c r="H352" s="18" t="n">
-        <v>-110</v>
+        <v>-298</v>
       </c>
       <c r="I352" s="20" t="n">
-        <v>0.3854233285750168</v>
+        <v>0.608985260770975</v>
       </c>
       <c r="J352" s="20" t="n">
-        <v>0.5</v>
+        <v>0.7179705215419501</v>
       </c>
       <c r="K352" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.7487437185929648</v>
       </c>
       <c r="L352" s="19" t="n">
-        <v>-0.1383861952345071</v>
+        <v>-0.1397584578219898</v>
       </c>
       <c r="M352" s="19" t="n">
-        <v>-0.264191827265877</v>
+        <v>-0.1866572691716508</v>
       </c>
       <c r="N352" s="20" t="n">
         <v>0</v>
@@ -24131,11 +24133,7 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q352" s="17" t="inlineStr">
-        <is>
-          <t>YSU isn't a full FBS participant this season — model doesn't rate them reliably</t>
-        </is>
-      </c>
+      <c r="Q352" s="17" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="12" t="inlineStr">
@@ -24145,7 +24143,7 @@
       </c>
       <c r="B353" s="12" t="inlineStr">
         <is>
-          <t>BAY @ AUB</t>
+          <t>TULN @ DUKE</t>
         </is>
       </c>
       <c r="C353" s="12" t="inlineStr">
@@ -24158,32 +24156,34 @@
       </c>
       <c r="E353" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F353" s="12" t="inlineStr">
         <is>
-          <t>AUB ML</t>
-        </is>
-      </c>
-      <c r="G353" s="23" t="n"/>
+          <t>Under 50.5</t>
+        </is>
+      </c>
+      <c r="G353" s="23" t="n">
+        <v>50.5</v>
+      </c>
       <c r="H353" s="13" t="n">
-        <v>-298</v>
+        <v>-105</v>
       </c>
       <c r="I353" s="15" t="n">
-        <v>0.608985260770975</v>
+        <v>0.3718521858885648</v>
       </c>
       <c r="J353" s="15" t="n">
-        <v>0.7179705215419501</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K353" s="15" t="n">
-        <v>0.7487437185929648</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L353" s="14" t="n">
-        <v>-0.1397584578219898</v>
+        <v>-0.1403429360626547</v>
       </c>
       <c r="M353" s="14" t="n">
-        <v>-0.1866572691716508</v>
+        <v>-0.2740028751699449</v>
       </c>
       <c r="N353" s="15" t="n">
         <v>0</v>
@@ -24206,7 +24206,7 @@
       </c>
       <c r="B354" s="17" t="inlineStr">
         <is>
-          <t>TULN @ DUKE</t>
+          <t>BAY @ AUB</t>
         </is>
       </c>
       <c r="C354" s="17" t="inlineStr">
@@ -24224,29 +24224,29 @@
       </c>
       <c r="F354" s="17" t="inlineStr">
         <is>
-          <t>Under 50.5</t>
+          <t>Over 58.5</t>
         </is>
       </c>
       <c r="G354" s="26" t="n">
-        <v>50.5</v>
+        <v>58.5</v>
       </c>
       <c r="H354" s="18" t="n">
-        <v>-105</v>
+        <v>-118</v>
       </c>
       <c r="I354" s="20" t="n">
-        <v>0.3718521858885648</v>
+        <v>0.4008111918061066</v>
       </c>
       <c r="J354" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5173641257162701</v>
       </c>
       <c r="K354" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5412844036697247</v>
       </c>
       <c r="L354" s="19" t="n">
-        <v>-0.1403429360626547</v>
+        <v>-0.1404732118636182</v>
       </c>
       <c r="M354" s="19" t="n">
-        <v>-0.2740028751699449</v>
+        <v>-0.2595183066632946</v>
       </c>
       <c r="N354" s="20" t="n">
         <v>0</v>
@@ -27927,12 +27927,12 @@
       </c>
       <c r="B411" s="12" t="inlineStr">
         <is>
-          <t>FAU @ FLA</t>
+          <t>WMU @ MICH</t>
         </is>
       </c>
       <c r="C411" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 23:45</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D411" s="22" t="n">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="F411" s="12" t="inlineStr">
         <is>
-          <t>FLA ML</t>
+          <t>MICH ML</t>
         </is>
       </c>
       <c r="G411" s="23" t="n"/>
@@ -27992,12 +27992,12 @@
       </c>
       <c r="B412" s="17" t="inlineStr">
         <is>
-          <t>UAB @ ILL</t>
+          <t>FAU @ FLA</t>
         </is>
       </c>
       <c r="C412" s="17" t="inlineStr">
         <is>
-          <t>2026-09-04 01:00</t>
+          <t>2026-09-05 23:45</t>
         </is>
       </c>
       <c r="D412" s="25" t="n">
@@ -28010,27 +28010,27 @@
       </c>
       <c r="F412" s="17" t="inlineStr">
         <is>
-          <t>ILL ML</t>
+          <t>FLA ML</t>
         </is>
       </c>
       <c r="G412" s="26" t="n"/>
       <c r="H412" s="18" t="n">
-        <v>-10000</v>
+        <v>-5000</v>
       </c>
       <c r="I412" s="20" t="n">
-        <v>0.776123105734241</v>
+        <v>0.7664249001597467</v>
       </c>
       <c r="J412" s="20" t="n">
-        <v>0.9684473601999376</v>
+        <v>0.949050949050949</v>
       </c>
       <c r="K412" s="20" t="n">
-        <v>0.9900990099009901</v>
+        <v>0.9803921568627451</v>
       </c>
       <c r="L412" s="19" t="n">
-        <v>-0.2139759041667491</v>
+        <v>-0.2139672567029983</v>
       </c>
       <c r="M412" s="19" t="n">
-        <v>-0.2161156632084165</v>
+        <v>-0.2182466018370583</v>
       </c>
       <c r="N412" s="20" t="n">
         <v>0</v>
@@ -28057,12 +28057,12 @@
       </c>
       <c r="B413" s="12" t="inlineStr">
         <is>
-          <t>ECU @ ALA</t>
+          <t>UAB @ ILL</t>
         </is>
       </c>
       <c r="C413" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D413" s="22" t="n">
@@ -28075,7 +28075,7 @@
       </c>
       <c r="F413" s="12" t="inlineStr">
         <is>
-          <t>ALA ML</t>
+          <t>ILL ML</t>
         </is>
       </c>
       <c r="G413" s="23" t="n"/>
@@ -28122,12 +28122,12 @@
       </c>
       <c r="B414" s="17" t="inlineStr">
         <is>
-          <t>TXST @ TEX</t>
+          <t>ECU @ ALA</t>
         </is>
       </c>
       <c r="C414" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-05 16:00</t>
         </is>
       </c>
       <c r="D414" s="25" t="n">
@@ -28140,7 +28140,7 @@
       </c>
       <c r="F414" s="17" t="inlineStr">
         <is>
-          <t>TEX ML</t>
+          <t>ALA ML</t>
         </is>
       </c>
       <c r="G414" s="26" t="n"/>
@@ -28187,12 +28187,12 @@
       </c>
       <c r="B415" s="12" t="inlineStr">
         <is>
-          <t>NAU @ ARIZ</t>
+          <t>TXST @ TEX</t>
         </is>
       </c>
       <c r="C415" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 01:30</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D415" s="22" t="n">
@@ -28205,7 +28205,7 @@
       </c>
       <c r="F415" s="12" t="inlineStr">
         <is>
-          <t>ARIZ ML</t>
+          <t>TEX ML</t>
         </is>
       </c>
       <c r="G415" s="23" t="n"/>
@@ -28240,7 +28240,7 @@
       </c>
       <c r="Q415" s="12" t="inlineStr">
         <is>
-          <t>NAU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>price outside allowed range</t>
         </is>
       </c>
     </row>
@@ -28252,12 +28252,12 @@
       </c>
       <c r="B416" s="17" t="inlineStr">
         <is>
-          <t>SHSU @ TROY</t>
+          <t>NAU @ ARIZ</t>
         </is>
       </c>
       <c r="C416" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00</t>
+          <t>2026-09-06 01:30</t>
         </is>
       </c>
       <c r="D416" s="25" t="n">
@@ -28265,34 +28265,32 @@
       </c>
       <c r="E416" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F416" s="17" t="inlineStr">
         <is>
-          <t>TROY -16.5</t>
-        </is>
-      </c>
-      <c r="G416" s="26" t="n">
-        <v>-16.5</v>
-      </c>
+          <t>ARIZ ML</t>
+        </is>
+      </c>
+      <c r="G416" s="26" t="n"/>
       <c r="H416" s="18" t="n">
-        <v>-115</v>
+        <v>-10000</v>
       </c>
       <c r="I416" s="20" t="n">
-        <v>0.3203627251349395</v>
+        <v>0.776123105734241</v>
       </c>
       <c r="J416" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.9684473601999376</v>
       </c>
       <c r="K416" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.9900990099009901</v>
       </c>
       <c r="L416" s="19" t="n">
-        <v>-0.214520995795293</v>
+        <v>-0.2139759041667491</v>
       </c>
       <c r="M416" s="19" t="n">
-        <v>-0.4010609921390262</v>
+        <v>-0.2161156632084165</v>
       </c>
       <c r="N416" s="20" t="n">
         <v>0</v>
@@ -28307,7 +28305,7 @@
       </c>
       <c r="Q416" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>NAU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -28319,12 +28317,12 @@
       </c>
       <c r="B417" s="12" t="inlineStr">
         <is>
-          <t>MASS @ RUTG</t>
+          <t>SHSU @ TROY</t>
         </is>
       </c>
       <c r="C417" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 22:00</t>
+          <t>2026-09-05 23:00</t>
         </is>
       </c>
       <c r="D417" s="22" t="n">
@@ -28332,32 +28330,34 @@
       </c>
       <c r="E417" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F417" s="12" t="inlineStr">
         <is>
-          <t>RUTG ML</t>
-        </is>
-      </c>
-      <c r="G417" s="23" t="n"/>
+          <t>TROY -16.5</t>
+        </is>
+      </c>
+      <c r="G417" s="23" t="n">
+        <v>-16.5</v>
+      </c>
       <c r="H417" s="13" t="n">
-        <v>-9000</v>
+        <v>-115</v>
       </c>
       <c r="I417" s="15" t="n">
-        <v>0.7731828480941653</v>
+        <v>0.3203627251349395</v>
       </c>
       <c r="J417" s="15" t="n">
-        <v>0.9625668449197861</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K417" s="15" t="n">
-        <v>0.9890109890109891</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L417" s="14" t="n">
-        <v>-0.2158281409168238</v>
+        <v>-0.214520995795293</v>
       </c>
       <c r="M417" s="14" t="n">
-        <v>-0.2182262313714551</v>
+        <v>-0.4010609921390262</v>
       </c>
       <c r="N417" s="15" t="n">
         <v>0</v>
@@ -28372,7 +28372,7 @@
       </c>
       <c r="Q417" s="12" t="inlineStr">
         <is>
-          <t>price outside allowed range</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -28384,12 +28384,12 @@
       </c>
       <c r="B418" s="17" t="inlineStr">
         <is>
-          <t>RGV @ UTSA</t>
+          <t>MASS @ RUTG</t>
         </is>
       </c>
       <c r="C418" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-03 22:00</t>
         </is>
       </c>
       <c r="D418" s="25" t="n">
@@ -28402,7 +28402,7 @@
       </c>
       <c r="F418" s="17" t="inlineStr">
         <is>
-          <t>UTSA ML</t>
+          <t>RUTG ML</t>
         </is>
       </c>
       <c r="G418" s="26" t="n"/>
@@ -28437,7 +28437,7 @@
       </c>
       <c r="Q418" s="17" t="inlineStr">
         <is>
-          <t>RGV isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>price outside allowed range</t>
         </is>
       </c>
     </row>
@@ -28449,12 +28449,12 @@
       </c>
       <c r="B419" s="12" t="inlineStr">
         <is>
-          <t>WES @ KENN</t>
+          <t>RGV @ UTSA</t>
         </is>
       </c>
       <c r="C419" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D419" s="22" t="n">
@@ -28467,27 +28467,27 @@
       </c>
       <c r="F419" s="12" t="inlineStr">
         <is>
-          <t>KENN ML</t>
+          <t>UTSA ML</t>
         </is>
       </c>
       <c r="G419" s="23" t="n"/>
       <c r="H419" s="13" t="n">
-        <v>-6500</v>
+        <v>-9000</v>
       </c>
       <c r="I419" s="15" t="n">
-        <v>0.7688386289885699</v>
+        <v>0.7731828480941653</v>
       </c>
       <c r="J419" s="15" t="n">
-        <v>0.9538784067085954</v>
+        <v>0.9625668449197861</v>
       </c>
       <c r="K419" s="15" t="n">
-        <v>0.9848484848484849</v>
+        <v>0.9890109890109891</v>
       </c>
       <c r="L419" s="14" t="n">
-        <v>-0.2160098558599149</v>
+        <v>-0.2158281409168238</v>
       </c>
       <c r="M419" s="14" t="n">
-        <v>-0.219333084411606</v>
+        <v>-0.2182262313714551</v>
       </c>
       <c r="N419" s="15" t="n">
         <v>0</v>
@@ -28502,7 +28502,7 @@
       </c>
       <c r="Q419" s="12" t="inlineStr">
         <is>
-          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>RGV isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -28514,12 +28514,12 @@
       </c>
       <c r="B420" s="17" t="inlineStr">
         <is>
-          <t>ULM @ MSST</t>
+          <t>WES @ KENN</t>
         </is>
       </c>
       <c r="C420" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D420" s="25" t="n">
@@ -28532,7 +28532,7 @@
       </c>
       <c r="F420" s="17" t="inlineStr">
         <is>
-          <t>MSST ML</t>
+          <t>KENN ML</t>
         </is>
       </c>
       <c r="G420" s="26" t="n"/>
@@ -28567,7 +28567,7 @@
       </c>
       <c r="Q420" s="17" t="inlineStr">
         <is>
-          <t>price outside allowed range</t>
+          <t>WES isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -28579,7 +28579,7 @@
       </c>
       <c r="B421" s="12" t="inlineStr">
         <is>
-          <t>WMU @ MICH</t>
+          <t>ULM @ MSST</t>
         </is>
       </c>
       <c r="C421" s="12" t="inlineStr">
@@ -28597,7 +28597,7 @@
       </c>
       <c r="F421" s="12" t="inlineStr">
         <is>
-          <t>MICH ML</t>
+          <t>MSST ML</t>
         </is>
       </c>
       <c r="G421" s="23" t="n"/>
@@ -31570,12 +31570,12 @@
       </c>
       <c r="B466" s="17" t="inlineStr">
         <is>
-          <t>DUQ @ AFA</t>
+          <t>WMU @ MICH</t>
         </is>
       </c>
       <c r="C466" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 17:00</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D466" s="25" t="n">
@@ -31588,29 +31588,29 @@
       </c>
       <c r="F466" s="17" t="inlineStr">
         <is>
-          <t>AFA -30.5</t>
+          <t>MICH -27.5</t>
         </is>
       </c>
       <c r="G466" s="26" t="n">
-        <v>-30.5</v>
+        <v>-27.5</v>
       </c>
       <c r="H466" s="18" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I466" s="20" t="n">
-        <v>0.2550735580973746</v>
+        <v>0.2649561635761648</v>
       </c>
       <c r="J466" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K466" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L466" s="19" t="n">
-        <v>-0.2641572111333947</v>
+        <v>-0.263345723216288</v>
       </c>
       <c r="M466" s="19" t="n">
-        <v>-0.5087472214420933</v>
+        <v>-0.4984758332308309</v>
       </c>
       <c r="N466" s="20" t="n">
         <v>0</v>
@@ -31625,7 +31625,7 @@
       </c>
       <c r="Q466" s="17" t="inlineStr">
         <is>
-          <t>DUQ isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -31637,12 +31637,12 @@
       </c>
       <c r="B467" s="12" t="inlineStr">
         <is>
-          <t>TOW @ NAVY</t>
+          <t>DUQ @ AFA</t>
         </is>
       </c>
       <c r="C467" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-05 17:00</t>
         </is>
       </c>
       <c r="D467" s="22" t="n">
@@ -31655,7 +31655,7 @@
       </c>
       <c r="F467" s="12" t="inlineStr">
         <is>
-          <t>NAVY -30.5</t>
+          <t>AFA -30.5</t>
         </is>
       </c>
       <c r="G467" s="23" t="n">
@@ -31692,7 +31692,7 @@
       </c>
       <c r="Q467" s="12" t="inlineStr">
         <is>
-          <t>TOW isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>DUQ isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -31704,12 +31704,12 @@
       </c>
       <c r="B468" s="17" t="inlineStr">
         <is>
-          <t>MASS @ RUTG</t>
+          <t>TOW @ NAVY</t>
         </is>
       </c>
       <c r="C468" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 22:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D468" s="25" t="n">
@@ -31722,29 +31722,29 @@
       </c>
       <c r="F468" s="17" t="inlineStr">
         <is>
-          <t>RUTG -29.5</t>
+          <t>NAVY -30.5</t>
         </is>
       </c>
       <c r="G468" s="26" t="n">
-        <v>-29.5</v>
+        <v>-30.5</v>
       </c>
       <c r="H468" s="18" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I468" s="20" t="n">
-        <v>0.2587247949407175</v>
+        <v>0.2550735580973746</v>
       </c>
       <c r="J468" s="20" t="n">
-        <v>0.5</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K468" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L468" s="19" t="n">
-        <v>-0.2650847288688063</v>
+        <v>-0.2641572111333947</v>
       </c>
       <c r="M468" s="19" t="n">
-        <v>-0.5060708460222665</v>
+        <v>-0.5087472214420933</v>
       </c>
       <c r="N468" s="20" t="n">
         <v>0</v>
@@ -31759,7 +31759,7 @@
       </c>
       <c r="Q468" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>TOW isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -31771,12 +31771,12 @@
       </c>
       <c r="B469" s="12" t="inlineStr">
         <is>
-          <t>NAU @ ARIZ</t>
+          <t>MASS @ RUTG</t>
         </is>
       </c>
       <c r="C469" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 01:30</t>
+          <t>2026-09-03 22:00</t>
         </is>
       </c>
       <c r="D469" s="22" t="n">
@@ -31789,29 +31789,29 @@
       </c>
       <c r="F469" s="12" t="inlineStr">
         <is>
-          <t>ARIZ -31.5</t>
+          <t>RUTG -29.5</t>
         </is>
       </c>
       <c r="G469" s="23" t="n">
-        <v>-31.5</v>
+        <v>-29.5</v>
       </c>
       <c r="H469" s="13" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I469" s="15" t="n">
-        <v>0.2537478004324161</v>
+        <v>0.2587247949407175</v>
       </c>
       <c r="J469" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5</v>
       </c>
       <c r="K469" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L469" s="14" t="n">
-        <v>-0.2654829687983532</v>
+        <v>-0.2650847288688063</v>
       </c>
       <c r="M469" s="14" t="n">
-        <v>-0.511300532500532</v>
+        <v>-0.5060708460222665</v>
       </c>
       <c r="N469" s="15" t="n">
         <v>0</v>
@@ -31826,7 +31826,7 @@
       </c>
       <c r="Q469" s="12" t="inlineStr">
         <is>
-          <t>NAU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -31838,12 +31838,12 @@
       </c>
       <c r="B470" s="17" t="inlineStr">
         <is>
-          <t>WMU @ MICH</t>
+          <t>NAU @ ARIZ</t>
         </is>
       </c>
       <c r="C470" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-09-06 01:30</t>
         </is>
       </c>
       <c r="D470" s="25" t="n">
@@ -31856,29 +31856,29 @@
       </c>
       <c r="F470" s="17" t="inlineStr">
         <is>
-          <t>MICH -27.5</t>
+          <t>ARIZ -31.5</t>
         </is>
       </c>
       <c r="G470" s="26" t="n">
-        <v>-27.5</v>
+        <v>-31.5</v>
       </c>
       <c r="H470" s="18" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="I470" s="20" t="n">
-        <v>0.2682084046343548</v>
+        <v>0.2537478004324161</v>
       </c>
       <c r="J470" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K470" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L470" s="19" t="n">
-        <v>-0.2666753162958777</v>
+        <v>-0.2654829687983532</v>
       </c>
       <c r="M470" s="19" t="n">
-        <v>-0.4985668956835976</v>
+        <v>-0.511300532500532</v>
       </c>
       <c r="N470" s="20" t="n">
         <v>0</v>
@@ -31893,7 +31893,7 @@
       </c>
       <c r="Q470" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>NAU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -32843,12 +32843,12 @@
       </c>
       <c r="B485" s="12" t="inlineStr">
         <is>
-          <t>UTU @ BYU</t>
+          <t>BALL @ OSU</t>
         </is>
       </c>
       <c r="C485" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00</t>
+          <t>2026-09-05 16:30</t>
         </is>
       </c>
       <c r="D485" s="22" t="n">
@@ -32861,17 +32861,17 @@
       </c>
       <c r="F485" s="12" t="inlineStr">
         <is>
-          <t>BYU -49.5</t>
+          <t>OSU -50.5</t>
         </is>
       </c>
       <c r="G485" s="23" t="n">
-        <v>-49.5</v>
+        <v>-50.5</v>
       </c>
       <c r="H485" s="13" t="n">
         <v>-108</v>
       </c>
       <c r="I485" s="15" t="n">
-        <v>0.2479069293343283</v>
+        <v>0.2478884416817771</v>
       </c>
       <c r="J485" s="15" t="n">
         <v>0.4956702459300312</v>
@@ -32880,10 +32880,10 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L485" s="14" t="n">
-        <v>-0.271323839896441</v>
+        <v>-0.2713423275489921</v>
       </c>
       <c r="M485" s="14" t="n">
-        <v>-0.5225496175783306</v>
+        <v>-0.5225852234276884</v>
       </c>
       <c r="N485" s="15" t="n">
         <v>0</v>
@@ -32898,7 +32898,7 @@
       </c>
       <c r="Q485" s="12" t="inlineStr">
         <is>
-          <t>UTU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -32910,12 +32910,12 @@
       </c>
       <c r="B486" s="17" t="inlineStr">
         <is>
-          <t>BALL @ OSU</t>
+          <t>IDHO @ UTAH</t>
         </is>
       </c>
       <c r="C486" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 16:30</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
       <c r="D486" s="25" t="n">
@@ -32928,29 +32928,29 @@
       </c>
       <c r="F486" s="17" t="inlineStr">
         <is>
-          <t>OSU -50.5</t>
+          <t>UTAH -33.5</t>
         </is>
       </c>
       <c r="G486" s="26" t="n">
-        <v>-50.5</v>
+        <v>-33.5</v>
       </c>
       <c r="H486" s="18" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I486" s="20" t="n">
-        <v>0.2478884416817771</v>
+        <v>0.2561162209365798</v>
       </c>
       <c r="J486" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K486" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L486" s="19" t="n">
-        <v>-0.2713423275489921</v>
+        <v>-0.272185665855873</v>
       </c>
       <c r="M486" s="19" t="n">
-        <v>-0.5225852234276884</v>
+        <v>-0.5152085817986167</v>
       </c>
       <c r="N486" s="20" t="n">
         <v>0</v>
@@ -32965,7 +32965,7 @@
       </c>
       <c r="Q486" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -32977,12 +32977,12 @@
       </c>
       <c r="B487" s="12" t="inlineStr">
         <is>
-          <t>IDHO @ UTAH</t>
+          <t>LIU @ KU</t>
         </is>
       </c>
       <c r="C487" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04 01:00</t>
+          <t>2026-09-05 00:00</t>
         </is>
       </c>
       <c r="D487" s="22" t="n">
@@ -32995,29 +32995,29 @@
       </c>
       <c r="F487" s="12" t="inlineStr">
         <is>
-          <t>UTAH -33.5</t>
+          <t>KU -38.5</t>
         </is>
       </c>
       <c r="G487" s="23" t="n">
-        <v>-33.5</v>
+        <v>-38.5</v>
       </c>
       <c r="H487" s="13" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I487" s="15" t="n">
-        <v>0.2561162209365798</v>
+        <v>0.251313103350202</v>
       </c>
       <c r="J487" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K487" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L487" s="14" t="n">
-        <v>-0.272185665855873</v>
+        <v>-0.2724964204593218</v>
       </c>
       <c r="M487" s="14" t="n">
-        <v>-0.5152085817986167</v>
+        <v>-0.5202204390587052</v>
       </c>
       <c r="N487" s="15" t="n">
         <v>0</v>
@@ -33032,7 +33032,7 @@
       </c>
       <c r="Q487" s="12" t="inlineStr">
         <is>
-          <t>IDHO isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>LIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -33044,12 +33044,12 @@
       </c>
       <c r="B488" s="17" t="inlineStr">
         <is>
-          <t>LIU @ KU</t>
+          <t>PRST @ SDSU</t>
         </is>
       </c>
       <c r="C488" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 00:00</t>
+          <t>2026-09-06 01:30</t>
         </is>
       </c>
       <c r="D488" s="25" t="n">
@@ -33062,17 +33062,17 @@
       </c>
       <c r="F488" s="17" t="inlineStr">
         <is>
-          <t>KU -38.5</t>
+          <t>SDSU -40.5</t>
         </is>
       </c>
       <c r="G488" s="26" t="n">
-        <v>-38.5</v>
+        <v>-40.5</v>
       </c>
       <c r="H488" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I488" s="20" t="n">
-        <v>0.251313103350202</v>
+        <v>0.2508135889821394</v>
       </c>
       <c r="J488" s="20" t="n">
         <v>0.5</v>
@@ -33081,10 +33081,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L488" s="19" t="n">
-        <v>-0.2724964204593218</v>
+        <v>-0.2729959348273844</v>
       </c>
       <c r="M488" s="19" t="n">
-        <v>-0.5202204390587052</v>
+        <v>-0.5211740573977338</v>
       </c>
       <c r="N488" s="20" t="n">
         <v>0</v>
@@ -33099,7 +33099,7 @@
       </c>
       <c r="Q488" s="17" t="inlineStr">
         <is>
-          <t>LIU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>PRST isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -33111,12 +33111,12 @@
       </c>
       <c r="B489" s="12" t="inlineStr">
         <is>
-          <t>PRST @ SDSU</t>
+          <t>NORF @ ODU</t>
         </is>
       </c>
       <c r="C489" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 01:30</t>
+          <t>2026-09-05 22:00</t>
         </is>
       </c>
       <c r="D489" s="22" t="n">
@@ -33129,17 +33129,17 @@
       </c>
       <c r="F489" s="12" t="inlineStr">
         <is>
-          <t>SDSU -40.5</t>
+          <t>ODU -41.5</t>
         </is>
       </c>
       <c r="G489" s="23" t="n">
-        <v>-40.5</v>
+        <v>-41.5</v>
       </c>
       <c r="H489" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I489" s="15" t="n">
-        <v>0.2508135889821394</v>
+        <v>0.25063516823666</v>
       </c>
       <c r="J489" s="15" t="n">
         <v>0.5</v>
@@ -33148,10 +33148,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L489" s="14" t="n">
-        <v>-0.2729959348273844</v>
+        <v>-0.2731743555728638</v>
       </c>
       <c r="M489" s="14" t="n">
-        <v>-0.5211740573977338</v>
+        <v>-0.5215146788209218</v>
       </c>
       <c r="N489" s="15" t="n">
         <v>0</v>
@@ -33166,7 +33166,7 @@
       </c>
       <c r="Q489" s="12" t="inlineStr">
         <is>
-          <t>PRST isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>NORF isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -33178,12 +33178,12 @@
       </c>
       <c r="B490" s="17" t="inlineStr">
         <is>
-          <t>NORF @ ODU</t>
+          <t>MORG @ ASU</t>
         </is>
       </c>
       <c r="C490" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 22:00</t>
+          <t>2026-09-06 02:00</t>
         </is>
       </c>
       <c r="D490" s="25" t="n">
@@ -33196,7 +33196,7 @@
       </c>
       <c r="F490" s="17" t="inlineStr">
         <is>
-          <t>ODU -41.5</t>
+          <t>ASU -41.5</t>
         </is>
       </c>
       <c r="G490" s="26" t="n">
@@ -33233,7 +33233,7 @@
       </c>
       <c r="Q490" s="17" t="inlineStr">
         <is>
-          <t>NORF isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>MORG isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -33245,12 +33245,12 @@
       </c>
       <c r="B491" s="12" t="inlineStr">
         <is>
-          <t>MORG @ ASU</t>
+          <t>BCU @ UCF</t>
         </is>
       </c>
       <c r="C491" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 02:00</t>
+          <t>2026-09-03 23:00</t>
         </is>
       </c>
       <c r="D491" s="22" t="n">
@@ -33263,17 +33263,17 @@
       </c>
       <c r="F491" s="12" t="inlineStr">
         <is>
-          <t>ASU -41.5</t>
+          <t>UCF -42.5</t>
         </is>
       </c>
       <c r="G491" s="23" t="n">
-        <v>-41.5</v>
+        <v>-42.5</v>
       </c>
       <c r="H491" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I491" s="15" t="n">
-        <v>0.25063516823666</v>
+        <v>0.2504931550882666</v>
       </c>
       <c r="J491" s="15" t="n">
         <v>0.5</v>
@@ -33282,10 +33282,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L491" s="14" t="n">
-        <v>-0.2731743555728638</v>
+        <v>-0.2733163687212572</v>
       </c>
       <c r="M491" s="14" t="n">
-        <v>-0.5215146788209218</v>
+        <v>-0.5217857948314909</v>
       </c>
       <c r="N491" s="15" t="n">
         <v>0</v>
@@ -33300,7 +33300,7 @@
       </c>
       <c r="Q491" s="12" t="inlineStr">
         <is>
-          <t>MORG isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -33312,12 +33312,12 @@
       </c>
       <c r="B492" s="17" t="inlineStr">
         <is>
-          <t>BCU @ UCF</t>
+          <t>MVSU @ SAC</t>
         </is>
       </c>
       <c r="C492" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03 23:00</t>
+          <t>2026-09-06 02:00</t>
         </is>
       </c>
       <c r="D492" s="25" t="n">
@@ -33330,29 +33330,29 @@
       </c>
       <c r="F492" s="17" t="inlineStr">
         <is>
-          <t>UCF -42.5</t>
+          <t>SAC -35.5</t>
         </is>
       </c>
       <c r="G492" s="26" t="n">
-        <v>-42.5</v>
+        <v>-35.5</v>
       </c>
       <c r="H492" s="18" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="I492" s="20" t="n">
-        <v>0.2504931550882666</v>
+        <v>0.2548475978399337</v>
       </c>
       <c r="J492" s="20" t="n">
-        <v>0.5</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K492" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L492" s="19" t="n">
-        <v>-0.2733163687212572</v>
+        <v>-0.2734542889525192</v>
       </c>
       <c r="M492" s="19" t="n">
-        <v>-0.5217857948314909</v>
+        <v>-0.5176099040886971</v>
       </c>
       <c r="N492" s="20" t="n">
         <v>0</v>
@@ -33367,7 +33367,7 @@
       </c>
       <c r="Q492" s="17" t="inlineStr">
         <is>
-          <t>BCU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>MVSU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -33379,12 +33379,12 @@
       </c>
       <c r="B493" s="12" t="inlineStr">
         <is>
-          <t>MVSU @ SAC</t>
+          <t>FUR @ TENN</t>
         </is>
       </c>
       <c r="C493" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 02:00</t>
+          <t>2026-09-05 19:30</t>
         </is>
       </c>
       <c r="D493" s="22" t="n">
@@ -33397,29 +33397,29 @@
       </c>
       <c r="F493" s="12" t="inlineStr">
         <is>
-          <t>SAC -35.5</t>
+          <t>TENN -46.5</t>
         </is>
       </c>
       <c r="G493" s="23" t="n">
-        <v>-35.5</v>
+        <v>-46.5</v>
       </c>
       <c r="H493" s="13" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I493" s="15" t="n">
-        <v>0.2548475978399337</v>
+        <v>0.250169564483135</v>
       </c>
       <c r="J493" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K493" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L493" s="14" t="n">
-        <v>-0.2734542889525192</v>
+        <v>-0.2736399593263888</v>
       </c>
       <c r="M493" s="14" t="n">
-        <v>-0.5176099040886971</v>
+        <v>-0.522403558714015</v>
       </c>
       <c r="N493" s="15" t="n">
         <v>0</v>
@@ -33434,7 +33434,7 @@
       </c>
       <c r="Q493" s="12" t="inlineStr">
         <is>
-          <t>MVSU isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>FUR isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -33446,12 +33446,12 @@
       </c>
       <c r="B494" s="17" t="inlineStr">
         <is>
-          <t>FUR @ TENN</t>
+          <t>VMI @ VT</t>
         </is>
       </c>
       <c r="C494" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30</t>
+          <t>2026-09-05 23:30</t>
         </is>
       </c>
       <c r="D494" s="25" t="n">
@@ -33464,17 +33464,17 @@
       </c>
       <c r="F494" s="17" t="inlineStr">
         <is>
-          <t>TENN -46.5</t>
+          <t>VT -51.5</t>
         </is>
       </c>
       <c r="G494" s="26" t="n">
-        <v>-46.5</v>
+        <v>-51.5</v>
       </c>
       <c r="H494" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I494" s="20" t="n">
-        <v>0.250169564483135</v>
+        <v>0.2500393667038911</v>
       </c>
       <c r="J494" s="20" t="n">
         <v>0.5</v>
@@ -33483,10 +33483,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L494" s="19" t="n">
-        <v>-0.2736399593263888</v>
+        <v>-0.2737701571056327</v>
       </c>
       <c r="M494" s="19" t="n">
-        <v>-0.522403558714015</v>
+        <v>-0.5226521181107533</v>
       </c>
       <c r="N494" s="20" t="n">
         <v>0</v>
@@ -33501,7 +33501,7 @@
       </c>
       <c r="Q494" s="17" t="inlineStr">
         <is>
-          <t>FUR isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>VMI isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -33714,12 +33714,12 @@
       </c>
       <c r="B498" s="17" t="inlineStr">
         <is>
-          <t>VMI @ VT</t>
+          <t>UTU @ BYU</t>
         </is>
       </c>
       <c r="C498" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30</t>
+          <t>2026-09-06 00:00</t>
         </is>
       </c>
       <c r="D498" s="25" t="n">
@@ -33732,7 +33732,7 @@
       </c>
       <c r="F498" s="17" t="inlineStr">
         <is>
-          <t>VT -50.5</t>
+          <t>BYU -50.5</t>
         </is>
       </c>
       <c r="G498" s="26" t="n">
@@ -33769,7 +33769,7 @@
       </c>
       <c r="Q498" s="17" t="inlineStr">
         <is>
-          <t>VMI isn't a full FBS participant this season — model doesn't rate them reliably</t>
+          <t>UTU isn't a full FBS participant this season — model doesn't rate them reliably</t>
         </is>
       </c>
     </row>
@@ -38276,7 +38276,7 @@
         <v>-7</v>
       </c>
       <c r="J50" s="30" t="n">
-        <v>59.5</v>
+        <v>58.5</v>
       </c>
       <c r="K50" s="18" t="n">
         <v>240</v>
@@ -39045,7 +39045,7 @@
       </c>
       <c r="H66" s="17" t="inlineStr"/>
       <c r="I66" s="26" t="n">
-        <v>-3.5</v>
+        <v>-3</v>
       </c>
       <c r="J66" s="30" t="n">
         <v>47.5</v>
@@ -39372,16 +39372,16 @@
       </c>
       <c r="H73" s="12" t="inlineStr"/>
       <c r="I73" s="23" t="n">
-        <v>-8.5</v>
+        <v>-9.5</v>
       </c>
       <c r="J73" s="29" t="n">
         <v>53.5</v>
       </c>
       <c r="K73" s="13" t="n">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="L73" s="13" t="n">
-        <v>-305</v>
+        <v>-340</v>
       </c>
       <c r="M73" s="12" t="inlineStr">
         <is>
@@ -39862,7 +39862,7 @@
       </c>
       <c r="H83" s="12" t="inlineStr"/>
       <c r="I83" s="23" t="n">
-        <v>-50.5</v>
+        <v>-51.5</v>
       </c>
       <c r="J83" s="29" t="n">
         <v>57.5</v>
@@ -39913,10 +39913,10 @@
         <v>47.5</v>
       </c>
       <c r="K84" s="18" t="n">
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="L84" s="18" t="n">
-        <v>-6500</v>
+        <v>-5000</v>
       </c>
       <c r="M84" s="17" t="inlineStr">
         <is>
@@ -40050,7 +40050,7 @@
       </c>
       <c r="H87" s="12" t="inlineStr"/>
       <c r="I87" s="23" t="n">
-        <v>-49.5</v>
+        <v>-50.5</v>
       </c>
       <c r="J87" s="29" t="n">
         <v>54.5</v>

--- a/NCAAF_Edge_Model.xlsx
+++ b/NCAAF_Edge_Model.xlsx
@@ -642,7 +642,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-06T13:07:39+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
+          <t>Generated 2026-09-06T15:28:37+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
         </is>
       </c>
     </row>
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="E25" s="13" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>0.1100965613025194</v>
+        <v>0.1169510508323464</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0.4804669316728897</v>
+        <v>0.4740939079752036</v>
       </c>
       <c r="H25" s="16" t="n"/>
       <c r="I25" s="12" t="inlineStr">
@@ -1807,22 +1807,22 @@
       </c>
       <c r="G9" s="23" t="n"/>
       <c r="H9" s="13" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>0.4804669316728897</v>
+        <v>0.4740939079752036</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>0.3552708211997671</v>
+        <v>0.3425247738043947</v>
       </c>
       <c r="K9" s="15" t="n">
-        <v>0.3703703703703703</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="L9" s="14" t="n">
-        <v>0.1100965613025194</v>
+        <v>0.1169510508323464</v>
       </c>
       <c r="M9" s="14" t="n">
-        <v>0.2972607155168024</v>
+        <v>0.3274629423305699</v>
       </c>
       <c r="N9" s="15" t="n">
         <v>0</v>
@@ -2812,16 +2812,16 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>UL @ USC</t>
+          <t>WIS @ ND</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>2026-09-13 03:00</t>
+          <t>2026-09-06 23:30</t>
         </is>
       </c>
       <c r="D25" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
@@ -2830,35 +2830,35 @@
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>UL +28.5</t>
+          <t>WIS +21</t>
         </is>
       </c>
       <c r="G25" s="23" t="n">
-        <v>-28.5</v>
+        <v>-21</v>
       </c>
       <c r="H25" s="13" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>0.7341224033276599</v>
+        <v>0.7243553267010203</v>
       </c>
       <c r="J25" s="15" t="n">
-        <v>0.5</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K25" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L25" s="14" t="n">
-        <v>0.210312879518136</v>
+        <v>0.2121602047498008</v>
       </c>
       <c r="M25" s="14" t="n">
-        <v>0.4015064063528053</v>
+        <v>0.4102869840085517</v>
       </c>
       <c r="N25" s="15" t="n">
-        <v>0</v>
+        <v>0.0095</v>
       </c>
       <c r="O25" s="24" t="n">
-        <v>0.725</v>
+        <v>0.4</v>
       </c>
       <c r="P25" s="12" t="inlineStr">
         <is>
@@ -2879,16 +2879,16 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>WIS @ ND</t>
+          <t>UL @ USC</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>2026-09-06 23:30</t>
+          <t>2026-09-13 03:00</t>
         </is>
       </c>
       <c r="D26" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
@@ -2897,35 +2897,35 @@
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>WIS +20.5</t>
+          <t>UL +28.5</t>
         </is>
       </c>
       <c r="G26" s="26" t="n">
-        <v>-20.5</v>
+        <v>-28.5</v>
       </c>
       <c r="H26" s="18" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="I26" s="20" t="n">
-        <v>0.7198027099861445</v>
+        <v>0.7341224033276599</v>
       </c>
       <c r="J26" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5</v>
       </c>
       <c r="K26" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L26" s="19" t="n">
-        <v>0.207607588034925</v>
+        <v>0.210312879518136</v>
       </c>
       <c r="M26" s="19" t="n">
-        <v>0.4053291004491392</v>
+        <v>0.4015064063528053</v>
       </c>
       <c r="N26" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O26" s="27" t="n">
-        <v>0.4</v>
+        <v>0.725</v>
       </c>
       <c r="P26" s="17" t="inlineStr">
         <is>
@@ -5084,17 +5084,17 @@
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
-          <t>MICH +4.5</t>
+          <t>MICH +5.5</t>
         </is>
       </c>
       <c r="G59" s="23" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="H59" s="13" t="n">
         <v>-105</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>0.6171353381292989</v>
+        <v>0.6270122766739621</v>
       </c>
       <c r="J59" s="15" t="n">
         <v>0.4891657638136511</v>
@@ -5103,10 +5103,10 @@
         <v>0.5121951219512195</v>
       </c>
       <c r="L59" s="14" t="n">
-        <v>0.1049402161780794</v>
+        <v>0.1148171547227426</v>
       </c>
       <c r="M59" s="14" t="n">
-        <v>0.2048832792048216</v>
+        <v>0.2241668258872593</v>
       </c>
       <c r="N59" s="15" t="n">
         <v>0</v>
@@ -5588,58 +5588,64 @@
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>LOU @ MISS</t>
+          <t>APP @ ECU</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 23:30</t>
+          <t>2026-09-12 16:00</t>
         </is>
       </c>
       <c r="D67" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
         <is>
-          <t>LOU ML</t>
-        </is>
-      </c>
-      <c r="G67" s="23" t="n"/>
+          <t>APP +10</t>
+        </is>
+      </c>
+      <c r="G67" s="23" t="n">
+        <v>-10</v>
+      </c>
       <c r="H67" s="13" t="n">
-        <v>210</v>
+        <v>-110</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>0.4046035584729659</v>
+        <v>0.6048256402521389</v>
       </c>
       <c r="J67" s="15" t="n">
-        <v>0.3092071169459319</v>
+        <v>0.5</v>
       </c>
       <c r="K67" s="15" t="n">
-        <v>0.3225806451612903</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L67" s="14" t="n">
-        <v>0.0820229133116756</v>
+        <v>0.08101611644261508</v>
       </c>
       <c r="M67" s="14" t="n">
-        <v>0.2542710312661944</v>
+        <v>0.1489872529042741</v>
       </c>
       <c r="N67" s="15" t="n">
-        <v>0</v>
+        <v>0.0367</v>
       </c>
       <c r="O67" s="24" t="n">
-        <v>0.4</v>
+        <v>0.725</v>
       </c>
       <c r="P67" s="12" t="inlineStr">
         <is>
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q67" s="12" t="n"/>
+      <c r="Q67" s="12" t="inlineStr">
+        <is>
+          <t>outside the top 10 plays for this week</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="17" t="inlineStr">
@@ -5649,12 +5655,12 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>APP @ ECU</t>
+          <t>ARK @ UTAH</t>
         </is>
       </c>
       <c r="C68" s="17" t="inlineStr">
         <is>
-          <t>2026-09-12 16:00</t>
+          <t>2026-09-13 02:15</t>
         </is>
       </c>
       <c r="D68" s="25" t="n">
@@ -5667,32 +5673,32 @@
       </c>
       <c r="F68" s="17" t="inlineStr">
         <is>
-          <t>APP +10</t>
+          <t>ARK +11.5</t>
         </is>
       </c>
       <c r="G68" s="26" t="n">
-        <v>-10</v>
+        <v>-11.5</v>
       </c>
       <c r="H68" s="18" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I68" s="20" t="n">
-        <v>0.6048256402521389</v>
+        <v>0.5996411451304783</v>
       </c>
       <c r="J68" s="20" t="n">
-        <v>0.5</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K68" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L68" s="19" t="n">
-        <v>0.08101611644261508</v>
+        <v>0.08041037589970901</v>
       </c>
       <c r="M68" s="19" t="n">
-        <v>0.1489872529042741</v>
+        <v>0.154864427658699</v>
       </c>
       <c r="N68" s="20" t="n">
-        <v>0.0367</v>
+        <v>0</v>
       </c>
       <c r="O68" s="27" t="n">
         <v>0.725</v>
@@ -5716,64 +5722,58 @@
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>ARK @ UTAH</t>
+          <t>LOU @ MISS</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>2026-09-13 02:15</t>
+          <t>2026-09-06 23:30</t>
         </is>
       </c>
       <c r="D69" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
         <is>
-          <t>ARK +11.5</t>
-        </is>
-      </c>
-      <c r="G69" s="23" t="n">
-        <v>-11.5</v>
-      </c>
+          <t>LOU ML</t>
+        </is>
+      </c>
+      <c r="G69" s="23" t="n"/>
       <c r="H69" s="13" t="n">
-        <v>-108</v>
+        <v>205</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>0.5996411451304783</v>
+        <v>0.4073033707865168</v>
       </c>
       <c r="J69" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.3146067415730336</v>
       </c>
       <c r="K69" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.3278688524590164</v>
       </c>
       <c r="L69" s="14" t="n">
-        <v>0.08041037589970901</v>
+        <v>0.07943451832750043</v>
       </c>
       <c r="M69" s="14" t="n">
-        <v>0.154864427658699</v>
+        <v>0.2422752808988762</v>
       </c>
       <c r="N69" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O69" s="24" t="n">
-        <v>0.725</v>
+        <v>0.4</v>
       </c>
       <c r="P69" s="12" t="inlineStr">
         <is>
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q69" s="12" t="inlineStr">
-        <is>
-          <t>outside the top 10 plays for this week</t>
-        </is>
-      </c>
+      <c r="Q69" s="12" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="17" t="inlineStr">
@@ -5980,60 +5980,64 @@
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>WIS @ ND</t>
+          <t>USA @ TULN</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 23:30</t>
+          <t>2026-09-12 23:00</t>
         </is>
       </c>
       <c r="D73" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
+          <t>USA +10</t>
         </is>
       </c>
       <c r="G73" s="23" t="n">
-        <v>46.5</v>
+        <v>-10</v>
       </c>
       <c r="H73" s="13" t="n">
-        <v>-105</v>
+        <v>-112</v>
       </c>
       <c r="I73" s="15" t="n">
-        <v>0.5832382897791041</v>
+        <v>0.5969393227641155</v>
       </c>
       <c r="J73" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K73" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L73" s="14" t="n">
-        <v>0.07104316782788456</v>
+        <v>0.06863743597166272</v>
       </c>
       <c r="M73" s="14" t="n">
-        <v>0.1387033276639651</v>
+        <v>0.1250239810832942</v>
       </c>
       <c r="N73" s="15" t="n">
-        <v>0</v>
+        <v>0.0377</v>
       </c>
       <c r="O73" s="24" t="n">
-        <v>0.4</v>
+        <v>0.725</v>
       </c>
       <c r="P73" s="12" t="inlineStr">
         <is>
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q73" s="12" t="n"/>
+      <c r="Q73" s="12" t="inlineStr">
+        <is>
+          <t>outside the top 10 plays for this week</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="17" t="inlineStr">
@@ -6043,12 +6047,12 @@
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>OU @ MICH</t>
+          <t>OSU @ TEX</t>
         </is>
       </c>
       <c r="C74" s="17" t="inlineStr">
         <is>
-          <t>2026-09-12 16:00</t>
+          <t>2026-09-12 23:30</t>
         </is>
       </c>
       <c r="D74" s="25" t="n">
@@ -6061,29 +6065,29 @@
       </c>
       <c r="F74" s="17" t="inlineStr">
         <is>
-          <t>Over 44.5</t>
+          <t>Over 47.5</t>
         </is>
       </c>
       <c r="G74" s="26" t="n">
-        <v>44.5</v>
+        <v>47.5</v>
       </c>
       <c r="H74" s="18" t="n">
-        <v>-118</v>
+        <v>-110</v>
       </c>
       <c r="I74" s="20" t="n">
-        <v>0.6114217086662477</v>
+        <v>0.5922287555912803</v>
       </c>
       <c r="J74" s="20" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.5</v>
       </c>
       <c r="K74" s="20" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L74" s="19" t="n">
-        <v>0.07013730499652293</v>
+        <v>0.06841923178175646</v>
       </c>
       <c r="M74" s="19" t="n">
-        <v>0.1295756990613728</v>
+        <v>0.1306185334015352</v>
       </c>
       <c r="N74" s="20" t="n">
         <v>0</v>
@@ -6098,7 +6102,7 @@
       </c>
       <c r="Q74" s="17" t="inlineStr">
         <is>
-          <t>correlated with a stronger play on the same game</t>
+          <t>outside the top 10 plays for this week</t>
         </is>
       </c>
     </row>
@@ -6110,64 +6114,60 @@
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>USA @ TULN</t>
+          <t>WIS @ ND</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12 23:00</t>
+          <t>2026-09-06 23:30</t>
         </is>
       </c>
       <c r="D75" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
-          <t>USA +10</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="G75" s="23" t="n">
-        <v>-10</v>
+        <v>46.5</v>
       </c>
       <c r="H75" s="13" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="I75" s="15" t="n">
-        <v>0.5969393227641155</v>
+        <v>0.5864905308372941</v>
       </c>
       <c r="J75" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K75" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L75" s="14" t="n">
-        <v>0.06863743597166272</v>
+        <v>0.0672597616065248</v>
       </c>
       <c r="M75" s="14" t="n">
-        <v>0.1250239810832942</v>
+        <v>0.1295373186496035</v>
       </c>
       <c r="N75" s="15" t="n">
-        <v>0.0377</v>
+        <v>0</v>
       </c>
       <c r="O75" s="24" t="n">
-        <v>0.725</v>
+        <v>0.4</v>
       </c>
       <c r="P75" s="12" t="inlineStr">
         <is>
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q75" s="12" t="inlineStr">
-        <is>
-          <t>outside the top 10 plays for this week</t>
-        </is>
-      </c>
+      <c r="Q75" s="12" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="17" t="inlineStr">
@@ -6177,12 +6177,12 @@
       </c>
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>OSU @ TEX</t>
+          <t>SDSU @ UCLA</t>
         </is>
       </c>
       <c r="C76" s="17" t="inlineStr">
         <is>
-          <t>2026-09-12 23:30</t>
+          <t>2026-09-12 23:15</t>
         </is>
       </c>
       <c r="D76" s="25" t="n">
@@ -6195,17 +6195,17 @@
       </c>
       <c r="F76" s="17" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="G76" s="26" t="n">
-        <v>47.5</v>
+        <v>48.5</v>
       </c>
       <c r="H76" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I76" s="20" t="n">
-        <v>0.5922287555912803</v>
+        <v>0.5904462655465561</v>
       </c>
       <c r="J76" s="20" t="n">
         <v>0.5</v>
@@ -6214,10 +6214,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L76" s="19" t="n">
-        <v>0.06841923178175646</v>
+        <v>0.06663674173703227</v>
       </c>
       <c r="M76" s="19" t="n">
-        <v>0.1306185334015352</v>
+        <v>0.1272155978616072</v>
       </c>
       <c r="N76" s="20" t="n">
         <v>0</v>
@@ -6244,12 +6244,12 @@
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>SDSU @ UCLA</t>
+          <t>MSST @ MINN</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12 23:15</t>
+          <t>2026-09-12 19:30</t>
         </is>
       </c>
       <c r="D77" s="22" t="n">
@@ -6257,34 +6257,34 @@
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>MINN +1.5</t>
         </is>
       </c>
       <c r="G77" s="23" t="n">
-        <v>48.5</v>
+        <v>1.5</v>
       </c>
       <c r="H77" s="13" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="I77" s="15" t="n">
-        <v>0.5904462655465561</v>
+        <v>0.5943465059010947</v>
       </c>
       <c r="J77" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K77" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L77" s="14" t="n">
-        <v>0.06663674173703227</v>
+        <v>0.0660446191086419</v>
       </c>
       <c r="M77" s="14" t="n">
-        <v>0.1272155978616072</v>
+        <v>0.1250130290270721</v>
       </c>
       <c r="N77" s="15" t="n">
         <v>0</v>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="Q77" s="12" t="inlineStr">
         <is>
-          <t>outside the top 10 plays for this week</t>
+          <t>correlated with a stronger play on the same game</t>
         </is>
       </c>
     </row>
@@ -6311,12 +6311,12 @@
       </c>
       <c r="B78" s="17" t="inlineStr">
         <is>
-          <t>MSST @ MINN</t>
+          <t>OU @ MICH</t>
         </is>
       </c>
       <c r="C78" s="17" t="inlineStr">
         <is>
-          <t>2026-09-12 19:30</t>
+          <t>2026-09-12 16:00</t>
         </is>
       </c>
       <c r="D78" s="25" t="n">
@@ -6324,34 +6324,34 @@
       </c>
       <c r="E78" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F78" s="17" t="inlineStr">
         <is>
-          <t>MINN +1.5</t>
+          <t>Over 45.5</t>
         </is>
       </c>
       <c r="G78" s="26" t="n">
-        <v>1.5</v>
+        <v>45.5</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="I78" s="20" t="n">
-        <v>0.5943465059010947</v>
+        <v>0.5828841461753553</v>
       </c>
       <c r="J78" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K78" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L78" s="19" t="n">
-        <v>0.0660446191086419</v>
+        <v>0.06365337694458606</v>
       </c>
       <c r="M78" s="19" t="n">
-        <v>0.1250130290270721</v>
+        <v>0.122591688930314</v>
       </c>
       <c r="N78" s="20" t="n">
         <v>0</v>
@@ -9268,16 +9268,16 @@
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>WSU @ WASH</t>
+          <t>PSU @ TEM</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 20:00</t>
+          <t>2026-09-12 16:00</t>
         </is>
       </c>
       <c r="D125" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E125" s="12" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>-105</v>
       </c>
       <c r="I125" s="15" t="n">
-        <v>0.5085402935366987</v>
+        <v>0.5045564584546383</v>
       </c>
       <c r="J125" s="15" t="n">
         <v>0.4891657638136511</v>
@@ -9305,16 +9305,16 @@
         <v>0.5121951219512195</v>
       </c>
       <c r="L125" s="14" t="n">
-        <v>-0.003654828414520805</v>
+        <v>-0.007638663496581266</v>
       </c>
       <c r="M125" s="14" t="n">
-        <v>-0.007135617380731096</v>
+        <v>-0.01491358111237295</v>
       </c>
       <c r="N125" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O125" s="24" t="n">
-        <v>0.4</v>
+        <v>0.725</v>
       </c>
       <c r="P125" s="12" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
       </c>
       <c r="B126" s="17" t="inlineStr">
         <is>
-          <t>PSU @ TEM</t>
+          <t>USF @ ARMY</t>
         </is>
       </c>
       <c r="C126" s="17" t="inlineStr">
@@ -9349,29 +9349,29 @@
       </c>
       <c r="F126" s="17" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>Under 52.5</t>
         </is>
       </c>
       <c r="G126" s="26" t="n">
-        <v>51.5</v>
+        <v>52.5</v>
       </c>
       <c r="H126" s="18" t="n">
-        <v>-105</v>
+        <v>-112</v>
       </c>
       <c r="I126" s="20" t="n">
-        <v>0.5045564584546383</v>
+        <v>0.520100508114556</v>
       </c>
       <c r="J126" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K126" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L126" s="19" t="n">
-        <v>-0.007638663496581266</v>
+        <v>-0.008201378677896831</v>
       </c>
       <c r="M126" s="19" t="n">
-        <v>-0.01491358111237295</v>
+        <v>-0.01552403821173332</v>
       </c>
       <c r="N126" s="20" t="n">
         <v>0</v>
@@ -9394,12 +9394,12 @@
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>USF @ ARMY</t>
+          <t>ARIZ @ BYU</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12 16:00</t>
+          <t>2026-09-12 19:30</t>
         </is>
       </c>
       <c r="D127" s="22" t="n">
@@ -9412,29 +9412,29 @@
       </c>
       <c r="F127" s="12" t="inlineStr">
         <is>
-          <t>Under 52.5</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="G127" s="23" t="n">
-        <v>52.5</v>
+        <v>51.5</v>
       </c>
       <c r="H127" s="13" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="I127" s="15" t="n">
-        <v>0.520100508114556</v>
+        <v>0.5078086995128284</v>
       </c>
       <c r="J127" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K127" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L127" s="14" t="n">
-        <v>-0.008201378677896831</v>
+        <v>-0.01142206971794091</v>
       </c>
       <c r="M127" s="14" t="n">
-        <v>-0.01552403821173332</v>
+        <v>-0.02199806019751566</v>
       </c>
       <c r="N127" s="15" t="n">
         <v>0</v>
@@ -9457,12 +9457,12 @@
       </c>
       <c r="B128" s="17" t="inlineStr">
         <is>
-          <t>ARIZ @ BYU</t>
+          <t>ODU @ VT</t>
         </is>
       </c>
       <c r="C128" s="17" t="inlineStr">
         <is>
-          <t>2026-09-12 19:30</t>
+          <t>2026-09-12 16:00</t>
         </is>
       </c>
       <c r="D128" s="25" t="n">
@@ -9482,22 +9482,22 @@
         <v>51.5</v>
       </c>
       <c r="H128" s="18" t="n">
-        <v>-108</v>
+        <v>-115</v>
       </c>
       <c r="I128" s="20" t="n">
-        <v>0.5078086995128284</v>
+        <v>0.5233527870201667</v>
       </c>
       <c r="J128" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K128" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L128" s="19" t="n">
-        <v>-0.01142206971794091</v>
+        <v>-0.01153093391006577</v>
       </c>
       <c r="M128" s="19" t="n">
-        <v>-0.02199806019751566</v>
+        <v>-0.02155783296229702</v>
       </c>
       <c r="N128" s="20" t="n">
         <v>0</v>
@@ -9520,16 +9520,16 @@
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>ODU @ VT</t>
+          <t>WSU @ WASH</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12 16:00</t>
+          <t>2026-09-06 20:00</t>
         </is>
       </c>
       <c r="D129" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E129" s="12" t="inlineStr">
         <is>
@@ -9545,28 +9545,28 @@
         <v>51.5</v>
       </c>
       <c r="H129" s="13" t="n">
-        <v>-115</v>
+        <v>-112</v>
       </c>
       <c r="I129" s="15" t="n">
-        <v>0.5233527870201667</v>
+        <v>0.5161222886648575</v>
       </c>
       <c r="J129" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K129" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L129" s="14" t="n">
-        <v>-0.01153093391006577</v>
+        <v>-0.01217959812759528</v>
       </c>
       <c r="M129" s="14" t="n">
-        <v>-0.02155783296229702</v>
+        <v>-0.02305423931294825</v>
       </c>
       <c r="N129" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O129" s="24" t="n">
-        <v>0.725</v>
+        <v>0.4</v>
       </c>
       <c r="P129" s="12" t="inlineStr">
         <is>
@@ -10591,16 +10591,16 @@
       </c>
       <c r="B146" s="17" t="inlineStr">
         <is>
-          <t>ODU @ VT</t>
+          <t>WSU @ WASH</t>
         </is>
       </c>
       <c r="C146" s="17" t="inlineStr">
         <is>
-          <t>2026-09-12 16:00</t>
+          <t>2026-09-06 20:00</t>
         </is>
       </c>
       <c r="D146" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E146" s="17" t="inlineStr">
         <is>
@@ -10616,28 +10616,28 @@
         <v>51.5</v>
       </c>
       <c r="H146" s="18" t="n">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="I146" s="20" t="n">
-        <v>0.4766472129798333</v>
+        <v>0.4838777113351425</v>
       </c>
       <c r="J146" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K146" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L146" s="19" t="n">
-        <v>-0.03554790897138627</v>
+        <v>-0.03535305789562682</v>
       </c>
       <c r="M146" s="19" t="n">
-        <v>-0.06940306037270655</v>
+        <v>-0.06808737076194782</v>
       </c>
       <c r="N146" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O146" s="27" t="n">
-        <v>0.725</v>
+        <v>0.4</v>
       </c>
       <c r="P146" s="17" t="inlineStr">
         <is>
@@ -10654,12 +10654,12 @@
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t>ARIZ @ BYU</t>
+          <t>ODU @ VT</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12 19:30</t>
+          <t>2026-09-12 16:00</t>
         </is>
       </c>
       <c r="D147" s="22" t="n">
@@ -10679,22 +10679,22 @@
         <v>51.5</v>
       </c>
       <c r="H147" s="13" t="n">
-        <v>-112</v>
+        <v>-105</v>
       </c>
       <c r="I147" s="15" t="n">
-        <v>0.4921913004871716</v>
+        <v>0.4766472129798333</v>
       </c>
       <c r="J147" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K147" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L147" s="14" t="n">
-        <v>-0.03611058630528119</v>
+        <v>-0.03554790897138627</v>
       </c>
       <c r="M147" s="14" t="n">
-        <v>-0.06835218122071085</v>
+        <v>-0.06940306037270655</v>
       </c>
       <c r="N147" s="15" t="n">
         <v>0</v>
@@ -10717,12 +10717,12 @@
       </c>
       <c r="B148" s="17" t="inlineStr">
         <is>
-          <t>USF @ ARMY</t>
+          <t>ARIZ @ BYU</t>
         </is>
       </c>
       <c r="C148" s="17" t="inlineStr">
         <is>
-          <t>2026-09-12 16:00</t>
+          <t>2026-09-12 19:30</t>
         </is>
       </c>
       <c r="D148" s="25" t="n">
@@ -10735,29 +10735,29 @@
       </c>
       <c r="F148" s="17" t="inlineStr">
         <is>
-          <t>Over 52.5</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="G148" s="26" t="n">
-        <v>52.5</v>
+        <v>51.5</v>
       </c>
       <c r="H148" s="18" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I148" s="20" t="n">
-        <v>0.479899491885444</v>
+        <v>0.4921913004871716</v>
       </c>
       <c r="J148" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K148" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L148" s="19" t="n">
-        <v>-0.03933127734532527</v>
+        <v>-0.03611058630528119</v>
       </c>
       <c r="M148" s="19" t="n">
-        <v>-0.0757491267391448</v>
+        <v>-0.06835218122071085</v>
       </c>
       <c r="N148" s="20" t="n">
         <v>0</v>
@@ -10780,7 +10780,7 @@
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t>PSU @ TEM</t>
+          <t>USF @ ARMY</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
@@ -10798,29 +10798,29 @@
       </c>
       <c r="F149" s="12" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>Over 52.5</t>
         </is>
       </c>
       <c r="G149" s="23" t="n">
-        <v>51.5</v>
+        <v>52.5</v>
       </c>
       <c r="H149" s="13" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="I149" s="15" t="n">
-        <v>0.4954435415453617</v>
+        <v>0.479899491885444</v>
       </c>
       <c r="J149" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K149" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L149" s="14" t="n">
-        <v>-0.03944017938487077</v>
+        <v>-0.03933127734532527</v>
       </c>
       <c r="M149" s="14" t="n">
-        <v>-0.0737359875456281</v>
+        <v>-0.0757491267391448</v>
       </c>
       <c r="N149" s="15" t="n">
         <v>0</v>
@@ -10843,16 +10843,16 @@
       </c>
       <c r="B150" s="17" t="inlineStr">
         <is>
-          <t>WSU @ WASH</t>
+          <t>PSU @ TEM</t>
         </is>
       </c>
       <c r="C150" s="17" t="inlineStr">
         <is>
-          <t>2026-09-06 20:00</t>
+          <t>2026-09-12 16:00</t>
         </is>
       </c>
       <c r="D150" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E150" s="17" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
         <v>-115</v>
       </c>
       <c r="I150" s="20" t="n">
-        <v>0.4914597064633013</v>
+        <v>0.4954435415453617</v>
       </c>
       <c r="J150" s="20" t="n">
         <v>0.5108342361863488</v>
@@ -10880,16 +10880,16 @@
         <v>0.5348837209302325</v>
       </c>
       <c r="L150" s="19" t="n">
-        <v>-0.04342401446693123</v>
+        <v>-0.03944017938487077</v>
       </c>
       <c r="M150" s="19" t="n">
-        <v>-0.08118402704687161</v>
+        <v>-0.0737359875456281</v>
       </c>
       <c r="N150" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O150" s="27" t="n">
-        <v>0.4</v>
+        <v>0.725</v>
       </c>
       <c r="P150" s="17" t="inlineStr">
         <is>
@@ -13780,12 +13780,12 @@
       </c>
       <c r="B197" s="12" t="inlineStr">
         <is>
-          <t>MSST @ MINN</t>
+          <t>OU @ MICH</t>
         </is>
       </c>
       <c r="C197" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12 19:30</t>
+          <t>2026-09-12 16:00</t>
         </is>
       </c>
       <c r="D197" s="22" t="n">
@@ -13793,34 +13793,34 @@
       </c>
       <c r="E197" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F197" s="12" t="inlineStr">
         <is>
-          <t>MSST -1.5</t>
+          <t>Under 45.5</t>
         </is>
       </c>
       <c r="G197" s="23" t="n">
-        <v>1.5</v>
+        <v>45.5</v>
       </c>
       <c r="H197" s="13" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I197" s="15" t="n">
-        <v>0.4056534940989053</v>
+        <v>0.4171158538246447</v>
       </c>
       <c r="J197" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K197" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L197" s="14" t="n">
-        <v>-0.113577275131864</v>
+        <v>-0.1111860329678082</v>
       </c>
       <c r="M197" s="14" t="n">
-        <v>-0.2187414187724787</v>
+        <v>-0.2104592766890655</v>
       </c>
       <c r="N197" s="15" t="n">
         <v>0</v>
@@ -13843,12 +13843,12 @@
       </c>
       <c r="B198" s="17" t="inlineStr">
         <is>
-          <t>SDSU @ UCLA</t>
+          <t>MSST @ MINN</t>
         </is>
       </c>
       <c r="C198" s="17" t="inlineStr">
         <is>
-          <t>2026-09-12 23:15</t>
+          <t>2026-09-12 19:30</t>
         </is>
       </c>
       <c r="D198" s="25" t="n">
@@ -13856,34 +13856,34 @@
       </c>
       <c r="E198" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F198" s="17" t="inlineStr">
         <is>
-          <t>Under 48.5</t>
+          <t>MSST -1.5</t>
         </is>
       </c>
       <c r="G198" s="26" t="n">
-        <v>48.5</v>
+        <v>1.5</v>
       </c>
       <c r="H198" s="18" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I198" s="20" t="n">
-        <v>0.4095537344534439</v>
+        <v>0.4056534940989053</v>
       </c>
       <c r="J198" s="20" t="n">
-        <v>0.5</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K198" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L198" s="19" t="n">
-        <v>-0.1142557893560799</v>
+        <v>-0.113577275131864</v>
       </c>
       <c r="M198" s="19" t="n">
-        <v>-0.218124688770698</v>
+        <v>-0.2187414187724787</v>
       </c>
       <c r="N198" s="20" t="n">
         <v>0</v>
@@ -13906,12 +13906,12 @@
       </c>
       <c r="B199" s="12" t="inlineStr">
         <is>
-          <t>MSST @ MINN</t>
+          <t>SDSU @ UCLA</t>
         </is>
       </c>
       <c r="C199" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12 19:30</t>
+          <t>2026-09-12 23:15</t>
         </is>
       </c>
       <c r="D199" s="22" t="n">
@@ -13919,32 +13919,34 @@
       </c>
       <c r="E199" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F199" s="12" t="inlineStr">
         <is>
-          <t>MSST ML</t>
-        </is>
-      </c>
-      <c r="G199" s="23" t="n"/>
+          <t>Under 48.5</t>
+        </is>
+      </c>
+      <c r="G199" s="23" t="n">
+        <v>48.5</v>
+      </c>
       <c r="H199" s="13" t="n">
-        <v>-125</v>
+        <v>-110</v>
       </c>
       <c r="I199" s="15" t="n">
-        <v>0.4406866615660716</v>
+        <v>0.4095537344534439</v>
       </c>
       <c r="J199" s="15" t="n">
-        <v>0.5324675324675325</v>
+        <v>0.5</v>
       </c>
       <c r="K199" s="15" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L199" s="14" t="n">
-        <v>-0.114868893989484</v>
+        <v>-0.1142557893560799</v>
       </c>
       <c r="M199" s="14" t="n">
-        <v>-0.2067640091810711</v>
+        <v>-0.218124688770698</v>
       </c>
       <c r="N199" s="15" t="n">
         <v>0</v>
@@ -13967,16 +13969,16 @@
       </c>
       <c r="B200" s="17" t="inlineStr">
         <is>
-          <t>OSU @ TEX</t>
+          <t>WIS @ ND</t>
         </is>
       </c>
       <c r="C200" s="17" t="inlineStr">
         <is>
-          <t>2026-09-12 23:30</t>
+          <t>2026-09-06 23:30</t>
         </is>
       </c>
       <c r="D200" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E200" s="17" t="inlineStr">
         <is>
@@ -13985,35 +13987,35 @@
       </c>
       <c r="F200" s="17" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
+          <t>Under 46.5</t>
         </is>
       </c>
       <c r="G200" s="26" t="n">
-        <v>47.5</v>
+        <v>46.5</v>
       </c>
       <c r="H200" s="18" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="I200" s="20" t="n">
-        <v>0.4077712444087197</v>
+        <v>0.4135094691627059</v>
       </c>
       <c r="J200" s="20" t="n">
-        <v>0.5</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K200" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L200" s="19" t="n">
-        <v>-0.1160382794008041</v>
+        <v>-0.1147924176297469</v>
       </c>
       <c r="M200" s="19" t="n">
-        <v>-0.221527624310626</v>
+        <v>-0.2172856476563066</v>
       </c>
       <c r="N200" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O200" s="27" t="n">
-        <v>0.725</v>
+        <v>0.4</v>
       </c>
       <c r="P200" s="17" t="inlineStr">
         <is>
@@ -14030,12 +14032,12 @@
       </c>
       <c r="B201" s="12" t="inlineStr">
         <is>
-          <t>USA @ TULN</t>
+          <t>MSST @ MINN</t>
         </is>
       </c>
       <c r="C201" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12 23:00</t>
+          <t>2026-09-12 19:30</t>
         </is>
       </c>
       <c r="D201" s="22" t="n">
@@ -14043,37 +14045,35 @@
       </c>
       <c r="E201" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F201" s="12" t="inlineStr">
         <is>
-          <t>TULN -10</t>
-        </is>
-      </c>
-      <c r="G201" s="23" t="n">
-        <v>-10</v>
-      </c>
+          <t>MSST ML</t>
+        </is>
+      </c>
+      <c r="G201" s="23" t="n"/>
       <c r="H201" s="13" t="n">
-        <v>-108</v>
+        <v>-125</v>
       </c>
       <c r="I201" s="15" t="n">
-        <v>0.4030606772358844</v>
+        <v>0.4406866615660716</v>
       </c>
       <c r="J201" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5324675324675325</v>
       </c>
       <c r="K201" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="L201" s="14" t="n">
-        <v>-0.1161700919948849</v>
+        <v>-0.114868893989484</v>
       </c>
       <c r="M201" s="14" t="n">
-        <v>-0.2153021401066282</v>
+        <v>-0.2067640091810711</v>
       </c>
       <c r="N201" s="15" t="n">
-        <v>0.0377</v>
+        <v>0</v>
       </c>
       <c r="O201" s="24" t="n">
         <v>0.725</v>
@@ -14093,12 +14093,12 @@
       </c>
       <c r="B202" s="17" t="inlineStr">
         <is>
-          <t>OU @ MICH</t>
+          <t>OSU @ TEX</t>
         </is>
       </c>
       <c r="C202" s="17" t="inlineStr">
         <is>
-          <t>2026-09-12 16:00</t>
+          <t>2026-09-12 23:30</t>
         </is>
       </c>
       <c r="D202" s="25" t="n">
@@ -14111,29 +14111,29 @@
       </c>
       <c r="F202" s="17" t="inlineStr">
         <is>
-          <t>Under 44.5</t>
+          <t>Under 47.5</t>
         </is>
       </c>
       <c r="G202" s="26" t="n">
-        <v>44.5</v>
+        <v>47.5</v>
       </c>
       <c r="H202" s="18" t="n">
-        <v>-102</v>
+        <v>-110</v>
       </c>
       <c r="I202" s="20" t="n">
-        <v>0.3885782913337523</v>
+        <v>0.4077712444087197</v>
       </c>
       <c r="J202" s="20" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.5</v>
       </c>
       <c r="K202" s="20" t="n">
-        <v>0.504950495049505</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L202" s="19" t="n">
-        <v>-0.1163722037157526</v>
+        <v>-0.1160382794008041</v>
       </c>
       <c r="M202" s="19" t="n">
-        <v>-0.2304625995155101</v>
+        <v>-0.221527624310626</v>
       </c>
       <c r="N202" s="20" t="n">
         <v>0</v>
@@ -14156,53 +14156,53 @@
       </c>
       <c r="B203" s="12" t="inlineStr">
         <is>
-          <t>WIS @ ND</t>
+          <t>USA @ TULN</t>
         </is>
       </c>
       <c r="C203" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 23:30</t>
+          <t>2026-09-12 23:00</t>
         </is>
       </c>
       <c r="D203" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E203" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F203" s="12" t="inlineStr">
         <is>
-          <t>Under 46.5</t>
+          <t>TULN -10</t>
         </is>
       </c>
       <c r="G203" s="23" t="n">
-        <v>46.5</v>
+        <v>-10</v>
       </c>
       <c r="H203" s="13" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="I203" s="15" t="n">
-        <v>0.4167617102208959</v>
+        <v>0.4030606772358844</v>
       </c>
       <c r="J203" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K203" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L203" s="14" t="n">
-        <v>-0.1181220107093366</v>
+        <v>-0.1161700919948849</v>
       </c>
       <c r="M203" s="14" t="n">
-        <v>-0.220836802630499</v>
+        <v>-0.2153021401066282</v>
       </c>
       <c r="N203" s="15" t="n">
-        <v>0</v>
+        <v>0.0377</v>
       </c>
       <c r="O203" s="24" t="n">
-        <v>0.4</v>
+        <v>0.725</v>
       </c>
       <c r="P203" s="12" t="inlineStr">
         <is>
@@ -14280,16 +14280,16 @@
       </c>
       <c r="B205" s="12" t="inlineStr">
         <is>
-          <t>ASU @ TA&amp;M</t>
+          <t>LOU @ MISS</t>
         </is>
       </c>
       <c r="C205" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12 16:00</t>
+          <t>2026-09-06 23:30</t>
         </is>
       </c>
       <c r="D205" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E205" s="12" t="inlineStr">
         <is>
@@ -14298,44 +14298,40 @@
       </c>
       <c r="F205" s="12" t="inlineStr">
         <is>
-          <t>TA&amp;M ML</t>
+          <t>MISS ML</t>
         </is>
       </c>
       <c r="G205" s="23" t="n"/>
       <c r="H205" s="13" t="n">
-        <v>-650</v>
+        <v>-250</v>
       </c>
       <c r="I205" s="15" t="n">
-        <v>0.7419084049890994</v>
+        <v>0.5926966292134832</v>
       </c>
       <c r="J205" s="15" t="n">
-        <v>0.8316498316498315</v>
+        <v>0.6853932584269663</v>
       </c>
       <c r="K205" s="15" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="L205" s="14" t="n">
-        <v>-0.1247582616775673</v>
+        <v>-0.1215890850722311</v>
       </c>
       <c r="M205" s="14" t="n">
-        <v>-0.1439518403971931</v>
+        <v>-0.1702247191011236</v>
       </c>
       <c r="N205" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O205" s="24" t="n">
-        <v>0.725</v>
+        <v>0.4</v>
       </c>
       <c r="P205" s="12" t="inlineStr">
         <is>
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q205" s="12" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+      <c r="Q205" s="12" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="17" t="inlineStr">
@@ -14345,12 +14341,12 @@
       </c>
       <c r="B206" s="17" t="inlineStr">
         <is>
-          <t>MTSU @ MRSH</t>
+          <t>ASU @ TA&amp;M</t>
         </is>
       </c>
       <c r="C206" s="17" t="inlineStr">
         <is>
-          <t>2026-09-12 23:00</t>
+          <t>2026-09-12 16:00</t>
         </is>
       </c>
       <c r="D206" s="25" t="n">
@@ -14358,34 +14354,32 @@
       </c>
       <c r="E206" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F206" s="17" t="inlineStr">
         <is>
-          <t>Over 57.5</t>
-        </is>
-      </c>
-      <c r="G206" s="26" t="n">
-        <v>57.5</v>
-      </c>
+          <t>TA&amp;M ML</t>
+        </is>
+      </c>
+      <c r="G206" s="26" t="n"/>
       <c r="H206" s="18" t="n">
-        <v>-115</v>
+        <v>-650</v>
       </c>
       <c r="I206" s="20" t="n">
-        <v>0.4096491933569829</v>
+        <v>0.7419084049890994</v>
       </c>
       <c r="J206" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.8316498316498315</v>
       </c>
       <c r="K206" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="L206" s="19" t="n">
-        <v>-0.1252345275732496</v>
+        <v>-0.1247582616775673</v>
       </c>
       <c r="M206" s="19" t="n">
-        <v>-0.2341341167673798</v>
+        <v>-0.1439518403971931</v>
       </c>
       <c r="N206" s="20" t="n">
         <v>0</v>
@@ -14398,7 +14392,11 @@
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q206" s="17" t="n"/>
+      <c r="Q206" s="17" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="12" t="inlineStr">
@@ -14408,51 +14406,53 @@
       </c>
       <c r="B207" s="12" t="inlineStr">
         <is>
-          <t>LOU @ MISS</t>
+          <t>MTSU @ MRSH</t>
         </is>
       </c>
       <c r="C207" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06 23:30</t>
+          <t>2026-09-12 23:00</t>
         </is>
       </c>
       <c r="D207" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E207" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F207" s="12" t="inlineStr">
         <is>
-          <t>MISS ML</t>
-        </is>
-      </c>
-      <c r="G207" s="23" t="n"/>
+          <t>Over 57.5</t>
+        </is>
+      </c>
+      <c r="G207" s="23" t="n">
+        <v>57.5</v>
+      </c>
       <c r="H207" s="13" t="n">
-        <v>-258</v>
+        <v>-115</v>
       </c>
       <c r="I207" s="15" t="n">
-        <v>0.5953964415270341</v>
+        <v>0.4096491933569829</v>
       </c>
       <c r="J207" s="15" t="n">
-        <v>0.6907928830540681</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K207" s="15" t="n">
-        <v>0.7206703910614525</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L207" s="14" t="n">
-        <v>-0.1252739495344184</v>
+        <v>-0.1252345275732496</v>
       </c>
       <c r="M207" s="14" t="n">
-        <v>-0.1738297439276039</v>
+        <v>-0.2341341167673798</v>
       </c>
       <c r="N207" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O207" s="24" t="n">
-        <v>0.4</v>
+        <v>0.725</v>
       </c>
       <c r="P207" s="12" t="inlineStr">
         <is>
@@ -15353,12 +15353,12 @@
       </c>
       <c r="B222" s="17" t="inlineStr">
         <is>
-          <t>OU @ MICH</t>
+          <t>USU @ WASH</t>
         </is>
       </c>
       <c r="C222" s="17" t="inlineStr">
         <is>
-          <t>2026-09-12 16:00</t>
+          <t>2026-09-12 19:30</t>
         </is>
       </c>
       <c r="D222" s="25" t="n">
@@ -15366,47 +15366,49 @@
       </c>
       <c r="E222" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F222" s="17" t="inlineStr">
         <is>
-          <t>OU -4.5</t>
-        </is>
-      </c>
-      <c r="G222" s="26" t="n">
-        <v>4.5</v>
-      </c>
+          <t>WASH ML</t>
+        </is>
+      </c>
+      <c r="G222" s="26" t="n"/>
       <c r="H222" s="18" t="n">
-        <v>-115</v>
+        <v>-2400</v>
       </c>
       <c r="I222" s="20" t="n">
-        <v>0.3828646618707011</v>
+        <v>0.8035054206790249</v>
       </c>
       <c r="J222" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.9258160237388724</v>
       </c>
       <c r="K222" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.96</v>
       </c>
       <c r="L222" s="19" t="n">
-        <v>-0.1520190590595314</v>
+        <v>-0.1564945793209751</v>
       </c>
       <c r="M222" s="19" t="n">
-        <v>-0.2842095451982545</v>
+        <v>-0.1630151867926824</v>
       </c>
       <c r="N222" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O222" s="27" t="n">
-        <v>0.725</v>
+        <v>0.4</v>
       </c>
       <c r="P222" s="17" t="inlineStr">
         <is>
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q222" s="17" t="n"/>
+      <c r="Q222" s="17" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="12" t="inlineStr">
@@ -15439,22 +15441,22 @@
       </c>
       <c r="G223" s="23" t="n"/>
       <c r="H223" s="13" t="n">
-        <v>-205</v>
+        <v>-218</v>
       </c>
       <c r="I223" s="15" t="n">
-        <v>0.5195330683271102</v>
+        <v>0.5259060920247964</v>
       </c>
       <c r="J223" s="15" t="n">
-        <v>0.6447291788002329</v>
+        <v>0.6574752261956054</v>
       </c>
       <c r="K223" s="15" t="n">
-        <v>0.6721311475409836</v>
+        <v>0.6855345911949685</v>
       </c>
       <c r="L223" s="14" t="n">
-        <v>-0.1525980792138734</v>
+        <v>-0.1596284991701721</v>
       </c>
       <c r="M223" s="14" t="n">
-        <v>-0.227036166635275</v>
+        <v>-0.2328525813583245</v>
       </c>
       <c r="N223" s="15" t="n">
         <v>0</v>
@@ -15477,12 +15479,12 @@
       </c>
       <c r="B224" s="17" t="inlineStr">
         <is>
-          <t>USU @ WASH</t>
+          <t>MTSU @ MRSH</t>
         </is>
       </c>
       <c r="C224" s="17" t="inlineStr">
         <is>
-          <t>2026-09-12 19:30</t>
+          <t>2026-09-12 23:00</t>
         </is>
       </c>
       <c r="D224" s="25" t="n">
@@ -15495,33 +15497,33 @@
       </c>
       <c r="F224" s="17" t="inlineStr">
         <is>
-          <t>WASH ML</t>
+          <t>MRSH ML</t>
         </is>
       </c>
       <c r="G224" s="26" t="n"/>
       <c r="H224" s="18" t="n">
-        <v>-2400</v>
+        <v>-1000</v>
       </c>
       <c r="I224" s="20" t="n">
-        <v>0.8035054206790249</v>
+        <v>0.7492447435969138</v>
       </c>
       <c r="J224" s="20" t="n">
-        <v>0.9258160237388724</v>
+        <v>0.8720930232558138</v>
       </c>
       <c r="K224" s="20" t="n">
-        <v>0.96</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="L224" s="19" t="n">
-        <v>-0.1564945793209751</v>
+        <v>-0.1598461654939952</v>
       </c>
       <c r="M224" s="19" t="n">
-        <v>-0.1630151867926824</v>
+        <v>-0.1758307820433947</v>
       </c>
       <c r="N224" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O224" s="27" t="n">
-        <v>0.4</v>
+        <v>0.725</v>
       </c>
       <c r="P224" s="17" t="inlineStr">
         <is>
@@ -15542,12 +15544,12 @@
       </c>
       <c r="B225" s="12" t="inlineStr">
         <is>
-          <t>MTSU @ MRSH</t>
+          <t>NMSU @ HAW</t>
         </is>
       </c>
       <c r="C225" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12 23:00</t>
+          <t>2026-09-13 03:59</t>
         </is>
       </c>
       <c r="D225" s="22" t="n">
@@ -15555,49 +15557,47 @@
       </c>
       <c r="E225" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F225" s="12" t="inlineStr">
         <is>
-          <t>MRSH ML</t>
-        </is>
-      </c>
-      <c r="G225" s="23" t="n"/>
+          <t>HAW -11.5</t>
+        </is>
+      </c>
+      <c r="G225" s="23" t="n">
+        <v>-11.5</v>
+      </c>
       <c r="H225" s="13" t="n">
-        <v>-1000</v>
+        <v>-112</v>
       </c>
       <c r="I225" s="15" t="n">
-        <v>0.7492447435969138</v>
+        <v>0.366946682340708</v>
       </c>
       <c r="J225" s="15" t="n">
-        <v>0.8720930232558138</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K225" s="15" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L225" s="14" t="n">
-        <v>-0.1598461654939952</v>
+        <v>-0.1613552044517448</v>
       </c>
       <c r="M225" s="14" t="n">
-        <v>-0.1758307820433947</v>
+        <v>-0.3054223512836598</v>
       </c>
       <c r="N225" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O225" s="24" t="n">
-        <v>0.725</v>
+        <v>0.839</v>
       </c>
       <c r="P225" s="12" t="inlineStr">
         <is>
           <t>DraftKings</t>
         </is>
       </c>
-      <c r="Q225" s="12" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+      <c r="Q225" s="12" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="17" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="B226" s="17" t="inlineStr">
         <is>
-          <t>NMSU @ HAW</t>
+          <t>OU @ MICH</t>
         </is>
       </c>
       <c r="C226" s="17" t="inlineStr">
         <is>
-          <t>2026-09-13 03:59</t>
+          <t>2026-09-12 16:00</t>
         </is>
       </c>
       <c r="D226" s="25" t="n">
@@ -15625,35 +15625,35 @@
       </c>
       <c r="F226" s="17" t="inlineStr">
         <is>
-          <t>HAW -11.5</t>
+          <t>OU -5.5</t>
         </is>
       </c>
       <c r="G226" s="26" t="n">
-        <v>-11.5</v>
+        <v>5.5</v>
       </c>
       <c r="H226" s="18" t="n">
-        <v>-112</v>
+        <v>-115</v>
       </c>
       <c r="I226" s="20" t="n">
-        <v>0.366946682340708</v>
+        <v>0.3729877233260379</v>
       </c>
       <c r="J226" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K226" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L226" s="19" t="n">
-        <v>-0.1613552044517448</v>
+        <v>-0.1618959976041946</v>
       </c>
       <c r="M226" s="19" t="n">
-        <v>-0.3054223512836598</v>
+        <v>-0.3026751259556683</v>
       </c>
       <c r="N226" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O226" s="27" t="n">
-        <v>0.839</v>
+        <v>0.725</v>
       </c>
       <c r="P226" s="17" t="inlineStr">
         <is>
@@ -17847,53 +17847,51 @@
       </c>
       <c r="B260" s="17" t="inlineStr">
         <is>
-          <t>WIS @ ND</t>
+          <t>TLSA @ SHSU</t>
         </is>
       </c>
       <c r="C260" s="17" t="inlineStr">
         <is>
-          <t>2026-09-06 23:30</t>
+          <t>2026-09-12 23:00</t>
         </is>
       </c>
       <c r="D260" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E260" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F260" s="17" t="inlineStr">
         <is>
-          <t>ND -20.5</t>
-        </is>
-      </c>
-      <c r="G260" s="26" t="n">
-        <v>-20.5</v>
-      </c>
+          <t>TLSA ML</t>
+        </is>
+      </c>
+      <c r="G260" s="26" t="n"/>
       <c r="H260" s="18" t="n">
-        <v>-115</v>
+        <v>-425</v>
       </c>
       <c r="I260" s="20" t="n">
-        <v>0.2801972900138555</v>
+        <v>0.5543580019223056</v>
       </c>
       <c r="J260" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.7768331562167907</v>
       </c>
       <c r="K260" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="L260" s="19" t="n">
-        <v>-0.254686430916377</v>
+        <v>-0.255165807601504</v>
       </c>
       <c r="M260" s="19" t="n">
-        <v>-0.4761528925827919</v>
+        <v>-0.315204821154799</v>
       </c>
       <c r="N260" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O260" s="27" t="n">
-        <v>0.4</v>
+        <v>0.725</v>
       </c>
       <c r="P260" s="17" t="inlineStr">
         <is>
@@ -17902,7 +17900,7 @@
       </c>
       <c r="Q260" s="17" t="inlineStr">
         <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
+          <t>price outside allowed range</t>
         </is>
       </c>
     </row>
@@ -17914,12 +17912,12 @@
       </c>
       <c r="B261" s="12" t="inlineStr">
         <is>
-          <t>TLSA @ SHSU</t>
+          <t>UL @ USC</t>
         </is>
       </c>
       <c r="C261" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12 23:00</t>
+          <t>2026-09-13 03:00</t>
         </is>
       </c>
       <c r="D261" s="22" t="n">
@@ -17927,32 +17925,34 @@
       </c>
       <c r="E261" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F261" s="12" t="inlineStr">
         <is>
-          <t>TLSA ML</t>
-        </is>
-      </c>
-      <c r="G261" s="23" t="n"/>
+          <t>USC -28.5</t>
+        </is>
+      </c>
+      <c r="G261" s="23" t="n">
+        <v>-28.5</v>
+      </c>
       <c r="H261" s="13" t="n">
-        <v>-425</v>
+        <v>-110</v>
       </c>
       <c r="I261" s="15" t="n">
-        <v>0.5543580019223056</v>
+        <v>0.2658775966723402</v>
       </c>
       <c r="J261" s="15" t="n">
-        <v>0.7768331562167907</v>
+        <v>0.5</v>
       </c>
       <c r="K261" s="15" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L261" s="14" t="n">
-        <v>-0.255165807601504</v>
+        <v>-0.2579319271371837</v>
       </c>
       <c r="M261" s="14" t="n">
-        <v>-0.315204821154799</v>
+        <v>-0.492415497261896</v>
       </c>
       <c r="N261" s="15" t="n">
         <v>0</v>
@@ -17967,7 +17967,7 @@
       </c>
       <c r="Q261" s="12" t="inlineStr">
         <is>
-          <t>price outside allowed range</t>
+          <t>raw model/market disagreement exceeds the safety limit</t>
         </is>
       </c>
     </row>
@@ -17979,16 +17979,16 @@
       </c>
       <c r="B262" s="17" t="inlineStr">
         <is>
-          <t>UL @ USC</t>
+          <t>WIS @ ND</t>
         </is>
       </c>
       <c r="C262" s="17" t="inlineStr">
         <is>
-          <t>2026-09-13 03:00</t>
+          <t>2026-09-06 23:30</t>
         </is>
       </c>
       <c r="D262" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E262" s="17" t="inlineStr">
         <is>
@@ -17997,35 +17997,35 @@
       </c>
       <c r="F262" s="17" t="inlineStr">
         <is>
-          <t>USC -28.5</t>
+          <t>ND -21</t>
         </is>
       </c>
       <c r="G262" s="26" t="n">
-        <v>-28.5</v>
+        <v>-21</v>
       </c>
       <c r="H262" s="18" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="I262" s="20" t="n">
-        <v>0.2658775966723402</v>
+        <v>0.2756446732989797</v>
       </c>
       <c r="J262" s="20" t="n">
-        <v>0.5</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K262" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L262" s="19" t="n">
-        <v>-0.2579319271371837</v>
+        <v>-0.2592390476312528</v>
       </c>
       <c r="M262" s="19" t="n">
-        <v>-0.492415497261896</v>
+        <v>-0.4800652702801479</v>
       </c>
       <c r="N262" s="20" t="n">
-        <v>0</v>
+        <v>0.0095</v>
       </c>
       <c r="O262" s="27" t="n">
-        <v>0.725</v>
+        <v>0.4</v>
       </c>
       <c r="P262" s="17" t="inlineStr">
         <is>
@@ -19428,24 +19428,24 @@
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>EMU @ MSU</t>
+          <t>CAL @ SYR</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>EMU ML</t>
+          <t>SYR +1.5</t>
         </is>
       </c>
       <c r="E18" s="13" t="n">
-        <v>550</v>
+        <v>-108</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -19466,17 +19466,17 @@
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>LEAN</t>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="L18" s="14" t="n">
-        <v>0.1106</v>
+        <v>0.0987</v>
       </c>
       <c r="M18" s="14" t="n"/>
       <c r="N18" s="12" t="n"/>
       <c r="O18" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>
@@ -19488,24 +19488,24 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>CAL @ SYR</t>
+          <t>EMU @ MSU</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D19" s="17" t="inlineStr">
         <is>
-          <t>SYR +1.5</t>
+          <t>EMU ML</t>
         </is>
       </c>
       <c r="E19" s="18" t="n">
-        <v>-108</v>
+        <v>550</v>
       </c>
       <c r="F19" s="21" t="n">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="G19" s="17" t="inlineStr">
         <is>
@@ -19526,17 +19526,17 @@
       </c>
       <c r="K19" s="17" t="inlineStr">
         <is>
-          <t>GOOD</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="L19" s="19" t="n">
-        <v>0.0987</v>
+        <v>0.1106</v>
       </c>
       <c r="M19" s="19" t="n"/>
       <c r="N19" s="17" t="n"/>
       <c r="O19" s="17" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
     </row>
@@ -19553,19 +19553,19 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
+          <t>MICH ML</t>
         </is>
       </c>
       <c r="E20" s="13" t="n">
-        <v>-105</v>
+        <v>170</v>
       </c>
       <c r="F20" s="16" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -19586,17 +19586,17 @@
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
-          <t>LEAN</t>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="L20" s="14" t="n">
-        <v>0.0851</v>
+        <v>0.1101</v>
       </c>
       <c r="M20" s="14" t="n"/>
       <c r="N20" s="12" t="n"/>
       <c r="O20" s="12" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>
@@ -19608,24 +19608,24 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>ASU @ TA&amp;M</t>
+          <t>OU @ MICH</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
-          <t>ASU +14.5</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="E21" s="18" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F21" s="21" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G21" s="17" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         </is>
       </c>
       <c r="L21" s="19" t="n">
-        <v>0.1221</v>
+        <v>0.0851</v>
       </c>
       <c r="M21" s="19" t="n"/>
       <c r="N21" s="17" t="n"/>
@@ -19673,19 +19673,19 @@
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>ASU ML</t>
+          <t>ASU +14.5</t>
         </is>
       </c>
       <c r="E22" s="13" t="n">
-        <v>410</v>
+        <v>-110</v>
       </c>
       <c r="F22" s="16" t="n">
-        <v>16.5</v>
+        <v>26</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -19710,13 +19710,13 @@
         </is>
       </c>
       <c r="L22" s="14" t="n">
-        <v>0.1061</v>
+        <v>0.1221</v>
       </c>
       <c r="M22" s="14" t="n"/>
       <c r="N22" s="12" t="n"/>
       <c r="O22" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
     </row>
@@ -19733,19 +19733,19 @@
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D23" s="17" t="inlineStr">
         <is>
-          <t>Over 50.5</t>
+          <t>ASU ML</t>
         </is>
       </c>
       <c r="E23" s="18" t="n">
-        <v>-112</v>
+        <v>410</v>
       </c>
       <c r="F23" s="21" t="n">
-        <v>25</v>
+        <v>16.5</v>
       </c>
       <c r="G23" s="17" t="inlineStr">
         <is>
@@ -19770,13 +19770,13 @@
         </is>
       </c>
       <c r="L23" s="19" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.1061</v>
       </c>
       <c r="M23" s="19" t="n"/>
       <c r="N23" s="17" t="n"/>
       <c r="O23" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>
@@ -19788,7 +19788,7 @@
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>ORE @ OKST</t>
+          <t>ASU @ TA&amp;M</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
@@ -19798,14 +19798,14 @@
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>Under 60.5</t>
+          <t>Over 50.5</t>
         </is>
       </c>
       <c r="E24" s="13" t="n">
         <v>-112</v>
       </c>
       <c r="F24" s="16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -19830,7 +19830,7 @@
         </is>
       </c>
       <c r="L24" s="14" t="n">
-        <v>0.1106</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="M24" s="14" t="n"/>
       <c r="N24" s="12" t="n"/>
@@ -19848,24 +19848,24 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>ODU @ VT</t>
+          <t>ORE @ OKST</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D25" s="17" t="inlineStr">
         <is>
-          <t>ODU ML</t>
+          <t>Under 60.5</t>
         </is>
       </c>
       <c r="E25" s="18" t="n">
-        <v>455</v>
+        <v>-112</v>
       </c>
       <c r="F25" s="21" t="n">
-        <v>15.5</v>
+        <v>26</v>
       </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         </is>
       </c>
       <c r="L25" s="19" t="n">
-        <v>0.1006</v>
+        <v>0.1106</v>
       </c>
       <c r="M25" s="19" t="n"/>
       <c r="N25" s="17" t="n"/>
@@ -19908,24 +19908,24 @@
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>WAKE @ PUR</t>
+          <t>ODU @ VT</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>PUR +3.5</t>
+          <t>ODU ML</t>
         </is>
       </c>
       <c r="E26" s="13" t="n">
-        <v>-115</v>
+        <v>455</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>26</v>
+        <v>15.5</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -19946,11 +19946,11 @@
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
-          <t>GOOD</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="L26" s="14" t="n">
-        <v>0.0922</v>
+        <v>0.1006</v>
       </c>
       <c r="M26" s="14" t="n"/>
       <c r="N26" s="12" t="n"/>
@@ -19973,19 +19973,19 @@
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D27" s="17" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
+          <t>PUR +3.5</t>
         </is>
       </c>
       <c r="E27" s="18" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F27" s="21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G27" s="17" t="inlineStr">
         <is>
@@ -20006,11 +20006,11 @@
       </c>
       <c r="K27" s="17" t="inlineStr">
         <is>
-          <t>LEAN</t>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="L27" s="19" t="n">
-        <v>0.1129</v>
+        <v>0.0922</v>
       </c>
       <c r="M27" s="19" t="n"/>
       <c r="N27" s="17" t="n"/>
@@ -20028,7 +20028,7 @@
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>PSU @ TEM</t>
+          <t>WAKE @ PUR</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
@@ -20038,11 +20038,11 @@
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>Over 49.5</t>
         </is>
       </c>
       <c r="E28" s="13" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="F28" s="16" t="n">
         <v>25</v>
@@ -20070,13 +20070,13 @@
         </is>
       </c>
       <c r="L28" s="14" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1129</v>
       </c>
       <c r="M28" s="14" t="n"/>
       <c r="N28" s="12" t="n"/>
       <c r="O28" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
     </row>
@@ -20088,24 +20088,24 @@
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>APP @ ECU</t>
+          <t>PSU @ TEM</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D29" s="17" t="inlineStr">
         <is>
-          <t>APP +10</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="E29" s="18" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F29" s="21" t="n">
-        <v>22.5</v>
+        <v>25</v>
       </c>
       <c r="G29" s="17" t="inlineStr">
         <is>
@@ -20126,17 +20126,17 @@
       </c>
       <c r="K29" s="17" t="inlineStr">
         <is>
-          <t>GOOD</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="L29" s="19" t="n">
-        <v>0.0818</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="M29" s="19" t="n"/>
       <c r="N29" s="17" t="n"/>
       <c r="O29" s="17" t="inlineStr">
         <is>
-          <t>Draft Kings</t>
+          <t>DraftKings</t>
         </is>
       </c>
     </row>
@@ -20148,24 +20148,24 @@
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>OU @ MICH</t>
+          <t>APP @ ECU</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>MICH ML</t>
+          <t>APP +10</t>
         </is>
       </c>
       <c r="E30" s="13" t="n">
-        <v>170</v>
+        <v>-110</v>
       </c>
       <c r="F30" s="16" t="n">
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -20190,13 +20190,13 @@
         </is>
       </c>
       <c r="L30" s="14" t="n">
-        <v>0.1101</v>
+        <v>0.0818</v>
       </c>
       <c r="M30" s="14" t="n"/>
       <c r="N30" s="12" t="n"/>
       <c r="O30" s="12" t="inlineStr">
         <is>
-          <t>DraftKings</t>
+          <t>Draft Kings</t>
         </is>
       </c>
     </row>
@@ -31664,10 +31664,10 @@
         <v>54.5</v>
       </c>
       <c r="K101" s="13" t="n">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="L101" s="13" t="n">
-        <v>-258</v>
+        <v>-250</v>
       </c>
       <c r="M101" s="12" t="inlineStr">
         <is>
@@ -31711,7 +31711,7 @@
         </is>
       </c>
       <c r="I102" s="26" t="n">
-        <v>-20.5</v>
+        <v>-21</v>
       </c>
       <c r="J102" s="30" t="n">
         <v>46.5</v>
@@ -32055,16 +32055,16 @@
       </c>
       <c r="H110" s="17" t="inlineStr"/>
       <c r="I110" s="26" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="J110" s="30" t="n">
-        <v>44.5</v>
+        <v>45.5</v>
       </c>
       <c r="K110" s="18" t="n">
-        <v>-205</v>
+        <v>-218</v>
       </c>
       <c r="L110" s="18" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="M110" s="17" t="inlineStr">
         <is>
